--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -274,15 +274,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -291,7 +291,7 @@
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -702,7 +702,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 08/09/2026 09:54:12 (09:54) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 08/09/2026 10:52:58 (10:52) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -795,25 +795,25 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10053130</t>
+          <t>10046653</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>OZIVY 1MG 1CAN 3ML EMS</t>
+          <t>MOUNJARO 5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>999</v>
+        <v>11801.58</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4571.32</v>
+        <v>26228.82</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-3572.32</v>
+        <v>-14427.24</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-0.7809999999999999</v>
+        <v>-0.55</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>155</v>
@@ -837,7 +837,7 @@
       </c>
       <c r="P5" s="13" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
     </row>
@@ -847,59 +847,49 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10046652</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>899</v>
+        <v>8237.6</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>2055.01</v>
+        <v>17698.96</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-1156.01</v>
+        <v>-9461.360000000001</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.535</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K6" s="18" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="L6" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M6" s="18" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="23" t="inlineStr">
-        <is>
-          <t>Preço Alinhado</t>
-        </is>
-      </c>
-      <c r="P6" s="23" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
+      <c r="K6" s="23" t="inlineStr"/>
+      <c r="L6" s="24" t="inlineStr"/>
+      <c r="M6" s="23" t="inlineStr"/>
+      <c r="N6" s="25" t="inlineStr"/>
+      <c r="O6" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P6" s="24" t="inlineStr">
+        <is>
+          <t>Detrator Crítico</t>
         </is>
       </c>
     </row>
@@ -909,28 +899,28 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10041262</t>
+          <t>10046655</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
+          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>416.84</v>
+        <v>3998</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1225.93</v>
+        <v>10670.71</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-809.09</v>
+        <v>-6672.71</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.66</v>
+        <v>-0.625</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I7" s="11" t="n">
         <v>0.01</v>
@@ -951,7 +941,7 @@
       </c>
       <c r="P7" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
     </row>
@@ -961,49 +951,49 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10042969</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO XXG 112UN</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>0</v>
+        <v>2596.72</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>793.25</v>
+        <v>7482.46</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-793.25</v>
+        <v>-4885.74</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>-1</v>
+        <v>-0.653</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K8" s="25" t="inlineStr"/>
-      <c r="L8" s="23" t="inlineStr"/>
-      <c r="M8" s="25" t="inlineStr"/>
-      <c r="N8" s="26" t="inlineStr"/>
-      <c r="O8" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P8" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
+      <c r="K8" s="23" t="inlineStr"/>
+      <c r="L8" s="24" t="inlineStr"/>
+      <c r="M8" s="23" t="inlineStr"/>
+      <c r="N8" s="25" t="inlineStr"/>
+      <c r="O8" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P8" s="24" t="inlineStr">
+        <is>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1013,31 +1003,31 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10053130</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>OZIVY 1MG 1CAN 3ML EMS</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0</v>
+        <v>1998</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>415.4</v>
+        <v>6782.27</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-415.4</v>
+        <v>-4784.27</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-1</v>
+        <v>-0.705</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>9</v>
+        <v>286</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.01</v>
+        <v>0.25</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1055,7 +1045,7 @@
       </c>
       <c r="P9" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1065,49 +1055,49 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10042968</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
         </is>
       </c>
       <c r="D10" s="18" t="n">
-        <v>0</v>
+        <v>1520.92</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>414.85</v>
+        <v>4615.84</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-414.85</v>
+        <v>-3094.92</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-1</v>
+        <v>-0.67</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr"/>
-      <c r="L10" s="23" t="inlineStr"/>
-      <c r="M10" s="25" t="inlineStr"/>
-      <c r="N10" s="26" t="inlineStr"/>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
+      <c r="K10" s="23" t="inlineStr"/>
+      <c r="L10" s="24" t="inlineStr"/>
+      <c r="M10" s="23" t="inlineStr"/>
+      <c r="N10" s="25" t="inlineStr"/>
+      <c r="O10" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P10" s="24" t="inlineStr">
+        <is>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1117,31 +1107,31 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10042967</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO G 128UN</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>73.98999999999999</v>
+        <v>1227.61</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>480.27</v>
+        <v>3682.98</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-406.28</v>
+        <v>-2455.37</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.846</v>
+        <v>-0.667</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>726</v>
+        <v>97</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.63</v>
+        <v>0.08</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1159,7 +1149,7 @@
       </c>
       <c r="P11" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1169,59 +1159,49 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>74.22</v>
+        <v>0</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>452.46</v>
+        <v>2154.6</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-378.24</v>
+        <v>-2154.6</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>-0.836</v>
+        <v>-1</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>582</v>
+        <v>3</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>74.22</v>
-      </c>
-      <c r="L12" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M12" s="18" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N12" s="27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O12" s="23" t="inlineStr">
-        <is>
-          <t>São João Mais Cara</t>
-        </is>
-      </c>
-      <c r="P12" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr"/>
+      <c r="L12" s="24" t="inlineStr"/>
+      <c r="M12" s="23" t="inlineStr"/>
+      <c r="N12" s="25" t="inlineStr"/>
+      <c r="O12" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P12" s="24" t="inlineStr">
+        <is>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1231,59 +1211,59 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
+        <v>899</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>3048.93</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>-2149.93</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>-0.705</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>136</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="N13" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="7" t="n">
-        <v>339.25</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>-339.25</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N13" s="28" t="n">
-        <v>0.113</v>
-      </c>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1293,49 +1273,49 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>10052532</t>
+          <t>10050654</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
+          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>1103.21</v>
+        <v>2338</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>1429.94</v>
+        <v>3930.14</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-326.73</v>
+        <v>-1592.14</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>-0.228</v>
+        <v>-0.405</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>825</v>
+        <v>27</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>0.72</v>
+        <v>0.02</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K14" s="25" t="inlineStr"/>
-      <c r="L14" s="23" t="inlineStr"/>
-      <c r="M14" s="25" t="inlineStr"/>
-      <c r="N14" s="26" t="inlineStr"/>
-      <c r="O14" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
+      <c r="K14" s="23" t="inlineStr"/>
+      <c r="L14" s="24" t="inlineStr"/>
+      <c r="M14" s="23" t="inlineStr"/>
+      <c r="N14" s="25" t="inlineStr"/>
+      <c r="O14" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P14" s="24" t="inlineStr">
+        <is>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1345,31 +1325,31 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>268.48</v>
+        <v>1508.65</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-268.48</v>
+        <v>-1508.65</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1387,7 +1367,7 @@
       </c>
       <c r="P15" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1397,59 +1377,49 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>10049738</t>
+          <t>10041262</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>OLIRE 6MG/ML 3ML 3APLIC INJ EMS</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>0</v>
+        <v>628.64</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>236.11</v>
+        <v>1818.86</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-236.11</v>
+        <v>-1190.22</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>-1</v>
+        <v>-0.654</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K16" s="18" t="n">
-        <v>866.24</v>
-      </c>
-      <c r="L16" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M16" s="18" t="n">
-        <v>866.24</v>
-      </c>
-      <c r="N16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="23" t="inlineStr">
-        <is>
-          <t>Preço Alinhado</t>
-        </is>
-      </c>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
+      <c r="K16" s="23" t="inlineStr"/>
+      <c r="L16" s="24" t="inlineStr"/>
+      <c r="M16" s="23" t="inlineStr"/>
+      <c r="N16" s="25" t="inlineStr"/>
+      <c r="O16" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P16" s="24" t="inlineStr">
+        <is>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1459,59 +1429,49 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10033757</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XXG 54UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>169.8</v>
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>359.35</v>
+        <v>1176.91</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-189.55</v>
+        <v>-1176.91</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-0.527</v>
+        <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>309</v>
+        <v>605</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="N17" s="28" t="n">
-        <v>0.165</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="13" t="inlineStr"/>
+      <c r="M17" s="12" t="inlineStr"/>
+      <c r="N17" s="14" t="inlineStr"/>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P17" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1521,57 +1481,47 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>100013179</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>UTROGESTAN 200MG 42CAP BESINS</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>188.89</v>
+        <v>816.53</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-188.89</v>
+        <v>-816.53</v>
       </c>
       <c r="G18" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>246.91</v>
-      </c>
-      <c r="L18" s="23" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M18" s="18" t="n">
-        <v>209.07</v>
-      </c>
-      <c r="N18" s="27" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="O18" s="23" t="inlineStr">
-        <is>
-          <t>São João Mais Cara</t>
-        </is>
-      </c>
-      <c r="P18" s="23" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr"/>
+      <c r="L18" s="24" t="inlineStr"/>
+      <c r="M18" s="23" t="inlineStr"/>
+      <c r="N18" s="25" t="inlineStr"/>
+      <c r="O18" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P18" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -1583,54 +1533,44 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10105170</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>TOALHAS UMED NATURAL BABY LV100 PG80</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>212.99</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>394.78</v>
+        <v>842.66</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-181.79</v>
+        <v>-746.76</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-0.46</v>
+        <v>-0.8859999999999999</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>4975</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>4.34</v>
+        <v>6</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>0.01</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="L19" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N19" s="28" t="n">
-        <v>0.375</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr"/>
+      <c r="L19" s="13" t="inlineStr"/>
+      <c r="M19" s="12" t="inlineStr"/>
+      <c r="N19" s="14" t="inlineStr"/>
       <c r="O19" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P19" s="13" t="inlineStr">
@@ -1645,31 +1585,31 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>SYSTEN CONTI 8 ADESIVOS THERAMEX</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>179.92</v>
+        <v>720.55</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-179.92</v>
+        <v>-720.55</v>
       </c>
       <c r="G20" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -1677,25 +1617,25 @@
         </is>
       </c>
       <c r="K20" s="18" t="n">
-        <v>170.87</v>
-      </c>
-      <c r="L20" s="23" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M20" s="18" t="n">
-        <v>125.98</v>
+        <v>58.99</v>
       </c>
       <c r="N20" s="27" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="O20" s="23" t="inlineStr">
+        <v>0.61</v>
+      </c>
+      <c r="O20" s="24" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P20" s="23" t="inlineStr">
+      <c r="P20" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -1707,40 +1647,38 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10041842</t>
+          <t>10042966</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>TOALHAS UMED PURO AMOR PAC 500TOALHAS PREMIUM</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>174.97</v>
+        <v>467.13</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>348.15</v>
+        <v>1115.96</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-173.18</v>
+        <v>-648.83</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-0.4970000000000001</v>
+        <v>-0.581</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>0.29</v>
+        <v>0.02</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K21" s="7" t="n">
-        <v>59.99</v>
-      </c>
+      <c r="K21" s="12" t="inlineStr"/>
       <c r="L21" s="13" t="inlineStr"/>
       <c r="M21" s="12" t="inlineStr"/>
       <c r="N21" s="14" t="inlineStr"/>
@@ -1761,57 +1699,47 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10047543</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>DULOXETINA 60MG 60CAP GEN EMS (C1)</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>0</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>171.54</v>
+        <v>712.5599999999999</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-171.54</v>
+        <v>-638.5700000000001</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>-1</v>
+        <v>-0.8959999999999999</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>120</v>
+        <v>964</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>0.1</v>
+        <v>0.84</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>162.69</v>
-      </c>
-      <c r="L22" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M22" s="18" t="n">
-        <v>154.99</v>
-      </c>
-      <c r="N22" s="27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O22" s="23" t="inlineStr">
-        <is>
-          <t>São João Mais Cara</t>
-        </is>
-      </c>
-      <c r="P22" s="23" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr"/>
+      <c r="L22" s="24" t="inlineStr"/>
+      <c r="M22" s="23" t="inlineStr"/>
+      <c r="N22" s="25" t="inlineStr"/>
+      <c r="O22" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P22" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -1823,31 +1751,31 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>463.6</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>631.95</v>
+        <v>616.3</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-168.35</v>
+        <v>-616.3</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.266</v>
+        <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>540</v>
+        <v>6</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>0.47</v>
+        <v>0.01</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1875,53 +1803,47 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10039205</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>SERUM CORP DOVE 380ML NIACINAMIDA</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>167.9</v>
+        <v>615.49</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-167.9</v>
+        <v>-615.49</v>
       </c>
       <c r="G24" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>120</v>
+        <v>252</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K24" s="25" t="inlineStr"/>
-      <c r="L24" s="23" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="n">
-        <v>29.89</v>
-      </c>
-      <c r="N24" s="26" t="inlineStr"/>
-      <c r="O24" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P24" s="23" t="inlineStr">
+      <c r="K24" s="23" t="inlineStr"/>
+      <c r="L24" s="24" t="inlineStr"/>
+      <c r="M24" s="23" t="inlineStr"/>
+      <c r="N24" s="25" t="inlineStr"/>
+      <c r="O24" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P24" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -1933,44 +1855,54 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>73.98999999999999</v>
+        <v>74.22</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>241.35</v>
+        <v>671.29</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-167.36</v>
+        <v>-597.0700000000001</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.889</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>457</v>
+        <v>700</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>0.4</v>
+        <v>0.61</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K25" s="12" t="inlineStr"/>
-      <c r="L25" s="13" t="inlineStr"/>
-      <c r="M25" s="12" t="inlineStr"/>
-      <c r="N25" s="14" t="inlineStr"/>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.333</v>
+      </c>
       <c r="O25" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P25" s="13" t="inlineStr">
@@ -1985,47 +1917,57 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10051318</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>DAPAGLIFLOZINA 10MG 30CP GEN EMS</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>87.98999999999999</v>
+        <v>149.4</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>240.86</v>
+        <v>717.02</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-152.87</v>
+        <v>-567.62</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>-0.635</v>
+        <v>-0.792</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>5067</v>
-      </c>
-      <c r="I26" s="30" t="n">
-        <v>4.42</v>
+        <v>60</v>
+      </c>
+      <c r="I26" s="22" t="n">
+        <v>0.05</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K26" s="25" t="inlineStr"/>
-      <c r="L26" s="23" t="inlineStr"/>
-      <c r="M26" s="25" t="inlineStr"/>
-      <c r="N26" s="26" t="inlineStr"/>
-      <c r="O26" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P26" s="23" t="inlineStr">
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L26" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M26" s="18" t="n">
+        <v>107</v>
+      </c>
+      <c r="N26" s="27" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="O26" s="24" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P26" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2037,31 +1979,31 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10099263</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>VENLAFAXINA 150MG 30CAP GEN EMS (C1)</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>146.86</v>
+        <v>564.64</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-146.86</v>
+        <v>-564.64</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2089,47 +2031,47 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10021286</t>
+          <t>10052532</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>TRELEGY 100+62,5+25MG 30DOSES GSK</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>0</v>
+        <v>1557.83</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>146.68</v>
+        <v>2121.53</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-146.68</v>
+        <v>-563.7</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>-1</v>
+        <v>-0.266</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>12</v>
+        <v>1220</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>0.01</v>
+        <v>1.06</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K28" s="25" t="inlineStr"/>
-      <c r="L28" s="23" t="inlineStr"/>
-      <c r="M28" s="25" t="inlineStr"/>
-      <c r="N28" s="26" t="inlineStr"/>
-      <c r="O28" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P28" s="23" t="inlineStr">
+      <c r="K28" s="23" t="inlineStr"/>
+      <c r="L28" s="24" t="inlineStr"/>
+      <c r="M28" s="23" t="inlineStr"/>
+      <c r="N28" s="25" t="inlineStr"/>
+      <c r="O28" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P28" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2141,54 +2083,44 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10098096</t>
+          <t>10028895</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>FR BIGFRAL DERMA PLUS ADULTO NOTURNA G 7UN</t>
+          <t>IZIZ 2,5MG+1,5MG 84CP LIBBS</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>140.83</v>
+        <v>514.0599999999999</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-140.83</v>
+        <v>-514.0599999999999</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>30.99</v>
-      </c>
-      <c r="L29" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="N29" s="28" t="n">
-        <v>0.245</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K29" s="12" t="inlineStr"/>
+      <c r="L29" s="13" t="inlineStr"/>
+      <c r="M29" s="12" t="inlineStr"/>
+      <c r="N29" s="14" t="inlineStr"/>
       <c r="O29" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P29" s="13" t="inlineStr">
@@ -2203,47 +2135,47 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10028705</t>
+          <t>10004419</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG G 60UN</t>
+          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
+        <v>999</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>1508.11</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>-509.11</v>
+      </c>
+      <c r="G30" s="20" t="n">
+        <v>-0.338</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="18" t="n">
-        <v>140.42</v>
-      </c>
-      <c r="F30" s="19" t="n">
-        <v>-140.42</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H30" s="21" t="n">
-        <v>359</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>0.31</v>
-      </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K30" s="25" t="inlineStr"/>
-      <c r="L30" s="23" t="inlineStr"/>
-      <c r="M30" s="25" t="inlineStr"/>
-      <c r="N30" s="26" t="inlineStr"/>
-      <c r="O30" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P30" s="23" t="inlineStr">
+      <c r="K30" s="23" t="inlineStr"/>
+      <c r="L30" s="24" t="inlineStr"/>
+      <c r="M30" s="23" t="inlineStr"/>
+      <c r="N30" s="25" t="inlineStr"/>
+      <c r="O30" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P30" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2255,31 +2187,31 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>10050634</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>EXTENSIOR 1MG 3ML NOVO EUROFARMA</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>119.6</v>
+        <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>259.07</v>
+        <v>504.32</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-139.47</v>
+        <v>-504.32</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-0.5379999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>0.22</v>
+        <v>0.04</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -2307,57 +2239,47 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10043691</t>
+          <t>10050642</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>BUP XL 150MG 60CP REV PROL 24H EUROFARMA (C1)</t>
+          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>135.21</v>
+        <v>1087.36</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-135.21</v>
+        <v>-497.36</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>-1</v>
+        <v>-0.457</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K32" s="18" t="n">
-        <v>182.2</v>
-      </c>
-      <c r="L32" s="23" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M32" s="18" t="n">
-        <v>152</v>
-      </c>
-      <c r="N32" s="27" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="O32" s="23" t="inlineStr">
-        <is>
-          <t>São João Mais Cara</t>
-        </is>
-      </c>
-      <c r="P32" s="23" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr"/>
+      <c r="L32" s="24" t="inlineStr"/>
+      <c r="M32" s="23" t="inlineStr"/>
+      <c r="N32" s="25" t="inlineStr"/>
+      <c r="O32" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P32" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2369,31 +2291,31 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10033463</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>480.66</v>
+        <v>463.6</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>611.5700000000001</v>
+        <v>937.6</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-130.91</v>
+        <v>-474</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.214</v>
+        <v>-0.506</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>370</v>
+        <v>742</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2421,47 +2343,47 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>1006900</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>NISTATINA+OXID ZINCO 60G GEN EMS</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>21.99</v>
+        <v>0</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>143.2</v>
+        <v>467.78</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-121.21</v>
+        <v>-467.78</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>-0.846</v>
+        <v>-1</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>1361</v>
+        <v>0</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K34" s="25" t="inlineStr"/>
-      <c r="L34" s="23" t="inlineStr"/>
-      <c r="M34" s="25" t="inlineStr"/>
-      <c r="N34" s="26" t="inlineStr"/>
-      <c r="O34" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P34" s="23" t="inlineStr">
+      <c r="K34" s="23" t="inlineStr"/>
+      <c r="L34" s="24" t="inlineStr"/>
+      <c r="M34" s="23" t="inlineStr"/>
+      <c r="N34" s="25" t="inlineStr"/>
+      <c r="O34" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P34" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2473,31 +2395,31 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10033462</t>
+          <t>10053171</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER M 68UN</t>
+          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>117.38</v>
+        <v>451.12</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-117.38</v>
+        <v>-451.12</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2525,47 +2447,47 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>1008501</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>KALOBA 20ML GOTAS HERBARIUM</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
-        <v>0</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>116.32</v>
+        <v>529.6799999999999</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-116.32</v>
+        <v>-444.78</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>-1</v>
+        <v>-0.84</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>39</v>
+        <v>286</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K36" s="25" t="inlineStr"/>
-      <c r="L36" s="23" t="inlineStr"/>
-      <c r="M36" s="25" t="inlineStr"/>
-      <c r="N36" s="26" t="inlineStr"/>
-      <c r="O36" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P36" s="23" t="inlineStr">
+      <c r="K36" s="23" t="inlineStr"/>
+      <c r="L36" s="24" t="inlineStr"/>
+      <c r="M36" s="23" t="inlineStr"/>
+      <c r="N36" s="25" t="inlineStr"/>
+      <c r="O36" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P36" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2577,31 +2499,31 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10049083</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350ML+COND 175ML RECONSTRUCAO+AMINOACIDOS</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>59.8</v>
+        <v>590</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>174.08</v>
+        <v>1007.38</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-114.28</v>
+        <v>-417.38</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.6559999999999999</v>
+        <v>-0.414</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2629,49 +2551,47 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>10046212</t>
+          <t>10030120</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>PAPEL HIG FLORAX PREMIUM FOLHA DUPLA 20M</t>
+          <t>RYBELSUS 7MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
-        <v>83.93000000000001</v>
+        <v>0</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>196.55</v>
+        <v>413.38</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-112.62</v>
+        <v>-413.38</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>-0.573</v>
+        <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>25982</v>
-      </c>
-      <c r="I38" s="30" t="n">
-        <v>22.65</v>
+        <v>8</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>0.01</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K38" s="18" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="L38" s="23" t="inlineStr"/>
-      <c r="M38" s="25" t="inlineStr"/>
-      <c r="N38" s="26" t="inlineStr"/>
-      <c r="O38" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P38" s="23" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr"/>
+      <c r="L38" s="24" t="inlineStr"/>
+      <c r="M38" s="23" t="inlineStr"/>
+      <c r="N38" s="25" t="inlineStr"/>
+      <c r="O38" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P38" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2683,31 +2603,31 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10030229</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>DR GOOD FINI MELATONINA 60GOMAS</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>107.93</v>
+        <v>398.34</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-107.93</v>
+        <v>-398.34</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2735,53 +2655,57 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>HASTES J&amp;J 75UN COTONETES</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>18.18</v>
+        <v>135.98</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>125.05</v>
+        <v>503.32</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-106.87</v>
+        <v>-367.34</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>-0.855</v>
+        <v>-0.73</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>160</v>
+        <v>279</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K40" s="25" t="inlineStr"/>
-      <c r="L40" s="23" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K40" s="18" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="L40" s="24" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M40" s="18" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="N40" s="26" t="inlineStr"/>
-      <c r="O40" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P40" s="23" t="inlineStr">
+        <v>61.06</v>
+      </c>
+      <c r="N40" s="27" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="O40" s="24" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P40" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2793,44 +2717,54 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>100012568</t>
+          <t>10033757</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>DUTASTERIDA 0,5MG 30CAP GEN BIOSINTETICA</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XXG 54UN</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0</v>
+        <v>169.8</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>105.26</v>
+        <v>533.15</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-105.26</v>
+        <v>-363.35</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-1</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>16</v>
+        <v>543</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>0.01</v>
+        <v>0.47</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K41" s="12" t="inlineStr"/>
-      <c r="L41" s="13" t="inlineStr"/>
-      <c r="M41" s="12" t="inlineStr"/>
-      <c r="N41" s="14" t="inlineStr"/>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="L41" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <v>0.165</v>
+      </c>
       <c r="O41" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P41" s="13" t="inlineStr">
@@ -2845,57 +2779,47 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10007354</t>
+          <t>10033463</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>ITRACONAZOL 100MG 15CAP GEN GEOLAB</t>
+          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>49.9</v>
+        <v>550.5599999999999</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>154.92</v>
+        <v>907.35</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-105.02</v>
+        <v>-356.79</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>-0.6779999999999999</v>
+        <v>-0.393</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>15</v>
+        <v>461</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K42" s="18" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="L42" s="23" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M42" s="18" t="n">
-        <v>75.98999999999999</v>
-      </c>
-      <c r="N42" s="24" t="n">
-        <v>-0.343</v>
-      </c>
-      <c r="O42" s="23" t="inlineStr">
-        <is>
-          <t>Líder de Preço</t>
-        </is>
-      </c>
-      <c r="P42" s="23" t="inlineStr">
+      <c r="K42" s="23" t="inlineStr"/>
+      <c r="L42" s="24" t="inlineStr"/>
+      <c r="M42" s="23" t="inlineStr"/>
+      <c r="N42" s="25" t="inlineStr"/>
+      <c r="O42" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P42" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2907,44 +2831,54 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>100022388</t>
+          <t>10097311</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>ENTRESTO 100MG 60CP REV NOVARTIS</t>
+          <t>NESTOGENO 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0</v>
+        <v>203.97</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>101.17</v>
+        <v>557.35</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-101.17</v>
+        <v>-353.38</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-1</v>
+        <v>-0.634</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>0.02</v>
+        <v>0.23</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K43" s="12" t="inlineStr"/>
-      <c r="L43" s="13" t="inlineStr"/>
-      <c r="M43" s="12" t="inlineStr"/>
-      <c r="N43" s="14" t="inlineStr"/>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="L43" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <v>0.081</v>
+      </c>
       <c r="O43" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P43" s="13" t="inlineStr">
@@ -2959,47 +2893,57 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>10033760</t>
+          <t>10049738</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER G 58UN</t>
+          <t>OLIRE 6MG/ML 3ML 3APLIC INJ EMS</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>100.9</v>
+        <v>350.3</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-100.9</v>
+        <v>-350.3</v>
       </c>
       <c r="G44" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K44" s="25" t="inlineStr"/>
-      <c r="L44" s="23" t="inlineStr"/>
-      <c r="M44" s="25" t="inlineStr"/>
-      <c r="N44" s="26" t="inlineStr"/>
-      <c r="O44" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P44" s="23" t="inlineStr">
+      <c r="K44" s="18" t="n">
+        <v>866.24</v>
+      </c>
+      <c r="L44" s="24" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M44" s="18" t="n">
+        <v>866.24</v>
+      </c>
+      <c r="N44" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="24" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P44" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -3011,31 +2955,31 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10021280</t>
+          <t>100011549</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>TRIMBOW 120DOSES SPRAY CHIESI</t>
+          <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0</v>
+        <v>132.49</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>100.7</v>
+        <v>482.35</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-100.7</v>
+        <v>-349.86</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-1</v>
+        <v>-0.725</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -3063,31 +3007,31 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10107350</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>PRIMOGYNA 2MG 28DRG GENOM</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>95.04000000000001</v>
+        <v>327.46</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-95.04000000000001</v>
+        <v>-327.46</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>23</v>
+        <v>420</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
@@ -3095,25 +3039,25 @@
         </is>
       </c>
       <c r="K46" s="18" t="n">
-        <v>117.25</v>
-      </c>
-      <c r="L46" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
+        <v>25.9</v>
+      </c>
+      <c r="L46" s="24" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M46" s="18" t="n">
-        <v>92.58</v>
+        <v>15.9</v>
       </c>
       <c r="N46" s="27" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="O46" s="23" t="inlineStr">
+        <v>0.629</v>
+      </c>
+      <c r="O46" s="24" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P46" s="23" t="inlineStr">
+      <c r="P46" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -3125,31 +3069,31 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10037546</t>
+          <t>10052539</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>ROUPA INT SAO JOAO ADULTO PANTS G/XG 16UN</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0</v>
+        <v>377.7</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>91.31999999999999</v>
+        <v>701.91</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-91.31999999999999</v>
+        <v>-324.21</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-1</v>
+        <v>-0.462</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>686</v>
+        <v>40</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>0.6</v>
+        <v>0.03</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3177,47 +3121,47 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>100011177</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>SUMAXPRO 85MG+500MG 2CP REV LIBBS</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>0</v>
+        <v>203.67</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>90.05</v>
+        <v>514.46</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-90.05</v>
+        <v>-310.79</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>-1</v>
+        <v>-0.604</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K48" s="25" t="inlineStr"/>
-      <c r="L48" s="23" t="inlineStr"/>
-      <c r="M48" s="25" t="inlineStr"/>
-      <c r="N48" s="26" t="inlineStr"/>
-      <c r="O48" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P48" s="23" t="inlineStr">
+      <c r="K48" s="23" t="inlineStr"/>
+      <c r="L48" s="24" t="inlineStr"/>
+      <c r="M48" s="23" t="inlineStr"/>
+      <c r="N48" s="25" t="inlineStr"/>
+      <c r="O48" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P48" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -3229,54 +3173,44 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10005584</t>
+          <t>10029021</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>TANSULOSINA 0,4MG 30CP LIB PROL GEN EMS</t>
+          <t>PANT SEC 50MG/ML SOL CAPI 3FR 50ML+1VALVSPR ACHE</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>87.28</v>
+        <v>307.22</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-87.28</v>
+        <v>-307.22</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>75.89</v>
-      </c>
-      <c r="L49" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="n">
-        <v>65.89</v>
-      </c>
-      <c r="N49" s="28" t="n">
-        <v>0.152</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr"/>
+      <c r="L49" s="13" t="inlineStr"/>
+      <c r="M49" s="12" t="inlineStr"/>
+      <c r="N49" s="14" t="inlineStr"/>
       <c r="O49" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P49" s="13" t="inlineStr">
@@ -3291,47 +3225,57 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>100021381</t>
+          <t>10105170</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>DEXILANT 60MG 60CAP LIB RET TAKEDA</t>
+          <t>TOALHAS UMED NATURAL BABY LV100 PG80</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>0</v>
+        <v>282.29</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>86.45</v>
+        <v>585.71</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-86.45</v>
+        <v>-303.42</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>-1</v>
+        <v>-0.518</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="I50" s="22" t="n">
-        <v>0.08</v>
+        <v>8221</v>
+      </c>
+      <c r="I50" s="30" t="n">
+        <v>7.17</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K50" s="25" t="inlineStr"/>
-      <c r="L50" s="23" t="inlineStr"/>
-      <c r="M50" s="25" t="inlineStr"/>
-      <c r="N50" s="26" t="inlineStr"/>
-      <c r="O50" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P50" s="23" t="inlineStr">
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="L50" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M50" s="18" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N50" s="27" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="O50" s="24" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P50" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -3343,31 +3287,31 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>100001424</t>
+          <t>10034467</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>ESCITALOPRAM 10MG 60CP REV GEN EMS (C1)</t>
+          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>40.49</v>
+        <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>126.73</v>
+        <v>294.82</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-86.23999999999999</v>
+        <v>-294.82</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.6809999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>219</v>
+        <v>9</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>0.19</v>
+        <v>0.01</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -3395,47 +3339,47 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>10035173</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>ESC DENT COLGATE 4UN SLIMSOFT BLACK</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>26.49</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>111.46</v>
+        <v>358.09</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-84.97</v>
+        <v>-284.1</v>
       </c>
       <c r="G52" s="20" t="n">
-        <v>-0.762</v>
+        <v>-0.7929999999999999</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>125</v>
+        <v>501</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K52" s="25" t="inlineStr"/>
-      <c r="L52" s="23" t="inlineStr"/>
-      <c r="M52" s="25" t="inlineStr"/>
-      <c r="N52" s="26" t="inlineStr"/>
-      <c r="O52" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P52" s="23" t="inlineStr">
+      <c r="K52" s="23" t="inlineStr"/>
+      <c r="L52" s="24" t="inlineStr"/>
+      <c r="M52" s="23" t="inlineStr"/>
+      <c r="N52" s="25" t="inlineStr"/>
+      <c r="O52" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P52" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -3447,54 +3391,44 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>10041858</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>PROCTYL POM 30G 10APLIC TAKEDA</t>
+          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>81.29000000000001</v>
+        <v>282.01</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-81.29000000000001</v>
+        <v>-282.01</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>109.18</v>
-      </c>
-      <c r="L53" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
-        <v>80.95</v>
-      </c>
-      <c r="N53" s="28" t="n">
-        <v>0.349</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr"/>
+      <c r="L53" s="13" t="inlineStr"/>
+      <c r="M53" s="12" t="inlineStr"/>
+      <c r="N53" s="14" t="inlineStr"/>
       <c r="O53" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P53" s="13" t="inlineStr">
@@ -3509,47 +3443,47 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>100015009</t>
+          <t>10046473</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>SAB DOVE 90G LV+ PG- 6UN ORIGINAL</t>
+          <t>ROUPA INT SAO JOAO ADULTO PANTS G/XG 32UN</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>251.1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>330.88</v>
+        <v>281.85</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-79.78</v>
+        <v>-281.85</v>
       </c>
       <c r="G54" s="20" t="n">
-        <v>-0.241</v>
+        <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>12334</v>
-      </c>
-      <c r="I54" s="30" t="n">
-        <v>10.75</v>
+        <v>290</v>
+      </c>
+      <c r="I54" s="22" t="n">
+        <v>0.25</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K54" s="25" t="inlineStr"/>
-      <c r="L54" s="23" t="inlineStr"/>
-      <c r="M54" s="25" t="inlineStr"/>
-      <c r="N54" s="26" t="inlineStr"/>
-      <c r="O54" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P54" s="23" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K54" s="23" t="inlineStr"/>
+      <c r="L54" s="24" t="inlineStr"/>
+      <c r="M54" s="23" t="inlineStr"/>
+      <c r="N54" s="25" t="inlineStr"/>
+      <c r="O54" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P54" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -237,7 +237,7 @@
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -270,7 +270,7 @@
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,7 +282,10 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -291,10 +294,7 @@
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -702,7 +702,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 08/09/2026 10:52:58 (10:52) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 08/09/2026 12:53:08 (12:53) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -804,26 +804,26 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>11801.58</v>
+        <v>19389.87</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>26228.82</v>
+        <v>43874.73</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-14427.24</v>
+        <v>-24484.86</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-0.55</v>
+        <v>-0.5579999999999999</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>155</v>
+        <v>11783</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.14</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr"/>
@@ -847,35 +847,35 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>10046652</t>
+          <t>10042969</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO XXG 112UN</t>
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>8237.6</v>
+        <v>4012.69</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>17698.96</v>
+        <v>12516.41</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-9461.360000000001</v>
+        <v>-8503.719999999999</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>-0.535</v>
+        <v>-0.679</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>115</v>
+        <v>10635</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>0.1</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
@@ -908,26 +908,26 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3998</v>
+        <v>10695</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>10670.71</v>
+        <v>17849.62</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-6672.71</v>
+        <v>-7154.62</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.625</v>
+        <v>-0.401</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>10</v>
+        <v>3194</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.01</v>
+        <v>2.54</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr"/>
@@ -951,35 +951,35 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>10042969</t>
+          <t>10053130</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO XXG 112UN</t>
+          <t>OZIVY 1MG 1CAN 3ML EMS</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>2596.72</v>
+        <v>4925.62</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>7482.46</v>
+        <v>11345.16</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-4885.74</v>
+        <v>-6419.54</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>-0.653</v>
+        <v>-0.5660000000000001</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>339</v>
+        <v>12111</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>0.3</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="P8" s="24" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
     </row>
@@ -1003,35 +1003,35 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10053130</t>
+          <t>10046652</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>OZIVY 1MG 1CAN 3ML EMS</t>
+          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1998</v>
+        <v>24428.3</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6782.27</v>
+        <v>29606.25</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-4784.27</v>
+        <v>-5177.95</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.705</v>
+        <v>-0.175</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>286</v>
+        <v>9805</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.25</v>
+        <v>7.79</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr"/>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="P9" s="13" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
     </row>
@@ -1064,26 +1064,26 @@
         </is>
       </c>
       <c r="D10" s="18" t="n">
-        <v>1520.92</v>
+        <v>2720.52</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>4615.84</v>
+        <v>7721.22</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-3094.92</v>
+        <v>-5000.7</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-0.67</v>
+        <v>-0.648</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>55</v>
+        <v>2116</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>0.05</v>
+        <v>1.68</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="P10" s="24" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
     </row>
@@ -1116,26 +1116,26 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1227.61</v>
+        <v>1977.42</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3682.98</v>
+        <v>6160.78</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-2455.37</v>
+        <v>-4183.36</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.667</v>
+        <v>-0.679</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>97</v>
+        <v>7624</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.08</v>
+        <v>6.06</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr"/>
@@ -1159,31 +1159,31 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>2154.6</v>
+        <v>2523.62</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-2154.6</v>
+        <v>-2523.62</v>
       </c>
       <c r="G12" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>0</v>
+        <v>1770</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>1.41</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -1211,54 +1211,44 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>899</v>
+        <v>1398</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3048.93</v>
+        <v>3604.14</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-2149.93</v>
+        <v>-2206.14</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.705</v>
+        <v>-0.612</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>136</v>
+        <v>3359</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.12</v>
+        <v>2.67</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N13" s="26" t="n">
-        <v>0</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr"/>
+      <c r="L13" s="13" t="inlineStr"/>
+      <c r="M13" s="12" t="inlineStr"/>
+      <c r="N13" s="14" t="inlineStr"/>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr">
@@ -1273,35 +1263,35 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>10050654</t>
+          <t>10041262</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>2338</v>
+        <v>1047.81</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>3930.14</v>
+        <v>3042.52</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-1592.14</v>
+        <v>-1994.71</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>-0.405</v>
+        <v>-0.6559999999999999</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>27</v>
+        <v>2289</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>0.02</v>
+        <v>1.82</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
@@ -1325,35 +1315,35 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>10004419</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1508.65</v>
+        <v>2522.72</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-1508.65</v>
+        <v>-1523.72</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-1</v>
+        <v>-0.604</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>4</v>
+        <v>2511</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr"/>
@@ -1377,35 +1367,35 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>10041262</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>628.64</v>
+        <v>571.85</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>1818.86</v>
+        <v>1968.69</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-1190.22</v>
+        <v>-1396.84</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>-0.654</v>
+        <v>-0.71</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>18</v>
+        <v>8641</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>0.02</v>
+        <v>6.86</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
@@ -1429,31 +1419,31 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1176.91</v>
+        <v>1365.87</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-1176.91</v>
+        <v>-1365.87</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>605</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>0.53</v>
+        <v>1277</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>1.01</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1481,35 +1471,35 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>816.53</v>
+        <v>1409.57</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-816.53</v>
+        <v>-1313.67</v>
       </c>
       <c r="G18" s="20" t="n">
-        <v>-1</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>9</v>
+        <v>3254</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>0.01</v>
+        <v>2.58</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
@@ -1523,7 +1513,7 @@
       </c>
       <c r="P18" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1533,35 +1523,35 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10052532</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>95.90000000000001</v>
+        <v>2247.93</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>842.66</v>
+        <v>3548.83</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-746.76</v>
+        <v>-1300.9</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-0.8859999999999999</v>
+        <v>-0.367</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>6</v>
+        <v>16881</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>0.01</v>
+        <v>13.41</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr"/>
@@ -1575,7 +1565,7 @@
       </c>
       <c r="P19" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1597,23 +1587,23 @@
         <v>0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>720.55</v>
+        <v>1205.31</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-720.55</v>
+        <v>-1205.31</v>
       </c>
       <c r="G20" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>3</v>
+        <v>4849</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K20" s="18" t="n">
@@ -1627,7 +1617,7 @@
       <c r="M20" s="18" t="n">
         <v>58.99</v>
       </c>
-      <c r="N20" s="27" t="n">
+      <c r="N20" s="28" t="n">
         <v>0.61</v>
       </c>
       <c r="O20" s="24" t="inlineStr">
@@ -1637,7 +1627,7 @@
       </c>
       <c r="P20" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1647,35 +1637,35 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10042966</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>467.13</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1115.96</v>
+        <v>1191.95</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-648.83</v>
+        <v>-1117.96</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-0.581</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>21</v>
+        <v>40618</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>0.02</v>
+        <v>32.26</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr"/>
@@ -1689,7 +1679,7 @@
       </c>
       <c r="P21" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1699,35 +1689,35 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10042966</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>73.98999999999999</v>
+        <v>766.9299999999999</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>712.5599999999999</v>
+        <v>1866.75</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-638.5700000000001</v>
+        <v>-1099.82</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>-0.8959999999999999</v>
+        <v>-0.589</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>964</v>
+        <v>3834</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>0.84</v>
+        <v>3.05</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
@@ -1741,7 +1731,7 @@
       </c>
       <c r="P22" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1751,49 +1741,59 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0</v>
+        <v>149.4</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>616.3</v>
+        <v>1199.41</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-616.3</v>
+        <v>-1050.01</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-1</v>
+        <v>-0.875</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>6</v>
+        <v>4074</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>0.01</v>
+        <v>3.24</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="inlineStr"/>
-      <c r="L23" s="13" t="inlineStr"/>
-      <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="N23" s="29" t="n">
+        <v>0.396</v>
+      </c>
       <c r="O23" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P23" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1803,31 +1803,31 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>615.49</v>
+        <v>1030.93</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-615.49</v>
+        <v>-1030.93</v>
       </c>
       <c r="G24" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>252</v>
-      </c>
-      <c r="I24" s="22" t="n">
-        <v>0.22</v>
+        <v>864</v>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="P24" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1855,39 +1855,39 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>74.22</v>
+        <v>4095</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>671.29</v>
+        <v>5100.15</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-597.0700000000001</v>
+        <v>-1005.15</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.889</v>
+        <v>-0.197</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>700</v>
+        <v>9899</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>0.61</v>
+        <v>7.86</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K25" s="7" t="n">
-        <v>74.22</v>
+        <v>988.22</v>
       </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
@@ -1895,19 +1895,19 @@
         </is>
       </c>
       <c r="M25" s="7" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N25" s="28" t="n">
-        <v>0.333</v>
+        <v>988.22</v>
+      </c>
+      <c r="N25" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="O25" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P25" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
@@ -1917,54 +1917,44 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>149.4</v>
+        <v>0</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>717.02</v>
+        <v>944.51</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-567.62</v>
+        <v>-944.51</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>-0.792</v>
+        <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>60</v>
+        <v>2108</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>0.05</v>
+        <v>1.67</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K26" s="18" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="L26" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M26" s="18" t="n">
-        <v>107</v>
-      </c>
-      <c r="N26" s="27" t="n">
-        <v>0.396</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K26" s="23" t="inlineStr"/>
+      <c r="L26" s="24" t="inlineStr"/>
+      <c r="M26" s="23" t="inlineStr"/>
+      <c r="N26" s="25" t="inlineStr"/>
       <c r="O26" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P26" s="24" t="inlineStr">
@@ -1979,35 +1969,35 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10030119</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>564.64</v>
+        <v>2074.45</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-564.64</v>
+        <v>-924.45</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-1</v>
+        <v>-0.446</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>3</v>
+        <v>2918</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr"/>
@@ -2031,35 +2021,35 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10052532</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>1557.83</v>
+        <v>695.4</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>2121.53</v>
+        <v>1568.39</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-563.7</v>
+        <v>-872.99</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>-0.266</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>1220</v>
+        <v>16250</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>1.06</v>
+        <v>12.91</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr"/>
@@ -2083,31 +2073,31 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10028895</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>IZIZ 2,5MG+1,5MG 84CP LIBBS</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>514.0599999999999</v>
+        <v>782.49</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-514.0599999999999</v>
+        <v>-782.49</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="I29" s="11" t="n">
-        <v>0.04</v>
+        <v>212</v>
+      </c>
+      <c r="I29" s="27" t="n">
+        <v>0.17</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2135,31 +2125,31 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10004419</t>
+          <t>10053171</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
+          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>1508.11</v>
+        <v>754.62</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-509.11</v>
+        <v>-754.62</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>-0.338</v>
+        <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>0</v>
+        <v>1643</v>
+      </c>
+      <c r="I30" s="26" t="n">
+        <v>1.31</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -2187,44 +2177,54 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10050634</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>EXTENSIOR 1MG 3ML NOVO EUROFARMA</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>504.32</v>
+        <v>1122.92</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-504.32</v>
+        <v>-743.92</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-1</v>
+        <v>-0.662</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>49</v>
+        <v>17247</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>0.04</v>
+        <v>13.7</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K31" s="12" t="inlineStr"/>
-      <c r="L31" s="13" t="inlineStr"/>
-      <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="N31" s="29" t="n">
+        <v>0.333</v>
+      </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P31" s="13" t="inlineStr">
@@ -2239,35 +2239,35 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10050642</t>
+          <t>10030120</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
+          <t>RYBELSUS 7MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>1087.36</v>
+        <v>691.48</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-497.36</v>
+        <v>-691.48</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>-0.457</v>
+        <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>45</v>
+        <v>2004</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>0.04</v>
+        <v>1.59</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr"/>
@@ -2291,35 +2291,35 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>463.6</v>
+        <v>340.62</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>937.6</v>
+        <v>1029.57</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-474</v>
+        <v>-688.95</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.506</v>
+        <v>-0.669</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>742</v>
+        <v>11671</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>0.65</v>
+        <v>9.27</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr"/>
@@ -2343,35 +2343,35 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>10025098</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>0</v>
+        <v>203.67</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>467.78</v>
+        <v>860.5700000000001</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-467.78</v>
+        <v>-656.9</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>-1</v>
+        <v>-0.763</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>0</v>
+        <v>2850</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr"/>
@@ -2395,35 +2395,35 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10053171</t>
+          <t>10028895</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
+          <t>IZIZ 2,5MG+1,5MG 84CP LIBBS</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0</v>
+        <v>287.47</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>451.12</v>
+        <v>859.91</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-451.12</v>
+        <v>-572.4400000000001</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-1</v>
+        <v>-0.6659999999999999</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8</v>
+        <v>4477</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>0.01</v>
+        <v>3.56</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr"/>
@@ -2447,44 +2447,54 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
-        <v>84.90000000000001</v>
+        <v>271.96</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>529.6799999999999</v>
+        <v>841.95</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-444.78</v>
+        <v>-569.99</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>-0.84</v>
+        <v>-0.677</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>286</v>
+        <v>13240</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>0.25</v>
+        <v>10.52</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr"/>
-      <c r="L36" s="24" t="inlineStr"/>
-      <c r="M36" s="23" t="inlineStr"/>
-      <c r="N36" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="L36" s="24" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M36" s="18" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.113</v>
+      </c>
       <c r="O36" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P36" s="24" t="inlineStr">
@@ -2499,35 +2509,35 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10050640</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>590</v>
+        <v>98.58</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>1007.38</v>
+        <v>666.3200000000001</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-417.38</v>
+        <v>-567.74</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.414</v>
+        <v>-0.852</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>33</v>
+        <v>12080</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>0.03</v>
+        <v>9.59</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr"/>
@@ -2551,35 +2561,35 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>10030120</t>
+          <t>100011547</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>RYBELSUS 7MG 30CP NOVO NORDISK</t>
+          <t>NAN SUPREME 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
-        <v>0</v>
+        <v>132.49</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>413.38</v>
+        <v>685.71</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-413.38</v>
+        <v>-553.22</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>-1</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>8</v>
+        <v>8308</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>0.01</v>
+        <v>6.6</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr"/>
@@ -2603,35 +2613,35 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10033463</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0</v>
+        <v>969.96</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>398.34</v>
+        <v>1517.79</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-398.34</v>
+        <v>-547.83</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-1</v>
+        <v>-0.361</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>95</v>
+        <v>12293</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>0.08</v>
+        <v>9.76</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr"/>
@@ -2655,54 +2665,44 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>100011549</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>135.98</v>
+        <v>264.98</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>503.32</v>
+        <v>806.87</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-367.34</v>
+        <v>-541.89</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>-0.73</v>
+        <v>-0.672</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>279</v>
+        <v>7821</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>0.24</v>
+        <v>6.21</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K40" s="18" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="L40" s="24" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M40" s="18" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N40" s="27" t="n">
-        <v>0.113</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr"/>
+      <c r="L40" s="24" t="inlineStr"/>
+      <c r="M40" s="23" t="inlineStr"/>
+      <c r="N40" s="25" t="inlineStr"/>
       <c r="O40" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P40" s="24" t="inlineStr">
@@ -2717,54 +2717,44 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10033757</t>
+          <t>10050634</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XXG 54UN</t>
+          <t>EXTENSIOR 1MG 3ML NOVO EUROFARMA</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>169.8</v>
+        <v>309</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>533.15</v>
+        <v>843.61</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-363.35</v>
+        <v>-534.61</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.634</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>543</v>
+        <v>4354</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>0.47</v>
+        <v>3.46</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="L41" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="N41" s="28" t="n">
-        <v>0.165</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K41" s="12" t="inlineStr"/>
+      <c r="L41" s="13" t="inlineStr"/>
+      <c r="M41" s="12" t="inlineStr"/>
+      <c r="N41" s="14" t="inlineStr"/>
       <c r="O41" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P41" s="13" t="inlineStr">
@@ -2779,44 +2769,54 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10033463</t>
+          <t>10097311</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
+          <t>NESTOGENO 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>550.5599999999999</v>
+        <v>407.94</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>907.35</v>
+        <v>932.3200000000001</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-356.79</v>
+        <v>-524.38</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>-0.393</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>461</v>
+        <v>10934</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>0.4</v>
+        <v>8.68</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="inlineStr"/>
-      <c r="L42" s="24" t="inlineStr"/>
-      <c r="M42" s="23" t="inlineStr"/>
-      <c r="N42" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K42" s="18" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="L42" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M42" s="18" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.081</v>
+      </c>
       <c r="O42" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P42" s="24" t="inlineStr">
@@ -2831,54 +2831,44 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10097311</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 1 800G NESTLE</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>203.97</v>
+        <v>149.5</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>557.35</v>
+        <v>642.96</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-353.38</v>
+        <v>-493.46</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-0.634</v>
+        <v>-0.767</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>266</v>
+        <v>10271</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>0.23</v>
+        <v>8.16</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="L43" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="N43" s="28" t="n">
-        <v>0.081</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K43" s="12" t="inlineStr"/>
+      <c r="L43" s="13" t="inlineStr"/>
+      <c r="M43" s="12" t="inlineStr"/>
+      <c r="N43" s="14" t="inlineStr"/>
       <c r="O43" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P43" s="13" t="inlineStr">
@@ -2893,54 +2883,44 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>10049738</t>
+          <t>10034467</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>OLIRE 6MG/ML 3ML 3APLIC INJ EMS</t>
+          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>350.3</v>
+        <v>493.16</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-350.3</v>
+        <v>-493.16</v>
       </c>
       <c r="G44" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>8</v>
+        <v>3854</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>0.01</v>
+        <v>3.06</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K44" s="18" t="n">
-        <v>866.24</v>
-      </c>
-      <c r="L44" s="24" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M44" s="18" t="n">
-        <v>866.24</v>
-      </c>
-      <c r="N44" s="29" t="n">
-        <v>0</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr"/>
+      <c r="L44" s="24" t="inlineStr"/>
+      <c r="M44" s="23" t="inlineStr"/>
+      <c r="N44" s="25" t="inlineStr"/>
       <c r="O44" s="24" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P44" s="24" t="inlineStr">
@@ -2955,31 +2935,31 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>100011549</t>
+          <t>10041858</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
+          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>132.49</v>
+        <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>482.35</v>
+        <v>471.74</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-349.86</v>
+        <v>-471.74</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-0.725</v>
+        <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="I45" s="11" t="n">
-        <v>0.08</v>
+        <v>666</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>0.53</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -3007,54 +2987,44 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10046473</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>ROUPA INT SAO JOAO ADULTO PANTS G/XG 32UN</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>327.46</v>
+        <v>471.47</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-327.46</v>
+        <v>-471.47</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>420</v>
+        <v>19751</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>0.37</v>
+        <v>15.69</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K46" s="18" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="L46" s="24" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M46" s="18" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N46" s="27" t="n">
-        <v>0.629</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="inlineStr"/>
+      <c r="L46" s="24" t="inlineStr"/>
+      <c r="M46" s="23" t="inlineStr"/>
+      <c r="N46" s="25" t="inlineStr"/>
       <c r="O46" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P46" s="24" t="inlineStr">
@@ -3069,44 +3039,54 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10052539</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>377.7</v>
+        <v>77.7</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>701.91</v>
+        <v>547.76</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-324.21</v>
+        <v>-470.06</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-0.462</v>
+        <v>-0.858</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>40</v>
+        <v>23012</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>0.03</v>
+        <v>18.28</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K47" s="12" t="inlineStr"/>
-      <c r="L47" s="13" t="inlineStr"/>
-      <c r="M47" s="12" t="inlineStr"/>
-      <c r="N47" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N47" s="29" t="n">
+        <v>0.629</v>
+      </c>
       <c r="O47" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P47" s="13" t="inlineStr">
@@ -3121,44 +3101,54 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>100013179</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>UTROGESTAN 200MG 42CAP BESINS</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>203.67</v>
+        <v>0</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>514.46</v>
+        <v>468.79</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-310.79</v>
+        <v>-468.79</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>-0.604</v>
+        <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>123</v>
+        <v>3370</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>0.11</v>
+        <v>2.68</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="inlineStr"/>
-      <c r="L48" s="24" t="inlineStr"/>
-      <c r="M48" s="23" t="inlineStr"/>
-      <c r="N48" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K48" s="18" t="n">
+        <v>246.91</v>
+      </c>
+      <c r="L48" s="24" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M48" s="18" t="n">
+        <v>209.07</v>
+      </c>
+      <c r="N48" s="28" t="n">
+        <v>0.181</v>
+      </c>
       <c r="O48" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P48" s="24" t="inlineStr">
@@ -3173,35 +3163,35 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10029021</t>
+          <t>10050654</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>PANT SEC 50MG/ML SOL CAPI 3FR 50ML+1VALVSPR ACHE</t>
+          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0</v>
+        <v>6120</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>307.22</v>
+        <v>6574.22</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-307.22</v>
+        <v>-454.22</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-1</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>3</v>
+        <v>4215</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr"/>
@@ -3225,54 +3215,44 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>10105170</t>
+          <t>10052539</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>TOALHAS UMED NATURAL BABY LV100 PG80</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>282.29</v>
+        <v>727.24</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>585.71</v>
+        <v>1174.13</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-303.42</v>
+        <v>-446.89</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>-0.518</v>
+        <v>-0.381</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>8221</v>
-      </c>
-      <c r="I50" s="30" t="n">
-        <v>7.17</v>
+        <v>5078</v>
+      </c>
+      <c r="I50" s="22" t="n">
+        <v>4.03</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K50" s="18" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="L50" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M50" s="18" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N50" s="27" t="n">
-        <v>0.375</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="inlineStr"/>
+      <c r="L50" s="24" t="inlineStr"/>
+      <c r="M50" s="23" t="inlineStr"/>
+      <c r="N50" s="25" t="inlineStr"/>
       <c r="O50" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P50" s="24" t="inlineStr">
@@ -3287,44 +3267,54 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10034467</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
+          <t>SYSTEN CONTI 8 ADESIVOS THERAMEX</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>294.82</v>
+        <v>446.52</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-294.82</v>
+        <v>-446.52</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>9</v>
+        <v>5661</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>0.01</v>
+        <v>4.5</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr"/>
-      <c r="L51" s="13" t="inlineStr"/>
-      <c r="M51" s="12" t="inlineStr"/>
-      <c r="N51" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>170.87</v>
+      </c>
+      <c r="L51" s="13" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>125.98</v>
+      </c>
+      <c r="N51" s="29" t="n">
+        <v>0.356</v>
+      </c>
       <c r="O51" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P51" s="13" t="inlineStr">
@@ -3339,35 +3329,35 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>10022882</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>ACICLOVIR 400MG 30CP GEN PRATI</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>73.98999999999999</v>
+        <v>214.47</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>358.09</v>
+        <v>646.23</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-284.1</v>
+        <v>-431.76</v>
       </c>
       <c r="G52" s="20" t="n">
-        <v>-0.7929999999999999</v>
+        <v>-0.6679999999999999</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>501</v>
+        <v>5328</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>0.44</v>
+        <v>4.23</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K52" s="23" t="inlineStr"/>
@@ -3391,31 +3381,31 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>10041858</t>
+          <t>10034591</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
+          <t>PANTOGAR NEO 90CAP BIOLAB</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>282.01</v>
+        <v>429.57</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-282.01</v>
+        <v>-429.57</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="11" t="n">
-        <v>0</v>
+        <v>1755</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>1.39</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3443,44 +3433,54 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>10046473</t>
+          <t>100011848</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>ROUPA INT SAO JOAO ADULTO PANTS G/XG 32UN</t>
+          <t>DES AXE AERO 150ML APOLLO</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>0</v>
+        <v>74.3</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>281.85</v>
+        <v>459.59</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-281.85</v>
+        <v>-385.29</v>
       </c>
       <c r="G54" s="20" t="n">
-        <v>-1</v>
+        <v>-0.838</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>290</v>
+        <v>58984</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>0.25</v>
+        <v>46.85</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K54" s="23" t="inlineStr"/>
-      <c r="L54" s="24" t="inlineStr"/>
-      <c r="M54" s="23" t="inlineStr"/>
-      <c r="N54" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K54" s="18" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L54" s="24" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M54" s="18" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="N54" s="28" t="n">
+        <v>0.214</v>
+      </c>
       <c r="O54" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P54" s="24" t="inlineStr">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -241,12 +241,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,19 +279,25 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -826,68 +829,78 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr"/>
-      <c r="L5" s="13" t="inlineStr"/>
-      <c r="M5" s="12" t="inlineStr"/>
-      <c r="N5" s="14" t="inlineStr"/>
-      <c r="O5" s="13" t="inlineStr">
+      <c r="K5" s="7" t="n">
+        <v>2382.23</v>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>2382.23</v>
+      </c>
+      <c r="N5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>Detrator Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>10042969</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>FR PAMPERS CONFORTSEC JUMBO XXG 112UN</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>4012.69</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>12516.41</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>-8503.719999999999</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>-0.679</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>10635</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr"/>
+      <c r="L6" s="23" t="inlineStr"/>
+      <c r="M6" s="22" t="inlineStr"/>
+      <c r="N6" s="24" t="inlineStr"/>
+      <c r="O6" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P5" s="13" t="inlineStr">
-        <is>
-          <t>Detrator Crítico</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>10042969</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO XXG 112UN</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>4012.69</v>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>12516.41</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>-8503.719999999999</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <v>-0.679</v>
-      </c>
-      <c r="H6" s="21" t="n">
-        <v>10635</v>
-      </c>
-      <c r="I6" s="22" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="J6" s="15" t="inlineStr">
-        <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr"/>
-      <c r="M6" s="23" t="inlineStr"/>
-      <c r="N6" s="25" t="inlineStr"/>
-      <c r="O6" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P6" s="24" t="inlineStr">
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t>Detrator Crítico</t>
         </is>
@@ -930,68 +943,78 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr"/>
-      <c r="L7" s="13" t="inlineStr"/>
-      <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="14" t="inlineStr"/>
-      <c r="O7" s="13" t="inlineStr">
+      <c r="K7" s="7" t="n">
+        <v>3210.85</v>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>3210.85</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>Detrator Crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>10053130</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>OZIVY 1MG 1CAN 3ML EMS</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>4925.62</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>11345.16</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>-6419.54</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>-0.5660000000000001</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>12111</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr"/>
+      <c r="L8" s="23" t="inlineStr"/>
+      <c r="M8" s="22" t="inlineStr"/>
+      <c r="N8" s="24" t="inlineStr"/>
+      <c r="O8" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P7" s="13" t="inlineStr">
-        <is>
-          <t>Detrator Crítico</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>10053130</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>OZIVY 1MG 1CAN 3ML EMS</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>4925.62</v>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>11345.16</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>-6419.54</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>-0.5660000000000001</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>12111</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="J8" s="15" t="inlineStr">
-        <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr"/>
-      <c r="M8" s="23" t="inlineStr"/>
-      <c r="N8" s="25" t="inlineStr"/>
-      <c r="O8" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P8" s="24" t="inlineStr">
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t>Detrator Crítico</t>
         </is>
@@ -1034,68 +1057,88 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K9" s="12" t="inlineStr"/>
-      <c r="L9" s="13" t="inlineStr"/>
-      <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="14" t="inlineStr"/>
-      <c r="O9" s="13" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P9" s="13" t="inlineStr">
+      <c r="K9" s="7" t="n">
+        <v>1905.6</v>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>1905.6</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t>Detrator Crítico</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>10042968</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="17" t="n">
         <v>2720.52</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="17" t="n">
         <v>7721.22</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>-5000.7</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="19" t="n">
         <v>-0.648</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="H10" s="20" t="n">
         <v>2116</v>
       </c>
-      <c r="I10" s="22" t="n">
+      <c r="I10" s="21" t="n">
         <v>1.68</v>
       </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr"/>
-      <c r="M10" s="23" t="inlineStr"/>
-      <c r="N10" s="25" t="inlineStr"/>
-      <c r="O10" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P10" s="24" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="N10" s="25" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="O10" s="23" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>Detrator Crítico</t>
         </is>
@@ -1138,68 +1181,78 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr"/>
-      <c r="L11" s="13" t="inlineStr"/>
-      <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="14" t="inlineStr"/>
-      <c r="O11" s="13" t="inlineStr">
+      <c r="K11" s="26" t="inlineStr"/>
+      <c r="L11" s="12" t="inlineStr"/>
+      <c r="M11" s="26" t="inlineStr"/>
+      <c r="N11" s="27" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P11" s="13" t="inlineStr">
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>10040801</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="17" t="n">
         <v>2523.62</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>-2523.62</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="19" t="n">
         <v>-1</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H12" s="20" t="n">
         <v>1770</v>
       </c>
-      <c r="I12" s="26" t="n">
+      <c r="I12" s="28" t="n">
         <v>1.41</v>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr"/>
-      <c r="M12" s="23" t="inlineStr"/>
-      <c r="N12" s="25" t="inlineStr"/>
-      <c r="O12" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P12" s="24" t="inlineStr">
+      <c r="K12" s="17" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="N12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="23" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
@@ -1242,68 +1295,78 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr"/>
-      <c r="L13" s="13" t="inlineStr"/>
-      <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="14" t="inlineStr"/>
-      <c r="O13" s="13" t="inlineStr">
+      <c r="K13" s="7" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P13" s="12" t="inlineStr">
+        <is>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>10041262</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>1047.81</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>3042.52</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>-1994.71</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>-0.6559999999999999</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>2289</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr"/>
+      <c r="L14" s="23" t="inlineStr"/>
+      <c r="M14" s="22" t="inlineStr"/>
+      <c r="N14" s="24" t="inlineStr"/>
+      <c r="O14" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P13" s="13" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>10041262</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>1047.81</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>3042.52</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>-1994.71</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>-0.6559999999999999</v>
-      </c>
-      <c r="H14" s="21" t="n">
-        <v>2289</v>
-      </c>
-      <c r="I14" s="22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr"/>
-      <c r="M14" s="23" t="inlineStr"/>
-      <c r="N14" s="25" t="inlineStr"/>
-      <c r="O14" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P14" s="24" t="inlineStr">
+      <c r="P14" s="23" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
@@ -1346,68 +1409,68 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K15" s="12" t="inlineStr"/>
-      <c r="L15" s="13" t="inlineStr"/>
-      <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="14" t="inlineStr"/>
-      <c r="O15" s="13" t="inlineStr">
+      <c r="K15" s="26" t="inlineStr"/>
+      <c r="L15" s="12" t="inlineStr"/>
+      <c r="M15" s="26" t="inlineStr"/>
+      <c r="N15" s="27" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P15" s="13" t="inlineStr">
+      <c r="P15" s="12" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>10052534</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="17" t="n">
         <v>571.85</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="17" t="n">
         <v>1968.69</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="18" t="n">
         <v>-1396.84</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="19" t="n">
         <v>-0.71</v>
       </c>
-      <c r="H16" s="21" t="n">
+      <c r="H16" s="20" t="n">
         <v>8641</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="21" t="n">
         <v>6.86</v>
       </c>
-      <c r="J16" s="15" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr"/>
-      <c r="M16" s="23" t="inlineStr"/>
-      <c r="N16" s="25" t="inlineStr"/>
-      <c r="O16" s="24" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr"/>
+      <c r="L16" s="23" t="inlineStr"/>
+      <c r="M16" s="22" t="inlineStr"/>
+      <c r="N16" s="24" t="inlineStr"/>
+      <c r="O16" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P16" s="24" t="inlineStr">
+      <c r="P16" s="23" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
@@ -1442,7 +1505,7 @@
       <c r="H17" s="10" t="n">
         <v>1277</v>
       </c>
-      <c r="I17" s="27" t="n">
+      <c r="I17" s="30" t="n">
         <v>1.01</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1450,68 +1513,68 @@
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="13" t="inlineStr"/>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="14" t="inlineStr"/>
-      <c r="O17" s="13" t="inlineStr">
+      <c r="K17" s="26" t="inlineStr"/>
+      <c r="L17" s="12" t="inlineStr"/>
+      <c r="M17" s="26" t="inlineStr"/>
+      <c r="N17" s="27" t="inlineStr"/>
+      <c r="O17" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P17" s="13" t="inlineStr">
+      <c r="P17" s="12" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>10041263</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="17" t="n">
         <v>95.90000000000001</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="17" t="n">
         <v>1409.57</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="18" t="n">
         <v>-1313.67</v>
       </c>
-      <c r="G18" s="20" t="n">
+      <c r="G18" s="19" t="n">
         <v>-0.9320000000000001</v>
       </c>
-      <c r="H18" s="21" t="n">
+      <c r="H18" s="20" t="n">
         <v>3254</v>
       </c>
-      <c r="I18" s="22" t="n">
+      <c r="I18" s="21" t="n">
         <v>2.58</v>
       </c>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr"/>
-      <c r="M18" s="23" t="inlineStr"/>
-      <c r="N18" s="25" t="inlineStr"/>
-      <c r="O18" s="24" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr"/>
+      <c r="L18" s="23" t="inlineStr"/>
+      <c r="M18" s="22" t="inlineStr"/>
+      <c r="N18" s="24" t="inlineStr"/>
+      <c r="O18" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P18" s="24" t="inlineStr">
+      <c r="P18" s="23" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
@@ -1554,78 +1617,78 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr"/>
-      <c r="L19" s="13" t="inlineStr"/>
-      <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="14" t="inlineStr"/>
-      <c r="O19" s="13" t="inlineStr">
+      <c r="K19" s="26" t="inlineStr"/>
+      <c r="L19" s="12" t="inlineStr"/>
+      <c r="M19" s="26" t="inlineStr"/>
+      <c r="N19" s="27" t="inlineStr"/>
+      <c r="O19" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P19" s="13" t="inlineStr">
+      <c r="P19" s="12" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>100016230</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="17" t="n">
         <v>1205.31</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="18" t="n">
         <v>-1205.31</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="19" t="n">
         <v>-1</v>
       </c>
-      <c r="H20" s="21" t="n">
+      <c r="H20" s="20" t="n">
         <v>4849</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="21" t="n">
         <v>3.85</v>
       </c>
-      <c r="J20" s="15" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K20" s="18" t="n">
+      <c r="K20" s="17" t="n">
         <v>94.98999999999999</v>
       </c>
-      <c r="L20" s="24" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M20" s="18" t="n">
-        <v>58.99</v>
-      </c>
-      <c r="N20" s="28" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="O20" s="24" t="inlineStr">
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M20" s="17" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="N20" s="25" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="O20" s="23" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P20" s="24" t="inlineStr">
+      <c r="P20" s="23" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
@@ -1668,68 +1731,68 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr"/>
-      <c r="L21" s="13" t="inlineStr"/>
-      <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="14" t="inlineStr"/>
-      <c r="O21" s="13" t="inlineStr">
+      <c r="K21" s="26" t="inlineStr"/>
+      <c r="L21" s="12" t="inlineStr"/>
+      <c r="M21" s="26" t="inlineStr"/>
+      <c r="N21" s="27" t="inlineStr"/>
+      <c r="O21" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P21" s="13" t="inlineStr">
+      <c r="P21" s="12" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>10042966</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
         </is>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="17" t="n">
         <v>766.9299999999999</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="17" t="n">
         <v>1866.75</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="18" t="n">
         <v>-1099.82</v>
       </c>
-      <c r="G22" s="20" t="n">
+      <c r="G22" s="19" t="n">
         <v>-0.589</v>
       </c>
-      <c r="H22" s="21" t="n">
+      <c r="H22" s="20" t="n">
         <v>3834</v>
       </c>
-      <c r="I22" s="22" t="n">
+      <c r="I22" s="21" t="n">
         <v>3.05</v>
       </c>
-      <c r="J22" s="15" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr"/>
-      <c r="M22" s="23" t="inlineStr"/>
-      <c r="N22" s="25" t="inlineStr"/>
-      <c r="O22" s="24" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr"/>
+      <c r="L22" s="23" t="inlineStr"/>
+      <c r="M22" s="22" t="inlineStr"/>
+      <c r="N22" s="24" t="inlineStr"/>
+      <c r="O22" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P22" s="24" t="inlineStr">
+      <c r="P22" s="23" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
@@ -1775,7 +1838,7 @@
       <c r="K23" s="7" t="n">
         <v>149.4</v>
       </c>
-      <c r="L23" s="13" t="inlineStr">
+      <c r="L23" s="12" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
@@ -1783,67 +1846,77 @@
       <c r="M23" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="N23" s="29" t="n">
+      <c r="N23" s="31" t="n">
         <v>0.396</v>
       </c>
-      <c r="O23" s="13" t="inlineStr">
+      <c r="O23" s="12" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P23" s="13" t="inlineStr">
+      <c r="P23" s="12" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>10050440</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="17" t="n">
         <v>1030.93</v>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="18" t="n">
         <v>-1030.93</v>
       </c>
-      <c r="G24" s="20" t="n">
+      <c r="G24" s="19" t="n">
         <v>-1</v>
       </c>
-      <c r="H24" s="21" t="n">
+      <c r="H24" s="20" t="n">
         <v>864</v>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I24" s="28" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr"/>
-      <c r="M24" s="23" t="inlineStr"/>
-      <c r="N24" s="25" t="inlineStr"/>
-      <c r="O24" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P24" s="24" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v>315.46</v>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M24" s="17" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="N24" s="25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O24" s="23" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P24" s="23" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
@@ -1889,7 +1962,7 @@
       <c r="K25" s="7" t="n">
         <v>988.22</v>
       </c>
-      <c r="L25" s="13" t="inlineStr">
+      <c r="L25" s="12" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
@@ -1897,67 +1970,73 @@
       <c r="M25" s="7" t="n">
         <v>988.22</v>
       </c>
-      <c r="N25" s="30" t="n">
+      <c r="N25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="13" t="inlineStr">
+      <c r="O25" s="12" t="inlineStr">
         <is>
           <t>Preço Alinhado</t>
         </is>
       </c>
-      <c r="P25" s="13" t="inlineStr">
+      <c r="P25" s="12" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>10034724</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="17" t="n">
         <v>944.51</v>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="18" t="n">
         <v>-944.51</v>
       </c>
-      <c r="G26" s="20" t="n">
+      <c r="G26" s="19" t="n">
         <v>-1</v>
       </c>
-      <c r="H26" s="21" t="n">
+      <c r="H26" s="20" t="n">
         <v>2108</v>
       </c>
-      <c r="I26" s="22" t="n">
+      <c r="I26" s="21" t="n">
         <v>1.67</v>
       </c>
-      <c r="J26" s="15" t="inlineStr">
+      <c r="J26" s="14" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr"/>
-      <c r="M26" s="23" t="inlineStr"/>
-      <c r="N26" s="25" t="inlineStr"/>
-      <c r="O26" s="24" t="inlineStr">
+      <c r="K26" s="22" t="inlineStr"/>
+      <c r="L26" s="23" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M26" s="17" t="n">
+        <v>549.9</v>
+      </c>
+      <c r="N26" s="24" t="inlineStr"/>
+      <c r="O26" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P26" s="24" t="inlineStr">
+      <c r="P26" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2000,68 +2079,78 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K27" s="12" t="inlineStr"/>
-      <c r="L27" s="13" t="inlineStr"/>
-      <c r="M27" s="12" t="inlineStr"/>
-      <c r="N27" s="14" t="inlineStr"/>
-      <c r="O27" s="13" t="inlineStr">
+      <c r="K27" s="7" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P27" s="12" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>10052533</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>695.4</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>1568.39</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>-872.99</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>-0.5570000000000001</v>
+      </c>
+      <c r="H28" s="20" t="n">
+        <v>16250</v>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr"/>
+      <c r="L28" s="23" t="inlineStr"/>
+      <c r="M28" s="22" t="inlineStr"/>
+      <c r="N28" s="24" t="inlineStr"/>
+      <c r="O28" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P27" s="13" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="15" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>10052533</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>695.4</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>1568.39</v>
-      </c>
-      <c r="F28" s="19" t="n">
-        <v>-872.99</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>-0.5570000000000001</v>
-      </c>
-      <c r="H28" s="21" t="n">
-        <v>16250</v>
-      </c>
-      <c r="I28" s="22" t="n">
-        <v>12.91</v>
-      </c>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr"/>
-      <c r="M28" s="23" t="inlineStr"/>
-      <c r="N28" s="25" t="inlineStr"/>
-      <c r="O28" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P28" s="24" t="inlineStr">
+      <c r="P28" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2096,7 +2185,7 @@
       <c r="H29" s="10" t="n">
         <v>212</v>
       </c>
-      <c r="I29" s="27" t="n">
+      <c r="I29" s="30" t="n">
         <v>0.17</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2104,68 +2193,74 @@
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K29" s="12" t="inlineStr"/>
-      <c r="L29" s="13" t="inlineStr"/>
-      <c r="M29" s="12" t="inlineStr"/>
-      <c r="N29" s="14" t="inlineStr"/>
-      <c r="O29" s="13" t="inlineStr">
+      <c r="K29" s="26" t="inlineStr"/>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>1212.9</v>
+      </c>
+      <c r="N29" s="27" t="inlineStr"/>
+      <c r="O29" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P29" s="13" t="inlineStr">
+      <c r="P29" s="12" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>10053171</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
         </is>
       </c>
-      <c r="D30" s="18" t="n">
+      <c r="D30" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E30" s="17" t="n">
         <v>754.62</v>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="18" t="n">
         <v>-754.62</v>
       </c>
-      <c r="G30" s="20" t="n">
+      <c r="G30" s="19" t="n">
         <v>-1</v>
       </c>
-      <c r="H30" s="21" t="n">
+      <c r="H30" s="20" t="n">
         <v>1643</v>
       </c>
-      <c r="I30" s="26" t="n">
+      <c r="I30" s="28" t="n">
         <v>1.31</v>
       </c>
-      <c r="J30" s="15" t="inlineStr">
+      <c r="J30" s="14" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K30" s="23" t="inlineStr"/>
-      <c r="L30" s="24" t="inlineStr"/>
-      <c r="M30" s="23" t="inlineStr"/>
-      <c r="N30" s="25" t="inlineStr"/>
-      <c r="O30" s="24" t="inlineStr">
+      <c r="K30" s="22" t="inlineStr"/>
+      <c r="L30" s="23" t="inlineStr"/>
+      <c r="M30" s="22" t="inlineStr"/>
+      <c r="N30" s="24" t="inlineStr"/>
+      <c r="O30" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P30" s="24" t="inlineStr">
+      <c r="P30" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2211,7 +2306,7 @@
       <c r="K31" s="7" t="n">
         <v>74.22</v>
       </c>
-      <c r="L31" s="13" t="inlineStr">
+      <c r="L31" s="12" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
@@ -2219,67 +2314,77 @@
       <c r="M31" s="7" t="n">
         <v>55.67</v>
       </c>
-      <c r="N31" s="29" t="n">
+      <c r="N31" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="O31" s="13" t="inlineStr">
+      <c r="O31" s="12" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P31" s="13" t="inlineStr">
+      <c r="P31" s="12" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>10030120</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>RYBELSUS 7MG 30CP NOVO NORDISK</t>
         </is>
       </c>
-      <c r="D32" s="18" t="n">
+      <c r="D32" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="18" t="n">
+      <c r="E32" s="17" t="n">
         <v>691.48</v>
       </c>
-      <c r="F32" s="19" t="n">
+      <c r="F32" s="18" t="n">
         <v>-691.48</v>
       </c>
-      <c r="G32" s="20" t="n">
+      <c r="G32" s="19" t="n">
         <v>-1</v>
       </c>
-      <c r="H32" s="21" t="n">
+      <c r="H32" s="20" t="n">
         <v>2004</v>
       </c>
-      <c r="I32" s="22" t="n">
+      <c r="I32" s="21" t="n">
         <v>1.59</v>
       </c>
-      <c r="J32" s="15" t="inlineStr">
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr"/>
-      <c r="L32" s="24" t="inlineStr"/>
-      <c r="M32" s="23" t="inlineStr"/>
-      <c r="N32" s="25" t="inlineStr"/>
-      <c r="O32" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P32" s="24" t="inlineStr">
+      <c r="K32" s="17" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="L32" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M32" s="17" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="N32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="23" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P32" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2322,68 +2427,78 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K33" s="12" t="inlineStr"/>
-      <c r="L33" s="13" t="inlineStr"/>
-      <c r="M33" s="12" t="inlineStr"/>
-      <c r="N33" s="14" t="inlineStr"/>
-      <c r="O33" s="13" t="inlineStr">
+      <c r="K33" s="26" t="inlineStr"/>
+      <c r="L33" s="12" t="inlineStr"/>
+      <c r="M33" s="26" t="inlineStr"/>
+      <c r="N33" s="27" t="inlineStr"/>
+      <c r="O33" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P33" s="13" t="inlineStr">
+      <c r="P33" s="12" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>10049094</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
-      <c r="D34" s="18" t="n">
+      <c r="D34" s="17" t="n">
         <v>203.67</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="17" t="n">
         <v>860.5700000000001</v>
       </c>
-      <c r="F34" s="19" t="n">
+      <c r="F34" s="18" t="n">
         <v>-656.9</v>
       </c>
-      <c r="G34" s="20" t="n">
+      <c r="G34" s="19" t="n">
         <v>-0.763</v>
       </c>
-      <c r="H34" s="21" t="n">
+      <c r="H34" s="20" t="n">
         <v>2850</v>
       </c>
-      <c r="I34" s="22" t="n">
+      <c r="I34" s="21" t="n">
         <v>2.26</v>
       </c>
-      <c r="J34" s="15" t="inlineStr">
-        <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="inlineStr"/>
-      <c r="L34" s="24" t="inlineStr"/>
-      <c r="M34" s="23" t="inlineStr"/>
-      <c r="N34" s="25" t="inlineStr"/>
-      <c r="O34" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P34" s="24" t="inlineStr">
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K34" s="17" t="n">
+        <v>218.67</v>
+      </c>
+      <c r="L34" s="23" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M34" s="17" t="n">
+        <v>197.18</v>
+      </c>
+      <c r="N34" s="25" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="O34" s="23" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P34" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2423,81 +2538,91 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K35" s="12" t="inlineStr"/>
-      <c r="L35" s="13" t="inlineStr"/>
-      <c r="M35" s="12" t="inlineStr"/>
-      <c r="N35" s="14" t="inlineStr"/>
-      <c r="O35" s="13" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P35" s="13" t="inlineStr">
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>164.09</v>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="N35" s="31" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P35" s="12" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="15" t="n">
+      <c r="A36" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>10097312</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
-      <c r="D36" s="18" t="n">
+      <c r="D36" s="17" t="n">
         <v>271.96</v>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="17" t="n">
         <v>841.95</v>
       </c>
-      <c r="F36" s="19" t="n">
+      <c r="F36" s="18" t="n">
         <v>-569.99</v>
       </c>
-      <c r="G36" s="20" t="n">
+      <c r="G36" s="19" t="n">
         <v>-0.677</v>
       </c>
-      <c r="H36" s="21" t="n">
+      <c r="H36" s="20" t="n">
         <v>13240</v>
       </c>
-      <c r="I36" s="22" t="n">
+      <c r="I36" s="21" t="n">
         <v>10.52</v>
       </c>
-      <c r="J36" s="15" t="inlineStr">
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K36" s="18" t="n">
+      <c r="K36" s="17" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="L36" s="24" t="inlineStr">
+      <c r="L36" s="23" t="inlineStr">
         <is>
           <t>DROGARAIA</t>
         </is>
       </c>
-      <c r="M36" s="18" t="n">
+      <c r="M36" s="17" t="n">
         <v>61.06</v>
       </c>
-      <c r="N36" s="28" t="n">
+      <c r="N36" s="25" t="n">
         <v>0.113</v>
       </c>
-      <c r="O36" s="24" t="inlineStr">
+      <c r="O36" s="23" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P36" s="24" t="inlineStr">
+      <c r="P36" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2540,68 +2665,78 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K37" s="12" t="inlineStr"/>
-      <c r="L37" s="13" t="inlineStr"/>
-      <c r="M37" s="12" t="inlineStr"/>
-      <c r="N37" s="14" t="inlineStr"/>
-      <c r="O37" s="13" t="inlineStr">
+      <c r="K37" s="26" t="inlineStr"/>
+      <c r="L37" s="12" t="inlineStr"/>
+      <c r="M37" s="26" t="inlineStr"/>
+      <c r="N37" s="27" t="inlineStr"/>
+      <c r="O37" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P37" s="13" t="inlineStr">
+      <c r="P37" s="12" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="15" t="n">
+      <c r="A38" s="14" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>100011547</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>NAN SUPREME 1 800G NESTLE</t>
         </is>
       </c>
-      <c r="D38" s="18" t="n">
+      <c r="D38" s="17" t="n">
         <v>132.49</v>
       </c>
-      <c r="E38" s="18" t="n">
+      <c r="E38" s="17" t="n">
         <v>685.71</v>
       </c>
-      <c r="F38" s="19" t="n">
+      <c r="F38" s="18" t="n">
         <v>-553.22</v>
       </c>
-      <c r="G38" s="20" t="n">
+      <c r="G38" s="19" t="n">
         <v>-0.8070000000000001</v>
       </c>
-      <c r="H38" s="21" t="n">
+      <c r="H38" s="20" t="n">
         <v>8308</v>
       </c>
-      <c r="I38" s="22" t="n">
+      <c r="I38" s="21" t="n">
         <v>6.6</v>
       </c>
-      <c r="J38" s="15" t="inlineStr">
-        <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr"/>
-      <c r="L38" s="24" t="inlineStr"/>
-      <c r="M38" s="23" t="inlineStr"/>
-      <c r="N38" s="25" t="inlineStr"/>
-      <c r="O38" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P38" s="24" t="inlineStr">
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K38" s="17" t="n">
+        <v>132.49</v>
+      </c>
+      <c r="L38" s="23" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M38" s="17" t="n">
+        <v>124.19</v>
+      </c>
+      <c r="N38" s="25" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="O38" s="23" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P38" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2641,71 +2776,81 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="N39" s="31" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P39" s="12" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>100011549</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>NAN SUPREME 2 800G NESTLE</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>264.98</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>806.87</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>-541.89</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <v>-0.672</v>
+      </c>
+      <c r="H40" s="20" t="n">
+        <v>7821</v>
+      </c>
+      <c r="I40" s="21" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K39" s="12" t="inlineStr"/>
-      <c r="L39" s="13" t="inlineStr"/>
-      <c r="M39" s="12" t="inlineStr"/>
-      <c r="N39" s="14" t="inlineStr"/>
-      <c r="O39" s="13" t="inlineStr">
+      <c r="K40" s="22" t="inlineStr"/>
+      <c r="L40" s="23" t="inlineStr"/>
+      <c r="M40" s="22" t="inlineStr"/>
+      <c r="N40" s="24" t="inlineStr"/>
+      <c r="O40" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P39" s="13" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="15" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>100011549</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
-        </is>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>264.98</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>806.87</v>
-      </c>
-      <c r="F40" s="19" t="n">
-        <v>-541.89</v>
-      </c>
-      <c r="G40" s="20" t="n">
-        <v>-0.672</v>
-      </c>
-      <c r="H40" s="21" t="n">
-        <v>7821</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="J40" s="15" t="inlineStr">
-        <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr"/>
-      <c r="L40" s="24" t="inlineStr"/>
-      <c r="M40" s="23" t="inlineStr"/>
-      <c r="N40" s="25" t="inlineStr"/>
-      <c r="O40" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P40" s="24" t="inlineStr">
+      <c r="P40" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2748,78 +2893,84 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K41" s="12" t="inlineStr"/>
-      <c r="L41" s="13" t="inlineStr"/>
-      <c r="M41" s="12" t="inlineStr"/>
-      <c r="N41" s="14" t="inlineStr"/>
-      <c r="O41" s="13" t="inlineStr">
+      <c r="K41" s="26" t="inlineStr"/>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="N41" s="27" t="inlineStr"/>
+      <c r="O41" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P41" s="13" t="inlineStr">
+      <c r="P41" s="12" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="15" t="n">
+      <c r="A42" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>10097311</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>NESTOGENO 1 800G NESTLE</t>
         </is>
       </c>
-      <c r="D42" s="18" t="n">
+      <c r="D42" s="17" t="n">
         <v>407.94</v>
       </c>
-      <c r="E42" s="18" t="n">
+      <c r="E42" s="17" t="n">
         <v>932.3200000000001</v>
       </c>
-      <c r="F42" s="19" t="n">
+      <c r="F42" s="18" t="n">
         <v>-524.38</v>
       </c>
-      <c r="G42" s="20" t="n">
+      <c r="G42" s="19" t="n">
         <v>-0.5620000000000001</v>
       </c>
-      <c r="H42" s="21" t="n">
+      <c r="H42" s="20" t="n">
         <v>10934</v>
       </c>
-      <c r="I42" s="22" t="n">
+      <c r="I42" s="21" t="n">
         <v>8.68</v>
       </c>
-      <c r="J42" s="15" t="inlineStr">
+      <c r="J42" s="14" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K42" s="18" t="n">
+      <c r="K42" s="17" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="L42" s="24" t="inlineStr">
+      <c r="L42" s="23" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
-      <c r="M42" s="18" t="n">
+      <c r="M42" s="17" t="n">
         <v>62.9</v>
       </c>
-      <c r="N42" s="28" t="n">
+      <c r="N42" s="25" t="n">
         <v>0.081</v>
       </c>
-      <c r="O42" s="24" t="inlineStr">
+      <c r="O42" s="23" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P42" s="24" t="inlineStr">
+      <c r="P42" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2862,68 +3013,74 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K43" s="12" t="inlineStr"/>
-      <c r="L43" s="13" t="inlineStr"/>
-      <c r="M43" s="12" t="inlineStr"/>
-      <c r="N43" s="14" t="inlineStr"/>
-      <c r="O43" s="13" t="inlineStr">
+      <c r="K43" s="26" t="inlineStr"/>
+      <c r="L43" s="12" t="inlineStr"/>
+      <c r="M43" s="26" t="inlineStr"/>
+      <c r="N43" s="27" t="inlineStr"/>
+      <c r="O43" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P43" s="13" t="inlineStr">
+      <c r="P43" s="12" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="15" t="n">
+      <c r="A44" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>10034467</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
         </is>
       </c>
-      <c r="D44" s="18" t="n">
+      <c r="D44" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="18" t="n">
+      <c r="E44" s="17" t="n">
         <v>493.16</v>
       </c>
-      <c r="F44" s="19" t="n">
+      <c r="F44" s="18" t="n">
         <v>-493.16</v>
       </c>
-      <c r="G44" s="20" t="n">
+      <c r="G44" s="19" t="n">
         <v>-1</v>
       </c>
-      <c r="H44" s="21" t="n">
+      <c r="H44" s="20" t="n">
         <v>3854</v>
       </c>
-      <c r="I44" s="22" t="n">
+      <c r="I44" s="21" t="n">
         <v>3.06</v>
       </c>
-      <c r="J44" s="15" t="inlineStr">
+      <c r="J44" s="14" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K44" s="23" t="inlineStr"/>
-      <c r="L44" s="24" t="inlineStr"/>
-      <c r="M44" s="23" t="inlineStr"/>
-      <c r="N44" s="25" t="inlineStr"/>
-      <c r="O44" s="24" t="inlineStr">
+      <c r="K44" s="22" t="inlineStr"/>
+      <c r="L44" s="23" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M44" s="17" t="n">
+        <v>234.98</v>
+      </c>
+      <c r="N44" s="24" t="inlineStr"/>
+      <c r="O44" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P44" s="24" t="inlineStr">
+      <c r="P44" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -2958,7 +3115,7 @@
       <c r="H45" s="10" t="n">
         <v>666</v>
       </c>
-      <c r="I45" s="27" t="n">
+      <c r="I45" s="30" t="n">
         <v>0.53</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -2966,68 +3123,68 @@
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr"/>
-      <c r="L45" s="13" t="inlineStr"/>
-      <c r="M45" s="12" t="inlineStr"/>
-      <c r="N45" s="14" t="inlineStr"/>
-      <c r="O45" s="13" t="inlineStr">
+      <c r="K45" s="26" t="inlineStr"/>
+      <c r="L45" s="12" t="inlineStr"/>
+      <c r="M45" s="26" t="inlineStr"/>
+      <c r="N45" s="27" t="inlineStr"/>
+      <c r="O45" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P45" s="13" t="inlineStr">
+      <c r="P45" s="12" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="15" t="n">
+      <c r="A46" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>10046473</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>ROUPA INT SAO JOAO ADULTO PANTS G/XG 32UN</t>
         </is>
       </c>
-      <c r="D46" s="18" t="n">
+      <c r="D46" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="18" t="n">
+      <c r="E46" s="17" t="n">
         <v>471.47</v>
       </c>
-      <c r="F46" s="19" t="n">
+      <c r="F46" s="18" t="n">
         <v>-471.47</v>
       </c>
-      <c r="G46" s="20" t="n">
+      <c r="G46" s="19" t="n">
         <v>-1</v>
       </c>
-      <c r="H46" s="21" t="n">
+      <c r="H46" s="20" t="n">
         <v>19751</v>
       </c>
-      <c r="I46" s="22" t="n">
+      <c r="I46" s="21" t="n">
         <v>15.69</v>
       </c>
-      <c r="J46" s="15" t="inlineStr">
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K46" s="23" t="inlineStr"/>
-      <c r="L46" s="24" t="inlineStr"/>
-      <c r="M46" s="23" t="inlineStr"/>
-      <c r="N46" s="25" t="inlineStr"/>
-      <c r="O46" s="24" t="inlineStr">
+      <c r="K46" s="22" t="inlineStr"/>
+      <c r="L46" s="23" t="inlineStr"/>
+      <c r="M46" s="22" t="inlineStr"/>
+      <c r="N46" s="24" t="inlineStr"/>
+      <c r="O46" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P46" s="24" t="inlineStr">
+      <c r="P46" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -3073,7 +3230,7 @@
       <c r="K47" s="7" t="n">
         <v>25.9</v>
       </c>
-      <c r="L47" s="13" t="inlineStr">
+      <c r="L47" s="12" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
@@ -3081,77 +3238,77 @@
       <c r="M47" s="7" t="n">
         <v>15.9</v>
       </c>
-      <c r="N47" s="29" t="n">
+      <c r="N47" s="31" t="n">
         <v>0.629</v>
       </c>
-      <c r="O47" s="13" t="inlineStr">
+      <c r="O47" s="12" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P47" s="13" t="inlineStr">
+      <c r="P47" s="12" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="15" t="n">
+      <c r="A48" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>100013179</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>UTROGESTAN 200MG 42CAP BESINS</t>
         </is>
       </c>
-      <c r="D48" s="18" t="n">
+      <c r="D48" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="18" t="n">
+      <c r="E48" s="17" t="n">
         <v>468.79</v>
       </c>
-      <c r="F48" s="19" t="n">
+      <c r="F48" s="18" t="n">
         <v>-468.79</v>
       </c>
-      <c r="G48" s="20" t="n">
+      <c r="G48" s="19" t="n">
         <v>-1</v>
       </c>
-      <c r="H48" s="21" t="n">
+      <c r="H48" s="20" t="n">
         <v>3370</v>
       </c>
-      <c r="I48" s="22" t="n">
+      <c r="I48" s="21" t="n">
         <v>2.68</v>
       </c>
-      <c r="J48" s="15" t="inlineStr">
+      <c r="J48" s="14" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K48" s="18" t="n">
+      <c r="K48" s="17" t="n">
         <v>246.91</v>
       </c>
-      <c r="L48" s="24" t="inlineStr">
+      <c r="L48" s="23" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
-      <c r="M48" s="18" t="n">
+      <c r="M48" s="17" t="n">
         <v>209.07</v>
       </c>
-      <c r="N48" s="28" t="n">
+      <c r="N48" s="25" t="n">
         <v>0.181</v>
       </c>
-      <c r="O48" s="24" t="inlineStr">
+      <c r="O48" s="23" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P48" s="24" t="inlineStr">
+      <c r="P48" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -3194,68 +3351,78 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr"/>
-      <c r="L49" s="13" t="inlineStr"/>
-      <c r="M49" s="12" t="inlineStr"/>
-      <c r="N49" s="14" t="inlineStr"/>
-      <c r="O49" s="13" t="inlineStr">
+      <c r="K49" s="7" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="12" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P49" s="12" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>10052539</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>727.24</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>1174.13</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <v>-446.89</v>
+      </c>
+      <c r="G50" s="19" t="n">
+        <v>-0.381</v>
+      </c>
+      <c r="H50" s="20" t="n">
+        <v>5078</v>
+      </c>
+      <c r="I50" s="21" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K50" s="22" t="inlineStr"/>
+      <c r="L50" s="23" t="inlineStr"/>
+      <c r="M50" s="22" t="inlineStr"/>
+      <c r="N50" s="24" t="inlineStr"/>
+      <c r="O50" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P49" s="13" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>10052539</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
-        </is>
-      </c>
-      <c r="D50" s="18" t="n">
-        <v>727.24</v>
-      </c>
-      <c r="E50" s="18" t="n">
-        <v>1174.13</v>
-      </c>
-      <c r="F50" s="19" t="n">
-        <v>-446.89</v>
-      </c>
-      <c r="G50" s="20" t="n">
-        <v>-0.381</v>
-      </c>
-      <c r="H50" s="21" t="n">
-        <v>5078</v>
-      </c>
-      <c r="I50" s="22" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J50" s="15" t="inlineStr">
-        <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="inlineStr"/>
-      <c r="L50" s="24" t="inlineStr"/>
-      <c r="M50" s="23" t="inlineStr"/>
-      <c r="N50" s="25" t="inlineStr"/>
-      <c r="O50" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P50" s="24" t="inlineStr">
+      <c r="P50" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -3301,7 +3468,7 @@
       <c r="K51" s="7" t="n">
         <v>170.87</v>
       </c>
-      <c r="L51" s="13" t="inlineStr">
+      <c r="L51" s="12" t="inlineStr">
         <is>
           <t>DROGARAIA</t>
         </is>
@@ -3309,67 +3476,77 @@
       <c r="M51" s="7" t="n">
         <v>125.98</v>
       </c>
-      <c r="N51" s="29" t="n">
+      <c r="N51" s="31" t="n">
         <v>0.356</v>
       </c>
-      <c r="O51" s="13" t="inlineStr">
+      <c r="O51" s="12" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P51" s="13" t="inlineStr">
+      <c r="P51" s="12" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="15" t="n">
+      <c r="A52" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>10022882</t>
         </is>
       </c>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>ACICLOVIR 400MG 30CP GEN PRATI</t>
         </is>
       </c>
-      <c r="D52" s="18" t="n">
+      <c r="D52" s="17" t="n">
         <v>214.47</v>
       </c>
-      <c r="E52" s="18" t="n">
+      <c r="E52" s="17" t="n">
         <v>646.23</v>
       </c>
-      <c r="F52" s="19" t="n">
+      <c r="F52" s="18" t="n">
         <v>-431.76</v>
       </c>
-      <c r="G52" s="20" t="n">
+      <c r="G52" s="19" t="n">
         <v>-0.6679999999999999</v>
       </c>
-      <c r="H52" s="21" t="n">
+      <c r="H52" s="20" t="n">
         <v>5328</v>
       </c>
-      <c r="I52" s="22" t="n">
+      <c r="I52" s="21" t="n">
         <v>4.23</v>
       </c>
-      <c r="J52" s="15" t="inlineStr">
+      <c r="J52" s="14" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K52" s="23" t="inlineStr"/>
-      <c r="L52" s="24" t="inlineStr"/>
-      <c r="M52" s="23" t="inlineStr"/>
-      <c r="N52" s="25" t="inlineStr"/>
-      <c r="O52" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P52" s="24" t="inlineStr">
+      <c r="K52" s="17" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="L52" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M52" s="17" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="N52" s="29" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="O52" s="23" t="inlineStr">
+        <is>
+          <t>Líder de Preço</t>
+        </is>
+      </c>
+      <c r="P52" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
@@ -3404,127 +3581,137 @@
       <c r="H53" s="10" t="n">
         <v>1755</v>
       </c>
-      <c r="I53" s="27" t="n">
+      <c r="I53" s="30" t="n">
         <v>1.39</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K53" s="12" t="inlineStr"/>
-      <c r="L53" s="13" t="inlineStr"/>
-      <c r="M53" s="12" t="inlineStr"/>
-      <c r="N53" s="14" t="inlineStr"/>
-      <c r="O53" s="13" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P53" s="13" t="inlineStr">
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>210.44</v>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="N53" s="31" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="O53" s="12" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="15" t="n">
+      <c r="A54" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>100011848</t>
         </is>
       </c>
-      <c r="C54" s="17" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>DES AXE AERO 150ML APOLLO</t>
         </is>
       </c>
-      <c r="D54" s="18" t="n">
+      <c r="D54" s="17" t="n">
         <v>74.3</v>
       </c>
-      <c r="E54" s="18" t="n">
+      <c r="E54" s="17" t="n">
         <v>459.59</v>
       </c>
-      <c r="F54" s="19" t="n">
+      <c r="F54" s="18" t="n">
         <v>-385.29</v>
       </c>
-      <c r="G54" s="20" t="n">
+      <c r="G54" s="19" t="n">
         <v>-0.838</v>
       </c>
-      <c r="H54" s="21" t="n">
+      <c r="H54" s="20" t="n">
         <v>58984</v>
       </c>
-      <c r="I54" s="22" t="n">
+      <c r="I54" s="21" t="n">
         <v>46.85</v>
       </c>
-      <c r="J54" s="15" t="inlineStr">
+      <c r="J54" s="14" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K54" s="18" t="n">
+      <c r="K54" s="17" t="n">
         <v>10.9</v>
       </c>
-      <c r="L54" s="24" t="inlineStr">
+      <c r="L54" s="23" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
-      <c r="M54" s="18" t="n">
+      <c r="M54" s="17" t="n">
         <v>8.98</v>
       </c>
-      <c r="N54" s="28" t="n">
+      <c r="N54" s="25" t="n">
         <v>0.214</v>
       </c>
-      <c r="O54" s="24" t="inlineStr">
+      <c r="O54" s="23" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P54" s="24" t="inlineStr">
+      <c r="P54" s="23" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="31" t="inlineStr">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t>TOTAL TOP 50</t>
         </is>
       </c>
-      <c r="B55" s="32" t="n"/>
-      <c r="C55" s="32" t="n"/>
-      <c r="D55" s="33">
+      <c r="B55" s="33" t="n"/>
+      <c r="C55" s="33" t="n"/>
+      <c r="D55" s="34">
         <f>SUM(D5:D54)</f>
         <v/>
       </c>
-      <c r="E55" s="33">
+      <c r="E55" s="34">
         <f>SUM(E5:E54)</f>
         <v/>
       </c>
-      <c r="F55" s="34">
+      <c r="F55" s="35">
         <f>SUM(F5:F54)</f>
         <v/>
       </c>
-      <c r="G55" s="35">
+      <c r="G55" s="36">
         <f>(D55-E55)/E55</f>
         <v/>
       </c>
-      <c r="H55" s="36">
+      <c r="H55" s="37">
         <f>SUM(H5:H54)</f>
         <v/>
       </c>
-      <c r="I55" s="37" t="inlineStr"/>
-      <c r="J55" s="37" t="inlineStr"/>
-      <c r="K55" s="37" t="inlineStr"/>
-      <c r="L55" s="37" t="inlineStr"/>
-      <c r="M55" s="37" t="inlineStr"/>
-      <c r="N55" s="37" t="inlineStr"/>
-      <c r="O55" s="37" t="inlineStr"/>
-      <c r="P55" s="37" t="inlineStr"/>
+      <c r="I55" s="38" t="inlineStr"/>
+      <c r="J55" s="38" t="inlineStr"/>
+      <c r="K55" s="38" t="inlineStr"/>
+      <c r="L55" s="38" t="inlineStr"/>
+      <c r="M55" s="38" t="inlineStr"/>
+      <c r="N55" s="38" t="inlineStr"/>
+      <c r="O55" s="38" t="inlineStr"/>
+      <c r="P55" s="38" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -246,6 +246,9 @@
     <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -279,6 +282,9 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -304,10 +310,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="10" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -674,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -693,6 +698,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -791,6 +797,11 @@
           <t>Classificação</t>
         </is>
       </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Ação Recomendada</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -853,56 +864,66 @@
           <t>Detrator Crítico</t>
         </is>
       </c>
+      <c r="Q5" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="14" t="n">
+      <c r="A6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>10042969</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>FR PAMPERS CONFORTSEC JUMBO XXG 112UN</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>4012.69</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>12516.41</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>-8503.719999999999</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="20" t="n">
         <v>-0.679</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="21" t="n">
         <v>10635</v>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="22" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr"/>
-      <c r="L6" s="23" t="inlineStr"/>
-      <c r="M6" s="22" t="inlineStr"/>
-      <c r="N6" s="24" t="inlineStr"/>
-      <c r="O6" s="23" t="inlineStr">
+      <c r="K6" s="23" t="inlineStr"/>
+      <c r="L6" s="24" t="inlineStr"/>
+      <c r="M6" s="23" t="inlineStr"/>
+      <c r="N6" s="25" t="inlineStr"/>
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P6" s="24" t="inlineStr">
         <is>
           <t>Detrator Crítico</t>
+        </is>
+      </c>
+      <c r="Q6" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -967,56 +988,66 @@
           <t>Detrator Crítico</t>
         </is>
       </c>
+      <c r="Q7" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>10053130</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>OZIVY 1MG 1CAN 3ML EMS</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>4925.62</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>11345.16</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>-6419.54</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="20" t="n">
         <v>-0.5660000000000001</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="21" t="n">
         <v>12111</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="22" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr"/>
-      <c r="L8" s="23" t="inlineStr"/>
-      <c r="M8" s="22" t="inlineStr"/>
-      <c r="N8" s="24" t="inlineStr"/>
-      <c r="O8" s="23" t="inlineStr">
+      <c r="K8" s="23" t="inlineStr"/>
+      <c r="L8" s="24" t="inlineStr"/>
+      <c r="M8" s="23" t="inlineStr"/>
+      <c r="N8" s="25" t="inlineStr"/>
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P8" s="23" t="inlineStr">
+      <c r="P8" s="24" t="inlineStr">
         <is>
           <t>Detrator Crítico</t>
+        </is>
+      </c>
+      <c r="Q8" s="26" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1081,66 +1112,76 @@
           <t>Detrator Crítico</t>
         </is>
       </c>
+      <c r="Q9" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>10042968</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>2720.52</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>7721.22</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>-5000.7</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <v>-0.648</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="21" t="n">
         <v>2116</v>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="22" t="n">
         <v>1.68</v>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="K10" s="18" t="n">
         <v>159.9</v>
       </c>
-      <c r="L10" s="23" t="inlineStr">
+      <c r="L10" s="24" t="inlineStr">
         <is>
           <t>PANVEL</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="18" t="n">
         <v>149.9</v>
       </c>
-      <c r="N10" s="25" t="n">
+      <c r="N10" s="27" t="n">
         <v>0.067</v>
       </c>
-      <c r="O10" s="23" t="inlineStr">
+      <c r="O10" s="24" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P10" s="23" t="inlineStr">
+      <c r="P10" s="24" t="inlineStr">
         <is>
           <t>Detrator Crítico</t>
+        </is>
+      </c>
+      <c r="Q10" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
         </is>
       </c>
     </row>
@@ -1181,10 +1222,10 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr"/>
+      <c r="K11" s="28" t="inlineStr"/>
       <c r="L11" s="12" t="inlineStr"/>
-      <c r="M11" s="26" t="inlineStr"/>
-      <c r="N11" s="27" t="inlineStr"/>
+      <c r="M11" s="28" t="inlineStr"/>
+      <c r="N11" s="29" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1195,66 +1236,76 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
+      <c r="Q11" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>10040801</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>2523.62</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>-2523.62</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="21" t="n">
         <v>1770</v>
       </c>
-      <c r="I12" s="28" t="n">
+      <c r="I12" s="30" t="n">
         <v>1.41</v>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K12" s="17" t="n">
+      <c r="K12" s="18" t="n">
         <v>1945.09</v>
       </c>
-      <c r="L12" s="23" t="inlineStr">
+      <c r="L12" s="24" t="inlineStr">
         <is>
           <t>PANVEL</t>
         </is>
       </c>
-      <c r="M12" s="17" t="n">
+      <c r="M12" s="18" t="n">
         <v>1945.09</v>
       </c>
-      <c r="N12" s="29" t="n">
+      <c r="N12" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="23" t="inlineStr">
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t>Preço Alinhado</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
+      <c r="P12" s="24" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q12" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1319,56 +1370,66 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
+      <c r="Q13" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>10041262</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>1047.81</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>3042.52</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>-1994.71</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="20" t="n">
         <v>-0.6559999999999999</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="21" t="n">
         <v>2289</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="22" t="n">
         <v>1.82</v>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr"/>
-      <c r="L14" s="23" t="inlineStr"/>
-      <c r="M14" s="22" t="inlineStr"/>
-      <c r="N14" s="24" t="inlineStr"/>
-      <c r="O14" s="23" t="inlineStr">
+      <c r="K14" s="23" t="inlineStr"/>
+      <c r="L14" s="24" t="inlineStr"/>
+      <c r="M14" s="23" t="inlineStr"/>
+      <c r="N14" s="25" t="inlineStr"/>
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P14" s="23" t="inlineStr">
+      <c r="P14" s="24" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q14" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1409,10 +1470,10 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K15" s="26" t="inlineStr"/>
+      <c r="K15" s="28" t="inlineStr"/>
       <c r="L15" s="12" t="inlineStr"/>
-      <c r="M15" s="26" t="inlineStr"/>
-      <c r="N15" s="27" t="inlineStr"/>
+      <c r="M15" s="28" t="inlineStr"/>
+      <c r="N15" s="29" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1423,56 +1484,66 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
+      <c r="Q15" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>10052534</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>571.85</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <v>1968.69</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="19" t="n">
         <v>-1396.84</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="20" t="n">
         <v>-0.71</v>
       </c>
-      <c r="H16" s="20" t="n">
+      <c r="H16" s="21" t="n">
         <v>8641</v>
       </c>
-      <c r="I16" s="21" t="n">
+      <c r="I16" s="22" t="n">
         <v>6.86</v>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr"/>
-      <c r="L16" s="23" t="inlineStr"/>
-      <c r="M16" s="22" t="inlineStr"/>
-      <c r="N16" s="24" t="inlineStr"/>
-      <c r="O16" s="23" t="inlineStr">
+      <c r="K16" s="23" t="inlineStr"/>
+      <c r="L16" s="24" t="inlineStr"/>
+      <c r="M16" s="23" t="inlineStr"/>
+      <c r="N16" s="25" t="inlineStr"/>
+      <c r="O16" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P16" s="23" t="inlineStr">
+      <c r="P16" s="24" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q16" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1576,7 @@
       <c r="H17" s="10" t="n">
         <v>1277</v>
       </c>
-      <c r="I17" s="30" t="n">
+      <c r="I17" s="32" t="n">
         <v>1.01</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1513,10 +1584,10 @@
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K17" s="26" t="inlineStr"/>
+      <c r="K17" s="28" t="inlineStr"/>
       <c r="L17" s="12" t="inlineStr"/>
-      <c r="M17" s="26" t="inlineStr"/>
-      <c r="N17" s="27" t="inlineStr"/>
+      <c r="M17" s="28" t="inlineStr"/>
+      <c r="N17" s="29" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1527,56 +1598,66 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
+      <c r="Q17" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>10041263</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <v>95.90000000000001</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="18" t="n">
         <v>1409.57</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="19" t="n">
         <v>-1313.67</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="20" t="n">
         <v>-0.9320000000000001</v>
       </c>
-      <c r="H18" s="20" t="n">
+      <c r="H18" s="21" t="n">
         <v>3254</v>
       </c>
-      <c r="I18" s="21" t="n">
+      <c r="I18" s="22" t="n">
         <v>2.58</v>
       </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="J18" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K18" s="22" t="inlineStr"/>
-      <c r="L18" s="23" t="inlineStr"/>
-      <c r="M18" s="22" t="inlineStr"/>
-      <c r="N18" s="24" t="inlineStr"/>
-      <c r="O18" s="23" t="inlineStr">
+      <c r="K18" s="23" t="inlineStr"/>
+      <c r="L18" s="24" t="inlineStr"/>
+      <c r="M18" s="23" t="inlineStr"/>
+      <c r="N18" s="25" t="inlineStr"/>
+      <c r="O18" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P18" s="23" t="inlineStr">
+      <c r="P18" s="24" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q18" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1617,10 +1698,10 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K19" s="26" t="inlineStr"/>
+      <c r="K19" s="28" t="inlineStr"/>
       <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="26" t="inlineStr"/>
-      <c r="N19" s="27" t="inlineStr"/>
+      <c r="M19" s="28" t="inlineStr"/>
+      <c r="N19" s="29" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1631,66 +1712,76 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
+      <c r="Q19" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>100016230</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="18" t="n">
         <v>1205.31</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="19" t="n">
         <v>-1205.31</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G20" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="H20" s="20" t="n">
+      <c r="H20" s="21" t="n">
         <v>4849</v>
       </c>
-      <c r="I20" s="21" t="n">
+      <c r="I20" s="22" t="n">
         <v>3.85</v>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="J20" s="15" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K20" s="17" t="n">
+      <c r="K20" s="18" t="n">
         <v>94.98999999999999</v>
       </c>
-      <c r="L20" s="23" t="inlineStr">
+      <c r="L20" s="24" t="inlineStr">
         <is>
           <t>AMAZON</t>
         </is>
       </c>
-      <c r="M20" s="17" t="n">
+      <c r="M20" s="18" t="n">
         <v>49.9</v>
       </c>
-      <c r="N20" s="25" t="n">
+      <c r="N20" s="27" t="n">
         <v>0.904</v>
       </c>
-      <c r="O20" s="23" t="inlineStr">
+      <c r="O20" s="24" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P20" s="23" t="inlineStr">
+      <c r="P20" s="24" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q20" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -1731,10 +1822,10 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K21" s="26" t="inlineStr"/>
+      <c r="K21" s="28" t="inlineStr"/>
       <c r="L21" s="12" t="inlineStr"/>
-      <c r="M21" s="26" t="inlineStr"/>
-      <c r="N21" s="27" t="inlineStr"/>
+      <c r="M21" s="28" t="inlineStr"/>
+      <c r="N21" s="29" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1745,56 +1836,66 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
+      <c r="Q21" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>10042966</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
         </is>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="18" t="n">
         <v>766.9299999999999</v>
       </c>
-      <c r="E22" s="17" t="n">
+      <c r="E22" s="18" t="n">
         <v>1866.75</v>
       </c>
-      <c r="F22" s="18" t="n">
+      <c r="F22" s="19" t="n">
         <v>-1099.82</v>
       </c>
-      <c r="G22" s="19" t="n">
+      <c r="G22" s="20" t="n">
         <v>-0.589</v>
       </c>
-      <c r="H22" s="20" t="n">
+      <c r="H22" s="21" t="n">
         <v>3834</v>
       </c>
-      <c r="I22" s="21" t="n">
+      <c r="I22" s="22" t="n">
         <v>3.05</v>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J22" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K22" s="22" t="inlineStr"/>
-      <c r="L22" s="23" t="inlineStr"/>
-      <c r="M22" s="22" t="inlineStr"/>
-      <c r="N22" s="24" t="inlineStr"/>
-      <c r="O22" s="23" t="inlineStr">
+      <c r="K22" s="23" t="inlineStr"/>
+      <c r="L22" s="24" t="inlineStr"/>
+      <c r="M22" s="23" t="inlineStr"/>
+      <c r="N22" s="25" t="inlineStr"/>
+      <c r="O22" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P22" s="23" t="inlineStr">
+      <c r="P22" s="24" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q22" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1947,7 @@
       <c r="M23" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="N23" s="31" t="n">
+      <c r="N23" s="33" t="n">
         <v>0.396</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
@@ -1859,66 +1960,76 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>10050440</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="18" t="n">
         <v>1030.93</v>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="F24" s="19" t="n">
         <v>-1030.93</v>
       </c>
-      <c r="G24" s="19" t="n">
+      <c r="G24" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="H24" s="20" t="n">
+      <c r="H24" s="21" t="n">
         <v>864</v>
       </c>
-      <c r="I24" s="28" t="n">
+      <c r="I24" s="30" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J24" s="15" t="inlineStr">
         <is>
           <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
-      <c r="K24" s="17" t="n">
+      <c r="K24" s="18" t="n">
         <v>315.46</v>
       </c>
-      <c r="L24" s="23" t="inlineStr">
+      <c r="L24" s="24" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
-      <c r="M24" s="17" t="n">
+      <c r="M24" s="18" t="n">
         <v>236.6</v>
       </c>
-      <c r="N24" s="25" t="n">
+      <c r="N24" s="27" t="n">
         <v>0.333</v>
       </c>
-      <c r="O24" s="23" t="inlineStr">
+      <c r="O24" s="24" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P24" s="23" t="inlineStr">
+      <c r="P24" s="24" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -1983,62 +2094,72 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
+      <c r="Q25" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>10034724</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E26" s="18" t="n">
         <v>944.51</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F26" s="19" t="n">
         <v>-944.51</v>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G26" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="H26" s="20" t="n">
+      <c r="H26" s="21" t="n">
         <v>2108</v>
       </c>
-      <c r="I26" s="21" t="n">
+      <c r="I26" s="22" t="n">
         <v>1.67</v>
       </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="J26" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K26" s="22" t="inlineStr"/>
-      <c r="L26" s="23" t="inlineStr">
+      <c r="K26" s="23" t="inlineStr"/>
+      <c r="L26" s="24" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
-      <c r="M26" s="17" t="n">
+      <c r="M26" s="18" t="n">
         <v>549.9</v>
       </c>
-      <c r="N26" s="24" t="inlineStr"/>
-      <c r="O26" s="23" t="inlineStr">
+      <c r="N26" s="25" t="inlineStr"/>
+      <c r="O26" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P26" s="23" t="inlineStr">
+      <c r="P26" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q26" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2103,56 +2224,66 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q27" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>10052533</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <v>695.4</v>
       </c>
-      <c r="E28" s="17" t="n">
+      <c r="E28" s="18" t="n">
         <v>1568.39</v>
       </c>
-      <c r="F28" s="18" t="n">
+      <c r="F28" s="19" t="n">
         <v>-872.99</v>
       </c>
-      <c r="G28" s="19" t="n">
+      <c r="G28" s="20" t="n">
         <v>-0.5570000000000001</v>
       </c>
-      <c r="H28" s="20" t="n">
+      <c r="H28" s="21" t="n">
         <v>16250</v>
       </c>
-      <c r="I28" s="21" t="n">
+      <c r="I28" s="22" t="n">
         <v>12.91</v>
       </c>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="J28" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K28" s="22" t="inlineStr"/>
-      <c r="L28" s="23" t="inlineStr"/>
-      <c r="M28" s="22" t="inlineStr"/>
-      <c r="N28" s="24" t="inlineStr"/>
-      <c r="O28" s="23" t="inlineStr">
+      <c r="K28" s="23" t="inlineStr"/>
+      <c r="L28" s="24" t="inlineStr"/>
+      <c r="M28" s="23" t="inlineStr"/>
+      <c r="N28" s="25" t="inlineStr"/>
+      <c r="O28" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P28" s="23" t="inlineStr">
+      <c r="P28" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q28" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2316,7 @@
       <c r="H29" s="10" t="n">
         <v>212</v>
       </c>
-      <c r="I29" s="30" t="n">
+      <c r="I29" s="32" t="n">
         <v>0.17</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2193,7 +2324,7 @@
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K29" s="26" t="inlineStr"/>
+      <c r="K29" s="28" t="inlineStr"/>
       <c r="L29" s="12" t="inlineStr">
         <is>
           <t>PANVEL</t>
@@ -2202,7 +2333,7 @@
       <c r="M29" s="7" t="n">
         <v>1212.9</v>
       </c>
-      <c r="N29" s="27" t="inlineStr"/>
+      <c r="N29" s="29" t="inlineStr"/>
       <c r="O29" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2213,56 +2344,66 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q29" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>10053171</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
         </is>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="18" t="n">
         <v>754.62</v>
       </c>
-      <c r="F30" s="18" t="n">
+      <c r="F30" s="19" t="n">
         <v>-754.62</v>
       </c>
-      <c r="G30" s="19" t="n">
+      <c r="G30" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="H30" s="20" t="n">
+      <c r="H30" s="21" t="n">
         <v>1643</v>
       </c>
-      <c r="I30" s="28" t="n">
+      <c r="I30" s="30" t="n">
         <v>1.31</v>
       </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="J30" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K30" s="22" t="inlineStr"/>
-      <c r="L30" s="23" t="inlineStr"/>
-      <c r="M30" s="22" t="inlineStr"/>
-      <c r="N30" s="24" t="inlineStr"/>
-      <c r="O30" s="23" t="inlineStr">
+      <c r="K30" s="23" t="inlineStr"/>
+      <c r="L30" s="24" t="inlineStr"/>
+      <c r="M30" s="23" t="inlineStr"/>
+      <c r="N30" s="25" t="inlineStr"/>
+      <c r="O30" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P30" s="23" t="inlineStr">
+      <c r="P30" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q30" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2455,7 @@
       <c r="M31" s="7" t="n">
         <v>55.67</v>
       </c>
-      <c r="N31" s="31" t="n">
+      <c r="N31" s="33" t="n">
         <v>0.333</v>
       </c>
       <c r="O31" s="12" t="inlineStr">
@@ -2327,66 +2468,76 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>10030120</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>RYBELSUS 7MG 30CP NOVO NORDISK</t>
         </is>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="17" t="n">
+      <c r="E32" s="18" t="n">
         <v>691.48</v>
       </c>
-      <c r="F32" s="18" t="n">
+      <c r="F32" s="19" t="n">
         <v>-691.48</v>
       </c>
-      <c r="G32" s="19" t="n">
+      <c r="G32" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="H32" s="20" t="n">
+      <c r="H32" s="21" t="n">
         <v>2004</v>
       </c>
-      <c r="I32" s="21" t="n">
+      <c r="I32" s="22" t="n">
         <v>1.59</v>
       </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="J32" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K32" s="17" t="n">
+      <c r="K32" s="18" t="n">
         <v>1301.17</v>
       </c>
-      <c r="L32" s="23" t="inlineStr">
+      <c r="L32" s="24" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
-      <c r="M32" s="17" t="n">
+      <c r="M32" s="18" t="n">
         <v>1301.17</v>
       </c>
-      <c r="N32" s="29" t="n">
+      <c r="N32" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="23" t="inlineStr">
+      <c r="O32" s="24" t="inlineStr">
         <is>
           <t>Preço Alinhado</t>
         </is>
       </c>
-      <c r="P32" s="23" t="inlineStr">
+      <c r="P32" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q32" s="26" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2427,10 +2578,10 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K33" s="26" t="inlineStr"/>
+      <c r="K33" s="28" t="inlineStr"/>
       <c r="L33" s="12" t="inlineStr"/>
-      <c r="M33" s="26" t="inlineStr"/>
-      <c r="N33" s="27" t="inlineStr"/>
+      <c r="M33" s="28" t="inlineStr"/>
+      <c r="N33" s="29" t="inlineStr"/>
       <c r="O33" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2441,66 +2592,76 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q33" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>10049094</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="18" t="n">
         <v>203.67</v>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E34" s="18" t="n">
         <v>860.5700000000001</v>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="F34" s="19" t="n">
         <v>-656.9</v>
       </c>
-      <c r="G34" s="19" t="n">
+      <c r="G34" s="20" t="n">
         <v>-0.763</v>
       </c>
-      <c r="H34" s="20" t="n">
+      <c r="H34" s="21" t="n">
         <v>2850</v>
       </c>
-      <c r="I34" s="21" t="n">
+      <c r="I34" s="22" t="n">
         <v>2.26</v>
       </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="J34" s="15" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K34" s="17" t="n">
+      <c r="K34" s="18" t="n">
         <v>218.67</v>
       </c>
-      <c r="L34" s="23" t="inlineStr">
+      <c r="L34" s="24" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
-      <c r="M34" s="17" t="n">
+      <c r="M34" s="18" t="n">
         <v>197.18</v>
       </c>
-      <c r="N34" s="25" t="n">
+      <c r="N34" s="27" t="n">
         <v>0.109</v>
       </c>
-      <c r="O34" s="23" t="inlineStr">
+      <c r="O34" s="24" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P34" s="23" t="inlineStr">
+      <c r="P34" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2713,7 @@
       <c r="M35" s="7" t="n">
         <v>115.9</v>
       </c>
-      <c r="N35" s="31" t="n">
+      <c r="N35" s="33" t="n">
         <v>0.416</v>
       </c>
       <c r="O35" s="12" t="inlineStr">
@@ -2565,66 +2726,76 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 115.90)</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>10097312</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="18" t="n">
         <v>271.96</v>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E36" s="18" t="n">
         <v>841.95</v>
       </c>
-      <c r="F36" s="18" t="n">
+      <c r="F36" s="19" t="n">
         <v>-569.99</v>
       </c>
-      <c r="G36" s="19" t="n">
+      <c r="G36" s="20" t="n">
         <v>-0.677</v>
       </c>
-      <c r="H36" s="20" t="n">
+      <c r="H36" s="21" t="n">
         <v>13240</v>
       </c>
-      <c r="I36" s="21" t="n">
+      <c r="I36" s="22" t="n">
         <v>10.52</v>
       </c>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="J36" s="15" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K36" s="17" t="n">
+      <c r="K36" s="18" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="L36" s="23" t="inlineStr">
+      <c r="L36" s="24" t="inlineStr">
         <is>
           <t>DROGARAIA</t>
         </is>
       </c>
-      <c r="M36" s="17" t="n">
+      <c r="M36" s="18" t="n">
         <v>61.06</v>
       </c>
-      <c r="N36" s="25" t="n">
+      <c r="N36" s="27" t="n">
         <v>0.113</v>
       </c>
-      <c r="O36" s="23" t="inlineStr">
+      <c r="O36" s="24" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P36" s="23" t="inlineStr">
+      <c r="P36" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -2665,10 +2836,10 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K37" s="26" t="inlineStr"/>
+      <c r="K37" s="28" t="inlineStr"/>
       <c r="L37" s="12" t="inlineStr"/>
-      <c r="M37" s="26" t="inlineStr"/>
-      <c r="N37" s="27" t="inlineStr"/>
+      <c r="M37" s="28" t="inlineStr"/>
+      <c r="N37" s="29" t="inlineStr"/>
       <c r="O37" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2679,66 +2850,76 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q37" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>100011547</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>NAN SUPREME 1 800G NESTLE</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="18" t="n">
         <v>132.49</v>
       </c>
-      <c r="E38" s="17" t="n">
+      <c r="E38" s="18" t="n">
         <v>685.71</v>
       </c>
-      <c r="F38" s="18" t="n">
+      <c r="F38" s="19" t="n">
         <v>-553.22</v>
       </c>
-      <c r="G38" s="19" t="n">
+      <c r="G38" s="20" t="n">
         <v>-0.8070000000000001</v>
       </c>
-      <c r="H38" s="20" t="n">
+      <c r="H38" s="21" t="n">
         <v>8308</v>
       </c>
-      <c r="I38" s="21" t="n">
+      <c r="I38" s="22" t="n">
         <v>6.6</v>
       </c>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="J38" s="15" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K38" s="17" t="n">
+      <c r="K38" s="18" t="n">
         <v>132.49</v>
       </c>
-      <c r="L38" s="23" t="inlineStr">
+      <c r="L38" s="24" t="inlineStr">
         <is>
           <t>AMAZON</t>
         </is>
       </c>
-      <c r="M38" s="17" t="n">
+      <c r="M38" s="18" t="n">
         <v>124.19</v>
       </c>
-      <c r="N38" s="25" t="n">
+      <c r="N38" s="27" t="n">
         <v>0.067</v>
       </c>
-      <c r="O38" s="23" t="inlineStr">
+      <c r="O38" s="24" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P38" s="23" t="inlineStr">
+      <c r="P38" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 124.19)</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2971,7 @@
       <c r="M39" s="7" t="n">
         <v>59.9</v>
       </c>
-      <c r="N39" s="31" t="n">
+      <c r="N39" s="33" t="n">
         <v>0.167</v>
       </c>
       <c r="O39" s="12" t="inlineStr">
@@ -2803,56 +2984,66 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="14" t="n">
+      <c r="A40" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>100011549</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="18" t="n">
         <v>264.98</v>
       </c>
-      <c r="E40" s="17" t="n">
+      <c r="E40" s="18" t="n">
         <v>806.87</v>
       </c>
-      <c r="F40" s="18" t="n">
+      <c r="F40" s="19" t="n">
         <v>-541.89</v>
       </c>
-      <c r="G40" s="19" t="n">
+      <c r="G40" s="20" t="n">
         <v>-0.672</v>
       </c>
-      <c r="H40" s="20" t="n">
+      <c r="H40" s="21" t="n">
         <v>7821</v>
       </c>
-      <c r="I40" s="21" t="n">
+      <c r="I40" s="22" t="n">
         <v>6.21</v>
       </c>
-      <c r="J40" s="14" t="inlineStr">
+      <c r="J40" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K40" s="22" t="inlineStr"/>
-      <c r="L40" s="23" t="inlineStr"/>
-      <c r="M40" s="22" t="inlineStr"/>
-      <c r="N40" s="24" t="inlineStr"/>
-      <c r="O40" s="23" t="inlineStr">
+      <c r="K40" s="23" t="inlineStr"/>
+      <c r="L40" s="24" t="inlineStr"/>
+      <c r="M40" s="23" t="inlineStr"/>
+      <c r="N40" s="25" t="inlineStr"/>
+      <c r="O40" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P40" s="23" t="inlineStr">
+      <c r="P40" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q40" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2893,7 +3084,7 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K41" s="26" t="inlineStr"/>
+      <c r="K41" s="28" t="inlineStr"/>
       <c r="L41" s="12" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
@@ -2902,7 +3093,7 @@
       <c r="M41" s="7" t="n">
         <v>988.22</v>
       </c>
-      <c r="N41" s="27" t="inlineStr"/>
+      <c r="N41" s="29" t="inlineStr"/>
       <c r="O41" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2913,66 +3104,76 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q41" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="14" t="n">
+      <c r="A42" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>10097311</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>NESTOGENO 1 800G NESTLE</t>
         </is>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="18" t="n">
         <v>407.94</v>
       </c>
-      <c r="E42" s="17" t="n">
+      <c r="E42" s="18" t="n">
         <v>932.3200000000001</v>
       </c>
-      <c r="F42" s="18" t="n">
+      <c r="F42" s="19" t="n">
         <v>-524.38</v>
       </c>
-      <c r="G42" s="19" t="n">
+      <c r="G42" s="20" t="n">
         <v>-0.5620000000000001</v>
       </c>
-      <c r="H42" s="20" t="n">
+      <c r="H42" s="21" t="n">
         <v>10934</v>
       </c>
-      <c r="I42" s="21" t="n">
+      <c r="I42" s="22" t="n">
         <v>8.68</v>
       </c>
-      <c r="J42" s="14" t="inlineStr">
+      <c r="J42" s="15" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K42" s="17" t="n">
+      <c r="K42" s="18" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="L42" s="23" t="inlineStr">
+      <c r="L42" s="24" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
-      <c r="M42" s="17" t="n">
+      <c r="M42" s="18" t="n">
         <v>62.9</v>
       </c>
-      <c r="N42" s="25" t="n">
+      <c r="N42" s="27" t="n">
         <v>0.081</v>
       </c>
-      <c r="O42" s="23" t="inlineStr">
+      <c r="O42" s="24" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P42" s="23" t="inlineStr">
+      <c r="P42" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q42" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 62.90)</t>
         </is>
       </c>
     </row>
@@ -3013,10 +3214,10 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K43" s="26" t="inlineStr"/>
+      <c r="K43" s="28" t="inlineStr"/>
       <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="26" t="inlineStr"/>
-      <c r="N43" s="27" t="inlineStr"/>
+      <c r="M43" s="28" t="inlineStr"/>
+      <c r="N43" s="29" t="inlineStr"/>
       <c r="O43" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3027,62 +3228,72 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q43" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="14" t="n">
+      <c r="A44" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>10034467</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
         </is>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="17" t="n">
+      <c r="E44" s="18" t="n">
         <v>493.16</v>
       </c>
-      <c r="F44" s="18" t="n">
+      <c r="F44" s="19" t="n">
         <v>-493.16</v>
       </c>
-      <c r="G44" s="19" t="n">
+      <c r="G44" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="H44" s="20" t="n">
+      <c r="H44" s="21" t="n">
         <v>3854</v>
       </c>
-      <c r="I44" s="21" t="n">
+      <c r="I44" s="22" t="n">
         <v>3.06</v>
       </c>
-      <c r="J44" s="14" t="inlineStr">
+      <c r="J44" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K44" s="22" t="inlineStr"/>
-      <c r="L44" s="23" t="inlineStr">
+      <c r="K44" s="23" t="inlineStr"/>
+      <c r="L44" s="24" t="inlineStr">
         <is>
           <t>DROGARAIA</t>
         </is>
       </c>
-      <c r="M44" s="17" t="n">
+      <c r="M44" s="18" t="n">
         <v>234.98</v>
       </c>
-      <c r="N44" s="24" t="inlineStr"/>
-      <c r="O44" s="23" t="inlineStr">
+      <c r="N44" s="25" t="inlineStr"/>
+      <c r="O44" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P44" s="23" t="inlineStr">
+      <c r="P44" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q44" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3326,7 @@
       <c r="H45" s="10" t="n">
         <v>666</v>
       </c>
-      <c r="I45" s="30" t="n">
+      <c r="I45" s="32" t="n">
         <v>0.53</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3123,10 +3334,10 @@
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K45" s="26" t="inlineStr"/>
+      <c r="K45" s="28" t="inlineStr"/>
       <c r="L45" s="12" t="inlineStr"/>
-      <c r="M45" s="26" t="inlineStr"/>
-      <c r="N45" s="27" t="inlineStr"/>
+      <c r="M45" s="28" t="inlineStr"/>
+      <c r="N45" s="29" t="inlineStr"/>
       <c r="O45" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3137,56 +3348,66 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q45" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="14" t="n">
+      <c r="A46" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>10046473</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>ROUPA INT SAO JOAO ADULTO PANTS G/XG 32UN</t>
         </is>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="17" t="n">
+      <c r="E46" s="18" t="n">
         <v>471.47</v>
       </c>
-      <c r="F46" s="18" t="n">
+      <c r="F46" s="19" t="n">
         <v>-471.47</v>
       </c>
-      <c r="G46" s="19" t="n">
+      <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="H46" s="20" t="n">
+      <c r="H46" s="21" t="n">
         <v>19751</v>
       </c>
-      <c r="I46" s="21" t="n">
+      <c r="I46" s="22" t="n">
         <v>15.69</v>
       </c>
-      <c r="J46" s="14" t="inlineStr">
+      <c r="J46" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K46" s="22" t="inlineStr"/>
-      <c r="L46" s="23" t="inlineStr"/>
-      <c r="M46" s="22" t="inlineStr"/>
-      <c r="N46" s="24" t="inlineStr"/>
-      <c r="O46" s="23" t="inlineStr">
+      <c r="K46" s="23" t="inlineStr"/>
+      <c r="L46" s="24" t="inlineStr"/>
+      <c r="M46" s="23" t="inlineStr"/>
+      <c r="N46" s="25" t="inlineStr"/>
+      <c r="O46" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P46" s="23" t="inlineStr">
+      <c r="P46" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q46" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3459,7 @@
       <c r="M47" s="7" t="n">
         <v>15.9</v>
       </c>
-      <c r="N47" s="31" t="n">
+      <c r="N47" s="33" t="n">
         <v>0.629</v>
       </c>
       <c r="O47" s="12" t="inlineStr">
@@ -3251,66 +3472,76 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="14" t="n">
+      <c r="A48" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>100013179</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>UTROGESTAN 200MG 42CAP BESINS</t>
         </is>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="D48" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="17" t="n">
+      <c r="E48" s="18" t="n">
         <v>468.79</v>
       </c>
-      <c r="F48" s="18" t="n">
+      <c r="F48" s="19" t="n">
         <v>-468.79</v>
       </c>
-      <c r="G48" s="19" t="n">
+      <c r="G48" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="H48" s="20" t="n">
+      <c r="H48" s="21" t="n">
         <v>3370</v>
       </c>
-      <c r="I48" s="21" t="n">
+      <c r="I48" s="22" t="n">
         <v>2.68</v>
       </c>
-      <c r="J48" s="14" t="inlineStr">
+      <c r="J48" s="15" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K48" s="17" t="n">
+      <c r="K48" s="18" t="n">
         <v>246.91</v>
       </c>
-      <c r="L48" s="23" t="inlineStr">
+      <c r="L48" s="24" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
-      <c r="M48" s="17" t="n">
+      <c r="M48" s="18" t="n">
         <v>209.07</v>
       </c>
-      <c r="N48" s="25" t="n">
+      <c r="N48" s="27" t="n">
         <v>0.181</v>
       </c>
-      <c r="O48" s="23" t="inlineStr">
+      <c r="O48" s="24" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P48" s="23" t="inlineStr">
+      <c r="P48" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q48" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 209.07)</t>
         </is>
       </c>
     </row>
@@ -3375,56 +3606,66 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q49" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="14" t="n">
+      <c r="A50" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>10052539</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
         </is>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D50" s="18" t="n">
         <v>727.24</v>
       </c>
-      <c r="E50" s="17" t="n">
+      <c r="E50" s="18" t="n">
         <v>1174.13</v>
       </c>
-      <c r="F50" s="18" t="n">
+      <c r="F50" s="19" t="n">
         <v>-446.89</v>
       </c>
-      <c r="G50" s="19" t="n">
+      <c r="G50" s="20" t="n">
         <v>-0.381</v>
       </c>
-      <c r="H50" s="20" t="n">
+      <c r="H50" s="21" t="n">
         <v>5078</v>
       </c>
-      <c r="I50" s="21" t="n">
+      <c r="I50" s="22" t="n">
         <v>4.03</v>
       </c>
-      <c r="J50" s="14" t="inlineStr">
+      <c r="J50" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K50" s="22" t="inlineStr"/>
-      <c r="L50" s="23" t="inlineStr"/>
-      <c r="M50" s="22" t="inlineStr"/>
-      <c r="N50" s="24" t="inlineStr"/>
-      <c r="O50" s="23" t="inlineStr">
+      <c r="K50" s="23" t="inlineStr"/>
+      <c r="L50" s="24" t="inlineStr"/>
+      <c r="M50" s="23" t="inlineStr"/>
+      <c r="N50" s="25" t="inlineStr"/>
+      <c r="O50" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P50" s="23" t="inlineStr">
+      <c r="P50" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q50" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3717,7 @@
       <c r="M51" s="7" t="n">
         <v>125.98</v>
       </c>
-      <c r="N51" s="31" t="n">
+      <c r="N51" s="33" t="n">
         <v>0.356</v>
       </c>
       <c r="O51" s="12" t="inlineStr">
@@ -3489,66 +3730,76 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 125.98)</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="14" t="n">
+      <c r="A52" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>10022882</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
+      <c r="C52" s="17" t="inlineStr">
         <is>
           <t>ACICLOVIR 400MG 30CP GEN PRATI</t>
         </is>
       </c>
-      <c r="D52" s="17" t="n">
+      <c r="D52" s="18" t="n">
         <v>214.47</v>
       </c>
-      <c r="E52" s="17" t="n">
+      <c r="E52" s="18" t="n">
         <v>646.23</v>
       </c>
-      <c r="F52" s="18" t="n">
+      <c r="F52" s="19" t="n">
         <v>-431.76</v>
       </c>
-      <c r="G52" s="19" t="n">
+      <c r="G52" s="20" t="n">
         <v>-0.6679999999999999</v>
       </c>
-      <c r="H52" s="20" t="n">
+      <c r="H52" s="21" t="n">
         <v>5328</v>
       </c>
-      <c r="I52" s="21" t="n">
+      <c r="I52" s="22" t="n">
         <v>4.23</v>
       </c>
-      <c r="J52" s="14" t="inlineStr">
+      <c r="J52" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K52" s="17" t="n">
+      <c r="K52" s="18" t="n">
         <v>71.48999999999999</v>
       </c>
-      <c r="L52" s="23" t="inlineStr">
+      <c r="L52" s="24" t="inlineStr">
         <is>
           <t>PANVEL</t>
         </is>
       </c>
-      <c r="M52" s="17" t="n">
+      <c r="M52" s="18" t="n">
         <v>72.98999999999999</v>
       </c>
-      <c r="N52" s="29" t="n">
+      <c r="N52" s="31" t="n">
         <v>-0.021</v>
       </c>
-      <c r="O52" s="23" t="inlineStr">
+      <c r="O52" s="24" t="inlineStr">
         <is>
           <t>Líder de Preço</t>
         </is>
       </c>
-      <c r="P52" s="23" t="inlineStr">
+      <c r="P52" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q52" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3832,7 @@
       <c r="H53" s="10" t="n">
         <v>1755</v>
       </c>
-      <c r="I53" s="30" t="n">
+      <c r="I53" s="32" t="n">
         <v>1.39</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3600,7 +3851,7 @@
       <c r="M53" s="7" t="n">
         <v>149.99</v>
       </c>
-      <c r="N53" s="31" t="n">
+      <c r="N53" s="33" t="n">
         <v>0.403</v>
       </c>
       <c r="O53" s="12" t="inlineStr">
@@ -3613,105 +3864,113 @@
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Amazon R$ 149.99)</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="14" t="n">
+      <c r="A54" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>100011848</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="C54" s="17" t="inlineStr">
         <is>
           <t>DES AXE AERO 150ML APOLLO</t>
         </is>
       </c>
-      <c r="D54" s="17" t="n">
+      <c r="D54" s="18" t="n">
         <v>74.3</v>
       </c>
-      <c r="E54" s="17" t="n">
+      <c r="E54" s="18" t="n">
         <v>459.59</v>
       </c>
-      <c r="F54" s="18" t="n">
+      <c r="F54" s="19" t="n">
         <v>-385.29</v>
       </c>
-      <c r="G54" s="19" t="n">
+      <c r="G54" s="20" t="n">
         <v>-0.838</v>
       </c>
-      <c r="H54" s="20" t="n">
+      <c r="H54" s="21" t="n">
         <v>58984</v>
       </c>
-      <c r="I54" s="21" t="n">
+      <c r="I54" s="22" t="n">
         <v>46.85</v>
       </c>
-      <c r="J54" s="14" t="inlineStr">
+      <c r="J54" s="15" t="inlineStr">
         <is>
           <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
-      <c r="K54" s="17" t="n">
+      <c r="K54" s="18" t="n">
         <v>10.9</v>
       </c>
-      <c r="L54" s="23" t="inlineStr">
+      <c r="L54" s="24" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
-      <c r="M54" s="17" t="n">
+      <c r="M54" s="18" t="n">
         <v>8.98</v>
       </c>
-      <c r="N54" s="25" t="n">
+      <c r="N54" s="27" t="n">
         <v>0.214</v>
       </c>
-      <c r="O54" s="23" t="inlineStr">
+      <c r="O54" s="24" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P54" s="23" t="inlineStr">
+      <c r="P54" s="24" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 8.98)</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="32" t="inlineStr">
+      <c r="A55" s="34" t="inlineStr">
         <is>
           <t>TOTAL TOP 50</t>
         </is>
       </c>
-      <c r="B55" s="33" t="n"/>
-      <c r="C55" s="33" t="n"/>
-      <c r="D55" s="34">
+      <c r="B55" s="35" t="n"/>
+      <c r="C55" s="35" t="n"/>
+      <c r="D55" s="36">
         <f>SUM(D5:D54)</f>
         <v/>
       </c>
-      <c r="E55" s="34">
+      <c r="E55" s="36">
         <f>SUM(E5:E54)</f>
         <v/>
       </c>
-      <c r="F55" s="35">
+      <c r="F55" s="37">
         <f>SUM(F5:F54)</f>
         <v/>
       </c>
-      <c r="G55" s="36">
+      <c r="G55" s="38">
         <f>(D55-E55)/E55</f>
         <v/>
       </c>
-      <c r="H55" s="37">
-        <f>SUM(H5:H54)</f>
-        <v/>
-      </c>
-      <c r="I55" s="38" t="inlineStr"/>
-      <c r="J55" s="38" t="inlineStr"/>
-      <c r="K55" s="38" t="inlineStr"/>
-      <c r="L55" s="38" t="inlineStr"/>
-      <c r="M55" s="38" t="inlineStr"/>
-      <c r="N55" s="38" t="inlineStr"/>
-      <c r="O55" s="38" t="inlineStr"/>
-      <c r="P55" s="38" t="inlineStr"/>
+      <c r="H55" s="39" t="n"/>
+      <c r="I55" s="39" t="inlineStr"/>
+      <c r="J55" s="39" t="inlineStr"/>
+      <c r="K55" s="39" t="inlineStr"/>
+      <c r="L55" s="39" t="inlineStr"/>
+      <c r="M55" s="39" t="inlineStr"/>
+      <c r="N55" s="39" t="inlineStr"/>
+      <c r="O55" s="39" t="inlineStr"/>
+      <c r="P55" s="39" t="inlineStr"/>
+      <c r="Q55" s="39" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -285,7 +285,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -294,16 +294,16 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 08/09/2026 12:53:08 (12:53) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 08/09/2026 20:52:41 (20:52) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -809,31 +809,31 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10046653</t>
+          <t>10046655</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 5MG 4CAN APLIC LILLY</t>
+          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>19389.87</v>
+        <v>30685</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>43874.73</v>
+        <v>53992.89</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-24484.86</v>
+        <v>-23307.89</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-0.5579999999999999</v>
+        <v>-0.4320000000000001</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>11783</v>
+        <v>3194</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>9.359999999999999</v>
+        <v>2.54</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -841,15 +841,15 @@
         </is>
       </c>
       <c r="K5" s="7" t="n">
-        <v>2382.23</v>
+        <v>3210.85</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
-        <v>2382.23</v>
+        <v>3210.85</v>
       </c>
       <c r="N5" s="13" t="n">
         <v>0</v>
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>4012.69</v>
+        <v>15920.37</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>12516.41</v>
+        <v>37860.58</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-8503.719999999999</v>
+        <v>-21940.21</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>-0.679</v>
+        <v>-0.58</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>10635</v>
@@ -933,39 +933,39 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10046655</t>
+          <t>10042968</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>10695</v>
+        <v>9132.200000000001</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>17849.62</v>
+        <v>23355.74</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-7154.62</v>
+        <v>-14223.54</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.401</v>
+        <v>-0.609</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>3194</v>
+        <v>2116</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>2.54</v>
+        <v>1.68</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3210.85</v>
+        <v>159.9</v>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
@@ -973,14 +973,14 @@
         </is>
       </c>
       <c r="M7" s="7" t="n">
-        <v>3210.85</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>0</v>
+        <v>149.9</v>
+      </c>
+      <c r="N7" s="27" t="n">
+        <v>0.067</v>
       </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
@@ -988,9 +988,9 @@
           <t>Detrator Crítico</t>
         </is>
       </c>
-      <c r="Q7" s="14" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
         </is>
       </c>
     </row>
@@ -1009,16 +1009,16 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>4925.62</v>
+        <v>21887.77</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>11345.16</v>
+        <v>34317.68</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-6419.54</v>
+        <v>-12429.91</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>-0.5660000000000001</v>
+        <v>-0.362</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>12111</v>
@@ -1057,54 +1057,44 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10046652</t>
+          <t>10042967</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO G 128UN</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>24428.3</v>
+        <v>8504.200000000001</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>29606.25</v>
+        <v>18635.58</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-5177.95</v>
+        <v>-10131.38</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.175</v>
+        <v>-0.544</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>9805</v>
+        <v>7624</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>7.79</v>
+        <v>6.06</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K9" s="7" t="n">
-        <v>1905.6</v>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>1905.6</v>
-      </c>
-      <c r="N9" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K9" s="28" t="inlineStr"/>
+      <c r="L9" s="12" t="inlineStr"/>
+      <c r="M9" s="28" t="inlineStr"/>
+      <c r="N9" s="29" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr">
@@ -1114,7 +1104,7 @@
       </c>
       <c r="Q9" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1124,54 +1114,54 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>10042968</t>
+          <t>10050654</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
+          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D10" s="18" t="n">
-        <v>2720.52</v>
+        <v>11071</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>7721.22</v>
+        <v>19886.18</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-5000.7</v>
+        <v>-8815.18</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-0.648</v>
+        <v>-0.4429999999999999</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>2116</v>
+        <v>4215</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>1.68</v>
+        <v>3.35</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K10" s="18" t="n">
-        <v>159.9</v>
+        <v>1617.66</v>
       </c>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M10" s="18" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="N10" s="27" t="n">
-        <v>0.067</v>
+        <v>1617.66</v>
+      </c>
+      <c r="N10" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P10" s="24" t="inlineStr">
@@ -1179,9 +1169,9 @@
           <t>Detrator Crítico</t>
         </is>
       </c>
-      <c r="Q10" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
+      <c r="Q10" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1191,54 +1181,64 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10042967</t>
+          <t>10046653</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO G 128UN</t>
+          <t>MOUNJARO 5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1977.42</v>
+        <v>125121.67</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>6160.78</v>
+        <v>132715.59</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-4183.36</v>
+        <v>-7593.92</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.679</v>
+        <v>-0.057</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>7624</v>
+        <v>11783</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>6.06</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr"/>
-      <c r="M11" s="28" t="inlineStr"/>
-      <c r="N11" s="29" t="inlineStr"/>
+      <c r="K11" s="7" t="n">
+        <v>2382.23</v>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>2382.23</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
       <c r="Q11" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1248,59 +1248,49 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>10046657</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>0</v>
+        <v>4598</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>2523.62</v>
+        <v>11545.02</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-2523.62</v>
+        <v>-6947.02</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>-1</v>
+        <v>-0.602</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>1770</v>
-      </c>
-      <c r="I12" s="30" t="n">
-        <v>1.41</v>
+        <v>1100</v>
+      </c>
+      <c r="I12" s="31" t="n">
+        <v>0.87</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K12" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="L12" s="24" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M12" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="N12" s="31" t="n">
-        <v>0</v>
-      </c>
+      <c r="K12" s="23" t="inlineStr"/>
+      <c r="L12" s="24" t="inlineStr"/>
+      <c r="M12" s="23" t="inlineStr"/>
+      <c r="N12" s="25" t="inlineStr"/>
       <c r="O12" s="24" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P12" s="24" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
       <c r="Q12" s="26" t="inlineStr">
@@ -1315,64 +1305,54 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10041262</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1398</v>
+        <v>4100.94</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3604.14</v>
+        <v>9203.25</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-2206.14</v>
+        <v>-5102.31</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.612</v>
+        <v>-0.5539999999999999</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>3359</v>
+        <v>2289</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>2.67</v>
+        <v>1.82</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K13" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" s="28" t="inlineStr"/>
+      <c r="L13" s="12" t="inlineStr"/>
+      <c r="M13" s="28" t="inlineStr"/>
+      <c r="N13" s="29" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
       <c r="Q13" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1382,44 +1362,54 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>10041262</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>1047.81</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>3042.52</v>
+        <v>3645.93</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-1994.71</v>
+        <v>-3557.72</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>-0.6559999999999999</v>
+        <v>-0.976</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>2289</v>
+        <v>4849</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>1.82</v>
+        <v>3.85</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr"/>
-      <c r="M14" s="23" t="inlineStr"/>
-      <c r="N14" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="N14" s="32" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P14" s="24" t="inlineStr">
@@ -1427,9 +1417,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q14" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q14" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -1439,35 +1429,35 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10004419</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>999</v>
+        <v>621.2</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2522.72</v>
+        <v>4131.58</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-1523.72</v>
+        <v>-3510.38</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-0.604</v>
+        <v>-0.85</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>2511</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>1.99</v>
+        <v>1277</v>
+      </c>
+      <c r="I15" s="33" t="n">
+        <v>1.01</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
@@ -1486,7 +1476,7 @@
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1496,44 +1486,54 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>571.85</v>
+        <v>4197</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>1968.69</v>
+        <v>7633.63</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-1396.84</v>
+        <v>-3436.63</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>-0.71</v>
+        <v>-0.45</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>8641</v>
-      </c>
-      <c r="I16" s="22" t="n">
-        <v>6.86</v>
+        <v>1770</v>
+      </c>
+      <c r="I16" s="31" t="n">
+        <v>1.41</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr"/>
-      <c r="M16" s="23" t="inlineStr"/>
-      <c r="N16" s="25" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="L16" s="24" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="N16" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P16" s="24" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="Q16" s="26" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1553,35 +1553,35 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10042966</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0</v>
+        <v>2332.26</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1365.87</v>
+        <v>5646.69</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-1365.87</v>
+        <v>-3314.43</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-1</v>
+        <v>-0.5870000000000001</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>1277</v>
-      </c>
-      <c r="I17" s="32" t="n">
-        <v>1.01</v>
+        <v>3834</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>3.05</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="D18" s="18" t="n">
-        <v>95.90000000000001</v>
+        <v>1148.24</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>1409.57</v>
+        <v>4263.78</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-1313.67</v>
+        <v>-3115.54</v>
       </c>
       <c r="G18" s="20" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.731</v>
       </c>
       <c r="H18" s="21" t="n">
         <v>3254</v>
@@ -1667,44 +1667,54 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10052532</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2247.93</v>
+        <v>12410</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>3548.83</v>
+        <v>15427.32</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-1300.9</v>
+        <v>-3017.32</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-0.367</v>
+        <v>-0.196</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>16881</v>
+        <v>9899</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>13.41</v>
+        <v>7.86</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="28" t="inlineStr"/>
-      <c r="N19" s="29" t="inlineStr"/>
+      <c r="K19" s="7" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P19" s="12" t="inlineStr">
@@ -1724,50 +1734,50 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>0</v>
+        <v>251.09</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>1205.31</v>
+        <v>3118.44</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-1205.31</v>
+        <v>-2867.35</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>-1</v>
+        <v>-0.919</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>4849</v>
-      </c>
-      <c r="I20" s="22" t="n">
-        <v>3.85</v>
+        <v>864</v>
+      </c>
+      <c r="I20" s="31" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K20" s="18" t="n">
-        <v>94.98999999999999</v>
+        <v>315.46</v>
       </c>
       <c r="L20" s="24" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M20" s="18" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N20" s="27" t="n">
-        <v>0.904</v>
+        <v>236.6</v>
+      </c>
+      <c r="N20" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="O20" s="24" t="inlineStr">
         <is>
@@ -1781,7 +1791,7 @@
       </c>
       <c r="Q20" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -1800,16 +1810,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>73.98999999999999</v>
+        <v>872.84</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1191.95</v>
+        <v>3605.49</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-1117.96</v>
+        <v>-2732.65</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.758</v>
       </c>
       <c r="H21" s="10" t="n">
         <v>40618</v>
@@ -1848,31 +1858,31 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10042966</t>
+          <t>10004419</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
+          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>766.9299999999999</v>
+        <v>4995</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>1866.75</v>
+        <v>7630.9</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-1099.82</v>
+        <v>-2635.9</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>-0.589</v>
+        <v>-0.345</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>3834</v>
+        <v>2511</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>3.05</v>
+        <v>1.99</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
@@ -1895,7 +1905,7 @@
       </c>
       <c r="Q22" s="26" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1914,16 +1924,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>149.4</v>
+        <v>1040.15</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1199.41</v>
+        <v>3628.07</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-1050.01</v>
+        <v>-2587.92</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.875</v>
+        <v>-0.713</v>
       </c>
       <c r="H23" s="10" t="n">
         <v>4074</v>
@@ -1947,7 +1957,7 @@
       <c r="M23" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="N23" s="33" t="n">
+      <c r="N23" s="27" t="n">
         <v>0.396</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
@@ -1972,54 +1982,54 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
+        <v>8391</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>10902.07</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>-2511.07</v>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>3359</v>
+      </c>
+      <c r="I24" s="22" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L24" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M24" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N24" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="18" t="n">
-        <v>1030.93</v>
-      </c>
-      <c r="F24" s="19" t="n">
-        <v>-1030.93</v>
-      </c>
-      <c r="G24" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H24" s="21" t="n">
-        <v>864</v>
-      </c>
-      <c r="I24" s="30" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K24" s="18" t="n">
-        <v>315.46</v>
-      </c>
-      <c r="L24" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N24" s="27" t="n">
-        <v>0.333</v>
-      </c>
       <c r="O24" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P24" s="24" t="inlineStr">
@@ -2027,9 +2037,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q24" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+      <c r="Q24" s="26" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2039,39 +2049,39 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>4095</v>
+        <v>944.33</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>5100.15</v>
+        <v>3396.69</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-1005.15</v>
+        <v>-2452.36</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.197</v>
+        <v>-0.722</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>9899</v>
+        <v>17247</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>7.86</v>
+        <v>13.7</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K25" s="7" t="n">
-        <v>988.22</v>
+        <v>74.22</v>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
@@ -2079,14 +2089,14 @@
         </is>
       </c>
       <c r="M25" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N25" s="13" t="n">
-        <v>0</v>
+        <v>55.67</v>
+      </c>
+      <c r="N25" s="27" t="n">
+        <v>0.333</v>
       </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr">
@@ -2094,9 +2104,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q25" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -2106,55 +2116,59 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
+        <v>2805</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>5097.27</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>-2292.27</v>
+      </c>
+      <c r="G26" s="20" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>6401</v>
+      </c>
+      <c r="I26" s="22" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="J26" s="15" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>831.76</v>
+      </c>
+      <c r="L26" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M26" s="18" t="n">
+        <v>831.76</v>
+      </c>
+      <c r="N26" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="18" t="n">
-        <v>944.51</v>
-      </c>
-      <c r="F26" s="19" t="n">
-        <v>-944.51</v>
-      </c>
-      <c r="G26" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H26" s="21" t="n">
-        <v>2108</v>
-      </c>
-      <c r="I26" s="22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M26" s="18" t="n">
-        <v>549.9</v>
-      </c>
-      <c r="N26" s="25" t="inlineStr"/>
       <c r="O26" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P26" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q26" s="26" t="inlineStr">
@@ -2169,31 +2183,31 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10030119</t>
+          <t>10050642</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
+          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1150</v>
+        <v>3250</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>2074.45</v>
+        <v>5501.96</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-924.45</v>
+        <v>-2251.96</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.446</v>
+        <v>-0.409</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>2918</v>
+        <v>5949</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>2.32</v>
+        <v>4.73</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2201,7 +2215,7 @@
         </is>
       </c>
       <c r="K27" s="7" t="n">
-        <v>1301.17</v>
+        <v>955.85</v>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
@@ -2209,7 +2223,7 @@
         </is>
       </c>
       <c r="M27" s="7" t="n">
-        <v>1301.17</v>
+        <v>955.85</v>
       </c>
       <c r="N27" s="13" t="n">
         <v>0</v>
@@ -2221,12 +2235,12 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2236,54 +2250,64 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>695.4</v>
+        <v>412.04</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>1568.39</v>
+        <v>2603.13</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-872.99</v>
+        <v>-2191.09</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.8420000000000001</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>16250</v>
+        <v>2850</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>12.91</v>
+        <v>2.26</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr"/>
-      <c r="M28" s="23" t="inlineStr"/>
-      <c r="N28" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K28" s="18" t="n">
+        <v>218.67</v>
+      </c>
+      <c r="L28" s="24" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M28" s="18" t="n">
+        <v>197.18</v>
+      </c>
+      <c r="N28" s="32" t="n">
+        <v>0.109</v>
+      </c>
       <c r="O28" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P28" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q28" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q28" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -2293,46 +2317,40 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10025098</t>
+          <t>10052532</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0</v>
+        <v>8632.889999999999</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>782.49</v>
+        <v>10734.78</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-782.49</v>
+        <v>-2101.89</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-1</v>
+        <v>-0.196</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>212</v>
-      </c>
-      <c r="I29" s="32" t="n">
-        <v>0.17</v>
+        <v>16881</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>13.41</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K29" s="28" t="inlineStr"/>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>1212.9</v>
-      </c>
+      <c r="L29" s="12" t="inlineStr"/>
+      <c r="M29" s="28" t="inlineStr"/>
       <c r="N29" s="29" t="inlineStr"/>
       <c r="O29" s="12" t="inlineStr">
         <is>
@@ -2341,12 +2359,12 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2356,35 +2374,35 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10053171</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
-        <v>0</v>
+        <v>4040.38</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>754.62</v>
+        <v>5955.04</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-754.62</v>
+        <v>-1914.66</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>-1</v>
+        <v>-0.322</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>1643</v>
-      </c>
-      <c r="I30" s="30" t="n">
-        <v>1.31</v>
+        <v>8641</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>6.86</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr"/>
@@ -2398,12 +2416,12 @@
       </c>
       <c r="P30" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q30" s="26" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2413,64 +2431,60 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>379</v>
+        <v>1033.8</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>1122.92</v>
+        <v>2857.03</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-743.92</v>
+        <v>-1823.23</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-0.662</v>
+        <v>-0.638</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>17247</v>
+        <v>2108</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>13.7</v>
+        <v>1.67</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>74.22</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K31" s="28" t="inlineStr"/>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M31" s="7" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N31" s="33" t="n">
-        <v>0.333</v>
-      </c>
+        <v>549.9</v>
+      </c>
+      <c r="N31" s="29" t="inlineStr"/>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q31" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2480,64 +2494,54 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10030120</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>RYBELSUS 7MG 30CP NOVO NORDISK</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
-        <v>0</v>
+        <v>204.57</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>691.48</v>
+        <v>2015.55</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-691.48</v>
+        <v>-1810.98</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>-1</v>
+        <v>-0.899</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>2004</v>
+        <v>12080</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>1.59</v>
+        <v>9.59</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K32" s="18" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="L32" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M32" s="18" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="N32" s="31" t="n">
-        <v>0</v>
-      </c>
+      <c r="K32" s="23" t="inlineStr"/>
+      <c r="L32" s="24" t="inlineStr"/>
+      <c r="M32" s="23" t="inlineStr"/>
+      <c r="N32" s="25" t="inlineStr"/>
       <c r="O32" s="24" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P32" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q32" s="26" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2547,31 +2551,31 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>100011549</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>340.62</v>
+        <v>662.45</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1029.57</v>
+        <v>2440.67</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-688.95</v>
+        <v>-1778.22</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.669</v>
+        <v>-0.7290000000000001</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>11671</v>
+        <v>7821</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>9.27</v>
+        <v>6.21</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2589,7 +2593,7 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q33" s="14" t="inlineStr">
@@ -2604,31 +2608,31 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10101654</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>NAN COMFOR 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>203.67</v>
+        <v>1049.88</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>860.5700000000001</v>
+        <v>2820.44</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-656.9</v>
+        <v>-1770.56</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>-0.763</v>
+        <v>-0.628</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>2850</v>
+        <v>13826</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>2.26</v>
+        <v>10.98</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -2636,18 +2640,18 @@
         </is>
       </c>
       <c r="K34" s="18" t="n">
-        <v>218.67</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="L34" s="24" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M34" s="18" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N34" s="27" t="n">
-        <v>0.109</v>
+        <v>79.98999999999999</v>
+      </c>
+      <c r="N34" s="32" t="n">
+        <v>0.094</v>
       </c>
       <c r="O34" s="24" t="inlineStr">
         <is>
@@ -2656,12 +2660,12 @@
       </c>
       <c r="P34" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q34" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Reprecificar no Digital (Amazon R$ 79.99)</t>
         </is>
       </c>
     </row>
@@ -2671,64 +2675,54 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10028895</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>IZIZ 2,5MG+1,5MG 84CP LIBBS</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>287.47</v>
+        <v>3028.45</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>859.91</v>
+        <v>4744.17</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-572.4400000000001</v>
+        <v>-1715.72</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-0.6659999999999999</v>
+        <v>-0.362</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>4477</v>
+        <v>16250</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>3.56</v>
+        <v>12.91</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>164.09</v>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M35" s="7" t="n">
-        <v>115.9</v>
-      </c>
-      <c r="N35" s="33" t="n">
-        <v>0.416</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K35" s="28" t="inlineStr"/>
+      <c r="L35" s="12" t="inlineStr"/>
+      <c r="M35" s="28" t="inlineStr"/>
+      <c r="N35" s="29" t="inlineStr"/>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 115.90)</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q35" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2738,64 +2732,60 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10050634</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>EXTENSIOR 1MG 3ML NOVO EUROFARMA</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
-        <v>271.96</v>
+        <v>927</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>841.95</v>
+        <v>2551.82</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-569.99</v>
+        <v>-1624.82</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>-0.677</v>
+        <v>-0.637</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>13240</v>
+        <v>4354</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>10.52</v>
+        <v>3.46</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K36" s="18" t="n">
-        <v>67.98999999999999</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr"/>
       <c r="L36" s="24" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M36" s="18" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N36" s="27" t="n">
-        <v>0.113</v>
-      </c>
+        <v>988.22</v>
+      </c>
+      <c r="N36" s="25" t="inlineStr"/>
       <c r="O36" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P36" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q36" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2805,54 +2795,64 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10033463</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>98.58</v>
+        <v>2983</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>666.3200000000001</v>
+        <v>4591.13</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-567.74</v>
+        <v>-1608.13</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.852</v>
+        <v>-0.35</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>12080</v>
+        <v>12293</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>9.59</v>
+        <v>9.76</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K37" s="28" t="inlineStr"/>
-      <c r="L37" s="12" t="inlineStr"/>
-      <c r="M37" s="28" t="inlineStr"/>
-      <c r="N37" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="N37" s="27" t="n">
+        <v>0.167</v>
+      </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q37" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
         </is>
       </c>
     </row>
@@ -2862,31 +2862,31 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>100011547</t>
+          <t>10097311</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>NAN SUPREME 1 800G NESTLE</t>
+          <t>NESTOGENO 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
-        <v>132.49</v>
+        <v>1223.82</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>685.71</v>
+        <v>2820.16</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-553.22</v>
+        <v>-1596.34</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.5660000000000001</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>8308</v>
+        <v>10934</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>6.6</v>
+        <v>8.68</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -2894,18 +2894,18 @@
         </is>
       </c>
       <c r="K38" s="18" t="n">
-        <v>132.49</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L38" s="24" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M38" s="18" t="n">
-        <v>124.19</v>
-      </c>
-      <c r="N38" s="27" t="n">
-        <v>0.067</v>
+        <v>62.9</v>
+      </c>
+      <c r="N38" s="32" t="n">
+        <v>0.081</v>
       </c>
       <c r="O38" s="24" t="inlineStr">
         <is>
@@ -2914,12 +2914,12 @@
       </c>
       <c r="P38" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q38" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 124.19)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 62.90)</t>
         </is>
       </c>
     </row>
@@ -2929,31 +2929,31 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10033463</t>
+          <t>10001096</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
+          <t>TOALHAS UMED HUGGIES 192UN RECEM NASCIDO</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>969.96</v>
+        <v>2210.29</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1517.79</v>
+        <v>3764.33</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-547.83</v>
+        <v>-1554.04</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.361</v>
+        <v>-0.413</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>12293</v>
+        <v>10126</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>9.76</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2961,18 +2961,18 @@
         </is>
       </c>
       <c r="K39" s="7" t="n">
-        <v>69.90000000000001</v>
+        <v>38.9</v>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M39" s="7" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="N39" s="33" t="n">
-        <v>0.167</v>
+        <v>35.9</v>
+      </c>
+      <c r="N39" s="27" t="n">
+        <v>0.08400000000000001</v>
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
+          <t>Reprecificar no Digital (Panvel R$ 35.90)</t>
         </is>
       </c>
     </row>
@@ -2996,54 +2996,64 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>100011549</t>
+          <t>100011547</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
+          <t>NAN SUPREME 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>264.98</v>
+        <v>536.7</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>806.87</v>
+        <v>2074.18</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-541.89</v>
+        <v>-1537.48</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>-0.672</v>
+        <v>-0.741</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>7821</v>
+        <v>8308</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>6.21</v>
+        <v>6.6</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr"/>
-      <c r="L40" s="24" t="inlineStr"/>
-      <c r="M40" s="23" t="inlineStr"/>
-      <c r="N40" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K40" s="18" t="n">
+        <v>132.49</v>
+      </c>
+      <c r="L40" s="24" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M40" s="18" t="n">
+        <v>124.19</v>
+      </c>
+      <c r="N40" s="32" t="n">
+        <v>0.067</v>
+      </c>
       <c r="O40" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P40" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q40" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 124.19)</t>
         </is>
       </c>
     </row>
@@ -3053,31 +3063,31 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10050634</t>
+          <t>10034467</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>EXTENSIOR 1MG 3ML NOVO EUROFARMA</t>
+          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>843.61</v>
+        <v>1491.74</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-534.61</v>
+        <v>-1491.74</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-0.634</v>
+        <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>4354</v>
+        <v>3854</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>3.46</v>
+        <v>3.06</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -3087,11 +3097,11 @@
       <c r="K41" s="28" t="inlineStr"/>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
-        <v>988.22</v>
+        <v>234.98</v>
       </c>
       <c r="N41" s="29" t="inlineStr"/>
       <c r="O41" s="12" t="inlineStr">
@@ -3101,7 +3111,7 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q41" s="14" t="inlineStr">
@@ -3116,64 +3126,54 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10097311</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>NESTOGENO 1 800G NESTLE</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>407.94</v>
+        <v>1195.6</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>932.3200000000001</v>
+        <v>2680.14</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-524.38</v>
+        <v>-1484.54</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.5539999999999999</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>10934</v>
+        <v>26558</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>8.68</v>
+        <v>21.09</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K42" s="18" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="L42" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M42" s="18" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="N42" s="27" t="n">
-        <v>0.081</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr"/>
+      <c r="L42" s="24" t="inlineStr"/>
+      <c r="M42" s="23" t="inlineStr"/>
+      <c r="N42" s="25" t="inlineStr"/>
       <c r="O42" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P42" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q42" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 62.90)</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q42" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3183,49 +3183,59 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>10022882</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>ACICLOVIR 400MG 30CP GEN PRATI</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>149.5</v>
+        <v>491.46</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>642.96</v>
+        <v>1954.75</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-493.46</v>
+        <v>-1463.29</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-0.767</v>
+        <v>-0.7490000000000001</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>10271</v>
+        <v>5328</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>8.16</v>
+        <v>4.23</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K43" s="28" t="inlineStr"/>
-      <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="28" t="inlineStr"/>
-      <c r="N43" s="29" t="inlineStr"/>
+      <c r="K43" s="7" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>-0.021</v>
+      </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q43" s="14" t="inlineStr">
@@ -3240,31 +3250,31 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>10034467</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>0</v>
+        <v>351.15</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>493.16</v>
+        <v>1811.88</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-493.16</v>
+        <v>-1460.73</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>-1</v>
+        <v>-0.8059999999999999</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>3854</v>
+        <v>31066</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>3.06</v>
+        <v>24.68</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
@@ -3272,14 +3282,8 @@
         </is>
       </c>
       <c r="K44" s="23" t="inlineStr"/>
-      <c r="L44" s="24" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M44" s="18" t="n">
-        <v>234.98</v>
-      </c>
+      <c r="L44" s="24" t="inlineStr"/>
+      <c r="M44" s="23" t="inlineStr"/>
       <c r="N44" s="25" t="inlineStr"/>
       <c r="O44" s="24" t="inlineStr">
         <is>
@@ -3288,7 +3292,7 @@
       </c>
       <c r="P44" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q44" s="26" t="inlineStr">
@@ -3303,54 +3307,64 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10041858</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0</v>
+        <v>1098.84</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>471.74</v>
+        <v>2546.78</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-471.74</v>
+        <v>-1447.94</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-1</v>
+        <v>-0.569</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>666</v>
-      </c>
-      <c r="I45" s="32" t="n">
-        <v>0.53</v>
+        <v>13240</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>10.52</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K45" s="28" t="inlineStr"/>
-      <c r="L45" s="12" t="inlineStr"/>
-      <c r="M45" s="28" t="inlineStr"/>
-      <c r="N45" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="N45" s="27" t="n">
+        <v>0.113</v>
+      </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q45" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -3360,35 +3374,35 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10046473</t>
+          <t>10041858</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>ROUPA INT SAO JOAO ADULTO PANTS G/XG 32UN</t>
+          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>471.47</v>
+        <v>1426.96</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-471.47</v>
+        <v>-1426.96</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>19751</v>
-      </c>
-      <c r="I46" s="22" t="n">
-        <v>15.69</v>
+        <v>666</v>
+      </c>
+      <c r="I46" s="31" t="n">
+        <v>0.53</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr"/>
@@ -3402,12 +3416,12 @@
       </c>
       <c r="P46" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q46" s="26" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3417,31 +3431,31 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>100013179</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>UTROGESTAN 200MG 42CAP BESINS</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>77.7</v>
+        <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>547.76</v>
+        <v>1418.03</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-470.06</v>
+        <v>-1418.03</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-0.858</v>
+        <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>23012</v>
+        <v>3370</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>18.28</v>
+        <v>2.68</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3449,7 +3463,7 @@
         </is>
       </c>
       <c r="K47" s="7" t="n">
-        <v>25.9</v>
+        <v>246.91</v>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
@@ -3457,10 +3471,10 @@
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N47" s="33" t="n">
-        <v>0.629</v>
+        <v>209.07</v>
+      </c>
+      <c r="N47" s="27" t="n">
+        <v>0.181</v>
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
@@ -3469,12 +3483,12 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 209.07)</t>
         </is>
       </c>
     </row>
@@ -3484,64 +3498,54 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>100013179</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>UTROGESTAN 200MG 42CAP BESINS</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>0</v>
+        <v>544.21</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>468.79</v>
+        <v>1944.88</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-468.79</v>
+        <v>-1400.67</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>-1</v>
+        <v>-0.72</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>3370</v>
+        <v>10271</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>2.68</v>
+        <v>8.16</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K48" s="18" t="n">
-        <v>246.91</v>
-      </c>
-      <c r="L48" s="24" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M48" s="18" t="n">
-        <v>209.07</v>
-      </c>
-      <c r="N48" s="27" t="n">
-        <v>0.181</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="inlineStr"/>
+      <c r="L48" s="24" t="inlineStr"/>
+      <c r="M48" s="23" t="inlineStr"/>
+      <c r="N48" s="25" t="inlineStr"/>
       <c r="O48" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P48" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q48" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 209.07)</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q48" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3551,59 +3555,49 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10050654</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>6120</v>
+        <v>1714.08</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>6574.22</v>
+        <v>3114.33</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-454.22</v>
+        <v>-1400.25</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.45</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>4215</v>
+        <v>11671</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>3.35</v>
+        <v>9.27</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K49" s="7" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="N49" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K49" s="28" t="inlineStr"/>
+      <c r="L49" s="12" t="inlineStr"/>
+      <c r="M49" s="28" t="inlineStr"/>
+      <c r="N49" s="29" t="inlineStr"/>
       <c r="O49" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q49" s="14" t="inlineStr">
@@ -3618,31 +3612,31 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>10052539</t>
+          <t>10033461</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
+          <t>FR BABYSEC ULTRA HIPER G 60UN</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>727.24</v>
+        <v>1758.4</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>1174.13</v>
+        <v>3108.42</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-446.89</v>
+        <v>-1350.02</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>-0.381</v>
+        <v>-0.434</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>5078</v>
+        <v>11917</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>4.03</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
@@ -3660,7 +3654,7 @@
       </c>
       <c r="P50" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q50" s="26" t="inlineStr">
@@ -3675,31 +3669,31 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>SYSTEN CONTI 8 ADESIVOS THERAMEX</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0</v>
+        <v>353.6</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>446.52</v>
+        <v>1656.92</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-446.52</v>
+        <v>-1303.32</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-1</v>
+        <v>-0.787</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>5661</v>
+        <v>23012</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>4.5</v>
+        <v>18.28</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -3707,18 +3701,18 @@
         </is>
       </c>
       <c r="K51" s="7" t="n">
-        <v>170.87</v>
+        <v>25.9</v>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
-        <v>125.98</v>
-      </c>
-      <c r="N51" s="33" t="n">
-        <v>0.356</v>
+        <v>15.9</v>
+      </c>
+      <c r="N51" s="27" t="n">
+        <v>0.629</v>
       </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
@@ -3727,12 +3721,12 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 125.98)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -3742,59 +3736,49 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>10022882</t>
+          <t>100012751</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>ACICLOVIR 400MG 30CP GEN PRATI</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIG SUPERIOR</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>214.47</v>
+        <v>538.64</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>646.23</v>
+        <v>1807</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-431.76</v>
+        <v>-1268.36</v>
       </c>
       <c r="G52" s="20" t="n">
-        <v>-0.6679999999999999</v>
+        <v>-0.7020000000000001</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>5328</v>
+        <v>14619</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>4.23</v>
+        <v>11.61</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K52" s="18" t="n">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="L52" s="24" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M52" s="18" t="n">
-        <v>72.98999999999999</v>
-      </c>
-      <c r="N52" s="31" t="n">
-        <v>-0.021</v>
-      </c>
+      <c r="K52" s="23" t="inlineStr"/>
+      <c r="L52" s="24" t="inlineStr"/>
+      <c r="M52" s="23" t="inlineStr"/>
+      <c r="N52" s="25" t="inlineStr"/>
       <c r="O52" s="24" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P52" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q52" s="26" t="inlineStr">
@@ -3809,50 +3793,50 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>10034591</t>
+          <t>100011848</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>PANTOGAR NEO 90CAP BIOLAB</t>
+          <t>DES AXE AERO 150ML APOLLO</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0</v>
+        <v>207.1</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>429.57</v>
+        <v>1390.2</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-429.57</v>
+        <v>-1183.1</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>-1</v>
+        <v>-0.851</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>1755</v>
-      </c>
-      <c r="I53" s="32" t="n">
-        <v>1.39</v>
+        <v>58984</v>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>46.85</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K53" s="7" t="n">
-        <v>210.44</v>
+        <v>10.9</v>
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M53" s="7" t="n">
-        <v>149.99</v>
-      </c>
-      <c r="N53" s="33" t="n">
-        <v>0.403</v>
+        <v>8.98</v>
+      </c>
+      <c r="N53" s="27" t="n">
+        <v>0.214</v>
       </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
@@ -3861,12 +3845,12 @@
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Amazon R$ 149.99)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 8.98)</t>
         </is>
       </c>
     </row>
@@ -3876,39 +3860,39 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>100011848</t>
+          <t>10037713</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>DES AXE AERO 150ML APOLLO</t>
+          <t>RELUZE 60CAP GBIO</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>74.3</v>
+        <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>459.59</v>
+        <v>1146.52</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-385.29</v>
+        <v>-1146.52</v>
       </c>
       <c r="G54" s="20" t="n">
-        <v>-0.838</v>
+        <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>58984</v>
+        <v>2307</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>46.85</v>
+        <v>1.83</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K54" s="18" t="n">
-        <v>10.9</v>
+        <v>106.8</v>
       </c>
       <c r="L54" s="24" t="inlineStr">
         <is>
@@ -3916,10 +3900,10 @@
         </is>
       </c>
       <c r="M54" s="18" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="N54" s="27" t="n">
-        <v>0.214</v>
+        <v>103.85</v>
+      </c>
+      <c r="N54" s="32" t="n">
+        <v>0.028</v>
       </c>
       <c r="O54" s="24" t="inlineStr">
         <is>
@@ -3928,12 +3912,12 @@
       </c>
       <c r="P54" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q54" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 8.98)</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q54" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -285,7 +285,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -300,10 +300,10 @@
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 08/09/2026 20:52:41 (20:52) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 08/09/2026 21:52:45 (21:52) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>30685</v>
+        <v>26687</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>53992.89</v>
+        <v>57177.97</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-23307.89</v>
+        <v>-30490.97</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-0.4320000000000001</v>
+        <v>-0.5329999999999999</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>3194</v>
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>15920.37</v>
+        <v>17121.48</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>37860.58</v>
+        <v>40094</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-21940.21</v>
+        <v>-22972.52</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>-0.58</v>
+        <v>-0.573</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>10635</v>
@@ -933,54 +933,54 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10042968</t>
+          <t>10046653</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
+          <t>MOUNJARO 5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>9132.200000000001</v>
+        <v>123526.1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>23355.74</v>
+        <v>140544.58</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-14223.54</v>
+        <v>-17018.48</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.609</v>
+        <v>-0.121</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>2116</v>
+        <v>11783</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>1.68</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K7" s="7" t="n">
-        <v>159.9</v>
+        <v>2382.23</v>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M7" s="7" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="N7" s="27" t="n">
-        <v>0.067</v>
+        <v>2382.23</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
@@ -988,9 +988,9 @@
           <t>Detrator Crítico</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
+      <c r="Q7" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1000,44 +1000,54 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>10053130</t>
+          <t>10042968</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>OZIVY 1MG 1CAN 3ML EMS</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>21887.77</v>
+        <v>8973.84</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>34317.68</v>
+        <v>24733.51</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-12429.91</v>
+        <v>-15759.67</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>-0.362</v>
+        <v>-0.637</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>12111</v>
+        <v>2116</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>9.619999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr"/>
-      <c r="M8" s="23" t="inlineStr"/>
-      <c r="N8" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="N8" s="27" t="n">
+        <v>0.067</v>
+      </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P8" s="24" t="inlineStr">
@@ -1045,9 +1055,9 @@
           <t>Detrator Crítico</t>
         </is>
       </c>
-      <c r="Q8" s="26" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="Q8" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
         </is>
       </c>
     </row>
@@ -1057,31 +1067,31 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10042967</t>
+          <t>10053130</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO G 128UN</t>
+          <t>OZIVY 1MG 1CAN 3ML EMS</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8504.200000000001</v>
+        <v>21887.77</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>18635.58</v>
+        <v>36342.11</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-10131.38</v>
+        <v>-14454.34</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.544</v>
+        <v>-0.398</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7624</v>
+        <v>12111</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>6.06</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1104,7 +1114,7 @@
       </c>
       <c r="Q9" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1123,16 +1133,16 @@
         </is>
       </c>
       <c r="D10" s="18" t="n">
-        <v>11071</v>
+        <v>9902</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>19886.18</v>
+        <v>21059.28</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-8815.18</v>
+        <v>-11157.28</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-0.4429999999999999</v>
+        <v>-0.53</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>4215</v>
@@ -1181,54 +1191,44 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10046653</t>
+          <t>10042967</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 5MG 4CAN APLIC LILLY</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO G 128UN</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>125121.67</v>
+        <v>9645.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>132715.59</v>
+        <v>19734.91</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-7593.92</v>
+        <v>-10089.51</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.057</v>
+        <v>-0.511</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>11783</v>
+        <v>7624</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>9.359999999999999</v>
+        <v>6.06</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K11" s="7" t="n">
-        <v>2382.23</v>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>2382.23</v>
-      </c>
-      <c r="N11" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K11" s="28" t="inlineStr"/>
+      <c r="L11" s="12" t="inlineStr"/>
+      <c r="M11" s="28" t="inlineStr"/>
+      <c r="N11" s="29" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Q11" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1260,13 +1260,13 @@
         <v>4598</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>11545.02</v>
+        <v>12226.08</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-6947.02</v>
+        <v>-7628.08</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>-0.602</v>
+        <v>-0.624</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>1100</v>
@@ -1314,16 +1314,16 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>4100.94</v>
+        <v>4418.64</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9203.25</v>
+        <v>9746.16</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-5102.31</v>
+        <v>-5327.52</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.5539999999999999</v>
+        <v>-0.547</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>2289</v>
@@ -1362,54 +1362,44 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10004419</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>88.20999999999999</v>
+        <v>3996</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>3645.93</v>
+        <v>8081.06</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-3557.72</v>
+        <v>-4085.06</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>-0.976</v>
+        <v>-0.506</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>4849</v>
+        <v>2511</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>3.85</v>
+        <v>1.99</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>94.98999999999999</v>
-      </c>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N14" s="32" t="n">
-        <v>0.904</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr"/>
+      <c r="L14" s="24" t="inlineStr"/>
+      <c r="M14" s="23" t="inlineStr"/>
+      <c r="N14" s="25" t="inlineStr"/>
       <c r="O14" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P14" s="24" t="inlineStr">
@@ -1417,9 +1407,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q14" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+      <c r="Q14" s="26" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1429,44 +1419,54 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>621.2</v>
+        <v>4197</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>4131.58</v>
+        <v>8083.94</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-3510.38</v>
+        <v>-3886.94</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-0.85</v>
+        <v>-0.481</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>1277</v>
-      </c>
-      <c r="I15" s="33" t="n">
-        <v>1.01</v>
+        <v>1770</v>
+      </c>
+      <c r="I15" s="32" t="n">
+        <v>1.41</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="12" t="inlineStr"/>
-      <c r="M15" s="28" t="inlineStr"/>
-      <c r="N15" s="29" t="inlineStr"/>
+      <c r="K15" s="7" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
@@ -1486,54 +1486,54 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>4197</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>7633.63</v>
+        <v>3861</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-3436.63</v>
+        <v>-3772.79</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>-0.45</v>
+        <v>-0.977</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>1770</v>
-      </c>
-      <c r="I16" s="31" t="n">
-        <v>1.41</v>
+        <v>4849</v>
+      </c>
+      <c r="I16" s="22" t="n">
+        <v>3.85</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K16" s="18" t="n">
-        <v>1945.09</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M16" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="N16" s="30" t="n">
-        <v>0</v>
+        <v>49.9</v>
+      </c>
+      <c r="N16" s="27" t="n">
+        <v>0.904</v>
       </c>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P16" s="24" t="inlineStr">
@@ -1541,9 +1541,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q16" s="26" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q16" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -1565,13 +1565,13 @@
         <v>2332.26</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>5646.69</v>
+        <v>5979.79</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-3314.43</v>
+        <v>-3647.53</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-0.5870000000000001</v>
+        <v>-0.61</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>3834</v>
@@ -1610,35 +1610,35 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
-        <v>1148.24</v>
+        <v>833</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>4263.78</v>
+        <v>4375.31</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-3115.54</v>
+        <v>-3542.31</v>
       </c>
       <c r="G18" s="20" t="n">
-        <v>-0.731</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I18" s="22" t="n">
-        <v>2.58</v>
+        <v>1277</v>
+      </c>
+      <c r="I18" s="31" t="n">
+        <v>1.01</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Q18" s="26" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>12410</v>
+        <v>12900</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>15427.32</v>
+        <v>16337.39</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-3017.32</v>
+        <v>-3437.39</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-0.196</v>
+        <v>-0.21</v>
       </c>
       <c r="H19" s="10" t="n">
         <v>9899</v>
@@ -1734,54 +1734,44 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>251.09</v>
+        <v>1254.14</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>3118.44</v>
+        <v>4515.31</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-2867.35</v>
+        <v>-3261.17</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>-0.919</v>
+        <v>-0.722</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>864</v>
-      </c>
-      <c r="I20" s="31" t="n">
-        <v>0.6899999999999999</v>
+        <v>3254</v>
+      </c>
+      <c r="I20" s="22" t="n">
+        <v>2.58</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>315.46</v>
-      </c>
-      <c r="L20" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M20" s="18" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N20" s="32" t="n">
-        <v>0.333</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr"/>
+      <c r="L20" s="24" t="inlineStr"/>
+      <c r="M20" s="23" t="inlineStr"/>
+      <c r="N20" s="25" t="inlineStr"/>
       <c r="O20" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P20" s="24" t="inlineStr">
@@ -1789,9 +1779,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q20" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+      <c r="Q20" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1801,44 +1791,54 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10030119</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>872.84</v>
+        <v>3450</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>3605.49</v>
+        <v>6645.13</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-2732.65</v>
+        <v>-3195.13</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-0.758</v>
+        <v>-0.481</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>40618</v>
+        <v>2918</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>32.26</v>
+        <v>2.32</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="12" t="inlineStr"/>
-      <c r="M21" s="28" t="inlineStr"/>
-      <c r="N21" s="29" t="inlineStr"/>
+      <c r="K21" s="7" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1858,44 +1858,54 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10004419</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>4995</v>
+        <v>8391</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>7630.9</v>
+        <v>11545.19</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-2635.9</v>
+        <v>-3154.19</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>-0.345</v>
+        <v>-0.273</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>2511</v>
+        <v>3359</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>1.99</v>
+        <v>2.67</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr"/>
-      <c r="M22" s="23" t="inlineStr"/>
-      <c r="N22" s="25" t="inlineStr"/>
+      <c r="K22" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L22" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M22" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N22" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="O22" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P22" s="24" t="inlineStr">
@@ -1915,39 +1925,39 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>1040.15</v>
+        <v>251.09</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>3628.07</v>
+        <v>3302.4</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-2587.92</v>
+        <v>-3051.31</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.713</v>
+        <v>-0.924</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>4074</v>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>3.24</v>
+        <v>864</v>
+      </c>
+      <c r="I23" s="32" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K23" s="7" t="n">
-        <v>149.4</v>
+        <v>315.46</v>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
@@ -1955,10 +1965,10 @@
         </is>
       </c>
       <c r="M23" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="N23" s="27" t="n">
-        <v>0.396</v>
+        <v>236.6</v>
+      </c>
+      <c r="N23" s="33" t="n">
+        <v>0.333</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
@@ -1972,7 +1982,7 @@
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -1982,54 +1992,44 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>8391</v>
+        <v>1094.81</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>10902.07</v>
+        <v>3818.18</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-2511.07</v>
+        <v>-2723.37</v>
       </c>
       <c r="G24" s="20" t="n">
-        <v>-0.23</v>
+        <v>-0.713</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>3359</v>
+        <v>40618</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>2.67</v>
+        <v>32.26</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K24" s="18" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="L24" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N24" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="K24" s="23" t="inlineStr"/>
+      <c r="L24" s="24" t="inlineStr"/>
+      <c r="M24" s="23" t="inlineStr"/>
+      <c r="N24" s="25" t="inlineStr"/>
       <c r="O24" s="24" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P24" s="24" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Q24" s="26" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2049,39 +2049,39 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>944.33</v>
+        <v>2805</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>3396.69</v>
+        <v>5397.96</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-2452.36</v>
+        <v>-2592.96</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.722</v>
+        <v>-0.48</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>17247</v>
+        <v>6401</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>13.7</v>
+        <v>5.08</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K25" s="7" t="n">
-        <v>74.22</v>
+        <v>831.76</v>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
@@ -2089,14 +2089,14 @@
         </is>
       </c>
       <c r="M25" s="7" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N25" s="27" t="n">
-        <v>0.333</v>
+        <v>831.76</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr">
@@ -2104,9 +2104,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+      <c r="Q25" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10050640</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>2805</v>
+        <v>1005.72</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>5097.27</v>
+        <v>3597.07</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-2292.27</v>
+        <v>-2591.35</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>-0.45</v>
+        <v>-0.72</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>6401</v>
+        <v>17247</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>5.08</v>
+        <v>13.7</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K26" s="18" t="n">
-        <v>831.76</v>
+        <v>74.22</v>
       </c>
       <c r="L26" s="24" t="inlineStr">
         <is>
@@ -2156,14 +2156,14 @@
         </is>
       </c>
       <c r="M26" s="18" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="N26" s="30" t="n">
-        <v>0</v>
+        <v>55.67</v>
+      </c>
+      <c r="N26" s="27" t="n">
+        <v>0.333</v>
       </c>
       <c r="O26" s="24" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P26" s="24" t="inlineStr">
@@ -2171,9 +2171,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q26" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2195,13 @@
         <v>3250</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>5501.96</v>
+        <v>5826.53</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-2251.96</v>
+        <v>-2576.53</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.409</v>
+        <v>-0.442</v>
       </c>
       <c r="H27" s="10" t="n">
         <v>5949</v>
@@ -2250,31 +2250,31 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>412.04</v>
+        <v>1271.11</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>2603.13</v>
+        <v>3842.09</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-2191.09</v>
+        <v>-2570.98</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>-0.8420000000000001</v>
+        <v>-0.669</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>2850</v>
+        <v>4074</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>2.26</v>
+        <v>3.24</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -2282,18 +2282,18 @@
         </is>
       </c>
       <c r="K28" s="18" t="n">
-        <v>218.67</v>
+        <v>149.4</v>
       </c>
       <c r="L28" s="24" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M28" s="18" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N28" s="32" t="n">
-        <v>0.109</v>
+        <v>107</v>
+      </c>
+      <c r="N28" s="27" t="n">
+        <v>0.396</v>
       </c>
       <c r="O28" s="24" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="Q28" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -2317,44 +2317,54 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10052532</t>
+          <t>10046652</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
+          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>8632.889999999999</v>
+        <v>92281.58</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>10734.78</v>
+        <v>94838.13</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-2101.89</v>
+        <v>-2556.55</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-0.196</v>
+        <v>-0.027</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>16881</v>
+        <v>9805</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>13.41</v>
+        <v>7.79</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K29" s="28" t="inlineStr"/>
-      <c r="L29" s="12" t="inlineStr"/>
-      <c r="M29" s="28" t="inlineStr"/>
-      <c r="N29" s="29" t="inlineStr"/>
+      <c r="K29" s="7" t="n">
+        <v>1905.6</v>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>1905.6</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
@@ -2364,7 +2374,7 @@
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2374,31 +2384,31 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10052532</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
-        <v>4040.38</v>
+        <v>8858.18</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>5955.04</v>
+        <v>11368.03</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-1914.66</v>
+        <v>-2509.85</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>-0.322</v>
+        <v>-0.221</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>8641</v>
+        <v>16881</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>6.86</v>
+        <v>13.41</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -2431,50 +2441,54 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1033.8</v>
+        <v>412.04</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>2857.03</v>
+        <v>2756.69</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-1823.23</v>
+        <v>-2344.65</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-0.638</v>
+        <v>-0.851</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>2108</v>
+        <v>2850</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.67</v>
+        <v>2.26</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K31" s="28" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>218.67</v>
+      </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
       <c r="M31" s="7" t="n">
-        <v>549.9</v>
-      </c>
-      <c r="N31" s="29" t="inlineStr"/>
+        <v>197.18</v>
+      </c>
+      <c r="N31" s="33" t="n">
+        <v>0.109</v>
+      </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr">
@@ -2482,9 +2496,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q31" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2508,31 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
-        <v>204.57</v>
+        <v>4261.16</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>2015.55</v>
+        <v>6306.33</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-1810.98</v>
+        <v>-2045.17</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>-0.899</v>
+        <v>-0.324</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>12080</v>
+        <v>8641</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>9.59</v>
+        <v>6.86</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -2551,44 +2565,54 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>100011549</t>
+          <t>10101654</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
+          <t>NAN COMFOR 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>662.45</v>
+        <v>962.39</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>2440.67</v>
+        <v>2986.82</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-1778.22</v>
+        <v>-2024.43</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.7290000000000001</v>
+        <v>-0.6779999999999999</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>7821</v>
+        <v>13826</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>6.21</v>
+        <v>10.98</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K33" s="28" t="inlineStr"/>
-      <c r="L33" s="12" t="inlineStr"/>
-      <c r="M33" s="28" t="inlineStr"/>
-      <c r="N33" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="N33" s="33" t="n">
+        <v>0.094</v>
+      </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
@@ -2596,9 +2620,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q33" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 79.99)</t>
         </is>
       </c>
     </row>
@@ -2608,54 +2632,44 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>10101654</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>NAN COMFOR 2 800G NESTLE</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>1049.88</v>
+        <v>204.57</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>2820.44</v>
+        <v>2134.44</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-1770.56</v>
+        <v>-1929.87</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>-0.628</v>
+        <v>-0.904</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>13826</v>
+        <v>12080</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>10.98</v>
+        <v>9.59</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K34" s="18" t="n">
-        <v>87.48999999999999</v>
-      </c>
-      <c r="L34" s="24" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M34" s="18" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="N34" s="32" t="n">
-        <v>0.094</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr"/>
+      <c r="L34" s="24" t="inlineStr"/>
+      <c r="M34" s="23" t="inlineStr"/>
+      <c r="N34" s="25" t="inlineStr"/>
       <c r="O34" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P34" s="24" t="inlineStr">
@@ -2663,9 +2677,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q34" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 79.99)</t>
+      <c r="Q34" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2675,44 +2689,54 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10033463</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>3028.45</v>
+        <v>2983</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>4744.17</v>
+        <v>4861.96</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-1715.72</v>
+        <v>-1878.96</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-0.362</v>
+        <v>-0.386</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>16250</v>
+        <v>12293</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>12.91</v>
+        <v>9.76</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K35" s="28" t="inlineStr"/>
-      <c r="L35" s="12" t="inlineStr"/>
-      <c r="M35" s="28" t="inlineStr"/>
-      <c r="N35" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="N35" s="33" t="n">
+        <v>0.167</v>
+      </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
@@ -2720,9 +2744,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q35" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
         </is>
       </c>
     </row>
@@ -2732,50 +2756,54 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>10050634</t>
+          <t>10097311</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>EXTENSIOR 1MG 3ML NOVO EUROFARMA</t>
+          <t>NESTOGENO 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
-        <v>927</v>
+        <v>1155.83</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>2551.82</v>
+        <v>2986.52</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-1624.82</v>
+        <v>-1830.69</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>-0.637</v>
+        <v>-0.613</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>4354</v>
+        <v>10934</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>3.46</v>
+        <v>8.68</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>67.98999999999999</v>
+      </c>
       <c r="L36" s="24" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M36" s="18" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N36" s="25" t="inlineStr"/>
+        <v>62.9</v>
+      </c>
+      <c r="N36" s="27" t="n">
+        <v>0.081</v>
+      </c>
       <c r="O36" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P36" s="24" t="inlineStr">
@@ -2783,9 +2811,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q36" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 62.90)</t>
         </is>
       </c>
     </row>
@@ -2795,31 +2823,31 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10033463</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2983</v>
+        <v>1036.35</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>4591.13</v>
+        <v>2697.02</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-1608.13</v>
+        <v>-1660.67</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.35</v>
+        <v>-0.616</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>12293</v>
+        <v>13240</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>9.76</v>
+        <v>10.52</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2827,18 +2855,18 @@
         </is>
       </c>
       <c r="K37" s="7" t="n">
-        <v>69.90000000000001</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="N37" s="27" t="n">
-        <v>0.167</v>
+        <v>61.06</v>
+      </c>
+      <c r="N37" s="33" t="n">
+        <v>0.113</v>
       </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
@@ -2852,7 +2880,7 @@
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -2862,31 +2890,31 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>10097311</t>
+          <t>100011547</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>NESTOGENO 1 800G NESTLE</t>
+          <t>NAN SUPREME 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
-        <v>1223.82</v>
+        <v>536.7</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>2820.16</v>
+        <v>2196.54</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-1596.34</v>
+        <v>-1659.84</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>-0.5660000000000001</v>
+        <v>-0.7559999999999999</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>10934</v>
+        <v>8308</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>8.68</v>
+        <v>6.6</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -2894,18 +2922,18 @@
         </is>
       </c>
       <c r="K38" s="18" t="n">
-        <v>67.98999999999999</v>
+        <v>132.49</v>
       </c>
       <c r="L38" s="24" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M38" s="18" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="N38" s="32" t="n">
-        <v>0.081</v>
+        <v>124.19</v>
+      </c>
+      <c r="N38" s="27" t="n">
+        <v>0.067</v>
       </c>
       <c r="O38" s="24" t="inlineStr">
         <is>
@@ -2919,7 +2947,7 @@
       </c>
       <c r="Q38" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 62.90)</t>
+          <t>Reprecificar no Digital (Amazon R$ 124.19)</t>
         </is>
       </c>
     </row>
@@ -2929,54 +2957,44 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10001096</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN RECEM NASCIDO</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>2210.29</v>
+        <v>1195.6</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>3764.33</v>
+        <v>2838.24</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-1554.04</v>
+        <v>-1642.64</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.413</v>
+        <v>-0.579</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>10126</v>
+        <v>26558</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>8.039999999999999</v>
+        <v>21.09</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="L39" s="12" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="N39" s="27" t="n">
-        <v>0.08400000000000001</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K39" s="28" t="inlineStr"/>
+      <c r="L39" s="12" t="inlineStr"/>
+      <c r="M39" s="28" t="inlineStr"/>
+      <c r="N39" s="29" t="inlineStr"/>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
@@ -2984,9 +3002,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Panvel R$ 35.90)</t>
+      <c r="Q39" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2996,54 +3014,44 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>100011547</t>
+          <t>10033461</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>NAN SUPREME 1 800G NESTLE</t>
+          <t>FR BABYSEC ULTRA HIPER G 60UN</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>536.7</v>
+        <v>1688.5</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>2074.18</v>
+        <v>3291.79</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-1537.48</v>
+        <v>-1603.29</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>-0.741</v>
+        <v>-0.487</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>8308</v>
+        <v>11917</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>6.6</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K40" s="18" t="n">
-        <v>132.49</v>
-      </c>
-      <c r="L40" s="24" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M40" s="18" t="n">
-        <v>124.19</v>
-      </c>
-      <c r="N40" s="32" t="n">
-        <v>0.067</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr"/>
+      <c r="L40" s="24" t="inlineStr"/>
+      <c r="M40" s="23" t="inlineStr"/>
+      <c r="N40" s="25" t="inlineStr"/>
       <c r="O40" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P40" s="24" t="inlineStr">
@@ -3051,9 +3059,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q40" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 124.19)</t>
+      <c r="Q40" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3063,31 +3071,31 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10034467</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0</v>
+        <v>1714.08</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1491.74</v>
+        <v>3298.05</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-1491.74</v>
+        <v>-1583.97</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-1</v>
+        <v>-0.48</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>3854</v>
+        <v>11671</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>3.06</v>
+        <v>9.27</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -3095,14 +3103,8 @@
         </is>
       </c>
       <c r="K41" s="28" t="inlineStr"/>
-      <c r="L41" s="12" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="n">
-        <v>234.98</v>
-      </c>
+      <c r="L41" s="12" t="inlineStr"/>
+      <c r="M41" s="28" t="inlineStr"/>
       <c r="N41" s="29" t="inlineStr"/>
       <c r="O41" s="12" t="inlineStr">
         <is>
@@ -3126,31 +3128,31 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10034467</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>1195.6</v>
+        <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>2680.14</v>
+        <v>1579.74</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-1484.54</v>
+        <v>-1579.74</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>-0.5539999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>26558</v>
+        <v>3854</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>21.09</v>
+        <v>3.06</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
@@ -3158,8 +3160,14 @@
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr"/>
-      <c r="L42" s="24" t="inlineStr"/>
-      <c r="M42" s="23" t="inlineStr"/>
+      <c r="L42" s="24" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M42" s="18" t="n">
+        <v>234.98</v>
+      </c>
       <c r="N42" s="25" t="inlineStr"/>
       <c r="O42" s="24" t="inlineStr">
         <is>
@@ -3195,13 +3203,13 @@
         <v>491.46</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>1954.75</v>
+        <v>2070.06</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-1463.29</v>
+        <v>-1578.6</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-0.7490000000000001</v>
+        <v>-0.763</v>
       </c>
       <c r="H43" s="10" t="n">
         <v>5328</v>
@@ -3262,13 +3270,13 @@
         <v>351.15</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1811.88</v>
+        <v>1918.77</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-1460.73</v>
+        <v>-1567.62</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>-0.8059999999999999</v>
+        <v>-0.8170000000000001</v>
       </c>
       <c r="H44" s="21" t="n">
         <v>31066</v>
@@ -3307,54 +3315,44 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1098.84</v>
+        <v>3471.75</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>2546.78</v>
+        <v>5024.04</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-1447.94</v>
+        <v>-1552.29</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-0.569</v>
+        <v>-0.309</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>13240</v>
+        <v>16250</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>10.52</v>
+        <v>12.91</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N45" s="27" t="n">
-        <v>0.113</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K45" s="28" t="inlineStr"/>
+      <c r="L45" s="12" t="inlineStr"/>
+      <c r="M45" s="28" t="inlineStr"/>
+      <c r="N45" s="29" t="inlineStr"/>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
@@ -3362,9 +3360,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+      <c r="Q45" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3374,44 +3372,54 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10041858</t>
+          <t>10001096</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
+          <t>TOALHAS UMED HUGGIES 192UN RECEM NASCIDO</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>0</v>
+        <v>2443.69</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>1426.96</v>
+        <v>3986.39</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-1426.96</v>
+        <v>-1542.7</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>-1</v>
+        <v>-0.387</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>666</v>
-      </c>
-      <c r="I46" s="31" t="n">
-        <v>0.53</v>
+        <v>10126</v>
+      </c>
+      <c r="I46" s="22" t="n">
+        <v>8.039999999999999</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K46" s="23" t="inlineStr"/>
-      <c r="L46" s="24" t="inlineStr"/>
-      <c r="M46" s="23" t="inlineStr"/>
-      <c r="N46" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K46" s="18" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="L46" s="24" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M46" s="18" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="N46" s="27" t="n">
+        <v>0.08400000000000001</v>
+      </c>
       <c r="O46" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P46" s="24" t="inlineStr">
@@ -3419,9 +3427,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q46" s="26" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q46" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Panvel R$ 35.90)</t>
         </is>
       </c>
     </row>
@@ -3431,54 +3439,44 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>100013179</t>
+          <t>10041858</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>UTROGESTAN 200MG 42CAP BESINS</t>
+          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1418.03</v>
+        <v>1511.14</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-1418.03</v>
+        <v>-1511.14</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>3370</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>2.68</v>
+        <v>666</v>
+      </c>
+      <c r="I47" s="32" t="n">
+        <v>0.53</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>246.91</v>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="n">
-        <v>209.07</v>
-      </c>
-      <c r="N47" s="27" t="n">
-        <v>0.181</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="inlineStr"/>
+      <c r="L47" s="12" t="inlineStr"/>
+      <c r="M47" s="28" t="inlineStr"/>
+      <c r="N47" s="29" t="inlineStr"/>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
@@ -3486,9 +3484,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 209.07)</t>
+      <c r="Q47" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3498,44 +3496,54 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>100013179</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>UTROGESTAN 200MG 42CAP BESINS</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>544.21</v>
+        <v>0</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>1944.88</v>
+        <v>1501.68</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-1400.67</v>
+        <v>-1501.68</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>-0.72</v>
+        <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>10271</v>
+        <v>3370</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>8.16</v>
+        <v>2.68</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="inlineStr"/>
-      <c r="L48" s="24" t="inlineStr"/>
-      <c r="M48" s="23" t="inlineStr"/>
-      <c r="N48" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K48" s="18" t="n">
+        <v>246.91</v>
+      </c>
+      <c r="L48" s="24" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M48" s="18" t="n">
+        <v>209.07</v>
+      </c>
+      <c r="N48" s="27" t="n">
+        <v>0.181</v>
+      </c>
       <c r="O48" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P48" s="24" t="inlineStr">
@@ -3543,9 +3551,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q48" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q48" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 209.07)</t>
         </is>
       </c>
     </row>
@@ -3555,31 +3563,31 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1714.08</v>
+        <v>611.12</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>3114.33</v>
+        <v>2059.61</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-1400.25</v>
+        <v>-1448.49</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-0.45</v>
+        <v>-0.703</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>11671</v>
+        <v>10271</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>9.27</v>
+        <v>8.16</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -3612,44 +3620,54 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>10033461</t>
+          <t>10040802</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER G 60UN</t>
+          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>1758.4</v>
+        <v>23836</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>3108.42</v>
+        <v>25265.94</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-1350.02</v>
+        <v>-1429.94</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>-0.434</v>
+        <v>-0.057</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>11917</v>
+        <v>3794</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>9.470000000000001</v>
+        <v>3.01</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K50" s="23" t="inlineStr"/>
-      <c r="L50" s="24" t="inlineStr"/>
-      <c r="M50" s="23" t="inlineStr"/>
-      <c r="N50" s="25" t="inlineStr"/>
+      <c r="K50" s="18" t="n">
+        <v>2501.8</v>
+      </c>
+      <c r="L50" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M50" s="18" t="n">
+        <v>2501.8</v>
+      </c>
+      <c r="N50" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="O50" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P50" s="24" t="inlineStr">
@@ -3659,7 +3677,7 @@
       </c>
       <c r="Q50" s="26" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -3669,54 +3687,44 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>100011549</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>353.6</v>
+        <v>1192.41</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>1656.92</v>
+        <v>2584.65</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-1303.32</v>
+        <v>-1392.24</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.787</v>
+        <v>-0.539</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>23012</v>
+        <v>7821</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>18.28</v>
+        <v>6.21</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N51" s="27" t="n">
-        <v>0.629</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K51" s="28" t="inlineStr"/>
+      <c r="L51" s="12" t="inlineStr"/>
+      <c r="M51" s="28" t="inlineStr"/>
+      <c r="N51" s="29" t="inlineStr"/>
       <c r="O51" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P51" s="12" t="inlineStr">
@@ -3724,9 +3732,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+      <c r="Q51" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3736,44 +3744,54 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>100012751</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIG SUPERIOR</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>538.64</v>
+        <v>379.5</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>1807</v>
+        <v>1754.66</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-1268.36</v>
+        <v>-1375.16</v>
       </c>
       <c r="G52" s="20" t="n">
-        <v>-0.7020000000000001</v>
+        <v>-0.784</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>14619</v>
+        <v>23012</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>11.61</v>
+        <v>18.28</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K52" s="23" t="inlineStr"/>
-      <c r="L52" s="24" t="inlineStr"/>
-      <c r="M52" s="23" t="inlineStr"/>
-      <c r="N52" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K52" s="18" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L52" s="24" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M52" s="18" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N52" s="27" t="n">
+        <v>0.629</v>
+      </c>
       <c r="O52" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P52" s="24" t="inlineStr">
@@ -3781,9 +3799,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q52" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -3793,54 +3811,44 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>100011848</t>
+          <t>100012751</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>DES AXE AERO 150ML APOLLO</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIG SUPERIOR</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>207.1</v>
+        <v>538.64</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1390.2</v>
+        <v>1913.6</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-1183.1</v>
+        <v>-1374.96</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>-0.851</v>
+        <v>-0.7190000000000001</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>58984</v>
+        <v>14619</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>46.85</v>
+        <v>11.61</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L53" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="N53" s="27" t="n">
-        <v>0.214</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="inlineStr"/>
+      <c r="L53" s="12" t="inlineStr"/>
+      <c r="M53" s="28" t="inlineStr"/>
+      <c r="N53" s="29" t="inlineStr"/>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
@@ -3848,9 +3856,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 8.98)</t>
+      <c r="Q53" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3860,54 +3868,44 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>10037713</t>
+          <t>10001098</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>RELUZE 60CAP GBIO</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>0</v>
+        <v>1574.61</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>1146.52</v>
+        <v>2837.27</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-1146.52</v>
+        <v>-1262.66</v>
       </c>
       <c r="G54" s="20" t="n">
-        <v>-1</v>
+        <v>-0.445</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>2307</v>
+        <v>8729</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>1.83</v>
+        <v>6.93</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K54" s="18" t="n">
-        <v>106.8</v>
-      </c>
-      <c r="L54" s="24" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M54" s="18" t="n">
-        <v>103.85</v>
-      </c>
-      <c r="N54" s="32" t="n">
-        <v>0.028</v>
-      </c>
+      <c r="K54" s="23" t="inlineStr"/>
+      <c r="L54" s="24" t="inlineStr"/>
+      <c r="M54" s="23" t="inlineStr"/>
+      <c r="N54" s="25" t="inlineStr"/>
       <c r="O54" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P54" s="24" t="inlineStr">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -300,10 +300,10 @@
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 08/09/2026 21:52:45 (21:52) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 08/09/2026 22:52:58 (22:52) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         <v>26687</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>57177.97</v>
+        <v>58772.35</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-30490.97</v>
+        <v>-32085.35</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-0.5329999999999999</v>
+        <v>-0.546</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>3194</v>
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>17121.48</v>
+        <v>18040.88</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>40094</v>
+        <v>41212.01</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-22972.52</v>
+        <v>-23171.13</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>-0.573</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>10635</v>
@@ -945,13 +945,13 @@
         <v>123526.1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>140544.58</v>
+        <v>144463.62</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-17018.48</v>
+        <v>-20937.52</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.121</v>
+        <v>-0.145</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>11783</v>
@@ -1009,16 +1009,16 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>8973.84</v>
+        <v>9123.74</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>24733.51</v>
+        <v>25423.19</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-15759.67</v>
+        <v>-16299.45</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>-0.637</v>
+        <v>-0.6409999999999999</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>2116</v>
@@ -1079,13 +1079,13 @@
         <v>21887.77</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>36342.11</v>
+        <v>37355.49</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-14454.34</v>
+        <v>-15467.72</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.398</v>
+        <v>-0.414</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>12111</v>
@@ -1133,16 +1133,16 @@
         </is>
       </c>
       <c r="D10" s="18" t="n">
-        <v>9902</v>
+        <v>11071</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>21059.28</v>
+        <v>21646.51</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-11157.28</v>
+        <v>-10575.51</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-0.53</v>
+        <v>-0.489</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>4215</v>
@@ -1200,16 +1200,16 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>9645.4</v>
+        <v>9955.200000000001</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>19734.91</v>
+        <v>20285.21</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-10089.51</v>
+        <v>-10330.01</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.511</v>
+        <v>-0.509</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>7624</v>
@@ -1260,13 +1260,13 @@
         <v>4598</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>12226.08</v>
+        <v>12566.99</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-7628.08</v>
+        <v>-7968.99</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>-0.624</v>
+        <v>-0.634</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>1100</v>
@@ -1314,16 +1314,16 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>4418.64</v>
+        <v>4524.54</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9746.16</v>
+        <v>10017.93</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-5327.52</v>
+        <v>-5493.39</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.547</v>
+        <v>-0.5479999999999999</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>2289</v>
@@ -1362,49 +1362,59 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>10004419</t>
+          <t>10046652</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
+          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>3996</v>
+        <v>92281.58</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>8081.06</v>
+        <v>97482.66</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-4085.06</v>
+        <v>-5201.08</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>-0.506</v>
+        <v>-0.053</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>2511</v>
+        <v>9805</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>1.99</v>
+        <v>7.79</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr"/>
-      <c r="M14" s="23" t="inlineStr"/>
-      <c r="N14" s="25" t="inlineStr"/>
+      <c r="K14" s="18" t="n">
+        <v>1905.6</v>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="n">
+        <v>1905.6</v>
+      </c>
+      <c r="N14" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P14" s="24" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
       <c r="Q14" s="26" t="inlineStr">
@@ -1419,54 +1429,44 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>10004419</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>4197</v>
+        <v>3996</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>8083.94</v>
+        <v>8306.389999999999</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-3886.94</v>
+        <v>-4310.39</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-0.481</v>
+        <v>-0.519</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>1770</v>
-      </c>
-      <c r="I15" s="32" t="n">
-        <v>1.41</v>
+        <v>2511</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>1.99</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="N15" s="13" t="n">
-        <v>0</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K15" s="28" t="inlineStr"/>
+      <c r="L15" s="12" t="inlineStr"/>
+      <c r="M15" s="28" t="inlineStr"/>
+      <c r="N15" s="29" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1486,54 +1486,54 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>88.20999999999999</v>
+        <v>4197</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>3861</v>
+        <v>8309.360000000001</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-3772.79</v>
+        <v>-4112.36</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>-0.977</v>
+        <v>-0.495</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>4849</v>
-      </c>
-      <c r="I16" s="22" t="n">
-        <v>3.85</v>
+        <v>1770</v>
+      </c>
+      <c r="I16" s="31" t="n">
+        <v>1.41</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K16" s="18" t="n">
-        <v>94.98999999999999</v>
+        <v>1945.09</v>
       </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M16" s="18" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N16" s="27" t="n">
-        <v>0.904</v>
+        <v>1945.09</v>
+      </c>
+      <c r="N16" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P16" s="24" t="inlineStr">
@@ -1541,9 +1541,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q16" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+      <c r="Q16" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1553,44 +1553,54 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10042966</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2332.26</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>5979.79</v>
+        <v>3968.67</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-3647.53</v>
+        <v>-3880.46</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-0.61</v>
+        <v>-0.978</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>3834</v>
+        <v>4849</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="12" t="inlineStr"/>
-      <c r="M17" s="28" t="inlineStr"/>
-      <c r="N17" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="N17" s="32" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
@@ -1598,9 +1608,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q17" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -1610,35 +1620,35 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10042966</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
-        <v>833</v>
+        <v>2332.26</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>4375.31</v>
+        <v>6146.53</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-3542.31</v>
+        <v>-3814.27</v>
       </c>
       <c r="G18" s="20" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.621</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>1277</v>
-      </c>
-      <c r="I18" s="31" t="n">
-        <v>1.01</v>
+        <v>3834</v>
+      </c>
+      <c r="I18" s="22" t="n">
+        <v>3.05</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
@@ -1657,7 +1667,7 @@
       </c>
       <c r="Q18" s="26" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1667,54 +1677,44 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>12900</v>
+        <v>833</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>16337.39</v>
+        <v>4497.31</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-3437.39</v>
+        <v>-3664.31</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-0.21</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>9899</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>7.86</v>
+        <v>1277</v>
+      </c>
+      <c r="I19" s="33" t="n">
+        <v>1.01</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N19" s="13" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K19" s="28" t="inlineStr"/>
+      <c r="L19" s="12" t="inlineStr"/>
+      <c r="M19" s="28" t="inlineStr"/>
+      <c r="N19" s="29" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P19" s="12" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1734,44 +1734,54 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>1254.14</v>
+        <v>8391</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>4515.31</v>
+        <v>11867.12</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-3261.17</v>
+        <v>-3476.12</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>-0.722</v>
+        <v>-0.293</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>3254</v>
+        <v>3359</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr"/>
-      <c r="M20" s="23" t="inlineStr"/>
-      <c r="N20" s="25" t="inlineStr"/>
+      <c r="K20" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N20" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="O20" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P20" s="24" t="inlineStr">
@@ -1781,7 +1791,7 @@
       </c>
       <c r="Q20" s="26" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1791,31 +1801,31 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10030119</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3450</v>
+        <v>13390</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6645.13</v>
+        <v>16792.95</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-3195.13</v>
+        <v>-3402.95</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-0.481</v>
+        <v>-0.203</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>2918</v>
+        <v>9899</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>2.32</v>
+        <v>7.86</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1823,7 +1833,7 @@
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>1301.17</v>
+        <v>988.22</v>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
@@ -1831,7 +1841,7 @@
         </is>
       </c>
       <c r="M21" s="7" t="n">
-        <v>1301.17</v>
+        <v>988.22</v>
       </c>
       <c r="N21" s="13" t="n">
         <v>0</v>
@@ -1848,7 +1858,7 @@
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1858,54 +1868,44 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>8391</v>
+        <v>1360.04</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>11545.19</v>
+        <v>4641.22</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-3154.19</v>
+        <v>-3281.18</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>-0.273</v>
+        <v>-0.7070000000000001</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>3359</v>
+        <v>3254</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K22" s="18" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="L22" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M22" s="18" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N22" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="K22" s="23" t="inlineStr"/>
+      <c r="L22" s="24" t="inlineStr"/>
+      <c r="M22" s="23" t="inlineStr"/>
+      <c r="N22" s="25" t="inlineStr"/>
       <c r="O22" s="24" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P22" s="24" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Q22" s="26" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>251.09</v>
+        <v>502.18</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>3302.4</v>
+        <v>3394.48</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-3051.31</v>
+        <v>-2892.3</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.924</v>
+        <v>-0.852</v>
       </c>
       <c r="H23" s="10" t="n">
         <v>864</v>
       </c>
-      <c r="I23" s="32" t="n">
+      <c r="I23" s="33" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       <c r="M23" s="7" t="n">
         <v>236.6</v>
       </c>
-      <c r="N23" s="33" t="n">
+      <c r="N23" s="32" t="n">
         <v>0.333</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
@@ -2004,13 +2004,13 @@
         <v>1094.81</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>3818.18</v>
+        <v>3924.64</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-2723.37</v>
+        <v>-2829.83</v>
       </c>
       <c r="G24" s="20" t="n">
-        <v>-0.713</v>
+        <v>-0.721</v>
       </c>
       <c r="H24" s="21" t="n">
         <v>40618</v>
@@ -2049,31 +2049,31 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10050640</t>
+          <t>10030119</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
+          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2805</v>
+        <v>4025</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>5397.96</v>
+        <v>6830.43</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-2592.96</v>
+        <v>-2805.43</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.48</v>
+        <v>-0.411</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>6401</v>
+        <v>2918</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>5.08</v>
+        <v>2.32</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="K25" s="7" t="n">
-        <v>831.76</v>
+        <v>1301.17</v>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="M25" s="7" t="n">
-        <v>831.76</v>
+        <v>1301.17</v>
       </c>
       <c r="N25" s="13" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>1005.72</v>
+        <v>2805</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>3597.07</v>
+        <v>5548.48</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-2591.35</v>
+        <v>-2743.48</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>-0.72</v>
+        <v>-0.494</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>17247</v>
+        <v>6401</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>13.7</v>
+        <v>5.08</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K26" s="18" t="n">
-        <v>74.22</v>
+        <v>831.76</v>
       </c>
       <c r="L26" s="24" t="inlineStr">
         <is>
@@ -2156,14 +2156,14 @@
         </is>
       </c>
       <c r="M26" s="18" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N26" s="27" t="n">
-        <v>0.333</v>
+        <v>831.76</v>
+      </c>
+      <c r="N26" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="O26" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P26" s="24" t="inlineStr">
@@ -2171,9 +2171,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q26" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+      <c r="Q26" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2195,13 @@
         <v>3250</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>5826.53</v>
+        <v>5989</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-2576.53</v>
+        <v>-2739</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.442</v>
+        <v>-0.457</v>
       </c>
       <c r="H27" s="10" t="n">
         <v>5949</v>
@@ -2250,54 +2250,44 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10052532</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>1271.11</v>
+        <v>8974.08</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>3842.09</v>
+        <v>11685.03</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-2570.98</v>
+        <v>-2710.95</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>-0.669</v>
+        <v>-0.232</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>4074</v>
+        <v>16881</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>3.24</v>
+        <v>13.41</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="L28" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M28" s="18" t="n">
-        <v>107</v>
-      </c>
-      <c r="N28" s="27" t="n">
-        <v>0.396</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr"/>
+      <c r="L28" s="24" t="inlineStr"/>
+      <c r="M28" s="23" t="inlineStr"/>
+      <c r="N28" s="25" t="inlineStr"/>
       <c r="O28" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P28" s="24" t="inlineStr">
@@ -2305,9 +2295,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q28" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+      <c r="Q28" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2317,39 +2307,39 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10046652</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>92281.58</v>
+        <v>1271.11</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>94838.13</v>
+        <v>3949.22</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-2556.55</v>
+        <v>-2678.11</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-0.027</v>
+        <v>-0.6779999999999999</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>9805</v>
+        <v>4074</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>7.79</v>
+        <v>3.24</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K29" s="7" t="n">
-        <v>1905.6</v>
+        <v>149.4</v>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
@@ -2357,14 +2347,14 @@
         </is>
       </c>
       <c r="M29" s="7" t="n">
-        <v>1905.6</v>
-      </c>
-      <c r="N29" s="13" t="n">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="N29" s="32" t="n">
+        <v>0.396</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
@@ -2372,9 +2362,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q29" s="14" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -2384,44 +2374,54 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10052532</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
-        <v>8858.18</v>
+        <v>1154.16</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>11368.03</v>
+        <v>3697.37</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-2509.85</v>
+        <v>-2543.21</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>-0.221</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>16881</v>
+        <v>17247</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>13.41</v>
+        <v>13.7</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr"/>
-      <c r="L30" s="24" t="inlineStr"/>
-      <c r="M30" s="23" t="inlineStr"/>
-      <c r="N30" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="L30" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M30" s="18" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="N30" s="27" t="n">
+        <v>0.333</v>
+      </c>
       <c r="O30" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P30" s="24" t="inlineStr">
@@ -2429,9 +2429,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q30" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -2453,13 +2453,13 @@
         <v>412.04</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>2756.69</v>
+        <v>2833.56</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-2344.65</v>
+        <v>-2421.52</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-0.851</v>
+        <v>-0.855</v>
       </c>
       <c r="H31" s="10" t="n">
         <v>2850</v>
@@ -2483,7 +2483,7 @@
       <c r="M31" s="7" t="n">
         <v>197.18</v>
       </c>
-      <c r="N31" s="33" t="n">
+      <c r="N31" s="32" t="n">
         <v>0.109</v>
       </c>
       <c r="O31" s="12" t="inlineStr">
@@ -2520,13 +2520,13 @@
         <v>4261.16</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>6306.33</v>
+        <v>6482.18</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-2045.17</v>
+        <v>-2221.02</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>-0.324</v>
+        <v>-0.343</v>
       </c>
       <c r="H32" s="21" t="n">
         <v>8641</v>
@@ -2565,54 +2565,54 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10101654</t>
+          <t>10040802</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>NAN COMFOR 2 800G NESTLE</t>
+          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>962.39</v>
+        <v>23836</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>2986.82</v>
+        <v>25970.47</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-2024.43</v>
+        <v>-2134.47</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.6779999999999999</v>
+        <v>-0.08199999999999999</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>13826</v>
+        <v>3794</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>10.98</v>
+        <v>3.01</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K33" s="7" t="n">
-        <v>87.48999999999999</v>
+        <v>2501.8</v>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M33" s="7" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="N33" s="33" t="n">
-        <v>0.094</v>
+        <v>2501.8</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
@@ -2620,9 +2620,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 79.99)</t>
+      <c r="Q33" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2644,13 +2644,13 @@
         <v>204.57</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>2134.44</v>
+        <v>2193.96</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-1929.87</v>
+        <v>-1989.39</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>-0.904</v>
+        <v>-0.907</v>
       </c>
       <c r="H34" s="21" t="n">
         <v>12080</v>
@@ -2698,16 +2698,16 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>2983</v>
+        <v>3052.9</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>4861.96</v>
+        <v>4997.54</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-1878.96</v>
+        <v>-1944.64</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-0.386</v>
+        <v>-0.389</v>
       </c>
       <c r="H35" s="10" t="n">
         <v>12293</v>
@@ -2731,7 +2731,7 @@
       <c r="M35" s="7" t="n">
         <v>59.9</v>
       </c>
-      <c r="N35" s="33" t="n">
+      <c r="N35" s="32" t="n">
         <v>0.167</v>
       </c>
       <c r="O35" s="12" t="inlineStr">
@@ -2756,31 +2756,31 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>10097311</t>
+          <t>10101654</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>NESTOGENO 1 800G NESTLE</t>
+          <t>NAN COMFOR 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
-        <v>1155.83</v>
+        <v>1129.87</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>2986.52</v>
+        <v>3070.11</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-1830.69</v>
+        <v>-1940.24</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>-0.613</v>
+        <v>-0.632</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>10934</v>
+        <v>13826</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>8.68</v>
+        <v>10.98</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -2788,18 +2788,18 @@
         </is>
       </c>
       <c r="K36" s="18" t="n">
-        <v>67.98999999999999</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="L36" s="24" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M36" s="18" t="n">
-        <v>62.9</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="N36" s="27" t="n">
-        <v>0.081</v>
+        <v>0.094</v>
       </c>
       <c r="O36" s="24" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Q36" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 62.90)</t>
+          <t>Reprecificar no Digital (Amazon R$ 79.99)</t>
         </is>
       </c>
     </row>
@@ -2823,31 +2823,31 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10097311</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>NESTOGENO 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>1036.35</v>
+        <v>1155.83</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>2697.02</v>
+        <v>3069.8</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-1660.67</v>
+        <v>-1913.97</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.616</v>
+        <v>-0.623</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>13240</v>
+        <v>10934</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>10.52</v>
+        <v>8.68</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2859,14 +2859,14 @@
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N37" s="33" t="n">
-        <v>0.113</v>
+        <v>62.9</v>
+      </c>
+      <c r="N37" s="32" t="n">
+        <v>0.081</v>
       </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 62.90)</t>
         </is>
       </c>
     </row>
@@ -2890,54 +2890,44 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>100011547</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>NAN SUPREME 1 800G NESTLE</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
-        <v>536.7</v>
+        <v>1195.6</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>2196.54</v>
+        <v>2917.38</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-1659.84</v>
+        <v>-1721.78</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>-0.7559999999999999</v>
+        <v>-0.59</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>8308</v>
+        <v>26558</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>6.6</v>
+        <v>21.09</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K38" s="18" t="n">
-        <v>132.49</v>
-      </c>
-      <c r="L38" s="24" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M38" s="18" t="n">
-        <v>124.19</v>
-      </c>
-      <c r="N38" s="27" t="n">
-        <v>0.067</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr"/>
+      <c r="L38" s="24" t="inlineStr"/>
+      <c r="M38" s="23" t="inlineStr"/>
+      <c r="N38" s="25" t="inlineStr"/>
       <c r="O38" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P38" s="24" t="inlineStr">
@@ -2945,9 +2935,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q38" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 124.19)</t>
+      <c r="Q38" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2957,44 +2947,54 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>100011547</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>NAN SUPREME 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1195.6</v>
+        <v>536.7</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>2838.24</v>
+        <v>2257.79</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-1642.64</v>
+        <v>-1721.09</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.579</v>
+        <v>-0.762</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>26558</v>
+        <v>8308</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>21.09</v>
+        <v>6.6</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K39" s="28" t="inlineStr"/>
-      <c r="L39" s="12" t="inlineStr"/>
-      <c r="M39" s="28" t="inlineStr"/>
-      <c r="N39" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>132.49</v>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>124.19</v>
+      </c>
+      <c r="N39" s="32" t="n">
+        <v>0.067</v>
+      </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
@@ -3002,9 +3002,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q39" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 124.19)</t>
         </is>
       </c>
     </row>
@@ -3026,13 +3026,13 @@
         <v>1688.5</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>3291.79</v>
+        <v>3383.58</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-1603.29</v>
+        <v>-1695.08</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>-0.487</v>
+        <v>-0.501</v>
       </c>
       <c r="H40" s="21" t="n">
         <v>11917</v>
@@ -3071,31 +3071,31 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1714.08</v>
+        <v>3471.75</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>3298.05</v>
+        <v>5164.13</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-1583.97</v>
+        <v>-1692.38</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-0.48</v>
+        <v>-0.328</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>11671</v>
+        <v>16250</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>9.27</v>
+        <v>12.91</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -3128,50 +3128,54 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10034467</t>
+          <t>10022882</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
+          <t>ACICLOVIR 400MG 30CP GEN PRATI</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>0</v>
+        <v>491.46</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>1579.74</v>
+        <v>2127.79</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-1579.74</v>
+        <v>-1636.33</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>-1</v>
+        <v>-0.769</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>3854</v>
+        <v>5328</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>3.06</v>
+        <v>4.23</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K42" s="23" t="inlineStr"/>
+      <c r="K42" s="18" t="n">
+        <v>71.48999999999999</v>
+      </c>
       <c r="L42" s="24" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M42" s="18" t="n">
-        <v>234.98</v>
-      </c>
-      <c r="N42" s="25" t="inlineStr"/>
+        <v>72.98999999999999</v>
+      </c>
+      <c r="N42" s="30" t="n">
+        <v>-0.021</v>
+      </c>
       <c r="O42" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P42" s="24" t="inlineStr">
@@ -3191,54 +3195,44 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10022882</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>ACICLOVIR 400MG 30CP GEN PRATI</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>491.46</v>
+        <v>351.15</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>2070.06</v>
+        <v>1972.27</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-1578.6</v>
+        <v>-1621.12</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-0.763</v>
+        <v>-0.8220000000000001</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>5328</v>
+        <v>31066</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>4.23</v>
+        <v>24.68</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K43" s="7" t="n">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="L43" s="12" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="n">
-        <v>72.98999999999999</v>
-      </c>
-      <c r="N43" s="13" t="n">
-        <v>-0.021</v>
-      </c>
+      <c r="K43" s="28" t="inlineStr"/>
+      <c r="L43" s="12" t="inlineStr"/>
+      <c r="M43" s="28" t="inlineStr"/>
+      <c r="N43" s="29" t="inlineStr"/>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
@@ -3258,44 +3252,54 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>10001096</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>TOALHAS UMED HUGGIES 192UN RECEM NASCIDO</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>351.15</v>
+        <v>2482.59</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1918.77</v>
+        <v>4097.55</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-1567.62</v>
+        <v>-1614.96</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>-0.8170000000000001</v>
+        <v>-0.394</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>31066</v>
+        <v>10126</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>24.68</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="inlineStr"/>
-      <c r="L44" s="24" t="inlineStr"/>
-      <c r="M44" s="23" t="inlineStr"/>
-      <c r="N44" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K44" s="18" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="L44" s="24" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M44" s="18" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="N44" s="27" t="n">
+        <v>0.08400000000000001</v>
+      </c>
       <c r="O44" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P44" s="24" t="inlineStr">
@@ -3303,9 +3307,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q44" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q44" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Panvel R$ 35.90)</t>
         </is>
       </c>
     </row>
@@ -3315,35 +3319,35 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10041858</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>3471.75</v>
+        <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>5024.04</v>
+        <v>1553.28</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-1552.29</v>
+        <v>-1553.28</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-0.309</v>
+        <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>16250</v>
-      </c>
-      <c r="I45" s="11" t="n">
-        <v>12.91</v>
+        <v>666</v>
+      </c>
+      <c r="I45" s="33" t="n">
+        <v>0.53</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K45" s="28" t="inlineStr"/>
@@ -3362,7 +3366,7 @@
       </c>
       <c r="Q45" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3372,31 +3376,31 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10001096</t>
+          <t>100013179</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN RECEM NASCIDO</t>
+          <t>UTROGESTAN 200MG 42CAP BESINS</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>2443.69</v>
+        <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>3986.39</v>
+        <v>1543.56</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-1542.7</v>
+        <v>-1543.56</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>-0.387</v>
+        <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>10126</v>
+        <v>3370</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>8.039999999999999</v>
+        <v>2.68</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
@@ -3404,18 +3408,18 @@
         </is>
       </c>
       <c r="K46" s="18" t="n">
-        <v>38.9</v>
+        <v>246.91</v>
       </c>
       <c r="L46" s="24" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M46" s="18" t="n">
-        <v>35.9</v>
+        <v>209.07</v>
       </c>
       <c r="N46" s="27" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.181</v>
       </c>
       <c r="O46" s="24" t="inlineStr">
         <is>
@@ -3429,7 +3433,7 @@
       </c>
       <c r="Q46" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Panvel R$ 35.90)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 209.07)</t>
         </is>
       </c>
     </row>
@@ -3439,44 +3443,54 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10041858</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0</v>
+        <v>1308.31</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1511.14</v>
+        <v>2772.22</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-1511.14</v>
+        <v>-1463.91</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-1</v>
+        <v>-0.528</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>666</v>
-      </c>
-      <c r="I47" s="32" t="n">
-        <v>0.53</v>
+        <v>13240</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>10.52</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K47" s="28" t="inlineStr"/>
-      <c r="L47" s="12" t="inlineStr"/>
-      <c r="M47" s="28" t="inlineStr"/>
-      <c r="N47" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="N47" s="32" t="n">
+        <v>0.113</v>
+      </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
@@ -3484,9 +3498,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q47" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -3496,54 +3510,44 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>100013179</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>UTROGESTAN 200MG 42CAP BESINS</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>0</v>
+        <v>1939.9</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>1501.68</v>
+        <v>3390.01</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-1501.68</v>
+        <v>-1450.11</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>-1</v>
+        <v>-0.428</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>3370</v>
+        <v>11671</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>2.68</v>
+        <v>9.27</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K48" s="18" t="n">
-        <v>246.91</v>
-      </c>
-      <c r="L48" s="24" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M48" s="18" t="n">
-        <v>209.07</v>
-      </c>
-      <c r="N48" s="27" t="n">
-        <v>0.181</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="inlineStr"/>
+      <c r="L48" s="24" t="inlineStr"/>
+      <c r="M48" s="23" t="inlineStr"/>
+      <c r="N48" s="25" t="inlineStr"/>
       <c r="O48" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P48" s="24" t="inlineStr">
@@ -3551,9 +3555,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q48" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 209.07)</t>
+      <c r="Q48" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3563,31 +3567,31 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>100012751</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIG SUPERIOR</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>611.12</v>
+        <v>538.64</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>2059.61</v>
+        <v>1966.95</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-1448.49</v>
+        <v>-1428.31</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-0.703</v>
+        <v>-0.726</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>10271</v>
+        <v>14619</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>8.16</v>
+        <v>11.61</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -3620,54 +3624,44 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>10040802</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>23836</v>
+        <v>700.8200000000001</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>25265.94</v>
+        <v>2117.05</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-1429.94</v>
+        <v>-1416.23</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>-0.057</v>
+        <v>-0.669</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>3794</v>
+        <v>10271</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>3.01</v>
+        <v>8.16</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K50" s="18" t="n">
-        <v>2501.8</v>
-      </c>
-      <c r="L50" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M50" s="18" t="n">
-        <v>2501.8</v>
-      </c>
-      <c r="N50" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="K50" s="23" t="inlineStr"/>
+      <c r="L50" s="24" t="inlineStr"/>
+      <c r="M50" s="23" t="inlineStr"/>
+      <c r="N50" s="25" t="inlineStr"/>
       <c r="O50" s="24" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P50" s="24" t="inlineStr">
@@ -3677,7 +3671,7 @@
       </c>
       <c r="Q50" s="26" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3687,44 +3681,54 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>100011549</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1192.41</v>
+        <v>405.4</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>2584.65</v>
+        <v>1803.59</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-1392.24</v>
+        <v>-1398.19</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.539</v>
+        <v>-0.775</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7821</v>
+        <v>23012</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>6.21</v>
+        <v>18.28</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K51" s="28" t="inlineStr"/>
-      <c r="L51" s="12" t="inlineStr"/>
-      <c r="M51" s="28" t="inlineStr"/>
-      <c r="N51" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N51" s="32" t="n">
+        <v>0.629</v>
+      </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P51" s="12" t="inlineStr">
@@ -3732,9 +3736,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q51" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -3744,54 +3748,50 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10034467</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>379.5</v>
+        <v>226.49</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>1754.66</v>
+        <v>1623.79</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-1375.16</v>
+        <v>-1397.3</v>
       </c>
       <c r="G52" s="20" t="n">
-        <v>-0.784</v>
+        <v>-0.861</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>23012</v>
+        <v>3854</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>18.28</v>
+        <v>3.06</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K52" s="18" t="n">
-        <v>25.9</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K52" s="23" t="inlineStr"/>
       <c r="L52" s="24" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M52" s="18" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N52" s="27" t="n">
-        <v>0.629</v>
-      </c>
+        <v>234.98</v>
+      </c>
+      <c r="N52" s="25" t="inlineStr"/>
       <c r="O52" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P52" s="24" t="inlineStr">
@@ -3799,9 +3799,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q52" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+      <c r="Q52" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3811,31 +3811,31 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>100012751</t>
+          <t>100011549</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIG SUPERIOR</t>
+          <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>538.64</v>
+        <v>1324.9</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1913.6</v>
+        <v>2656.72</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-1374.96</v>
+        <v>-1331.82</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>-0.7190000000000001</v>
+        <v>-0.501</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>14619</v>
+        <v>7821</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>11.61</v>
+        <v>6.21</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3868,44 +3868,54 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>10001098</t>
+          <t>100001702</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
+          <t>FR MATURI CARE CONFORT G 30UN</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>1574.61</v>
+        <v>455.94</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>2837.27</v>
+        <v>1707.34</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-1262.66</v>
+        <v>-1251.4</v>
       </c>
       <c r="G54" s="20" t="n">
-        <v>-0.445</v>
+        <v>-0.733</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>8729</v>
+        <v>6462</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>6.93</v>
+        <v>5.13</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K54" s="23" t="inlineStr"/>
-      <c r="L54" s="24" t="inlineStr"/>
-      <c r="M54" s="23" t="inlineStr"/>
-      <c r="N54" s="25" t="inlineStr"/>
+      <c r="K54" s="18" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="L54" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M54" s="18" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="N54" s="30" t="n">
+        <v>-0.135</v>
+      </c>
       <c r="O54" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P54" s="24" t="inlineStr">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -274,19 +274,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -294,16 +288,22 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 08/09/2026 22:52:58 (22:52) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 00:00:00 (00:00) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -809,31 +809,31 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10046655</t>
+          <t>10046653</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
+          <t>MOUNJARO 5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>26687</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>58772.35</v>
+        <v>686.6799999999999</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-32085.35</v>
+        <v>-686.6799999999999</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-0.546</v>
+        <v>-1</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>3194</v>
+        <v>11783</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>2.54</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -841,15 +841,15 @@
         </is>
       </c>
       <c r="K5" s="7" t="n">
-        <v>3210.85</v>
+        <v>2382.23</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
-        <v>3210.85</v>
+        <v>2382.23</v>
       </c>
       <c r="N5" s="13" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>Detrator Crítico</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q5" s="14" t="inlineStr">
@@ -876,54 +876,64 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>10042969</t>
+          <t>10046652</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO XXG 112UN</t>
+          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>18040.88</v>
+        <v>0</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>41212.01</v>
+        <v>321.74</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-23171.13</v>
+        <v>-321.74</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>10635</v>
+        <v>9805</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>8.449999999999999</v>
+        <v>7.79</v>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr"/>
-      <c r="M6" s="23" t="inlineStr"/>
-      <c r="N6" s="25" t="inlineStr"/>
-      <c r="O6" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P6" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Crítico</t>
-        </is>
-      </c>
-      <c r="Q6" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="K6" s="18" t="n">
+        <v>1905.6</v>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="n">
+        <v>1905.6</v>
+      </c>
+      <c r="N6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="23" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q6" s="25" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -933,64 +943,54 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10046653</t>
+          <t>10042969</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 5MG 4CAN APLIC LILLY</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO XXG 112UN</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>123526.1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>144463.62</v>
+        <v>213.1</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-20937.52</v>
+        <v>-213.1</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.145</v>
+        <v>-1</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>11783</v>
+        <v>10635</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>9.359999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K7" s="7" t="n">
-        <v>2382.23</v>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>2382.23</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" s="26" t="inlineStr"/>
+      <c r="L7" s="12" t="inlineStr"/>
+      <c r="M7" s="26" t="inlineStr"/>
+      <c r="N7" s="27" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>Detrator Crítico</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q7" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1000,64 +1000,64 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>10042968</t>
+          <t>10046654</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
+          <t>MOUNJARO 7,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>9123.74</v>
+        <v>0</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>25423.19</v>
+        <v>146.44</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-16299.45</v>
+        <v>-146.44</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>-0.6409999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>2116</v>
+        <v>4477</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>1.68</v>
+        <v>3.56</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K8" s="18" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="L8" s="24" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
+        <v>2766.26</v>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M8" s="18" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="N8" s="27" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="O8" s="24" t="inlineStr">
-        <is>
-          <t>São João Mais Cara</t>
-        </is>
-      </c>
-      <c r="P8" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Crítico</t>
-        </is>
-      </c>
-      <c r="Q8" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
+        <v>2766.26</v>
+      </c>
+      <c r="N8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="23" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P8" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q8" s="25" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>21887.77</v>
+        <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>37355.49</v>
+        <v>97.12</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-15467.72</v>
+        <v>-97.12</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.414</v>
+        <v>-1</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>12111</v>
@@ -1098,10 +1098,10 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr"/>
+      <c r="K9" s="26" t="inlineStr"/>
       <c r="L9" s="12" t="inlineStr"/>
-      <c r="M9" s="28" t="inlineStr"/>
-      <c r="N9" s="29" t="inlineStr"/>
+      <c r="M9" s="26" t="inlineStr"/>
+      <c r="N9" s="27" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>Detrator Crítico</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q9" s="14" t="inlineStr">
@@ -1124,62 +1124,52 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>10050654</t>
+          <t>10042967</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO G 128UN</t>
         </is>
       </c>
       <c r="D10" s="18" t="n">
-        <v>11071</v>
+        <v>0</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>21646.51</v>
+        <v>90.53</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-10575.51</v>
+        <v>-90.53</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-0.489</v>
+        <v>-1</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>4215</v>
+        <v>7624</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>3.35</v>
+        <v>6.06</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K10" s="18" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="L10" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M10" s="18" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="N10" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="24" t="inlineStr">
-        <is>
-          <t>Preço Alinhado</t>
-        </is>
-      </c>
-      <c r="P10" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Crítico</t>
-        </is>
-      </c>
-      <c r="Q10" s="26" t="inlineStr">
+      <c r="K10" s="28" t="inlineStr"/>
+      <c r="L10" s="23" t="inlineStr"/>
+      <c r="M10" s="28" t="inlineStr"/>
+      <c r="N10" s="29" t="inlineStr"/>
+      <c r="O10" s="23" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P10" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t>Ação Promocional / Destaque Home</t>
         </is>
@@ -1191,54 +1181,64 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10042967</t>
+          <t>10042968</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO G 128UN</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>9955.200000000001</v>
+        <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>20285.21</v>
+        <v>89.61</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-10330.01</v>
+        <v>-89.61</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.509</v>
+        <v>-1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>7624</v>
+        <v>2116</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>6.06</v>
+        <v>1.68</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr"/>
-      <c r="M11" s="28" t="inlineStr"/>
-      <c r="N11" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="N11" s="30" t="n">
+        <v>0.067</v>
+      </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>Detrator Crítico</t>
-        </is>
-      </c>
-      <c r="Q11" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
         </is>
       </c>
     </row>
@@ -1248,54 +1248,64 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>10046657</t>
+          <t>10046655</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
+          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>4598</v>
+        <v>0</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>12566.99</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-7968.99</v>
+        <v>-86.95999999999999</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>-0.634</v>
+        <v>-1</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I12" s="31" t="n">
-        <v>0.87</v>
+        <v>3194</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>2.54</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr"/>
-      <c r="M12" s="23" t="inlineStr"/>
-      <c r="N12" s="25" t="inlineStr"/>
-      <c r="O12" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P12" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Crítico</t>
-        </is>
-      </c>
-      <c r="Q12" s="26" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>3210.85</v>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="n">
+        <v>3210.85</v>
+      </c>
+      <c r="N12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="23" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q12" s="25" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1305,54 +1315,64 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10041262</t>
+          <t>10040802</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
+          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>4524.54</v>
+        <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>10017.93</v>
+        <v>75.45</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-5493.39</v>
+        <v>-75.45</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.5479999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>2289</v>
+        <v>3794</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>1.82</v>
+        <v>3.01</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="12" t="inlineStr"/>
-      <c r="M13" s="28" t="inlineStr"/>
-      <c r="N13" s="29" t="inlineStr"/>
+      <c r="K13" s="7" t="n">
+        <v>2501.8</v>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>2501.8</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>Detrator Crítico</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q13" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1362,64 +1382,54 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>10046652</t>
+          <t>10046657</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
+          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>92281.58</v>
+        <v>0</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>97482.66</v>
+        <v>68.97</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-5201.08</v>
+        <v>-68.97</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>-0.053</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>9805</v>
-      </c>
-      <c r="I14" s="22" t="n">
-        <v>7.79</v>
+        <v>1100</v>
+      </c>
+      <c r="I14" s="31" t="n">
+        <v>0.87</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>1905.6</v>
-      </c>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="n">
-        <v>1905.6</v>
-      </c>
-      <c r="N14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="24" t="inlineStr">
-        <is>
-          <t>Preço Alinhado</t>
-        </is>
-      </c>
-      <c r="P14" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Crítico</t>
-        </is>
-      </c>
-      <c r="Q14" s="26" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K14" s="28" t="inlineStr"/>
+      <c r="L14" s="23" t="inlineStr"/>
+      <c r="M14" s="28" t="inlineStr"/>
+      <c r="N14" s="29" t="inlineStr"/>
+      <c r="O14" s="23" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q14" s="25" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1429,41 +1439,41 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10004419</t>
+          <t>100001402</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
+          <t>SERVICO DOMICILIO</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3996</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>8306.389999999999</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-4310.39</v>
+        <v>-66.20999999999999</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-0.519</v>
+        <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>2511</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>1.99</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K15" s="28" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K15" s="26" t="inlineStr"/>
       <c r="L15" s="12" t="inlineStr"/>
-      <c r="M15" s="28" t="inlineStr"/>
-      <c r="N15" s="29" t="inlineStr"/>
+      <c r="M15" s="26" t="inlineStr"/>
+      <c r="N15" s="27" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1471,12 +1481,12 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1486,64 +1496,54 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>10041257</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>FR HUGGIES MAXIMA PROT MAX XXG 80UN</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>4197</v>
+        <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>8309.360000000001</v>
+        <v>65.55</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-4112.36</v>
+        <v>-65.55</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>-0.495</v>
+        <v>-1</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>1770</v>
-      </c>
-      <c r="I16" s="31" t="n">
-        <v>1.41</v>
+        <v>7370</v>
+      </c>
+      <c r="I16" s="22" t="n">
+        <v>5.85</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="L16" s="24" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M16" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="N16" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="24" t="inlineStr">
-        <is>
-          <t>Preço Alinhado</t>
-        </is>
-      </c>
-      <c r="P16" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q16" s="26" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K16" s="28" t="inlineStr"/>
+      <c r="L16" s="23" t="inlineStr"/>
+      <c r="M16" s="28" t="inlineStr"/>
+      <c r="N16" s="29" t="inlineStr"/>
+      <c r="O16" s="23" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q16" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1553,64 +1553,64 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>88.20999999999999</v>
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>3968.67</v>
+        <v>61.66</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-3880.46</v>
+        <v>-61.66</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-0.978</v>
+        <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>4849</v>
+        <v>9899</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>3.85</v>
+        <v>7.86</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K17" s="7" t="n">
-        <v>94.98999999999999</v>
+        <v>988.22</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N17" s="32" t="n">
-        <v>0.904</v>
+        <v>988.22</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q17" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1620,52 +1620,62 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>10042966</t>
+          <t>10050654</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
+          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
-        <v>2332.26</v>
+        <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>6146.53</v>
+        <v>55.36</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-3814.27</v>
+        <v>-55.36</v>
       </c>
       <c r="G18" s="20" t="n">
-        <v>-0.621</v>
+        <v>-1</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>3834</v>
+        <v>4215</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr"/>
-      <c r="M18" s="23" t="inlineStr"/>
-      <c r="N18" s="25" t="inlineStr"/>
-      <c r="O18" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P18" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q18" s="26" t="inlineStr">
+      <c r="K18" s="18" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="N18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="23" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P18" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q18" s="25" t="inlineStr">
         <is>
           <t>Ação Promocional / Destaque Home</t>
         </is>
@@ -1677,54 +1687,64 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>100005474</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>NANLAC COMFOR 3 800G NESTLE</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>833</v>
+        <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>4497.31</v>
+        <v>53.95</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-3664.31</v>
+        <v>-53.95</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>1277</v>
-      </c>
-      <c r="I19" s="33" t="n">
-        <v>1.01</v>
+        <v>16452</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>13.07</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="28" t="inlineStr"/>
-      <c r="N19" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>80.48999999999999</v>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="N19" s="30" t="n">
+        <v>0.342</v>
+      </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q19" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
         </is>
       </c>
     </row>
@@ -1734,64 +1754,54 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10041258</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>FR HUGGIES MAXIMA PROT MAX XG 82UN</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>8391</v>
+        <v>0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>11867.12</v>
+        <v>48.63</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-3476.12</v>
+        <v>-48.63</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>-0.293</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>3359</v>
+        <v>11878</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>2.67</v>
+        <v>9.43</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K20" s="18" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="L20" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M20" s="18" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N20" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="24" t="inlineStr">
-        <is>
-          <t>Preço Alinhado</t>
-        </is>
-      </c>
-      <c r="P20" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q20" s="26" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="K20" s="28" t="inlineStr"/>
+      <c r="L20" s="23" t="inlineStr"/>
+      <c r="M20" s="28" t="inlineStr"/>
+      <c r="N20" s="29" t="inlineStr"/>
+      <c r="O20" s="23" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P20" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q20" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1801,64 +1811,54 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10046656</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>13390</v>
+        <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>16792.95</v>
+        <v>45.98</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-3402.95</v>
+        <v>-45.98</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-0.203</v>
+        <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>9899</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>7.86</v>
+        <v>520</v>
+      </c>
+      <c r="I21" s="32" t="n">
+        <v>0.41</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N21" s="13" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K21" s="26" t="inlineStr"/>
+      <c r="L21" s="12" t="inlineStr"/>
+      <c r="M21" s="26" t="inlineStr"/>
+      <c r="N21" s="27" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1868,52 +1868,52 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10052532</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1360.04</v>
+        <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>4641.22</v>
+        <v>45.19</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-3281.18</v>
+        <v>-45.19</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>-0.7070000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>3254</v>
+        <v>16881</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>2.58</v>
+        <v>13.41</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr"/>
-      <c r="M22" s="23" t="inlineStr"/>
-      <c r="N22" s="25" t="inlineStr"/>
-      <c r="O22" s="24" t="inlineStr">
+      <c r="K22" s="28" t="inlineStr"/>
+      <c r="L22" s="23" t="inlineStr"/>
+      <c r="M22" s="28" t="inlineStr"/>
+      <c r="N22" s="29" t="inlineStr"/>
+      <c r="O22" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P22" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q22" s="26" t="inlineStr">
+      <c r="P22" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q22" s="25" t="inlineStr">
         <is>
           <t>Ação Promocional / Destaque Home</t>
         </is>
@@ -1925,64 +1925,54 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10041262</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>502.18</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>3394.48</v>
+        <v>43.05</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-2892.3</v>
+        <v>-43.05</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.852</v>
+        <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>864</v>
-      </c>
-      <c r="I23" s="33" t="n">
-        <v>0.6899999999999999</v>
+        <v>2289</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>1.82</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>315.46</v>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N23" s="32" t="n">
-        <v>0.333</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K23" s="26" t="inlineStr"/>
+      <c r="L23" s="12" t="inlineStr"/>
+      <c r="M23" s="26" t="inlineStr"/>
+      <c r="N23" s="27" t="inlineStr"/>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q23" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1992,52 +1982,62 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10001064</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG SUPER XXG 56UN</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1094.81</v>
+        <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>3924.64</v>
+        <v>40.08</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-2829.83</v>
+        <v>-40.08</v>
       </c>
       <c r="G24" s="20" t="n">
-        <v>-0.721</v>
+        <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>40618</v>
+        <v>40516</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>32.26</v>
+        <v>32.18</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr"/>
-      <c r="M24" s="23" t="inlineStr"/>
-      <c r="N24" s="25" t="inlineStr"/>
-      <c r="O24" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P24" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q24" s="26" t="inlineStr">
+      <c r="K24" s="18" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M24" s="18" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="N24" s="24" t="n">
+        <v>-0.133</v>
+      </c>
+      <c r="O24" s="23" t="inlineStr">
+        <is>
+          <t>Líder de Preço</t>
+        </is>
+      </c>
+      <c r="P24" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q24" s="25" t="inlineStr">
         <is>
           <t>Ação Promocional / Destaque Home</t>
         </is>
@@ -2049,64 +2049,54 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10030119</t>
+          <t>10041259</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
+          <t>FR HUGGIES MAXIMA PROT MAX G 92UN</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>4025</v>
+        <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>6830.43</v>
+        <v>38.27</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-2805.43</v>
+        <v>-38.27</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.411</v>
+        <v>-1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>2918</v>
+        <v>10177</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>2.32</v>
+        <v>8.08</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K25" s="7" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="N25" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K25" s="26" t="inlineStr"/>
+      <c r="L25" s="12" t="inlineStr"/>
+      <c r="M25" s="26" t="inlineStr"/>
+      <c r="N25" s="27" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2116,62 +2106,52 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10050640</t>
+          <t>10041297</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
+          <t>FR HUGGIES MAXIMA PROT MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>2805</v>
+        <v>0</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>5548.48</v>
+        <v>35.11</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-2743.48</v>
+        <v>-35.11</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>-0.494</v>
+        <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>6401</v>
+        <v>11077</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>5.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K26" s="18" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="L26" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M26" s="18" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="N26" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="24" t="inlineStr">
-        <is>
-          <t>Preço Alinhado</t>
-        </is>
-      </c>
-      <c r="P26" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q26" s="26" t="inlineStr">
+      <c r="K26" s="28" t="inlineStr"/>
+      <c r="L26" s="23" t="inlineStr"/>
+      <c r="M26" s="28" t="inlineStr"/>
+      <c r="N26" s="29" t="inlineStr"/>
+      <c r="O26" s="23" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P26" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q26" s="25" t="inlineStr">
         <is>
           <t>Ação Promocional / Destaque Home</t>
         </is>
@@ -2183,31 +2163,31 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10050642</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>5989</v>
+        <v>34.97</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-2739</v>
+        <v>-34.97</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.457</v>
+        <v>-1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>5949</v>
+        <v>3359</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>4.73</v>
+        <v>2.67</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2215,7 +2195,7 @@
         </is>
       </c>
       <c r="K27" s="7" t="n">
-        <v>955.85</v>
+        <v>1298.54</v>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
@@ -2223,7 +2203,7 @@
         </is>
       </c>
       <c r="M27" s="7" t="n">
-        <v>955.85</v>
+        <v>1298.54</v>
       </c>
       <c r="N27" s="13" t="n">
         <v>0</v>
@@ -2235,12 +2215,12 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2250,52 +2230,52 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10052532</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>8974.08</v>
+        <v>0</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>11685.03</v>
+        <v>32.91</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-2710.95</v>
+        <v>-32.91</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>-0.232</v>
+        <v>-1</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>16881</v>
+        <v>8641</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>13.41</v>
+        <v>6.86</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr"/>
-      <c r="M28" s="23" t="inlineStr"/>
-      <c r="N28" s="25" t="inlineStr"/>
-      <c r="O28" s="24" t="inlineStr">
+      <c r="K28" s="28" t="inlineStr"/>
+      <c r="L28" s="23" t="inlineStr"/>
+      <c r="M28" s="28" t="inlineStr"/>
+      <c r="N28" s="29" t="inlineStr"/>
+      <c r="O28" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P28" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q28" s="26" t="inlineStr">
+      <c r="P28" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q28" s="25" t="inlineStr">
         <is>
           <t>Ação Promocional / Destaque Home</t>
         </is>
@@ -2307,31 +2287,31 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>1271.11</v>
+        <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3949.22</v>
+        <v>30.97</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-2678.11</v>
+        <v>-30.97</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-0.6779999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>4074</v>
+        <v>2492</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>3.24</v>
+        <v>1.98</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2339,18 +2319,18 @@
         </is>
       </c>
       <c r="K29" s="7" t="n">
-        <v>149.4</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="N29" s="32" t="n">
-        <v>0.396</v>
+        <v>46.85</v>
+      </c>
+      <c r="N29" s="30" t="n">
+        <v>1.132</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
@@ -2359,12 +2339,12 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -2374,31 +2354,31 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10106687</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>APTANUTRI PREMIUM 3 800G DANONE</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
-        <v>1154.16</v>
+        <v>0</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>3697.37</v>
+        <v>30.68</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-2543.21</v>
+        <v>-30.68</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>17247</v>
+        <v>19037</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>13.7</v>
+        <v>15.12</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -2406,32 +2386,32 @@
         </is>
       </c>
       <c r="K30" s="18" t="n">
-        <v>74.22</v>
-      </c>
-      <c r="L30" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
+        <v>79.98999999999999</v>
+      </c>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M30" s="18" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N30" s="27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O30" s="24" t="inlineStr">
+        <v>52.84</v>
+      </c>
+      <c r="N30" s="33" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="O30" s="23" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P30" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
+      <c r="P30" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q30" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
         </is>
       </c>
     </row>
@@ -2441,64 +2421,64 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10030119</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>412.04</v>
+        <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>2833.56</v>
+        <v>30.07</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-2421.52</v>
+        <v>-30.07</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-0.855</v>
+        <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>2850</v>
+        <v>2918</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K31" s="7" t="n">
-        <v>218.67</v>
+        <v>1301.17</v>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M31" s="7" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N31" s="32" t="n">
-        <v>0.109</v>
+        <v>1301.17</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q31" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2508,52 +2488,52 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10001144</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG SUPER XG 58UN</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
-        <v>4261.16</v>
+        <v>0</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>6482.18</v>
+        <v>27.39</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-2221.02</v>
+        <v>-27.39</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>-0.343</v>
+        <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>8641</v>
+        <v>25884</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>6.86</v>
+        <v>20.56</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr"/>
-      <c r="L32" s="24" t="inlineStr"/>
-      <c r="M32" s="23" t="inlineStr"/>
-      <c r="N32" s="25" t="inlineStr"/>
-      <c r="O32" s="24" t="inlineStr">
+      <c r="K32" s="28" t="inlineStr"/>
+      <c r="L32" s="23" t="inlineStr"/>
+      <c r="M32" s="28" t="inlineStr"/>
+      <c r="N32" s="29" t="inlineStr"/>
+      <c r="O32" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P32" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q32" s="26" t="inlineStr">
+      <c r="P32" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q32" s="25" t="inlineStr">
         <is>
           <t>Ação Promocional / Destaque Home</t>
         </is>
@@ -2565,64 +2545,60 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10040802</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>23836</v>
+        <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>25970.47</v>
+        <v>25.84</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-2134.47</v>
+        <v>-25.84</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.08199999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>3794</v>
+        <v>2108</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>3.01</v>
+        <v>1.67</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K33" s="7" t="n">
-        <v>2501.8</v>
-      </c>
+      <c r="K33" s="26" t="inlineStr"/>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M33" s="7" t="n">
-        <v>2501.8</v>
-      </c>
-      <c r="N33" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>549.9</v>
+      </c>
+      <c r="N33" s="27" t="inlineStr"/>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q33" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2632,52 +2608,52 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10052538</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XXG 74</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>204.57</v>
+        <v>0</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>2193.96</v>
+        <v>24.41</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-1989.39</v>
+        <v>-24.41</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>-0.907</v>
+        <v>-1</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>12080</v>
+        <v>5014</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>9.59</v>
+        <v>3.98</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K34" s="23" t="inlineStr"/>
-      <c r="L34" s="24" t="inlineStr"/>
-      <c r="M34" s="23" t="inlineStr"/>
-      <c r="N34" s="25" t="inlineStr"/>
-      <c r="O34" s="24" t="inlineStr">
+      <c r="K34" s="28" t="inlineStr"/>
+      <c r="L34" s="23" t="inlineStr"/>
+      <c r="M34" s="28" t="inlineStr"/>
+      <c r="N34" s="29" t="inlineStr"/>
+      <c r="O34" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P34" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q34" s="26" t="inlineStr">
+      <c r="P34" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q34" s="25" t="inlineStr">
         <is>
           <t>Ação Promocional / Destaque Home</t>
         </is>
@@ -2689,64 +2665,54 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10033463</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>3052.9</v>
+        <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>4997.54</v>
+        <v>22.47</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-1944.64</v>
+        <v>-22.47</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-0.389</v>
+        <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>12293</v>
+        <v>26558</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>9.76</v>
+        <v>21.09</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M35" s="7" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="N35" s="32" t="n">
-        <v>0.167</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K35" s="26" t="inlineStr"/>
+      <c r="L35" s="12" t="inlineStr"/>
+      <c r="M35" s="26" t="inlineStr"/>
+      <c r="N35" s="27" t="inlineStr"/>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q35" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2756,64 +2722,54 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>10101654</t>
+          <t>10001143</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>NAN COMFOR 2 800G NESTLE</t>
+          <t>FR PAMPERS CONFORTSEC BAG SUPER G 60UN</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
-        <v>1129.87</v>
+        <v>0</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>3070.11</v>
+        <v>22.24</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-1940.24</v>
+        <v>-22.24</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>-0.632</v>
+        <v>-1</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>13826</v>
+        <v>37042</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>10.98</v>
+        <v>29.42</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K36" s="18" t="n">
-        <v>87.48999999999999</v>
-      </c>
-      <c r="L36" s="24" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M36" s="18" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="N36" s="27" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="O36" s="24" t="inlineStr">
-        <is>
-          <t>São João Mais Cara</t>
-        </is>
-      </c>
-      <c r="P36" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 79.99)</t>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K36" s="28" t="inlineStr"/>
+      <c r="L36" s="23" t="inlineStr"/>
+      <c r="M36" s="28" t="inlineStr"/>
+      <c r="N36" s="29" t="inlineStr"/>
+      <c r="O36" s="23" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P36" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q36" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2823,64 +2779,54 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10097311</t>
+          <t>10052539</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 1 800G NESTLE</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>1155.83</v>
+        <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>3069.8</v>
+        <v>21.64</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-1913.97</v>
+        <v>-21.64</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.623</v>
+        <v>-1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>10934</v>
+        <v>5078</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>8.68</v>
+        <v>4.03</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="N37" s="32" t="n">
-        <v>0.081</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K37" s="26" t="inlineStr"/>
+      <c r="L37" s="12" t="inlineStr"/>
+      <c r="M37" s="26" t="inlineStr"/>
+      <c r="N37" s="27" t="inlineStr"/>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 62.90)</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q37" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2890,54 +2836,64 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
-        <v>1195.6</v>
+        <v>0</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>2917.38</v>
+        <v>20.98</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-1721.78</v>
+        <v>-20.98</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>-0.59</v>
+        <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>26558</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>21.09</v>
+        <v>1770</v>
+      </c>
+      <c r="I38" s="31" t="n">
+        <v>1.41</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr"/>
-      <c r="L38" s="24" t="inlineStr"/>
-      <c r="M38" s="23" t="inlineStr"/>
-      <c r="N38" s="25" t="inlineStr"/>
-      <c r="O38" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P38" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q38" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K38" s="18" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="L38" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M38" s="18" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="N38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="23" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P38" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q38" s="25" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2947,39 +2903,39 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>100011547</t>
+          <t>10051359</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>NAN SUPREME 1 800G NESTLE</t>
+          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>536.7</v>
+        <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>2257.79</v>
+        <v>20.91</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-1721.09</v>
+        <v>-20.91</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.762</v>
+        <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8308</v>
-      </c>
-      <c r="I39" s="11" t="n">
-        <v>6.6</v>
+        <v>975</v>
+      </c>
+      <c r="I39" s="32" t="n">
+        <v>0.77</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K39" s="7" t="n">
-        <v>132.49</v>
+        <v>309</v>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
@@ -2987,24 +2943,24 @@
         </is>
       </c>
       <c r="M39" s="7" t="n">
-        <v>124.19</v>
-      </c>
-      <c r="N39" s="32" t="n">
-        <v>0.067</v>
+        <v>449</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>-0.312</v>
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 124.19)</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q39" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3014,52 +2970,52 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>10033461</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER G 60UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>1688.5</v>
+        <v>0</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>3383.58</v>
+        <v>20.83</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-1695.08</v>
+        <v>-20.83</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>-0.501</v>
+        <v>-1</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>11917</v>
+        <v>16250</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>9.470000000000001</v>
+        <v>12.91</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K40" s="23" t="inlineStr"/>
-      <c r="L40" s="24" t="inlineStr"/>
-      <c r="M40" s="23" t="inlineStr"/>
-      <c r="N40" s="25" t="inlineStr"/>
-      <c r="O40" s="24" t="inlineStr">
+      <c r="K40" s="28" t="inlineStr"/>
+      <c r="L40" s="23" t="inlineStr"/>
+      <c r="M40" s="28" t="inlineStr"/>
+      <c r="N40" s="29" t="inlineStr"/>
+      <c r="O40" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P40" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q40" s="26" t="inlineStr">
+      <c r="P40" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q40" s="25" t="inlineStr">
         <is>
           <t>Ação Promocional / Destaque Home</t>
         </is>
@@ -3071,49 +3027,59 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10026836</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>3471.75</v>
+        <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>5164.13</v>
+        <v>20.76</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-1692.38</v>
+        <v>-20.76</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-0.328</v>
+        <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>16250</v>
+        <v>3282</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>12.91</v>
+        <v>2.61</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K41" s="28" t="inlineStr"/>
-      <c r="L41" s="12" t="inlineStr"/>
-      <c r="M41" s="28" t="inlineStr"/>
-      <c r="N41" s="29" t="inlineStr"/>
+      <c r="K41" s="7" t="n">
+        <v>153.23</v>
+      </c>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>173.71</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>-0.118</v>
+      </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q41" s="14" t="inlineStr">
@@ -3128,31 +3094,31 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10022882</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>ACICLOVIR 400MG 30CP GEN PRATI</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>491.46</v>
+        <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>2127.79</v>
+        <v>20.68</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-1636.33</v>
+        <v>-20.68</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>-0.769</v>
+        <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>5328</v>
+        <v>6401</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>4.23</v>
+        <v>5.08</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
@@ -3160,30 +3126,30 @@
         </is>
       </c>
       <c r="K42" s="18" t="n">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="L42" s="24" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
+        <v>831.76</v>
+      </c>
+      <c r="L42" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M42" s="18" t="n">
-        <v>72.98999999999999</v>
-      </c>
-      <c r="N42" s="30" t="n">
-        <v>-0.021</v>
-      </c>
-      <c r="O42" s="24" t="inlineStr">
-        <is>
-          <t>Líder de Preço</t>
-        </is>
-      </c>
-      <c r="P42" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q42" s="26" t="inlineStr">
+        <v>831.76</v>
+      </c>
+      <c r="N42" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="23" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P42" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q42" s="25" t="inlineStr">
         <is>
           <t>Ação Promocional / Destaque Home</t>
         </is>
@@ -3195,54 +3161,64 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>351.15</v>
+        <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>1972.27</v>
+        <v>20.48</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-1621.12</v>
+        <v>-20.48</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-0.8220000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>31066</v>
+        <v>9302</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>24.68</v>
+        <v>7.39</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K43" s="28" t="inlineStr"/>
-      <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="28" t="inlineStr"/>
-      <c r="N43" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>108.49</v>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="N43" s="30" t="n">
+        <v>0.111</v>
+      </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q43" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -3252,31 +3228,31 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>10001096</t>
+          <t>10106679</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN RECEM NASCIDO</t>
+          <t>NICORETTE 4MG 30GOMAS ICE MENTA</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>2482.59</v>
+        <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>4097.55</v>
+        <v>20.11</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-1614.96</v>
+        <v>-20.11</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>-0.394</v>
+        <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>10126</v>
+        <v>8714</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>8.039999999999999</v>
+        <v>6.92</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
@@ -3284,32 +3260,32 @@
         </is>
       </c>
       <c r="K44" s="18" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="L44" s="24" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
+        <v>117.76</v>
+      </c>
+      <c r="L44" s="23" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M44" s="18" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="N44" s="27" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="O44" s="24" t="inlineStr">
+        <v>83.44</v>
+      </c>
+      <c r="N44" s="33" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="O44" s="23" t="inlineStr">
         <is>
           <t>São João Mais Cara</t>
         </is>
       </c>
-      <c r="P44" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
+      <c r="P44" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q44" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Panvel R$ 35.90)</t>
+          <t>Reprecificar no Digital (Drogaraia R$ 83.44)</t>
         </is>
       </c>
     </row>
@@ -3319,41 +3295,41 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10041858</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1553.28</v>
+        <v>19.98</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-1553.28</v>
+        <v>-19.98</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>666</v>
-      </c>
-      <c r="I45" s="33" t="n">
-        <v>0.53</v>
+        <v>3254</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>2.58</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K45" s="28" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K45" s="26" t="inlineStr"/>
       <c r="L45" s="12" t="inlineStr"/>
-      <c r="M45" s="28" t="inlineStr"/>
-      <c r="N45" s="29" t="inlineStr"/>
+      <c r="M45" s="26" t="inlineStr"/>
+      <c r="N45" s="27" t="inlineStr"/>
       <c r="O45" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3361,12 +3337,12 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q45" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3376,64 +3352,54 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>100013179</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>UTROGESTAN 200MG 42CAP BESINS</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>1543.56</v>
+        <v>19.86</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-1543.56</v>
+        <v>-19.86</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>3370</v>
+        <v>40618</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>2.68</v>
+        <v>32.26</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K46" s="18" t="n">
-        <v>246.91</v>
-      </c>
-      <c r="L46" s="24" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M46" s="18" t="n">
-        <v>209.07</v>
-      </c>
-      <c r="N46" s="27" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="O46" s="24" t="inlineStr">
-        <is>
-          <t>São João Mais Cara</t>
-        </is>
-      </c>
-      <c r="P46" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q46" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 209.07)</t>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K46" s="28" t="inlineStr"/>
+      <c r="L46" s="23" t="inlineStr"/>
+      <c r="M46" s="28" t="inlineStr"/>
+      <c r="N46" s="29" t="inlineStr"/>
+      <c r="O46" s="23" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P46" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q46" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3443,31 +3409,31 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>1308.31</v>
+        <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>2772.22</v>
+        <v>19.44</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-1463.91</v>
+        <v>-19.44</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-0.528</v>
+        <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>13240</v>
+        <v>2850</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>10.52</v>
+        <v>2.26</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3475,18 +3441,18 @@
         </is>
       </c>
       <c r="K47" s="7" t="n">
-        <v>67.98999999999999</v>
+        <v>218.67</v>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N47" s="32" t="n">
-        <v>0.113</v>
+        <v>197.18</v>
+      </c>
+      <c r="N47" s="30" t="n">
+        <v>0.109</v>
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
@@ -3495,12 +3461,12 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -3510,54 +3476,64 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10033757</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XXG 54UN</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>1939.9</v>
+        <v>0</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>3390.01</v>
+        <v>18.99</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-1450.11</v>
+        <v>-18.99</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>-0.428</v>
+        <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>11671</v>
+        <v>24688</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>9.27</v>
+        <v>19.61</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="inlineStr"/>
-      <c r="L48" s="24" t="inlineStr"/>
-      <c r="M48" s="23" t="inlineStr"/>
-      <c r="N48" s="25" t="inlineStr"/>
-      <c r="O48" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P48" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q48" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K48" s="18" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="L48" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M48" s="18" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="N48" s="33" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="O48" s="23" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P48" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q48" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 72.90)</t>
         </is>
       </c>
     </row>
@@ -3567,41 +3543,41 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>100012751</t>
+          <t>10042966</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIG SUPERIOR</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>538.64</v>
+        <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1966.95</v>
+        <v>18.56</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-1428.31</v>
+        <v>-18.56</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-0.726</v>
+        <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>14619</v>
+        <v>3834</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>11.61</v>
+        <v>3.05</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K49" s="28" t="inlineStr"/>
+      <c r="K49" s="26" t="inlineStr"/>
       <c r="L49" s="12" t="inlineStr"/>
-      <c r="M49" s="28" t="inlineStr"/>
-      <c r="N49" s="29" t="inlineStr"/>
+      <c r="M49" s="26" t="inlineStr"/>
+      <c r="N49" s="27" t="inlineStr"/>
       <c r="O49" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3609,7 +3585,7 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q49" s="14" t="inlineStr">
@@ -3624,54 +3600,64 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>700.8200000000001</v>
+        <v>0</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>2117.05</v>
+        <v>18.35</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-1416.23</v>
+        <v>-18.35</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>-0.669</v>
+        <v>-1</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>10271</v>
-      </c>
-      <c r="I50" s="22" t="n">
-        <v>8.16</v>
+        <v>864</v>
+      </c>
+      <c r="I50" s="31" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="inlineStr"/>
-      <c r="L50" s="24" t="inlineStr"/>
-      <c r="M50" s="23" t="inlineStr"/>
-      <c r="N50" s="25" t="inlineStr"/>
-      <c r="O50" s="24" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P50" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q50" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>315.46</v>
+      </c>
+      <c r="L50" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M50" s="18" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="N50" s="33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O50" s="23" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P50" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q50" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -3681,31 +3667,31 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>405.4</v>
+        <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>1803.59</v>
+        <v>17.88</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-1398.19</v>
+        <v>-17.88</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.775</v>
+        <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>23012</v>
+        <v>17247</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>18.28</v>
+        <v>13.7</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -3713,18 +3699,18 @@
         </is>
       </c>
       <c r="K51" s="7" t="n">
-        <v>25.9</v>
+        <v>74.22</v>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N51" s="32" t="n">
-        <v>0.629</v>
+        <v>55.67</v>
+      </c>
+      <c r="N51" s="30" t="n">
+        <v>0.333</v>
       </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
@@ -3733,12 +3719,12 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -3748,60 +3734,54 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>10034467</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>226.49</v>
+        <v>0</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>1623.79</v>
+        <v>17.81</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-1397.3</v>
+        <v>-17.81</v>
       </c>
       <c r="G52" s="20" t="n">
-        <v>-0.861</v>
+        <v>-1</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>3854</v>
-      </c>
-      <c r="I52" s="22" t="n">
-        <v>3.06</v>
+        <v>1277</v>
+      </c>
+      <c r="I52" s="31" t="n">
+        <v>1.01</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K52" s="23" t="inlineStr"/>
-      <c r="L52" s="24" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M52" s="18" t="n">
-        <v>234.98</v>
-      </c>
-      <c r="N52" s="25" t="inlineStr"/>
-      <c r="O52" s="24" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="inlineStr"/>
+      <c r="L52" s="23" t="inlineStr"/>
+      <c r="M52" s="28" t="inlineStr"/>
+      <c r="N52" s="29" t="inlineStr"/>
+      <c r="O52" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P52" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q52" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="P52" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q52" s="25" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3811,54 +3791,64 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>100011549</t>
+          <t>10033463</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
+          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1324.9</v>
+        <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>2656.72</v>
+        <v>17.76</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-1331.82</v>
+        <v>-17.76</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>-0.501</v>
+        <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7821</v>
+        <v>12293</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>6.21</v>
+        <v>9.76</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="inlineStr"/>
-      <c r="L53" s="12" t="inlineStr"/>
-      <c r="M53" s="28" t="inlineStr"/>
-      <c r="N53" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="N53" s="30" t="n">
+        <v>0.167</v>
+      </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q53" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
         </is>
       </c>
     </row>
@@ -3868,64 +3858,64 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>100001702</t>
+          <t>100015081</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>FR MATURI CARE CONFORT G 30UN</t>
+          <t>LEITE NINHO 800G 1+PREBIO LATA</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>455.94</v>
+        <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>1707.34</v>
+        <v>17.62</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-1251.4</v>
+        <v>-17.62</v>
       </c>
       <c r="G54" s="20" t="n">
-        <v>-0.733</v>
+        <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>6462</v>
+        <v>52657</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>5.13</v>
+        <v>41.82</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K54" s="18" t="n">
-        <v>75.98999999999999</v>
-      </c>
-      <c r="L54" s="24" t="inlineStr">
+        <v>58.49</v>
+      </c>
+      <c r="L54" s="23" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M54" s="18" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="N54" s="30" t="n">
-        <v>-0.135</v>
-      </c>
-      <c r="O54" s="24" t="inlineStr">
-        <is>
-          <t>Líder de Preço</t>
-        </is>
-      </c>
-      <c r="P54" s="24" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q54" s="26" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+        <v>47.99</v>
+      </c>
+      <c r="N54" s="33" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="O54" s="23" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P54" s="23" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 47.99)</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 00:00:00 (00:00) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 00:40:00 (00:40) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -294,16 +294,16 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 00:40:00 (00:40) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 00:33:48 (00:33) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -1181,39 +1181,39 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10042968</t>
+          <t>10046655</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
+          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>89.61</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-89.61</v>
+        <v>-86.95999999999999</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>2116</v>
+        <v>3194</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>1.68</v>
+        <v>2.54</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K11" s="7" t="n">
-        <v>159.9</v>
+        <v>3210.85</v>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
@@ -1221,14 +1221,14 @@
         </is>
       </c>
       <c r="M11" s="7" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="N11" s="30" t="n">
-        <v>0.067</v>
+        <v>3210.85</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
@@ -1236,9 +1236,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
+      <c r="Q11" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1248,31 +1248,31 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>10046655</t>
+          <t>10040802</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
+          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>86.95999999999999</v>
+        <v>75.45</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-86.95999999999999</v>
+        <v>-75.45</v>
       </c>
       <c r="G12" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>3194</v>
+        <v>3794</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>2.54</v>
+        <v>3.01</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -1280,15 +1280,15 @@
         </is>
       </c>
       <c r="K12" s="18" t="n">
-        <v>3210.85</v>
+        <v>2501.8</v>
       </c>
       <c r="L12" s="23" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M12" s="18" t="n">
-        <v>3210.85</v>
+        <v>2501.8</v>
       </c>
       <c r="N12" s="24" t="n">
         <v>0</v>
@@ -1315,54 +1315,44 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10040802</t>
+          <t>10046657</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
+          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>75.45</v>
+        <v>68.97</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-75.45</v>
+        <v>-68.97</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>3794</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>3.01</v>
+        <v>1100</v>
+      </c>
+      <c r="I13" s="30" t="n">
+        <v>0.87</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>2501.8</v>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>2501.8</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K13" s="26" t="inlineStr"/>
+      <c r="L13" s="12" t="inlineStr"/>
+      <c r="M13" s="26" t="inlineStr"/>
+      <c r="N13" s="27" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
@@ -1372,7 +1362,7 @@
       </c>
       <c r="Q13" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1382,44 +1372,54 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>10046657</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>68.97</v>
+        <v>61.66</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-68.97</v>
+        <v>-61.66</v>
       </c>
       <c r="G14" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I14" s="31" t="n">
-        <v>0.87</v>
+        <v>9899</v>
+      </c>
+      <c r="I14" s="22" t="n">
+        <v>7.86</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K14" s="28" t="inlineStr"/>
-      <c r="L14" s="23" t="inlineStr"/>
-      <c r="M14" s="28" t="inlineStr"/>
-      <c r="N14" s="29" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="N14" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O14" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P14" s="23" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q14" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1448,21 +1448,21 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>66.20999999999999</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-66.20999999999999</v>
+        <v>-56.31</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-1</v>
+        <v>-0.85</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="32" t="n">
+      <c r="I15" s="30" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1496,44 +1496,54 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>10041257</t>
+          <t>10050654</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX XXG 80UN</t>
+          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>65.55</v>
+        <v>55.36</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-65.55</v>
+        <v>-55.36</v>
       </c>
       <c r="G16" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>7370</v>
+        <v>4215</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>5.85</v>
+        <v>3.35</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K16" s="28" t="inlineStr"/>
-      <c r="L16" s="23" t="inlineStr"/>
-      <c r="M16" s="28" t="inlineStr"/>
-      <c r="N16" s="29" t="inlineStr"/>
+      <c r="K16" s="18" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="N16" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O16" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P16" s="23" t="inlineStr">
@@ -1553,39 +1563,39 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>100005474</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>NANLAC COMFOR 3 800G NESTLE</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>61.66</v>
+        <v>53.95</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-61.66</v>
+        <v>-53.95</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>9899</v>
+        <v>16452</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>7.86</v>
+        <v>13.07</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K17" s="7" t="n">
-        <v>988.22</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
@@ -1593,14 +1603,14 @@
         </is>
       </c>
       <c r="M17" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N17" s="13" t="n">
-        <v>0</v>
+        <v>59.99</v>
+      </c>
+      <c r="N17" s="31" t="n">
+        <v>0.342</v>
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
@@ -1608,9 +1618,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q17" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
         </is>
       </c>
     </row>
@@ -1620,54 +1630,44 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>10050654</t>
+          <t>10041258</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
+          <t>FR HUGGIES MAXIMA PROT MAX XG 82UN</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>55.36</v>
+        <v>48.63</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-55.36</v>
+        <v>-48.63</v>
       </c>
       <c r="G18" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>4215</v>
+        <v>11878</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>3.35</v>
+        <v>9.43</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K18" s="18" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="L18" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M18" s="18" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="N18" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="K18" s="28" t="inlineStr"/>
+      <c r="L18" s="23" t="inlineStr"/>
+      <c r="M18" s="28" t="inlineStr"/>
+      <c r="N18" s="29" t="inlineStr"/>
       <c r="O18" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P18" s="23" t="inlineStr">
@@ -1687,54 +1687,44 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>100005474</t>
+          <t>10046656</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>NANLAC COMFOR 3 800G NESTLE</t>
+          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>53.95</v>
+        <v>45.98</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-53.95</v>
+        <v>-45.98</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>16452</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>13.07</v>
+        <v>520</v>
+      </c>
+      <c r="I19" s="30" t="n">
+        <v>0.41</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>80.48999999999999</v>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>59.99</v>
-      </c>
-      <c r="N19" s="30" t="n">
-        <v>0.342</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K19" s="26" t="inlineStr"/>
+      <c r="L19" s="12" t="inlineStr"/>
+      <c r="M19" s="26" t="inlineStr"/>
+      <c r="N19" s="27" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P19" s="12" t="inlineStr">
@@ -1742,9 +1732,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
+      <c r="Q19" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1754,31 +1744,31 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>10041258</t>
+          <t>10052532</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX XG 82UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>48.63</v>
+        <v>45.19</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-48.63</v>
+        <v>-45.19</v>
       </c>
       <c r="G20" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>11878</v>
+        <v>16881</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>9.43</v>
+        <v>13.41</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
@@ -1811,35 +1801,35 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10046656</t>
+          <t>10041262</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>45.98</v>
+        <v>43.05</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-45.98</v>
+        <v>-43.05</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>520</v>
-      </c>
-      <c r="I21" s="32" t="n">
-        <v>0.41</v>
+        <v>2289</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>1.82</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K21" s="26" t="inlineStr"/>
@@ -1858,7 +1848,7 @@
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1868,44 +1858,54 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10052532</t>
+          <t>10001064</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG SUPER XXG 56UN</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>45.19</v>
+        <v>40.08</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-45.19</v>
+        <v>-40.08</v>
       </c>
       <c r="G22" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>16881</v>
+        <v>40516</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>13.41</v>
+        <v>32.18</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K22" s="28" t="inlineStr"/>
-      <c r="L22" s="23" t="inlineStr"/>
-      <c r="M22" s="28" t="inlineStr"/>
-      <c r="N22" s="29" t="inlineStr"/>
+      <c r="K22" s="18" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M22" s="18" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="N22" s="24" t="n">
+        <v>-0.133</v>
+      </c>
       <c r="O22" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P22" s="23" t="inlineStr">
@@ -1925,31 +1925,31 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10041262</t>
+          <t>10041259</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
+          <t>FR HUGGIES MAXIMA PROT MAX G 92UN</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>43.05</v>
+        <v>38.27</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-43.05</v>
+        <v>-38.27</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>2289</v>
+        <v>10177</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.82</v>
+        <v>8.08</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1982,54 +1982,44 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10001064</t>
+          <t>10041297</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG SUPER XXG 56UN</t>
+          <t>FR HUGGIES MAXIMA PROT MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>40.08</v>
+        <v>35.11</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-40.08</v>
+        <v>-35.11</v>
       </c>
       <c r="G24" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>40516</v>
+        <v>11077</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>32.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K24" s="18" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="L24" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="N24" s="24" t="n">
-        <v>-0.133</v>
-      </c>
+      <c r="K24" s="28" t="inlineStr"/>
+      <c r="L24" s="23" t="inlineStr"/>
+      <c r="M24" s="28" t="inlineStr"/>
+      <c r="N24" s="29" t="inlineStr"/>
       <c r="O24" s="23" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P24" s="23" t="inlineStr">
@@ -2049,44 +2039,54 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10041259</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX G 92UN</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>38.27</v>
+        <v>34.97</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-38.27</v>
+        <v>-34.97</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>10177</v>
+        <v>3359</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>8.08</v>
+        <v>2.67</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K25" s="26" t="inlineStr"/>
-      <c r="L25" s="12" t="inlineStr"/>
-      <c r="M25" s="26" t="inlineStr"/>
-      <c r="N25" s="27" t="inlineStr"/>
+      <c r="K25" s="7" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2106,31 +2106,31 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10041297</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX XXXG 70UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>35.11</v>
+        <v>32.91</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-35.11</v>
+        <v>-32.91</v>
       </c>
       <c r="G26" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>11077</v>
+        <v>8641</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>8.800000000000001</v>
+        <v>6.86</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -2163,54 +2163,54 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>34.97</v>
+        <v>30.97</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-34.97</v>
+        <v>-30.97</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>3359</v>
+        <v>2492</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>2.67</v>
+        <v>1.98</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K27" s="7" t="n">
-        <v>1298.54</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M27" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N27" s="13" t="n">
-        <v>0</v>
+        <v>46.85</v>
+      </c>
+      <c r="N27" s="31" t="n">
+        <v>1.132</v>
       </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P27" s="12" t="inlineStr">
@@ -2218,9 +2218,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q27" s="14" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -2230,44 +2230,54 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10106687</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>APTANUTRI PREMIUM 3 800G DANONE</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>32.91</v>
+        <v>30.68</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-32.91</v>
+        <v>-30.68</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>8641</v>
+        <v>19037</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>6.86</v>
+        <v>15.12</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K28" s="28" t="inlineStr"/>
-      <c r="L28" s="23" t="inlineStr"/>
-      <c r="M28" s="28" t="inlineStr"/>
-      <c r="N28" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K28" s="18" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="L28" s="23" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M28" s="18" t="n">
+        <v>52.84</v>
+      </c>
+      <c r="N28" s="32" t="n">
+        <v>0.514</v>
+      </c>
       <c r="O28" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P28" s="23" t="inlineStr">
@@ -2275,9 +2285,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q28" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q28" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
         </is>
       </c>
     </row>
@@ -2287,54 +2297,54 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10030119</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>30.97</v>
+        <v>30.07</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-30.97</v>
+        <v>-30.07</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>2492</v>
+        <v>2918</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K29" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>1301.17</v>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N29" s="30" t="n">
-        <v>1.132</v>
+        <v>1301.17</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
@@ -2342,9 +2352,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+      <c r="Q29" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2354,54 +2364,44 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10106687</t>
+          <t>10001144</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>APTANUTRI PREMIUM 3 800G DANONE</t>
+          <t>FR PAMPERS CONFORTSEC BAG SUPER XG 58UN</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>30.68</v>
+        <v>27.39</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-30.68</v>
+        <v>-27.39</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>19037</v>
+        <v>25884</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>15.12</v>
+        <v>20.56</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K30" s="18" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="L30" s="23" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M30" s="18" t="n">
-        <v>52.84</v>
-      </c>
-      <c r="N30" s="33" t="n">
-        <v>0.514</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K30" s="28" t="inlineStr"/>
+      <c r="L30" s="23" t="inlineStr"/>
+      <c r="M30" s="28" t="inlineStr"/>
+      <c r="N30" s="29" t="inlineStr"/>
       <c r="O30" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P30" s="23" t="inlineStr">
@@ -2409,9 +2409,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q30" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
+      <c r="Q30" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2421,54 +2421,50 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10030119</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>30.07</v>
+        <v>25.84</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-30.07</v>
+        <v>-25.84</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>2918</v>
+        <v>2108</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>2.32</v>
+        <v>1.67</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K31" s="7" t="n">
-        <v>1301.17</v>
-      </c>
+      <c r="K31" s="26" t="inlineStr"/>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M31" s="7" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="N31" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>549.9</v>
+      </c>
+      <c r="N31" s="27" t="inlineStr"/>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr">
@@ -2478,7 +2474,7 @@
       </c>
       <c r="Q31" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2488,31 +2484,31 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10001144</t>
+          <t>10052538</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG SUPER XG 58UN</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XXG 74</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>27.39</v>
+        <v>24.41</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-27.39</v>
+        <v>-24.41</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>25884</v>
+        <v>5014</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>20.56</v>
+        <v>3.98</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -2545,31 +2541,31 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>25.84</v>
+        <v>22.47</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-25.84</v>
+        <v>-22.47</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>2108</v>
+        <v>26558</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.67</v>
+        <v>21.09</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2577,14 +2573,8 @@
         </is>
       </c>
       <c r="K33" s="26" t="inlineStr"/>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M33" s="7" t="n">
-        <v>549.9</v>
-      </c>
+      <c r="L33" s="12" t="inlineStr"/>
+      <c r="M33" s="26" t="inlineStr"/>
       <c r="N33" s="27" t="inlineStr"/>
       <c r="O33" s="12" t="inlineStr">
         <is>
@@ -2608,31 +2598,31 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>10052538</t>
+          <t>10001143</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XXG 74</t>
+          <t>FR PAMPERS CONFORTSEC BAG SUPER G 60UN</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>24.41</v>
+        <v>22.24</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-24.41</v>
+        <v>-22.24</v>
       </c>
       <c r="G34" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>5014</v>
+        <v>37042</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>3.98</v>
+        <v>29.42</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -2665,31 +2655,31 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10052539</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.47</v>
+        <v>21.64</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-22.47</v>
+        <v>-21.64</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>26558</v>
+        <v>5078</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>21.09</v>
+        <v>4.03</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2722,44 +2712,54 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>10001143</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG SUPER G 60UN</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>22.24</v>
+        <v>20.98</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-22.24</v>
+        <v>-20.98</v>
       </c>
       <c r="G36" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>37042</v>
-      </c>
-      <c r="I36" s="22" t="n">
-        <v>29.42</v>
+        <v>1770</v>
+      </c>
+      <c r="I36" s="33" t="n">
+        <v>1.41</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K36" s="28" t="inlineStr"/>
-      <c r="L36" s="23" t="inlineStr"/>
-      <c r="M36" s="28" t="inlineStr"/>
-      <c r="N36" s="29" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="L36" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M36" s="18" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="N36" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O36" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P36" s="23" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="Q36" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2779,44 +2779,54 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10052539</t>
+          <t>10051359</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
+          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>21.64</v>
+        <v>20.91</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-21.64</v>
+        <v>-20.91</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>5078</v>
-      </c>
-      <c r="I37" s="11" t="n">
-        <v>4.03</v>
+        <v>975</v>
+      </c>
+      <c r="I37" s="30" t="n">
+        <v>0.77</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K37" s="26" t="inlineStr"/>
-      <c r="L37" s="12" t="inlineStr"/>
-      <c r="M37" s="26" t="inlineStr"/>
-      <c r="N37" s="27" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>309</v>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>449</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>-0.312</v>
+      </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
@@ -2826,7 +2836,7 @@
       </c>
       <c r="Q37" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2836,54 +2846,44 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>20.98</v>
+        <v>20.83</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-20.98</v>
+        <v>-20.83</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>1770</v>
-      </c>
-      <c r="I38" s="31" t="n">
-        <v>1.41</v>
+        <v>16250</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>12.91</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K38" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="L38" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M38" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="N38" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K38" s="28" t="inlineStr"/>
+      <c r="L38" s="23" t="inlineStr"/>
+      <c r="M38" s="28" t="inlineStr"/>
+      <c r="N38" s="29" t="inlineStr"/>
       <c r="O38" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P38" s="23" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="Q38" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2903,50 +2903,50 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10051359</t>
+          <t>10026836</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
+          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>20.91</v>
+        <v>20.76</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-20.91</v>
+        <v>-20.76</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>975</v>
-      </c>
-      <c r="I39" s="32" t="n">
-        <v>0.77</v>
+        <v>3282</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>2.61</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K39" s="7" t="n">
-        <v>309</v>
+        <v>153.23</v>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M39" s="7" t="n">
-        <v>449</v>
+        <v>173.71</v>
       </c>
       <c r="N39" s="13" t="n">
-        <v>-0.312</v>
+        <v>-0.118</v>
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="Q39" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2970,44 +2970,54 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>20.83</v>
+        <v>20.68</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-20.83</v>
+        <v>-20.68</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>16250</v>
+        <v>6401</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>12.91</v>
+        <v>5.08</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K40" s="28" t="inlineStr"/>
-      <c r="L40" s="23" t="inlineStr"/>
-      <c r="M40" s="28" t="inlineStr"/>
-      <c r="N40" s="29" t="inlineStr"/>
+      <c r="K40" s="18" t="n">
+        <v>831.76</v>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M40" s="18" t="n">
+        <v>831.76</v>
+      </c>
+      <c r="N40" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O40" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P40" s="23" t="inlineStr">
@@ -3027,54 +3037,54 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10026836</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>20.76</v>
+        <v>20.48</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-20.76</v>
+        <v>-20.48</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>3282</v>
+        <v>9302</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>2.61</v>
+        <v>7.39</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K41" s="7" t="n">
-        <v>153.23</v>
+        <v>108.49</v>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
-        <v>173.71</v>
-      </c>
-      <c r="N41" s="13" t="n">
-        <v>-0.118</v>
+        <v>97.69</v>
+      </c>
+      <c r="N41" s="31" t="n">
+        <v>0.111</v>
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
@@ -3082,9 +3092,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q41" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -3094,54 +3104,54 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10050640</t>
+          <t>10106679</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
+          <t>NICORETTE 4MG 30GOMAS ICE MENTA</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>20.68</v>
+        <v>20.11</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-20.68</v>
+        <v>-20.11</v>
       </c>
       <c r="G42" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>6401</v>
+        <v>8714</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>5.08</v>
+        <v>6.92</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K42" s="18" t="n">
-        <v>831.76</v>
+        <v>117.76</v>
       </c>
       <c r="L42" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M42" s="18" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="N42" s="24" t="n">
-        <v>0</v>
+        <v>83.44</v>
+      </c>
+      <c r="N42" s="32" t="n">
+        <v>0.411</v>
       </c>
       <c r="O42" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P42" s="23" t="inlineStr">
@@ -3149,9 +3159,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q42" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q42" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 83.44)</t>
         </is>
       </c>
     </row>
@@ -3161,54 +3171,44 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>20.48</v>
+        <v>19.98</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-20.48</v>
+        <v>-19.98</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>9302</v>
+        <v>3254</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>7.39</v>
+        <v>2.58</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>108.49</v>
-      </c>
-      <c r="L43" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N43" s="30" t="n">
-        <v>0.111</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K43" s="26" t="inlineStr"/>
+      <c r="L43" s="12" t="inlineStr"/>
+      <c r="M43" s="26" t="inlineStr"/>
+      <c r="N43" s="27" t="inlineStr"/>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
@@ -3216,9 +3216,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+      <c r="Q43" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3228,54 +3228,44 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>10106679</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>NICORETTE 4MG 30GOMAS ICE MENTA</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>20.11</v>
+        <v>19.86</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-20.11</v>
+        <v>-19.86</v>
       </c>
       <c r="G44" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>8714</v>
+        <v>40618</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>6.92</v>
+        <v>32.26</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K44" s="18" t="n">
-        <v>117.76</v>
-      </c>
-      <c r="L44" s="23" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M44" s="18" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="N44" s="33" t="n">
-        <v>0.411</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K44" s="28" t="inlineStr"/>
+      <c r="L44" s="23" t="inlineStr"/>
+      <c r="M44" s="28" t="inlineStr"/>
+      <c r="N44" s="29" t="inlineStr"/>
       <c r="O44" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P44" s="23" t="inlineStr">
@@ -3283,9 +3273,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q44" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 83.44)</t>
+      <c r="Q44" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3295,44 +3285,54 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>19.98</v>
+        <v>19.44</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-19.98</v>
+        <v>-19.44</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>3254</v>
+        <v>2850</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K45" s="26" t="inlineStr"/>
-      <c r="L45" s="12" t="inlineStr"/>
-      <c r="M45" s="26" t="inlineStr"/>
-      <c r="N45" s="27" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>218.67</v>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>197.18</v>
+      </c>
+      <c r="N45" s="31" t="n">
+        <v>0.109</v>
+      </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
@@ -3340,9 +3340,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q45" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -3352,31 +3352,31 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10042966</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>19.86</v>
+        <v>18.56</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-19.86</v>
+        <v>-18.56</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>40618</v>
+        <v>3834</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>32.26</v>
+        <v>3.05</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
@@ -3409,50 +3409,50 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>19.44</v>
+        <v>18.35</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-19.44</v>
+        <v>-18.35</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>2850</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>2.26</v>
+        <v>864</v>
+      </c>
+      <c r="I47" s="30" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K47" s="7" t="n">
-        <v>218.67</v>
+        <v>315.46</v>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N47" s="30" t="n">
-        <v>0.109</v>
+        <v>236.6</v>
+      </c>
+      <c r="N47" s="31" t="n">
+        <v>0.333</v>
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -3476,31 +3476,31 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>10033757</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XXG 54UN</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>18.99</v>
+        <v>17.88</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-18.99</v>
+        <v>-17.88</v>
       </c>
       <c r="G48" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>24688</v>
+        <v>17247</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>19.61</v>
+        <v>13.7</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="K48" s="18" t="n">
-        <v>84.90000000000001</v>
+        <v>74.22</v>
       </c>
       <c r="L48" s="23" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="M48" s="18" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="N48" s="33" t="n">
-        <v>0.165</v>
+        <v>55.67</v>
+      </c>
+      <c r="N48" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="O48" s="23" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Q48" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 72.90)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -3543,35 +3543,35 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10042966</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>18.56</v>
+        <v>17.81</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-18.56</v>
+        <v>-17.81</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>3834</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>3.05</v>
+        <v>1277</v>
+      </c>
+      <c r="I49" s="30" t="n">
+        <v>1.01</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K49" s="26" t="inlineStr"/>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="Q49" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3600,39 +3600,39 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10033463</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>18.35</v>
+        <v>17.76</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-18.35</v>
+        <v>-17.76</v>
       </c>
       <c r="G50" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>864</v>
-      </c>
-      <c r="I50" s="31" t="n">
-        <v>0.6899999999999999</v>
+        <v>12293</v>
+      </c>
+      <c r="I50" s="22" t="n">
+        <v>9.76</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K50" s="18" t="n">
-        <v>315.46</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L50" s="23" t="inlineStr">
         <is>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="M50" s="18" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N50" s="33" t="n">
-        <v>0.333</v>
+        <v>59.9</v>
+      </c>
+      <c r="N50" s="32" t="n">
+        <v>0.167</v>
       </c>
       <c r="O50" s="23" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="Q50" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
         </is>
       </c>
     </row>
@@ -3667,31 +3667,31 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>17.88</v>
+        <v>17.48</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-17.88</v>
+        <v>-17.48</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>17247</v>
+        <v>4074</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>13.7</v>
+        <v>3.24</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="K51" s="7" t="n">
-        <v>74.22</v>
+        <v>149.4</v>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="M51" s="7" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N51" s="30" t="n">
-        <v>0.333</v>
+        <v>107</v>
+      </c>
+      <c r="N51" s="31" t="n">
+        <v>0.396</v>
       </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -3734,40 +3734,46 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>17.81</v>
+        <v>16.98</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-17.81</v>
+        <v>-16.98</v>
       </c>
       <c r="G52" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>1277</v>
-      </c>
-      <c r="I52" s="31" t="n">
-        <v>1.01</v>
+        <v>4480</v>
+      </c>
+      <c r="I52" s="22" t="n">
+        <v>3.56</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K52" s="28" t="inlineStr"/>
-      <c r="L52" s="23" t="inlineStr"/>
-      <c r="M52" s="28" t="inlineStr"/>
+      <c r="L52" s="23" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M52" s="18" t="n">
+        <v>50.25</v>
+      </c>
       <c r="N52" s="29" t="inlineStr"/>
       <c r="O52" s="23" t="inlineStr">
         <is>
@@ -3781,7 +3787,7 @@
       </c>
       <c r="Q52" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3791,54 +3797,44 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>10033463</t>
+          <t>10004419</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
+          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>17.76</v>
+        <v>16.98</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-17.76</v>
+        <v>-16.98</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>12293</v>
+        <v>2511</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>9.76</v>
+        <v>1.99</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="L53" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="N53" s="30" t="n">
-        <v>0.167</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K53" s="26" t="inlineStr"/>
+      <c r="L53" s="12" t="inlineStr"/>
+      <c r="M53" s="26" t="inlineStr"/>
+      <c r="N53" s="27" t="inlineStr"/>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
@@ -3846,9 +3842,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
+      <c r="Q53" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -3858,31 +3854,31 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>100015081</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO LATA</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>17.62</v>
+        <v>16.63</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-17.62</v>
+        <v>-16.63</v>
       </c>
       <c r="G54" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>52657</v>
+        <v>4849</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>41.82</v>
+        <v>3.85</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
@@ -3890,18 +3886,18 @@
         </is>
       </c>
       <c r="K54" s="18" t="n">
-        <v>58.49</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="L54" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M54" s="18" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="N54" s="33" t="n">
-        <v>0.219</v>
+        <v>49.9</v>
+      </c>
+      <c r="N54" s="32" t="n">
+        <v>0.904</v>
       </c>
       <c r="O54" s="23" t="inlineStr">
         <is>
@@ -3915,7 +3911,7 @@
       </c>
       <c r="Q54" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 47.99)</t>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -297,13 +297,13 @@
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 00:33:48 (00:33) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 01:32:50 (01:32) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -1439,44 +1439,54 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>100001402</t>
+          <t>10050654</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>SERVICO DOMICILIO</t>
+          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>66.20999999999999</v>
+        <v>55.36</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-56.31</v>
+        <v>-55.36</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-0.85</v>
+        <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="30" t="n">
-        <v>0</v>
+        <v>4215</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>3.35</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K15" s="26" t="inlineStr"/>
-      <c r="L15" s="12" t="inlineStr"/>
-      <c r="M15" s="26" t="inlineStr"/>
-      <c r="N15" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
@@ -1486,7 +1496,7 @@
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1496,39 +1506,39 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>10050654</t>
+          <t>100005474</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
+          <t>NANLAC COMFOR 3 800G NESTLE</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>55.36</v>
+        <v>53.95</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-55.36</v>
+        <v>-53.95</v>
       </c>
       <c r="G16" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>4215</v>
+        <v>16452</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>3.35</v>
+        <v>13.07</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K16" s="18" t="n">
-        <v>1617.66</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="L16" s="23" t="inlineStr">
         <is>
@@ -1536,14 +1546,14 @@
         </is>
       </c>
       <c r="M16" s="18" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="N16" s="24" t="n">
-        <v>0</v>
+        <v>59.99</v>
+      </c>
+      <c r="N16" s="31" t="n">
+        <v>0.342</v>
       </c>
       <c r="O16" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P16" s="23" t="inlineStr">
@@ -1551,9 +1561,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q16" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q16" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
         </is>
       </c>
     </row>
@@ -1563,54 +1573,44 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>100005474</t>
+          <t>10041258</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>NANLAC COMFOR 3 800G NESTLE</t>
+          <t>FR HUGGIES MAXIMA PROT MAX XG 82UN</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>53.95</v>
+        <v>48.63</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-53.95</v>
+        <v>-48.63</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>16452</v>
+        <v>11878</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>13.07</v>
+        <v>9.43</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>80.48999999999999</v>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>59.99</v>
-      </c>
-      <c r="N17" s="31" t="n">
-        <v>0.342</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K17" s="26" t="inlineStr"/>
+      <c r="L17" s="12" t="inlineStr"/>
+      <c r="M17" s="26" t="inlineStr"/>
+      <c r="N17" s="27" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
@@ -1618,9 +1618,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
+      <c r="Q17" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1630,35 +1630,35 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>10041258</t>
+          <t>10046656</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX XG 82UN</t>
+          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>48.63</v>
+        <v>45.98</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-48.63</v>
+        <v>-45.98</v>
       </c>
       <c r="G18" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>11878</v>
-      </c>
-      <c r="I18" s="22" t="n">
-        <v>9.43</v>
+        <v>520</v>
+      </c>
+      <c r="I18" s="32" t="n">
+        <v>0.41</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K18" s="28" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Q18" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1687,35 +1687,35 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10046656</t>
+          <t>10052532</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>45.98</v>
+        <v>45.19</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-45.98</v>
+        <v>-45.19</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>520</v>
-      </c>
-      <c r="I19" s="30" t="n">
-        <v>0.41</v>
+        <v>16881</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>13.41</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K19" s="26" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1744,35 +1744,35 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>10052532</t>
+          <t>100001402</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
+          <t>SERVICO DOMICILIO</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>45.19</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-45.19</v>
+        <v>-44.51</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>-1</v>
+        <v>-0.672</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>16881</v>
-      </c>
-      <c r="I20" s="22" t="n">
-        <v>13.41</v>
+        <v>0</v>
+      </c>
+      <c r="I20" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K20" s="28" t="inlineStr"/>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Q20" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1858,54 +1858,44 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10001064</t>
+          <t>10041259</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG SUPER XXG 56UN</t>
+          <t>FR HUGGIES MAXIMA PROT MAX G 92UN</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>40.08</v>
+        <v>38.27</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-40.08</v>
+        <v>-38.27</v>
       </c>
       <c r="G22" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>40516</v>
+        <v>10177</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>32.18</v>
+        <v>8.08</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K22" s="18" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="L22" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M22" s="18" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="N22" s="24" t="n">
-        <v>-0.133</v>
-      </c>
+      <c r="K22" s="28" t="inlineStr"/>
+      <c r="L22" s="23" t="inlineStr"/>
+      <c r="M22" s="28" t="inlineStr"/>
+      <c r="N22" s="29" t="inlineStr"/>
       <c r="O22" s="23" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P22" s="23" t="inlineStr">
@@ -1925,31 +1915,31 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10041259</t>
+          <t>10041297</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX G 92UN</t>
+          <t>FR HUGGIES MAXIMA PROT MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>38.27</v>
+        <v>35.11</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-38.27</v>
+        <v>-35.11</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>10177</v>
+        <v>11077</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>8.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1982,44 +1972,54 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10041297</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX XXXG 70UN</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>35.11</v>
+        <v>34.97</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-35.11</v>
+        <v>-34.97</v>
       </c>
       <c r="G24" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>11077</v>
+        <v>3359</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>8.800000000000001</v>
+        <v>2.67</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K24" s="28" t="inlineStr"/>
-      <c r="L24" s="23" t="inlineStr"/>
-      <c r="M24" s="28" t="inlineStr"/>
-      <c r="N24" s="29" t="inlineStr"/>
+      <c r="K24" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M24" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N24" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O24" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P24" s="23" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Q24" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2039,54 +2039,44 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>34.97</v>
+        <v>32.91</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-34.97</v>
+        <v>-32.91</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>3359</v>
+        <v>8641</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>2.67</v>
+        <v>6.86</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K25" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N25" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K25" s="26" t="inlineStr"/>
+      <c r="L25" s="12" t="inlineStr"/>
+      <c r="M25" s="26" t="inlineStr"/>
+      <c r="N25" s="27" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr">
@@ -2096,7 +2086,7 @@
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2106,44 +2096,54 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>32.91</v>
+        <v>30.97</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-32.91</v>
+        <v>-30.97</v>
       </c>
       <c r="G26" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>8641</v>
+        <v>2492</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>6.86</v>
+        <v>1.98</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K26" s="28" t="inlineStr"/>
-      <c r="L26" s="23" t="inlineStr"/>
-      <c r="M26" s="28" t="inlineStr"/>
-      <c r="N26" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="L26" s="23" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M26" s="18" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="N26" s="31" t="n">
+        <v>1.132</v>
+      </c>
       <c r="O26" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P26" s="23" t="inlineStr">
@@ -2151,9 +2151,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q26" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -2163,31 +2163,31 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10106687</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>APTANUTRI PREMIUM 3 800G DANONE</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>30.97</v>
+        <v>30.68</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-30.97</v>
+        <v>-30.68</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>2492</v>
+        <v>19037</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.98</v>
+        <v>15.12</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="K27" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="M27" s="7" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N27" s="31" t="n">
-        <v>1.132</v>
+        <v>52.84</v>
+      </c>
+      <c r="N27" s="33" t="n">
+        <v>0.514</v>
       </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
         </is>
       </c>
     </row>
@@ -2230,54 +2230,54 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10106687</t>
+          <t>10030119</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>APTANUTRI PREMIUM 3 800G DANONE</t>
+          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>30.68</v>
+        <v>30.07</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-30.68</v>
+        <v>-30.07</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>19037</v>
+        <v>2918</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>15.12</v>
+        <v>2.32</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K28" s="18" t="n">
-        <v>79.98999999999999</v>
+        <v>1301.17</v>
       </c>
       <c r="L28" s="23" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M28" s="18" t="n">
-        <v>52.84</v>
-      </c>
-      <c r="N28" s="32" t="n">
-        <v>0.514</v>
+        <v>1301.17</v>
+      </c>
+      <c r="N28" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="O28" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P28" s="23" t="inlineStr">
@@ -2285,9 +2285,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q28" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
+      <c r="Q28" s="25" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2297,54 +2297,44 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10030119</t>
+          <t>10001144</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
+          <t>FR PAMPERS CONFORTSEC BAG SUPER XG 58UN</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>30.07</v>
+        <v>27.39</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-30.07</v>
+        <v>-27.39</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>2918</v>
+        <v>25884</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>2.32</v>
+        <v>20.56</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K29" s="7" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="N29" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K29" s="26" t="inlineStr"/>
+      <c r="L29" s="12" t="inlineStr"/>
+      <c r="M29" s="26" t="inlineStr"/>
+      <c r="N29" s="27" t="inlineStr"/>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
@@ -2354,7 +2344,7 @@
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2364,31 +2354,31 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10001144</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG SUPER XG 58UN</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>27.39</v>
+        <v>25.84</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-27.39</v>
+        <v>-25.84</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>25884</v>
+        <v>2108</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>20.56</v>
+        <v>1.67</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -2396,8 +2386,14 @@
         </is>
       </c>
       <c r="K30" s="28" t="inlineStr"/>
-      <c r="L30" s="23" t="inlineStr"/>
-      <c r="M30" s="28" t="inlineStr"/>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M30" s="18" t="n">
+        <v>549.9</v>
+      </c>
       <c r="N30" s="29" t="inlineStr"/>
       <c r="O30" s="23" t="inlineStr">
         <is>
@@ -2421,31 +2417,31 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10052538</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XXG 74</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>25.84</v>
+        <v>24.41</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-25.84</v>
+        <v>-24.41</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>2108</v>
+        <v>5014</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.67</v>
+        <v>3.98</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -2453,14 +2449,8 @@
         </is>
       </c>
       <c r="K31" s="26" t="inlineStr"/>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="n">
-        <v>549.9</v>
-      </c>
+      <c r="L31" s="12" t="inlineStr"/>
+      <c r="M31" s="26" t="inlineStr"/>
       <c r="N31" s="27" t="inlineStr"/>
       <c r="O31" s="12" t="inlineStr">
         <is>
@@ -2484,31 +2474,31 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10052538</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XXG 74</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>24.41</v>
+        <v>22.47</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-24.41</v>
+        <v>-22.47</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>5014</v>
+        <v>26558</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>3.98</v>
+        <v>21.09</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -2541,31 +2531,31 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10052539</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.47</v>
+        <v>21.64</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-22.47</v>
+        <v>-21.64</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>26558</v>
+        <v>5078</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>21.09</v>
+        <v>4.03</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2598,44 +2588,54 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>10001143</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG SUPER G 60UN</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>22.24</v>
+        <v>20.98</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-22.24</v>
+        <v>-20.98</v>
       </c>
       <c r="G34" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>37042</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>29.42</v>
+        <v>1770</v>
+      </c>
+      <c r="I34" s="32" t="n">
+        <v>1.41</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K34" s="28" t="inlineStr"/>
-      <c r="L34" s="23" t="inlineStr"/>
-      <c r="M34" s="28" t="inlineStr"/>
-      <c r="N34" s="29" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K34" s="18" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="L34" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M34" s="18" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="N34" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O34" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P34" s="23" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="Q34" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2655,44 +2655,54 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10052539</t>
+          <t>10051359</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
+          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>21.64</v>
+        <v>20.91</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-21.64</v>
+        <v>-20.91</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>5078</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>4.03</v>
+        <v>975</v>
+      </c>
+      <c r="I35" s="30" t="n">
+        <v>0.77</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K35" s="26" t="inlineStr"/>
-      <c r="L35" s="12" t="inlineStr"/>
-      <c r="M35" s="26" t="inlineStr"/>
-      <c r="N35" s="27" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>309</v>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>449</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>-0.312</v>
+      </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
@@ -2702,7 +2712,7 @@
       </c>
       <c r="Q35" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2712,54 +2722,44 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>20.98</v>
+        <v>20.83</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-20.98</v>
+        <v>-20.83</v>
       </c>
       <c r="G36" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>1770</v>
-      </c>
-      <c r="I36" s="33" t="n">
-        <v>1.41</v>
+        <v>16250</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>12.91</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K36" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="L36" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M36" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="N36" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K36" s="28" t="inlineStr"/>
+      <c r="L36" s="23" t="inlineStr"/>
+      <c r="M36" s="28" t="inlineStr"/>
+      <c r="N36" s="29" t="inlineStr"/>
       <c r="O36" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P36" s="23" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="Q36" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2779,50 +2779,50 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10051359</t>
+          <t>10026836</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
+          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>20.91</v>
+        <v>20.76</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-20.91</v>
+        <v>-20.76</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>975</v>
-      </c>
-      <c r="I37" s="30" t="n">
-        <v>0.77</v>
+        <v>3282</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>2.61</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K37" s="7" t="n">
-        <v>309</v>
+        <v>153.23</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
-        <v>449</v>
+        <v>173.71</v>
       </c>
       <c r="N37" s="13" t="n">
-        <v>-0.312</v>
+        <v>-0.118</v>
       </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="Q37" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2846,44 +2846,54 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>20.83</v>
+        <v>20.68</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-20.83</v>
+        <v>-20.68</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>16250</v>
+        <v>6401</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>12.91</v>
+        <v>5.08</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K38" s="28" t="inlineStr"/>
-      <c r="L38" s="23" t="inlineStr"/>
-      <c r="M38" s="28" t="inlineStr"/>
-      <c r="N38" s="29" t="inlineStr"/>
+      <c r="K38" s="18" t="n">
+        <v>831.76</v>
+      </c>
+      <c r="L38" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M38" s="18" t="n">
+        <v>831.76</v>
+      </c>
+      <c r="N38" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O38" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P38" s="23" t="inlineStr">
@@ -2903,54 +2913,54 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10026836</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>20.76</v>
+        <v>20.48</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-20.76</v>
+        <v>-20.48</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>3282</v>
+        <v>9302</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>2.61</v>
+        <v>7.39</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K39" s="7" t="n">
-        <v>153.23</v>
+        <v>108.49</v>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M39" s="7" t="n">
-        <v>173.71</v>
-      </c>
-      <c r="N39" s="13" t="n">
-        <v>-0.118</v>
+        <v>97.69</v>
+      </c>
+      <c r="N39" s="33" t="n">
+        <v>0.111</v>
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
@@ -2958,9 +2968,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q39" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -2970,54 +2980,54 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>10050640</t>
+          <t>10106679</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
+          <t>NICORETTE 4MG 30GOMAS ICE MENTA</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>20.68</v>
+        <v>20.11</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-20.68</v>
+        <v>-20.11</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>6401</v>
+        <v>8714</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>5.08</v>
+        <v>6.92</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K40" s="18" t="n">
-        <v>831.76</v>
+        <v>117.76</v>
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M40" s="18" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="N40" s="24" t="n">
-        <v>0</v>
+        <v>83.44</v>
+      </c>
+      <c r="N40" s="31" t="n">
+        <v>0.411</v>
       </c>
       <c r="O40" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P40" s="23" t="inlineStr">
@@ -3025,9 +3035,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q40" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 83.44)</t>
         </is>
       </c>
     </row>
@@ -3037,54 +3047,44 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>20.48</v>
+        <v>19.98</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-20.48</v>
+        <v>-19.98</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>9302</v>
+        <v>3254</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>7.39</v>
+        <v>2.58</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>108.49</v>
-      </c>
-      <c r="L41" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N41" s="31" t="n">
-        <v>0.111</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K41" s="26" t="inlineStr"/>
+      <c r="L41" s="12" t="inlineStr"/>
+      <c r="M41" s="26" t="inlineStr"/>
+      <c r="N41" s="27" t="inlineStr"/>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
@@ -3092,9 +3092,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+      <c r="Q41" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3104,54 +3104,44 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10106679</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>NICORETTE 4MG 30GOMAS ICE MENTA</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>20.11</v>
+        <v>19.86</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-20.11</v>
+        <v>-19.86</v>
       </c>
       <c r="G42" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>8714</v>
+        <v>40618</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>6.92</v>
+        <v>32.26</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K42" s="18" t="n">
-        <v>117.76</v>
-      </c>
-      <c r="L42" s="23" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M42" s="18" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="N42" s="32" t="n">
-        <v>0.411</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K42" s="28" t="inlineStr"/>
+      <c r="L42" s="23" t="inlineStr"/>
+      <c r="M42" s="28" t="inlineStr"/>
+      <c r="N42" s="29" t="inlineStr"/>
       <c r="O42" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P42" s="23" t="inlineStr">
@@ -3159,9 +3149,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q42" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 83.44)</t>
+      <c r="Q42" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3171,44 +3161,54 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>19.98</v>
+        <v>19.44</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-19.98</v>
+        <v>-19.44</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>3254</v>
+        <v>2850</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K43" s="26" t="inlineStr"/>
-      <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="26" t="inlineStr"/>
-      <c r="N43" s="27" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>218.67</v>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>197.18</v>
+      </c>
+      <c r="N43" s="33" t="n">
+        <v>0.109</v>
+      </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
@@ -3216,9 +3216,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q43" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -3228,31 +3228,31 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10042966</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>19.86</v>
+        <v>18.56</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-19.86</v>
+        <v>-18.56</v>
       </c>
       <c r="G44" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>40618</v>
+        <v>3834</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>32.26</v>
+        <v>3.05</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
@@ -3285,50 +3285,50 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>19.44</v>
+        <v>18.35</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-19.44</v>
+        <v>-18.35</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>2850</v>
-      </c>
-      <c r="I45" s="11" t="n">
-        <v>2.26</v>
+        <v>864</v>
+      </c>
+      <c r="I45" s="30" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K45" s="7" t="n">
-        <v>218.67</v>
+        <v>315.46</v>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N45" s="31" t="n">
-        <v>0.109</v>
+        <v>236.6</v>
+      </c>
+      <c r="N45" s="33" t="n">
+        <v>0.333</v>
       </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -3352,44 +3352,54 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10042966</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>18.56</v>
+        <v>17.88</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-18.56</v>
+        <v>-17.88</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>3834</v>
+        <v>17247</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>3.05</v>
+        <v>13.7</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K46" s="28" t="inlineStr"/>
-      <c r="L46" s="23" t="inlineStr"/>
-      <c r="M46" s="28" t="inlineStr"/>
-      <c r="N46" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K46" s="18" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="L46" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M46" s="18" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="N46" s="31" t="n">
+        <v>0.333</v>
+      </c>
       <c r="O46" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P46" s="23" t="inlineStr">
@@ -3397,9 +3407,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q46" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q46" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -3409,54 +3419,44 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>18.35</v>
+        <v>17.81</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-18.35</v>
+        <v>-17.81</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>864</v>
+        <v>1277</v>
       </c>
       <c r="I47" s="30" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>315.46</v>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N47" s="31" t="n">
-        <v>0.333</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K47" s="26" t="inlineStr"/>
+      <c r="L47" s="12" t="inlineStr"/>
+      <c r="M47" s="26" t="inlineStr"/>
+      <c r="N47" s="27" t="inlineStr"/>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
@@ -3464,9 +3464,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+      <c r="Q47" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3476,31 +3476,31 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10033463</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>17.88</v>
+        <v>17.76</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-17.88</v>
+        <v>-17.76</v>
       </c>
       <c r="G48" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>17247</v>
+        <v>12293</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>13.7</v>
+        <v>9.76</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="K48" s="18" t="n">
-        <v>74.22</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L48" s="23" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="M48" s="18" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N48" s="32" t="n">
-        <v>0.333</v>
+        <v>59.9</v>
+      </c>
+      <c r="N48" s="31" t="n">
+        <v>0.167</v>
       </c>
       <c r="O48" s="23" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Q48" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
         </is>
       </c>
     </row>
@@ -3543,44 +3543,54 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>17.81</v>
+        <v>17.48</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-17.81</v>
+        <v>-17.48</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>1277</v>
-      </c>
-      <c r="I49" s="30" t="n">
-        <v>1.01</v>
+        <v>4074</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>3.24</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K49" s="26" t="inlineStr"/>
-      <c r="L49" s="12" t="inlineStr"/>
-      <c r="M49" s="26" t="inlineStr"/>
-      <c r="N49" s="27" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="N49" s="33" t="n">
+        <v>0.396</v>
+      </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
@@ -3588,9 +3598,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q49" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -3600,54 +3610,50 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>10033463</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>17.76</v>
+        <v>16.98</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-17.76</v>
+        <v>-16.98</v>
       </c>
       <c r="G50" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>12293</v>
+        <v>4480</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>9.76</v>
+        <v>3.56</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K50" s="18" t="n">
-        <v>69.90000000000001</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K50" s="28" t="inlineStr"/>
       <c r="L50" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M50" s="18" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="N50" s="32" t="n">
-        <v>0.167</v>
-      </c>
+        <v>50.25</v>
+      </c>
+      <c r="N50" s="29" t="inlineStr"/>
       <c r="O50" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P50" s="23" t="inlineStr">
@@ -3655,9 +3661,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q50" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
+      <c r="Q50" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3667,54 +3673,44 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10004419</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>17.48</v>
+        <v>16.98</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-17.48</v>
+        <v>-16.98</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>4074</v>
+        <v>2511</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>3.24</v>
+        <v>1.99</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="N51" s="31" t="n">
-        <v>0.396</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K51" s="26" t="inlineStr"/>
+      <c r="L51" s="12" t="inlineStr"/>
+      <c r="M51" s="26" t="inlineStr"/>
+      <c r="N51" s="27" t="inlineStr"/>
       <c r="O51" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P51" s="12" t="inlineStr">
@@ -3722,9 +3718,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+      <c r="Q51" s="14" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -3734,50 +3730,54 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>10041248</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>CREATINA MONOHIDRATADA 300G DUX</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>16.98</v>
+        <v>16.63</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-16.98</v>
+        <v>-16.63</v>
       </c>
       <c r="G52" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>4480</v>
+        <v>4849</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>3.56</v>
+        <v>3.85</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K52" s="18" t="n">
+        <v>94.98999999999999</v>
+      </c>
       <c r="L52" s="23" t="inlineStr">
         <is>
           <t>AMAZON</t>
         </is>
       </c>
       <c r="M52" s="18" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="N52" s="29" t="inlineStr"/>
+        <v>49.9</v>
+      </c>
+      <c r="N52" s="31" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O52" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P52" s="23" t="inlineStr">
@@ -3785,9 +3785,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q52" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -3797,44 +3797,54 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>10004419</t>
+          <t>10001096</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
+          <t>TOALHAS UMED HUGGIES 192UN RECEM NASCIDO</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>16.98</v>
+        <v>16.58</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-16.98</v>
+        <v>-16.58</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>2511</v>
+        <v>10126</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>1.99</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K53" s="26" t="inlineStr"/>
-      <c r="L53" s="12" t="inlineStr"/>
-      <c r="M53" s="26" t="inlineStr"/>
-      <c r="N53" s="27" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="N53" s="33" t="n">
+        <v>0.08400000000000001</v>
+      </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
@@ -3842,9 +3852,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q53" s="14" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Panvel R$ 35.90)</t>
         </is>
       </c>
     </row>
@@ -3854,54 +3864,44 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10038743</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>FR PAMPERS CONFORTSEC BAG SUPER XXXG 44U</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>16.63</v>
+        <v>16.55</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-16.63</v>
+        <v>-16.55</v>
       </c>
       <c r="G54" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>4849</v>
+        <v>11018</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>3.85</v>
+        <v>8.75</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K54" s="18" t="n">
-        <v>94.98999999999999</v>
-      </c>
-      <c r="L54" s="23" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M54" s="18" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N54" s="32" t="n">
-        <v>0.904</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K54" s="28" t="inlineStr"/>
+      <c r="L54" s="23" t="inlineStr"/>
+      <c r="M54" s="28" t="inlineStr"/>
+      <c r="N54" s="29" t="inlineStr"/>
       <c r="O54" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P54" s="23" t="inlineStr">
@@ -3909,9 +3909,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q54" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+      <c r="Q54" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -237,7 +237,7 @@
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -270,7 +270,7 @@
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -294,13 +294,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -830,14 +824,14 @@
         <v>-1</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>11783</v>
+        <v>0</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>9.359999999999999</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K5" s="7" t="n">
@@ -866,7 +860,7 @@
       </c>
       <c r="Q5" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -897,14 +891,14 @@
         <v>-1</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>9805</v>
+        <v>0</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>7.79</v>
+        <v>0</v>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K6" s="18" t="n">
@@ -933,7 +927,7 @@
       </c>
       <c r="Q6" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -964,14 +958,14 @@
         <v>-1</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>10635</v>
+        <v>21</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>8.449999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K7" s="26" t="inlineStr"/>
@@ -990,7 +984,7 @@
       </c>
       <c r="Q7" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1021,14 +1015,14 @@
         <v>-1</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>4477</v>
+        <v>0</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K8" s="18" t="n">
@@ -1057,7 +1051,7 @@
       </c>
       <c r="Q8" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1088,14 +1082,14 @@
         <v>-1</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>12111</v>
+        <v>3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>9.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K9" s="26" t="inlineStr"/>
@@ -1114,7 +1108,7 @@
       </c>
       <c r="Q9" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1145,14 +1139,14 @@
         <v>-1</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>7624</v>
+        <v>0</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K10" s="28" t="inlineStr"/>
@@ -1171,7 +1165,7 @@
       </c>
       <c r="Q10" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1202,14 +1196,14 @@
         <v>-1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>3194</v>
+        <v>0</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K11" s="7" t="n">
@@ -1238,7 +1232,7 @@
       </c>
       <c r="Q11" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1269,14 +1263,14 @@
         <v>-1</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>3794</v>
+        <v>0</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K12" s="18" t="n">
@@ -1305,7 +1299,7 @@
       </c>
       <c r="Q12" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1336,10 +1330,10 @@
         <v>-1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I13" s="30" t="n">
-        <v>0.87</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1393,14 +1387,14 @@
         <v>-1</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>9899</v>
+        <v>0</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>7.86</v>
+        <v>0</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K14" s="18" t="n">
@@ -1429,7 +1423,7 @@
       </c>
       <c r="Q14" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1460,14 +1454,14 @@
         <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>4215</v>
+        <v>8</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>3.35</v>
+        <v>0.01</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K15" s="7" t="n">
@@ -1496,7 +1490,7 @@
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1527,14 +1521,14 @@
         <v>-1</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>16452</v>
+        <v>52</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>13.07</v>
+        <v>0.04</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K16" s="18" t="n">
@@ -1548,7 +1542,7 @@
       <c r="M16" s="18" t="n">
         <v>59.99</v>
       </c>
-      <c r="N16" s="31" t="n">
+      <c r="N16" s="30" t="n">
         <v>0.342</v>
       </c>
       <c r="O16" s="23" t="inlineStr">
@@ -1563,7 +1557,7 @@
       </c>
       <c r="Q16" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 59.99)</t>
         </is>
       </c>
     </row>
@@ -1594,14 +1588,14 @@
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>11878</v>
+        <v>4</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K17" s="26" t="inlineStr"/>
@@ -1620,7 +1614,7 @@
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1651,10 +1645,10 @@
         <v>-1</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>520</v>
-      </c>
-      <c r="I18" s="32" t="n">
-        <v>0.41</v>
+        <v>0</v>
+      </c>
+      <c r="I18" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -1708,14 +1702,14 @@
         <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>16881</v>
+        <v>6</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>13.41</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K19" s="26" t="inlineStr"/>
@@ -1734,7 +1728,7 @@
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1761,7 @@
       <c r="H20" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="32" t="n">
+      <c r="I20" s="22" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
@@ -1822,14 +1816,14 @@
         <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>2289</v>
+        <v>0</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K21" s="26" t="inlineStr"/>
@@ -1848,7 +1842,7 @@
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1879,14 +1873,14 @@
         <v>-1</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>10177</v>
+        <v>0</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K22" s="28" t="inlineStr"/>
@@ -1905,7 +1899,7 @@
       </c>
       <c r="Q22" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1936,14 +1930,14 @@
         <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>11077</v>
+        <v>2</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K23" s="26" t="inlineStr"/>
@@ -1962,7 +1956,7 @@
       </c>
       <c r="Q23" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1987,14 @@
         <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>3359</v>
+        <v>0</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K24" s="18" t="n">
@@ -2029,7 +2023,7 @@
       </c>
       <c r="Q24" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2060,14 +2054,14 @@
         <v>-1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>8641</v>
+        <v>0</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>6.86</v>
+        <v>0</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K25" s="26" t="inlineStr"/>
@@ -2086,7 +2080,7 @@
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2117,14 +2111,14 @@
         <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>2492</v>
+        <v>0</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K26" s="18" t="n">
@@ -2138,7 +2132,7 @@
       <c r="M26" s="18" t="n">
         <v>46.85</v>
       </c>
-      <c r="N26" s="31" t="n">
+      <c r="N26" s="30" t="n">
         <v>1.132</v>
       </c>
       <c r="O26" s="23" t="inlineStr">
@@ -2153,7 +2147,7 @@
       </c>
       <c r="Q26" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+          <t>Reprecificar e Remanejar (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -2184,14 +2178,14 @@
         <v>-1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>19037</v>
+        <v>29</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>15.12</v>
+        <v>0.02</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K27" s="7" t="n">
@@ -2205,7 +2199,7 @@
       <c r="M27" s="7" t="n">
         <v>52.84</v>
       </c>
-      <c r="N27" s="33" t="n">
+      <c r="N27" s="31" t="n">
         <v>0.514</v>
       </c>
       <c r="O27" s="12" t="inlineStr">
@@ -2220,7 +2214,7 @@
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
+          <t>Reprecificar e Remanejar (Amazon R$ 52.84)</t>
         </is>
       </c>
     </row>
@@ -2251,14 +2245,14 @@
         <v>-1</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>2918</v>
+        <v>0</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K28" s="18" t="n">
@@ -2287,7 +2281,7 @@
       </c>
       <c r="Q28" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2318,14 +2312,14 @@
         <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>25884</v>
+        <v>92</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>20.56</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K29" s="26" t="inlineStr"/>
@@ -2344,7 +2338,7 @@
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2375,14 +2369,14 @@
         <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K30" s="28" t="inlineStr"/>
@@ -2407,7 +2401,7 @@
       </c>
       <c r="Q30" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2438,14 +2432,14 @@
         <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>5014</v>
+        <v>0</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K31" s="26" t="inlineStr"/>
@@ -2464,7 +2458,7 @@
       </c>
       <c r="Q31" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2495,14 +2489,14 @@
         <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>26558</v>
+        <v>16</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>21.09</v>
+        <v>0.01</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K32" s="28" t="inlineStr"/>
@@ -2521,7 +2515,7 @@
       </c>
       <c r="Q32" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2552,14 +2546,14 @@
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>5078</v>
+        <v>0</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K33" s="26" t="inlineStr"/>
@@ -2578,7 +2572,7 @@
       </c>
       <c r="Q33" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2609,10 +2603,10 @@
         <v>-1</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>1770</v>
-      </c>
-      <c r="I34" s="32" t="n">
-        <v>1.41</v>
+        <v>0</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -2676,10 +2670,10 @@
         <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>975</v>
-      </c>
-      <c r="I35" s="30" t="n">
-        <v>0.77</v>
+        <v>0</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2743,14 +2737,14 @@
         <v>-1</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>16250</v>
+        <v>0</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>12.91</v>
+        <v>0</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K36" s="28" t="inlineStr"/>
@@ -2769,7 +2763,7 @@
       </c>
       <c r="Q36" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2800,14 +2794,14 @@
         <v>-1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>3282</v>
+        <v>0</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K37" s="7" t="n">
@@ -2836,7 +2830,7 @@
       </c>
       <c r="Q37" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2867,14 +2861,14 @@
         <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>6401</v>
+        <v>0</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K38" s="18" t="n">
@@ -2903,7 +2897,7 @@
       </c>
       <c r="Q38" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2934,14 +2928,14 @@
         <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>9302</v>
+        <v>0</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K39" s="7" t="n">
@@ -2955,7 +2949,7 @@
       <c r="M39" s="7" t="n">
         <v>97.69</v>
       </c>
-      <c r="N39" s="33" t="n">
+      <c r="N39" s="31" t="n">
         <v>0.111</v>
       </c>
       <c r="O39" s="12" t="inlineStr">
@@ -2970,7 +2964,7 @@
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -3001,14 +2995,14 @@
         <v>-1</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>8714</v>
+        <v>0</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K40" s="18" t="n">
@@ -3022,7 +3016,7 @@
       <c r="M40" s="18" t="n">
         <v>83.44</v>
       </c>
-      <c r="N40" s="31" t="n">
+      <c r="N40" s="30" t="n">
         <v>0.411</v>
       </c>
       <c r="O40" s="23" t="inlineStr">
@@ -3037,7 +3031,7 @@
       </c>
       <c r="Q40" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 83.44)</t>
+          <t>Reprecificar e Remanejar (Drogaraia R$ 83.44)</t>
         </is>
       </c>
     </row>
@@ -3068,14 +3062,14 @@
         <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>3254</v>
+        <v>0</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K41" s="26" t="inlineStr"/>
@@ -3094,7 +3088,7 @@
       </c>
       <c r="Q41" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3125,14 +3119,14 @@
         <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>40618</v>
+        <v>28</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>32.26</v>
+        <v>0.02</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K42" s="28" t="inlineStr"/>
@@ -3151,7 +3145,7 @@
       </c>
       <c r="Q42" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3182,14 +3176,14 @@
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>2850</v>
+        <v>0</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K43" s="7" t="n">
@@ -3203,7 +3197,7 @@
       <c r="M43" s="7" t="n">
         <v>197.18</v>
       </c>
-      <c r="N43" s="33" t="n">
+      <c r="N43" s="31" t="n">
         <v>0.109</v>
       </c>
       <c r="O43" s="12" t="inlineStr">
@@ -3218,7 +3212,7 @@
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Reprecificar e Remanejar (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -3249,14 +3243,14 @@
         <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>3834</v>
+        <v>0</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K44" s="28" t="inlineStr"/>
@@ -3275,7 +3269,7 @@
       </c>
       <c r="Q44" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3306,10 +3300,10 @@
         <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>864</v>
-      </c>
-      <c r="I45" s="30" t="n">
-        <v>0.6899999999999999</v>
+        <v>2</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -3327,7 +3321,7 @@
       <c r="M45" s="7" t="n">
         <v>236.6</v>
       </c>
-      <c r="N45" s="33" t="n">
+      <c r="N45" s="31" t="n">
         <v>0.333</v>
       </c>
       <c r="O45" s="12" t="inlineStr">
@@ -3373,14 +3367,14 @@
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>17247</v>
+        <v>16</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>13.7</v>
+        <v>0.01</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K46" s="18" t="n">
@@ -3394,7 +3388,7 @@
       <c r="M46" s="18" t="n">
         <v>55.67</v>
       </c>
-      <c r="N46" s="31" t="n">
+      <c r="N46" s="30" t="n">
         <v>0.333</v>
       </c>
       <c r="O46" s="23" t="inlineStr">
@@ -3409,7 +3403,7 @@
       </c>
       <c r="Q46" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -3440,10 +3434,10 @@
         <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>1277</v>
-      </c>
-      <c r="I47" s="30" t="n">
-        <v>1.01</v>
+        <v>0</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3497,14 +3491,14 @@
         <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>12293</v>
+        <v>0</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>9.76</v>
+        <v>0</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K48" s="18" t="n">
@@ -3518,7 +3512,7 @@
       <c r="M48" s="18" t="n">
         <v>59.9</v>
       </c>
-      <c r="N48" s="31" t="n">
+      <c r="N48" s="30" t="n">
         <v>0.167</v>
       </c>
       <c r="O48" s="23" t="inlineStr">
@@ -3533,7 +3527,7 @@
       </c>
       <c r="Q48" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 59.90)</t>
         </is>
       </c>
     </row>
@@ -3564,14 +3558,14 @@
         <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>4074</v>
+        <v>8</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>3.24</v>
+        <v>0.01</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K49" s="7" t="n">
@@ -3585,7 +3579,7 @@
       <c r="M49" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="N49" s="33" t="n">
+      <c r="N49" s="31" t="n">
         <v>0.396</v>
       </c>
       <c r="O49" s="12" t="inlineStr">
@@ -3600,7 +3594,7 @@
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -3631,14 +3625,14 @@
         <v>-1</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>4480</v>
+        <v>0</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K50" s="28" t="inlineStr"/>
@@ -3663,7 +3657,7 @@
       </c>
       <c r="Q50" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3694,14 +3688,14 @@
         <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>2511</v>
+        <v>0</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K51" s="26" t="inlineStr"/>
@@ -3720,7 +3714,7 @@
       </c>
       <c r="Q51" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3751,14 +3745,14 @@
         <v>-1</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>4849</v>
+        <v>0</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K52" s="18" t="n">
@@ -3772,7 +3766,7 @@
       <c r="M52" s="18" t="n">
         <v>49.9</v>
       </c>
-      <c r="N52" s="31" t="n">
+      <c r="N52" s="30" t="n">
         <v>0.904</v>
       </c>
       <c r="O52" s="23" t="inlineStr">
@@ -3787,7 +3781,7 @@
       </c>
       <c r="Q52" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+          <t>Reprecificar e Remanejar (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -3818,14 +3812,14 @@
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>10126</v>
+        <v>0</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K53" s="7" t="n">
@@ -3839,7 +3833,7 @@
       <c r="M53" s="7" t="n">
         <v>35.9</v>
       </c>
-      <c r="N53" s="33" t="n">
+      <c r="N53" s="31" t="n">
         <v>0.08400000000000001</v>
       </c>
       <c r="O53" s="12" t="inlineStr">
@@ -3854,7 +3848,7 @@
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Panvel R$ 35.90)</t>
+          <t>Reprecificar e Remanejar (Panvel R$ 35.90)</t>
         </is>
       </c>
     </row>
@@ -3885,14 +3879,14 @@
         <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>11018</v>
+        <v>1</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K54" s="28" t="inlineStr"/>
@@ -3911,44 +3905,44 @@
       </c>
       <c r="Q54" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="34" t="inlineStr">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t>TOTAL TOP 50</t>
         </is>
       </c>
-      <c r="B55" s="35" t="n"/>
-      <c r="C55" s="35" t="n"/>
-      <c r="D55" s="36">
+      <c r="B55" s="33" t="n"/>
+      <c r="C55" s="33" t="n"/>
+      <c r="D55" s="34">
         <f>SUM(D5:D54)</f>
         <v/>
       </c>
-      <c r="E55" s="36">
+      <c r="E55" s="34">
         <f>SUM(E5:E54)</f>
         <v/>
       </c>
-      <c r="F55" s="37">
+      <c r="F55" s="35">
         <f>SUM(F5:F54)</f>
         <v/>
       </c>
-      <c r="G55" s="38">
+      <c r="G55" s="36">
         <f>(D55-E55)/E55</f>
         <v/>
       </c>
-      <c r="H55" s="39" t="n"/>
-      <c r="I55" s="39" t="inlineStr"/>
-      <c r="J55" s="39" t="inlineStr"/>
-      <c r="K55" s="39" t="inlineStr"/>
-      <c r="L55" s="39" t="inlineStr"/>
-      <c r="M55" s="39" t="inlineStr"/>
-      <c r="N55" s="39" t="inlineStr"/>
-      <c r="O55" s="39" t="inlineStr"/>
-      <c r="P55" s="39" t="inlineStr"/>
-      <c r="Q55" s="39" t="inlineStr"/>
+      <c r="H55" s="37" t="n"/>
+      <c r="I55" s="37" t="inlineStr"/>
+      <c r="J55" s="37" t="inlineStr"/>
+      <c r="K55" s="37" t="inlineStr"/>
+      <c r="L55" s="37" t="inlineStr"/>
+      <c r="M55" s="37" t="inlineStr"/>
+      <c r="N55" s="37" t="inlineStr"/>
+      <c r="O55" s="37" t="inlineStr"/>
+      <c r="P55" s="37" t="inlineStr"/>
+      <c r="Q55" s="37" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -237,7 +237,7 @@
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -270,7 +270,7 @@
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -294,7 +294,13 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -824,14 +830,14 @@
         <v>-1</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0</v>
+        <v>11783</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K5" s="7" t="n">
@@ -860,7 +866,7 @@
       </c>
       <c r="Q5" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -891,14 +897,14 @@
         <v>-1</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>0</v>
+        <v>9805</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>0</v>
+        <v>7.79</v>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K6" s="18" t="n">
@@ -927,7 +933,7 @@
       </c>
       <c r="Q6" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -958,14 +964,14 @@
         <v>-1</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>21</v>
+        <v>10635</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.02</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K7" s="26" t="inlineStr"/>
@@ -984,7 +990,7 @@
       </c>
       <c r="Q7" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1015,14 +1021,14 @@
         <v>-1</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>0</v>
+        <v>4477</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K8" s="18" t="n">
@@ -1051,7 +1057,7 @@
       </c>
       <c r="Q8" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1082,14 +1088,14 @@
         <v>-1</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>3</v>
+        <v>12111</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K9" s="26" t="inlineStr"/>
@@ -1108,7 +1114,7 @@
       </c>
       <c r="Q9" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1139,14 +1145,14 @@
         <v>-1</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>0</v>
+        <v>7624</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K10" s="28" t="inlineStr"/>
@@ -1165,7 +1171,7 @@
       </c>
       <c r="Q10" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1196,14 +1202,14 @@
         <v>-1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0</v>
+        <v>3194</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K11" s="7" t="n">
@@ -1232,7 +1238,7 @@
       </c>
       <c r="Q11" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1263,14 +1269,14 @@
         <v>-1</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>0</v>
+        <v>3794</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K12" s="18" t="n">
@@ -1299,7 +1305,7 @@
       </c>
       <c r="Q12" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1330,10 +1336,10 @@
         <v>-1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="I13" s="30" t="n">
+        <v>0.87</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1387,14 +1393,14 @@
         <v>-1</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>0</v>
+        <v>9899</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>0</v>
+        <v>7.86</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K14" s="18" t="n">
@@ -1423,7 +1429,7 @@
       </c>
       <c r="Q14" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1454,14 +1460,14 @@
         <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8</v>
+        <v>4215</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.01</v>
+        <v>3.35</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K15" s="7" t="n">
@@ -1490,7 +1496,7 @@
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1521,14 +1527,14 @@
         <v>-1</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>52</v>
+        <v>16452</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>0.04</v>
+        <v>13.07</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K16" s="18" t="n">
@@ -1542,7 +1548,7 @@
       <c r="M16" s="18" t="n">
         <v>59.99</v>
       </c>
-      <c r="N16" s="30" t="n">
+      <c r="N16" s="31" t="n">
         <v>0.342</v>
       </c>
       <c r="O16" s="23" t="inlineStr">
@@ -1557,7 +1563,7 @@
       </c>
       <c r="Q16" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 59.99)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
         </is>
       </c>
     </row>
@@ -1588,14 +1594,14 @@
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>4</v>
+        <v>11878</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0</v>
+        <v>9.43</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K17" s="26" t="inlineStr"/>
@@ -1614,7 +1620,7 @@
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1645,10 +1651,10 @@
         <v>-1</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="22" t="n">
-        <v>0</v>
+        <v>520</v>
+      </c>
+      <c r="I18" s="32" t="n">
+        <v>0.41</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -1702,14 +1708,14 @@
         <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>6</v>
+        <v>16881</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>0</v>
+        <v>13.41</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K19" s="26" t="inlineStr"/>
@@ -1728,7 +1734,7 @@
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1767,7 @@
       <c r="H20" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
@@ -1816,14 +1822,14 @@
         <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>0</v>
+        <v>2289</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K21" s="26" t="inlineStr"/>
@@ -1842,7 +1848,7 @@
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1873,14 +1879,14 @@
         <v>-1</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>0</v>
+        <v>10177</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K22" s="28" t="inlineStr"/>
@@ -1899,7 +1905,7 @@
       </c>
       <c r="Q22" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1930,14 +1936,14 @@
         <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>2</v>
+        <v>11077</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K23" s="26" t="inlineStr"/>
@@ -1956,7 +1962,7 @@
       </c>
       <c r="Q23" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1987,14 +1993,14 @@
         <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>0</v>
+        <v>3359</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K24" s="18" t="n">
@@ -2023,7 +2029,7 @@
       </c>
       <c r="Q24" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2054,14 +2060,14 @@
         <v>-1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>0</v>
+        <v>8641</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K25" s="26" t="inlineStr"/>
@@ -2080,7 +2086,7 @@
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2111,14 +2117,14 @@
         <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>0</v>
+        <v>2492</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K26" s="18" t="n">
@@ -2132,7 +2138,7 @@
       <c r="M26" s="18" t="n">
         <v>46.85</v>
       </c>
-      <c r="N26" s="30" t="n">
+      <c r="N26" s="31" t="n">
         <v>1.132</v>
       </c>
       <c r="O26" s="23" t="inlineStr">
@@ -2147,7 +2153,7 @@
       </c>
       <c r="Q26" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Amazon R$ 46.85)</t>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -2178,14 +2184,14 @@
         <v>-1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>29</v>
+        <v>19037</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>0.02</v>
+        <v>15.12</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K27" s="7" t="n">
@@ -2199,7 +2205,7 @@
       <c r="M27" s="7" t="n">
         <v>52.84</v>
       </c>
-      <c r="N27" s="31" t="n">
+      <c r="N27" s="33" t="n">
         <v>0.514</v>
       </c>
       <c r="O27" s="12" t="inlineStr">
@@ -2214,7 +2220,7 @@
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Amazon R$ 52.84)</t>
+          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
         </is>
       </c>
     </row>
@@ -2245,14 +2251,14 @@
         <v>-1</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>0</v>
+        <v>2918</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K28" s="18" t="n">
@@ -2281,7 +2287,7 @@
       </c>
       <c r="Q28" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2312,14 +2318,14 @@
         <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>92</v>
+        <v>25884</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>20.56</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K29" s="26" t="inlineStr"/>
@@ -2338,7 +2344,7 @@
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2369,14 +2375,14 @@
         <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K30" s="28" t="inlineStr"/>
@@ -2401,7 +2407,7 @@
       </c>
       <c r="Q30" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2432,14 +2438,14 @@
         <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>0</v>
+        <v>5014</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K31" s="26" t="inlineStr"/>
@@ -2458,7 +2464,7 @@
       </c>
       <c r="Q31" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2489,14 +2495,14 @@
         <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>16</v>
+        <v>26558</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>0.01</v>
+        <v>21.09</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K32" s="28" t="inlineStr"/>
@@ -2515,7 +2521,7 @@
       </c>
       <c r="Q32" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2546,14 +2552,14 @@
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>0</v>
+        <v>5078</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K33" s="26" t="inlineStr"/>
@@ -2572,7 +2578,7 @@
       </c>
       <c r="Q33" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2603,10 +2609,10 @@
         <v>-1</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>0</v>
+        <v>1770</v>
+      </c>
+      <c r="I34" s="32" t="n">
+        <v>1.41</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -2670,10 +2676,10 @@
         <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>0</v>
+        <v>975</v>
+      </c>
+      <c r="I35" s="30" t="n">
+        <v>0.77</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2737,14 +2743,14 @@
         <v>-1</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>0</v>
+        <v>16250</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>0</v>
+        <v>12.91</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K36" s="28" t="inlineStr"/>
@@ -2763,7 +2769,7 @@
       </c>
       <c r="Q36" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2794,14 +2800,14 @@
         <v>-1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>0</v>
+        <v>3282</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K37" s="7" t="n">
@@ -2830,7 +2836,7 @@
       </c>
       <c r="Q37" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2861,14 +2867,14 @@
         <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>0</v>
+        <v>6401</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K38" s="18" t="n">
@@ -2897,7 +2903,7 @@
       </c>
       <c r="Q38" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2928,14 +2934,14 @@
         <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>0</v>
+        <v>9302</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K39" s="7" t="n">
@@ -2949,7 +2955,7 @@
       <c r="M39" s="7" t="n">
         <v>97.69</v>
       </c>
-      <c r="N39" s="31" t="n">
+      <c r="N39" s="33" t="n">
         <v>0.111</v>
       </c>
       <c r="O39" s="12" t="inlineStr">
@@ -2964,7 +2970,7 @@
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 97.69)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -2995,14 +3001,14 @@
         <v>-1</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>0</v>
+        <v>8714</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K40" s="18" t="n">
@@ -3016,7 +3022,7 @@
       <c r="M40" s="18" t="n">
         <v>83.44</v>
       </c>
-      <c r="N40" s="30" t="n">
+      <c r="N40" s="31" t="n">
         <v>0.411</v>
       </c>
       <c r="O40" s="23" t="inlineStr">
@@ -3031,7 +3037,7 @@
       </c>
       <c r="Q40" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Drogaraia R$ 83.44)</t>
+          <t>Reprecificar no Digital (Drogaraia R$ 83.44)</t>
         </is>
       </c>
     </row>
@@ -3062,14 +3068,14 @@
         <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>0</v>
+        <v>3254</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K41" s="26" t="inlineStr"/>
@@ -3088,7 +3094,7 @@
       </c>
       <c r="Q41" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3119,14 +3125,14 @@
         <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>28</v>
+        <v>40618</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>0.02</v>
+        <v>32.26</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K42" s="28" t="inlineStr"/>
@@ -3145,7 +3151,7 @@
       </c>
       <c r="Q42" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3176,14 +3182,14 @@
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>0</v>
+        <v>2850</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K43" s="7" t="n">
@@ -3197,7 +3203,7 @@
       <c r="M43" s="7" t="n">
         <v>197.18</v>
       </c>
-      <c r="N43" s="31" t="n">
+      <c r="N43" s="33" t="n">
         <v>0.109</v>
       </c>
       <c r="O43" s="12" t="inlineStr">
@@ -3212,7 +3218,7 @@
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Farmaciasnissei R$ 197.18)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -3243,14 +3249,14 @@
         <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>0</v>
+        <v>3834</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K44" s="28" t="inlineStr"/>
@@ -3269,7 +3275,7 @@
       </c>
       <c r="Q44" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3300,10 +3306,10 @@
         <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" s="11" t="n">
-        <v>0</v>
+        <v>864</v>
+      </c>
+      <c r="I45" s="30" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -3321,7 +3327,7 @@
       <c r="M45" s="7" t="n">
         <v>236.6</v>
       </c>
-      <c r="N45" s="31" t="n">
+      <c r="N45" s="33" t="n">
         <v>0.333</v>
       </c>
       <c r="O45" s="12" t="inlineStr">
@@ -3367,14 +3373,14 @@
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>16</v>
+        <v>17247</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>0.01</v>
+        <v>13.7</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K46" s="18" t="n">
@@ -3388,7 +3394,7 @@
       <c r="M46" s="18" t="n">
         <v>55.67</v>
       </c>
-      <c r="N46" s="30" t="n">
+      <c r="N46" s="31" t="n">
         <v>0.333</v>
       </c>
       <c r="O46" s="23" t="inlineStr">
@@ -3403,7 +3409,7 @@
       </c>
       <c r="Q46" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 55.67)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -3434,10 +3440,10 @@
         <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>0</v>
+        <v>1277</v>
+      </c>
+      <c r="I47" s="30" t="n">
+        <v>1.01</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3491,14 +3497,14 @@
         <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>0</v>
+        <v>12293</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K48" s="18" t="n">
@@ -3512,7 +3518,7 @@
       <c r="M48" s="18" t="n">
         <v>59.9</v>
       </c>
-      <c r="N48" s="30" t="n">
+      <c r="N48" s="31" t="n">
         <v>0.167</v>
       </c>
       <c r="O48" s="23" t="inlineStr">
@@ -3527,7 +3533,7 @@
       </c>
       <c r="Q48" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 59.90)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
         </is>
       </c>
     </row>
@@ -3558,14 +3564,14 @@
         <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>8</v>
+        <v>4074</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>0.01</v>
+        <v>3.24</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K49" s="7" t="n">
@@ -3579,7 +3585,7 @@
       <c r="M49" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="N49" s="31" t="n">
+      <c r="N49" s="33" t="n">
         <v>0.396</v>
       </c>
       <c r="O49" s="12" t="inlineStr">
@@ -3594,7 +3600,7 @@
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 107.00)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -3625,14 +3631,14 @@
         <v>-1</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>0</v>
+        <v>4480</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K50" s="28" t="inlineStr"/>
@@ -3657,7 +3663,7 @@
       </c>
       <c r="Q50" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3688,14 +3694,14 @@
         <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>0</v>
+        <v>2511</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K51" s="26" t="inlineStr"/>
@@ -3714,7 +3720,7 @@
       </c>
       <c r="Q51" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -3745,14 +3751,14 @@
         <v>-1</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>0</v>
+        <v>4849</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K52" s="18" t="n">
@@ -3766,7 +3772,7 @@
       <c r="M52" s="18" t="n">
         <v>49.9</v>
       </c>
-      <c r="N52" s="30" t="n">
+      <c r="N52" s="31" t="n">
         <v>0.904</v>
       </c>
       <c r="O52" s="23" t="inlineStr">
@@ -3781,7 +3787,7 @@
       </c>
       <c r="Q52" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Amazon R$ 49.90)</t>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -3812,14 +3818,14 @@
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>0</v>
+        <v>10126</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K53" s="7" t="n">
@@ -3833,7 +3839,7 @@
       <c r="M53" s="7" t="n">
         <v>35.9</v>
       </c>
-      <c r="N53" s="31" t="n">
+      <c r="N53" s="33" t="n">
         <v>0.08400000000000001</v>
       </c>
       <c r="O53" s="12" t="inlineStr">
@@ -3848,7 +3854,7 @@
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Panvel R$ 35.90)</t>
+          <t>Reprecificar no Digital (Panvel R$ 35.90)</t>
         </is>
       </c>
     </row>
@@ -3879,14 +3885,14 @@
         <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>1</v>
+        <v>11018</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K54" s="28" t="inlineStr"/>
@@ -3905,44 +3911,44 @@
       </c>
       <c r="Q54" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="32" t="inlineStr">
+      <c r="A55" s="34" t="inlineStr">
         <is>
           <t>TOTAL TOP 50</t>
         </is>
       </c>
-      <c r="B55" s="33" t="n"/>
-      <c r="C55" s="33" t="n"/>
-      <c r="D55" s="34">
+      <c r="B55" s="35" t="n"/>
+      <c r="C55" s="35" t="n"/>
+      <c r="D55" s="36">
         <f>SUM(D5:D54)</f>
         <v/>
       </c>
-      <c r="E55" s="34">
+      <c r="E55" s="36">
         <f>SUM(E5:E54)</f>
         <v/>
       </c>
-      <c r="F55" s="35">
+      <c r="F55" s="37">
         <f>SUM(F5:F54)</f>
         <v/>
       </c>
-      <c r="G55" s="36">
+      <c r="G55" s="38">
         <f>(D55-E55)/E55</f>
         <v/>
       </c>
-      <c r="H55" s="37" t="n"/>
-      <c r="I55" s="37" t="inlineStr"/>
-      <c r="J55" s="37" t="inlineStr"/>
-      <c r="K55" s="37" t="inlineStr"/>
-      <c r="L55" s="37" t="inlineStr"/>
-      <c r="M55" s="37" t="inlineStr"/>
-      <c r="N55" s="37" t="inlineStr"/>
-      <c r="O55" s="37" t="inlineStr"/>
-      <c r="P55" s="37" t="inlineStr"/>
-      <c r="Q55" s="37" t="inlineStr"/>
+      <c r="H55" s="39" t="n"/>
+      <c r="I55" s="39" t="inlineStr"/>
+      <c r="J55" s="39" t="inlineStr"/>
+      <c r="K55" s="39" t="inlineStr"/>
+      <c r="L55" s="39" t="inlineStr"/>
+      <c r="M55" s="39" t="inlineStr"/>
+      <c r="N55" s="39" t="inlineStr"/>
+      <c r="O55" s="39" t="inlineStr"/>
+      <c r="P55" s="39" t="inlineStr"/>
+      <c r="Q55" s="39" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 01:32:50 (01:32) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 05:53:44 (05:53) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -830,10 +830,10 @@
         <v>-1</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>11783</v>
+        <v>11192</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>9.359999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
         <v>-1</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>9805</v>
+        <v>9353</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>7.79</v>
+        <v>7.43</v>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         <v>-1</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>10635</v>
+        <v>10632</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>8.449999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         <v>-1</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>4477</v>
+        <v>4288</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>3.56</v>
+        <v>3.41</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
         <v>-1</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>12111</v>
+        <v>10582</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>9.619999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1145,10 +1145,10 @@
         <v>-1</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>7624</v>
+        <v>9727</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>6.06</v>
+        <v>7.73</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
@@ -1202,10 +1202,10 @@
         <v>-1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>3194</v>
+        <v>3069</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
         <v>-1</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>3794</v>
+        <v>3723</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         <v>-1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>1100</v>
+        <v>1048</v>
       </c>
       <c r="I13" s="30" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         <v>-1</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>9899</v>
+        <v>9409</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>7.86</v>
+        <v>7.47</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -1460,10 +1460,10 @@
         <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>4215</v>
+        <v>4038</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1527,10 +1527,10 @@
         <v>-1</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>16452</v>
+        <v>14766</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>13.07</v>
+        <v>11.73</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>11878</v>
+        <v>11073</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>9.43</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1651,10 +1651,10 @@
         <v>-1</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="I18" s="32" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>16881</v>
+        <v>16016</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>13.41</v>
+        <v>12.72</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1744,35 +1744,35 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>100001402</t>
+          <t>10041262</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>SERVICO DOMICILIO</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>66.20999999999999</v>
+        <v>43.05</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-44.51</v>
+        <v>-43.05</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>-0.672</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="32" t="n">
-        <v>0</v>
+        <v>2151</v>
+      </c>
+      <c r="I20" s="22" t="n">
+        <v>1.71</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K20" s="28" t="inlineStr"/>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Q20" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1801,31 +1801,31 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10041262</t>
+          <t>10041259</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
+          <t>FR HUGGIES MAXIMA PROT MAX G 92UN</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>43.05</v>
+        <v>38.27</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-43.05</v>
+        <v>-38.27</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>2289</v>
+        <v>9391</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1.82</v>
+        <v>7.46</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1858,31 +1858,31 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10041259</t>
+          <t>10041297</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX G 92UN</t>
+          <t>FR HUGGIES MAXIMA PROT MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>38.27</v>
+        <v>35.11</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-38.27</v>
+        <v>-35.11</v>
       </c>
       <c r="G22" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>10177</v>
+        <v>10099</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>8.08</v>
+        <v>8.02</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
@@ -1915,44 +1915,54 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10041297</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX XXXG 70UN</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>35.11</v>
+        <v>34.97</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-35.11</v>
+        <v>-34.97</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>11077</v>
+        <v>3321</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>8.800000000000001</v>
+        <v>2.64</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K23" s="26" t="inlineStr"/>
-      <c r="L23" s="12" t="inlineStr"/>
-      <c r="M23" s="26" t="inlineStr"/>
-      <c r="N23" s="27" t="inlineStr"/>
+      <c r="K23" s="7" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
@@ -1962,7 +1972,7 @@
       </c>
       <c r="Q23" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1972,54 +1982,44 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>34.97</v>
+        <v>32.91</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-34.97</v>
+        <v>-32.91</v>
       </c>
       <c r="G24" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>3359</v>
+        <v>8275</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>2.67</v>
+        <v>6.57</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K24" s="18" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="L24" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N24" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="K24" s="28" t="inlineStr"/>
+      <c r="L24" s="23" t="inlineStr"/>
+      <c r="M24" s="28" t="inlineStr"/>
+      <c r="N24" s="29" t="inlineStr"/>
       <c r="O24" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P24" s="23" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Q24" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2039,35 +2039,35 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>100001402</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>SERVICO DOMICILIO</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0</v>
+        <v>33.5</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>32.91</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-32.91</v>
+        <v>-32.71</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-1</v>
+        <v>-0.494</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>8641</v>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>6.86</v>
+        <v>0</v>
+      </c>
+      <c r="I25" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K25" s="26" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2117,10 +2117,10 @@
         <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>2492</v>
+        <v>2446</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
         <v>-1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>19037</v>
+        <v>17535</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>15.12</v>
+        <v>13.93</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2251,10 +2251,10 @@
         <v>-1</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>2918</v>
+        <v>2858</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
@@ -2318,10 +2318,10 @@
         <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>25884</v>
+        <v>26491</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>20.56</v>
+        <v>21.04</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
         <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>2108</v>
+        <v>2081</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
@@ -2438,10 +2438,10 @@
         <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>5014</v>
+        <v>4696</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -2495,10 +2495,10 @@
         <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>26558</v>
+        <v>26223</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>21.09</v>
+        <v>20.83</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
@@ -2552,10 +2552,10 @@
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>5078</v>
+        <v>4816</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>4.03</v>
+        <v>3.83</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
         <v>-1</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>1770</v>
+        <v>1758</v>
       </c>
       <c r="I34" s="32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>975</v>
+        <v>962</v>
       </c>
       <c r="I35" s="30" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         <v>-1</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>16250</v>
+        <v>15647</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>12.91</v>
+        <v>12.43</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         <v>-1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>3282</v>
+        <v>3213</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2867,10 +2867,10 @@
         <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>6401</v>
+        <v>6179</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>5.08</v>
+        <v>4.91</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>9302</v>
+        <v>8909</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>7.39</v>
+        <v>7.08</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         <v>-1</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>8714</v>
+        <v>8432</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>6.92</v>
+        <v>6.7</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>3254</v>
+        <v>3146</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -3125,10 +3125,10 @@
         <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>40618</v>
+        <v>39477</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>32.26</v>
+        <v>31.36</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>2850</v>
+        <v>2931</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
         <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>3834</v>
+        <v>3758</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>864</v>
+        <v>837</v>
       </c>
       <c r="I45" s="30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>17247</v>
+        <v>16877</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>13.7</v>
+        <v>13.41</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="I47" s="30" t="n">
         <v>1.01</v>
@@ -3497,10 +3497,10 @@
         <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>12293</v>
+        <v>11473</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>9.76</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
@@ -3564,10 +3564,10 @@
         <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>4074</v>
+        <v>3992</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         <v>-1</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>4480</v>
+        <v>4427</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
         <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>2511</v>
+        <v>2481</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -3751,10 +3751,10 @@
         <v>-1</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>4849</v>
+        <v>4815</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
@@ -3818,10 +3818,10 @@
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>10126</v>
+        <v>9757</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>8.039999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3864,44 +3864,54 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>10038743</t>
+          <t>10050642</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG SUPER XXXG 44U</t>
+          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>16.55</v>
+        <v>16.23</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-16.55</v>
+        <v>-16.23</v>
       </c>
       <c r="G54" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>11018</v>
+        <v>5711</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>8.75</v>
+        <v>4.54</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K54" s="28" t="inlineStr"/>
-      <c r="L54" s="23" t="inlineStr"/>
-      <c r="M54" s="28" t="inlineStr"/>
-      <c r="N54" s="29" t="inlineStr"/>
+      <c r="K54" s="18" t="n">
+        <v>955.85</v>
+      </c>
+      <c r="L54" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M54" s="18" t="n">
+        <v>955.85</v>
+      </c>
+      <c r="N54" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O54" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P54" s="23" t="inlineStr">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -282,28 +282,28 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 05:53:44 (05:53) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 07:03:12 (07:03) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>686.6799999999999</v>
+        <v>979.1799999999999</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-686.6799999999999</v>
+        <v>-979.1799999999999</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>-1</v>
@@ -888,10 +888,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>321.74</v>
+        <v>458.79</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-321.74</v>
+        <v>-458.79</v>
       </c>
       <c r="G6" s="20" t="n">
         <v>-1</v>
@@ -943,44 +943,54 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10042969</t>
+          <t>10046654</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO XXG 112UN</t>
+          <t>MOUNJARO 7,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>213.1</v>
+        <v>208.81</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-213.1</v>
+        <v>-208.81</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>10632</v>
+        <v>4288</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>8.44</v>
+        <v>3.41</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K7" s="26" t="inlineStr"/>
-      <c r="L7" s="12" t="inlineStr"/>
-      <c r="M7" s="26" t="inlineStr"/>
-      <c r="N7" s="27" t="inlineStr"/>
+      <c r="K7" s="7" t="n">
+        <v>2766.26</v>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>2766.26</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
@@ -990,7 +1000,7 @@
       </c>
       <c r="Q7" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1000,54 +1010,44 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>10046654</t>
+          <t>10053130</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 7,5MG 4CAN APLIC LILLY</t>
+          <t>OZIVY 1MG 1CAN 3ML EMS</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>146.44</v>
+        <v>138.5</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-146.44</v>
+        <v>-138.5</v>
       </c>
       <c r="G8" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>4288</v>
+        <v>10582</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>3.41</v>
+        <v>8.41</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K8" s="18" t="n">
-        <v>2766.26</v>
-      </c>
-      <c r="L8" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M8" s="18" t="n">
-        <v>2766.26</v>
-      </c>
-      <c r="N8" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="K8" s="26" t="inlineStr"/>
+      <c r="L8" s="23" t="inlineStr"/>
+      <c r="M8" s="26" t="inlineStr"/>
+      <c r="N8" s="27" t="inlineStr"/>
       <c r="O8" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P8" s="23" t="inlineStr">
@@ -1067,41 +1067,41 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10053130</t>
+          <t>10042967</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>OZIVY 1MG 1CAN 3ML EMS</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO G 128UN</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>97.12</v>
+        <v>129.09</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-97.12</v>
+        <v>-129.09</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>10582</v>
+        <v>9727</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>8.41</v>
+        <v>7.73</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K9" s="26" t="inlineStr"/>
+      <c r="K9" s="28" t="inlineStr"/>
       <c r="L9" s="12" t="inlineStr"/>
-      <c r="M9" s="26" t="inlineStr"/>
-      <c r="N9" s="27" t="inlineStr"/>
+      <c r="M9" s="28" t="inlineStr"/>
+      <c r="N9" s="29" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Q9" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1124,44 +1124,54 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>10042967</t>
+          <t>10046655</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO G 128UN</t>
+          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>90.53</v>
+        <v>124</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-90.53</v>
+        <v>-124</v>
       </c>
       <c r="G10" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>9727</v>
+        <v>3069</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>7.73</v>
+        <v>2.44</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K10" s="28" t="inlineStr"/>
-      <c r="L10" s="23" t="inlineStr"/>
-      <c r="M10" s="28" t="inlineStr"/>
-      <c r="N10" s="29" t="inlineStr"/>
+      <c r="K10" s="18" t="n">
+        <v>3210.85</v>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="n">
+        <v>3210.85</v>
+      </c>
+      <c r="N10" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O10" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P10" s="23" t="inlineStr">
@@ -1171,7 +1181,7 @@
       </c>
       <c r="Q10" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1181,31 +1191,31 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10046655</t>
+          <t>10040802</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
+          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>86.95999999999999</v>
+        <v>107.6</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-86.95999999999999</v>
+        <v>-107.6</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>3069</v>
+        <v>3723</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1213,15 +1223,15 @@
         </is>
       </c>
       <c r="K11" s="7" t="n">
-        <v>3210.85</v>
+        <v>2501.8</v>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
-        <v>3210.85</v>
+        <v>2501.8</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>0</v>
@@ -1248,54 +1258,44 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>10040802</t>
+          <t>10046657</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
+          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>75.45</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-75.45</v>
+        <v>-98.34999999999999</v>
       </c>
       <c r="G12" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>3723</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>2.96</v>
+        <v>1048</v>
+      </c>
+      <c r="I12" s="30" t="n">
+        <v>0.83</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>2501.8</v>
-      </c>
-      <c r="L12" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M12" s="18" t="n">
-        <v>2501.8</v>
-      </c>
-      <c r="N12" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K12" s="26" t="inlineStr"/>
+      <c r="L12" s="23" t="inlineStr"/>
+      <c r="M12" s="26" t="inlineStr"/>
+      <c r="N12" s="27" t="inlineStr"/>
       <c r="O12" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P12" s="23" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Q12" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1315,44 +1315,54 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10046657</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>68.97</v>
+        <v>87.92</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-68.97</v>
+        <v>-87.92</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>1048</v>
-      </c>
-      <c r="I13" s="30" t="n">
-        <v>0.83</v>
+        <v>9409</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>7.47</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K13" s="26" t="inlineStr"/>
-      <c r="L13" s="12" t="inlineStr"/>
-      <c r="M13" s="26" t="inlineStr"/>
-      <c r="N13" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
@@ -1362,7 +1372,7 @@
       </c>
       <c r="Q13" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1372,31 +1382,31 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10050654</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>61.66</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-61.66</v>
+        <v>-78.93000000000001</v>
       </c>
       <c r="G14" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>9409</v>
+        <v>4038</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>7.47</v>
+        <v>3.21</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -1404,7 +1414,7 @@
         </is>
       </c>
       <c r="K14" s="18" t="n">
-        <v>988.22</v>
+        <v>1617.66</v>
       </c>
       <c r="L14" s="23" t="inlineStr">
         <is>
@@ -1412,7 +1422,7 @@
         </is>
       </c>
       <c r="M14" s="18" t="n">
-        <v>988.22</v>
+        <v>1617.66</v>
       </c>
       <c r="N14" s="24" t="n">
         <v>0</v>
@@ -1439,39 +1449,39 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10050654</t>
+          <t>100005474</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
+          <t>NANLAC COMFOR 3 800G NESTLE</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>55.36</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-55.36</v>
+        <v>-76.93000000000001</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>4038</v>
+        <v>14766</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>3.21</v>
+        <v>11.73</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K15" s="7" t="n">
-        <v>1617.66</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
@@ -1479,14 +1489,14 @@
         </is>
       </c>
       <c r="M15" s="7" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="N15" s="13" t="n">
-        <v>0</v>
+        <v>59.99</v>
+      </c>
+      <c r="N15" s="31" t="n">
+        <v>0.342</v>
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
@@ -1494,9 +1504,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q15" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
         </is>
       </c>
     </row>
@@ -1506,54 +1516,44 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>100005474</t>
+          <t>10041258</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>NANLAC COMFOR 3 800G NESTLE</t>
+          <t>FR HUGGIES MAXIMA PROT MAX XG 82UN</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>53.95</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-53.95</v>
+        <v>-69.34999999999999</v>
       </c>
       <c r="G16" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>14766</v>
+        <v>11073</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>11.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>80.48999999999999</v>
-      </c>
-      <c r="L16" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M16" s="18" t="n">
-        <v>59.99</v>
-      </c>
-      <c r="N16" s="31" t="n">
-        <v>0.342</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K16" s="26" t="inlineStr"/>
+      <c r="L16" s="23" t="inlineStr"/>
+      <c r="M16" s="26" t="inlineStr"/>
+      <c r="N16" s="27" t="inlineStr"/>
       <c r="O16" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P16" s="23" t="inlineStr">
@@ -1561,9 +1561,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q16" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
+      <c r="Q16" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1573,41 +1573,41 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10041258</t>
+          <t>10046656</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX XG 82UN</t>
+          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>48.63</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-48.63</v>
+        <v>-65.56999999999999</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>11073</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>8.800000000000001</v>
+        <v>494</v>
+      </c>
+      <c r="I17" s="32" t="n">
+        <v>0.39</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K17" s="26" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K17" s="28" t="inlineStr"/>
       <c r="L17" s="12" t="inlineStr"/>
-      <c r="M17" s="26" t="inlineStr"/>
-      <c r="N17" s="27" t="inlineStr"/>
+      <c r="M17" s="28" t="inlineStr"/>
+      <c r="N17" s="29" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1630,41 +1630,41 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>10046656</t>
+          <t>10052532</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>45.98</v>
+        <v>64.44</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-45.98</v>
+        <v>-64.44</v>
       </c>
       <c r="G18" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>494</v>
-      </c>
-      <c r="I18" s="32" t="n">
-        <v>0.39</v>
+        <v>16016</v>
+      </c>
+      <c r="I18" s="22" t="n">
+        <v>12.72</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K18" s="28" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K18" s="26" t="inlineStr"/>
       <c r="L18" s="23" t="inlineStr"/>
-      <c r="M18" s="28" t="inlineStr"/>
-      <c r="N18" s="29" t="inlineStr"/>
+      <c r="M18" s="26" t="inlineStr"/>
+      <c r="N18" s="27" t="inlineStr"/>
       <c r="O18" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Q18" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1687,41 +1687,41 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10052532</t>
+          <t>10041262</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>45.19</v>
+        <v>61.39</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-45.19</v>
+        <v>-61.39</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>16016</v>
+        <v>2151</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>12.72</v>
+        <v>1.71</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K19" s="26" t="inlineStr"/>
+      <c r="K19" s="28" t="inlineStr"/>
       <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="26" t="inlineStr"/>
-      <c r="N19" s="27" t="inlineStr"/>
+      <c r="M19" s="28" t="inlineStr"/>
+      <c r="N19" s="29" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1744,44 +1744,54 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>10041262</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>43.05</v>
+        <v>49.86</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-43.05</v>
+        <v>-49.86</v>
       </c>
       <c r="G20" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>2151</v>
+        <v>3321</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>1.71</v>
+        <v>2.64</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K20" s="28" t="inlineStr"/>
-      <c r="L20" s="23" t="inlineStr"/>
-      <c r="M20" s="28" t="inlineStr"/>
-      <c r="N20" s="29" t="inlineStr"/>
+      <c r="K20" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N20" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O20" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P20" s="23" t="inlineStr">
@@ -1791,7 +1801,7 @@
       </c>
       <c r="Q20" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1801,41 +1811,41 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10041259</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX G 92UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>38.27</v>
+        <v>46.93</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-38.27</v>
+        <v>-46.93</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>9391</v>
+        <v>8275</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>7.46</v>
+        <v>6.57</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K21" s="26" t="inlineStr"/>
+      <c r="K21" s="28" t="inlineStr"/>
       <c r="L21" s="12" t="inlineStr"/>
-      <c r="M21" s="26" t="inlineStr"/>
-      <c r="N21" s="27" t="inlineStr"/>
+      <c r="M21" s="28" t="inlineStr"/>
+      <c r="N21" s="29" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1858,44 +1868,54 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10041297</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX XXXG 70UN</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>35.11</v>
+        <v>44.16</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-35.11</v>
+        <v>-44.16</v>
       </c>
       <c r="G22" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>10099</v>
+        <v>2446</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>8.02</v>
+        <v>1.94</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K22" s="28" t="inlineStr"/>
-      <c r="L22" s="23" t="inlineStr"/>
-      <c r="M22" s="28" t="inlineStr"/>
-      <c r="N22" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M22" s="18" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="N22" s="33" t="n">
+        <v>1.132</v>
+      </c>
       <c r="O22" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P22" s="23" t="inlineStr">
@@ -1903,9 +1923,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q22" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -1915,54 +1935,54 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10106687</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>APTANUTRI PREMIUM 3 800G DANONE</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>34.97</v>
+        <v>43.75</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-34.97</v>
+        <v>-43.75</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>3321</v>
+        <v>17535</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>2.64</v>
+        <v>13.93</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K23" s="7" t="n">
-        <v>1298.54</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N23" s="13" t="n">
-        <v>0</v>
+        <v>52.84</v>
+      </c>
+      <c r="N23" s="31" t="n">
+        <v>0.514</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
@@ -1970,9 +1990,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q23" s="14" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
         </is>
       </c>
     </row>
@@ -1982,44 +2002,54 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10030119</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>32.91</v>
+        <v>42.88</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-32.91</v>
+        <v>-42.88</v>
       </c>
       <c r="G24" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>8275</v>
+        <v>2858</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>6.57</v>
+        <v>2.27</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K24" s="28" t="inlineStr"/>
-      <c r="L24" s="23" t="inlineStr"/>
-      <c r="M24" s="28" t="inlineStr"/>
-      <c r="N24" s="29" t="inlineStr"/>
+      <c r="K24" s="18" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M24" s="18" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="N24" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O24" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P24" s="23" t="inlineStr">
@@ -2029,7 +2059,7 @@
       </c>
       <c r="Q24" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2039,41 +2069,47 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>100001402</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>SERVICO DOMICILIO</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>33.5</v>
+        <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>66.20999999999999</v>
+        <v>36.85</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-32.71</v>
+        <v>-36.85</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.494</v>
+        <v>-1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="30" t="n">
-        <v>0</v>
+        <v>2081</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>1.65</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K25" s="26" t="inlineStr"/>
-      <c r="L25" s="12" t="inlineStr"/>
-      <c r="M25" s="26" t="inlineStr"/>
-      <c r="N25" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K25" s="28" t="inlineStr"/>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>549.9</v>
+      </c>
+      <c r="N25" s="29" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2086,7 +2122,7 @@
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2096,54 +2132,44 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10052538</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XXG 74</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>30.97</v>
+        <v>34.81</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-30.97</v>
+        <v>-34.81</v>
       </c>
       <c r="G26" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>2446</v>
+        <v>4696</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>1.94</v>
+        <v>3.73</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K26" s="18" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="L26" s="23" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M26" s="18" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N26" s="31" t="n">
-        <v>1.132</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K26" s="26" t="inlineStr"/>
+      <c r="L26" s="23" t="inlineStr"/>
+      <c r="M26" s="26" t="inlineStr"/>
+      <c r="N26" s="27" t="inlineStr"/>
       <c r="O26" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P26" s="23" t="inlineStr">
@@ -2151,9 +2177,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q26" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+      <c r="Q26" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2163,54 +2189,44 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10106687</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>APTANUTRI PREMIUM 3 800G DANONE</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>30.68</v>
+        <v>32.04</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-30.68</v>
+        <v>-32.04</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>17535</v>
+        <v>26223</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>13.93</v>
+        <v>20.83</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>52.84</v>
-      </c>
-      <c r="N27" s="33" t="n">
-        <v>0.514</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K27" s="28" t="inlineStr"/>
+      <c r="L27" s="12" t="inlineStr"/>
+      <c r="M27" s="28" t="inlineStr"/>
+      <c r="N27" s="29" t="inlineStr"/>
       <c r="O27" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P27" s="12" t="inlineStr">
@@ -2218,9 +2234,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
+      <c r="Q27" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2230,54 +2246,44 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10030119</t>
+          <t>10052539</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>30.07</v>
+        <v>30.86</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-30.07</v>
+        <v>-30.86</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>2858</v>
+        <v>4816</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>2.27</v>
+        <v>3.83</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K28" s="18" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="L28" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M28" s="18" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="N28" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="K28" s="26" t="inlineStr"/>
+      <c r="L28" s="23" t="inlineStr"/>
+      <c r="M28" s="26" t="inlineStr"/>
+      <c r="N28" s="27" t="inlineStr"/>
       <c r="O28" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P28" s="23" t="inlineStr">
@@ -2287,7 +2293,7 @@
       </c>
       <c r="Q28" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2297,44 +2303,54 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10001144</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG SUPER XG 58UN</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>27.39</v>
+        <v>29.92</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-27.39</v>
+        <v>-29.92</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>26491</v>
-      </c>
-      <c r="I29" s="11" t="n">
-        <v>21.04</v>
+        <v>1758</v>
+      </c>
+      <c r="I29" s="32" t="n">
+        <v>1.4</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K29" s="26" t="inlineStr"/>
-      <c r="L29" s="12" t="inlineStr"/>
-      <c r="M29" s="26" t="inlineStr"/>
-      <c r="N29" s="27" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>1945.09</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
@@ -2344,7 +2360,7 @@
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2354,50 +2370,54 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10051359</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>25.84</v>
+        <v>29.81</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-25.84</v>
+        <v>-29.81</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>2081</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>1.65</v>
+        <v>962</v>
+      </c>
+      <c r="I30" s="30" t="n">
+        <v>0.76</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K30" s="28" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>309</v>
+      </c>
       <c r="L30" s="23" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M30" s="18" t="n">
-        <v>549.9</v>
-      </c>
-      <c r="N30" s="29" t="inlineStr"/>
+        <v>449</v>
+      </c>
+      <c r="N30" s="24" t="n">
+        <v>-0.312</v>
+      </c>
       <c r="O30" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P30" s="23" t="inlineStr">
@@ -2407,7 +2427,7 @@
       </c>
       <c r="Q30" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2417,41 +2437,41 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10052538</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XXG 74</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>24.41</v>
+        <v>29.7</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-24.41</v>
+        <v>-29.7</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>4696</v>
+        <v>15647</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>3.73</v>
+        <v>12.43</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K31" s="26" t="inlineStr"/>
+      <c r="K31" s="28" t="inlineStr"/>
       <c r="L31" s="12" t="inlineStr"/>
-      <c r="M31" s="26" t="inlineStr"/>
-      <c r="N31" s="27" t="inlineStr"/>
+      <c r="M31" s="28" t="inlineStr"/>
+      <c r="N31" s="29" t="inlineStr"/>
       <c r="O31" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2474,44 +2494,54 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10026836</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>22.47</v>
+        <v>29.61</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-22.47</v>
+        <v>-29.61</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>26223</v>
+        <v>3213</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>20.83</v>
+        <v>2.55</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K32" s="28" t="inlineStr"/>
-      <c r="L32" s="23" t="inlineStr"/>
-      <c r="M32" s="28" t="inlineStr"/>
-      <c r="N32" s="29" t="inlineStr"/>
+      <c r="K32" s="18" t="n">
+        <v>153.23</v>
+      </c>
+      <c r="L32" s="23" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M32" s="18" t="n">
+        <v>173.71</v>
+      </c>
+      <c r="N32" s="24" t="n">
+        <v>-0.118</v>
+      </c>
       <c r="O32" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P32" s="23" t="inlineStr">
@@ -2531,44 +2561,54 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10052539</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>21.64</v>
+        <v>29.48</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-21.64</v>
+        <v>-29.48</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>4816</v>
+        <v>6179</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>3.83</v>
+        <v>4.91</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K33" s="26" t="inlineStr"/>
-      <c r="L33" s="12" t="inlineStr"/>
-      <c r="M33" s="26" t="inlineStr"/>
-      <c r="N33" s="27" t="inlineStr"/>
+      <c r="K33" s="7" t="n">
+        <v>831.76</v>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>831.76</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
@@ -2588,54 +2628,54 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>20.98</v>
+        <v>29.21</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-20.98</v>
+        <v>-29.21</v>
       </c>
       <c r="G34" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>1758</v>
-      </c>
-      <c r="I34" s="32" t="n">
-        <v>1.4</v>
+        <v>8909</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>7.08</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K34" s="18" t="n">
-        <v>1945.09</v>
+        <v>108.49</v>
       </c>
       <c r="L34" s="23" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M34" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="N34" s="24" t="n">
-        <v>0</v>
+        <v>97.69</v>
+      </c>
+      <c r="N34" s="33" t="n">
+        <v>0.111</v>
       </c>
       <c r="O34" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P34" s="23" t="inlineStr">
@@ -2643,9 +2683,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q34" s="25" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -2655,54 +2695,54 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10051359</t>
+          <t>10106679</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
+          <t>NICORETTE 4MG 30GOMAS ICE MENTA</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>20.91</v>
+        <v>28.68</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-20.91</v>
+        <v>-28.68</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>962</v>
-      </c>
-      <c r="I35" s="30" t="n">
-        <v>0.76</v>
+        <v>8432</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>6.7</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K35" s="7" t="n">
-        <v>309</v>
+        <v>117.76</v>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M35" s="7" t="n">
-        <v>449</v>
-      </c>
-      <c r="N35" s="13" t="n">
-        <v>-0.312</v>
+        <v>83.44</v>
+      </c>
+      <c r="N35" s="31" t="n">
+        <v>0.411</v>
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
@@ -2710,9 +2750,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q35" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 83.44)</t>
         </is>
       </c>
     </row>
@@ -2722,41 +2762,41 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>20.83</v>
+        <v>28.49</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-20.83</v>
+        <v>-28.49</v>
       </c>
       <c r="G36" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>15647</v>
+        <v>3146</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>12.43</v>
+        <v>2.5</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K36" s="28" t="inlineStr"/>
+      <c r="K36" s="26" t="inlineStr"/>
       <c r="L36" s="23" t="inlineStr"/>
-      <c r="M36" s="28" t="inlineStr"/>
-      <c r="N36" s="29" t="inlineStr"/>
+      <c r="M36" s="26" t="inlineStr"/>
+      <c r="N36" s="27" t="inlineStr"/>
       <c r="O36" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2779,54 +2819,44 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10026836</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>20.76</v>
+        <v>28.32</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-20.76</v>
+        <v>-28.32</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>3213</v>
+        <v>39477</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>2.55</v>
+        <v>31.36</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K37" s="7" t="n">
-        <v>153.23</v>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="n">
-        <v>173.71</v>
-      </c>
-      <c r="N37" s="13" t="n">
-        <v>-0.118</v>
-      </c>
+      <c r="K37" s="28" t="inlineStr"/>
+      <c r="L37" s="12" t="inlineStr"/>
+      <c r="M37" s="28" t="inlineStr"/>
+      <c r="N37" s="29" t="inlineStr"/>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
@@ -2846,54 +2876,54 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>10050640</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>20.68</v>
+        <v>27.72</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-20.68</v>
+        <v>-27.72</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>6179</v>
+        <v>2931</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>4.91</v>
+        <v>2.33</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K38" s="18" t="n">
-        <v>831.76</v>
+        <v>218.67</v>
       </c>
       <c r="L38" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M38" s="18" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="N38" s="24" t="n">
-        <v>0</v>
+        <v>197.18</v>
+      </c>
+      <c r="N38" s="33" t="n">
+        <v>0.109</v>
       </c>
       <c r="O38" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P38" s="23" t="inlineStr">
@@ -2901,9 +2931,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q38" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -2913,54 +2943,44 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10042966</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>20.48</v>
+        <v>26.46</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-20.48</v>
+        <v>-26.46</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8909</v>
+        <v>3758</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>7.08</v>
+        <v>2.98</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>108.49</v>
-      </c>
-      <c r="L39" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N39" s="33" t="n">
-        <v>0.111</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K39" s="28" t="inlineStr"/>
+      <c r="L39" s="12" t="inlineStr"/>
+      <c r="M39" s="28" t="inlineStr"/>
+      <c r="N39" s="29" t="inlineStr"/>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
@@ -2968,9 +2988,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+      <c r="Q39" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2980,50 +3000,50 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>10106679</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>NICORETTE 4MG 30GOMAS ICE MENTA</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>20.11</v>
+        <v>26.16</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-20.11</v>
+        <v>-26.16</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>8432</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>6.7</v>
+        <v>837</v>
+      </c>
+      <c r="I40" s="30" t="n">
+        <v>0.66</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K40" s="18" t="n">
-        <v>117.76</v>
+        <v>315.46</v>
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M40" s="18" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="N40" s="31" t="n">
-        <v>0.411</v>
+        <v>236.6</v>
+      </c>
+      <c r="N40" s="33" t="n">
+        <v>0.333</v>
       </c>
       <c r="O40" s="23" t="inlineStr">
         <is>
@@ -3037,7 +3057,7 @@
       </c>
       <c r="Q40" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 83.44)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -3047,44 +3067,54 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>19.98</v>
+        <v>25.5</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-19.98</v>
+        <v>-25.5</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>3146</v>
+        <v>16877</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>2.5</v>
+        <v>13.41</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K41" s="26" t="inlineStr"/>
-      <c r="L41" s="12" t="inlineStr"/>
-      <c r="M41" s="26" t="inlineStr"/>
-      <c r="N41" s="27" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="N41" s="31" t="n">
+        <v>0.333</v>
+      </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
@@ -3092,9 +3122,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q41" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -3104,41 +3134,41 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>19.86</v>
+        <v>25.39</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-19.86</v>
+        <v>-25.39</v>
       </c>
       <c r="G42" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>39477</v>
-      </c>
-      <c r="I42" s="22" t="n">
-        <v>31.36</v>
+        <v>1270</v>
+      </c>
+      <c r="I42" s="30" t="n">
+        <v>1.01</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K42" s="28" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K42" s="26" t="inlineStr"/>
       <c r="L42" s="23" t="inlineStr"/>
-      <c r="M42" s="28" t="inlineStr"/>
-      <c r="N42" s="29" t="inlineStr"/>
+      <c r="M42" s="26" t="inlineStr"/>
+      <c r="N42" s="27" t="inlineStr"/>
       <c r="O42" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3151,7 +3181,7 @@
       </c>
       <c r="Q42" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3161,31 +3191,31 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10033463</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>19.44</v>
+        <v>25.33</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-19.44</v>
+        <v>-25.33</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>2931</v>
+        <v>11473</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>2.33</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -3193,18 +3223,18 @@
         </is>
       </c>
       <c r="K43" s="7" t="n">
-        <v>218.67</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N43" s="33" t="n">
-        <v>0.109</v>
+        <v>59.9</v>
+      </c>
+      <c r="N43" s="31" t="n">
+        <v>0.167</v>
       </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
@@ -3218,7 +3248,7 @@
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
         </is>
       </c>
     </row>
@@ -3228,44 +3258,54 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>10042966</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>18.56</v>
+        <v>24.93</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-18.56</v>
+        <v>-24.93</v>
       </c>
       <c r="G44" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>3758</v>
+        <v>3992</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>2.98</v>
+        <v>3.17</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K44" s="28" t="inlineStr"/>
-      <c r="L44" s="23" t="inlineStr"/>
-      <c r="M44" s="28" t="inlineStr"/>
-      <c r="N44" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K44" s="18" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L44" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M44" s="18" t="n">
+        <v>107</v>
+      </c>
+      <c r="N44" s="33" t="n">
+        <v>0.396</v>
+      </c>
       <c r="O44" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P44" s="23" t="inlineStr">
@@ -3273,9 +3313,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q44" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q44" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -3285,54 +3325,50 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>18.35</v>
+        <v>24.22</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-18.35</v>
+        <v>-24.22</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>837</v>
-      </c>
-      <c r="I45" s="30" t="n">
-        <v>0.66</v>
+        <v>4427</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>3.52</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>315.46</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K45" s="28" t="inlineStr"/>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N45" s="33" t="n">
-        <v>0.333</v>
-      </c>
+        <v>50.25</v>
+      </c>
+      <c r="N45" s="29" t="inlineStr"/>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
@@ -3340,9 +3376,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+      <c r="Q45" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3352,54 +3388,44 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10004419</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>17.88</v>
+        <v>24.21</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-17.88</v>
+        <v>-24.21</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>16877</v>
+        <v>2481</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>13.41</v>
+        <v>1.97</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K46" s="18" t="n">
-        <v>74.22</v>
-      </c>
-      <c r="L46" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M46" s="18" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N46" s="31" t="n">
-        <v>0.333</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K46" s="26" t="inlineStr"/>
+      <c r="L46" s="23" t="inlineStr"/>
+      <c r="M46" s="26" t="inlineStr"/>
+      <c r="N46" s="27" t="inlineStr"/>
       <c r="O46" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P46" s="23" t="inlineStr">
@@ -3407,9 +3433,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q46" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+      <c r="Q46" s="25" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -3419,44 +3445,54 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>17.81</v>
+        <v>23.71</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-17.81</v>
+        <v>-23.71</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>1270</v>
-      </c>
-      <c r="I47" s="30" t="n">
-        <v>1.01</v>
+        <v>4815</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>3.82</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K47" s="26" t="inlineStr"/>
-      <c r="L47" s="12" t="inlineStr"/>
-      <c r="M47" s="26" t="inlineStr"/>
-      <c r="N47" s="27" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="N47" s="31" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
@@ -3464,9 +3500,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q47" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -3476,39 +3512,39 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>10033463</t>
+          <t>10050642</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
+          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>17.76</v>
+        <v>23.14</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-17.76</v>
+        <v>-23.14</v>
       </c>
       <c r="G48" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>11473</v>
+        <v>5711</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>9.109999999999999</v>
+        <v>4.54</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K48" s="18" t="n">
-        <v>69.90000000000001</v>
+        <v>955.85</v>
       </c>
       <c r="L48" s="23" t="inlineStr">
         <is>
@@ -3516,14 +3552,14 @@
         </is>
       </c>
       <c r="M48" s="18" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="N48" s="31" t="n">
-        <v>0.167</v>
+        <v>955.85</v>
+      </c>
+      <c r="N48" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="O48" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P48" s="23" t="inlineStr">
@@ -3531,9 +3567,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q48" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
+      <c r="Q48" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3543,31 +3579,31 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>17.48</v>
+        <v>22.67</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-17.48</v>
+        <v>-22.67</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>3992</v>
+        <v>12853</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>3.17</v>
+        <v>10.21</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -3575,18 +3611,18 @@
         </is>
       </c>
       <c r="K49" s="7" t="n">
-        <v>149.4</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="N49" s="33" t="n">
-        <v>0.396</v>
+        <v>61.06</v>
+      </c>
+      <c r="N49" s="31" t="n">
+        <v>0.113</v>
       </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
@@ -3600,7 +3636,7 @@
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -3610,47 +3646,41 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>10041248</t>
+          <t>10001098</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>CREATINA MONOHIDRATADA 300G DUX</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>16.98</v>
+        <v>21</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-16.98</v>
+        <v>-21</v>
       </c>
       <c r="G50" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>4427</v>
+        <v>8492</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>3.52</v>
+        <v>6.75</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K50" s="28" t="inlineStr"/>
-      <c r="L50" s="23" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M50" s="18" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="N50" s="29" t="inlineStr"/>
+      <c r="K50" s="26" t="inlineStr"/>
+      <c r="L50" s="23" t="inlineStr"/>
+      <c r="M50" s="26" t="inlineStr"/>
+      <c r="N50" s="27" t="inlineStr"/>
       <c r="O50" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3673,41 +3703,41 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10004419</t>
+          <t>10099241</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
+          <t>NAN COMFOR 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>16.98</v>
+        <v>20.34</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-16.98</v>
+        <v>-20.34</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>2481</v>
+        <v>13024</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>1.97</v>
+        <v>10.34</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K51" s="26" t="inlineStr"/>
+      <c r="K51" s="28" t="inlineStr"/>
       <c r="L51" s="12" t="inlineStr"/>
-      <c r="M51" s="26" t="inlineStr"/>
-      <c r="N51" s="27" t="inlineStr"/>
+      <c r="M51" s="28" t="inlineStr"/>
+      <c r="N51" s="29" t="inlineStr"/>
       <c r="O51" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3720,7 +3750,7 @@
       </c>
       <c r="Q51" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3730,54 +3760,44 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>16.63</v>
+        <v>19.36</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-16.63</v>
+        <v>-19.36</v>
       </c>
       <c r="G52" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>4815</v>
+        <v>11106</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>3.82</v>
+        <v>8.82</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K52" s="18" t="n">
-        <v>94.98999999999999</v>
-      </c>
-      <c r="L52" s="23" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M52" s="18" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N52" s="31" t="n">
-        <v>0.904</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K52" s="26" t="inlineStr"/>
+      <c r="L52" s="23" t="inlineStr"/>
+      <c r="M52" s="26" t="inlineStr"/>
+      <c r="N52" s="27" t="inlineStr"/>
       <c r="O52" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P52" s="23" t="inlineStr">
@@ -3785,9 +3805,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q52" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+      <c r="Q52" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3797,31 +3817,31 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>10001096</t>
+          <t>100015009</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN RECEM NASCIDO</t>
+          <t>SAB DOVE 90G LV+ PG- 6UN ORIGINAL</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>16.58</v>
+        <v>19.28</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-16.58</v>
+        <v>-19.28</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>9757</v>
+        <v>59877</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>7.75</v>
+        <v>47.56</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3829,7 +3849,7 @@
         </is>
       </c>
       <c r="K53" s="7" t="n">
-        <v>38.9</v>
+        <v>27.9</v>
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
@@ -3837,10 +3857,10 @@
         </is>
       </c>
       <c r="M53" s="7" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="N53" s="33" t="n">
-        <v>0.08400000000000001</v>
+        <v>24.9</v>
+      </c>
+      <c r="N53" s="31" t="n">
+        <v>0.12</v>
       </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3874,7 @@
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Panvel R$ 35.90)</t>
+          <t>Reprecificar no Digital (Panvel R$ 24.90)</t>
         </is>
       </c>
     </row>
@@ -3864,54 +3884,44 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>10050642</t>
+          <t>10025717</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
+          <t>FR PAMPERS CONFORTSEC BAG SUPER P 72UN</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>16.23</v>
+        <v>19.25</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-16.23</v>
+        <v>-19.25</v>
       </c>
       <c r="G54" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>5711</v>
+        <v>12883</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>4.54</v>
+        <v>10.23</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K54" s="18" t="n">
-        <v>955.85</v>
-      </c>
-      <c r="L54" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M54" s="18" t="n">
-        <v>955.85</v>
-      </c>
-      <c r="N54" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="K54" s="26" t="inlineStr"/>
+      <c r="L54" s="23" t="inlineStr"/>
+      <c r="M54" s="26" t="inlineStr"/>
+      <c r="N54" s="27" t="inlineStr"/>
       <c r="O54" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P54" s="23" t="inlineStr">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -282,12 +282,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -297,13 +291,19 @@
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 07:03:12 (07:03) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 07:54:11 (07:54) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>979.1799999999999</v>
+        <v>4174.46</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-979.1799999999999</v>
+        <v>-4174.46</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>-1</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q5" s="14" t="inlineStr">
@@ -888,10 +888,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>458.79</v>
+        <v>1955.92</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-458.79</v>
+        <v>-1955.92</v>
       </c>
       <c r="G6" s="20" t="n">
         <v>-1</v>
@@ -928,7 +928,7 @@
       </c>
       <c r="P6" s="23" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q6" s="25" t="inlineStr">
@@ -943,54 +943,44 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10046654</t>
+          <t>10053130</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 7,5MG 4CAN APLIC LILLY</t>
+          <t>OZIVY 1MG 1CAN 3ML EMS</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>208.81</v>
+        <v>590.4400000000001</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-208.81</v>
+        <v>-590.4400000000001</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>4288</v>
+        <v>10582</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>3.41</v>
+        <v>8.41</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K7" s="7" t="n">
-        <v>2766.26</v>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>2766.26</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" s="26" t="inlineStr"/>
+      <c r="L7" s="12" t="inlineStr"/>
+      <c r="M7" s="26" t="inlineStr"/>
+      <c r="N7" s="27" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
@@ -1010,44 +1000,54 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>10053130</t>
+          <t>10046655</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>OZIVY 1MG 1CAN 3ML EMS</t>
+          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>138.5</v>
+        <v>528.65</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-138.5</v>
+        <v>-528.65</v>
       </c>
       <c r="G8" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>10582</v>
+        <v>3069</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>8.41</v>
+        <v>2.44</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr"/>
-      <c r="L8" s="23" t="inlineStr"/>
-      <c r="M8" s="26" t="inlineStr"/>
-      <c r="N8" s="27" t="inlineStr"/>
+      <c r="K8" s="18" t="n">
+        <v>3210.85</v>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="n">
+        <v>3210.85</v>
+      </c>
+      <c r="N8" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O8" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P8" s="23" t="inlineStr">
@@ -1067,44 +1067,54 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10042967</t>
+          <t>10040802</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO G 128UN</t>
+          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>129.09</v>
+        <v>458.7</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-129.09</v>
+        <v>-458.7</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>9727</v>
+        <v>3723</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>7.73</v>
+        <v>2.96</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="12" t="inlineStr"/>
-      <c r="M9" s="28" t="inlineStr"/>
-      <c r="N9" s="29" t="inlineStr"/>
+      <c r="K9" s="7" t="n">
+        <v>2501.8</v>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>2501.8</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr">
@@ -1114,7 +1124,7 @@
       </c>
       <c r="Q9" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1124,54 +1134,44 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>10046655</t>
+          <t>10046657</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
+          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>124</v>
+        <v>419.28</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-124</v>
+        <v>-419.28</v>
       </c>
       <c r="G10" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>3069</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>2.44</v>
+        <v>1048</v>
+      </c>
+      <c r="I10" s="28" t="n">
+        <v>0.83</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>3210.85</v>
-      </c>
-      <c r="L10" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M10" s="18" t="n">
-        <v>3210.85</v>
-      </c>
-      <c r="N10" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K10" s="29" t="inlineStr"/>
+      <c r="L10" s="23" t="inlineStr"/>
+      <c r="M10" s="29" t="inlineStr"/>
+      <c r="N10" s="30" t="inlineStr"/>
       <c r="O10" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P10" s="23" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Q10" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1191,31 +1191,31 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10040802</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>107.6</v>
+        <v>374.84</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-107.6</v>
+        <v>-374.84</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>3723</v>
+        <v>9409</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>2.96</v>
+        <v>7.47</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="K11" s="7" t="n">
-        <v>2501.8</v>
+        <v>988.22</v>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="M11" s="7" t="n">
-        <v>2501.8</v>
+        <v>988.22</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Q11" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1258,44 +1258,54 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>10046657</t>
+          <t>10050654</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
+          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>98.34999999999999</v>
+        <v>336.51</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-98.34999999999999</v>
+        <v>-336.51</v>
       </c>
       <c r="G12" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>1048</v>
-      </c>
-      <c r="I12" s="30" t="n">
-        <v>0.83</v>
+        <v>4038</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>3.21</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K12" s="26" t="inlineStr"/>
-      <c r="L12" s="23" t="inlineStr"/>
-      <c r="M12" s="26" t="inlineStr"/>
-      <c r="N12" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="N12" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O12" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P12" s="23" t="inlineStr">
@@ -1305,7 +1315,7 @@
       </c>
       <c r="Q12" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1315,54 +1325,44 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10046656</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>87.92</v>
+        <v>279.52</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-87.92</v>
+        <v>-279.52</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>9409</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>7.47</v>
+        <v>494</v>
+      </c>
+      <c r="I13" s="31" t="n">
+        <v>0.39</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K13" s="26" t="inlineStr"/>
+      <c r="L13" s="12" t="inlineStr"/>
+      <c r="M13" s="26" t="inlineStr"/>
+      <c r="N13" s="27" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Q13" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1382,39 +1382,39 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>10050654</t>
+          <t>100005474</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
+          <t>NANLAC COMFOR 3 800G NESTLE</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>0</v>
+        <v>108.25</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>78.93000000000001</v>
+        <v>327.98</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-78.93000000000001</v>
+        <v>-219.73</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>-1</v>
+        <v>-0.67</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>4038</v>
+        <v>14766</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>3.21</v>
+        <v>11.73</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K14" s="18" t="n">
-        <v>1617.66</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="L14" s="23" t="inlineStr">
         <is>
@@ -1422,14 +1422,14 @@
         </is>
       </c>
       <c r="M14" s="18" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="N14" s="24" t="n">
-        <v>0</v>
+        <v>59.99</v>
+      </c>
+      <c r="N14" s="32" t="n">
+        <v>0.342</v>
       </c>
       <c r="O14" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P14" s="23" t="inlineStr">
@@ -1437,9 +1437,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q14" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q14" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
         </is>
       </c>
     </row>
@@ -1449,31 +1449,31 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>100005474</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>NANLAC COMFOR 3 800G NESTLE</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>76.93000000000001</v>
+        <v>188.27</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-76.93000000000001</v>
+        <v>-188.27</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>14766</v>
+        <v>2446</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>11.73</v>
+        <v>1.94</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1481,18 +1481,18 @@
         </is>
       </c>
       <c r="K15" s="7" t="n">
-        <v>80.48999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
-        <v>59.99</v>
-      </c>
-      <c r="N15" s="31" t="n">
-        <v>0.342</v>
+        <v>46.85</v>
+      </c>
+      <c r="N15" s="33" t="n">
+        <v>1.132</v>
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -1516,44 +1516,54 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>10041258</t>
+          <t>10106687</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX XG 82UN</t>
+          <t>APTANUTRI PREMIUM 3 800G DANONE</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>69.34999999999999</v>
+        <v>186.52</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-69.34999999999999</v>
+        <v>-186.52</v>
       </c>
       <c r="G16" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>11073</v>
+        <v>17535</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>8.800000000000001</v>
+        <v>13.93</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K16" s="26" t="inlineStr"/>
-      <c r="L16" s="23" t="inlineStr"/>
-      <c r="M16" s="26" t="inlineStr"/>
-      <c r="N16" s="27" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="n">
+        <v>52.84</v>
+      </c>
+      <c r="N16" s="32" t="n">
+        <v>0.514</v>
+      </c>
       <c r="O16" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P16" s="23" t="inlineStr">
@@ -1561,9 +1571,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q16" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q16" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
         </is>
       </c>
     </row>
@@ -1573,44 +1583,54 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10046656</t>
+          <t>10030119</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
+          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>65.56999999999999</v>
+        <v>182.8</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-65.56999999999999</v>
+        <v>-182.8</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>494</v>
-      </c>
-      <c r="I17" s="32" t="n">
-        <v>0.39</v>
+        <v>2858</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>2.27</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="12" t="inlineStr"/>
-      <c r="M17" s="28" t="inlineStr"/>
-      <c r="N17" s="29" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
@@ -1620,7 +1640,7 @@
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1630,41 +1650,47 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>10052532</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXXG 70UN</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>64.44</v>
+        <v>157.12</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-64.44</v>
+        <v>-157.12</v>
       </c>
       <c r="G18" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>16016</v>
+        <v>2081</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>12.72</v>
+        <v>1.65</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K18" s="26" t="inlineStr"/>
-      <c r="L18" s="23" t="inlineStr"/>
-      <c r="M18" s="26" t="inlineStr"/>
-      <c r="N18" s="27" t="inlineStr"/>
+      <c r="K18" s="29" t="inlineStr"/>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="n">
+        <v>549.9</v>
+      </c>
+      <c r="N18" s="30" t="inlineStr"/>
       <c r="O18" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1687,41 +1713,41 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10041262</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XG 80</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>61.39</v>
+        <v>136.58</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-61.39</v>
+        <v>-136.58</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>2151</v>
+        <v>26223</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>1.71</v>
+        <v>20.83</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K19" s="28" t="inlineStr"/>
+      <c r="K19" s="26" t="inlineStr"/>
       <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="28" t="inlineStr"/>
-      <c r="N19" s="29" t="inlineStr"/>
+      <c r="M19" s="26" t="inlineStr"/>
+      <c r="N19" s="27" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1744,47 +1770,47 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>49.86</v>
+        <v>127.57</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-49.86</v>
+        <v>-127.57</v>
       </c>
       <c r="G20" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>3321</v>
-      </c>
-      <c r="I20" s="22" t="n">
-        <v>2.64</v>
+        <v>1758</v>
+      </c>
+      <c r="I20" s="28" t="n">
+        <v>1.4</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K20" s="18" t="n">
-        <v>1298.54</v>
+        <v>1945.09</v>
       </c>
       <c r="L20" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M20" s="18" t="n">
-        <v>1298.54</v>
+        <v>1945.09</v>
       </c>
       <c r="N20" s="24" t="n">
         <v>0</v>
@@ -1801,7 +1827,7 @@
       </c>
       <c r="Q20" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1811,44 +1837,54 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10051359</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>46.93</v>
+        <v>127.09</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-46.93</v>
+        <v>-127.09</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>8275</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>6.57</v>
+        <v>962</v>
+      </c>
+      <c r="I21" s="31" t="n">
+        <v>0.76</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="12" t="inlineStr"/>
-      <c r="M21" s="28" t="inlineStr"/>
-      <c r="N21" s="29" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>309</v>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>449</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>-0.312</v>
+      </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
@@ -1858,7 +1894,7 @@
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1868,54 +1904,54 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10026836</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>44.16</v>
+        <v>126.22</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-44.16</v>
+        <v>-126.22</v>
       </c>
       <c r="G22" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>2446</v>
+        <v>3213</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K22" s="18" t="n">
-        <v>99.90000000000001</v>
+        <v>153.23</v>
       </c>
       <c r="L22" s="23" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M22" s="18" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N22" s="33" t="n">
-        <v>1.132</v>
+        <v>173.71</v>
+      </c>
+      <c r="N22" s="24" t="n">
+        <v>-0.118</v>
       </c>
       <c r="O22" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P22" s="23" t="inlineStr">
@@ -1923,9 +1959,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q22" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+      <c r="Q22" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1935,54 +1971,54 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10106687</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>APTANUTRI PREMIUM 3 800G DANONE</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>43.75</v>
+        <v>125.69</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-43.75</v>
+        <v>-125.69</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>17535</v>
+        <v>6179</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>13.93</v>
+        <v>4.91</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K23" s="7" t="n">
-        <v>79.98999999999999</v>
+        <v>831.76</v>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
-        <v>52.84</v>
-      </c>
-      <c r="N23" s="31" t="n">
-        <v>0.514</v>
+        <v>831.76</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
@@ -1990,9 +2026,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
+      <c r="Q23" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2002,39 +2038,39 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10030119</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>42.88</v>
+        <v>124.51</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-42.88</v>
+        <v>-124.51</v>
       </c>
       <c r="G24" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>2858</v>
+        <v>8909</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>2.27</v>
+        <v>7.08</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K24" s="18" t="n">
-        <v>1301.17</v>
+        <v>108.49</v>
       </c>
       <c r="L24" s="23" t="inlineStr">
         <is>
@@ -2042,14 +2078,14 @@
         </is>
       </c>
       <c r="M24" s="18" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="N24" s="24" t="n">
-        <v>0</v>
+        <v>97.69</v>
+      </c>
+      <c r="N24" s="32" t="n">
+        <v>0.111</v>
       </c>
       <c r="O24" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P24" s="23" t="inlineStr">
@@ -2057,9 +2093,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q24" s="25" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2105,41 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>36.85</v>
+        <v>121.46</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-36.85</v>
+        <v>-121.46</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>2081</v>
+        <v>3146</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K25" s="28" t="inlineStr"/>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="n">
-        <v>549.9</v>
-      </c>
-      <c r="N25" s="29" t="inlineStr"/>
+      <c r="K25" s="26" t="inlineStr"/>
+      <c r="L25" s="12" t="inlineStr"/>
+      <c r="M25" s="26" t="inlineStr"/>
+      <c r="N25" s="27" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2132,41 +2162,41 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10052538</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XXG 74</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>34.81</v>
+        <v>120.73</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-34.81</v>
+        <v>-120.73</v>
       </c>
       <c r="G26" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>4696</v>
+        <v>39477</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>3.73</v>
+        <v>31.36</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K26" s="26" t="inlineStr"/>
+      <c r="K26" s="29" t="inlineStr"/>
       <c r="L26" s="23" t="inlineStr"/>
-      <c r="M26" s="26" t="inlineStr"/>
-      <c r="N26" s="27" t="inlineStr"/>
+      <c r="M26" s="29" t="inlineStr"/>
+      <c r="N26" s="30" t="inlineStr"/>
       <c r="O26" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2189,44 +2219,54 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>32.04</v>
+        <v>118.17</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-32.04</v>
+        <v>-118.17</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>26223</v>
+        <v>2931</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>20.83</v>
+        <v>2.33</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K27" s="28" t="inlineStr"/>
-      <c r="L27" s="12" t="inlineStr"/>
-      <c r="M27" s="28" t="inlineStr"/>
-      <c r="N27" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>218.67</v>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>197.18</v>
+      </c>
+      <c r="N27" s="33" t="n">
+        <v>0.109</v>
+      </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P27" s="12" t="inlineStr">
@@ -2234,9 +2274,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q27" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -2246,41 +2286,41 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10052539</t>
+          <t>10042966</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX XG 82U</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>30.86</v>
+        <v>112.82</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-30.86</v>
+        <v>-112.82</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>4816</v>
+        <v>3758</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>3.83</v>
+        <v>2.98</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K28" s="26" t="inlineStr"/>
+      <c r="K28" s="29" t="inlineStr"/>
       <c r="L28" s="23" t="inlineStr"/>
-      <c r="M28" s="26" t="inlineStr"/>
-      <c r="N28" s="27" t="inlineStr"/>
+      <c r="M28" s="29" t="inlineStr"/>
+      <c r="N28" s="30" t="inlineStr"/>
       <c r="O28" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2303,54 +2343,54 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>29.92</v>
+        <v>111.54</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-29.92</v>
+        <v>-111.54</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>1758</v>
-      </c>
-      <c r="I29" s="32" t="n">
-        <v>1.4</v>
+        <v>837</v>
+      </c>
+      <c r="I29" s="31" t="n">
+        <v>0.66</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K29" s="7" t="n">
-        <v>1945.09</v>
+        <v>315.46</v>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="N29" s="13" t="n">
-        <v>0</v>
+        <v>236.6</v>
+      </c>
+      <c r="N29" s="33" t="n">
+        <v>0.333</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
@@ -2358,9 +2398,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q29" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -2370,54 +2410,54 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10051359</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>29.81</v>
+        <v>108.72</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-29.81</v>
+        <v>-108.72</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>962</v>
-      </c>
-      <c r="I30" s="30" t="n">
-        <v>0.76</v>
+        <v>16877</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>13.41</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K30" s="18" t="n">
-        <v>309</v>
+        <v>74.22</v>
       </c>
       <c r="L30" s="23" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M30" s="18" t="n">
-        <v>449</v>
-      </c>
-      <c r="N30" s="24" t="n">
-        <v>-0.312</v>
+        <v>55.67</v>
+      </c>
+      <c r="N30" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="O30" s="23" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P30" s="23" t="inlineStr">
@@ -2425,9 +2465,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q30" s="25" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -2437,41 +2477,41 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>29.7</v>
+        <v>108.24</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-29.7</v>
+        <v>-108.24</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>15647</v>
-      </c>
-      <c r="I31" s="11" t="n">
-        <v>12.43</v>
+        <v>1270</v>
+      </c>
+      <c r="I31" s="31" t="n">
+        <v>1.01</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K31" s="28" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K31" s="26" t="inlineStr"/>
       <c r="L31" s="12" t="inlineStr"/>
-      <c r="M31" s="28" t="inlineStr"/>
-      <c r="N31" s="29" t="inlineStr"/>
+      <c r="M31" s="26" t="inlineStr"/>
+      <c r="N31" s="27" t="inlineStr"/>
       <c r="O31" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2484,7 +2524,7 @@
       </c>
       <c r="Q31" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2494,54 +2534,54 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10026836</t>
+          <t>10033463</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
+          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>29.61</v>
+        <v>107.97</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-29.61</v>
+        <v>-107.97</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>3213</v>
+        <v>11473</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>2.55</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K32" s="18" t="n">
-        <v>153.23</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L32" s="23" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M32" s="18" t="n">
-        <v>173.71</v>
-      </c>
-      <c r="N32" s="24" t="n">
-        <v>-0.118</v>
+        <v>59.9</v>
+      </c>
+      <c r="N32" s="32" t="n">
+        <v>0.167</v>
       </c>
       <c r="O32" s="23" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P32" s="23" t="inlineStr">
@@ -2549,9 +2589,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q32" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
         </is>
       </c>
     </row>
@@ -2561,39 +2601,39 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10050640</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>29.48</v>
+        <v>106.28</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-29.48</v>
+        <v>-106.28</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>6179</v>
+        <v>3992</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>4.91</v>
+        <v>3.17</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K33" s="7" t="n">
-        <v>831.76</v>
+        <v>149.4</v>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
@@ -2601,14 +2641,14 @@
         </is>
       </c>
       <c r="M33" s="7" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="N33" s="13" t="n">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="N33" s="33" t="n">
+        <v>0.396</v>
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
@@ -2616,9 +2656,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q33" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -2628,31 +2668,31 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10042968</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>0</v>
+        <v>440.14</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>29.21</v>
+        <v>544.77</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-29.21</v>
+        <v>-104.63</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>-1</v>
+        <v>-0.192</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>8909</v>
+        <v>5925</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>7.08</v>
+        <v>4.71</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -2660,18 +2700,18 @@
         </is>
       </c>
       <c r="K34" s="18" t="n">
-        <v>108.49</v>
+        <v>159.9</v>
       </c>
       <c r="L34" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M34" s="18" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N34" s="33" t="n">
-        <v>0.111</v>
+        <v>149.9</v>
+      </c>
+      <c r="N34" s="32" t="n">
+        <v>0.067</v>
       </c>
       <c r="O34" s="23" t="inlineStr">
         <is>
@@ -2685,7 +2725,7 @@
       </c>
       <c r="Q34" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
         </is>
       </c>
     </row>
@@ -2695,54 +2735,50 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10106679</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>NICORETTE 4MG 30GOMAS ICE MENTA</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>28.68</v>
+        <v>103.24</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-28.68</v>
+        <v>-103.24</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8432</v>
+        <v>4427</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>6.7</v>
+        <v>3.52</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>117.76</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K35" s="26" t="inlineStr"/>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M35" s="7" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="N35" s="31" t="n">
-        <v>0.411</v>
-      </c>
+        <v>50.25</v>
+      </c>
+      <c r="N35" s="27" t="inlineStr"/>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
@@ -2750,9 +2786,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 83.44)</t>
+      <c r="Q35" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2762,41 +2798,41 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10004419</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>28.49</v>
+        <v>103.22</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-28.49</v>
+        <v>-103.22</v>
       </c>
       <c r="G36" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>3146</v>
+        <v>2481</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K36" s="26" t="inlineStr"/>
+      <c r="K36" s="29" t="inlineStr"/>
       <c r="L36" s="23" t="inlineStr"/>
-      <c r="M36" s="26" t="inlineStr"/>
-      <c r="N36" s="27" t="inlineStr"/>
+      <c r="M36" s="29" t="inlineStr"/>
+      <c r="N36" s="30" t="inlineStr"/>
       <c r="O36" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2809,7 +2845,7 @@
       </c>
       <c r="Q36" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2819,44 +2855,54 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>28.32</v>
+        <v>101.08</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-28.32</v>
+        <v>-101.08</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>39477</v>
+        <v>4815</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>31.36</v>
+        <v>3.82</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K37" s="28" t="inlineStr"/>
-      <c r="L37" s="12" t="inlineStr"/>
-      <c r="M37" s="28" t="inlineStr"/>
-      <c r="N37" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="N37" s="33" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
@@ -2864,9 +2910,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q37" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -2876,54 +2922,54 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10050642</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>27.72</v>
+        <v>98.63</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-27.72</v>
+        <v>-98.63</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>2931</v>
+        <v>5711</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>2.33</v>
+        <v>4.54</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K38" s="18" t="n">
-        <v>218.67</v>
+        <v>955.85</v>
       </c>
       <c r="L38" s="23" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M38" s="18" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N38" s="33" t="n">
-        <v>0.109</v>
+        <v>955.85</v>
+      </c>
+      <c r="N38" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="O38" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P38" s="23" t="inlineStr">
@@ -2931,9 +2977,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q38" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+      <c r="Q38" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2943,41 +2989,41 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10042966</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0</v>
+        <v>115.9</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>26.46</v>
+        <v>200.08</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-26.46</v>
+        <v>-84.18000000000001</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-1</v>
+        <v>-0.421</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>3758</v>
+        <v>8275</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>2.98</v>
+        <v>6.57</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K39" s="28" t="inlineStr"/>
+      <c r="K39" s="26" t="inlineStr"/>
       <c r="L39" s="12" t="inlineStr"/>
-      <c r="M39" s="28" t="inlineStr"/>
-      <c r="N39" s="29" t="inlineStr"/>
+      <c r="M39" s="26" t="inlineStr"/>
+      <c r="N39" s="27" t="inlineStr"/>
       <c r="O39" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3000,54 +3046,44 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>26.16</v>
+        <v>82.55</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-26.16</v>
+        <v>-82.55</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>837</v>
-      </c>
-      <c r="I40" s="30" t="n">
-        <v>0.66</v>
+        <v>11106</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>8.82</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K40" s="18" t="n">
-        <v>315.46</v>
-      </c>
-      <c r="L40" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M40" s="18" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N40" s="33" t="n">
-        <v>0.333</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K40" s="29" t="inlineStr"/>
+      <c r="L40" s="23" t="inlineStr"/>
+      <c r="M40" s="29" t="inlineStr"/>
+      <c r="N40" s="30" t="inlineStr"/>
       <c r="O40" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P40" s="23" t="inlineStr">
@@ -3055,9 +3091,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q40" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+      <c r="Q40" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3067,31 +3103,31 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10046027</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>FR PAMPERS SUPERSEC XG 56UN</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>25.5</v>
+        <v>80.63</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-25.5</v>
+        <v>-80.63</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>16877</v>
+        <v>11875</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>13.41</v>
+        <v>9.43</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -3099,7 +3135,7 @@
         </is>
       </c>
       <c r="K41" s="7" t="n">
-        <v>74.22</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
@@ -3107,10 +3143,10 @@
         </is>
       </c>
       <c r="M41" s="7" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N41" s="31" t="n">
-        <v>0.333</v>
+        <v>59.9</v>
+      </c>
+      <c r="N41" s="33" t="n">
+        <v>0.434</v>
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
@@ -3124,7 +3160,7 @@
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
         </is>
       </c>
     </row>
@@ -3134,41 +3170,47 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>25.39</v>
+        <v>79.11</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-25.39</v>
+        <v>-79.11</v>
       </c>
       <c r="G42" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>1270</v>
-      </c>
-      <c r="I42" s="30" t="n">
-        <v>1.01</v>
+        <v>204</v>
+      </c>
+      <c r="I42" s="28" t="n">
+        <v>0.16</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K42" s="26" t="inlineStr"/>
-      <c r="L42" s="23" t="inlineStr"/>
-      <c r="M42" s="26" t="inlineStr"/>
-      <c r="N42" s="27" t="inlineStr"/>
+      <c r="K42" s="29" t="inlineStr"/>
+      <c r="L42" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M42" s="18" t="n">
+        <v>1212.9</v>
+      </c>
+      <c r="N42" s="30" t="inlineStr"/>
       <c r="O42" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3191,54 +3233,50 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10033463</t>
+          <t>10093877</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
+          <t>MIRENA 52MG 1END+INS BAYER</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>25.33</v>
+        <v>79.02</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-25.33</v>
+        <v>-79.02</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>11473</v>
-      </c>
-      <c r="I43" s="11" t="n">
-        <v>9.109999999999999</v>
+        <v>501</v>
+      </c>
+      <c r="I43" s="31" t="n">
+        <v>0.4</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>69.90000000000001</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K43" s="26" t="inlineStr"/>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="N43" s="31" t="n">
-        <v>0.167</v>
-      </c>
+        <v>1225.89</v>
+      </c>
+      <c r="N43" s="27" t="inlineStr"/>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
@@ -3246,9 +3284,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
+      <c r="Q43" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3258,31 +3296,31 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10101654</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>NAN COMFOR 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>24.93</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-24.93</v>
+        <v>-77.90000000000001</v>
       </c>
       <c r="G44" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>3992</v>
+        <v>13534</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>3.17</v>
+        <v>10.75</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
@@ -3290,18 +3328,18 @@
         </is>
       </c>
       <c r="K44" s="18" t="n">
-        <v>149.4</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="L44" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M44" s="18" t="n">
-        <v>107</v>
-      </c>
-      <c r="N44" s="33" t="n">
-        <v>0.396</v>
+        <v>79.98999999999999</v>
+      </c>
+      <c r="N44" s="32" t="n">
+        <v>0.094</v>
       </c>
       <c r="O44" s="23" t="inlineStr">
         <is>
@@ -3315,7 +3353,7 @@
       </c>
       <c r="Q44" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+          <t>Reprecificar no Digital (Amazon R$ 79.99)</t>
         </is>
       </c>
     </row>
@@ -3325,50 +3363,54 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10041248</t>
+          <t>10050653</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>CREATINA MONOHIDRATADA 300G DUX</t>
+          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>24.22</v>
+        <v>75.59</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-24.22</v>
+        <v>-75.59</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>4427</v>
+        <v>2647</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>3.52</v>
+        <v>2.1</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K45" s="28" t="inlineStr"/>
+      <c r="K45" s="7" t="n">
+        <v>1347.91</v>
+      </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="N45" s="29" t="inlineStr"/>
+        <v>1347.89</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
@@ -3388,41 +3430,41 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10004419</t>
+          <t>10052540</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>24.21</v>
+        <v>74.91</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-24.21</v>
+        <v>-74.91</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>2481</v>
+        <v>2601</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K46" s="26" t="inlineStr"/>
+      <c r="K46" s="29" t="inlineStr"/>
       <c r="L46" s="23" t="inlineStr"/>
-      <c r="M46" s="26" t="inlineStr"/>
-      <c r="N46" s="27" t="inlineStr"/>
+      <c r="M46" s="29" t="inlineStr"/>
+      <c r="N46" s="30" t="inlineStr"/>
       <c r="O46" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3435,7 +3477,7 @@
       </c>
       <c r="Q46" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3445,31 +3487,31 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10097311</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>NESTOGENO 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>23.71</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-23.71</v>
+        <v>-74.76000000000001</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>4815</v>
+        <v>10627</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>3.82</v>
+        <v>8.44</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3477,18 +3519,18 @@
         </is>
       </c>
       <c r="K47" s="7" t="n">
-        <v>94.98999999999999</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N47" s="31" t="n">
-        <v>0.904</v>
+        <v>62.9</v>
+      </c>
+      <c r="N47" s="33" t="n">
+        <v>0.081</v>
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
@@ -3502,7 +3544,7 @@
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 62.90)</t>
         </is>
       </c>
     </row>
@@ -3512,54 +3554,50 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>10050642</t>
+          <t>10005850</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
+          <t>SERTRALINA 100MG 30CP REV GEN PRATI (C1)</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>23.14</v>
+        <v>73.37</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-23.14</v>
+        <v>-73.37</v>
       </c>
       <c r="G48" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>5711</v>
+        <v>9718</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>4.54</v>
+        <v>7.72</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K48" s="18" t="n">
-        <v>955.85</v>
-      </c>
+      <c r="K48" s="29" t="inlineStr"/>
       <c r="L48" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M48" s="18" t="n">
-        <v>955.85</v>
-      </c>
-      <c r="N48" s="24" t="n">
-        <v>0</v>
-      </c>
+        <v>54.99</v>
+      </c>
+      <c r="N48" s="30" t="inlineStr"/>
       <c r="O48" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P48" s="23" t="inlineStr">
@@ -3579,54 +3617,54 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10024521</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.67</v>
+        <v>72.94</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-22.67</v>
+        <v>-72.94</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>12853</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>10.21</v>
+        <v>575</v>
+      </c>
+      <c r="I49" s="31" t="n">
+        <v>0.46</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K49" s="7" t="n">
-        <v>67.98999999999999</v>
+        <v>799.9</v>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N49" s="31" t="n">
-        <v>0.113</v>
+        <v>814.9</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>-0.018</v>
       </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
@@ -3634,9 +3672,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+      <c r="Q49" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3646,41 +3684,41 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>10001098</t>
+          <t>100011549</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
+          <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>21</v>
+        <v>72.61</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-21</v>
+        <v>-72.61</v>
       </c>
       <c r="G50" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>8492</v>
+        <v>7665</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>6.75</v>
+        <v>6.09</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K50" s="26" t="inlineStr"/>
+      <c r="K50" s="29" t="inlineStr"/>
       <c r="L50" s="23" t="inlineStr"/>
-      <c r="M50" s="26" t="inlineStr"/>
-      <c r="N50" s="27" t="inlineStr"/>
+      <c r="M50" s="29" t="inlineStr"/>
+      <c r="N50" s="30" t="inlineStr"/>
       <c r="O50" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3703,41 +3741,47 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10099241</t>
+          <t>10034467</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>NAN COMFOR 1 800G NESTLE</t>
+          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>20.34</v>
+        <v>71.56</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-20.34</v>
+        <v>-71.56</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>13024</v>
+        <v>3778</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>10.34</v>
+        <v>3</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K51" s="28" t="inlineStr"/>
-      <c r="L51" s="12" t="inlineStr"/>
-      <c r="M51" s="28" t="inlineStr"/>
-      <c r="N51" s="29" t="inlineStr"/>
+      <c r="K51" s="26" t="inlineStr"/>
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>234.98</v>
+      </c>
+      <c r="N51" s="27" t="inlineStr"/>
       <c r="O51" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3760,44 +3804,54 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10041853</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>FR PAMPERS PANTS PREMIUM CARE XXG 90UN</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>19.36</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-19.36</v>
+        <v>-69.65000000000001</v>
       </c>
       <c r="G52" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>11106</v>
-      </c>
-      <c r="I52" s="22" t="n">
-        <v>8.82</v>
+        <v>1601</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>1.27</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K52" s="26" t="inlineStr"/>
-      <c r="L52" s="23" t="inlineStr"/>
-      <c r="M52" s="26" t="inlineStr"/>
-      <c r="N52" s="27" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K52" s="18" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="L52" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M52" s="18" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="N52" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O52" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P52" s="23" t="inlineStr">
@@ -3807,7 +3861,7 @@
       </c>
       <c r="Q52" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3817,54 +3871,44 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>100015009</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>SAB DOVE 90G LV+ PG- 6UN ORIGINAL</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>19.28</v>
+        <v>68.94</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-19.28</v>
+        <v>-68.94</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>59877</v>
+        <v>9864</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>47.56</v>
+        <v>7.83</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="L53" s="12" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="N53" s="31" t="n">
-        <v>0.12</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K53" s="26" t="inlineStr"/>
+      <c r="L53" s="12" t="inlineStr"/>
+      <c r="M53" s="26" t="inlineStr"/>
+      <c r="N53" s="27" t="inlineStr"/>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
@@ -3872,9 +3916,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Panvel R$ 24.90)</t>
+      <c r="Q53" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3884,41 +3928,41 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>10025717</t>
+          <t>10053171</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG SUPER P 72UN</t>
+          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>19.25</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-19.25</v>
+        <v>-67.81999999999999</v>
       </c>
       <c r="G54" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>12883</v>
-      </c>
-      <c r="I54" s="22" t="n">
-        <v>10.23</v>
+        <v>1454</v>
+      </c>
+      <c r="I54" s="28" t="n">
+        <v>1.15</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K54" s="26" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K54" s="29" t="inlineStr"/>
       <c r="L54" s="23" t="inlineStr"/>
-      <c r="M54" s="26" t="inlineStr"/>
-      <c r="N54" s="27" t="inlineStr"/>
+      <c r="M54" s="29" t="inlineStr"/>
+      <c r="N54" s="30" t="inlineStr"/>
       <c r="O54" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3931,7 +3975,7 @@
       </c>
       <c r="Q54" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -288,6 +288,9 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -297,13 +300,10 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 07:54:11 (07:54) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 08:54:04 (08:54) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4174.46</v>
+        <v>9135.200000000001</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-4174.46</v>
+        <v>-9135.200000000001</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>-1</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
       <c r="Q5" s="14" t="inlineStr">
@@ -888,10 +888,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>1955.92</v>
+        <v>4280.24</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-1955.92</v>
+        <v>-4280.24</v>
       </c>
       <c r="G6" s="20" t="n">
         <v>-1</v>
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>590.4400000000001</v>
+        <v>1292.09</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-590.4400000000001</v>
+        <v>-1292.09</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>-1</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q7" s="14" t="inlineStr">
@@ -1012,10 +1012,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>528.65</v>
+        <v>1156.86</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-528.65</v>
+        <v>-1156.86</v>
       </c>
       <c r="G8" s="20" t="n">
         <v>-1</v>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P8" s="23" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q8" s="25" t="inlineStr">
@@ -1067,54 +1067,44 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10040802</t>
+          <t>10046657</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 2,4MG 3ML NOVO NORDISK</t>
+          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>458.7</v>
+        <v>917.53</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-458.7</v>
+        <v>-917.53</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>3723</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>2.96</v>
+        <v>1048</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>0.83</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>2501.8</v>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>2501.8</v>
-      </c>
-      <c r="N9" s="13" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K9" s="26" t="inlineStr"/>
+      <c r="L9" s="12" t="inlineStr"/>
+      <c r="M9" s="26" t="inlineStr"/>
+      <c r="N9" s="27" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr">
@@ -1124,7 +1114,7 @@
       </c>
       <c r="Q9" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1134,44 +1124,54 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>10046657</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>419.28</v>
+        <v>820.29</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-419.28</v>
+        <v>-820.29</v>
       </c>
       <c r="G10" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>1048</v>
-      </c>
-      <c r="I10" s="28" t="n">
-        <v>0.83</v>
+        <v>9409</v>
+      </c>
+      <c r="I10" s="22" t="n">
+        <v>7.47</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K10" s="29" t="inlineStr"/>
-      <c r="L10" s="23" t="inlineStr"/>
-      <c r="M10" s="29" t="inlineStr"/>
-      <c r="N10" s="30" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="N10" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O10" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P10" s="23" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Q10" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1191,31 +1191,31 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10050654</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>374.84</v>
+        <v>736.41</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-374.84</v>
+        <v>-736.41</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>9409</v>
+        <v>4038</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>7.47</v>
+        <v>3.21</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="K11" s="7" t="n">
-        <v>988.22</v>
+        <v>1617.66</v>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="M11" s="7" t="n">
-        <v>988.22</v>
+        <v>1617.66</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>0</v>
@@ -1258,54 +1258,44 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>10050654</t>
+          <t>10046656</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
+          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>336.51</v>
+        <v>611.6900000000001</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-336.51</v>
+        <v>-611.6900000000001</v>
       </c>
       <c r="G12" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>4038</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>3.21</v>
+        <v>494</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>0.39</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="L12" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M12" s="18" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="N12" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K12" s="30" t="inlineStr"/>
+      <c r="L12" s="23" t="inlineStr"/>
+      <c r="M12" s="30" t="inlineStr"/>
+      <c r="N12" s="31" t="inlineStr"/>
       <c r="O12" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P12" s="23" t="inlineStr">
@@ -1315,7 +1305,7 @@
       </c>
       <c r="Q12" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1325,44 +1315,54 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10046656</t>
+          <t>10030119</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
+          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>279.52</v>
+        <v>400.03</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-279.52</v>
+        <v>-400.03</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>494</v>
-      </c>
-      <c r="I13" s="31" t="n">
-        <v>0.39</v>
+        <v>2858</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>2.27</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K13" s="26" t="inlineStr"/>
-      <c r="L13" s="12" t="inlineStr"/>
-      <c r="M13" s="26" t="inlineStr"/>
-      <c r="N13" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Q13" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1382,54 +1382,44 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>100005474</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>NANLAC COMFOR 3 800G NESTLE</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>108.25</v>
+        <v>0</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>327.98</v>
+        <v>298.88</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-219.73</v>
+        <v>-298.88</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>-0.67</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>14766</v>
+        <v>26223</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>11.73</v>
+        <v>20.83</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>80.48999999999999</v>
-      </c>
-      <c r="L14" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="n">
-        <v>59.99</v>
-      </c>
-      <c r="N14" s="32" t="n">
-        <v>0.342</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K14" s="30" t="inlineStr"/>
+      <c r="L14" s="23" t="inlineStr"/>
+      <c r="M14" s="30" t="inlineStr"/>
+      <c r="N14" s="31" t="inlineStr"/>
       <c r="O14" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P14" s="23" t="inlineStr">
@@ -1437,9 +1427,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q14" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.99)</t>
+      <c r="Q14" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1449,54 +1439,54 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>188.27</v>
+        <v>279.17</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-188.27</v>
+        <v>-279.17</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>2446</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>1.94</v>
+        <v>1758</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>1.4</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K15" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>1945.09</v>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N15" s="33" t="n">
-        <v>1.132</v>
+        <v>1945.09</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
@@ -1504,9 +1494,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+      <c r="Q15" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1516,39 +1506,39 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>10106687</t>
+          <t>10051359</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>APTANUTRI PREMIUM 3 800G DANONE</t>
+          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>186.52</v>
+        <v>278.12</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-186.52</v>
+        <v>-278.12</v>
       </c>
       <c r="G16" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>17535</v>
-      </c>
-      <c r="I16" s="22" t="n">
-        <v>13.93</v>
+        <v>962</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>0.76</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K16" s="18" t="n">
-        <v>79.98999999999999</v>
+        <v>309</v>
       </c>
       <c r="L16" s="23" t="inlineStr">
         <is>
@@ -1556,14 +1546,14 @@
         </is>
       </c>
       <c r="M16" s="18" t="n">
-        <v>52.84</v>
-      </c>
-      <c r="N16" s="32" t="n">
-        <v>0.514</v>
+        <v>449</v>
+      </c>
+      <c r="N16" s="24" t="n">
+        <v>-0.312</v>
       </c>
       <c r="O16" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P16" s="23" t="inlineStr">
@@ -1571,9 +1561,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q16" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 52.84)</t>
+      <c r="Q16" s="25" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1583,31 +1573,31 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10030119</t>
+          <t>10026836</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
+          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>182.8</v>
+        <v>276.21</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-182.8</v>
+        <v>-276.21</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>2858</v>
+        <v>3213</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1615,22 +1605,22 @@
         </is>
       </c>
       <c r="K17" s="7" t="n">
-        <v>1301.17</v>
+        <v>153.23</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
-        <v>1301.17</v>
+        <v>173.71</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>0</v>
+        <v>-0.118</v>
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
@@ -1640,7 +1630,7 @@
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1650,50 +1640,54 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>157.12</v>
+        <v>275.05</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-157.12</v>
+        <v>-275.05</v>
       </c>
       <c r="G18" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>2081</v>
+        <v>6179</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>1.65</v>
+        <v>4.91</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K18" s="29" t="inlineStr"/>
+      <c r="K18" s="18" t="n">
+        <v>831.76</v>
+      </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M18" s="18" t="n">
-        <v>549.9</v>
-      </c>
-      <c r="N18" s="30" t="inlineStr"/>
+        <v>831.76</v>
+      </c>
+      <c r="N18" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O18" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P18" s="23" t="inlineStr">
@@ -1713,31 +1707,31 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>136.58</v>
+        <v>265.8</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-136.58</v>
+        <v>-265.8</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>26223</v>
+        <v>3146</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>20.83</v>
+        <v>2.5</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1770,54 +1764,44 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>127.57</v>
+        <v>264.19</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-127.57</v>
+        <v>-264.19</v>
       </c>
       <c r="G20" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>1758</v>
-      </c>
-      <c r="I20" s="28" t="n">
-        <v>1.4</v>
+        <v>39477</v>
+      </c>
+      <c r="I20" s="22" t="n">
+        <v>31.36</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="L20" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M20" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="N20" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K20" s="30" t="inlineStr"/>
+      <c r="L20" s="23" t="inlineStr"/>
+      <c r="M20" s="30" t="inlineStr"/>
+      <c r="N20" s="31" t="inlineStr"/>
       <c r="O20" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P20" s="23" t="inlineStr">
@@ -1827,7 +1811,7 @@
       </c>
       <c r="Q20" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1837,54 +1821,54 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10051359</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>127.09</v>
+        <v>258.6</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-127.09</v>
+        <v>-258.6</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>962</v>
-      </c>
-      <c r="I21" s="31" t="n">
-        <v>0.76</v>
+        <v>2931</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>2.33</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>309</v>
+        <v>218.67</v>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
-        <v>449</v>
-      </c>
-      <c r="N21" s="13" t="n">
-        <v>-0.312</v>
+        <v>197.18</v>
+      </c>
+      <c r="N21" s="32" t="n">
+        <v>0.109</v>
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
@@ -1892,9 +1876,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q21" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -1904,54 +1888,54 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10026836</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>126.22</v>
+        <v>244.09</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-126.22</v>
+        <v>-244.09</v>
       </c>
       <c r="G22" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>3213</v>
-      </c>
-      <c r="I22" s="22" t="n">
-        <v>2.55</v>
+        <v>837</v>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>0.66</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K22" s="18" t="n">
-        <v>153.23</v>
+        <v>315.46</v>
       </c>
       <c r="L22" s="23" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M22" s="18" t="n">
-        <v>173.71</v>
-      </c>
-      <c r="N22" s="24" t="n">
-        <v>-0.118</v>
+        <v>236.6</v>
+      </c>
+      <c r="N22" s="33" t="n">
+        <v>0.333</v>
       </c>
       <c r="O22" s="23" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P22" s="23" t="inlineStr">
@@ -1959,9 +1943,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q22" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -1971,54 +1955,44 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10050640</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>125.69</v>
+        <v>236.87</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-125.69</v>
+        <v>-236.87</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>6179</v>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>4.91</v>
+        <v>1270</v>
+      </c>
+      <c r="I23" s="28" t="n">
+        <v>1.01</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="N23" s="13" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K23" s="26" t="inlineStr"/>
+      <c r="L23" s="12" t="inlineStr"/>
+      <c r="M23" s="26" t="inlineStr"/>
+      <c r="N23" s="27" t="inlineStr"/>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
@@ -2028,7 +2002,7 @@
       </c>
       <c r="Q23" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2038,31 +2012,31 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>124.51</v>
+        <v>232.58</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-124.51</v>
+        <v>-232.58</v>
       </c>
       <c r="G24" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>8909</v>
+        <v>3992</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>7.08</v>
+        <v>3.17</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -2070,7 +2044,7 @@
         </is>
       </c>
       <c r="K24" s="18" t="n">
-        <v>108.49</v>
+        <v>149.4</v>
       </c>
       <c r="L24" s="23" t="inlineStr">
         <is>
@@ -2078,10 +2052,10 @@
         </is>
       </c>
       <c r="M24" s="18" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N24" s="32" t="n">
-        <v>0.111</v>
+        <v>107</v>
+      </c>
+      <c r="N24" s="33" t="n">
+        <v>0.396</v>
       </c>
       <c r="O24" s="23" t="inlineStr">
         <is>
@@ -2095,7 +2069,7 @@
       </c>
       <c r="Q24" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -2105,31 +2079,31 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>121.46</v>
+        <v>225.93</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-121.46</v>
+        <v>-225.93</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>3146</v>
+        <v>4427</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>2.5</v>
+        <v>3.52</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -2137,8 +2111,14 @@
         </is>
       </c>
       <c r="K25" s="26" t="inlineStr"/>
-      <c r="L25" s="12" t="inlineStr"/>
-      <c r="M25" s="26" t="inlineStr"/>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>50.25</v>
+      </c>
       <c r="N25" s="27" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr">
         <is>
@@ -2162,44 +2142,54 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>120.73</v>
+        <v>221.19</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-120.73</v>
+        <v>-221.19</v>
       </c>
       <c r="G26" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>39477</v>
+        <v>4815</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>31.36</v>
+        <v>3.82</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K26" s="29" t="inlineStr"/>
-      <c r="L26" s="23" t="inlineStr"/>
-      <c r="M26" s="29" t="inlineStr"/>
-      <c r="N26" s="30" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L26" s="23" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M26" s="18" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="N26" s="33" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O26" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P26" s="23" t="inlineStr">
@@ -2207,9 +2197,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q26" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -2219,54 +2209,44 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0</v>
+        <v>221.25</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>118.17</v>
+        <v>437.85</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-118.17</v>
+        <v>-216.6</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-1</v>
+        <v>-0.495</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>2931</v>
+        <v>8275</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>2.33</v>
+        <v>6.57</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>218.67</v>
-      </c>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N27" s="33" t="n">
-        <v>0.109</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K27" s="26" t="inlineStr"/>
+      <c r="L27" s="12" t="inlineStr"/>
+      <c r="M27" s="26" t="inlineStr"/>
+      <c r="N27" s="27" t="inlineStr"/>
       <c r="O27" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P27" s="12" t="inlineStr">
@@ -2274,9 +2254,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+      <c r="Q27" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2286,44 +2266,54 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10042966</t>
+          <t>10050642</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO M 148UN</t>
+          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>112.82</v>
+        <v>215.85</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-112.82</v>
+        <v>-215.85</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>3758</v>
+        <v>5711</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>2.98</v>
+        <v>4.54</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K28" s="29" t="inlineStr"/>
-      <c r="L28" s="23" t="inlineStr"/>
-      <c r="M28" s="29" t="inlineStr"/>
-      <c r="N28" s="30" t="inlineStr"/>
+      <c r="K28" s="18" t="n">
+        <v>955.85</v>
+      </c>
+      <c r="L28" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M28" s="18" t="n">
+        <v>955.85</v>
+      </c>
+      <c r="N28" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O28" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P28" s="23" t="inlineStr">
@@ -2343,50 +2333,50 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0</v>
+        <v>199.8</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>111.54</v>
+        <v>411.99</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-111.54</v>
+        <v>-212.19</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-1</v>
+        <v>-0.515</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>837</v>
-      </c>
-      <c r="I29" s="31" t="n">
-        <v>0.66</v>
+        <v>2446</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>1.94</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K29" s="7" t="n">
-        <v>315.46</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N29" s="33" t="n">
-        <v>0.333</v>
+        <v>46.85</v>
+      </c>
+      <c r="N29" s="32" t="n">
+        <v>1.132</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
@@ -2400,7 +2390,7 @@
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -2410,54 +2400,44 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>108.72</v>
+        <v>180.66</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-108.72</v>
+        <v>-180.66</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>16877</v>
+        <v>11106</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>13.41</v>
+        <v>8.82</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K30" s="18" t="n">
-        <v>74.22</v>
-      </c>
-      <c r="L30" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M30" s="18" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N30" s="32" t="n">
-        <v>0.333</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K30" s="30" t="inlineStr"/>
+      <c r="L30" s="23" t="inlineStr"/>
+      <c r="M30" s="30" t="inlineStr"/>
+      <c r="N30" s="31" t="inlineStr"/>
       <c r="O30" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P30" s="23" t="inlineStr">
@@ -2465,9 +2445,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q30" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+      <c r="Q30" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2477,31 +2457,31 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>108.24</v>
+        <v>173.12</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-108.24</v>
+        <v>-173.12</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>1270</v>
-      </c>
-      <c r="I31" s="31" t="n">
-        <v>1.01</v>
+        <v>204</v>
+      </c>
+      <c r="I31" s="28" t="n">
+        <v>0.16</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -2509,8 +2489,14 @@
         </is>
       </c>
       <c r="K31" s="26" t="inlineStr"/>
-      <c r="L31" s="12" t="inlineStr"/>
-      <c r="M31" s="26" t="inlineStr"/>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>1212.9</v>
+      </c>
       <c r="N31" s="27" t="inlineStr"/>
       <c r="O31" s="12" t="inlineStr">
         <is>
@@ -2534,54 +2520,50 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10033463</t>
+          <t>10093877</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>FR BABYSEC ULTRA HIPER XG 56UN</t>
+          <t>MIRENA 52MG 1END+INS BAYER</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>107.97</v>
+        <v>172.93</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-107.97</v>
+        <v>-172.93</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>11473</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>9.109999999999999</v>
+        <v>501</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>0.4</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K32" s="18" t="n">
-        <v>69.90000000000001</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K32" s="30" t="inlineStr"/>
       <c r="L32" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M32" s="18" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="N32" s="32" t="n">
-        <v>0.167</v>
-      </c>
+        <v>1225.89</v>
+      </c>
+      <c r="N32" s="31" t="inlineStr"/>
       <c r="O32" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P32" s="23" t="inlineStr">
@@ -2589,9 +2571,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q32" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
+      <c r="Q32" s="25" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2601,39 +2583,39 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10050653</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>106.28</v>
+        <v>165.43</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-106.28</v>
+        <v>-165.43</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>3992</v>
+        <v>2647</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K33" s="7" t="n">
-        <v>149.4</v>
+        <v>1347.91</v>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
@@ -2641,14 +2623,14 @@
         </is>
       </c>
       <c r="M33" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="N33" s="33" t="n">
-        <v>0.396</v>
+        <v>1347.89</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
@@ -2656,9 +2638,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+      <c r="Q33" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2668,54 +2650,44 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>10042968</t>
+          <t>10052540</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>440.14</v>
+        <v>0</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>544.77</v>
+        <v>163.92</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-104.63</v>
+        <v>-163.92</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>-0.192</v>
+        <v>-1</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>5925</v>
+        <v>2601</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>4.71</v>
+        <v>2.07</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K34" s="18" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="L34" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M34" s="18" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="N34" s="32" t="n">
-        <v>0.067</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K34" s="30" t="inlineStr"/>
+      <c r="L34" s="23" t="inlineStr"/>
+      <c r="M34" s="30" t="inlineStr"/>
+      <c r="N34" s="31" t="inlineStr"/>
       <c r="O34" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P34" s="23" t="inlineStr">
@@ -2723,9 +2695,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q34" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
+      <c r="Q34" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2735,50 +2707,54 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10041248</t>
+          <t>10024521</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>CREATINA MONOHIDRATADA 300G DUX</t>
+          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>103.24</v>
+        <v>159.62</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-103.24</v>
+        <v>-159.62</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>4427</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>3.52</v>
+        <v>575</v>
+      </c>
+      <c r="I35" s="28" t="n">
+        <v>0.46</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K35" s="26" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>799.9</v>
+      </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M35" s="7" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="N35" s="27" t="inlineStr"/>
+        <v>814.9</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>-0.018</v>
+      </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
@@ -2788,7 +2764,7 @@
       </c>
       <c r="Q35" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2798,41 +2774,41 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>10004419</t>
+          <t>100011549</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>OZEMPIC 1MG 4AGULHAS NOVOFINE 4MM NOVO NORDISK</t>
+          <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>103.22</v>
+        <v>158.9</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-103.22</v>
+        <v>-158.9</v>
       </c>
       <c r="G36" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>2481</v>
+        <v>7665</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>1.97</v>
+        <v>6.09</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K36" s="29" t="inlineStr"/>
+      <c r="K36" s="30" t="inlineStr"/>
       <c r="L36" s="23" t="inlineStr"/>
-      <c r="M36" s="29" t="inlineStr"/>
-      <c r="N36" s="30" t="inlineStr"/>
+      <c r="M36" s="30" t="inlineStr"/>
+      <c r="N36" s="31" t="inlineStr"/>
       <c r="O36" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2845,7 +2821,7 @@
       </c>
       <c r="Q36" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2855,54 +2831,54 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10041853</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>FR PAMPERS PANTS PREMIUM CARE XXG 90UN</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>101.08</v>
+        <v>152.41</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-101.08</v>
+        <v>-152.41</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>4815</v>
-      </c>
-      <c r="I37" s="11" t="n">
-        <v>3.82</v>
+        <v>1601</v>
+      </c>
+      <c r="I37" s="28" t="n">
+        <v>1.27</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K37" s="7" t="n">
-        <v>94.98999999999999</v>
+        <v>169.9</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N37" s="33" t="n">
-        <v>0.904</v>
+        <v>169.9</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
@@ -2910,9 +2886,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+      <c r="Q37" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2922,54 +2898,44 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>10050642</t>
+          <t>10053171</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
+          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>98.63</v>
+        <v>148.41</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-98.63</v>
+        <v>-148.41</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>5711</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>4.54</v>
+        <v>1454</v>
+      </c>
+      <c r="I38" s="29" t="n">
+        <v>1.15</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K38" s="18" t="n">
-        <v>955.85</v>
-      </c>
-      <c r="L38" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M38" s="18" t="n">
-        <v>955.85</v>
-      </c>
-      <c r="N38" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K38" s="30" t="inlineStr"/>
+      <c r="L38" s="23" t="inlineStr"/>
+      <c r="M38" s="30" t="inlineStr"/>
+      <c r="N38" s="31" t="inlineStr"/>
       <c r="O38" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P38" s="23" t="inlineStr">
@@ -2979,7 +2945,7 @@
       </c>
       <c r="Q38" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2989,31 +2955,31 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10028321</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>PREGABALINA 150MG 30CAP GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>115.9</v>
+        <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>200.08</v>
+        <v>148.07</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-84.18000000000001</v>
+        <v>-148.07</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.421</v>
+        <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8275</v>
+        <v>5385</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>6.57</v>
+        <v>4.28</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -3046,44 +3012,54 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10025745</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>82.55</v>
+        <v>147.08</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-82.55</v>
+        <v>-147.08</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>11106</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>8.82</v>
+        <v>122</v>
+      </c>
+      <c r="I40" s="29" t="n">
+        <v>0.1</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K40" s="29" t="inlineStr"/>
-      <c r="L40" s="23" t="inlineStr"/>
-      <c r="M40" s="29" t="inlineStr"/>
-      <c r="N40" s="30" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K40" s="18" t="n">
+        <v>1105.6</v>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M40" s="18" t="n">
+        <v>1170.01</v>
+      </c>
+      <c r="N40" s="24" t="n">
+        <v>-0.055</v>
+      </c>
       <c r="O40" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P40" s="23" t="inlineStr">
@@ -3093,7 +3069,7 @@
       </c>
       <c r="Q40" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3103,54 +3079,54 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10046027</t>
+          <t>10096528</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS SUPERSEC XG 56UN</t>
+          <t>AVAMYS 120DOSES GSK</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>80.63</v>
+        <v>143.6</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-80.63</v>
+        <v>-143.6</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>11875</v>
+        <v>28493</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>9.43</v>
+        <v>22.63</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K41" s="7" t="n">
-        <v>85.90000000000001</v>
+        <v>76.14</v>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="N41" s="33" t="n">
-        <v>0.434</v>
+        <v>76.14</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
@@ -3158,9 +3134,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 59.90)</t>
+      <c r="Q41" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3170,47 +3146,41 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10025098</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>79.11</v>
+        <v>143.12</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-79.11</v>
+        <v>-143.12</v>
       </c>
       <c r="G42" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>204</v>
-      </c>
-      <c r="I42" s="28" t="n">
-        <v>0.16</v>
+        <v>11806</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>9.380000000000001</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K42" s="29" t="inlineStr"/>
-      <c r="L42" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M42" s="18" t="n">
-        <v>1212.9</v>
-      </c>
-      <c r="N42" s="30" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K42" s="30" t="inlineStr"/>
+      <c r="L42" s="23" t="inlineStr"/>
+      <c r="M42" s="30" t="inlineStr"/>
+      <c r="N42" s="31" t="inlineStr"/>
       <c r="O42" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3223,7 +3193,7 @@
       </c>
       <c r="Q42" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3233,46 +3203,40 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10093877</t>
+          <t>10046473</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>MIRENA 52MG 1END+INS BAYER</t>
+          <t>ROUPA INT SAO JOAO ADULTO PANTS G/XG 32UN</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>79.02</v>
+        <v>137.96</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-79.02</v>
+        <v>-137.96</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>501</v>
-      </c>
-      <c r="I43" s="31" t="n">
-        <v>0.4</v>
+        <v>19129</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>15.19</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K43" s="26" t="inlineStr"/>
-      <c r="L43" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="n">
-        <v>1225.89</v>
-      </c>
+      <c r="L43" s="12" t="inlineStr"/>
+      <c r="M43" s="26" t="inlineStr"/>
       <c r="N43" s="27" t="inlineStr"/>
       <c r="O43" s="12" t="inlineStr">
         <is>
@@ -3286,7 +3250,7 @@
       </c>
       <c r="Q43" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3296,54 +3260,50 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>10101654</t>
+          <t>10044745</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>NAN COMFOR 2 800G NESTLE</t>
+          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>77.90000000000001</v>
+        <v>124.04</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-77.90000000000001</v>
+        <v>-124.04</v>
       </c>
       <c r="G44" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>13534</v>
+        <v>5858</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>10.75</v>
+        <v>4.65</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K44" s="18" t="n">
-        <v>87.48999999999999</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K44" s="30" t="inlineStr"/>
       <c r="L44" s="23" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M44" s="18" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="N44" s="32" t="n">
-        <v>0.094</v>
-      </c>
+        <v>83.92</v>
+      </c>
+      <c r="N44" s="31" t="inlineStr"/>
       <c r="O44" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P44" s="23" t="inlineStr">
@@ -3351,9 +3311,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q44" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 79.99)</t>
+      <c r="Q44" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3363,54 +3323,44 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10050653</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0</v>
+        <v>26.91</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>75.59</v>
+        <v>150.87</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-75.59</v>
+        <v>-123.96</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-1</v>
+        <v>-0.8220000000000001</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>2647</v>
+        <v>9864</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>2.1</v>
+        <v>7.83</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K45" s="7" t="n">
-        <v>1347.91</v>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="n">
-        <v>1347.89</v>
-      </c>
-      <c r="N45" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K45" s="26" t="inlineStr"/>
+      <c r="L45" s="12" t="inlineStr"/>
+      <c r="M45" s="26" t="inlineStr"/>
+      <c r="N45" s="27" t="inlineStr"/>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
@@ -3430,41 +3380,41 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10052540</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>74.91</v>
+        <v>122.14</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-74.91</v>
+        <v>-122.14</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>2601</v>
+        <v>30285</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>2.07</v>
+        <v>24.05</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K46" s="29" t="inlineStr"/>
+      <c r="K46" s="30" t="inlineStr"/>
       <c r="L46" s="23" t="inlineStr"/>
-      <c r="M46" s="29" t="inlineStr"/>
-      <c r="N46" s="30" t="inlineStr"/>
+      <c r="M46" s="30" t="inlineStr"/>
+      <c r="N46" s="31" t="inlineStr"/>
       <c r="O46" s="23" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3487,54 +3437,50 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10097311</t>
+          <t>10005850</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 1 800G NESTLE</t>
+          <t>SERTRALINA 100MG 30CP REV GEN PRATI (C1)</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0</v>
+        <v>39.9</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>74.76000000000001</v>
+        <v>160.57</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-74.76000000000001</v>
+        <v>-120.67</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-1</v>
+        <v>-0.752</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>10627</v>
+        <v>9718</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>8.44</v>
+        <v>7.72</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>67.98999999999999</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K47" s="26" t="inlineStr"/>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="N47" s="33" t="n">
-        <v>0.081</v>
-      </c>
+        <v>54.99</v>
+      </c>
+      <c r="N47" s="27" t="inlineStr"/>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
@@ -3542,9 +3488,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 62.90)</t>
+      <c r="Q47" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3554,50 +3500,54 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>10005850</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>SERTRALINA 100MG 30CP REV GEN PRATI (C1)</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>0</v>
+        <v>157.72</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>73.37</v>
+        <v>272.48</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-73.37</v>
+        <v>-114.76</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>-1</v>
+        <v>-0.421</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>9718</v>
+        <v>8909</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>7.72</v>
+        <v>7.08</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K48" s="29" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K48" s="18" t="n">
+        <v>108.49</v>
+      </c>
       <c r="L48" s="23" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M48" s="18" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="N48" s="30" t="inlineStr"/>
+        <v>97.69</v>
+      </c>
+      <c r="N48" s="33" t="n">
+        <v>0.111</v>
+      </c>
       <c r="O48" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P48" s="23" t="inlineStr">
@@ -3605,9 +3555,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q48" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q48" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -3617,54 +3567,54 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10024521</t>
+          <t>10030120</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
+          <t>RYBELSUS 7MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>72.94</v>
+        <v>114.74</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-72.94</v>
+        <v>-114.74</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>575</v>
-      </c>
-      <c r="I49" s="31" t="n">
-        <v>0.46</v>
+        <v>1978</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>1.57</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K49" s="7" t="n">
-        <v>799.9</v>
+        <v>1301.17</v>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>814.9</v>
+        <v>1301.17</v>
       </c>
       <c r="N49" s="13" t="n">
-        <v>-0.018</v>
+        <v>0</v>
       </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
@@ -3674,7 +3624,7 @@
       </c>
       <c r="Q49" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -3684,44 +3634,54 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>100011549</t>
+          <t>10032150</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
+          <t>APTAMIL PROFUTURA GOLD 2 800G DANONE</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>72.61</v>
+        <v>113.1</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-72.61</v>
+        <v>-113.1</v>
       </c>
       <c r="G50" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>7665</v>
+        <v>6215</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>6.09</v>
+        <v>4.94</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K50" s="29" t="inlineStr"/>
-      <c r="L50" s="23" t="inlineStr"/>
-      <c r="M50" s="29" t="inlineStr"/>
-      <c r="N50" s="30" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>131.99</v>
+      </c>
+      <c r="L50" s="23" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M50" s="18" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="N50" s="33" t="n">
+        <v>0.201</v>
+      </c>
       <c r="O50" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P50" s="23" t="inlineStr">
@@ -3729,9 +3689,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q50" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q50" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 109.90)</t>
         </is>
       </c>
     </row>
@@ -3741,50 +3701,54 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10034467</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>SLINDA 4MG 72CP+12PLACEBOS EXELTIS</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>71.56</v>
+        <v>137.84</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-71.56</v>
+        <v>-111.94</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-1</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>3778</v>
+        <v>22233</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>3</v>
+        <v>17.66</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K51" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>25.9</v>
+      </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
-        <v>234.98</v>
-      </c>
-      <c r="N51" s="27" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="N51" s="32" t="n">
+        <v>0.629</v>
+      </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P51" s="12" t="inlineStr">
@@ -3792,9 +3756,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q51" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -3804,54 +3768,50 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>10041853</t>
+          <t>10035030</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS PREMIUM CARE XXG 90UN</t>
+          <t>APTANUTRI PREMIUM 3 800G 30% DESC 2UN DANONE</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>69.65000000000001</v>
+        <v>108.55</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-69.65000000000001</v>
+        <v>-108.55</v>
       </c>
       <c r="G52" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>1601</v>
-      </c>
-      <c r="I52" s="28" t="n">
-        <v>1.27</v>
+        <v>3103</v>
+      </c>
+      <c r="I52" s="22" t="n">
+        <v>2.46</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K52" s="18" t="n">
-        <v>169.9</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K52" s="30" t="inlineStr"/>
       <c r="L52" s="23" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M52" s="18" t="n">
-        <v>169.9</v>
-      </c>
-      <c r="N52" s="24" t="n">
-        <v>0</v>
-      </c>
+        <v>125.9</v>
+      </c>
+      <c r="N52" s="31" t="inlineStr"/>
       <c r="O52" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P52" s="23" t="inlineStr">
@@ -3861,7 +3821,7 @@
       </c>
       <c r="Q52" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3871,44 +3831,54 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>100001748</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>ELANI CICLO 3MG+30MCG 3X21CP REV LIBBS</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>68.94</v>
+        <v>107.68</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-68.94</v>
+        <v>-107.68</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>9864</v>
+        <v>4373</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>7.83</v>
+        <v>3.47</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K53" s="26" t="inlineStr"/>
-      <c r="L53" s="12" t="inlineStr"/>
-      <c r="M53" s="26" t="inlineStr"/>
-      <c r="N53" s="27" t="inlineStr"/>
+      <c r="K53" s="7" t="n">
+        <v>113.72</v>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>122.49</v>
+      </c>
+      <c r="N53" s="13" t="n">
+        <v>-0.07200000000000001</v>
+      </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
@@ -3928,44 +3898,54 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>10053171</t>
+          <t>10047543</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
+          <t>DULOXETINA 60MG 60CAP GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>67.81999999999999</v>
+        <v>106.55</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-67.81999999999999</v>
+        <v>-106.55</v>
       </c>
       <c r="G54" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>1454</v>
-      </c>
-      <c r="I54" s="28" t="n">
-        <v>1.15</v>
+        <v>9931</v>
+      </c>
+      <c r="I54" s="22" t="n">
+        <v>7.89</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K54" s="29" t="inlineStr"/>
-      <c r="L54" s="23" t="inlineStr"/>
-      <c r="M54" s="29" t="inlineStr"/>
-      <c r="N54" s="30" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K54" s="18" t="n">
+        <v>162.69</v>
+      </c>
+      <c r="L54" s="23" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M54" s="18" t="n">
+        <v>154.99</v>
+      </c>
+      <c r="N54" s="33" t="n">
+        <v>0.05</v>
+      </c>
       <c r="O54" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P54" s="23" t="inlineStr">
@@ -3973,9 +3953,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q54" s="25" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Panvel R$ 154.99)</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -282,13 +282,13 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 08:54:04 (08:54) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 09:54:57 (09:54) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0</v>
+        <v>8897.15</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>9135.200000000001</v>
+        <v>15739.16</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-9135.200000000001</v>
+        <v>-6842.01</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-1</v>
+        <v>-0.435</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>11192</v>
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>0</v>
+        <v>4267.56</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>4280.24</v>
+        <v>7374.48</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-4280.24</v>
+        <v>-3106.92</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>-1</v>
+        <v>-0.421</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>9353</v>
@@ -943,41 +943,41 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10053130</t>
+          <t>10046657</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>OZIVY 1MG 1CAN 3ML EMS</t>
+          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1292.09</v>
+        <v>1580.83</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-1292.09</v>
+        <v>-1580.83</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>10582</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>8.41</v>
+        <v>1048</v>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>0.83</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K7" s="26" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K7" s="27" t="inlineStr"/>
       <c r="L7" s="12" t="inlineStr"/>
-      <c r="M7" s="26" t="inlineStr"/>
-      <c r="N7" s="27" t="inlineStr"/>
+      <c r="M7" s="27" t="inlineStr"/>
+      <c r="N7" s="28" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -990,7 +990,7 @@
       </c>
       <c r="Q7" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1000,31 +1000,31 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>10046655</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 10MG 4CAN APLIC LILLY</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>1156.86</v>
+        <v>1413.28</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-1156.86</v>
+        <v>-1413.28</v>
       </c>
       <c r="G8" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>3069</v>
+        <v>9409</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>2.44</v>
+        <v>7.47</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
@@ -1032,15 +1032,15 @@
         </is>
       </c>
       <c r="K8" s="18" t="n">
-        <v>3210.85</v>
+        <v>988.22</v>
       </c>
       <c r="L8" s="23" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M8" s="18" t="n">
-        <v>3210.85</v>
+        <v>988.22</v>
       </c>
       <c r="N8" s="24" t="n">
         <v>0</v>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Q8" s="25" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1067,54 +1067,64 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10046657</t>
+          <t>10050654</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
+          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>917.53</v>
+        <v>1268.77</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-917.53</v>
+        <v>-1268.77</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>1048</v>
-      </c>
-      <c r="I9" s="28" t="n">
-        <v>0.83</v>
+        <v>4038</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>3.21</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K9" s="26" t="inlineStr"/>
-      <c r="L9" s="12" t="inlineStr"/>
-      <c r="M9" s="26" t="inlineStr"/>
-      <c r="N9" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>1617.66</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q9" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1124,64 +1134,54 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10046656</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>820.29</v>
+        <v>1053.89</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-820.29</v>
+        <v>-1053.89</v>
       </c>
       <c r="G10" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>9409</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>7.47</v>
+        <v>494</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>0.39</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="L10" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M10" s="18" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N10" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K10" s="30" t="inlineStr"/>
+      <c r="L10" s="23" t="inlineStr"/>
+      <c r="M10" s="30" t="inlineStr"/>
+      <c r="N10" s="31" t="inlineStr"/>
       <c r="O10" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P10" s="23" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q10" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1191,54 +1191,44 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10050654</t>
+          <t>10053130</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
+          <t>OZIVY 1MG 1CAN 3ML EMS</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0</v>
+        <v>1463.81</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>736.41</v>
+        <v>2226.16</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-736.41</v>
+        <v>-762.35</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-1</v>
+        <v>-0.342</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>4038</v>
+        <v>10582</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>3.21</v>
+        <v>8.41</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K11" s="7" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="N11" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K11" s="27" t="inlineStr"/>
+      <c r="L11" s="12" t="inlineStr"/>
+      <c r="M11" s="27" t="inlineStr"/>
+      <c r="N11" s="28" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
@@ -1248,7 +1238,7 @@
       </c>
       <c r="Q11" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1258,44 +1248,54 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>10046656</t>
+          <t>10030119</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
+          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>611.6900000000001</v>
+        <v>689.22</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-611.6900000000001</v>
+        <v>-689.22</v>
       </c>
       <c r="G12" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>494</v>
-      </c>
-      <c r="I12" s="29" t="n">
-        <v>0.39</v>
+        <v>2858</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>2.27</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K12" s="30" t="inlineStr"/>
-      <c r="L12" s="23" t="inlineStr"/>
-      <c r="M12" s="30" t="inlineStr"/>
-      <c r="N12" s="31" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="N12" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="O12" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P12" s="23" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Q12" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1315,54 +1315,54 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10030119</t>
+          <t>10042968</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
+          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0</v>
+        <v>1445.73</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>400.03</v>
+        <v>2053.96</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-400.03</v>
+        <v>-608.23</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-1</v>
+        <v>-0.296</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>2858</v>
+        <v>5925</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>2.27</v>
+        <v>4.71</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>1301.17</v>
+        <v>159.9</v>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0</v>
+        <v>149.9</v>
+      </c>
+      <c r="N13" s="32" t="n">
+        <v>0.067</v>
       </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
@@ -1370,9 +1370,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q13" s="14" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
         </is>
       </c>
     </row>
@@ -1382,31 +1382,31 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>0</v>
+        <v>221.25</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>298.88</v>
+        <v>754.38</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-298.88</v>
+        <v>-533.13</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>-1</v>
+        <v>-0.7070000000000001</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>26223</v>
+        <v>8275</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>20.83</v>
+        <v>6.57</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
@@ -1439,54 +1439,44 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>279.17</v>
+        <v>514.9400000000001</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-279.17</v>
+        <v>-514.9400000000001</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>1758</v>
-      </c>
-      <c r="I15" s="28" t="n">
-        <v>1.4</v>
+        <v>26223</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>20.83</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="N15" s="13" t="n">
-        <v>0</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K15" s="27" t="inlineStr"/>
+      <c r="L15" s="12" t="inlineStr"/>
+      <c r="M15" s="27" t="inlineStr"/>
+      <c r="N15" s="28" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
@@ -1496,7 +1486,7 @@
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1506,31 +1496,31 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>10051359</t>
+          <t>10040801</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
+          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>278.12</v>
+        <v>480.99</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-278.12</v>
+        <v>-480.99</v>
       </c>
       <c r="G16" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>962</v>
+        <v>1758</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>0.76</v>
+        <v>1.4</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
@@ -1538,22 +1528,22 @@
         </is>
       </c>
       <c r="K16" s="18" t="n">
-        <v>309</v>
+        <v>1945.09</v>
       </c>
       <c r="L16" s="23" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M16" s="18" t="n">
-        <v>449</v>
+        <v>1945.09</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>-0.312</v>
+        <v>0</v>
       </c>
       <c r="O16" s="23" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P16" s="23" t="inlineStr">
@@ -1573,50 +1563,50 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10026836</t>
+          <t>10051359</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>IUMI ES 3MG+20MCG 120CP REV LIBBS</t>
+          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>276.21</v>
+        <v>479.17</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-276.21</v>
+        <v>-479.17</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>3213</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>2.55</v>
+        <v>962</v>
+      </c>
+      <c r="I17" s="26" t="n">
+        <v>0.76</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K17" s="7" t="n">
-        <v>153.23</v>
+        <v>309</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
-        <v>173.71</v>
+        <v>449</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>-0.118</v>
+        <v>-0.312</v>
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
@@ -1630,7 +1620,7 @@
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1652,10 +1642,10 @@
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>275.05</v>
+        <v>473.88</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-275.05</v>
+        <v>-473.88</v>
       </c>
       <c r="G18" s="20" t="n">
         <v>-1</v>
@@ -1719,10 +1709,10 @@
         <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>265.8</v>
+        <v>457.95</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-265.8</v>
+        <v>-457.95</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>-1</v>
@@ -1738,10 +1728,10 @@
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K19" s="26" t="inlineStr"/>
+      <c r="K19" s="27" t="inlineStr"/>
       <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="26" t="inlineStr"/>
-      <c r="N19" s="27" t="inlineStr"/>
+      <c r="M19" s="27" t="inlineStr"/>
+      <c r="N19" s="28" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1764,44 +1754,54 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>0</v>
+        <v>299.7</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>264.19</v>
+        <v>709.83</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-264.19</v>
+        <v>-410.13</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>-1</v>
+        <v>-0.578</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>39477</v>
+        <v>2446</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>31.36</v>
+        <v>1.94</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K20" s="30" t="inlineStr"/>
-      <c r="L20" s="23" t="inlineStr"/>
-      <c r="M20" s="30" t="inlineStr"/>
-      <c r="N20" s="31" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="N20" s="33" t="n">
+        <v>1.132</v>
+      </c>
       <c r="O20" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P20" s="23" t="inlineStr">
@@ -1809,9 +1809,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q20" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q20" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -1821,31 +1821,31 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>258.6</v>
+        <v>400.71</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-258.6</v>
+        <v>-400.71</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>2931</v>
+        <v>3992</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>2.33</v>
+        <v>3.17</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1853,18 +1853,18 @@
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>218.67</v>
+        <v>149.4</v>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
-        <v>197.18</v>
+        <v>107</v>
       </c>
       <c r="N21" s="32" t="n">
-        <v>0.109</v>
+        <v>0.396</v>
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -1888,54 +1888,50 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>244.09</v>
+        <v>389.26</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-244.09</v>
+        <v>-389.26</v>
       </c>
       <c r="G22" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>837</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>0.66</v>
+        <v>4427</v>
+      </c>
+      <c r="I22" s="22" t="n">
+        <v>3.52</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>315.46</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K22" s="30" t="inlineStr"/>
       <c r="L22" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M22" s="18" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N22" s="33" t="n">
-        <v>0.333</v>
-      </c>
+        <v>50.25</v>
+      </c>
+      <c r="N22" s="31" t="inlineStr"/>
       <c r="O22" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P22" s="23" t="inlineStr">
@@ -1943,9 +1939,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q22" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+      <c r="Q22" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1955,44 +1951,54 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>236.87</v>
+        <v>381.09</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-236.87</v>
+        <v>-381.09</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>1270</v>
-      </c>
-      <c r="I23" s="28" t="n">
-        <v>1.01</v>
+        <v>4815</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>3.82</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K23" s="26" t="inlineStr"/>
-      <c r="L23" s="12" t="inlineStr"/>
-      <c r="M23" s="26" t="inlineStr"/>
-      <c r="N23" s="27" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="N23" s="32" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
@@ -2000,9 +2006,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q23" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -2012,31 +2018,31 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>0</v>
+        <v>157.72</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>232.58</v>
+        <v>469.46</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-232.58</v>
+        <v>-311.74</v>
       </c>
       <c r="G24" s="20" t="n">
-        <v>-1</v>
+        <v>-0.664</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>3992</v>
+        <v>8909</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>3.17</v>
+        <v>7.08</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
@@ -2044,7 +2050,7 @@
         </is>
       </c>
       <c r="K24" s="18" t="n">
-        <v>149.4</v>
+        <v>108.49</v>
       </c>
       <c r="L24" s="23" t="inlineStr">
         <is>
@@ -2052,10 +2058,10 @@
         </is>
       </c>
       <c r="M24" s="18" t="n">
-        <v>107</v>
+        <v>97.69</v>
       </c>
       <c r="N24" s="33" t="n">
-        <v>0.396</v>
+        <v>0.111</v>
       </c>
       <c r="O24" s="23" t="inlineStr">
         <is>
@@ -2069,7 +2075,7 @@
       </c>
       <c r="Q24" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2085,41 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10041248</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>CREATINA MONOHIDRATADA 300G DUX</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>225.93</v>
+        <v>311.26</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-225.93</v>
+        <v>-311.26</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>4427</v>
+        <v>11106</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>3.52</v>
+        <v>8.82</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K25" s="26" t="inlineStr"/>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="N25" s="27" t="inlineStr"/>
+      <c r="K25" s="27" t="inlineStr"/>
+      <c r="L25" s="12" t="inlineStr"/>
+      <c r="M25" s="27" t="inlineStr"/>
+      <c r="N25" s="28" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2142,54 +2142,44 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>0</v>
+        <v>105.9</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>221.19</v>
+        <v>408.11</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-221.19</v>
+        <v>-302.21</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>-1</v>
+        <v>-0.741</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>4815</v>
-      </c>
-      <c r="I26" s="22" t="n">
-        <v>3.82</v>
+        <v>1270</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <v>1.01</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K26" s="18" t="n">
-        <v>94.98999999999999</v>
-      </c>
-      <c r="L26" s="23" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M26" s="18" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N26" s="33" t="n">
-        <v>0.904</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K26" s="30" t="inlineStr"/>
+      <c r="L26" s="23" t="inlineStr"/>
+      <c r="M26" s="30" t="inlineStr"/>
+      <c r="N26" s="31" t="inlineStr"/>
       <c r="O26" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P26" s="23" t="inlineStr">
@@ -2197,9 +2187,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q26" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+      <c r="Q26" s="25" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2209,41 +2199,47 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>221.25</v>
+        <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>437.85</v>
+        <v>298.28</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-216.6</v>
+        <v>-298.28</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.495</v>
+        <v>-1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>8275</v>
-      </c>
-      <c r="I27" s="11" t="n">
-        <v>6.57</v>
+        <v>204</v>
+      </c>
+      <c r="I27" s="26" t="n">
+        <v>0.16</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K27" s="26" t="inlineStr"/>
-      <c r="L27" s="12" t="inlineStr"/>
-      <c r="M27" s="26" t="inlineStr"/>
-      <c r="N27" s="27" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K27" s="27" t="inlineStr"/>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>1212.9</v>
+      </c>
+      <c r="N27" s="28" t="inlineStr"/>
       <c r="O27" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2256,7 +2252,7 @@
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2266,54 +2262,50 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10050642</t>
+          <t>10093877</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,5MG 1,5ML EUROFARMA</t>
+          <t>MIRENA 52MG 1END+INS BAYER</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>215.85</v>
+        <v>297.94</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-215.85</v>
+        <v>-297.94</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>5711</v>
-      </c>
-      <c r="I28" s="22" t="n">
-        <v>4.54</v>
+        <v>501</v>
+      </c>
+      <c r="I28" s="29" t="n">
+        <v>0.4</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="n">
-        <v>955.85</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K28" s="30" t="inlineStr"/>
       <c r="L28" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M28" s="18" t="n">
-        <v>955.85</v>
-      </c>
-      <c r="N28" s="24" t="n">
-        <v>0</v>
-      </c>
+        <v>1225.89</v>
+      </c>
+      <c r="N28" s="31" t="inlineStr"/>
       <c r="O28" s="23" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P28" s="23" t="inlineStr">
@@ -2323,7 +2315,7 @@
       </c>
       <c r="Q28" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2333,54 +2325,54 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10050653</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>199.8</v>
+        <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>411.99</v>
+        <v>285.02</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-212.19</v>
+        <v>-285.02</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-0.515</v>
+        <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>2446</v>
+        <v>2647</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K29" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>1347.91</v>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N29" s="32" t="n">
-        <v>1.132</v>
+        <v>1347.89</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
@@ -2388,9 +2380,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+      <c r="Q29" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2400,44 +2392,54 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10024521</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>180.66</v>
+        <v>275.01</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-180.66</v>
+        <v>-275.01</v>
       </c>
       <c r="G30" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>11106</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>8.82</v>
+        <v>575</v>
+      </c>
+      <c r="I30" s="29" t="n">
+        <v>0.46</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K30" s="30" t="inlineStr"/>
-      <c r="L30" s="23" t="inlineStr"/>
-      <c r="M30" s="30" t="inlineStr"/>
-      <c r="N30" s="31" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>799.9</v>
+      </c>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M30" s="18" t="n">
+        <v>814.9</v>
+      </c>
+      <c r="N30" s="24" t="n">
+        <v>-0.018</v>
+      </c>
       <c r="O30" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P30" s="23" t="inlineStr">
@@ -2447,7 +2449,7 @@
       </c>
       <c r="Q30" s="25" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2457,47 +2459,41 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10025098</t>
+          <t>10053171</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
+          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>173.12</v>
+        <v>255.69</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-173.12</v>
+        <v>-255.69</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>204</v>
-      </c>
-      <c r="I31" s="28" t="n">
-        <v>0.16</v>
+        <v>1454</v>
+      </c>
+      <c r="I31" s="26" t="n">
+        <v>1.15</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K31" s="26" t="inlineStr"/>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="n">
-        <v>1212.9</v>
-      </c>
-      <c r="N31" s="27" t="inlineStr"/>
+      <c r="K31" s="27" t="inlineStr"/>
+      <c r="L31" s="12" t="inlineStr"/>
+      <c r="M31" s="27" t="inlineStr"/>
+      <c r="N31" s="28" t="inlineStr"/>
       <c r="O31" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2520,50 +2516,54 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10093877</t>
+          <t>10025745</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>MIRENA 52MG 1END+INS BAYER</t>
+          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>172.93</v>
+        <v>253.41</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-172.93</v>
+        <v>-253.41</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>501</v>
+        <v>122</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K32" s="30" t="inlineStr"/>
+      <c r="K32" s="18" t="n">
+        <v>1105.6</v>
+      </c>
       <c r="L32" s="23" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M32" s="18" t="n">
-        <v>1225.89</v>
-      </c>
-      <c r="N32" s="31" t="inlineStr"/>
+        <v>1170.01</v>
+      </c>
+      <c r="N32" s="24" t="n">
+        <v>-0.055</v>
+      </c>
       <c r="O32" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P32" s="23" t="inlineStr">
@@ -2583,54 +2583,44 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10050653</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>165.43</v>
+        <v>246.58</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-165.43</v>
+        <v>-246.58</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>2647</v>
+        <v>11806</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>2.1</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K33" s="7" t="n">
-        <v>1347.91</v>
-      </c>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M33" s="7" t="n">
-        <v>1347.89</v>
-      </c>
-      <c r="N33" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K33" s="27" t="inlineStr"/>
+      <c r="L33" s="12" t="inlineStr"/>
+      <c r="M33" s="27" t="inlineStr"/>
+      <c r="N33" s="28" t="inlineStr"/>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
@@ -2650,31 +2640,31 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>10052540</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>0</v>
+        <v>221.97</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>163.92</v>
+        <v>455.18</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-163.92</v>
+        <v>-233.21</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>-1</v>
+        <v>-0.512</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>2601</v>
+        <v>39477</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>2.07</v>
+        <v>31.36</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
@@ -2707,54 +2697,44 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10024521</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0</v>
+        <v>26.91</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>159.62</v>
+        <v>259.93</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-159.62</v>
+        <v>-233.02</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-1</v>
+        <v>-0.8959999999999999</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>575</v>
-      </c>
-      <c r="I35" s="28" t="n">
-        <v>0.46</v>
+        <v>9864</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>7.83</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>799.9</v>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M35" s="7" t="n">
-        <v>814.9</v>
-      </c>
-      <c r="N35" s="13" t="n">
-        <v>-0.018</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K35" s="27" t="inlineStr"/>
+      <c r="L35" s="12" t="inlineStr"/>
+      <c r="M35" s="27" t="inlineStr"/>
+      <c r="N35" s="28" t="inlineStr"/>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
@@ -2764,7 +2744,7 @@
       </c>
       <c r="Q35" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2774,31 +2754,31 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>100011549</t>
+          <t>10028321</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
+          <t>PREGABALINA 150MG 30CAP GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
-        <v>0</v>
+        <v>31.63</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>158.9</v>
+        <v>255.11</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-158.9</v>
+        <v>-223.48</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>-1</v>
+        <v>-0.8759999999999999</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>7665</v>
+        <v>5385</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>6.09</v>
+        <v>4.28</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
@@ -2831,54 +2811,54 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10041853</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS PREMIUM CARE XXG 90UN</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>152.41</v>
+        <v>237.48</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-152.41</v>
+        <v>-211.58</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-1</v>
+        <v>-0.8909999999999999</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>1601</v>
-      </c>
-      <c r="I37" s="28" t="n">
-        <v>1.27</v>
+        <v>22233</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>17.66</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K37" s="7" t="n">
-        <v>169.9</v>
+        <v>25.9</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
-        <v>169.9</v>
-      </c>
-      <c r="N37" s="13" t="n">
-        <v>0</v>
+        <v>15.9</v>
+      </c>
+      <c r="N37" s="32" t="n">
+        <v>0.629</v>
       </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
@@ -2886,9 +2866,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q37" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -2898,35 +2878,35 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>10053171</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>148.41</v>
+        <v>210.43</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-148.41</v>
+        <v>-210.43</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>1454</v>
-      </c>
-      <c r="I38" s="29" t="n">
-        <v>1.15</v>
+        <v>30285</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>24.05</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K38" s="30" t="inlineStr"/>
@@ -2945,7 +2925,7 @@
       </c>
       <c r="Q38" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2955,44 +2935,54 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10028321</t>
+          <t>10030120</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>PREGABALINA 150MG 30CAP GEN EMS (C1)</t>
+          <t>RYBELSUS 7MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>148.07</v>
+        <v>197.69</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-148.07</v>
+        <v>-197.69</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>5385</v>
+        <v>1978</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>4.28</v>
+        <v>1.57</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K39" s="26" t="inlineStr"/>
-      <c r="L39" s="12" t="inlineStr"/>
-      <c r="M39" s="26" t="inlineStr"/>
-      <c r="N39" s="27" t="inlineStr"/>
+      <c r="K39" s="7" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>1301.17</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
@@ -3002,7 +2992,7 @@
       </c>
       <c r="Q39" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -3012,54 +3002,50 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>10025745</t>
+          <t>10005850</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
+          <t>SERTRALINA 100MG 30CP REV GEN PRATI (C1)</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>0</v>
+        <v>79.8</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>147.08</v>
+        <v>276.64</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-147.08</v>
+        <v>-196.84</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>-1</v>
+        <v>-0.7120000000000001</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>122</v>
-      </c>
-      <c r="I40" s="29" t="n">
-        <v>0.1</v>
+        <v>9718</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>7.72</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K40" s="18" t="n">
-        <v>1105.6</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K40" s="30" t="inlineStr"/>
       <c r="L40" s="23" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M40" s="18" t="n">
-        <v>1170.01</v>
-      </c>
-      <c r="N40" s="24" t="n">
-        <v>-0.055</v>
-      </c>
+        <v>54.99</v>
+      </c>
+      <c r="N40" s="31" t="inlineStr"/>
       <c r="O40" s="23" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P40" s="23" t="inlineStr">
@@ -3069,7 +3055,7 @@
       </c>
       <c r="Q40" s="25" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3079,54 +3065,54 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10096528</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>AVAMYS 120DOSES GSK</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0</v>
+        <v>231.09</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>143.6</v>
+        <v>420.55</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-143.6</v>
+        <v>-189.46</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-1</v>
+        <v>-0.45</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>28493</v>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>22.63</v>
+        <v>837</v>
+      </c>
+      <c r="I41" s="26" t="n">
+        <v>0.66</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K41" s="7" t="n">
-        <v>76.14</v>
+        <v>315.46</v>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
-        <v>76.14</v>
-      </c>
-      <c r="N41" s="13" t="n">
-        <v>0</v>
+        <v>236.6</v>
+      </c>
+      <c r="N41" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
@@ -3134,9 +3120,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q41" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -3146,31 +3132,31 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10035030</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>APTANUTRI PREMIUM 3 800G 30% DESC 2UN DANONE</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>143.12</v>
+        <v>187.02</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-143.12</v>
+        <v>-187.02</v>
       </c>
       <c r="G42" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>11806</v>
+        <v>3103</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>9.380000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
@@ -3178,8 +3164,14 @@
         </is>
       </c>
       <c r="K42" s="30" t="inlineStr"/>
-      <c r="L42" s="23" t="inlineStr"/>
-      <c r="M42" s="30" t="inlineStr"/>
+      <c r="L42" s="23" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M42" s="18" t="n">
+        <v>125.9</v>
+      </c>
       <c r="N42" s="31" t="inlineStr"/>
       <c r="O42" s="23" t="inlineStr">
         <is>
@@ -3203,41 +3195,41 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10046473</t>
+          <t>10053166</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>ROUPA INT SAO JOAO ADULTO PANTS G/XG 32UN</t>
+          <t>OZIVY 1MG 2CAN 3ML EMS</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>137.96</v>
+        <v>182.64</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-137.96</v>
+        <v>-182.64</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>19129</v>
+        <v>2941</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>15.19</v>
+        <v>2.34</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K43" s="26" t="inlineStr"/>
+      <c r="K43" s="27" t="inlineStr"/>
       <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="26" t="inlineStr"/>
-      <c r="N43" s="27" t="inlineStr"/>
+      <c r="M43" s="27" t="inlineStr"/>
+      <c r="N43" s="28" t="inlineStr"/>
       <c r="O43" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3250,7 +3242,7 @@
       </c>
       <c r="Q43" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -3260,50 +3252,54 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>10044745</t>
+          <t>100022270</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
+          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>124.04</v>
+        <v>179.14</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-124.04</v>
+        <v>-179.14</v>
       </c>
       <c r="G44" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>5858</v>
+        <v>1962</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>4.65</v>
+        <v>1.56</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K44" s="30" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K44" s="18" t="n">
+        <v>185.61</v>
+      </c>
       <c r="L44" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M44" s="18" t="n">
-        <v>83.92</v>
-      </c>
-      <c r="N44" s="31" t="inlineStr"/>
+        <v>158.66</v>
+      </c>
+      <c r="N44" s="33" t="n">
+        <v>0.17</v>
+      </c>
       <c r="O44" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P44" s="23" t="inlineStr">
@@ -3311,9 +3307,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q44" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q44" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
         </is>
       </c>
     </row>
@@ -3323,41 +3319,41 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>10052540</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>26.91</v>
+        <v>106.56</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>150.87</v>
+        <v>282.43</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-123.96</v>
+        <v>-175.87</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-0.8220000000000001</v>
+        <v>-0.623</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>9864</v>
+        <v>2601</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>7.83</v>
+        <v>2.07</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K45" s="26" t="inlineStr"/>
+      <c r="K45" s="27" t="inlineStr"/>
       <c r="L45" s="12" t="inlineStr"/>
-      <c r="M45" s="26" t="inlineStr"/>
-      <c r="N45" s="27" t="inlineStr"/>
+      <c r="M45" s="27" t="inlineStr"/>
+      <c r="N45" s="28" t="inlineStr"/>
       <c r="O45" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3380,31 +3376,31 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>10041260</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>FR HUGGIES MAXIMA PROT MAX M 104UN</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>122.14</v>
+        <v>169.18</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-122.14</v>
+        <v>-169.18</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>30285</v>
+        <v>6348</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>24.05</v>
+        <v>5.04</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
@@ -3437,50 +3433,54 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10005850</t>
+          <t>100022385</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>SERTRALINA 100MG 30CP REV GEN PRATI (C1)</t>
+          <t>ENTRESTO 50MG 28CP REV NOVARTIS</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>39.9</v>
+        <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>160.57</v>
+        <v>165.6</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-120.67</v>
+        <v>-165.6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-0.752</v>
+        <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>9718</v>
+        <v>6572</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>7.72</v>
+        <v>5.22</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K47" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>202.11</v>
+      </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="N47" s="27" t="inlineStr"/>
+        <v>171.85</v>
+      </c>
+      <c r="N47" s="32" t="n">
+        <v>0.176</v>
+      </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
@@ -3488,9 +3488,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q47" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 171.85)</t>
         </is>
       </c>
     </row>
@@ -3500,54 +3500,50 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>100009772</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>FERINJECT 50MG/ML 1FR/AMP 10ML BLANVER</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>157.72</v>
+        <v>0</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>272.48</v>
+        <v>161.59</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-114.76</v>
+        <v>-161.59</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>-0.421</v>
+        <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>8909</v>
-      </c>
-      <c r="I48" s="22" t="n">
-        <v>7.08</v>
+        <v>510</v>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>0.41</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K48" s="18" t="n">
-        <v>108.49</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K48" s="30" t="inlineStr"/>
       <c r="L48" s="23" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M48" s="18" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N48" s="33" t="n">
-        <v>0.111</v>
-      </c>
+        <v>719.9</v>
+      </c>
+      <c r="N48" s="31" t="inlineStr"/>
       <c r="O48" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P48" s="23" t="inlineStr">
@@ -3555,9 +3551,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q48" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+      <c r="Q48" s="25" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3567,54 +3563,54 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10030120</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>RYBELSUS 7MG 30CP NOVO NORDISK</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0</v>
+        <v>203.97</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>114.74</v>
+        <v>364.41</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-114.74</v>
+        <v>-160.44</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-1</v>
+        <v>-0.44</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>1978</v>
+        <v>12853</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>1.57</v>
+        <v>10.21</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K49" s="7" t="n">
-        <v>1301.17</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="N49" s="13" t="n">
-        <v>0</v>
+        <v>61.06</v>
+      </c>
+      <c r="N49" s="32" t="n">
+        <v>0.113</v>
       </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
@@ -3622,9 +3618,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q49" s="14" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -3634,54 +3630,44 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>10032150</t>
+          <t>100011549</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>APTAMIL PROFUTURA GOLD 2 800G DANONE</t>
+          <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>0</v>
+        <v>118.19</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>113.1</v>
+        <v>273.77</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-113.1</v>
+        <v>-155.58</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>-1</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>6215</v>
+        <v>7665</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>4.94</v>
+        <v>6.09</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K50" s="18" t="n">
-        <v>131.99</v>
-      </c>
-      <c r="L50" s="23" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M50" s="18" t="n">
-        <v>109.9</v>
-      </c>
-      <c r="N50" s="33" t="n">
-        <v>0.201</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K50" s="30" t="inlineStr"/>
+      <c r="L50" s="23" t="inlineStr"/>
+      <c r="M50" s="30" t="inlineStr"/>
+      <c r="N50" s="31" t="inlineStr"/>
       <c r="O50" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P50" s="23" t="inlineStr">
@@ -3689,9 +3675,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q50" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 109.90)</t>
+      <c r="Q50" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3701,54 +3687,44 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10045969</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>FR HUGGIES MAXIMA PROT GIGA G 136UN</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>137.84</v>
+        <v>154.61</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-111.94</v>
+        <v>-154.61</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>22233</v>
+        <v>2650</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>17.66</v>
+        <v>2.1</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N51" s="32" t="n">
-        <v>0.629</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K51" s="27" t="inlineStr"/>
+      <c r="L51" s="12" t="inlineStr"/>
+      <c r="M51" s="27" t="inlineStr"/>
+      <c r="N51" s="28" t="inlineStr"/>
       <c r="O51" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P51" s="12" t="inlineStr">
@@ -3756,9 +3732,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+      <c r="Q51" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3768,50 +3744,54 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>10035030</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>APTANUTRI PREMIUM 3 800G 30% DESC 2UN DANONE</t>
+          <t>DEPOSTERON 200MG 3AMP SOL INJ SIGMA PHARMA (C5)</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>108.55</v>
+        <v>145.89</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-108.55</v>
+        <v>-145.89</v>
       </c>
       <c r="G52" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>3103</v>
+        <v>2975</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K52" s="30" t="inlineStr"/>
+      <c r="K52" s="18" t="n">
+        <v>107.25</v>
+      </c>
       <c r="L52" s="23" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M52" s="18" t="n">
-        <v>125.9</v>
-      </c>
-      <c r="N52" s="31" t="inlineStr"/>
+        <v>111.99</v>
+      </c>
+      <c r="N52" s="24" t="n">
+        <v>-0.042</v>
+      </c>
       <c r="O52" s="23" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P52" s="23" t="inlineStr">
@@ -3831,54 +3811,44 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>100001748</t>
+          <t>100008756</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>ELANI CICLO 3MG+30MCG 3X21CP REV LIBBS</t>
+          <t>LEITE NEOCATE LCP 400G DANONE</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>107.68</v>
+        <v>141.3</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-107.68</v>
+        <v>-141.3</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>4373</v>
-      </c>
-      <c r="I53" s="11" t="n">
-        <v>3.47</v>
+        <v>1484</v>
+      </c>
+      <c r="I53" s="26" t="n">
+        <v>1.18</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>113.72</v>
-      </c>
-      <c r="L53" s="12" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
-        <v>122.49</v>
-      </c>
-      <c r="N53" s="13" t="n">
-        <v>-0.07200000000000001</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K53" s="27" t="inlineStr"/>
+      <c r="L53" s="12" t="inlineStr"/>
+      <c r="M53" s="27" t="inlineStr"/>
+      <c r="N53" s="28" t="inlineStr"/>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
@@ -3888,7 +3858,7 @@
       </c>
       <c r="Q53" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3898,54 +3868,54 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>10047543</t>
+          <t>100003186</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>DULOXETINA 60MG 60CAP GEN EMS (C1)</t>
+          <t>NACTALI 75MG 84CP REV LIBBS</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>106.55</v>
+        <v>139.76</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-106.55</v>
+        <v>-139.76</v>
       </c>
       <c r="G54" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>9931</v>
+        <v>4585</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>7.89</v>
+        <v>3.64</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K54" s="18" t="n">
-        <v>162.69</v>
+        <v>94.72</v>
       </c>
       <c r="L54" s="23" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M54" s="18" t="n">
-        <v>154.99</v>
-      </c>
-      <c r="N54" s="33" t="n">
-        <v>0.05</v>
+        <v>99.90000000000001</v>
+      </c>
+      <c r="N54" s="24" t="n">
+        <v>-0.052</v>
       </c>
       <c r="O54" s="23" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P54" s="23" t="inlineStr">
@@ -3953,9 +3923,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q54" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Panvel R$ 154.99)</t>
+      <c r="Q54" s="25" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -237,7 +237,7 @@
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -270,20 +270,20 @@
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -291,13 +291,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +705,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 09:54:57 (09:54) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 10:53:49 (10:53) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -818,26 +812,26 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>8897.15</v>
+        <v>14706.01</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>15739.16</v>
+        <v>23578.47</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-6842.01</v>
+        <v>-8872.459999999999</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-0.435</v>
+        <v>-0.376</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>11192</v>
+        <v>113</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>8.890000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K5" s="7" t="n">
@@ -866,7 +860,7 @@
       </c>
       <c r="Q5" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -876,64 +870,54 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>10046652</t>
+          <t>10046657</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
+          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>4267.56</v>
+        <v>0</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>7374.48</v>
+        <v>2368.21</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-3106.92</v>
+        <v>-2368.21</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>-0.421</v>
+        <v>-1</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>9353</v>
+        <v>0</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>7.43</v>
+        <v>0</v>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>1905.6</v>
-      </c>
-      <c r="L6" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M6" s="18" t="n">
-        <v>1905.6</v>
-      </c>
-      <c r="N6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="23" t="inlineStr">
-        <is>
-          <t>Preço Alinhado</t>
-        </is>
-      </c>
-      <c r="P6" s="23" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr"/>
+      <c r="L6" s="24" t="inlineStr"/>
+      <c r="M6" s="23" t="inlineStr"/>
+      <c r="N6" s="25" t="inlineStr"/>
+      <c r="O6" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P6" s="24" t="inlineStr">
         <is>
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q6" s="25" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="Q6" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -943,31 +927,31 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10046657</t>
+          <t>10046656</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 15MG 4CAN APLIC LILLY</t>
+          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1580.83</v>
+        <v>1578.81</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-1580.83</v>
+        <v>-1578.81</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>1048</v>
-      </c>
-      <c r="I7" s="26" t="n">
-        <v>0.83</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -1009,32 +993,32 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>0</v>
+        <v>1208</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>1413.28</v>
+        <v>2117.21</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-1413.28</v>
+        <v>-909.21</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>-1</v>
+        <v>-0.429</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>9409</v>
+        <v>127</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>7.47</v>
+        <v>0.1</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K8" s="18" t="n">
         <v>988.22</v>
       </c>
-      <c r="L8" s="23" t="inlineStr">
+      <c r="L8" s="24" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
@@ -1042,22 +1026,22 @@
       <c r="M8" s="18" t="n">
         <v>988.22</v>
       </c>
-      <c r="N8" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="23" t="inlineStr">
+      <c r="N8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>Preço Alinhado</t>
         </is>
       </c>
-      <c r="P8" s="23" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q8" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="P8" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q8" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1067,64 +1051,64 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10050654</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 2,4MG 3ML EUROFARMA</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0</v>
+        <v>399.6</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1268.77</v>
+        <v>1063.38</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1268.77</v>
+        <v>-663.78</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-1</v>
+        <v>-0.624</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>4038</v>
+        <v>9</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>3.21</v>
+        <v>0.01</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1617.66</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M9" s="7" t="n">
-        <v>1617.66</v>
-      </c>
-      <c r="N9" s="13" t="n">
-        <v>0</v>
+        <v>46.85</v>
+      </c>
+      <c r="N9" s="30" t="n">
+        <v>1.132</v>
       </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q9" s="14" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -1134,52 +1118,52 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>10046656</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>MOUNJARO 12,5MG 4CAN APLIC LILLY</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D10" s="18" t="n">
-        <v>0</v>
+        <v>169.8</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>1053.89</v>
+        <v>771.42</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-1053.89</v>
+        <v>-601.62</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-1</v>
+        <v>-0.78</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>494</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>0.39</v>
+        <v>262</v>
+      </c>
+      <c r="I10" s="22" t="n">
+        <v>0.21</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K10" s="30" t="inlineStr"/>
-      <c r="L10" s="23" t="inlineStr"/>
-      <c r="M10" s="30" t="inlineStr"/>
-      <c r="N10" s="31" t="inlineStr"/>
-      <c r="O10" s="23" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr"/>
+      <c r="L10" s="24" t="inlineStr"/>
+      <c r="M10" s="23" t="inlineStr"/>
+      <c r="N10" s="25" t="inlineStr"/>
+      <c r="O10" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="P10" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q10" s="26" t="inlineStr">
         <is>
           <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
@@ -1191,40 +1175,46 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10053130</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>OZIVY 1MG 1CAN 3ML EMS</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1463.81</v>
+        <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2226.16</v>
+        <v>583.14</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-762.35</v>
+        <v>-583.14</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.342</v>
+        <v>-1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>10582</v>
+        <v>15</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>8.41</v>
+        <v>0.01</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K11" s="27" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr"/>
-      <c r="M11" s="27" t="inlineStr"/>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>50.25</v>
+      </c>
       <c r="N11" s="28" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr">
         <is>
@@ -1238,7 +1228,7 @@
       </c>
       <c r="Q11" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1248,64 +1238,54 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>10030119</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>0</v>
+        <v>105.9</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>689.22</v>
+        <v>686.05</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-689.22</v>
+        <v>-580.15</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>-1</v>
+        <v>-0.846</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>2858</v>
+        <v>6</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="L12" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M12" s="18" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="N12" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="23" t="inlineStr">
-        <is>
-          <t>Preço Alinhado</t>
-        </is>
-      </c>
-      <c r="P12" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q12" s="25" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr"/>
+      <c r="L12" s="24" t="inlineStr"/>
+      <c r="M12" s="23" t="inlineStr"/>
+      <c r="N12" s="25" t="inlineStr"/>
+      <c r="O12" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P12" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q12" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1315,54 +1295,44 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10042968</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC JUMBO XG 116UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1445.73</v>
+        <v>563.62</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2053.96</v>
+        <v>1130.11</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-608.23</v>
+        <v>-566.49</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.296</v>
+        <v>-0.501</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>5925</v>
+        <v>901</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>4.71</v>
+        <v>0.72</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="N13" s="32" t="n">
-        <v>0.067</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K13" s="27" t="inlineStr"/>
+      <c r="L13" s="12" t="inlineStr"/>
+      <c r="M13" s="27" t="inlineStr"/>
+      <c r="N13" s="28" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
@@ -1370,9 +1340,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Panvel R$ 149.90)</t>
+      <c r="Q13" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1382,54 +1352,64 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>221.25</v>
+        <v>157.72</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>754.38</v>
+        <v>703.29</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-533.13</v>
+        <v>-545.5700000000001</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>-0.7070000000000001</v>
+        <v>-0.7759999999999999</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>8275</v>
+        <v>88</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>6.57</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K14" s="30" t="inlineStr"/>
-      <c r="L14" s="23" t="inlineStr"/>
-      <c r="M14" s="30" t="inlineStr"/>
-      <c r="N14" s="31" t="inlineStr"/>
-      <c r="O14" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q14" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>108.49</v>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="N14" s="31" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="O14" s="24" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P14" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q14" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -1439,35 +1419,35 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0</v>
+        <v>105.9</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>514.9400000000001</v>
+        <v>611.38</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-514.9400000000001</v>
+        <v>-505.48</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-1</v>
+        <v>-0.8270000000000001</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>26223</v>
+        <v>11</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>20.83</v>
+        <v>0.01</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K15" s="27" t="inlineStr"/>
@@ -1486,7 +1466,7 @@
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1496,62 +1476,52 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>10040801</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1,7MG 3ML NOVO NORDISK</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>0</v>
+        <v>221.97</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>480.99</v>
+        <v>681.9</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-480.99</v>
+        <v>-459.93</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>-1</v>
+        <v>-0.674</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>1758</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <v>1.4</v>
+        <v>758</v>
+      </c>
+      <c r="I16" s="22" t="n">
+        <v>0.6</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K16" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="L16" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M16" s="18" t="n">
-        <v>1945.09</v>
-      </c>
-      <c r="N16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="23" t="inlineStr">
-        <is>
-          <t>Preço Alinhado</t>
-        </is>
-      </c>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q16" s="25" t="inlineStr">
+      <c r="K16" s="23" t="inlineStr"/>
+      <c r="L16" s="24" t="inlineStr"/>
+      <c r="M16" s="23" t="inlineStr"/>
+      <c r="N16" s="25" t="inlineStr"/>
+      <c r="O16" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P16" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q16" s="26" t="inlineStr">
         <is>
           <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
@@ -1563,54 +1533,50 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10051359</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>479.17</v>
+        <v>446.84</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-479.17</v>
+        <v>-446.84</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>962</v>
-      </c>
-      <c r="I17" s="26" t="n">
-        <v>0.76</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K17" s="7" t="n">
-        <v>309</v>
-      </c>
+      <c r="K17" s="27" t="inlineStr"/>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
-        <v>449</v>
-      </c>
-      <c r="N17" s="13" t="n">
-        <v>-0.312</v>
-      </c>
+        <v>1212.9</v>
+      </c>
+      <c r="N17" s="28" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
@@ -1630,64 +1596,60 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>10050640</t>
+          <t>10093877</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
+          <t>MIRENA 52MG 1END+INS BAYER</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>473.88</v>
+        <v>446.34</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>-473.88</v>
+        <v>-446.34</v>
       </c>
       <c r="G18" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>6179</v>
+        <v>20</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>4.91</v>
+        <v>0.02</v>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="L18" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr"/>
+      <c r="L18" s="24" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M18" s="18" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="N18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="23" t="inlineStr">
-        <is>
-          <t>Preço Alinhado</t>
-        </is>
-      </c>
-      <c r="P18" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q18" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+        <v>1225.89</v>
+      </c>
+      <c r="N18" s="25" t="inlineStr"/>
+      <c r="O18" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P18" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q18" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1697,44 +1659,54 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10050653</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>457.95</v>
+        <v>426.98</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-457.95</v>
+        <v>-426.98</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>3146</v>
+        <v>4</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K19" s="27" t="inlineStr"/>
-      <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="27" t="inlineStr"/>
-      <c r="N19" s="28" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>1347.91</v>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>1347.89</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P19" s="12" t="inlineStr">
@@ -1744,7 +1716,7 @@
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1754,64 +1726,64 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>299.7</v>
+        <v>295</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>709.83</v>
+        <v>709.91</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-410.13</v>
+        <v>-414.91</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>-0.578</v>
+        <v>-0.584</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>2446</v>
+        <v>27</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>1.94</v>
+        <v>0.02</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K20" s="18" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="L20" s="23" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
+        <v>831.76</v>
+      </c>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M20" s="18" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N20" s="33" t="n">
-        <v>1.132</v>
-      </c>
-      <c r="O20" s="23" t="inlineStr">
-        <is>
-          <t>São João Mais Cara</t>
-        </is>
-      </c>
-      <c r="P20" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q20" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+        <v>831.76</v>
+      </c>
+      <c r="N20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="24" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P20" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q20" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1821,54 +1793,54 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10024521</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>400.71</v>
+        <v>411.99</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-400.71</v>
+        <v>-411.99</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>3992</v>
+        <v>0</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>149.4</v>
+        <v>799.9</v>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="N21" s="32" t="n">
-        <v>0.396</v>
+        <v>814.9</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>-0.018</v>
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
@@ -1876,9 +1848,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+      <c r="Q21" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1888,60 +1860,64 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10041248</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>CREATINA MONOHIDRATADA 300G DUX</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>0</v>
+        <v>231.09</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>389.26</v>
+        <v>630.01</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-389.26</v>
+        <v>-398.92</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>-1</v>
+        <v>-0.633</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>4427</v>
+        <v>9</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>3.52</v>
+        <v>0.01</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K22" s="30" t="inlineStr"/>
-      <c r="L22" s="23" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>315.46</v>
+      </c>
+      <c r="L22" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M22" s="18" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="N22" s="31" t="inlineStr"/>
-      <c r="O22" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P22" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q22" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+        <v>236.6</v>
+      </c>
+      <c r="N22" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O22" s="24" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P22" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -1960,26 +1936,26 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0</v>
+        <v>185.7</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>381.09</v>
+        <v>570.9</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-381.09</v>
+        <v>-385.2</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-1</v>
+        <v>-0.675</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>4815</v>
+        <v>13</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>3.82</v>
+        <v>0.01</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K23" s="7" t="n">
@@ -1993,7 +1969,7 @@
       <c r="M23" s="7" t="n">
         <v>49.9</v>
       </c>
-      <c r="N23" s="32" t="n">
+      <c r="N23" s="30" t="n">
         <v>0.904</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
@@ -2008,7 +1984,7 @@
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+          <t>Reprecificar e Remanejar (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -2018,64 +1994,54 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10053171</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>157.72</v>
+        <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>469.46</v>
+        <v>383.05</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-311.74</v>
+        <v>-383.05</v>
       </c>
       <c r="G24" s="20" t="n">
-        <v>-0.664</v>
+        <v>-1</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>8909</v>
+        <v>13</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>7.08</v>
+        <v>0.01</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K24" s="18" t="n">
-        <v>108.49</v>
-      </c>
-      <c r="L24" s="23" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N24" s="33" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="O24" s="23" t="inlineStr">
-        <is>
-          <t>São João Mais Cara</t>
-        </is>
-      </c>
-      <c r="P24" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q24" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr"/>
+      <c r="L24" s="24" t="inlineStr"/>
+      <c r="M24" s="23" t="inlineStr"/>
+      <c r="N24" s="25" t="inlineStr"/>
+      <c r="O24" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P24" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q24" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2085,44 +2051,54 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10025745</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>311.26</v>
+        <v>379.63</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-311.26</v>
+        <v>-379.63</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>11106</v>
+        <v>0</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>8.82</v>
+        <v>0</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K25" s="27" t="inlineStr"/>
-      <c r="L25" s="12" t="inlineStr"/>
-      <c r="M25" s="27" t="inlineStr"/>
-      <c r="N25" s="28" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>1105.6</v>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>1170.01</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>-0.055</v>
+      </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr">
@@ -2132,7 +2108,7 @@
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2142,52 +2118,52 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>105.9</v>
+        <v>0</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>408.11</v>
+        <v>369.4</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-302.21</v>
+        <v>-369.4</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>-0.741</v>
+        <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>1270</v>
-      </c>
-      <c r="I26" s="29" t="n">
-        <v>1.01</v>
+        <v>84</v>
+      </c>
+      <c r="I26" s="22" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K26" s="30" t="inlineStr"/>
-      <c r="L26" s="23" t="inlineStr"/>
-      <c r="M26" s="30" t="inlineStr"/>
-      <c r="N26" s="31" t="inlineStr"/>
-      <c r="O26" s="23" t="inlineStr">
+      <c r="K26" s="23" t="inlineStr"/>
+      <c r="L26" s="24" t="inlineStr"/>
+      <c r="M26" s="23" t="inlineStr"/>
+      <c r="N26" s="25" t="inlineStr"/>
+      <c r="O26" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P26" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q26" s="25" t="inlineStr">
+      <c r="P26" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q26" s="26" t="inlineStr">
         <is>
           <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
@@ -2199,31 +2175,31 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10025098</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0</v>
+        <v>56.81</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>298.28</v>
+        <v>389.4</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-298.28</v>
+        <v>-332.59</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-1</v>
+        <v>-0.8540000000000001</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>204</v>
-      </c>
-      <c r="I27" s="26" t="n">
-        <v>0.16</v>
+        <v>650</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>0.52</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2231,14 +2207,8 @@
         </is>
       </c>
       <c r="K27" s="27" t="inlineStr"/>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>1212.9</v>
-      </c>
+      <c r="L27" s="12" t="inlineStr"/>
+      <c r="M27" s="27" t="inlineStr"/>
       <c r="N27" s="28" t="inlineStr"/>
       <c r="O27" s="12" t="inlineStr">
         <is>
@@ -2262,60 +2232,64 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>10093877</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>MIRENA 52MG 1END+INS BAYER</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>297.94</v>
+        <v>355.76</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-297.94</v>
+        <v>-329.86</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>-1</v>
+        <v>-0.927</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>501</v>
-      </c>
-      <c r="I28" s="29" t="n">
-        <v>0.4</v>
+        <v>241</v>
+      </c>
+      <c r="I28" s="22" t="n">
+        <v>0.19</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K28" s="30" t="inlineStr"/>
-      <c r="L28" s="23" t="inlineStr">
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K28" s="18" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L28" s="24" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
       <c r="M28" s="18" t="n">
-        <v>1225.89</v>
-      </c>
-      <c r="N28" s="31" t="inlineStr"/>
-      <c r="O28" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P28" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q28" s="25" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+        <v>15.9</v>
+      </c>
+      <c r="N28" s="31" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="O28" s="24" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P28" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q28" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -2325,54 +2299,44 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10050653</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>285.02</v>
+        <v>315.24</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-285.02</v>
+        <v>-315.24</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>2647</v>
+        <v>304</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>2.1</v>
+        <v>0.24</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>1347.91</v>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>1347.89</v>
-      </c>
-      <c r="N29" s="13" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K29" s="27" t="inlineStr"/>
+      <c r="L29" s="12" t="inlineStr"/>
+      <c r="M29" s="27" t="inlineStr"/>
+      <c r="N29" s="28" t="inlineStr"/>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
@@ -2382,7 +2346,7 @@
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2392,62 +2356,52 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10024521</t>
+          <t>10028321</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
+          <t>PREGABALINA 150MG 30CAP GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
-        <v>0</v>
+        <v>67.62</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>275.01</v>
+        <v>382.17</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-275.01</v>
+        <v>-314.55</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>-1</v>
+        <v>-0.823</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>575</v>
-      </c>
-      <c r="I30" s="29" t="n">
-        <v>0.46</v>
+        <v>4</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K30" s="18" t="n">
-        <v>799.9</v>
-      </c>
-      <c r="L30" s="23" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M30" s="18" t="n">
-        <v>814.9</v>
-      </c>
-      <c r="N30" s="24" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="O30" s="23" t="inlineStr">
-        <is>
-          <t>Líder de Preço</t>
-        </is>
-      </c>
-      <c r="P30" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q30" s="25" t="inlineStr">
+      <c r="K30" s="23" t="inlineStr"/>
+      <c r="L30" s="24" t="inlineStr"/>
+      <c r="M30" s="23" t="inlineStr"/>
+      <c r="N30" s="25" t="inlineStr"/>
+      <c r="O30" s="24" t="inlineStr">
+        <is>
+          <t>Não Monitorado</t>
+        </is>
+      </c>
+      <c r="P30" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q30" s="26" t="inlineStr">
         <is>
           <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
@@ -2459,31 +2413,31 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10053171</t>
+          <t>10035030</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
+          <t>APTANUTRI PREMIUM 3 800G 30% DESC 2UN DANONE</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>255.69</v>
+        <v>280.17</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-255.69</v>
+        <v>-280.17</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>1454</v>
-      </c>
-      <c r="I31" s="26" t="n">
-        <v>1.15</v>
+        <v>6</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -2491,8 +2445,14 @@
         </is>
       </c>
       <c r="K31" s="27" t="inlineStr"/>
-      <c r="L31" s="12" t="inlineStr"/>
-      <c r="M31" s="27" t="inlineStr"/>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>125.9</v>
+      </c>
       <c r="N31" s="28" t="inlineStr"/>
       <c r="O31" s="12" t="inlineStr">
         <is>
@@ -2516,64 +2476,64 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10025745</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
-        <v>0</v>
+        <v>271.96</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>253.41</v>
+        <v>545.92</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-253.41</v>
+        <v>-273.96</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>-1</v>
+        <v>-0.502</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>122</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>0.1</v>
+        <v>254</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>0.2</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K32" s="18" t="n">
-        <v>1105.6</v>
-      </c>
-      <c r="L32" s="23" t="inlineStr">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="L32" s="24" t="inlineStr">
         <is>
           <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M32" s="18" t="n">
-        <v>1170.01</v>
-      </c>
-      <c r="N32" s="24" t="n">
-        <v>-0.055</v>
-      </c>
-      <c r="O32" s="23" t="inlineStr">
-        <is>
-          <t>Líder de Preço</t>
-        </is>
-      </c>
-      <c r="P32" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q32" s="25" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+        <v>61.06</v>
+      </c>
+      <c r="N32" s="31" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="O32" s="24" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P32" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -2583,35 +2543,35 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10053166</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>OZIVY 1MG 2CAN 3ML EMS</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>246.58</v>
+        <v>273.6</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-246.58</v>
+        <v>-273.6</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>11806</v>
+        <v>4</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K33" s="27" t="inlineStr"/>
@@ -2630,7 +2590,7 @@
       </c>
       <c r="Q33" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2640,54 +2600,64 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>100022270</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>221.97</v>
+        <v>0</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>455.18</v>
+        <v>268.37</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-233.21</v>
+        <v>-268.37</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>-0.512</v>
+        <v>-1</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>39477</v>
+        <v>5</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>31.36</v>
+        <v>0</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K34" s="30" t="inlineStr"/>
-      <c r="L34" s="23" t="inlineStr"/>
-      <c r="M34" s="30" t="inlineStr"/>
-      <c r="N34" s="31" t="inlineStr"/>
-      <c r="O34" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P34" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q34" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K34" s="18" t="n">
+        <v>185.61</v>
+      </c>
+      <c r="L34" s="24" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M34" s="18" t="n">
+        <v>158.66</v>
+      </c>
+      <c r="N34" s="31" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="O34" s="24" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P34" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Farmaciasnissei R$ 158.66)</t>
         </is>
       </c>
     </row>
@@ -2697,44 +2667,54 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>10046652</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>26.91</v>
+        <v>10785.12</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>259.93</v>
+        <v>11047.54</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-233.02</v>
+        <v>-262.42</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-0.8959999999999999</v>
+        <v>-0.024</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>9864</v>
+        <v>144</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>7.83</v>
+        <v>0.11</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K35" s="27" t="inlineStr"/>
-      <c r="L35" s="12" t="inlineStr"/>
-      <c r="M35" s="27" t="inlineStr"/>
-      <c r="N35" s="28" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>1905.6</v>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>1905.6</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
@@ -2744,7 +2724,7 @@
       </c>
       <c r="Q35" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2754,54 +2734,64 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>10028321</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>PREGABALINA 150MG 30CAP GEN EMS (C1)</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
-        <v>31.63</v>
+        <v>345.3</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>255.11</v>
+        <v>600.3</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-223.48</v>
+        <v>-255</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>-0.8759999999999999</v>
+        <v>-0.425</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>5385</v>
+        <v>37</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>4.28</v>
+        <v>0.03</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K36" s="30" t="inlineStr"/>
-      <c r="L36" s="23" t="inlineStr"/>
-      <c r="M36" s="30" t="inlineStr"/>
-      <c r="N36" s="31" t="inlineStr"/>
-      <c r="O36" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P36" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q36" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L36" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M36" s="18" t="n">
+        <v>107</v>
+      </c>
+      <c r="N36" s="31" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="O36" s="24" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P36" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -2811,54 +2801,44 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>25.9</v>
+        <v>463.6</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>237.48</v>
+        <v>715.26</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-211.58</v>
+        <v>-251.66</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.8909999999999999</v>
+        <v>-0.352</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>22233</v>
+        <v>502</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>17.66</v>
+        <v>0.4</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N37" s="32" t="n">
-        <v>0.629</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K37" s="27" t="inlineStr"/>
+      <c r="L37" s="12" t="inlineStr"/>
+      <c r="M37" s="27" t="inlineStr"/>
+      <c r="N37" s="28" t="inlineStr"/>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
@@ -2866,9 +2846,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+      <c r="Q37" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2878,54 +2858,60 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>100009772</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>FERINJECT 50MG/ML 1FR/AMP 10ML BLANVER</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>210.43</v>
+        <v>242.07</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-210.43</v>
+        <v>-242.07</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>30285</v>
+        <v>6</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>24.05</v>
+        <v>0</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K38" s="30" t="inlineStr"/>
-      <c r="L38" s="23" t="inlineStr"/>
-      <c r="M38" s="30" t="inlineStr"/>
-      <c r="N38" s="31" t="inlineStr"/>
-      <c r="O38" s="23" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr"/>
+      <c r="L38" s="24" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M38" s="18" t="n">
+        <v>719.9</v>
+      </c>
+      <c r="N38" s="25" t="inlineStr"/>
+      <c r="O38" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P38" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q38" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="P38" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q38" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2935,54 +2921,44 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10030120</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>RYBELSUS 7MG 30CP NOVO NORDISK</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0</v>
+        <v>231.8</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>197.69</v>
+        <v>466.29</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-197.69</v>
+        <v>-234.49</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-1</v>
+        <v>-0.503</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>1978</v>
+        <v>165</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>1.57</v>
+        <v>0.13</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="L39" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="n">
-        <v>1301.17</v>
-      </c>
-      <c r="N39" s="13" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K39" s="27" t="inlineStr"/>
+      <c r="L39" s="12" t="inlineStr"/>
+      <c r="M39" s="27" t="inlineStr"/>
+      <c r="N39" s="28" t="inlineStr"/>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
@@ -2992,7 +2968,7 @@
       </c>
       <c r="Q39" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3002,60 +2978,54 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>10005850</t>
+          <t>10045969</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>SERTRALINA 100MG 30CP REV GEN PRATI (C1)</t>
+          <t>FR HUGGIES MAXIMA PROT GIGA G 136UN</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>79.8</v>
+        <v>0</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>276.64</v>
+        <v>231.62</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-196.84</v>
+        <v>-231.62</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>-0.7120000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>9718</v>
+        <v>7</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>7.72</v>
+        <v>0.01</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K40" s="30" t="inlineStr"/>
-      <c r="L40" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M40" s="18" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="N40" s="31" t="inlineStr"/>
-      <c r="O40" s="23" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr"/>
+      <c r="L40" s="24" t="inlineStr"/>
+      <c r="M40" s="23" t="inlineStr"/>
+      <c r="N40" s="25" t="inlineStr"/>
+      <c r="O40" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P40" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q40" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="P40" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q40" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3065,54 +3035,50 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10044745</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>231.09</v>
+        <v>91.09</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>420.55</v>
+        <v>320.16</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-189.46</v>
+        <v>-229.07</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-0.45</v>
+        <v>-0.715</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>837</v>
-      </c>
-      <c r="I41" s="26" t="n">
-        <v>0.66</v>
+        <v>95</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>0.08</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>315.46</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K41" s="27" t="inlineStr"/>
       <c r="L41" s="12" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N41" s="32" t="n">
-        <v>0.333</v>
-      </c>
+        <v>83.92</v>
+      </c>
+      <c r="N41" s="28" t="inlineStr"/>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
@@ -3120,9 +3086,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+      <c r="Q41" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3132,60 +3098,54 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>10035030</t>
+          <t>100008756</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>APTANUTRI PREMIUM 3 800G 30% DESC 2UN DANONE</t>
+          <t>LEITE NEOCATE LCP 400G DANONE</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>187.02</v>
+        <v>211.68</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-187.02</v>
+        <v>-211.68</v>
       </c>
       <c r="G42" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>3103</v>
+        <v>2</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K42" s="30" t="inlineStr"/>
-      <c r="L42" s="23" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M42" s="18" t="n">
-        <v>125.9</v>
-      </c>
-      <c r="N42" s="31" t="inlineStr"/>
-      <c r="O42" s="23" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr"/>
+      <c r="L42" s="24" t="inlineStr"/>
+      <c r="M42" s="23" t="inlineStr"/>
+      <c r="N42" s="25" t="inlineStr"/>
+      <c r="O42" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P42" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q42" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="P42" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q42" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3195,44 +3155,54 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10053166</t>
+          <t>100003186</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>OZIVY 1MG 2CAN 3ML EMS</t>
+          <t>NACTALI 75MG 84CP REV LIBBS</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>182.64</v>
+        <v>209.37</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-182.64</v>
+        <v>-209.37</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>2941</v>
+        <v>51</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>2.34</v>
+        <v>0.04</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K43" s="27" t="inlineStr"/>
-      <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="27" t="inlineStr"/>
-      <c r="N43" s="28" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>94.72</v>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>-0.052</v>
+      </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
@@ -3242,7 +3212,7 @@
       </c>
       <c r="Q43" s="14" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3252,64 +3222,64 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>100022270</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>179.14</v>
+        <v>1200.59</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-179.14</v>
+        <v>-201.59</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>-1</v>
+        <v>-0.168</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>1962</v>
+        <v>9</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>1.56</v>
+        <v>0.01</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K44" s="18" t="n">
-        <v>185.61</v>
-      </c>
-      <c r="L44" s="23" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
+        <v>1298.54</v>
+      </c>
+      <c r="L44" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M44" s="18" t="n">
-        <v>158.66</v>
-      </c>
-      <c r="N44" s="33" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="O44" s="23" t="inlineStr">
-        <is>
-          <t>São João Mais Cara</t>
-        </is>
-      </c>
-      <c r="P44" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q44" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
+        <v>1298.54</v>
+      </c>
+      <c r="N44" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="24" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P44" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q44" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3319,35 +3289,35 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10052540</t>
+          <t>10044679</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
+          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>106.56</v>
+        <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>282.43</v>
+        <v>195.75</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-175.87</v>
+        <v>-195.75</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-0.623</v>
+        <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>2601</v>
+        <v>0</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K45" s="27" t="inlineStr"/>
@@ -3366,7 +3336,7 @@
       </c>
       <c r="Q45" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3376,54 +3346,54 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10041260</t>
+          <t>10041082</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT MAX M 104UN</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>169.18</v>
+        <v>192.39</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-169.18</v>
+        <v>-192.39</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>6348</v>
+        <v>28</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>5.04</v>
+        <v>0.02</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K46" s="30" t="inlineStr"/>
-      <c r="L46" s="23" t="inlineStr"/>
-      <c r="M46" s="30" t="inlineStr"/>
-      <c r="N46" s="31" t="inlineStr"/>
-      <c r="O46" s="23" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="inlineStr"/>
+      <c r="L46" s="24" t="inlineStr"/>
+      <c r="M46" s="23" t="inlineStr"/>
+      <c r="N46" s="25" t="inlineStr"/>
+      <c r="O46" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P46" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q46" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="P46" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q46" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3433,50 +3403,50 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>100022385</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>ENTRESTO 50MG 28CP REV NOVARTIS</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0</v>
+        <v>436.63</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>165.6</v>
+        <v>614.05</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-165.6</v>
+        <v>-177.42</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-1</v>
+        <v>-0.289</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>6572</v>
+        <v>706</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>5.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K47" s="7" t="n">
-        <v>202.11</v>
+        <v>74.22</v>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>171.85</v>
-      </c>
-      <c r="N47" s="32" t="n">
-        <v>0.176</v>
+        <v>55.67</v>
+      </c>
+      <c r="N47" s="30" t="n">
+        <v>0.333</v>
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
@@ -3490,7 +3460,7 @@
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 171.85)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -3500,58 +3470,62 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>100009772</t>
+          <t>10038798</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>FERINJECT 50MG/ML 1FR/AMP 10ML BLANVER</t>
+          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>161.59</v>
+        <v>172.84</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-161.59</v>
+        <v>-172.84</v>
       </c>
       <c r="G48" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>510</v>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>0.41</v>
+        <v>6</v>
+      </c>
+      <c r="I48" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K48" s="30" t="inlineStr"/>
-      <c r="L48" s="23" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
+      <c r="K48" s="18" t="n">
+        <v>180.79</v>
+      </c>
+      <c r="L48" s="24" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M48" s="18" t="n">
-        <v>719.9</v>
-      </c>
-      <c r="N48" s="31" t="inlineStr"/>
-      <c r="O48" s="23" t="inlineStr">
-        <is>
-          <t>Não Monitorado</t>
-        </is>
-      </c>
-      <c r="P48" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q48" s="25" t="inlineStr">
+        <v>175.9</v>
+      </c>
+      <c r="N48" s="31" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="O48" s="24" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P48" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q48" s="26" t="inlineStr">
         <is>
           <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
@@ -3563,54 +3537,54 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10040748</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>203.97</v>
+        <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>364.41</v>
+        <v>167.39</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-160.44</v>
+        <v>-167.39</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-0.44</v>
+        <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>12853</v>
+        <v>0</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>10.21</v>
+        <v>0</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K49" s="7" t="n">
-        <v>67.98999999999999</v>
+        <v>1298.54</v>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N49" s="32" t="n">
-        <v>0.113</v>
+        <v>1298.54</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
@@ -3618,9 +3592,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+      <c r="Q49" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3630,54 +3604,54 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>100011549</t>
+          <t>10049066</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
+          <t>KIT DOVE SH 350+COND 175ML HIDRATACAO+HIALURON VIT</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>118.19</v>
+        <v>25.83</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>273.77</v>
+        <v>186.77</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-155.58</v>
+        <v>-160.94</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.862</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>7665</v>
+        <v>802</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>6.09</v>
+        <v>0.64</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K50" s="30" t="inlineStr"/>
-      <c r="L50" s="23" t="inlineStr"/>
-      <c r="M50" s="30" t="inlineStr"/>
-      <c r="N50" s="31" t="inlineStr"/>
-      <c r="O50" s="23" t="inlineStr">
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="inlineStr"/>
+      <c r="L50" s="24" t="inlineStr"/>
+      <c r="M50" s="23" t="inlineStr"/>
+      <c r="N50" s="25" t="inlineStr"/>
+      <c r="O50" s="24" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
         </is>
       </c>
-      <c r="P50" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q50" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="P50" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q50" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3687,35 +3661,35 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10045969</t>
+          <t>100011549</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT GIGA G 136UN</t>
+          <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0</v>
+        <v>250.68</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>154.61</v>
+        <v>410.13</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-154.61</v>
+        <v>-159.45</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-1</v>
+        <v>-0.389</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>2650</v>
+        <v>115</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>2.1</v>
+        <v>0.09</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K51" s="27" t="inlineStr"/>
@@ -3734,7 +3708,7 @@
       </c>
       <c r="Q51" s="14" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3744,64 +3718,64 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>10097311</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>DEPOSTERON 200MG 3AMP SOL INJ SIGMA PHARMA (C5)</t>
+          <t>NESTOGENO 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>0</v>
+        <v>263.99</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>145.89</v>
+        <v>422.28</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-145.89</v>
+        <v>-158.29</v>
       </c>
       <c r="G52" s="20" t="n">
-        <v>-1</v>
+        <v>-0.375</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>2975</v>
+        <v>209</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>2.36</v>
+        <v>0.17</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K52" s="18" t="n">
-        <v>107.25</v>
-      </c>
-      <c r="L52" s="23" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
+        <v>67.98999999999999</v>
+      </c>
+      <c r="L52" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M52" s="18" t="n">
-        <v>111.99</v>
-      </c>
-      <c r="N52" s="24" t="n">
-        <v>-0.042</v>
-      </c>
-      <c r="O52" s="23" t="inlineStr">
-        <is>
-          <t>Líder de Preço</t>
-        </is>
-      </c>
-      <c r="P52" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q52" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+        <v>62.9</v>
+      </c>
+      <c r="N52" s="31" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="O52" s="24" t="inlineStr">
+        <is>
+          <t>São João Mais Cara</t>
+        </is>
+      </c>
+      <c r="P52" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 62.90)</t>
         </is>
       </c>
     </row>
@@ -3811,44 +3785,54 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>100008756</t>
+          <t>100011551</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>LEITE NEOCATE LCP 400G DANONE</t>
+          <t>ANDROGEL 50MG 10MG/G GEL 30ENV 5G</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>141.3</v>
+        <v>156.98</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-141.3</v>
+        <v>-156.98</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>1484</v>
-      </c>
-      <c r="I53" s="26" t="n">
-        <v>1.18</v>
+        <v>2</v>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K53" s="27" t="inlineStr"/>
-      <c r="L53" s="12" t="inlineStr"/>
-      <c r="M53" s="27" t="inlineStr"/>
-      <c r="N53" s="28" t="inlineStr"/>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>301.16</v>
+      </c>
+      <c r="N53" s="30" t="n">
+        <v>0.141</v>
+      </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
@@ -3856,9 +3840,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q53" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Farmaciasnissei R$ 301.16)</t>
         </is>
       </c>
     </row>
@@ -3868,101 +3852,101 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>100003186</t>
+          <t>10040738</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>NACTALI 75MG 84CP REV LIBBS</t>
+          <t>LYBERDIA 40MG 50ML GOTAS EMS (A3)</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>139.76</v>
+        <v>155.76</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-139.76</v>
+        <v>-155.76</v>
       </c>
       <c r="G54" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>4585</v>
+        <v>24</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>3.64</v>
+        <v>0.02</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K54" s="18" t="n">
-        <v>94.72</v>
-      </c>
-      <c r="L54" s="23" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
+        <v>567.02</v>
+      </c>
+      <c r="L54" s="24" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M54" s="18" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="N54" s="24" t="n">
-        <v>-0.052</v>
-      </c>
-      <c r="O54" s="23" t="inlineStr">
-        <is>
-          <t>Líder de Preço</t>
-        </is>
-      </c>
-      <c r="P54" s="23" t="inlineStr">
-        <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q54" s="25" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+        <v>567.02</v>
+      </c>
+      <c r="N54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="24" t="inlineStr">
+        <is>
+          <t>Preço Alinhado</t>
+        </is>
+      </c>
+      <c r="P54" s="24" t="inlineStr">
+        <is>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q54" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="34" t="inlineStr">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t>TOTAL TOP 50</t>
         </is>
       </c>
-      <c r="B55" s="35" t="n"/>
-      <c r="C55" s="35" t="n"/>
-      <c r="D55" s="36">
+      <c r="B55" s="33" t="n"/>
+      <c r="C55" s="33" t="n"/>
+      <c r="D55" s="34">
         <f>SUM(D5:D54)</f>
         <v/>
       </c>
-      <c r="E55" s="36">
+      <c r="E55" s="34">
         <f>SUM(E5:E54)</f>
         <v/>
       </c>
-      <c r="F55" s="37">
+      <c r="F55" s="35">
         <f>SUM(F5:F54)</f>
         <v/>
       </c>
-      <c r="G55" s="38">
+      <c r="G55" s="36">
         <f>(D55-E55)/E55</f>
         <v/>
       </c>
-      <c r="H55" s="39" t="n"/>
-      <c r="I55" s="39" t="inlineStr"/>
-      <c r="J55" s="39" t="inlineStr"/>
-      <c r="K55" s="39" t="inlineStr"/>
-      <c r="L55" s="39" t="inlineStr"/>
-      <c r="M55" s="39" t="inlineStr"/>
-      <c r="N55" s="39" t="inlineStr"/>
-      <c r="O55" s="39" t="inlineStr"/>
-      <c r="P55" s="39" t="inlineStr"/>
-      <c r="Q55" s="39" t="inlineStr"/>
+      <c r="H55" s="37" t="n"/>
+      <c r="I55" s="37" t="inlineStr"/>
+      <c r="J55" s="37" t="inlineStr"/>
+      <c r="K55" s="37" t="inlineStr"/>
+      <c r="L55" s="37" t="inlineStr"/>
+      <c r="M55" s="37" t="inlineStr"/>
+      <c r="N55" s="37" t="inlineStr"/>
+      <c r="O55" s="37" t="inlineStr"/>
+      <c r="P55" s="37" t="inlineStr"/>
+      <c r="Q55" s="37" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -237,7 +237,7 @@
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -285,10 +285,16 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -705,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 10:53:49 (10:53) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 11:53:57 (11:53) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -812,26 +818,26 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>14706.01</v>
+        <v>25382.59</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>23578.47</v>
+        <v>32564.73</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-8872.459999999999</v>
+        <v>-7182.14</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-0.376</v>
+        <v>-0.221</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>113</v>
+        <v>11192</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.09</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K5" s="7" t="n">
@@ -860,7 +866,7 @@
       </c>
       <c r="Q5" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -882,19 +888,19 @@
         <v>0</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>2368.21</v>
+        <v>3270.78</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>-2368.21</v>
+        <v>-3270.78</v>
       </c>
       <c r="G6" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>0</v>
+        <v>1048</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
@@ -939,29 +945,29 @@
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1578.81</v>
+        <v>2180.52</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-1578.81</v>
+        <v>-2180.52</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>0</v>
+        <v>494</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>0.39</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K7" s="27" t="inlineStr"/>
+      <c r="K7" s="28" t="inlineStr"/>
       <c r="L7" s="12" t="inlineStr"/>
-      <c r="M7" s="27" t="inlineStr"/>
-      <c r="N7" s="28" t="inlineStr"/>
+      <c r="M7" s="28" t="inlineStr"/>
+      <c r="N7" s="29" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -984,39 +990,39 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10046652</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>1208</v>
+        <v>13630.16</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>2117.21</v>
+        <v>15257.99</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>-909.21</v>
+        <v>-1627.83</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>-0.429</v>
+        <v>-0.107</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>127</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>0.1</v>
+        <v>9353</v>
+      </c>
+      <c r="I8" s="30" t="n">
+        <v>7.43</v>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K8" s="18" t="n">
-        <v>988.22</v>
+        <v>1905.6</v>
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
@@ -1024,9 +1030,9 @@
         </is>
       </c>
       <c r="M8" s="18" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N8" s="29" t="n">
+        <v>1905.6</v>
+      </c>
+      <c r="N8" s="31" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
@@ -1036,12 +1042,12 @@
       </c>
       <c r="P8" s="24" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q8" s="26" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1051,64 +1057,64 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>399.6</v>
+        <v>1517</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1063.38</v>
+        <v>2924.12</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-663.78</v>
+        <v>-1407.12</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.624</v>
+        <v>-0.481</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>9</v>
+        <v>9409</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.01</v>
+        <v>7.47</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K9" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>988.22</v>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M9" s="7" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N9" s="30" t="n">
-        <v>1.132</v>
+        <v>988.22</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Amazon R$ 46.85)</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q9" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1130,23 +1136,23 @@
         <v>169.8</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>771.42</v>
+        <v>1065.43</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>-601.62</v>
+        <v>-895.63</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-0.78</v>
+        <v>-0.841</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>262</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>0.21</v>
+        <v>26223</v>
+      </c>
+      <c r="I10" s="30" t="n">
+        <v>20.83</v>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
@@ -1165,7 +1171,7 @@
       </c>
       <c r="Q10" s="26" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1175,50 +1181,54 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10041248</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>CREATINA MONOHIDRATADA 300G DUX</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0</v>
+        <v>598.15</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>583.14</v>
+        <v>1468.65</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-583.14</v>
+        <v>-870.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-1</v>
+        <v>-0.593</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>15</v>
+        <v>2446</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.01</v>
+        <v>1.94</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K11" s="27" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>99.90000000000001</v>
+      </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
           <t>AMAZON</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="N11" s="28" t="inlineStr"/>
+        <v>46.85</v>
+      </c>
+      <c r="N11" s="32" t="n">
+        <v>1.132</v>
+      </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
@@ -1226,9 +1236,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q11" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -1238,44 +1248,54 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>105.9</v>
+        <v>157.72</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>686.05</v>
+        <v>971.33</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-580.15</v>
+        <v>-813.61</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>-0.846</v>
+        <v>-0.838</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>0</v>
+        <v>8909</v>
+      </c>
+      <c r="I12" s="30" t="n">
+        <v>7.08</v>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr"/>
-      <c r="M12" s="23" t="inlineStr"/>
-      <c r="N12" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>108.49</v>
+      </c>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="N12" s="33" t="n">
+        <v>0.111</v>
+      </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P12" s="24" t="inlineStr">
@@ -1283,9 +1303,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q12" s="26" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q12" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -1295,41 +1315,41 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>563.62</v>
+        <v>199.03</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1130.11</v>
+        <v>947.52</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-566.49</v>
+        <v>-748.49</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.501</v>
+        <v>-0.79</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>901</v>
+        <v>3146</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.72</v>
+        <v>2.5</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K13" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K13" s="28" t="inlineStr"/>
       <c r="L13" s="12" t="inlineStr"/>
-      <c r="M13" s="27" t="inlineStr"/>
-      <c r="N13" s="28" t="inlineStr"/>
+      <c r="M13" s="28" t="inlineStr"/>
+      <c r="N13" s="29" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1342,7 +1362,7 @@
       </c>
       <c r="Q13" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1352,54 +1372,44 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>157.72</v>
+        <v>105.9</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>703.29</v>
+        <v>844.39</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-545.5700000000001</v>
+        <v>-738.49</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>-0.7759999999999999</v>
+        <v>-0.875</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>88</v>
+        <v>1270</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>108.49</v>
-      </c>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N14" s="31" t="n">
-        <v>0.111</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr"/>
+      <c r="L14" s="24" t="inlineStr"/>
+      <c r="M14" s="23" t="inlineStr"/>
+      <c r="N14" s="25" t="inlineStr"/>
       <c r="O14" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P14" s="24" t="inlineStr">
@@ -1407,9 +1417,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q14" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 97.69)</t>
+      <c r="Q14" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1419,41 +1429,47 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>105.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>611.38</v>
+        <v>805.39</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-505.48</v>
+        <v>-725.49</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-0.8270000000000001</v>
+        <v>-0.9009999999999999</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>11</v>
+        <v>4427</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.01</v>
+        <v>3.52</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K15" s="27" t="inlineStr"/>
-      <c r="L15" s="12" t="inlineStr"/>
-      <c r="M15" s="27" t="inlineStr"/>
-      <c r="N15" s="28" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K15" s="28" t="inlineStr"/>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="N15" s="29" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1466,7 +1482,7 @@
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1488,23 +1504,23 @@
         <v>221.97</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>681.9</v>
+        <v>941.79</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-459.93</v>
+        <v>-719.8200000000001</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>-0.674</v>
+        <v>-0.764</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>758</v>
-      </c>
-      <c r="I16" s="22" t="n">
-        <v>0.6</v>
+        <v>39477</v>
+      </c>
+      <c r="I16" s="30" t="n">
+        <v>31.36</v>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
@@ -1523,7 +1539,7 @@
       </c>
       <c r="Q16" s="26" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1533,47 +1549,41 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10025098</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0</v>
+        <v>880.8200000000001</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>446.84</v>
+        <v>1560.83</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-446.84</v>
+        <v>-680.01</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-1</v>
+        <v>-0.436</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0</v>
+        <v>8275</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K17" s="27" t="inlineStr"/>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>1212.9</v>
-      </c>
-      <c r="N17" s="28" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K17" s="28" t="inlineStr"/>
+      <c r="L17" s="12" t="inlineStr"/>
+      <c r="M17" s="28" t="inlineStr"/>
+      <c r="N17" s="29" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -1586,7 +1596,7 @@
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1596,50 +1606,54 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>10093877</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>MIRENA 52MG 1END+INS BAYER</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
+        <v>999</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>1658.15</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>-659.15</v>
+      </c>
+      <c r="G18" s="20" t="n">
+        <v>-0.398</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>3321</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L18" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="18" t="n">
-        <v>446.34</v>
-      </c>
-      <c r="F18" s="19" t="n">
-        <v>-446.34</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H18" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="I18" s="22" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M18" s="18" t="n">
-        <v>1225.89</v>
-      </c>
-      <c r="N18" s="25" t="inlineStr"/>
       <c r="O18" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P18" s="24" t="inlineStr">
@@ -1649,7 +1663,7 @@
       </c>
       <c r="Q18" s="26" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1659,39 +1673,39 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10050653</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0</v>
+        <v>231.09</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>426.98</v>
+        <v>870.12</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-426.98</v>
+        <v>-639.03</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-1</v>
+        <v>-0.7340000000000001</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>0</v>
+        <v>837</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>0.66</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K19" s="7" t="n">
-        <v>1347.91</v>
+        <v>315.46</v>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
@@ -1699,14 +1713,14 @@
         </is>
       </c>
       <c r="M19" s="7" t="n">
-        <v>1347.89</v>
-      </c>
-      <c r="N19" s="13" t="n">
-        <v>0</v>
+        <v>236.6</v>
+      </c>
+      <c r="N19" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P19" s="12" t="inlineStr">
@@ -1714,9 +1728,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q19" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -1726,54 +1740,50 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>10050640</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>709.91</v>
+        <v>617.14</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>-414.91</v>
+        <v>-617.14</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>-0.584</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>27</v>
+        <v>204</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K20" s="18" t="n">
-        <v>831.76</v>
-      </c>
+      <c r="K20" s="23" t="inlineStr"/>
       <c r="L20" s="24" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M20" s="18" t="n">
-        <v>831.76</v>
-      </c>
-      <c r="N20" s="29" t="n">
-        <v>0</v>
-      </c>
+        <v>1212.9</v>
+      </c>
+      <c r="N20" s="25" t="inlineStr"/>
       <c r="O20" s="24" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P20" s="24" t="inlineStr">
@@ -1793,54 +1803,50 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10024521</t>
+          <t>10093877</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
+          <t>MIRENA 52MG 1END+INS BAYER</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>411.99</v>
+        <v>616.46</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-411.99</v>
+        <v>-616.46</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>0</v>
+        <v>501</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>0.4</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K21" s="7" t="n">
-        <v>799.9</v>
-      </c>
+      <c r="K21" s="28" t="inlineStr"/>
       <c r="L21" s="12" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
-        <v>814.9</v>
-      </c>
-      <c r="N21" s="13" t="n">
-        <v>-0.018</v>
-      </c>
+        <v>1225.89</v>
+      </c>
+      <c r="N21" s="29" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
@@ -1860,39 +1866,39 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10050653</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>231.09</v>
+        <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>630.01</v>
+        <v>589.71</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>-398.92</v>
+        <v>-589.71</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>-0.633</v>
+        <v>-1</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="I22" s="22" t="n">
-        <v>0.01</v>
+        <v>2647</v>
+      </c>
+      <c r="I22" s="30" t="n">
+        <v>2.1</v>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K22" s="18" t="n">
-        <v>315.46</v>
+        <v>1347.91</v>
       </c>
       <c r="L22" s="24" t="inlineStr">
         <is>
@@ -1900,14 +1906,14 @@
         </is>
       </c>
       <c r="M22" s="18" t="n">
-        <v>236.6</v>
+        <v>1347.89</v>
       </c>
       <c r="N22" s="31" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="O22" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P22" s="24" t="inlineStr">
@@ -1915,9 +1921,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q22" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+      <c r="Q22" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1927,54 +1933,54 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10024521</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>185.7</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>570.9</v>
+        <v>569.01</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-385.2</v>
+        <v>-569.01</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.675</v>
+        <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>0.01</v>
+        <v>575</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>0.46</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K23" s="7" t="n">
-        <v>94.98999999999999</v>
+        <v>799.9</v>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N23" s="30" t="n">
-        <v>0.904</v>
+        <v>814.9</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>-0.018</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
@@ -1982,9 +1988,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Amazon R$ 49.90)</t>
+      <c r="Q23" s="14" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1994,44 +2000,54 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>10053171</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>0</v>
+        <v>240.58</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>383.05</v>
+        <v>788.49</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>-383.05</v>
+        <v>-547.91</v>
       </c>
       <c r="G24" s="20" t="n">
-        <v>-1</v>
+        <v>-0.695</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="I24" s="22" t="n">
-        <v>0.01</v>
+        <v>4815</v>
+      </c>
+      <c r="I24" s="30" t="n">
+        <v>3.82</v>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr"/>
-      <c r="M24" s="23" t="inlineStr"/>
-      <c r="N24" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L24" s="24" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M24" s="18" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="N24" s="33" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O24" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P24" s="24" t="inlineStr">
@@ -2039,9 +2055,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q24" s="26" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -2051,54 +2067,44 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10025745</t>
+          <t>10053171</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
+          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>379.63</v>
+        <v>529.04</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-379.63</v>
+        <v>-529.04</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>0</v>
+        <v>1454</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>1.15</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K25" s="7" t="n">
-        <v>1105.6</v>
-      </c>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="n">
-        <v>1170.01</v>
-      </c>
-      <c r="N25" s="13" t="n">
-        <v>-0.055</v>
-      </c>
+      <c r="K25" s="28" t="inlineStr"/>
+      <c r="L25" s="12" t="inlineStr"/>
+      <c r="M25" s="28" t="inlineStr"/>
+      <c r="N25" s="29" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr">
@@ -2118,44 +2124,54 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10025745</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>369.4</v>
+        <v>524.3099999999999</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>-369.4</v>
+        <v>-524.3099999999999</v>
       </c>
       <c r="G26" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr"/>
-      <c r="M26" s="23" t="inlineStr"/>
-      <c r="N26" s="25" t="inlineStr"/>
+      <c r="K26" s="18" t="n">
+        <v>1105.6</v>
+      </c>
+      <c r="L26" s="24" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M26" s="18" t="n">
+        <v>1170.01</v>
+      </c>
+      <c r="N26" s="31" t="n">
+        <v>-0.055</v>
+      </c>
       <c r="O26" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P26" s="24" t="inlineStr">
@@ -2175,41 +2191,41 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>56.81</v>
+        <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>389.4</v>
+        <v>510.18</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-332.59</v>
+        <v>-510.18</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.8540000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>650</v>
+        <v>11806</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>0.52</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K27" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K27" s="28" t="inlineStr"/>
       <c r="L27" s="12" t="inlineStr"/>
-      <c r="M27" s="27" t="inlineStr"/>
-      <c r="N27" s="28" t="inlineStr"/>
+      <c r="M27" s="28" t="inlineStr"/>
+      <c r="N27" s="29" t="inlineStr"/>
       <c r="O27" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2222,7 +2238,7 @@
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2232,50 +2248,50 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>25.9</v>
+        <v>271.96</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>355.76</v>
+        <v>753.98</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>-329.86</v>
+        <v>-482.02</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>-0.927</v>
+        <v>-0.639</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>241</v>
-      </c>
-      <c r="I28" s="22" t="n">
-        <v>0.19</v>
+        <v>12853</v>
+      </c>
+      <c r="I28" s="30" t="n">
+        <v>10.21</v>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K28" s="18" t="n">
-        <v>25.9</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L28" s="24" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M28" s="18" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N28" s="31" t="n">
-        <v>0.629</v>
+        <v>61.06</v>
+      </c>
+      <c r="N28" s="33" t="n">
+        <v>0.113</v>
       </c>
       <c r="O28" s="24" t="inlineStr">
         <is>
@@ -2289,7 +2305,7 @@
       </c>
       <c r="Q28" s="17" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Farmaciasnissei R$ 15.90)</t>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -2299,44 +2315,54 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>315.24</v>
+        <v>491.35</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-315.24</v>
+        <v>-465.45</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-1</v>
+        <v>-0.9470000000000001</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>304</v>
+        <v>22233</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>0.24</v>
+        <v>17.66</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K29" s="27" t="inlineStr"/>
-      <c r="L29" s="12" t="inlineStr"/>
-      <c r="M29" s="27" t="inlineStr"/>
-      <c r="N29" s="28" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N29" s="32" t="n">
+        <v>0.629</v>
+      </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
@@ -2344,9 +2370,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q29" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -2356,35 +2382,35 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>10028321</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>PREGABALINA 150MG 30CAP GEN EMS (C1)</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
-        <v>67.62</v>
+        <v>0</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>382.17</v>
+        <v>435.39</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-314.55</v>
+        <v>-435.39</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>-0.823</v>
+        <v>-1</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>0</v>
+        <v>30285</v>
+      </c>
+      <c r="I30" s="30" t="n">
+        <v>24.05</v>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr"/>
@@ -2403,7 +2429,7 @@
       </c>
       <c r="Q30" s="26" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2413,50 +2439,54 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10035030</t>
+          <t>10050640</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>APTANUTRI PREMIUM 3 800G 30% DESC 2UN DANONE</t>
+          <t>POVIZTRA 0,25MG 1,5ML EUROFARMA</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
+        <v>590</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>980.48</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>-390.48</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>-0.398</v>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>6179</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>831.76</v>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>831.76</v>
+      </c>
+      <c r="N31" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="7" t="n">
-        <v>280.17</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>-280.17</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H31" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K31" s="27" t="inlineStr"/>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="n">
-        <v>125.9</v>
-      </c>
-      <c r="N31" s="28" t="inlineStr"/>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr">
@@ -2466,7 +2496,7 @@
       </c>
       <c r="Q31" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2476,54 +2506,50 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10035030</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>APTANUTRI PREMIUM 3 800G 30% DESC 2UN DANONE</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
-        <v>271.96</v>
+        <v>0</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>545.92</v>
+        <v>386.95</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>-273.96</v>
+        <v>-386.95</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>-0.502</v>
+        <v>-1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>254</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>0.2</v>
+        <v>3103</v>
+      </c>
+      <c r="I32" s="30" t="n">
+        <v>2.46</v>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K32" s="18" t="n">
-        <v>67.98999999999999</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr"/>
       <c r="L32" s="24" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M32" s="18" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N32" s="31" t="n">
-        <v>0.113</v>
-      </c>
+        <v>125.9</v>
+      </c>
+      <c r="N32" s="25" t="inlineStr"/>
       <c r="O32" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P32" s="24" t="inlineStr">
@@ -2531,9 +2557,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q32" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Drogaraia R$ 61.06)</t>
+      <c r="Q32" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2555,29 +2581,29 @@
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>273.6</v>
+        <v>377.88</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-273.6</v>
+        <v>-377.88</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>4</v>
+        <v>2941</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K33" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K33" s="28" t="inlineStr"/>
       <c r="L33" s="12" t="inlineStr"/>
-      <c r="M33" s="27" t="inlineStr"/>
-      <c r="N33" s="28" t="inlineStr"/>
+      <c r="M33" s="28" t="inlineStr"/>
+      <c r="N33" s="29" t="inlineStr"/>
       <c r="O33" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2590,7 +2616,7 @@
       </c>
       <c r="Q33" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2600,54 +2626,44 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>100022270</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>0</v>
+        <v>173.42</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>268.37</v>
+        <v>537.8099999999999</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-268.37</v>
+        <v>-364.39</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>-1</v>
+        <v>-0.6779999999999999</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>0</v>
+        <v>9864</v>
+      </c>
+      <c r="I34" s="30" t="n">
+        <v>7.83</v>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K34" s="18" t="n">
-        <v>185.61</v>
-      </c>
-      <c r="L34" s="24" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M34" s="18" t="n">
-        <v>158.66</v>
-      </c>
-      <c r="N34" s="31" t="n">
-        <v>0.17</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr"/>
+      <c r="L34" s="24" t="inlineStr"/>
+      <c r="M34" s="23" t="inlineStr"/>
+      <c r="N34" s="25" t="inlineStr"/>
       <c r="O34" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P34" s="24" t="inlineStr">
@@ -2655,9 +2671,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q34" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Farmaciasnissei R$ 158.66)</t>
+      <c r="Q34" s="26" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2667,39 +2683,39 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10046652</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 2,5MG 4CAN APLIC LILLY</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>10785.12</v>
+        <v>465.29</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>11047.54</v>
+        <v>829.08</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-262.42</v>
+        <v>-363.79</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-0.024</v>
+        <v>-0.439</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>144</v>
+        <v>3992</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>0.11</v>
+        <v>3.17</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K35" s="7" t="n">
-        <v>1905.6</v>
+        <v>149.4</v>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -2707,14 +2723,14 @@
         </is>
       </c>
       <c r="M35" s="7" t="n">
-        <v>1905.6</v>
-      </c>
-      <c r="N35" s="13" t="n">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="N35" s="32" t="n">
+        <v>0.396</v>
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
@@ -2722,9 +2738,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q35" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -2734,54 +2750,50 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>100009772</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>FERINJECT 50MG/ML 1FR/AMP 10ML BLANVER</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
-        <v>345.3</v>
+        <v>0</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>600.3</v>
+        <v>334.33</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-255</v>
+        <v>-334.33</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>-0.425</v>
+        <v>-1</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>37</v>
+        <v>510</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>0.03</v>
+        <v>0.41</v>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K36" s="18" t="n">
-        <v>149.4</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr"/>
       <c r="L36" s="24" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M36" s="18" t="n">
-        <v>107</v>
-      </c>
-      <c r="N36" s="31" t="n">
-        <v>0.396</v>
-      </c>
+        <v>719.9</v>
+      </c>
+      <c r="N36" s="25" t="inlineStr"/>
       <c r="O36" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P36" s="24" t="inlineStr">
@@ -2789,9 +2801,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 107.00)</t>
+      <c r="Q36" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2801,41 +2813,41 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>100011549</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>463.6</v>
+        <v>250.68</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>715.26</v>
+        <v>566.4400000000001</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-251.66</v>
+        <v>-315.76</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.352</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>502</v>
+        <v>7665</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>0.4</v>
+        <v>6.09</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K37" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K37" s="28" t="inlineStr"/>
       <c r="L37" s="12" t="inlineStr"/>
-      <c r="M37" s="27" t="inlineStr"/>
-      <c r="N37" s="28" t="inlineStr"/>
+      <c r="M37" s="28" t="inlineStr"/>
+      <c r="N37" s="29" t="inlineStr"/>
       <c r="O37" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2848,7 +2860,7 @@
       </c>
       <c r="Q37" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2858,46 +2870,40 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>100009772</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>FERINJECT 50MG/ML 1FR/AMP 10ML BLANVER</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
-        <v>0</v>
+        <v>340.2</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>242.07</v>
+        <v>644</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-242.07</v>
+        <v>-303.8</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>-1</v>
+        <v>-0.472</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>0</v>
+        <v>11106</v>
+      </c>
+      <c r="I38" s="30" t="n">
+        <v>8.82</v>
       </c>
       <c r="J38" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr"/>
-      <c r="L38" s="24" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M38" s="18" t="n">
-        <v>719.9</v>
-      </c>
+      <c r="L38" s="24" t="inlineStr"/>
+      <c r="M38" s="23" t="inlineStr"/>
       <c r="N38" s="25" t="inlineStr"/>
       <c r="O38" s="24" t="inlineStr">
         <is>
@@ -2911,7 +2917,7 @@
       </c>
       <c r="Q38" s="26" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2921,41 +2927,41 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>100008756</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>LEITE NEOCATE LCP 400G DANONE</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>231.8</v>
+        <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>466.29</v>
+        <v>292.35</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-234.49</v>
+        <v>-292.35</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.503</v>
+        <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>165</v>
-      </c>
-      <c r="I39" s="11" t="n">
-        <v>0.13</v>
+        <v>1484</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>1.18</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K39" s="27" t="inlineStr"/>
+      <c r="K39" s="28" t="inlineStr"/>
       <c r="L39" s="12" t="inlineStr"/>
-      <c r="M39" s="27" t="inlineStr"/>
-      <c r="N39" s="28" t="inlineStr"/>
+      <c r="M39" s="28" t="inlineStr"/>
+      <c r="N39" s="29" t="inlineStr"/>
       <c r="O39" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -2978,44 +2984,54 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>10045969</t>
+          <t>10102163</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT GIGA G 136UN</t>
+          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>0</v>
+        <v>559.41</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>231.62</v>
+        <v>848.08</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>-231.62</v>
+        <v>-288.67</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>-1</v>
+        <v>-0.34</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>0.01</v>
+        <v>16877</v>
+      </c>
+      <c r="I40" s="30" t="n">
+        <v>13.41</v>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr"/>
-      <c r="L40" s="24" t="inlineStr"/>
-      <c r="M40" s="23" t="inlineStr"/>
-      <c r="N40" s="25" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K40" s="18" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="L40" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M40" s="18" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="N40" s="33" t="n">
+        <v>0.333</v>
+      </c>
       <c r="O40" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P40" s="24" t="inlineStr">
@@ -3023,9 +3039,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q40" s="26" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
         </is>
       </c>
     </row>
@@ -3035,50 +3051,54 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10044745</t>
+          <t>10030119</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
+          <t>RYBELSUS 14MG 30CP NOVO NORDISK</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>91.09</v>
+        <v>1150</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>320.16</v>
+        <v>1426.02</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-229.07</v>
+        <v>-276.02</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-0.715</v>
+        <v>-0.194</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>95</v>
+        <v>2858</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>0.08</v>
+        <v>2.27</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K41" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>1301.17</v>
+      </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
-        <v>83.92</v>
-      </c>
-      <c r="N41" s="28" t="inlineStr"/>
+        <v>1301.17</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
@@ -3088,7 +3108,7 @@
       </c>
       <c r="Q41" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -3098,31 +3118,31 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>100008756</t>
+          <t>10044679</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>LEITE NEOCATE LCP 400G DANONE</t>
+          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>211.68</v>
+        <v>270.35</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>-211.68</v>
+        <v>-270.35</v>
       </c>
       <c r="G42" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>2</v>
+        <v>324</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="J42" s="15" t="inlineStr">
         <is>
@@ -3155,54 +3175,44 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>100003186</t>
+          <t>10041082</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>NACTALI 75MG 84CP REV LIBBS</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>209.37</v>
+        <v>265.71</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-209.37</v>
+        <v>-265.71</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>51</v>
+        <v>5609</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>0.04</v>
+        <v>4.46</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>94.72</v>
-      </c>
-      <c r="L43" s="12" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="N43" s="13" t="n">
-        <v>-0.052</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K43" s="28" t="inlineStr"/>
+      <c r="L43" s="12" t="inlineStr"/>
+      <c r="M43" s="28" t="inlineStr"/>
+      <c r="N43" s="29" t="inlineStr"/>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
@@ -3212,7 +3222,7 @@
       </c>
       <c r="Q43" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3222,31 +3232,31 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10038798</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1200.59</v>
+        <v>238.72</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>-201.59</v>
+        <v>-238.72</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>-0.168</v>
+        <v>-1</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>9</v>
+        <v>1623</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>0.01</v>
+        <v>1.29</v>
       </c>
       <c r="J44" s="15" t="inlineStr">
         <is>
@@ -3254,22 +3264,22 @@
         </is>
       </c>
       <c r="K44" s="18" t="n">
-        <v>1298.54</v>
+        <v>180.79</v>
       </c>
       <c r="L44" s="24" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M44" s="18" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N44" s="29" t="n">
-        <v>0</v>
+        <v>175.9</v>
+      </c>
+      <c r="N44" s="33" t="n">
+        <v>0.028</v>
       </c>
       <c r="O44" s="24" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P44" s="24" t="inlineStr">
@@ -3289,41 +3299,41 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10044679</t>
+          <t>10052540</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0</v>
+        <v>346.36</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>195.75</v>
+        <v>584.34</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-195.75</v>
+        <v>-237.98</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-1</v>
+        <v>-0.407</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>0</v>
+        <v>2601</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K45" s="27" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K45" s="28" t="inlineStr"/>
       <c r="L45" s="12" t="inlineStr"/>
-      <c r="M45" s="27" t="inlineStr"/>
-      <c r="N45" s="28" t="inlineStr"/>
+      <c r="M45" s="28" t="inlineStr"/>
+      <c r="N45" s="29" t="inlineStr"/>
       <c r="O45" s="12" t="inlineStr">
         <is>
           <t>Não Monitorado</t>
@@ -3336,7 +3346,7 @@
       </c>
       <c r="Q45" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3346,44 +3356,54 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>10041082</t>
+          <t>10040748</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
+          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>192.39</v>
+        <v>231.19</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>-192.39</v>
+        <v>-231.19</v>
       </c>
       <c r="G46" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>28</v>
+        <v>402</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>0.02</v>
+        <v>0.32</v>
       </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K46" s="23" t="inlineStr"/>
-      <c r="L46" s="24" t="inlineStr"/>
-      <c r="M46" s="23" t="inlineStr"/>
-      <c r="N46" s="25" t="inlineStr"/>
+      <c r="K46" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L46" s="24" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M46" s="18" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N46" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="O46" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P46" s="24" t="inlineStr">
@@ -3403,54 +3423,44 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10046010</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>FR PAMPERS SUPERSEC MEGA M 40UN</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>436.63</v>
+        <v>137.7</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>614.05</v>
+        <v>367.15</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-177.42</v>
+        <v>-229.45</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-0.289</v>
+        <v>-0.625</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>706</v>
+        <v>6394</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>0.5600000000000001</v>
+        <v>5.08</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>74.22</v>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N47" s="30" t="n">
-        <v>0.333</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="inlineStr"/>
+      <c r="L47" s="12" t="inlineStr"/>
+      <c r="M47" s="28" t="inlineStr"/>
+      <c r="N47" s="29" t="inlineStr"/>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
@@ -3458,9 +3468,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 55.67)</t>
+      <c r="Q47" s="14" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3470,50 +3480,50 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>10038798</t>
+          <t>100001425</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
+          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>0</v>
+        <v>79.7</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>172.84</v>
+        <v>302.32</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>-172.84</v>
+        <v>-222.62</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>-1</v>
+        <v>-0.736</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="I48" s="22" t="n">
-        <v>0</v>
+        <v>13421</v>
+      </c>
+      <c r="I48" s="30" t="n">
+        <v>10.66</v>
       </c>
       <c r="J48" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K48" s="18" t="n">
-        <v>180.79</v>
+        <v>29.9</v>
       </c>
       <c r="L48" s="24" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M48" s="18" t="n">
-        <v>175.9</v>
-      </c>
-      <c r="N48" s="31" t="n">
-        <v>0.028</v>
+        <v>28.9</v>
+      </c>
+      <c r="N48" s="33" t="n">
+        <v>0.035</v>
       </c>
       <c r="O48" s="24" t="inlineStr">
         <is>
@@ -3527,7 +3537,7 @@
       </c>
       <c r="Q48" s="26" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3537,39 +3547,39 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10040748</t>
+          <t>10033757</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XXG 54UN</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0</v>
+        <v>679.2</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>167.39</v>
+        <v>900.72</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-167.39</v>
+        <v>-221.52</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-1</v>
+        <v>-0.246</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>0</v>
+        <v>24254</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>0</v>
+        <v>19.26</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K49" s="7" t="n">
-        <v>1298.54</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
@@ -3577,14 +3587,14 @@
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N49" s="13" t="n">
-        <v>0</v>
+        <v>72.90000000000001</v>
+      </c>
+      <c r="N49" s="32" t="n">
+        <v>0.165</v>
       </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
@@ -3592,9 +3602,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q49" s="14" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 72.90)</t>
         </is>
       </c>
     </row>
@@ -3604,44 +3614,54 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>10049066</t>
+          <t>100011551</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 175ML HIDRATACAO+HIALURON VIT</t>
+          <t>ANDROGEL 50MG 10MG/G GEL 30ENV 5G</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>25.83</v>
+        <v>0</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>186.77</v>
+        <v>216.81</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>-160.94</v>
+        <v>-216.81</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>-0.862</v>
+        <v>-1</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>802</v>
+        <v>1698</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>0.64</v>
+        <v>1.35</v>
       </c>
       <c r="J50" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="inlineStr"/>
-      <c r="L50" s="24" t="inlineStr"/>
-      <c r="M50" s="23" t="inlineStr"/>
-      <c r="N50" s="25" t="inlineStr"/>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="L50" s="24" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M50" s="18" t="n">
+        <v>301.16</v>
+      </c>
+      <c r="N50" s="33" t="n">
+        <v>0.141</v>
+      </c>
       <c r="O50" s="24" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P50" s="24" t="inlineStr">
@@ -3649,9 +3669,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q50" s="26" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q50" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Farmaciasnissei R$ 301.16)</t>
         </is>
       </c>
     </row>
@@ -3661,44 +3681,54 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>100011549</t>
+          <t>10040738</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
+          <t>LYBERDIA 40MG 50ML GOTAS EMS (A3)</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>250.68</v>
+        <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>410.13</v>
+        <v>215.12</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-159.45</v>
+        <v>-215.12</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.389</v>
+        <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>115</v>
+        <v>2560</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>0.09</v>
+        <v>2.03</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K51" s="27" t="inlineStr"/>
-      <c r="L51" s="12" t="inlineStr"/>
-      <c r="M51" s="27" t="inlineStr"/>
-      <c r="N51" s="28" t="inlineStr"/>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>567.02</v>
+      </c>
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>567.02</v>
+      </c>
+      <c r="N51" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P51" s="12" t="inlineStr">
@@ -3708,7 +3738,7 @@
       </c>
       <c r="Q51" s="14" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3718,54 +3748,44 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>10097311</t>
+          <t>999705</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>NESTOGENO 1 800G NESTLE</t>
+          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>263.99</v>
+        <v>0</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>422.28</v>
+        <v>214.83</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>-158.29</v>
+        <v>-214.83</v>
       </c>
       <c r="G52" s="20" t="n">
-        <v>-0.375</v>
+        <v>-1</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>209</v>
+        <v>37</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
       <c r="J52" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K52" s="18" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="L52" s="24" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M52" s="18" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="N52" s="31" t="n">
-        <v>0.081</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K52" s="23" t="inlineStr"/>
+      <c r="L52" s="24" t="inlineStr"/>
+      <c r="M52" s="23" t="inlineStr"/>
+      <c r="N52" s="25" t="inlineStr"/>
       <c r="O52" s="24" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P52" s="24" t="inlineStr">
@@ -3773,9 +3793,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q52" s="17" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 62.90)</t>
+      <c r="Q52" s="26" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3785,31 +3805,31 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>100011551</t>
+          <t>10033355</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>ANDROGEL 50MG 10MG/G GEL 30ENV 5G</t>
+          <t>OMEGAFOR PLUS 1000MG 120CAP VITAFOR</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>156.98</v>
+        <v>212.96</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-156.98</v>
+        <v>-212.96</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" s="11" t="n">
-        <v>0</v>
+        <v>1713</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>1.36</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3817,18 +3837,18 @@
         </is>
       </c>
       <c r="K53" s="7" t="n">
-        <v>343.63</v>
+        <v>184</v>
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M53" s="7" t="n">
-        <v>301.16</v>
-      </c>
-      <c r="N53" s="30" t="n">
-        <v>0.141</v>
+        <v>132.9</v>
+      </c>
+      <c r="N53" s="32" t="n">
+        <v>0.384</v>
       </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
@@ -3842,7 +3862,7 @@
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Farmaciasnissei R$ 301.16)</t>
+          <t>Reprecificar e Remanejar (Amazon R$ 132.90)</t>
         </is>
       </c>
     </row>
@@ -3852,54 +3872,54 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>10040738</t>
+          <t>100008511</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>LYBERDIA 40MG 50ML GOTAS EMS (A3)</t>
+          <t>APTAMIL PEPTI 800G DANONE</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>155.76</v>
+        <v>211.97</v>
       </c>
       <c r="F54" s="19" t="n">
-        <v>-155.76</v>
+        <v>-211.97</v>
       </c>
       <c r="G54" s="20" t="n">
         <v>-1</v>
       </c>
       <c r="H54" s="21" t="n">
-        <v>24</v>
+        <v>1353</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>0.02</v>
+        <v>1.07</v>
       </c>
       <c r="J54" s="15" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K54" s="18" t="n">
-        <v>567.02</v>
+        <v>307.99</v>
       </c>
       <c r="L54" s="24" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M54" s="18" t="n">
-        <v>567.02</v>
-      </c>
-      <c r="N54" s="29" t="n">
-        <v>0</v>
+        <v>230.99</v>
+      </c>
+      <c r="N54" s="33" t="n">
+        <v>0.333</v>
       </c>
       <c r="O54" s="24" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P54" s="24" t="inlineStr">
@@ -3907,46 +3927,46 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q54" s="26" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Amazon R$ 230.99)</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="32" t="inlineStr">
+      <c r="A55" s="34" t="inlineStr">
         <is>
           <t>TOTAL TOP 50</t>
         </is>
       </c>
-      <c r="B55" s="33" t="n"/>
-      <c r="C55" s="33" t="n"/>
-      <c r="D55" s="34">
+      <c r="B55" s="35" t="n"/>
+      <c r="C55" s="35" t="n"/>
+      <c r="D55" s="36">
         <f>SUM(D5:D54)</f>
         <v/>
       </c>
-      <c r="E55" s="34">
+      <c r="E55" s="36">
         <f>SUM(E5:E54)</f>
         <v/>
       </c>
-      <c r="F55" s="35">
+      <c r="F55" s="37">
         <f>SUM(F5:F54)</f>
         <v/>
       </c>
-      <c r="G55" s="36">
+      <c r="G55" s="38">
         <f>(D55-E55)/E55</f>
         <v/>
       </c>
-      <c r="H55" s="37" t="n"/>
-      <c r="I55" s="37" t="inlineStr"/>
-      <c r="J55" s="37" t="inlineStr"/>
-      <c r="K55" s="37" t="inlineStr"/>
-      <c r="L55" s="37" t="inlineStr"/>
-      <c r="M55" s="37" t="inlineStr"/>
-      <c r="N55" s="37" t="inlineStr"/>
-      <c r="O55" s="37" t="inlineStr"/>
-      <c r="P55" s="37" t="inlineStr"/>
-      <c r="Q55" s="37" t="inlineStr"/>
+      <c r="H55" s="39" t="n"/>
+      <c r="I55" s="39" t="inlineStr"/>
+      <c r="J55" s="39" t="inlineStr"/>
+      <c r="K55" s="39" t="inlineStr"/>
+      <c r="L55" s="39" t="inlineStr"/>
+      <c r="M55" s="39" t="inlineStr"/>
+      <c r="N55" s="39" t="inlineStr"/>
+      <c r="O55" s="39" t="inlineStr"/>
+      <c r="P55" s="39" t="inlineStr"/>
+      <c r="Q55" s="39" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -291,19 +291,19 @@
     <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 12:53:53 (12:53) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 13:54:09 (13:54) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4108.34</v>
+        <v>4988.39</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-4108.34</v>
+        <v>-4988.39</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>-1</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>2738.89</v>
+        <v>3325.59</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>-2738.89</v>
+        <v>-3325.59</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>-1</v>
@@ -923,54 +923,44 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2135</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3672.91</v>
+        <v>1624.92</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-1537.91</v>
+        <v>-1540.02</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.419</v>
+        <v>-0.948</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>9409</v>
+        <v>26223</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>7.47</v>
+        <v>20.83</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K7" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N7" s="29" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" s="12" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
+      <c r="M7" s="12" t="inlineStr"/>
+      <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P7" s="13" t="inlineStr">
@@ -990,44 +980,54 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>169.8</v>
+        <v>3034</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>1338.25</v>
+        <v>4459.68</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>-1168.45</v>
+        <v>-1425.68</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>-0.873</v>
+        <v>-0.32</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>26223</v>
-      </c>
-      <c r="I8" s="30" t="n">
-        <v>20.83</v>
+        <v>9409</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>7.47</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K8" s="24" t="inlineStr"/>
-      <c r="L8" s="25" t="inlineStr"/>
-      <c r="M8" s="24" t="inlineStr"/>
-      <c r="N8" s="26" t="inlineStr"/>
+      <c r="K8" s="19" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M8" s="19" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="N8" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="O8" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P8" s="25" t="inlineStr">
@@ -1047,54 +1047,54 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>999</v>
+        <v>996.92</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2082.76</v>
+        <v>2239.89</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1083.76</v>
+        <v>-1242.97</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.52</v>
+        <v>-0.555</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>3321</v>
+        <v>2446</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>2.64</v>
+        <v>1.94</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1298.54</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M9" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N9" s="29" t="n">
-        <v>0</v>
+        <v>46.85</v>
+      </c>
+      <c r="N9" s="31" t="n">
+        <v>1.132</v>
       </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P9" s="13" t="inlineStr">
@@ -1102,9 +1102,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q9" s="15" t="inlineStr">
-        <is>
-          <t>Push CRM / Recompra 30d no App</t>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -1114,54 +1114,44 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>157.72</v>
+        <v>205.03</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>1220.06</v>
+        <v>1445.09</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-1062.34</v>
+        <v>-1240.06</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>-0.871</v>
+        <v>-0.858</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>8909</v>
-      </c>
-      <c r="I10" s="30" t="n">
-        <v>7.08</v>
+        <v>3146</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>2.5</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>108.49</v>
-      </c>
-      <c r="L10" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M10" s="19" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N10" s="31" t="n">
-        <v>0.111</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K10" s="24" t="inlineStr"/>
+      <c r="L10" s="25" t="inlineStr"/>
+      <c r="M10" s="24" t="inlineStr"/>
+      <c r="N10" s="26" t="inlineStr"/>
       <c r="O10" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P10" s="25" t="inlineStr">
@@ -1169,9 +1159,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q10" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+      <c r="Q10" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1193,13 +1183,13 @@
         <v>221.97</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1182.95</v>
+        <v>1436.35</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-960.98</v>
+        <v>-1214.38</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.845</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>39477</v>
@@ -1223,7 +1213,7 @@
       </c>
       <c r="P11" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q11" s="15" t="inlineStr">
@@ -1238,54 +1228,64 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>304.93</v>
+        <v>335.3</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>1190.15</v>
+        <v>1481.41</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>-885.22</v>
+        <v>-1146.11</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.7440000000000001</v>
+        <v>-0.774</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>3146</v>
-      </c>
-      <c r="I12" s="30" t="n">
-        <v>2.5</v>
+        <v>8909</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>7.08</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K12" s="24" t="inlineStr"/>
-      <c r="L12" s="25" t="inlineStr"/>
-      <c r="M12" s="24" t="inlineStr"/>
-      <c r="N12" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>108.49</v>
+      </c>
+      <c r="L12" s="25" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M12" s="19" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="N12" s="32" t="n">
+        <v>0.111</v>
+      </c>
       <c r="O12" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P12" s="25" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q12" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q12" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -1295,54 +1295,50 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>996.92</v>
+        <v>249.17</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1844.73</v>
+        <v>1228.33</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-847.8099999999999</v>
+        <v>-979.16</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.46</v>
+        <v>-0.797</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>2446</v>
+        <v>4427</v>
       </c>
       <c r="I13" s="28" t="n">
-        <v>1.94</v>
+        <v>3.52</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>99.90000000000001</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr"/>
       <c r="L13" s="13" t="inlineStr">
         <is>
           <t>AMAZON</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N13" s="32" t="n">
-        <v>1.132</v>
-      </c>
+        <v>50.25</v>
+      </c>
+      <c r="N13" s="14" t="inlineStr"/>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr">
@@ -1350,9 +1346,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+      <c r="Q13" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1374,10 +1370,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>775.1799999999999</v>
+        <v>941.23</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>-775.1799999999999</v>
+        <v>-941.23</v>
       </c>
       <c r="G14" s="21" t="n">
         <v>-1</v>
@@ -1437,10 +1433,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>774.3099999999999</v>
+        <v>940.1799999999999</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-774.3099999999999</v>
+        <v>-940.1799999999999</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>-1</v>
@@ -1488,46 +1484,40 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>10041248</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>CREATINA MONOHIDRATADA 300G DUX</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>249.17</v>
+        <v>415.06</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>1011.63</v>
+        <v>1287.8</v>
       </c>
       <c r="F16" s="20" t="n">
-        <v>-762.46</v>
+        <v>-872.74</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>-0.754</v>
+        <v>-0.6779999999999999</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>4427</v>
-      </c>
-      <c r="I16" s="30" t="n">
-        <v>3.52</v>
+        <v>1270</v>
+      </c>
+      <c r="I16" s="23" t="n">
+        <v>1.01</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K16" s="24" t="inlineStr"/>
-      <c r="L16" s="25" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>50.25</v>
-      </c>
+      <c r="L16" s="25" t="inlineStr"/>
+      <c r="M16" s="24" t="inlineStr"/>
       <c r="N16" s="26" t="inlineStr"/>
       <c r="O16" s="25" t="inlineStr">
         <is>
@@ -1541,7 +1531,7 @@
       </c>
       <c r="Q16" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1551,44 +1541,54 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10024521</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>309.16</v>
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1060.61</v>
+        <v>867.8099999999999</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-751.45</v>
+        <v>-867.8099999999999</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-0.7090000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>1270</v>
+        <v>575</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="13" t="inlineStr"/>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="14" t="inlineStr"/>
+      <c r="K17" s="7" t="n">
+        <v>799.9</v>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>814.9</v>
+      </c>
+      <c r="N17" s="33" t="n">
+        <v>-0.018</v>
+      </c>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P17" s="13" t="inlineStr">
@@ -1608,54 +1608,44 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>10050653</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>0</v>
+        <v>1517.04</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>740.72</v>
+        <v>2380.47</v>
       </c>
       <c r="F18" s="20" t="n">
-        <v>-740.72</v>
+        <v>-863.4299999999999</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>-1</v>
+        <v>-0.363</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>2647</v>
-      </c>
-      <c r="I18" s="30" t="n">
-        <v>2.1</v>
+        <v>8275</v>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>6.57</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K18" s="19" t="n">
-        <v>1347.91</v>
-      </c>
-      <c r="L18" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M18" s="19" t="n">
-        <v>1347.89</v>
-      </c>
-      <c r="N18" s="33" t="n">
-        <v>0</v>
-      </c>
+      <c r="K18" s="24" t="inlineStr"/>
+      <c r="L18" s="25" t="inlineStr"/>
+      <c r="M18" s="24" t="inlineStr"/>
+      <c r="N18" s="26" t="inlineStr"/>
       <c r="O18" s="25" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P18" s="25" t="inlineStr">
@@ -1675,54 +1665,54 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10024521</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
+        <v>1698</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>2528.91</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>-830.91</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>-0.329</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>3321</v>
+      </c>
+      <c r="I19" s="28" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N19" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>714.72</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>-714.72</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>575</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>799.9</v>
-      </c>
-      <c r="L19" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>814.9</v>
-      </c>
-      <c r="N19" s="29" t="n">
-        <v>-0.018</v>
-      </c>
       <c r="O19" s="13" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P19" s="13" t="inlineStr">
@@ -1732,7 +1722,7 @@
       </c>
       <c r="Q19" s="15" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1742,39 +1732,39 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>10025745</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>0</v>
+        <v>339.95</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>658.5700000000001</v>
+        <v>1149.92</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>-658.5700000000001</v>
+        <v>-809.97</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>-1</v>
+        <v>-0.7040000000000001</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>122</v>
-      </c>
-      <c r="I20" s="23" t="n">
-        <v>0.1</v>
+        <v>12853</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>10.21</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K20" s="19" t="n">
-        <v>1105.6</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L20" s="25" t="inlineStr">
         <is>
@@ -1782,14 +1772,14 @@
         </is>
       </c>
       <c r="M20" s="19" t="n">
-        <v>1170.01</v>
-      </c>
-      <c r="N20" s="33" t="n">
-        <v>-0.055</v>
+        <v>61.06</v>
+      </c>
+      <c r="N20" s="32" t="n">
+        <v>0.113</v>
       </c>
       <c r="O20" s="25" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P20" s="25" t="inlineStr">
@@ -1797,9 +1787,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q20" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q20" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -1809,44 +1799,54 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10025745</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>640.83</v>
+        <v>799.65</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-640.83</v>
+        <v>-799.65</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>11806</v>
-      </c>
-      <c r="I21" s="28" t="n">
-        <v>9.380000000000001</v>
+        <v>122</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>0.1</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="inlineStr"/>
-      <c r="L21" s="13" t="inlineStr"/>
-      <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="14" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>1105.6</v>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>1170.01</v>
+      </c>
+      <c r="N21" s="33" t="n">
+        <v>-0.055</v>
+      </c>
       <c r="O21" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P21" s="13" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="Q21" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1866,54 +1866,44 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D22" s="19" t="n">
-        <v>364.38</v>
+        <v>0</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>990.4</v>
+        <v>778.1</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>-626.02</v>
+        <v>-778.1</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>-0.632</v>
+        <v>-1</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>4815</v>
-      </c>
-      <c r="I22" s="30" t="n">
-        <v>3.82</v>
+        <v>11806</v>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>9.380000000000001</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>94.98999999999999</v>
-      </c>
-      <c r="L22" s="25" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M22" s="19" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N22" s="31" t="n">
-        <v>0.904</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="inlineStr"/>
+      <c r="L22" s="25" t="inlineStr"/>
+      <c r="M22" s="24" t="inlineStr"/>
+      <c r="N22" s="26" t="inlineStr"/>
       <c r="O22" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P22" s="25" t="inlineStr">
@@ -1921,9 +1911,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q22" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+      <c r="Q22" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1933,31 +1923,31 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>339.95</v>
+        <v>25.9</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>947.05</v>
+        <v>749.38</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-607.1</v>
+        <v>-723.48</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.6409999999999999</v>
+        <v>-0.965</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>12853</v>
+        <v>22233</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>10.21</v>
+        <v>17.66</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1965,18 +1955,18 @@
         </is>
       </c>
       <c r="K23" s="7" t="n">
-        <v>67.98999999999999</v>
+        <v>25.9</v>
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N23" s="32" t="n">
-        <v>0.113</v>
+        <v>15.9</v>
+      </c>
+      <c r="N23" s="31" t="n">
+        <v>0.629</v>
       </c>
       <c r="O23" s="13" t="inlineStr">
         <is>
@@ -1990,7 +1980,7 @@
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -2000,31 +1990,31 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D24" s="19" t="n">
-        <v>25.9</v>
+        <v>715.96</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>617.17</v>
+        <v>1405.96</v>
       </c>
       <c r="F24" s="20" t="n">
-        <v>-591.27</v>
+        <v>-690</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>-0.958</v>
+        <v>-0.491</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>22233</v>
-      </c>
-      <c r="I24" s="30" t="n">
-        <v>17.66</v>
+        <v>2931</v>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>2.33</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -2032,7 +2022,7 @@
         </is>
       </c>
       <c r="K24" s="19" t="n">
-        <v>25.9</v>
+        <v>218.67</v>
       </c>
       <c r="L24" s="25" t="inlineStr">
         <is>
@@ -2040,10 +2030,10 @@
         </is>
       </c>
       <c r="M24" s="19" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N24" s="31" t="n">
-        <v>0.629</v>
+        <v>197.18</v>
+      </c>
+      <c r="N24" s="32" t="n">
+        <v>0.109</v>
       </c>
       <c r="O24" s="25" t="inlineStr">
         <is>
@@ -2057,7 +2047,7 @@
       </c>
       <c r="Q24" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -2067,44 +2057,54 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0</v>
+        <v>577.28</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>546.88</v>
+        <v>1264.46</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-546.88</v>
+        <v>-687.1799999999999</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-1</v>
+        <v>-0.5429999999999999</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>30285</v>
+        <v>3992</v>
       </c>
       <c r="I25" s="28" t="n">
-        <v>24.05</v>
+        <v>3.17</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K25" s="12" t="inlineStr"/>
-      <c r="L25" s="13" t="inlineStr"/>
-      <c r="M25" s="12" t="inlineStr"/>
-      <c r="N25" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="N25" s="31" t="n">
+        <v>0.396</v>
+      </c>
       <c r="O25" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P25" s="13" t="inlineStr">
@@ -2112,9 +2112,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q25" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -2124,31 +2124,31 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>10053166</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>OZIVY 1MG 2CAN 3ML EMS</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D26" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>474.64</v>
+        <v>664.03</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>-474.64</v>
+        <v>-664.03</v>
       </c>
       <c r="G26" s="21" t="n">
         <v>-1</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>2941</v>
-      </c>
-      <c r="I26" s="30" t="n">
-        <v>2.34</v>
+        <v>30285</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <v>24.05</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="Q26" s="27" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2181,31 +2181,31 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>340.2</v>
+        <v>228.1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>808.92</v>
+        <v>820.23</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-468.72</v>
+        <v>-592.13</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.579</v>
+        <v>-0.722</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>11106</v>
+        <v>9864</v>
       </c>
       <c r="I27" s="28" t="n">
-        <v>8.82</v>
+        <v>7.83</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -2238,54 +2238,44 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10053166</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>OZIVY 1MG 2CAN 3ML EMS</t>
         </is>
       </c>
       <c r="D28" s="19" t="n">
-        <v>577.28</v>
+        <v>0</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>1041.39</v>
+        <v>576.3200000000001</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>-464.11</v>
+        <v>-576.3200000000001</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>-0.446</v>
+        <v>-1</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>3992</v>
-      </c>
-      <c r="I28" s="30" t="n">
-        <v>3.17</v>
+        <v>2941</v>
+      </c>
+      <c r="I28" s="29" t="n">
+        <v>2.34</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K28" s="19" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="L28" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>107</v>
-      </c>
-      <c r="N28" s="31" t="n">
-        <v>0.396</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr"/>
+      <c r="L28" s="25" t="inlineStr"/>
+      <c r="M28" s="24" t="inlineStr"/>
+      <c r="N28" s="26" t="inlineStr"/>
       <c r="O28" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P28" s="25" t="inlineStr">
@@ -2293,9 +2283,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q28" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+      <c r="Q28" s="27" t="inlineStr">
+        <is>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -2305,40 +2295,46 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>100009772</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>FERINJECT 50MG/ML 1FR/AMP 10ML BLANVER</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>228.1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>675.53</v>
+        <v>509.9</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-447.43</v>
+        <v>-509.9</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-0.662</v>
+        <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>9864</v>
-      </c>
-      <c r="I29" s="28" t="n">
-        <v>7.83</v>
+        <v>510</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0.41</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr"/>
-      <c r="L29" s="13" t="inlineStr"/>
-      <c r="M29" s="12" t="inlineStr"/>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>719.9</v>
+      </c>
       <c r="N29" s="14" t="inlineStr"/>
       <c r="O29" s="13" t="inlineStr">
         <is>
@@ -2352,7 +2348,7 @@
       </c>
       <c r="Q29" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2362,31 +2358,31 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10001098</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>1517.04</v>
+        <v>610.59</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>1960.51</v>
+        <v>1065.39</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>-443.47</v>
+        <v>-454.8</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>-0.226</v>
+        <v>-0.427</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>8275</v>
-      </c>
-      <c r="I30" s="30" t="n">
-        <v>6.57</v>
+        <v>8492</v>
+      </c>
+      <c r="I30" s="29" t="n">
+        <v>6.75</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -2419,54 +2415,44 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>100008756</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>LEITE NEOCATE LCP 400G DANONE</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>715.96</v>
+        <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>1157.92</v>
+        <v>445.88</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-441.96</v>
+        <v>-445.88</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-0.382</v>
+        <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>2931</v>
-      </c>
-      <c r="I31" s="28" t="n">
-        <v>2.33</v>
+        <v>1484</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>1.18</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>218.67</v>
-      </c>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N31" s="32" t="n">
-        <v>0.109</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="inlineStr"/>
+      <c r="L31" s="13" t="inlineStr"/>
+      <c r="M31" s="12" t="inlineStr"/>
+      <c r="N31" s="14" t="inlineStr"/>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P31" s="13" t="inlineStr">
@@ -2474,9 +2460,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+      <c r="Q31" s="15" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2486,46 +2472,40 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>100009772</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>FERINJECT 50MG/ML 1FR/AMP 10ML BLANVER</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D32" s="19" t="n">
-        <v>0</v>
+        <v>538.21</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>419.95</v>
+        <v>982.1900000000001</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>-419.95</v>
+        <v>-443.98</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>-1</v>
+        <v>-0.452</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>510</v>
-      </c>
-      <c r="I32" s="23" t="n">
-        <v>0.41</v>
+        <v>11106</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>8.82</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K32" s="24" t="inlineStr"/>
-      <c r="L32" s="25" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M32" s="19" t="n">
-        <v>719.9</v>
-      </c>
+      <c r="L32" s="25" t="inlineStr"/>
+      <c r="M32" s="24" t="inlineStr"/>
       <c r="N32" s="26" t="inlineStr"/>
       <c r="O32" s="25" t="inlineStr">
         <is>
@@ -2539,7 +2519,7 @@
       </c>
       <c r="Q32" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2549,44 +2529,54 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10053171</t>
+          <t>10033757</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XXG 54UN</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>278.89</v>
+        <v>933.9</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>664.51</v>
+        <v>1373.72</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-385.62</v>
+        <v>-439.82</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.58</v>
+        <v>-0.32</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>1454</v>
-      </c>
-      <c r="I33" s="11" t="n">
-        <v>1.15</v>
+        <v>24254</v>
+      </c>
+      <c r="I33" s="28" t="n">
+        <v>19.26</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K33" s="12" t="inlineStr"/>
-      <c r="L33" s="13" t="inlineStr"/>
-      <c r="M33" s="12" t="inlineStr"/>
-      <c r="N33" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="N33" s="31" t="n">
+        <v>0.165</v>
+      </c>
       <c r="O33" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P33" s="13" t="inlineStr">
@@ -2594,9 +2584,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q33" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 72.90)</t>
         </is>
       </c>
     </row>
@@ -2606,54 +2596,44 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>10033757</t>
+          <t>10052540</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XXG 54UN</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>764.1</v>
+        <v>454.66</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>1131.37</v>
+        <v>891.2</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>-367.27</v>
+        <v>-436.54</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>-0.325</v>
+        <v>-0.49</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>24254</v>
-      </c>
-      <c r="I34" s="30" t="n">
-        <v>19.26</v>
+        <v>2601</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <v>2.07</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K34" s="19" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="L34" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M34" s="19" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="N34" s="31" t="n">
-        <v>0.165</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="inlineStr"/>
+      <c r="L34" s="25" t="inlineStr"/>
+      <c r="M34" s="24" t="inlineStr"/>
+      <c r="N34" s="26" t="inlineStr"/>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P34" s="25" t="inlineStr">
@@ -2661,9 +2641,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q34" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 72.90)</t>
+      <c r="Q34" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2673,35 +2653,35 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>100008756</t>
+          <t>100008085</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>LEITE NEOCATE LCP 400G DANONE</t>
+          <t>ELIQUIS 5MG 60TBS PFIZER</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>367.22</v>
+        <v>440.65</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-367.22</v>
+        <v>-434.67</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-1</v>
+        <v>-0.986</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>1484</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>1.18</v>
+        <v>2887</v>
+      </c>
+      <c r="I35" s="28" t="n">
+        <v>2.29</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr"/>
@@ -2720,7 +2700,7 @@
       </c>
       <c r="Q35" s="15" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2730,46 +2710,40 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>10035030</t>
+          <t>10044679</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>APTANUTRI PREMIUM 3 800G 30% DESC 2UN DANONE</t>
+          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>135.99</v>
+        <v>0</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>486.03</v>
+        <v>412.32</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>-350.04</v>
+        <v>-412.32</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>-0.72</v>
+        <v>-1</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>3103</v>
-      </c>
-      <c r="I36" s="30" t="n">
-        <v>2.46</v>
+        <v>324</v>
+      </c>
+      <c r="I36" s="23" t="n">
+        <v>0.26</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K36" s="24" t="inlineStr"/>
-      <c r="L36" s="25" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M36" s="19" t="n">
-        <v>125.9</v>
-      </c>
+      <c r="L36" s="25" t="inlineStr"/>
+      <c r="M36" s="24" t="inlineStr"/>
       <c r="N36" s="26" t="inlineStr"/>
       <c r="O36" s="25" t="inlineStr">
         <is>
@@ -2783,7 +2757,7 @@
       </c>
       <c r="Q36" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2793,31 +2767,31 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10001098</t>
+          <t>10041082</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>532.79</v>
+        <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>877.4400000000001</v>
+        <v>405.25</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-344.65</v>
+        <v>-405.25</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.393</v>
+        <v>-1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>8492</v>
+        <v>5609</v>
       </c>
       <c r="I37" s="28" t="n">
-        <v>6.75</v>
+        <v>4.46</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2850,44 +2824,54 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>10044679</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>0</v>
+        <v>797.6799999999999</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>339.58</v>
+        <v>1202.55</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>-339.58</v>
+        <v>-404.87</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>-1</v>
+        <v>-0.337</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>324</v>
-      </c>
-      <c r="I38" s="23" t="n">
-        <v>0.26</v>
+        <v>4815</v>
+      </c>
+      <c r="I38" s="29" t="n">
+        <v>3.82</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K38" s="24" t="inlineStr"/>
-      <c r="L38" s="25" t="inlineStr"/>
-      <c r="M38" s="24" t="inlineStr"/>
-      <c r="N38" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L38" s="25" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M38" s="19" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="N38" s="32" t="n">
+        <v>0.904</v>
+      </c>
       <c r="O38" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P38" s="25" t="inlineStr">
@@ -2895,9 +2879,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q38" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q38" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -2907,44 +2891,54 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>100011549</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>376.93</v>
+        <v>936.36</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>711.5</v>
+        <v>1327.05</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-334.57</v>
+        <v>-390.69</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.47</v>
+        <v>-0.294</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7665</v>
-      </c>
-      <c r="I39" s="28" t="n">
-        <v>6.09</v>
+        <v>837</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>0.66</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K39" s="12" t="inlineStr"/>
-      <c r="L39" s="13" t="inlineStr"/>
-      <c r="M39" s="12" t="inlineStr"/>
-      <c r="N39" s="14" t="inlineStr"/>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>315.46</v>
+      </c>
+      <c r="L39" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="N39" s="31" t="n">
+        <v>0.333</v>
+      </c>
       <c r="O39" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P39" s="13" t="inlineStr">
@@ -2952,9 +2946,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q39" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -2964,44 +2958,54 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>10041082</t>
+          <t>10038798</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
+          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
         </is>
       </c>
       <c r="D40" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>333.75</v>
+        <v>364.08</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>-333.75</v>
+        <v>-364.08</v>
       </c>
       <c r="G40" s="21" t="n">
         <v>-1</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>5609</v>
-      </c>
-      <c r="I40" s="30" t="n">
-        <v>4.46</v>
+        <v>1623</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>1.29</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K40" s="24" t="inlineStr"/>
-      <c r="L40" s="25" t="inlineStr"/>
-      <c r="M40" s="24" t="inlineStr"/>
-      <c r="N40" s="26" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>180.79</v>
+      </c>
+      <c r="L40" s="25" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M40" s="19" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="N40" s="32" t="n">
+        <v>0.028</v>
+      </c>
       <c r="O40" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P40" s="25" t="inlineStr">
@@ -3011,7 +3015,7 @@
       </c>
       <c r="Q40" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3021,50 +3025,50 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>100001425</t>
+          <t>10100048</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
+          <t>RITALINA LA 10MG 30CP NOVARTIS (A3)</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>79.7</v>
+        <v>121.04</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>379.74</v>
+        <v>481.39</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-300.04</v>
+        <v>-360.35</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-0.79</v>
+        <v>-0.7490000000000001</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>13421</v>
+        <v>3843</v>
       </c>
       <c r="I41" s="28" t="n">
-        <v>10.66</v>
+        <v>3.05</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K41" s="7" t="n">
-        <v>29.9</v>
+        <v>137.55</v>
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="N41" s="32" t="n">
-        <v>0.035</v>
+        <v>120.9</v>
+      </c>
+      <c r="N41" s="31" t="n">
+        <v>0.138</v>
       </c>
       <c r="O41" s="13" t="inlineStr">
         <is>
@@ -3076,9 +3080,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q41" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 120.90)</t>
         </is>
       </c>
     </row>
@@ -3088,31 +3092,31 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>10038798</t>
+          <t>10040748</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
+          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D42" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>299.85</v>
+        <v>352.59</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>-299.85</v>
+        <v>-352.59</v>
       </c>
       <c r="G42" s="21" t="n">
         <v>-1</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>1623</v>
+        <v>402</v>
       </c>
       <c r="I42" s="23" t="n">
-        <v>1.29</v>
+        <v>0.32</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -3120,22 +3124,22 @@
         </is>
       </c>
       <c r="K42" s="19" t="n">
-        <v>180.79</v>
+        <v>1298.54</v>
       </c>
       <c r="L42" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M42" s="19" t="n">
-        <v>175.9</v>
-      </c>
-      <c r="N42" s="31" t="n">
-        <v>0.028</v>
+        <v>1298.54</v>
+      </c>
+      <c r="N42" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="O42" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P42" s="25" t="inlineStr">
@@ -3155,50 +3159,54 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10044745</t>
+          <t>10101654</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
+          <t>NAN COMFOR 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>264.17</v>
+        <v>583.98</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>555.41</v>
+        <v>926.84</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-291.24</v>
+        <v>-342.86</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-0.524</v>
+        <v>-0.37</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>5858</v>
+        <v>13534</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>4.65</v>
+        <v>10.75</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K43" s="12" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>87.48999999999999</v>
+      </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
-        <v>83.92</v>
-      </c>
-      <c r="N43" s="14" t="inlineStr"/>
+        <v>79.98999999999999</v>
+      </c>
+      <c r="N43" s="31" t="n">
+        <v>0.094</v>
+      </c>
       <c r="O43" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P43" s="13" t="inlineStr">
@@ -3206,9 +3214,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q43" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 79.99)</t>
         </is>
       </c>
     </row>
@@ -3218,54 +3226,54 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>10040748</t>
+          <t>100022270</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
+          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
         </is>
       </c>
       <c r="D44" s="19" t="n">
-        <v>0</v>
+        <v>225.46</v>
       </c>
       <c r="E44" s="19" t="n">
-        <v>290.39</v>
+        <v>565.29</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>-290.39</v>
+        <v>-339.83</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>-1</v>
+        <v>-0.601</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>402</v>
-      </c>
-      <c r="I44" s="23" t="n">
-        <v>0.32</v>
+        <v>1962</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>1.56</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K44" s="19" t="n">
-        <v>1298.54</v>
+        <v>185.61</v>
       </c>
       <c r="L44" s="25" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M44" s="19" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N44" s="33" t="n">
-        <v>0</v>
+        <v>158.66</v>
+      </c>
+      <c r="N44" s="32" t="n">
+        <v>0.17</v>
       </c>
       <c r="O44" s="25" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P44" s="25" t="inlineStr">
@@ -3273,9 +3281,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q44" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q44" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
         </is>
       </c>
     </row>
@@ -3285,44 +3293,54 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10052540</t>
+          <t>100001425</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
+          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>454.66</v>
+        <v>129.5</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>733.98</v>
+        <v>461.08</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-279.32</v>
+        <v>-331.58</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-0.381</v>
+        <v>-0.7190000000000001</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>2601</v>
+        <v>13421</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>2.07</v>
+        <v>10.66</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr"/>
-      <c r="L45" s="13" t="inlineStr"/>
-      <c r="M45" s="12" t="inlineStr"/>
-      <c r="N45" s="14" t="inlineStr"/>
+      <c r="K45" s="7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="L45" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="N45" s="31" t="n">
+        <v>0.035</v>
+      </c>
       <c r="O45" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P45" s="13" t="inlineStr">
@@ -3342,54 +3360,44 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>10100048</t>
+          <t>999705</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>RITALINA LA 10MG 30CP NOVARTIS (A3)</t>
+          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
         </is>
       </c>
       <c r="D46" s="19" t="n">
-        <v>121.04</v>
+        <v>0</v>
       </c>
       <c r="E46" s="19" t="n">
-        <v>396.46</v>
+        <v>327.64</v>
       </c>
       <c r="F46" s="20" t="n">
-        <v>-275.42</v>
+        <v>-327.64</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>-0.695</v>
+        <v>-1</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>3843</v>
-      </c>
-      <c r="I46" s="30" t="n">
-        <v>3.05</v>
+        <v>37</v>
+      </c>
+      <c r="I46" s="23" t="n">
+        <v>0.03</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K46" s="19" t="n">
-        <v>137.55</v>
-      </c>
-      <c r="L46" s="25" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M46" s="19" t="n">
-        <v>120.9</v>
-      </c>
-      <c r="N46" s="31" t="n">
-        <v>0.138</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="inlineStr"/>
+      <c r="L46" s="25" t="inlineStr"/>
+      <c r="M46" s="24" t="inlineStr"/>
+      <c r="N46" s="26" t="inlineStr"/>
       <c r="O46" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P46" s="25" t="inlineStr">
@@ -3397,9 +3405,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q46" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 120.90)</t>
+      <c r="Q46" s="27" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3409,31 +3417,31 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>100011551</t>
+          <t>100008511</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>ANDROGEL 50MG 10MG/G GEL 30ENV 5G</t>
+          <t>APTAMIL PEPTI 800G DANONE</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>272.33</v>
+        <v>323.29</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-272.33</v>
+        <v>-323.29</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>1698</v>
+        <v>1353</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>1.35</v>
+        <v>1.07</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3441,18 +3449,18 @@
         </is>
       </c>
       <c r="K47" s="7" t="n">
-        <v>343.63</v>
+        <v>307.99</v>
       </c>
       <c r="L47" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>301.16</v>
-      </c>
-      <c r="N47" s="32" t="n">
-        <v>0.141</v>
+        <v>230.99</v>
+      </c>
+      <c r="N47" s="31" t="n">
+        <v>0.333</v>
       </c>
       <c r="O47" s="13" t="inlineStr">
         <is>
@@ -3466,7 +3474,7 @@
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Farmaciasnissei R$ 301.16)</t>
+          <t>Reprecificar e Remanejar (Amazon R$ 230.99)</t>
         </is>
       </c>
     </row>
@@ -3476,54 +3484,50 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>10102163</t>
+          <t>10044745</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>QLAIRA 26CP+2CP REV BIOLAB</t>
+          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
         </is>
       </c>
       <c r="D48" s="19" t="n">
-        <v>794.09</v>
+        <v>355.26</v>
       </c>
       <c r="E48" s="19" t="n">
-        <v>1065.25</v>
+        <v>674.38</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>-271.16</v>
+        <v>-319.12</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>-0.255</v>
+        <v>-0.473</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>16877</v>
-      </c>
-      <c r="I48" s="30" t="n">
-        <v>13.41</v>
+        <v>5858</v>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>4.65</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K48" s="19" t="n">
-        <v>74.22</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="inlineStr"/>
       <c r="L48" s="25" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M48" s="19" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N48" s="31" t="n">
-        <v>0.333</v>
-      </c>
+        <v>83.92</v>
+      </c>
+      <c r="N48" s="26" t="inlineStr"/>
       <c r="O48" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P48" s="25" t="inlineStr">
@@ -3531,9 +3535,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q48" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 55.67)</t>
+      <c r="Q48" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3543,54 +3547,50 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10040738</t>
+          <t>10089756</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>LYBERDIA 40MG 50ML GOTAS EMS (A3)</t>
+          <t>RITALINA 10MG 60CP NOVARTIS (A3)</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0</v>
+        <v>-8.34</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>270.2</v>
+        <v>305.34</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-270.2</v>
+        <v>-313.68</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-1</v>
+        <v>-1.027</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>2560</v>
+        <v>7860</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>2.03</v>
+        <v>6.24</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K49" s="7" t="n">
-        <v>567.02</v>
-      </c>
+      <c r="K49" s="12" t="inlineStr"/>
       <c r="L49" s="13" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>567.02</v>
-      </c>
-      <c r="N49" s="29" t="n">
-        <v>0</v>
-      </c>
+        <v>92.95</v>
+      </c>
+      <c r="N49" s="14" t="inlineStr"/>
       <c r="O49" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P49" s="13" t="inlineStr">
@@ -3610,35 +3610,35 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>999705</t>
+          <t>10028321</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
+          <t>PREGABALINA 150MG 30CAP GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D50" s="19" t="n">
-        <v>0</v>
+        <v>493.37</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>269.84</v>
+        <v>805</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>-269.84</v>
+        <v>-311.63</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>-1</v>
+        <v>-0.387</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>37</v>
-      </c>
-      <c r="I50" s="23" t="n">
-        <v>0.03</v>
+        <v>5385</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>4.28</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K50" s="24" t="inlineStr"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="Q50" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3676,16 +3676,16 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>55.73</v>
+        <v>83.09</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>324.01</v>
+        <v>393.42</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-268.28</v>
+        <v>-310.33</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.828</v>
+        <v>-0.789</v>
       </c>
       <c r="H51" s="10" t="n">
         <v>18637</v>
@@ -3724,54 +3724,44 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>10101654</t>
+          <t>10041858</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>NAN COMFOR 2 800G NESTLE</t>
+          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
         </is>
       </c>
       <c r="D52" s="19" t="n">
-        <v>496.49</v>
+        <v>169.9</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>763.33</v>
+        <v>475.26</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>-266.84</v>
+        <v>-305.36</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>-0.35</v>
+        <v>-0.643</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>13534</v>
-      </c>
-      <c r="I52" s="30" t="n">
-        <v>10.75</v>
+        <v>646</v>
+      </c>
+      <c r="I52" s="23" t="n">
+        <v>0.51</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K52" s="19" t="n">
-        <v>87.48999999999999</v>
-      </c>
-      <c r="L52" s="25" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M52" s="19" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="N52" s="31" t="n">
-        <v>0.094</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K52" s="24" t="inlineStr"/>
+      <c r="L52" s="25" t="inlineStr"/>
+      <c r="M52" s="24" t="inlineStr"/>
+      <c r="N52" s="26" t="inlineStr"/>
       <c r="O52" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P52" s="25" t="inlineStr">
@@ -3779,9 +3769,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q52" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 79.99)</t>
+      <c r="Q52" s="27" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3791,31 +3781,31 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>100008511</t>
+          <t>10050453</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>APTAMIL PEPTI 800G DANONE</t>
+          <t>HORMUS 250MG/ML SOL INJ 2AMP 4ML EUROFARMA (C5)</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>266.26</v>
+        <v>304.63</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-266.26</v>
+        <v>-304.63</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>1353</v>
+        <v>834</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>1.07</v>
+        <v>0.66</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3823,18 +3813,18 @@
         </is>
       </c>
       <c r="K53" s="7" t="n">
-        <v>307.99</v>
+        <v>957.25</v>
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M53" s="7" t="n">
-        <v>230.99</v>
-      </c>
-      <c r="N53" s="32" t="n">
-        <v>0.333</v>
+        <v>438.02</v>
+      </c>
+      <c r="N53" s="31" t="n">
+        <v>1.185</v>
       </c>
       <c r="O53" s="13" t="inlineStr">
         <is>
@@ -3848,7 +3838,7 @@
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Amazon R$ 230.99)</t>
+          <t>Reprecificar e Remanejar (Drogaraia R$ 438.02)</t>
         </is>
       </c>
     </row>
@@ -3858,54 +3848,44 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>10098096</t>
+          <t>10052934</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>FR BIGFRAL DERMA PLUS ADULTO NOTURNA G 7UN</t>
+          <t>NEBULIZADOR COMPRESSOR HC032 TRAVEL MULTILASER</t>
         </is>
       </c>
       <c r="D54" s="19" t="n">
-        <v>30.99</v>
+        <v>0</v>
       </c>
       <c r="E54" s="19" t="n">
-        <v>291.66</v>
+        <v>296.33</v>
       </c>
       <c r="F54" s="20" t="n">
-        <v>-260.67</v>
+        <v>-296.33</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>-0.894</v>
+        <v>-1</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>7280</v>
-      </c>
-      <c r="I54" s="30" t="n">
-        <v>5.78</v>
+        <v>3068</v>
+      </c>
+      <c r="I54" s="29" t="n">
+        <v>2.44</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K54" s="19" t="n">
-        <v>30.99</v>
-      </c>
-      <c r="L54" s="25" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M54" s="19" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="N54" s="31" t="n">
-        <v>0.245</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K54" s="24" t="inlineStr"/>
+      <c r="L54" s="25" t="inlineStr"/>
+      <c r="M54" s="24" t="inlineStr"/>
+      <c r="N54" s="26" t="inlineStr"/>
       <c r="O54" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P54" s="25" t="inlineStr">
@@ -3913,9 +3893,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q54" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 24.90)</t>
+      <c r="Q54" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -291,6 +291,9 @@
     <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -301,9 +304,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 13:54:09 (13:54) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 14:54:03 (14:54) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4988.39</v>
+        <v>5935.91</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-4988.39</v>
+        <v>-5935.91</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>-1</v>
@@ -851,7 +851,7 @@
       </c>
       <c r="P5" s="13" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
       <c r="Q5" s="15" t="inlineStr">
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>3325.59</v>
+        <v>3957.27</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>-3325.59</v>
+        <v>-3957.27</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>-1</v>
@@ -923,44 +923,54 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10046653</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>MOUNJARO 5MG 4CAN APLIC LILLY</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>84.90000000000001</v>
+        <v>57044.61</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1624.92</v>
+        <v>59099.37</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-1540.02</v>
+        <v>-2054.76</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.948</v>
+        <v>-0.035</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>26223</v>
+        <v>11192</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>20.83</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr"/>
-      <c r="L7" s="13" t="inlineStr"/>
-      <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="14" t="inlineStr"/>
+      <c r="K7" s="7" t="n">
+        <v>2382.23</v>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>2382.23</v>
+      </c>
+      <c r="N7" s="29" t="n">
+        <v>0</v>
+      </c>
       <c r="O7" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P7" s="13" t="inlineStr">
@@ -970,7 +980,7 @@
       </c>
       <c r="Q7" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -989,21 +999,21 @@
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>3034</v>
+        <v>3343</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>4459.68</v>
+        <v>5306.77</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>-1425.68</v>
+        <v>-1963.77</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>-0.32</v>
+        <v>-0.37</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>9409</v>
       </c>
-      <c r="I8" s="29" t="n">
+      <c r="I8" s="30" t="n">
         <v>7.47</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
@@ -1022,7 +1032,7 @@
       <c r="M8" s="19" t="n">
         <v>988.22</v>
       </c>
-      <c r="N8" s="30" t="n">
+      <c r="N8" s="31" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="25" t="inlineStr">
@@ -1047,54 +1057,44 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>996.92</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2239.89</v>
+        <v>1933.56</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1242.97</v>
+        <v>-1848.66</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.555</v>
+        <v>-0.956</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>2446</v>
+        <v>26223</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>1.94</v>
+        <v>20.83</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N9" s="31" t="n">
-        <v>1.132</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="12" t="inlineStr"/>
+      <c r="N9" s="14" t="inlineStr"/>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P9" s="13" t="inlineStr">
@@ -1102,9 +1102,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+      <c r="Q9" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1114,31 +1114,31 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>205.03</v>
+        <v>221.97</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>1445.09</v>
+        <v>1709.18</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-1240.06</v>
+        <v>-1487.21</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>-0.858</v>
+        <v>-0.87</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>3146</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>2.5</v>
+        <v>39477</v>
+      </c>
+      <c r="I10" s="30" t="n">
+        <v>31.36</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -1171,44 +1171,54 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>221.97</v>
+        <v>1296.62</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1436.35</v>
+        <v>2665.35</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-1214.38</v>
+        <v>-1368.73</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.845</v>
+        <v>-0.514</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>39477</v>
+        <v>2446</v>
       </c>
       <c r="I11" s="28" t="n">
-        <v>31.36</v>
+        <v>1.94</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr"/>
-      <c r="L11" s="13" t="inlineStr"/>
-      <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="N11" s="32" t="n">
+        <v>1.132</v>
+      </c>
       <c r="O11" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P11" s="13" t="inlineStr">
@@ -1216,9 +1226,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q11" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -1228,54 +1238,44 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>335.3</v>
+        <v>404</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>1481.41</v>
+        <v>1719.58</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>-1146.11</v>
+        <v>-1315.58</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.774</v>
+        <v>-0.765</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>8909</v>
-      </c>
-      <c r="I12" s="29" t="n">
-        <v>7.08</v>
+        <v>3146</v>
+      </c>
+      <c r="I12" s="30" t="n">
+        <v>2.5</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>108.49</v>
-      </c>
-      <c r="L12" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M12" s="19" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N12" s="32" t="n">
-        <v>0.111</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K12" s="24" t="inlineStr"/>
+      <c r="L12" s="25" t="inlineStr"/>
+      <c r="M12" s="24" t="inlineStr"/>
+      <c r="N12" s="26" t="inlineStr"/>
       <c r="O12" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P12" s="25" t="inlineStr">
@@ -1283,9 +1283,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q12" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+      <c r="Q12" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1295,60 +1295,64 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10041248</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>CREATINA MONOHIDRATADA 300G DUX</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>249.17</v>
+        <v>1698</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1228.33</v>
+        <v>3009.27</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-979.16</v>
+        <v>-1311.27</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.797</v>
+        <v>-0.436</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>4427</v>
+        <v>3321</v>
       </c>
       <c r="I13" s="28" t="n">
-        <v>3.52</v>
+        <v>2.64</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr"/>
+      <c r="K13" s="7" t="n">
+        <v>1298.54</v>
+      </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="N13" s="14" t="inlineStr"/>
+        <v>1298.54</v>
+      </c>
+      <c r="N13" s="29" t="n">
+        <v>0</v>
+      </c>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q13" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1358,45 +1362,45 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>10025098</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0</v>
+        <v>249.17</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>941.23</v>
+        <v>1461.64</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>-941.23</v>
+        <v>-1212.47</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>-1</v>
+        <v>-0.83</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>204</v>
-      </c>
-      <c r="I14" s="23" t="n">
-        <v>0.16</v>
+        <v>4427</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <v>3.52</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K14" s="24" t="inlineStr"/>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M14" s="19" t="n">
-        <v>1212.9</v>
+        <v>50.25</v>
       </c>
       <c r="N14" s="26" t="inlineStr"/>
       <c r="O14" s="25" t="inlineStr">
@@ -1406,12 +1410,12 @@
       </c>
       <c r="P14" s="25" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q14" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1421,31 +1425,31 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10093877</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>MIRENA 52MG 1END+INS BAYER</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>940.1799999999999</v>
+        <v>1120.01</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-940.1799999999999</v>
+        <v>-1120.01</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>501</v>
+        <v>204</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1455,11 +1459,11 @@
       <c r="K15" s="12" t="inlineStr"/>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
-        <v>1225.89</v>
+        <v>1212.9</v>
       </c>
       <c r="N15" s="14" t="inlineStr"/>
       <c r="O15" s="13" t="inlineStr">
@@ -1469,7 +1473,7 @@
       </c>
       <c r="P15" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q15" s="15" t="inlineStr">
@@ -1484,31 +1488,31 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10093877</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>MIRENA 52MG 1END+INS BAYER</t>
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>415.06</v>
+        <v>0</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>1287.8</v>
+        <v>1118.76</v>
       </c>
       <c r="F16" s="20" t="n">
-        <v>-872.74</v>
+        <v>-1118.76</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>-0.6779999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>1270</v>
+        <v>501</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>1.01</v>
+        <v>0.4</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1516,8 +1520,14 @@
         </is>
       </c>
       <c r="K16" s="24" t="inlineStr"/>
-      <c r="L16" s="25" t="inlineStr"/>
-      <c r="M16" s="24" t="inlineStr"/>
+      <c r="L16" s="25" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M16" s="19" t="n">
+        <v>1225.89</v>
+      </c>
       <c r="N16" s="26" t="inlineStr"/>
       <c r="O16" s="25" t="inlineStr">
         <is>
@@ -1526,7 +1536,7 @@
       </c>
       <c r="P16" s="25" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q16" s="27" t="inlineStr">
@@ -1541,59 +1551,49 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10024521</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0</v>
+        <v>415.06</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>867.8099999999999</v>
+        <v>1532.41</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-867.8099999999999</v>
+        <v>-1117.35</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-1</v>
+        <v>-0.7290000000000001</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>575</v>
+        <v>1270</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.46</v>
+        <v>1.01</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K17" s="7" t="n">
-        <v>799.9</v>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>814.9</v>
-      </c>
-      <c r="N17" s="33" t="n">
-        <v>-0.018</v>
-      </c>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="13" t="inlineStr"/>
+      <c r="M17" s="12" t="inlineStr"/>
+      <c r="N17" s="14" t="inlineStr"/>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P17" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q17" s="15" t="inlineStr">
@@ -1608,54 +1608,64 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>1517.04</v>
+        <v>670.46</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>2380.47</v>
+        <v>1762.8</v>
       </c>
       <c r="F18" s="20" t="n">
-        <v>-863.4299999999999</v>
+        <v>-1092.34</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>-0.363</v>
+        <v>-0.62</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>8275</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>6.57</v>
+        <v>8909</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>7.08</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K18" s="24" t="inlineStr"/>
-      <c r="L18" s="25" t="inlineStr"/>
-      <c r="M18" s="24" t="inlineStr"/>
-      <c r="N18" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>108.49</v>
+      </c>
+      <c r="L18" s="25" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M18" s="19" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="N18" s="33" t="n">
+        <v>0.111</v>
+      </c>
       <c r="O18" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P18" s="25" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q18" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q18" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -1665,64 +1675,64 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10024521</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1698</v>
+        <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>2528.91</v>
+        <v>1032.65</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-830.91</v>
+        <v>-1032.65</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-0.329</v>
+        <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>3321</v>
-      </c>
-      <c r="I19" s="28" t="n">
-        <v>2.64</v>
+        <v>575</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>0.46</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K19" s="7" t="n">
-        <v>1298.54</v>
+        <v>799.9</v>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M19" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N19" s="33" t="n">
-        <v>0</v>
+        <v>814.9</v>
+      </c>
+      <c r="N19" s="29" t="n">
+        <v>-0.018</v>
       </c>
       <c r="O19" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P19" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q19" s="15" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1732,54 +1742,44 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>339.95</v>
+        <v>1858.64</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>1149.92</v>
+        <v>2832.63</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>-809.97</v>
+        <v>-973.99</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>-0.7040000000000001</v>
+        <v>-0.344</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>12853</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>10.21</v>
+        <v>8275</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>6.57</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="L20" s="25" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M20" s="19" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N20" s="32" t="n">
-        <v>0.113</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K20" s="24" t="inlineStr"/>
+      <c r="L20" s="25" t="inlineStr"/>
+      <c r="M20" s="24" t="inlineStr"/>
+      <c r="N20" s="26" t="inlineStr"/>
       <c r="O20" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P20" s="25" t="inlineStr">
@@ -1787,9 +1787,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q20" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+      <c r="Q20" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1799,54 +1799,54 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10025745</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0</v>
+        <v>715.96</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>799.65</v>
+        <v>1673.02</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-799.65</v>
+        <v>-957.0599999999999</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-1</v>
+        <v>-0.5720000000000001</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>122</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>0.1</v>
+        <v>2931</v>
+      </c>
+      <c r="I21" s="28" t="n">
+        <v>2.33</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>1105.6</v>
+        <v>218.67</v>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
-        <v>1170.01</v>
-      </c>
-      <c r="N21" s="33" t="n">
-        <v>-0.055</v>
+        <v>197.18</v>
+      </c>
+      <c r="N21" s="32" t="n">
+        <v>0.109</v>
       </c>
       <c r="O21" s="13" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P21" s="13" t="inlineStr">
@@ -1854,9 +1854,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q21" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -1866,44 +1866,54 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10025745</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
         </is>
       </c>
       <c r="D22" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>778.1</v>
+        <v>951.54</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>-778.1</v>
+        <v>-951.54</v>
       </c>
       <c r="G22" s="21" t="n">
         <v>-1</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>11806</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>9.380000000000001</v>
+        <v>122</v>
+      </c>
+      <c r="I22" s="23" t="n">
+        <v>0.1</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K22" s="24" t="inlineStr"/>
-      <c r="L22" s="25" t="inlineStr"/>
-      <c r="M22" s="24" t="inlineStr"/>
-      <c r="N22" s="26" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>1105.6</v>
+      </c>
+      <c r="L22" s="25" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M22" s="19" t="n">
+        <v>1170.01</v>
+      </c>
+      <c r="N22" s="31" t="n">
+        <v>-0.055</v>
+      </c>
       <c r="O22" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P22" s="25" t="inlineStr">
@@ -1913,7 +1923,7 @@
       </c>
       <c r="Q22" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1923,54 +1933,44 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>749.38</v>
+        <v>925.9</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-723.48</v>
+        <v>-925.9</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.965</v>
+        <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>22233</v>
+        <v>11806</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>17.66</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N23" s="31" t="n">
-        <v>0.629</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="inlineStr"/>
+      <c r="L23" s="13" t="inlineStr"/>
+      <c r="M23" s="12" t="inlineStr"/>
+      <c r="N23" s="14" t="inlineStr"/>
       <c r="O23" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P23" s="13" t="inlineStr">
@@ -1978,9 +1978,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+      <c r="Q23" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1990,31 +1990,31 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D24" s="19" t="n">
-        <v>715.96</v>
+        <v>463.48</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>1405.96</v>
+        <v>1368.34</v>
       </c>
       <c r="F24" s="20" t="n">
-        <v>-690</v>
+        <v>-904.86</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>-0.491</v>
+        <v>-0.6609999999999999</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>2931</v>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>2.33</v>
+        <v>12853</v>
+      </c>
+      <c r="I24" s="30" t="n">
+        <v>10.21</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -2022,18 +2022,18 @@
         </is>
       </c>
       <c r="K24" s="19" t="n">
-        <v>218.67</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L24" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M24" s="19" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N24" s="32" t="n">
-        <v>0.109</v>
+        <v>61.06</v>
+      </c>
+      <c r="N24" s="33" t="n">
+        <v>0.113</v>
       </c>
       <c r="O24" s="25" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Q24" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -2057,31 +2057,31 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>577.28</v>
+        <v>25.9</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>1264.46</v>
+        <v>891.72</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-687.1799999999999</v>
+        <v>-865.8200000000001</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.5429999999999999</v>
+        <v>-0.971</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>3992</v>
+        <v>22233</v>
       </c>
       <c r="I25" s="28" t="n">
-        <v>3.17</v>
+        <v>17.66</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -2089,18 +2089,18 @@
         </is>
       </c>
       <c r="K25" s="7" t="n">
-        <v>149.4</v>
+        <v>25.9</v>
       </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M25" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="N25" s="31" t="n">
-        <v>0.396</v>
+        <v>15.9</v>
+      </c>
+      <c r="N25" s="32" t="n">
+        <v>0.629</v>
       </c>
       <c r="O25" s="13" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -2136,10 +2136,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>664.03</v>
+        <v>790.15</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>-664.03</v>
+        <v>-790.15</v>
       </c>
       <c r="G26" s="21" t="n">
         <v>-1</v>
@@ -2147,7 +2147,7 @@
       <c r="H26" s="22" t="n">
         <v>30285</v>
       </c>
-      <c r="I26" s="29" t="n">
+      <c r="I26" s="30" t="n">
         <v>24.05</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
@@ -2181,44 +2181,54 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>228.1</v>
+        <v>801.22</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>820.23</v>
+        <v>1504.64</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-592.13</v>
+        <v>-703.42</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.722</v>
+        <v>-0.468</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>9864</v>
+        <v>3992</v>
       </c>
       <c r="I27" s="28" t="n">
-        <v>7.83</v>
+        <v>3.17</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K27" s="12" t="inlineStr"/>
-      <c r="L27" s="13" t="inlineStr"/>
-      <c r="M27" s="12" t="inlineStr"/>
-      <c r="N27" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="N27" s="32" t="n">
+        <v>0.396</v>
+      </c>
       <c r="O27" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr">
@@ -2226,9 +2236,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q27" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -2238,31 +2248,31 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>10053166</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>OZIVY 1MG 2CAN 3ML EMS</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D28" s="19" t="n">
-        <v>0</v>
+        <v>287.9</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>576.3200000000001</v>
+        <v>976.03</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>-576.3200000000001</v>
+        <v>-688.13</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>-1</v>
+        <v>-0.705</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>2941</v>
-      </c>
-      <c r="I28" s="29" t="n">
-        <v>2.34</v>
+        <v>9864</v>
+      </c>
+      <c r="I28" s="30" t="n">
+        <v>7.83</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -2285,7 +2295,7 @@
       </c>
       <c r="Q28" s="27" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2295,50 +2305,54 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>100009772</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>FERINJECT 50MG/ML 1FR/AMP 10ML BLANVER</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0</v>
+        <v>936.36</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>509.9</v>
+        <v>1579.12</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-509.9</v>
+        <v>-642.76</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-1</v>
+        <v>-0.407</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>510</v>
+        <v>837</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>0.41</v>
+        <v>0.66</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K29" s="12" t="inlineStr"/>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>315.46</v>
+      </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
-        <v>719.9</v>
-      </c>
-      <c r="N29" s="14" t="inlineStr"/>
+        <v>236.6</v>
+      </c>
+      <c r="N29" s="32" t="n">
+        <v>0.333</v>
+      </c>
       <c r="O29" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P29" s="13" t="inlineStr">
@@ -2346,9 +2360,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q29" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -2358,40 +2372,46 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>10001098</t>
+          <t>100009772</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
+          <t>FERINJECT 50MG/ML 1FR/AMP 10ML BLANVER</t>
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>610.59</v>
+        <v>0</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>1065.39</v>
+        <v>606.76</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>-454.8</v>
+        <v>-606.76</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>-0.427</v>
+        <v>-1</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>8492</v>
-      </c>
-      <c r="I30" s="29" t="n">
-        <v>6.75</v>
+        <v>510</v>
+      </c>
+      <c r="I30" s="23" t="n">
+        <v>0.41</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K30" s="24" t="inlineStr"/>
-      <c r="L30" s="25" t="inlineStr"/>
-      <c r="M30" s="24" t="inlineStr"/>
+      <c r="L30" s="25" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M30" s="19" t="n">
+        <v>719.9</v>
+      </c>
       <c r="N30" s="26" t="inlineStr"/>
       <c r="O30" s="25" t="inlineStr">
         <is>
@@ -2405,7 +2425,7 @@
       </c>
       <c r="Q30" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2415,35 +2435,35 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>100008756</t>
+          <t>10052540</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>LEITE NEOCATE LCP 400G DANONE</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0</v>
+        <v>454.66</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>445.88</v>
+        <v>1060.49</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-445.88</v>
+        <v>-605.83</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-1</v>
+        <v>-0.5710000000000001</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>1484</v>
-      </c>
-      <c r="I31" s="11" t="n">
-        <v>1.18</v>
+        <v>2601</v>
+      </c>
+      <c r="I31" s="28" t="n">
+        <v>2.07</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr"/>
@@ -2462,7 +2482,7 @@
       </c>
       <c r="Q31" s="15" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2472,35 +2492,35 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>100008756</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>LEITE NEOCATE LCP 400G DANONE</t>
         </is>
       </c>
       <c r="D32" s="19" t="n">
-        <v>538.21</v>
+        <v>0</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>982.1900000000001</v>
+        <v>530.5700000000001</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>-443.98</v>
+        <v>-530.5700000000001</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>-0.452</v>
+        <v>-1</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>11106</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>8.82</v>
+        <v>1484</v>
+      </c>
+      <c r="I32" s="23" t="n">
+        <v>1.18</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K32" s="24" t="inlineStr"/>
@@ -2519,7 +2539,7 @@
       </c>
       <c r="Q32" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2529,54 +2549,44 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10033757</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XXG 54UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>933.9</v>
+        <v>645.39</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1373.72</v>
+        <v>1168.76</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-439.82</v>
+        <v>-523.37</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.32</v>
+        <v>-0.448</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>24254</v>
+        <v>11106</v>
       </c>
       <c r="I33" s="28" t="n">
-        <v>19.26</v>
+        <v>8.82</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="L33" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M33" s="7" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="N33" s="31" t="n">
-        <v>0.165</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K33" s="12" t="inlineStr"/>
+      <c r="L33" s="13" t="inlineStr"/>
+      <c r="M33" s="12" t="inlineStr"/>
+      <c r="N33" s="14" t="inlineStr"/>
       <c r="O33" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P33" s="13" t="inlineStr">
@@ -2584,9 +2594,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 72.90)</t>
+      <c r="Q33" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2596,31 +2606,31 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>10052540</t>
+          <t>100008085</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
+          <t>ELIQUIS 5MG 60TBS PFIZER</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>454.66</v>
+        <v>5.98</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>891.2</v>
+        <v>524.35</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>-436.54</v>
+        <v>-518.37</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>-0.49</v>
+        <v>-0.9890000000000001</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>2601</v>
-      </c>
-      <c r="I34" s="29" t="n">
-        <v>2.07</v>
+        <v>2887</v>
+      </c>
+      <c r="I34" s="30" t="n">
+        <v>2.29</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -2653,31 +2663,31 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>100008085</t>
+          <t>10001098</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>ELIQUIS 5MG 60TBS PFIZER</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>5.98</v>
+        <v>754.77</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>440.65</v>
+        <v>1267.76</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-434.67</v>
+        <v>-512.99</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-0.986</v>
+        <v>-0.405</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>2887</v>
+        <v>8492</v>
       </c>
       <c r="I35" s="28" t="n">
-        <v>2.29</v>
+        <v>6.75</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2722,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>412.32</v>
+        <v>490.64</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>-412.32</v>
+        <v>-490.64</v>
       </c>
       <c r="G36" s="21" t="n">
         <v>-1</v>
@@ -2779,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>405.25</v>
+        <v>482.22</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-405.25</v>
+        <v>-482.22</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>-1</v>
@@ -2824,54 +2834,44 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10099241</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>NAN COMFOR 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>797.6799999999999</v>
+        <v>766.1</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>1202.55</v>
+        <v>1227.71</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>-404.87</v>
+        <v>-461.61</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>-0.337</v>
+        <v>-0.376</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>4815</v>
-      </c>
-      <c r="I38" s="29" t="n">
-        <v>3.82</v>
+        <v>13024</v>
+      </c>
+      <c r="I38" s="30" t="n">
+        <v>10.34</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K38" s="19" t="n">
-        <v>94.98999999999999</v>
-      </c>
-      <c r="L38" s="25" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M38" s="19" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N38" s="32" t="n">
-        <v>0.904</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K38" s="24" t="inlineStr"/>
+      <c r="L38" s="25" t="inlineStr"/>
+      <c r="M38" s="24" t="inlineStr"/>
+      <c r="N38" s="26" t="inlineStr"/>
       <c r="O38" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P38" s="25" t="inlineStr">
@@ -2879,9 +2879,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q38" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+      <c r="Q38" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2891,54 +2891,50 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10044745</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>936.36</v>
+        <v>355.26</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1327.05</v>
+        <v>802.48</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-390.69</v>
+        <v>-447.22</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.294</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>837</v>
-      </c>
-      <c r="I39" s="11" t="n">
-        <v>0.66</v>
+        <v>5858</v>
+      </c>
+      <c r="I39" s="28" t="n">
+        <v>4.65</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>315.46</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K39" s="12" t="inlineStr"/>
       <c r="L39" s="13" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M39" s="7" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N39" s="31" t="n">
-        <v>0.333</v>
-      </c>
+        <v>83.92</v>
+      </c>
+      <c r="N39" s="14" t="inlineStr"/>
       <c r="O39" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P39" s="13" t="inlineStr">
@@ -2946,9 +2942,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+      <c r="Q39" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2958,50 +2954,50 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>10038798</t>
+          <t>100022270</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
+          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
         </is>
       </c>
       <c r="D40" s="19" t="n">
-        <v>0</v>
+        <v>225.46</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>364.08</v>
+        <v>672.67</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>-364.08</v>
+        <v>-447.21</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>-1</v>
+        <v>-0.665</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>1623</v>
-      </c>
-      <c r="I40" s="23" t="n">
-        <v>1.29</v>
+        <v>1962</v>
+      </c>
+      <c r="I40" s="30" t="n">
+        <v>1.56</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K40" s="19" t="n">
-        <v>180.79</v>
+        <v>185.61</v>
       </c>
       <c r="L40" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M40" s="19" t="n">
-        <v>175.9</v>
-      </c>
-      <c r="N40" s="32" t="n">
-        <v>0.028</v>
+        <v>158.66</v>
+      </c>
+      <c r="N40" s="33" t="n">
+        <v>0.17</v>
       </c>
       <c r="O40" s="25" t="inlineStr">
         <is>
@@ -3013,9 +3009,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q40" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q40" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
         </is>
       </c>
     </row>
@@ -3025,50 +3021,50 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10100048</t>
+          <t>10038798</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>RITALINA LA 10MG 30CP NOVARTIS (A3)</t>
+          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>121.04</v>
+        <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>481.39</v>
+        <v>433.23</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-360.35</v>
+        <v>-433.23</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-0.7490000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>3843</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>3.05</v>
+        <v>1623</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>1.29</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K41" s="7" t="n">
-        <v>137.55</v>
+        <v>180.79</v>
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
-        <v>120.9</v>
-      </c>
-      <c r="N41" s="31" t="n">
-        <v>0.138</v>
+        <v>175.9</v>
+      </c>
+      <c r="N41" s="32" t="n">
+        <v>0.028</v>
       </c>
       <c r="O41" s="13" t="inlineStr">
         <is>
@@ -3080,9 +3076,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 120.90)</t>
+      <c r="Q41" s="15" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3092,54 +3088,44 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>10040748</t>
+          <t>10028321</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
+          <t>PREGABALINA 150MG 30CAP GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D42" s="19" t="n">
-        <v>0</v>
+        <v>529.36</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>352.59</v>
+        <v>957.9</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>-352.59</v>
+        <v>-428.54</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>-1</v>
+        <v>-0.447</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>402</v>
-      </c>
-      <c r="I42" s="23" t="n">
-        <v>0.32</v>
+        <v>5385</v>
+      </c>
+      <c r="I42" s="30" t="n">
+        <v>4.28</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K42" s="19" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="L42" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M42" s="19" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N42" s="30" t="n">
-        <v>0</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="inlineStr"/>
+      <c r="L42" s="25" t="inlineStr"/>
+      <c r="M42" s="24" t="inlineStr"/>
+      <c r="N42" s="26" t="inlineStr"/>
       <c r="O42" s="25" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P42" s="25" t="inlineStr">
@@ -3149,7 +3135,7 @@
       </c>
       <c r="Q42" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3159,54 +3145,54 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10101654</t>
+          <t>10040748</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>NAN COMFOR 2 800G NESTLE</t>
+          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>583.98</v>
+        <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>926.84</v>
+        <v>419.57</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-342.86</v>
+        <v>-419.57</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-0.37</v>
+        <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>13534</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>10.75</v>
+        <v>402</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>0.32</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K43" s="7" t="n">
-        <v>87.48999999999999</v>
+        <v>1298.54</v>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="N43" s="31" t="n">
-        <v>0.094</v>
+        <v>1298.54</v>
+      </c>
+      <c r="N43" s="29" t="n">
+        <v>0</v>
       </c>
       <c r="O43" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P43" s="13" t="inlineStr">
@@ -3214,9 +3200,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 79.99)</t>
+      <c r="Q43" s="15" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3226,50 +3212,50 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>100022270</t>
+          <t>100001425</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
+          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D44" s="19" t="n">
-        <v>225.46</v>
+        <v>129.5</v>
       </c>
       <c r="E44" s="19" t="n">
-        <v>565.29</v>
+        <v>548.66</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>-339.83</v>
+        <v>-419.16</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>-0.601</v>
+        <v>-0.764</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>1962</v>
-      </c>
-      <c r="I44" s="29" t="n">
-        <v>1.56</v>
+        <v>13421</v>
+      </c>
+      <c r="I44" s="30" t="n">
+        <v>10.66</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K44" s="19" t="n">
-        <v>185.61</v>
+        <v>29.9</v>
       </c>
       <c r="L44" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M44" s="19" t="n">
-        <v>158.66</v>
-      </c>
-      <c r="N44" s="32" t="n">
-        <v>0.17</v>
+        <v>28.9</v>
+      </c>
+      <c r="N44" s="33" t="n">
+        <v>0.035</v>
       </c>
       <c r="O44" s="25" t="inlineStr">
         <is>
@@ -3281,9 +3267,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q44" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
+      <c r="Q44" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3293,50 +3279,50 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>100001425</t>
+          <t>100016230</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
+          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>129.5</v>
+        <v>1020.56</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>461.08</v>
+        <v>1430.97</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-331.58</v>
+        <v>-410.41</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-0.7190000000000001</v>
+        <v>-0.287</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>13421</v>
+        <v>4815</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>10.66</v>
+        <v>3.82</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K45" s="7" t="n">
-        <v>29.9</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="N45" s="31" t="n">
-        <v>0.035</v>
+        <v>49.9</v>
+      </c>
+      <c r="N45" s="32" t="n">
+        <v>0.904</v>
       </c>
       <c r="O45" s="13" t="inlineStr">
         <is>
@@ -3348,9 +3334,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q45" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
         </is>
       </c>
     </row>
@@ -3360,31 +3346,31 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>999705</t>
+          <t>10053171</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
+          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
         </is>
       </c>
       <c r="D46" s="19" t="n">
-        <v>0</v>
+        <v>557.78</v>
       </c>
       <c r="E46" s="19" t="n">
-        <v>327.64</v>
+        <v>960.11</v>
       </c>
       <c r="F46" s="20" t="n">
-        <v>-327.64</v>
+        <v>-402.33</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>-1</v>
+        <v>-0.419</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>37</v>
+        <v>1454</v>
       </c>
       <c r="I46" s="23" t="n">
-        <v>0.03</v>
+        <v>1.15</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -3417,54 +3403,44 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>100008511</t>
+          <t>10041858</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>APTAMIL PEPTI 800G DANONE</t>
+          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0</v>
+        <v>169.9</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>323.29</v>
+        <v>565.53</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-323.29</v>
+        <v>-395.63</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>1353</v>
+        <v>646</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>1.07</v>
+        <v>0.51</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>307.99</v>
-      </c>
-      <c r="L47" s="13" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="n">
-        <v>230.99</v>
-      </c>
-      <c r="N47" s="31" t="n">
-        <v>0.333</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K47" s="12" t="inlineStr"/>
+      <c r="L47" s="13" t="inlineStr"/>
+      <c r="M47" s="12" t="inlineStr"/>
+      <c r="N47" s="14" t="inlineStr"/>
       <c r="O47" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P47" s="13" t="inlineStr">
@@ -3472,9 +3448,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Amazon R$ 230.99)</t>
+      <c r="Q47" s="15" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3484,46 +3460,40 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>10044745</t>
+          <t>999705</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
+          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
         </is>
       </c>
       <c r="D48" s="19" t="n">
-        <v>355.26</v>
+        <v>0</v>
       </c>
       <c r="E48" s="19" t="n">
-        <v>674.38</v>
+        <v>389.87</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>-319.12</v>
+        <v>-389.87</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>-0.473</v>
+        <v>-1</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>5858</v>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>4.65</v>
+        <v>37</v>
+      </c>
+      <c r="I48" s="23" t="n">
+        <v>0.03</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K48" s="24" t="inlineStr"/>
-      <c r="L48" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M48" s="19" t="n">
-        <v>83.92</v>
-      </c>
+      <c r="L48" s="25" t="inlineStr"/>
+      <c r="M48" s="24" t="inlineStr"/>
       <c r="N48" s="26" t="inlineStr"/>
       <c r="O48" s="25" t="inlineStr">
         <is>
@@ -3537,7 +3507,7 @@
       </c>
       <c r="Q48" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3547,31 +3517,31 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10089756</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>RITALINA 10MG 60CP NOVARTIS (A3)</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-8.34</v>
+        <v>1422.88</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>305.34</v>
+        <v>1792.79</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-313.68</v>
+        <v>-369.91</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-1.027</v>
+        <v>-0.206</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7860</v>
+        <v>15647</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>6.24</v>
+        <v>12.43</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -3579,14 +3549,8 @@
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr"/>
-      <c r="L49" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="n">
-        <v>92.95</v>
-      </c>
+      <c r="L49" s="13" t="inlineStr"/>
+      <c r="M49" s="12" t="inlineStr"/>
       <c r="N49" s="14" t="inlineStr"/>
       <c r="O49" s="13" t="inlineStr">
         <is>
@@ -3610,44 +3574,54 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>10028321</t>
+          <t>10050453</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>PREGABALINA 150MG 30CAP GEN EMS (C1)</t>
+          <t>HORMUS 250MG/ML SOL INJ 2AMP 4ML EUROFARMA (C5)</t>
         </is>
       </c>
       <c r="D50" s="19" t="n">
-        <v>493.37</v>
+        <v>0</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>805</v>
+        <v>362.5</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>-311.63</v>
+        <v>-362.5</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>-0.387</v>
+        <v>-1</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>5385</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>4.28</v>
+        <v>834</v>
+      </c>
+      <c r="I50" s="23" t="n">
+        <v>0.66</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K50" s="24" t="inlineStr"/>
-      <c r="L50" s="25" t="inlineStr"/>
-      <c r="M50" s="24" t="inlineStr"/>
-      <c r="N50" s="26" t="inlineStr"/>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K50" s="19" t="n">
+        <v>957.25</v>
+      </c>
+      <c r="L50" s="25" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M50" s="19" t="n">
+        <v>438.02</v>
+      </c>
+      <c r="N50" s="33" t="n">
+        <v>1.185</v>
+      </c>
       <c r="O50" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P50" s="25" t="inlineStr">
@@ -3655,9 +3629,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q50" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q50" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Drogaraia R$ 438.02)</t>
         </is>
       </c>
     </row>
@@ -3667,44 +3641,54 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10049066</t>
+          <t>10051359</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 175ML HIDRATACAO+HIALURON VIT</t>
+          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>83.09</v>
+        <v>1439.82</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>393.42</v>
+        <v>1799.25</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-310.33</v>
+        <v>-359.43</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.789</v>
+        <v>-0.2</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>18637</v>
-      </c>
-      <c r="I51" s="28" t="n">
-        <v>14.8</v>
+        <v>962</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>0.76</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr"/>
-      <c r="L51" s="13" t="inlineStr"/>
-      <c r="M51" s="12" t="inlineStr"/>
-      <c r="N51" s="14" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>309</v>
+      </c>
+      <c r="L51" s="13" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>449</v>
+      </c>
+      <c r="N51" s="29" t="n">
+        <v>-0.312</v>
+      </c>
       <c r="O51" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P51" s="13" t="inlineStr">
@@ -3714,7 +3698,7 @@
       </c>
       <c r="Q51" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3724,44 +3708,54 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>10041858</t>
+          <t>10051297</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
+          <t>LEAVE IN ELSEVE 100ML COLAGENO LIFTER</t>
         </is>
       </c>
       <c r="D52" s="19" t="n">
-        <v>169.9</v>
+        <v>110.16</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>475.26</v>
+        <v>463.53</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>-305.36</v>
+        <v>-353.37</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>-0.643</v>
+        <v>-0.762</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>646</v>
-      </c>
-      <c r="I52" s="23" t="n">
-        <v>0.51</v>
+        <v>6815</v>
+      </c>
+      <c r="I52" s="30" t="n">
+        <v>5.41</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K52" s="24" t="inlineStr"/>
-      <c r="L52" s="25" t="inlineStr"/>
-      <c r="M52" s="24" t="inlineStr"/>
-      <c r="N52" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K52" s="19" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="L52" s="25" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M52" s="19" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="N52" s="33" t="n">
+        <v>0.7190000000000001</v>
+      </c>
       <c r="O52" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P52" s="25" t="inlineStr">
@@ -3769,9 +3763,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q52" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q52" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 34.90)</t>
         </is>
       </c>
     </row>
@@ -3781,54 +3775,44 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>10050453</t>
+          <t>10052934</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>HORMUS 250MG/ML SOL INJ 2AMP 4ML EUROFARMA (C5)</t>
+          <t>NEBULIZADOR COMPRESSOR HC032 TRAVEL MULTILASER</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>304.63</v>
+        <v>352.61</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-304.63</v>
+        <v>-352.61</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>834</v>
-      </c>
-      <c r="I53" s="11" t="n">
-        <v>0.66</v>
+        <v>3068</v>
+      </c>
+      <c r="I53" s="28" t="n">
+        <v>2.44</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>957.25</v>
-      </c>
-      <c r="L53" s="13" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
-        <v>438.02</v>
-      </c>
-      <c r="N53" s="31" t="n">
-        <v>1.185</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr"/>
+      <c r="L53" s="13" t="inlineStr"/>
+      <c r="M53" s="12" t="inlineStr"/>
+      <c r="N53" s="14" t="inlineStr"/>
       <c r="O53" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P53" s="13" t="inlineStr">
@@ -3836,9 +3820,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Drogaraia R$ 438.02)</t>
+      <c r="Q53" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3848,44 +3832,54 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>10052934</t>
+          <t>10025441</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>NEBULIZADOR COMPRESSOR HC032 TRAVEL MULTILASER</t>
+          <t>CREATINE 300G MAXTITANIUM</t>
         </is>
       </c>
       <c r="D54" s="19" t="n">
-        <v>0</v>
+        <v>231.51</v>
       </c>
       <c r="E54" s="19" t="n">
-        <v>296.33</v>
+        <v>582.24</v>
       </c>
       <c r="F54" s="20" t="n">
-        <v>-296.33</v>
+        <v>-350.73</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>-1</v>
+        <v>-0.602</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>3068</v>
-      </c>
-      <c r="I54" s="29" t="n">
-        <v>2.44</v>
+        <v>3506</v>
+      </c>
+      <c r="I54" s="30" t="n">
+        <v>2.78</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K54" s="24" t="inlineStr"/>
-      <c r="L54" s="25" t="inlineStr"/>
-      <c r="M54" s="24" t="inlineStr"/>
-      <c r="N54" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K54" s="19" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L54" s="25" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M54" s="19" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="N54" s="33" t="n">
+        <v>0.499</v>
+      </c>
       <c r="O54" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P54" s="25" t="inlineStr">
@@ -3893,9 +3887,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q54" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q54" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 39.96)</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -291,19 +291,19 @@
     <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 14:54:03 (14:54) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 15:53:44 (15:53) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>5935.91</v>
+        <v>6830.17</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-5935.91</v>
+        <v>-6830.17</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>-1</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>3957.27</v>
+        <v>4553.44</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>-3957.27</v>
+        <v>-4553.44</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>-1</v>
@@ -923,54 +923,44 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10046653</t>
+          <t>10033758</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>MOUNJARO 5MG 4CAN APLIC LILLY</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>57044.61</v>
+        <v>334.4</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>59099.37</v>
+        <v>2224.86</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-2054.76</v>
+        <v>-1890.46</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.035</v>
+        <v>-0.85</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>11192</v>
+        <v>26223</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>8.890000000000001</v>
+        <v>20.83</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K7" s="7" t="n">
-        <v>2382.23</v>
-      </c>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>2382.23</v>
-      </c>
-      <c r="N7" s="29" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" s="12" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
+      <c r="M7" s="12" t="inlineStr"/>
+      <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P7" s="13" t="inlineStr">
@@ -980,7 +970,7 @@
       </c>
       <c r="Q7" s="15" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -990,31 +980,31 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10040750</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>3343</v>
+        <v>1698</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>5306.77</v>
+        <v>3462.62</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>-1963.77</v>
+        <v>-1764.62</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>-0.37</v>
+        <v>-0.51</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>9409</v>
-      </c>
-      <c r="I8" s="30" t="n">
-        <v>7.47</v>
+        <v>3321</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>2.64</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1012,7 @@
         </is>
       </c>
       <c r="K8" s="19" t="n">
-        <v>988.22</v>
+        <v>1298.54</v>
       </c>
       <c r="L8" s="25" t="inlineStr">
         <is>
@@ -1030,9 +1020,9 @@
         </is>
       </c>
       <c r="M8" s="19" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N8" s="31" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N8" s="30" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="25" t="inlineStr">
@@ -1047,7 +1037,7 @@
       </c>
       <c r="Q8" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Push CRM / Recompra 30d no App</t>
         </is>
       </c>
     </row>
@@ -1057,31 +1047,31 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>84.90000000000001</v>
+        <v>221.97</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1933.56</v>
+        <v>1966.67</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1848.66</v>
+        <v>-1744.7</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.956</v>
+        <v>-0.887</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>26223</v>
+        <v>39477</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>20.83</v>
+        <v>31.36</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1114,44 +1104,54 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>221.97</v>
+        <v>1496.42</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>1709.18</v>
+        <v>3066.89</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-1487.21</v>
+        <v>-1570.47</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>-0.87</v>
+        <v>-0.512</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>39477</v>
-      </c>
-      <c r="I10" s="30" t="n">
-        <v>31.36</v>
+        <v>2446</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>1.94</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K10" s="24" t="inlineStr"/>
-      <c r="L10" s="25" t="inlineStr"/>
-      <c r="M10" s="24" t="inlineStr"/>
-      <c r="N10" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="L10" s="25" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M10" s="19" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="N10" s="31" t="n">
+        <v>1.132</v>
+      </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P10" s="25" t="inlineStr">
@@ -1159,9 +1159,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q10" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q10" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -1171,54 +1171,44 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1296.62</v>
+        <v>509.9</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2665.35</v>
+        <v>1978.64</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-1368.73</v>
+        <v>-1468.74</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.514</v>
+        <v>-0.742</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>2446</v>
+        <v>3146</v>
       </c>
       <c r="I11" s="28" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N11" s="32" t="n">
-        <v>1.132</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr"/>
+      <c r="L11" s="13" t="inlineStr"/>
+      <c r="M11" s="12" t="inlineStr"/>
+      <c r="N11" s="14" t="inlineStr"/>
       <c r="O11" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P11" s="13" t="inlineStr">
@@ -1226,9 +1216,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+      <c r="Q11" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1238,31 +1228,31 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>404</v>
+        <v>249.17</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>1719.58</v>
+        <v>1681.84</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>-1315.58</v>
+        <v>-1432.67</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.765</v>
+        <v>-0.852</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>3146</v>
-      </c>
-      <c r="I12" s="30" t="n">
-        <v>2.5</v>
+        <v>4427</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>3.52</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -1270,8 +1260,14 @@
         </is>
       </c>
       <c r="K12" s="24" t="inlineStr"/>
-      <c r="L12" s="25" t="inlineStr"/>
-      <c r="M12" s="24" t="inlineStr"/>
+      <c r="L12" s="25" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M12" s="19" t="n">
+        <v>50.25</v>
+      </c>
       <c r="N12" s="26" t="inlineStr"/>
       <c r="O12" s="25" t="inlineStr">
         <is>
@@ -1295,54 +1291,44 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1698</v>
+        <v>415.06</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3009.27</v>
+        <v>1763.28</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-1311.27</v>
+        <v>-1348.22</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.436</v>
+        <v>-0.765</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>3321</v>
-      </c>
-      <c r="I13" s="28" t="n">
-        <v>2.64</v>
+        <v>1270</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>1.01</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N13" s="29" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr"/>
+      <c r="L13" s="13" t="inlineStr"/>
+      <c r="M13" s="12" t="inlineStr"/>
+      <c r="N13" s="14" t="inlineStr"/>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr">
@@ -1352,7 +1338,7 @@
       </c>
       <c r="Q13" s="15" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1362,45 +1348,45 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>10041248</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>CREATINA MONOHIDRATADA 300G DUX</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>249.17</v>
+        <v>0</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>1461.64</v>
+        <v>1288.74</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>-1212.47</v>
+        <v>-1288.74</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>-0.83</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>4427</v>
-      </c>
-      <c r="I14" s="30" t="n">
-        <v>3.52</v>
+        <v>204</v>
+      </c>
+      <c r="I14" s="23" t="n">
+        <v>0.16</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K14" s="24" t="inlineStr"/>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M14" s="19" t="n">
-        <v>50.25</v>
+        <v>1212.9</v>
       </c>
       <c r="N14" s="26" t="inlineStr"/>
       <c r="O14" s="25" t="inlineStr">
@@ -1415,7 +1401,7 @@
       </c>
       <c r="Q14" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1425,31 +1411,31 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10025098</t>
+          <t>10093877</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
+          <t>MIRENA 52MG 1END+INS BAYER</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1120.01</v>
+        <v>1287.3</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-1120.01</v>
+        <v>-1287.3</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>204</v>
+        <v>501</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1459,11 +1445,11 @@
       <c r="K15" s="12" t="inlineStr"/>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
-        <v>1212.9</v>
+        <v>1225.89</v>
       </c>
       <c r="N15" s="14" t="inlineStr"/>
       <c r="O15" s="13" t="inlineStr">
@@ -1488,50 +1474,54 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>10093877</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>MIRENA 52MG 1END+INS BAYER</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>0</v>
+        <v>833.04</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>1118.76</v>
+        <v>2028.37</v>
       </c>
       <c r="F16" s="20" t="n">
-        <v>-1118.76</v>
+        <v>-1195.33</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>-1</v>
+        <v>-0.589</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>501</v>
-      </c>
-      <c r="I16" s="23" t="n">
-        <v>0.4</v>
+        <v>8909</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>7.08</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K16" s="24" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>108.49</v>
+      </c>
       <c r="L16" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M16" s="19" t="n">
-        <v>1225.89</v>
-      </c>
-      <c r="N16" s="26" t="inlineStr"/>
+        <v>97.69</v>
+      </c>
+      <c r="N16" s="31" t="n">
+        <v>0.111</v>
+      </c>
       <c r="O16" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P16" s="25" t="inlineStr">
@@ -1539,9 +1529,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q16" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q16" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -1551,44 +1541,54 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10024521</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>415.06</v>
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1532.41</v>
+        <v>1188.22</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-1117.35</v>
+        <v>-1188.22</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-0.7290000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>1270</v>
+        <v>575</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="13" t="inlineStr"/>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="14" t="inlineStr"/>
+      <c r="K17" s="7" t="n">
+        <v>799.9</v>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>814.9</v>
+      </c>
+      <c r="N17" s="32" t="n">
+        <v>-0.018</v>
+      </c>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P17" s="13" t="inlineStr">
@@ -1608,54 +1608,44 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>670.46</v>
+        <v>2090.44</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>1762.8</v>
+        <v>3259.37</v>
       </c>
       <c r="F18" s="20" t="n">
-        <v>-1092.34</v>
+        <v>-1168.93</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>-0.62</v>
+        <v>-0.359</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>8909</v>
-      </c>
-      <c r="I18" s="30" t="n">
-        <v>7.08</v>
+        <v>8275</v>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>6.57</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>108.49</v>
-      </c>
-      <c r="L18" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M18" s="19" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N18" s="33" t="n">
-        <v>0.111</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K18" s="24" t="inlineStr"/>
+      <c r="L18" s="25" t="inlineStr"/>
+      <c r="M18" s="24" t="inlineStr"/>
+      <c r="N18" s="26" t="inlineStr"/>
       <c r="O18" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P18" s="25" t="inlineStr">
@@ -1663,9 +1653,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q18" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+      <c r="Q18" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1675,31 +1665,31 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10024521</t>
+          <t>10025745</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
+          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1032.65</v>
+        <v>1094.89</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-1032.65</v>
+        <v>-1094.89</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>575</v>
+        <v>122</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>0.46</v>
+        <v>0.1</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1707,18 +1697,18 @@
         </is>
       </c>
       <c r="K19" s="7" t="n">
-        <v>799.9</v>
+        <v>1105.6</v>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M19" s="7" t="n">
-        <v>814.9</v>
-      </c>
-      <c r="N19" s="29" t="n">
-        <v>-0.018</v>
+        <v>1170.01</v>
+      </c>
+      <c r="N19" s="32" t="n">
+        <v>-0.055</v>
       </c>
       <c r="O19" s="13" t="inlineStr">
         <is>
@@ -1742,31 +1732,31 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>1858.64</v>
+        <v>0</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>2832.63</v>
+        <v>1065.38</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>-973.99</v>
+        <v>-1065.38</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>-0.344</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>8275</v>
-      </c>
-      <c r="I20" s="30" t="n">
-        <v>6.57</v>
+        <v>11806</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>9.380000000000001</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1784,7 +1774,7 @@
       </c>
       <c r="P20" s="25" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q20" s="27" t="inlineStr">
@@ -1799,64 +1789,64 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>715.96</v>
+        <v>5041</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1673.02</v>
+        <v>6106.25</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-957.0599999999999</v>
+        <v>-1065.25</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-0.5720000000000001</v>
+        <v>-0.174</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>2931</v>
+        <v>9409</v>
       </c>
       <c r="I21" s="28" t="n">
-        <v>2.33</v>
+        <v>7.47</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>218.67</v>
+        <v>988.22</v>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
-        <v>197.18</v>
+        <v>988.22</v>
       </c>
       <c r="N21" s="32" t="n">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="O21" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P21" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q21" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1866,39 +1856,39 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>10025745</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D22" s="19" t="n">
-        <v>0</v>
+        <v>524.54</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>951.54</v>
+        <v>1574.48</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>-951.54</v>
+        <v>-1049.94</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>-1</v>
+        <v>-0.667</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>122</v>
-      </c>
-      <c r="I22" s="23" t="n">
-        <v>0.1</v>
+        <v>12853</v>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>10.21</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K22" s="19" t="n">
-        <v>1105.6</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L22" s="25" t="inlineStr">
         <is>
@@ -1906,24 +1896,24 @@
         </is>
       </c>
       <c r="M22" s="19" t="n">
-        <v>1170.01</v>
+        <v>61.06</v>
       </c>
       <c r="N22" s="31" t="n">
-        <v>-0.055</v>
+        <v>0.113</v>
       </c>
       <c r="O22" s="25" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P22" s="25" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q22" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q22" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -1933,54 +1923,64 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>925.9</v>
+        <v>1026.06</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-925.9</v>
+        <v>-1000.16</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-1</v>
+        <v>-0.975</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>11806</v>
+        <v>22233</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>9.380000000000001</v>
+        <v>17.66</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="inlineStr"/>
-      <c r="L23" s="13" t="inlineStr"/>
-      <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N23" s="33" t="n">
+        <v>0.629</v>
+      </c>
       <c r="O23" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P23" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q23" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -1990,54 +1990,44 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D24" s="19" t="n">
-        <v>463.48</v>
+        <v>0</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>1368.34</v>
+        <v>909.1900000000001</v>
       </c>
       <c r="F24" s="20" t="n">
-        <v>-904.86</v>
+        <v>-909.1900000000001</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>-0.6609999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>12853</v>
-      </c>
-      <c r="I24" s="30" t="n">
-        <v>10.21</v>
+        <v>30285</v>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>24.05</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K24" s="19" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="L24" s="25" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M24" s="19" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N24" s="33" t="n">
-        <v>0.113</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K24" s="24" t="inlineStr"/>
+      <c r="L24" s="25" t="inlineStr"/>
+      <c r="M24" s="24" t="inlineStr"/>
+      <c r="N24" s="26" t="inlineStr"/>
       <c r="O24" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P24" s="25" t="inlineStr">
@@ -2045,9 +2035,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q24" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+      <c r="Q24" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2057,50 +2047,50 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>25.9</v>
+        <v>936.36</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>891.72</v>
+        <v>1817.02</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-865.8200000000001</v>
+        <v>-880.66</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.971</v>
+        <v>-0.485</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>22233</v>
-      </c>
-      <c r="I25" s="28" t="n">
-        <v>17.66</v>
+        <v>837</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>0.66</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K25" s="7" t="n">
-        <v>25.9</v>
+        <v>315.46</v>
       </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M25" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N25" s="32" t="n">
-        <v>0.629</v>
+        <v>236.6</v>
+      </c>
+      <c r="N25" s="33" t="n">
+        <v>0.333</v>
       </c>
       <c r="O25" s="13" t="inlineStr">
         <is>
@@ -2114,7 +2104,7 @@
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -2124,44 +2114,54 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D26" s="19" t="n">
-        <v>0</v>
+        <v>1050.82</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>790.15</v>
+        <v>1925.06</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>-790.15</v>
+        <v>-874.24</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>-1</v>
+        <v>-0.454</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>30285</v>
-      </c>
-      <c r="I26" s="30" t="n">
-        <v>24.05</v>
+        <v>2931</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <v>2.33</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K26" s="24" t="inlineStr"/>
-      <c r="L26" s="25" t="inlineStr"/>
-      <c r="M26" s="24" t="inlineStr"/>
-      <c r="N26" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>218.67</v>
+      </c>
+      <c r="L26" s="25" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M26" s="19" t="n">
+        <v>197.18</v>
+      </c>
+      <c r="N26" s="31" t="n">
+        <v>0.109</v>
+      </c>
       <c r="O26" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P26" s="25" t="inlineStr">
@@ -2169,9 +2169,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q26" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q26" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -2181,54 +2181,44 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>801.22</v>
+        <v>315.09</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>1504.64</v>
+        <v>1123.08</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-703.42</v>
+        <v>-807.99</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.468</v>
+        <v>-0.7190000000000001</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>3992</v>
+        <v>9864</v>
       </c>
       <c r="I27" s="28" t="n">
-        <v>3.17</v>
+        <v>7.83</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="L27" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="N27" s="32" t="n">
-        <v>0.396</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K27" s="12" t="inlineStr"/>
+      <c r="L27" s="13" t="inlineStr"/>
+      <c r="M27" s="12" t="inlineStr"/>
+      <c r="N27" s="14" t="inlineStr"/>
       <c r="O27" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr">
@@ -2236,9 +2226,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+      <c r="Q27" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2248,44 +2238,54 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D28" s="19" t="n">
-        <v>287.9</v>
+        <v>1041.2</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>976.03</v>
+        <v>1731.32</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>-688.13</v>
+        <v>-690.12</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>-0.705</v>
+        <v>-0.399</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>9864</v>
-      </c>
-      <c r="I28" s="30" t="n">
-        <v>7.83</v>
+        <v>3992</v>
+      </c>
+      <c r="I28" s="29" t="n">
+        <v>3.17</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K28" s="24" t="inlineStr"/>
-      <c r="L28" s="25" t="inlineStr"/>
-      <c r="M28" s="24" t="inlineStr"/>
-      <c r="N28" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K28" s="19" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L28" s="25" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>107</v>
+      </c>
+      <c r="N28" s="31" t="n">
+        <v>0.396</v>
+      </c>
       <c r="O28" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P28" s="25" t="inlineStr">
@@ -2293,9 +2293,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q28" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q28" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -2305,54 +2305,44 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>100008085</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>ELIQUIS 5MG 60TBS PFIZER</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>936.36</v>
+        <v>5.98</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>1579.12</v>
+        <v>603.35</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-642.76</v>
+        <v>-597.37</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-0.407</v>
+        <v>-0.99</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>837</v>
-      </c>
-      <c r="I29" s="11" t="n">
-        <v>0.66</v>
+        <v>2887</v>
+      </c>
+      <c r="I29" s="28" t="n">
+        <v>2.29</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>315.46</v>
-      </c>
-      <c r="L29" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N29" s="32" t="n">
-        <v>0.333</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K29" s="12" t="inlineStr"/>
+      <c r="L29" s="13" t="inlineStr"/>
+      <c r="M29" s="12" t="inlineStr"/>
+      <c r="N29" s="14" t="inlineStr"/>
       <c r="O29" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P29" s="13" t="inlineStr">
@@ -2360,9 +2350,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+      <c r="Q29" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2372,46 +2362,40 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>100009772</t>
+          <t>10041082</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>FERINJECT 50MG/ML 1FR/AMP 10ML BLANVER</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
         </is>
       </c>
       <c r="D30" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>606.76</v>
+        <v>554.87</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>-606.76</v>
+        <v>-554.87</v>
       </c>
       <c r="G30" s="21" t="n">
         <v>-1</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>510</v>
-      </c>
-      <c r="I30" s="23" t="n">
-        <v>0.41</v>
+        <v>5609</v>
+      </c>
+      <c r="I30" s="29" t="n">
+        <v>4.46</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K30" s="24" t="inlineStr"/>
-      <c r="L30" s="25" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M30" s="19" t="n">
-        <v>719.9</v>
-      </c>
+      <c r="L30" s="25" t="inlineStr"/>
+      <c r="M30" s="24" t="inlineStr"/>
       <c r="N30" s="26" t="inlineStr"/>
       <c r="O30" s="25" t="inlineStr">
         <is>
@@ -2425,7 +2409,7 @@
       </c>
       <c r="Q30" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2435,44 +2419,54 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10052540</t>
+          <t>100022270</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
+          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>454.66</v>
+        <v>225.46</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>1060.49</v>
+        <v>774.01</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-605.83</v>
+        <v>-548.55</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-0.5710000000000001</v>
+        <v>-0.7090000000000001</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>2601</v>
+        <v>1962</v>
       </c>
       <c r="I31" s="28" t="n">
-        <v>2.07</v>
+        <v>1.56</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K31" s="12" t="inlineStr"/>
-      <c r="L31" s="13" t="inlineStr"/>
-      <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>185.61</v>
+      </c>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>158.66</v>
+      </c>
+      <c r="N31" s="33" t="n">
+        <v>0.17</v>
+      </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P31" s="13" t="inlineStr">
@@ -2480,9 +2474,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q31" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
         </is>
       </c>
     </row>
@@ -2492,40 +2486,46 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>100008756</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>LEITE NEOCATE LCP 400G DANONE</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D32" s="19" t="n">
-        <v>0</v>
+        <v>2019.56</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>530.5700000000001</v>
+        <v>2559.46</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>-530.5700000000001</v>
+        <v>-539.9</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>-1</v>
+        <v>-0.211</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>1484</v>
-      </c>
-      <c r="I32" s="23" t="n">
-        <v>1.18</v>
+        <v>2081</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>1.65</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K32" s="24" t="inlineStr"/>
-      <c r="L32" s="25" t="inlineStr"/>
-      <c r="M32" s="24" t="inlineStr"/>
+      <c r="L32" s="25" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M32" s="19" t="n">
+        <v>549.9</v>
+      </c>
       <c r="N32" s="26" t="inlineStr"/>
       <c r="O32" s="25" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="Q32" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2549,31 +2549,31 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10052540</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>645.39</v>
+        <v>687.12</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1168.76</v>
+        <v>1220.25</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-523.37</v>
+        <v>-533.13</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.448</v>
+        <v>-0.4370000000000001</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>11106</v>
+        <v>2601</v>
       </c>
       <c r="I33" s="28" t="n">
-        <v>8.82</v>
+        <v>2.07</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2606,44 +2606,54 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>100008085</t>
+          <t>10038798</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>ELIQUIS 5MG 60TBS PFIZER</t>
+          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>524.35</v>
+        <v>498.5</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>-518.37</v>
+        <v>-498.5</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>-0.9890000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>2887</v>
-      </c>
-      <c r="I34" s="30" t="n">
-        <v>2.29</v>
+        <v>1623</v>
+      </c>
+      <c r="I34" s="23" t="n">
+        <v>1.29</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K34" s="24" t="inlineStr"/>
-      <c r="L34" s="25" t="inlineStr"/>
-      <c r="M34" s="24" t="inlineStr"/>
-      <c r="N34" s="26" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>180.79</v>
+      </c>
+      <c r="L34" s="25" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M34" s="19" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="N34" s="31" t="n">
+        <v>0.028</v>
+      </c>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P34" s="25" t="inlineStr">
@@ -2653,7 +2663,7 @@
       </c>
       <c r="Q34" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2663,31 +2673,31 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10001098</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>754.77</v>
+        <v>857.6900000000001</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1267.76</v>
+        <v>1344.83</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-512.99</v>
+        <v>-487.14</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-0.405</v>
+        <v>-0.362</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8492</v>
+        <v>11106</v>
       </c>
       <c r="I35" s="28" t="n">
-        <v>6.75</v>
+        <v>8.82</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2720,35 +2730,35 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>10044679</t>
+          <t>10099241</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
+          <t>NAN COMFOR 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0</v>
+        <v>927.8200000000001</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>490.64</v>
+        <v>1412.66</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>-490.64</v>
+        <v>-484.84</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>-1</v>
+        <v>-0.343</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>324</v>
-      </c>
-      <c r="I36" s="23" t="n">
-        <v>0.26</v>
+        <v>13024</v>
+      </c>
+      <c r="I36" s="29" t="n">
+        <v>10.34</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K36" s="24" t="inlineStr"/>
@@ -2767,7 +2777,7 @@
       </c>
       <c r="Q36" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2777,44 +2787,54 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10041082</t>
+          <t>10040748</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
+          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>482.22</v>
+        <v>482.78</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-482.22</v>
+        <v>-482.78</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>5609</v>
-      </c>
-      <c r="I37" s="28" t="n">
-        <v>4.46</v>
+        <v>402</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>0.32</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K37" s="12" t="inlineStr"/>
-      <c r="L37" s="13" t="inlineStr"/>
-      <c r="M37" s="12" t="inlineStr"/>
-      <c r="N37" s="14" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N37" s="32" t="n">
+        <v>0</v>
+      </c>
       <c r="O37" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P37" s="13" t="inlineStr">
@@ -2824,7 +2844,7 @@
       </c>
       <c r="Q37" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2834,35 +2854,35 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>10099241</t>
+          <t>10041858</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>NAN COMFOR 1 800G NESTLE</t>
+          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>766.1</v>
+        <v>169.9</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>1227.71</v>
+        <v>650.73</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>-461.61</v>
+        <v>-480.83</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>-0.376</v>
+        <v>-0.7390000000000001</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>13024</v>
-      </c>
-      <c r="I38" s="30" t="n">
-        <v>10.34</v>
+        <v>646</v>
+      </c>
+      <c r="I38" s="23" t="n">
+        <v>0.51</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K38" s="24" t="inlineStr"/>
@@ -2881,7 +2901,7 @@
       </c>
       <c r="Q38" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2891,31 +2911,31 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10044745</t>
+          <t>10001098</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>355.26</v>
+        <v>978.5599999999999</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>802.48</v>
+        <v>1458.75</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-447.22</v>
+        <v>-480.19</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.329</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>5858</v>
+        <v>8492</v>
       </c>
       <c r="I39" s="28" t="n">
-        <v>4.65</v>
+        <v>6.75</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2923,14 +2943,8 @@
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr"/>
-      <c r="L39" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="n">
-        <v>83.92</v>
-      </c>
+      <c r="L39" s="13" t="inlineStr"/>
+      <c r="M39" s="12" t="inlineStr"/>
       <c r="N39" s="14" t="inlineStr"/>
       <c r="O39" s="13" t="inlineStr">
         <is>
@@ -2954,50 +2968,50 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>100022270</t>
+          <t>100001425</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
+          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D40" s="19" t="n">
-        <v>225.46</v>
+        <v>179.3</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>672.67</v>
+        <v>631.3200000000001</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>-447.21</v>
+        <v>-452.02</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>-0.665</v>
+        <v>-0.716</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>1962</v>
-      </c>
-      <c r="I40" s="30" t="n">
-        <v>1.56</v>
+        <v>13421</v>
+      </c>
+      <c r="I40" s="29" t="n">
+        <v>10.66</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K40" s="19" t="n">
-        <v>185.61</v>
+        <v>29.9</v>
       </c>
       <c r="L40" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M40" s="19" t="n">
-        <v>158.66</v>
-      </c>
-      <c r="N40" s="33" t="n">
-        <v>0.17</v>
+        <v>28.9</v>
+      </c>
+      <c r="N40" s="31" t="n">
+        <v>0.035</v>
       </c>
       <c r="O40" s="25" t="inlineStr">
         <is>
@@ -3009,9 +3023,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q40" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
+      <c r="Q40" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3021,54 +3035,44 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10038798</t>
+          <t>999705</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
+          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>433.23</v>
+        <v>448.61</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-433.23</v>
+        <v>-448.61</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>1623</v>
+        <v>37</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>1.29</v>
+        <v>0.03</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K41" s="7" t="n">
-        <v>180.79</v>
-      </c>
-      <c r="L41" s="13" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="n">
-        <v>175.9</v>
-      </c>
-      <c r="N41" s="32" t="n">
-        <v>0.028</v>
-      </c>
+      <c r="K41" s="12" t="inlineStr"/>
+      <c r="L41" s="13" t="inlineStr"/>
+      <c r="M41" s="12" t="inlineStr"/>
+      <c r="N41" s="14" t="inlineStr"/>
       <c r="O41" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P41" s="13" t="inlineStr">
@@ -3088,44 +3092,54 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>10028321</t>
+          <t>10025441</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>PREGABALINA 150MG 30CAP GEN EMS (C1)</t>
+          <t>CREATINE 300G MAXTITANIUM</t>
         </is>
       </c>
       <c r="D42" s="19" t="n">
-        <v>529.36</v>
+        <v>231.51</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>957.9</v>
+        <v>669.96</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>-428.54</v>
+        <v>-438.45</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>-0.447</v>
+        <v>-0.654</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>5385</v>
-      </c>
-      <c r="I42" s="30" t="n">
-        <v>4.28</v>
+        <v>3506</v>
+      </c>
+      <c r="I42" s="29" t="n">
+        <v>2.78</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K42" s="24" t="inlineStr"/>
-      <c r="L42" s="25" t="inlineStr"/>
-      <c r="M42" s="24" t="inlineStr"/>
-      <c r="N42" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L42" s="25" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M42" s="19" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="N42" s="31" t="n">
+        <v>0.499</v>
+      </c>
       <c r="O42" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P42" s="25" t="inlineStr">
@@ -3133,9 +3147,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q42" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q42" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 39.96)</t>
         </is>
       </c>
     </row>
@@ -3145,54 +3159,54 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10040748</t>
+          <t>10051297</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
+          <t>LEAVE IN ELSEVE 100ML COLAGENO LIFTER</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0</v>
+        <v>110.16</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>419.57</v>
+        <v>533.36</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-419.57</v>
+        <v>-423.2</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-1</v>
+        <v>-0.7929999999999999</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>402</v>
-      </c>
-      <c r="I43" s="11" t="n">
-        <v>0.32</v>
+        <v>6815</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>5.41</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K43" s="7" t="n">
-        <v>1298.54</v>
+        <v>59.99</v>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N43" s="29" t="n">
-        <v>0</v>
+        <v>34.9</v>
+      </c>
+      <c r="N43" s="33" t="n">
+        <v>0.7190000000000001</v>
       </c>
       <c r="O43" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P43" s="13" t="inlineStr">
@@ -3200,9 +3214,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q43" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 34.90)</t>
         </is>
       </c>
     </row>
@@ -3212,54 +3226,44 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>100001425</t>
+          <t>10044679</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
+          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
         </is>
       </c>
       <c r="D44" s="19" t="n">
-        <v>129.5</v>
+        <v>142.52</v>
       </c>
       <c r="E44" s="19" t="n">
-        <v>548.66</v>
+        <v>564.5599999999999</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>-419.16</v>
+        <v>-422.04</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>-0.764</v>
+        <v>-0.748</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>13421</v>
-      </c>
-      <c r="I44" s="30" t="n">
-        <v>10.66</v>
+        <v>324</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>0.26</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K44" s="19" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="L44" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M44" s="19" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="N44" s="33" t="n">
-        <v>0.035</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K44" s="24" t="inlineStr"/>
+      <c r="L44" s="25" t="inlineStr"/>
+      <c r="M44" s="24" t="inlineStr"/>
+      <c r="N44" s="26" t="inlineStr"/>
       <c r="O44" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P44" s="25" t="inlineStr">
@@ -3269,7 +3273,7 @@
       </c>
       <c r="Q44" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3279,50 +3283,50 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>100016230</t>
+          <t>10050453</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>NEUTROGENA GEL HID FACIAL 50G HYDRO BOOST WATER</t>
+          <t>HORMUS 250MG/ML SOL INJ 2AMP 4ML EUROFARMA (C5)</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1020.56</v>
+        <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1430.97</v>
+        <v>417.11</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-410.41</v>
+        <v>-417.11</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-0.287</v>
+        <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>4815</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>3.82</v>
+        <v>834</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>0.66</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K45" s="7" t="n">
-        <v>94.98999999999999</v>
+        <v>957.25</v>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="N45" s="32" t="n">
-        <v>0.904</v>
+        <v>438.02</v>
+      </c>
+      <c r="N45" s="33" t="n">
+        <v>1.185</v>
       </c>
       <c r="O45" s="13" t="inlineStr">
         <is>
@@ -3336,7 +3340,7 @@
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 49.90)</t>
+          <t>Reprecificar e Remanejar (Drogaraia R$ 438.02)</t>
         </is>
       </c>
     </row>
@@ -3346,44 +3350,54 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>10053171</t>
+          <t>10100048</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>OZIVY 0,25MG+0,5MG 1CAN 1,5ML EMS</t>
+          <t>RITALINA LA 10MG 30CP NOVARTIS (A3)</t>
         </is>
       </c>
       <c r="D46" s="19" t="n">
-        <v>557.78</v>
+        <v>242.08</v>
       </c>
       <c r="E46" s="19" t="n">
-        <v>960.11</v>
+        <v>659.12</v>
       </c>
       <c r="F46" s="20" t="n">
-        <v>-402.33</v>
+        <v>-417.04</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>-0.419</v>
+        <v>-0.633</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>1454</v>
-      </c>
-      <c r="I46" s="23" t="n">
-        <v>1.15</v>
+        <v>3843</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>3.05</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K46" s="24" t="inlineStr"/>
-      <c r="L46" s="25" t="inlineStr"/>
-      <c r="M46" s="24" t="inlineStr"/>
-      <c r="N46" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K46" s="19" t="n">
+        <v>137.55</v>
+      </c>
+      <c r="L46" s="25" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M46" s="19" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="N46" s="31" t="n">
+        <v>0.138</v>
+      </c>
       <c r="O46" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P46" s="25" t="inlineStr">
@@ -3391,9 +3405,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q46" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q46" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 120.90)</t>
         </is>
       </c>
     </row>
@@ -3403,35 +3417,35 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10041858</t>
+          <t>10033759</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER M 66UN</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>169.9</v>
+        <v>169.8</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>565.53</v>
+        <v>585.1</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-395.63</v>
+        <v>-415.3</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>646</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>0.51</v>
+        <v>10622</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>8.44</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr"/>
@@ -3450,7 +3464,7 @@
       </c>
       <c r="Q47" s="15" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3460,44 +3474,54 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>999705</t>
+          <t>10050653</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
+          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D48" s="19" t="n">
+        <v>829</v>
+      </c>
+      <c r="E48" s="19" t="n">
+        <v>1231.45</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>-402.45</v>
+      </c>
+      <c r="G48" s="21" t="n">
+        <v>-0.327</v>
+      </c>
+      <c r="H48" s="22" t="n">
+        <v>2647</v>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K48" s="19" t="n">
+        <v>1347.91</v>
+      </c>
+      <c r="L48" s="25" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M48" s="19" t="n">
+        <v>1347.89</v>
+      </c>
+      <c r="N48" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="19" t="n">
-        <v>389.87</v>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>-389.87</v>
-      </c>
-      <c r="G48" s="21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H48" s="22" t="n">
-        <v>37</v>
-      </c>
-      <c r="I48" s="23" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K48" s="24" t="inlineStr"/>
-      <c r="L48" s="25" t="inlineStr"/>
-      <c r="M48" s="24" t="inlineStr"/>
-      <c r="N48" s="26" t="inlineStr"/>
       <c r="O48" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P48" s="25" t="inlineStr">
@@ -3507,7 +3531,7 @@
       </c>
       <c r="Q48" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3517,31 +3541,31 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10049066</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>KIT DOVE SH 350+COND 175ML HIDRATACAO+HIALURON VIT</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1422.88</v>
+        <v>141.22</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1792.79</v>
+        <v>538.67</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-369.91</v>
+        <v>-397.45</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-0.206</v>
+        <v>-0.738</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>15647</v>
+        <v>18637</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>12.43</v>
+        <v>14.8</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -3574,54 +3598,54 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>10050453</t>
+          <t>10050639</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>HORMUS 250MG/ML SOL INJ 2AMP 4ML EUROFARMA (C5)</t>
+          <t>EXTENSIOR 0,25MG+0,5MG 1,5ML NOVO EUROFARMA</t>
         </is>
       </c>
       <c r="D50" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>362.5</v>
+        <v>395.13</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>-362.5</v>
+        <v>-395.13</v>
       </c>
       <c r="G50" s="21" t="n">
         <v>-1</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>834</v>
+        <v>784</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K50" s="19" t="n">
-        <v>957.25</v>
+        <v>955.85</v>
       </c>
       <c r="L50" s="25" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M50" s="19" t="n">
-        <v>438.02</v>
-      </c>
-      <c r="N50" s="33" t="n">
-        <v>1.185</v>
+        <v>955.85</v>
+      </c>
+      <c r="N50" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="O50" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P50" s="25" t="inlineStr">
@@ -3629,9 +3653,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q50" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Drogaraia R$ 438.02)</t>
+      <c r="Q50" s="27" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3641,54 +3665,50 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10051359</t>
+          <t>10044745</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>SENSOR SMART 2.0 GX-01S MEDLEVENSOHN</t>
+          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1439.82</v>
+        <v>532.29</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>1799.25</v>
+        <v>923.37</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-359.43</v>
+        <v>-391.08</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.2</v>
+        <v>-0.424</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>962</v>
-      </c>
-      <c r="I51" s="11" t="n">
-        <v>0.76</v>
+        <v>5858</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>4.65</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>309</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K51" s="12" t="inlineStr"/>
       <c r="L51" s="13" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
-        <v>449</v>
-      </c>
-      <c r="N51" s="29" t="n">
-        <v>-0.312</v>
-      </c>
+        <v>83.92</v>
+      </c>
+      <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="13" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P51" s="13" t="inlineStr">
@@ -3698,7 +3718,7 @@
       </c>
       <c r="Q51" s="15" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3708,31 +3728,31 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>10051297</t>
+          <t>10000913</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>LEAVE IN ELSEVE 100ML COLAGENO LIFTER</t>
+          <t>TADALAFILA 20MG 8CP REV GEN PRATI</t>
         </is>
       </c>
       <c r="D52" s="19" t="n">
-        <v>110.16</v>
+        <v>300.86</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>463.53</v>
+        <v>691.66</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>-353.37</v>
+        <v>-390.8</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>-0.762</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>6815</v>
-      </c>
-      <c r="I52" s="30" t="n">
-        <v>5.41</v>
+        <v>12867</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>10.22</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -3740,18 +3760,18 @@
         </is>
       </c>
       <c r="K52" s="19" t="n">
-        <v>59.99</v>
+        <v>59.31</v>
       </c>
       <c r="L52" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M52" s="19" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="N52" s="33" t="n">
-        <v>0.7190000000000001</v>
+        <v>19.9</v>
+      </c>
+      <c r="N52" s="31" t="n">
+        <v>1.98</v>
       </c>
       <c r="O52" s="25" t="inlineStr">
         <is>
@@ -3765,7 +3785,7 @@
       </c>
       <c r="Q52" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 34.90)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 19.90)</t>
         </is>
       </c>
     </row>
@@ -3775,44 +3795,54 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>10052934</t>
+          <t>100018652</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>NEBULIZADOR COMPRESSOR HC032 TRAVEL MULTILASER</t>
+          <t>OLEO BIO OIL 200ML PURCELLIN</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>352.61</v>
+        <v>380.07</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-352.61</v>
+        <v>-380.07</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>3068</v>
+        <v>2638</v>
       </c>
       <c r="I53" s="28" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K53" s="12" t="inlineStr"/>
-      <c r="L53" s="13" t="inlineStr"/>
-      <c r="M53" s="12" t="inlineStr"/>
-      <c r="N53" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>134.99</v>
+      </c>
+      <c r="L53" s="13" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>67.19</v>
+      </c>
+      <c r="N53" s="33" t="n">
+        <v>1.009</v>
+      </c>
       <c r="O53" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P53" s="13" t="inlineStr">
@@ -3820,9 +3850,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q53" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 67.19)</t>
         </is>
       </c>
     </row>
@@ -3832,31 +3862,31 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>10025441</t>
+          <t>100022385</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>CREATINE 300G MAXTITANIUM</t>
+          <t>ENTRESTO 50MG 28CP REV NOVARTIS</t>
         </is>
       </c>
       <c r="D54" s="19" t="n">
-        <v>231.51</v>
+        <v>343.58</v>
       </c>
       <c r="E54" s="19" t="n">
-        <v>582.24</v>
+        <v>715.51</v>
       </c>
       <c r="F54" s="20" t="n">
-        <v>-350.73</v>
+        <v>-371.93</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>-0.602</v>
+        <v>-0.52</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>3506</v>
-      </c>
-      <c r="I54" s="30" t="n">
-        <v>2.78</v>
+        <v>6572</v>
+      </c>
+      <c r="I54" s="29" t="n">
+        <v>5.22</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -3864,18 +3894,18 @@
         </is>
       </c>
       <c r="K54" s="19" t="n">
-        <v>59.9</v>
+        <v>202.11</v>
       </c>
       <c r="L54" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M54" s="19" t="n">
-        <v>39.96</v>
-      </c>
-      <c r="N54" s="33" t="n">
-        <v>0.499</v>
+        <v>171.85</v>
+      </c>
+      <c r="N54" s="31" t="n">
+        <v>0.176</v>
       </c>
       <c r="O54" s="25" t="inlineStr">
         <is>
@@ -3889,7 +3919,7 @@
       </c>
       <c r="Q54" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 39.96)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 171.85)</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -294,16 +294,16 @@
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 15:53:44 (15:53) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 16:53:43 (16:53) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>6830.17</v>
+        <v>7775.31</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-6830.17</v>
+        <v>-7775.31</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>-1</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>4553.44</v>
+        <v>5183.54</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>-4553.44</v>
+        <v>-5183.54</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>-1</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="P6" s="25" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Detrator Crítico</t>
         </is>
       </c>
       <c r="Q6" s="27" t="inlineStr">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>334.4</v>
+        <v>419.3</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>2224.86</v>
+        <v>2532.73</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-1890.46</v>
+        <v>-2113.43</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.85</v>
+        <v>-0.8340000000000001</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>26223</v>
@@ -980,54 +980,44 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>10040750</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>WEGOVY 1MG 3ML NOVO NORDISK</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>1698</v>
+        <v>295.96</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>3462.62</v>
+        <v>2238.81</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>-1764.62</v>
+        <v>-1942.85</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>-0.51</v>
+        <v>-0.868</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>3321</v>
+        <v>39477</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>2.64</v>
+        <v>31.36</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K8" s="19" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="L8" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M8" s="19" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N8" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="K8" s="24" t="inlineStr"/>
+      <c r="L8" s="25" t="inlineStr"/>
+      <c r="M8" s="24" t="inlineStr"/>
+      <c r="N8" s="26" t="inlineStr"/>
       <c r="O8" s="25" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P8" s="25" t="inlineStr">
@@ -1037,7 +1027,7 @@
       </c>
       <c r="Q8" s="27" t="inlineStr">
         <is>
-          <t>Push CRM / Recompra 30d no App</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1047,31 +1037,31 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>221.97</v>
+        <v>509.9</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1966.67</v>
+        <v>2252.44</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1744.7</v>
+        <v>-1742.54</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.887</v>
+        <v>-0.774</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>39477</v>
+        <v>3146</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>31.36</v>
+        <v>2.5</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1104,54 +1094,50 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10041248</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>CREATINA MONOHIDRATADA 300G DUX</t>
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>1496.42</v>
+        <v>249.17</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>3066.89</v>
+        <v>1914.57</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-1570.47</v>
+        <v>-1665.4</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>-0.512</v>
+        <v>-0.87</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>2446</v>
+        <v>4427</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>1.94</v>
+        <v>3.52</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>99.90000000000001</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K10" s="24" t="inlineStr"/>
       <c r="L10" s="25" t="inlineStr">
         <is>
           <t>AMAZON</t>
         </is>
       </c>
       <c r="M10" s="19" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N10" s="31" t="n">
-        <v>1.132</v>
-      </c>
+        <v>50.25</v>
+      </c>
+      <c r="N10" s="26" t="inlineStr"/>
       <c r="O10" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P10" s="25" t="inlineStr">
@@ -1159,9 +1145,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q10" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+      <c r="Q10" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1171,44 +1157,54 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>509.9</v>
+        <v>1995.92</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1978.64</v>
+        <v>3491.28</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-1468.74</v>
+        <v>-1495.36</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.742</v>
+        <v>-0.428</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>3146</v>
+        <v>2446</v>
       </c>
       <c r="I11" s="28" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr"/>
-      <c r="L11" s="13" t="inlineStr"/>
-      <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="N11" s="30" t="n">
+        <v>1.132</v>
+      </c>
       <c r="O11" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P11" s="13" t="inlineStr">
@@ -1216,9 +1212,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q11" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -1228,45 +1224,45 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>10041248</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>CREATINA MONOHIDRATADA 300G DUX</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>249.17</v>
+        <v>0</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>1681.84</v>
+        <v>1467.07</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>-1432.67</v>
+        <v>-1467.07</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.852</v>
+        <v>-1</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>4427</v>
-      </c>
-      <c r="I12" s="29" t="n">
-        <v>3.52</v>
+        <v>204</v>
+      </c>
+      <c r="I12" s="23" t="n">
+        <v>0.16</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K12" s="24" t="inlineStr"/>
       <c r="L12" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M12" s="19" t="n">
-        <v>50.25</v>
+        <v>1212.9</v>
       </c>
       <c r="N12" s="26" t="inlineStr"/>
       <c r="O12" s="25" t="inlineStr">
@@ -1281,7 +1277,7 @@
       </c>
       <c r="Q12" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1291,35 +1287,35 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>415.06</v>
+        <v>2291.87</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1763.28</v>
+        <v>3710.39</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-1348.22</v>
+        <v>-1418.52</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.765</v>
+        <v>-0.382</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>1270</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>1.01</v>
+        <v>8275</v>
+      </c>
+      <c r="I13" s="28" t="n">
+        <v>6.57</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr"/>
@@ -1338,7 +1334,7 @@
       </c>
       <c r="Q13" s="15" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1348,50 +1344,54 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>10025098</t>
+          <t>10024521</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
+          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D14" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>1288.74</v>
+        <v>1352.65</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>-1288.74</v>
+        <v>-1352.65</v>
       </c>
       <c r="G14" s="21" t="n">
         <v>-1</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>204</v>
+        <v>575</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>0.16</v>
+        <v>0.46</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K14" s="24" t="inlineStr"/>
+      <c r="K14" s="19" t="n">
+        <v>799.9</v>
+      </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M14" s="19" t="n">
-        <v>1212.9</v>
-      </c>
-      <c r="N14" s="26" t="inlineStr"/>
+        <v>814.9</v>
+      </c>
+      <c r="N14" s="31" t="n">
+        <v>-0.018</v>
+      </c>
       <c r="O14" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P14" s="25" t="inlineStr">
@@ -1411,50 +1411,54 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10093877</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>MIRENA 52MG 1END+INS BAYER</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0</v>
+        <v>1010.62</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1287.3</v>
+        <v>2309.05</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-1287.3</v>
+        <v>-1298.43</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-1</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>501</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>0.4</v>
+        <v>8909</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>7.08</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K15" s="12" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>108.49</v>
+      </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
-        <v>1225.89</v>
-      </c>
-      <c r="N15" s="14" t="inlineStr"/>
+        <v>97.69</v>
+      </c>
+      <c r="N15" s="30" t="n">
+        <v>0.111</v>
+      </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P15" s="13" t="inlineStr">
@@ -1462,9 +1466,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q15" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -1474,39 +1478,39 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>833.04</v>
+        <v>5659</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>2028.37</v>
+        <v>6951.22</v>
       </c>
       <c r="F16" s="20" t="n">
-        <v>-1195.33</v>
+        <v>-1292.22</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>-0.589</v>
+        <v>-0.186</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>8909</v>
+        <v>9409</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>7.08</v>
+        <v>7.47</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K16" s="19" t="n">
-        <v>108.49</v>
+        <v>988.22</v>
       </c>
       <c r="L16" s="25" t="inlineStr">
         <is>
@@ -1514,14 +1518,14 @@
         </is>
       </c>
       <c r="M16" s="19" t="n">
-        <v>97.69</v>
+        <v>988.22</v>
       </c>
       <c r="N16" s="31" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="O16" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P16" s="25" t="inlineStr">
@@ -1529,9 +1533,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q16" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+      <c r="Q16" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1541,31 +1545,31 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10024521</t>
+          <t>10025745</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
+          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1188.22</v>
+        <v>1246.39</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-1188.22</v>
+        <v>-1246.39</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>575</v>
+        <v>122</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.46</v>
+        <v>0.1</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1573,18 +1577,18 @@
         </is>
       </c>
       <c r="K17" s="7" t="n">
-        <v>799.9</v>
+        <v>1105.6</v>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
-        <v>814.9</v>
+        <v>1170.01</v>
       </c>
       <c r="N17" s="32" t="n">
-        <v>-0.018</v>
+        <v>-0.055</v>
       </c>
       <c r="O17" s="13" t="inlineStr">
         <is>
@@ -1608,31 +1612,31 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>2090.44</v>
+        <v>0</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>3259.37</v>
+        <v>1212.81</v>
       </c>
       <c r="F18" s="20" t="n">
-        <v>-1168.93</v>
+        <v>-1212.81</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>-0.359</v>
+        <v>-1</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>8275</v>
+        <v>11806</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>6.57</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1665,39 +1669,39 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10025745</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0</v>
+        <v>592.53</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1094.89</v>
+        <v>1792.36</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-1094.89</v>
+        <v>-1199.83</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-1</v>
+        <v>-0.669</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>122</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>0.1</v>
+        <v>12853</v>
+      </c>
+      <c r="I19" s="28" t="n">
+        <v>10.21</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K19" s="7" t="n">
-        <v>1105.6</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
@@ -1705,14 +1709,14 @@
         </is>
       </c>
       <c r="M19" s="7" t="n">
-        <v>1170.01</v>
-      </c>
-      <c r="N19" s="32" t="n">
-        <v>-0.055</v>
+        <v>61.06</v>
+      </c>
+      <c r="N19" s="30" t="n">
+        <v>0.113</v>
       </c>
       <c r="O19" s="13" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P19" s="13" t="inlineStr">
@@ -1720,9 +1724,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q19" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -1732,44 +1736,54 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>0</v>
+        <v>936.36</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>1065.38</v>
+        <v>2068.45</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>-1065.38</v>
+        <v>-1132.09</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>-1</v>
+        <v>-0.547</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>11806</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>9.380000000000001</v>
+        <v>837</v>
+      </c>
+      <c r="I20" s="23" t="n">
+        <v>0.66</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K20" s="24" t="inlineStr"/>
-      <c r="L20" s="25" t="inlineStr"/>
-      <c r="M20" s="24" t="inlineStr"/>
-      <c r="N20" s="26" t="inlineStr"/>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>315.46</v>
+      </c>
+      <c r="L20" s="25" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M20" s="19" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="N20" s="33" t="n">
+        <v>0.333</v>
+      </c>
       <c r="O20" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P20" s="25" t="inlineStr">
@@ -1777,9 +1791,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q20" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q20" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -1789,54 +1803,54 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>5041</v>
+        <v>90.02</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6106.25</v>
+        <v>1168.04</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-1065.25</v>
+        <v>-1078.02</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-0.174</v>
+        <v>-0.9229999999999999</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>9409</v>
+        <v>22233</v>
       </c>
       <c r="I21" s="28" t="n">
-        <v>7.47</v>
+        <v>17.66</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>988.22</v>
+        <v>25.9</v>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N21" s="32" t="n">
-        <v>0</v>
+        <v>15.9</v>
+      </c>
+      <c r="N21" s="30" t="n">
+        <v>0.629</v>
       </c>
       <c r="O21" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P21" s="13" t="inlineStr">
@@ -1844,9 +1858,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q21" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -1856,54 +1870,44 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D22" s="19" t="n">
-        <v>524.54</v>
+        <v>944.5599999999999</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>1574.48</v>
+        <v>2007.27</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>-1049.94</v>
+        <v>-1062.71</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>-0.667</v>
+        <v>-0.529</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>12853</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>10.21</v>
+        <v>1270</v>
+      </c>
+      <c r="I22" s="23" t="n">
+        <v>1.01</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="L22" s="25" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M22" s="19" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N22" s="31" t="n">
-        <v>0.113</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="inlineStr"/>
+      <c r="L22" s="25" t="inlineStr"/>
+      <c r="M22" s="24" t="inlineStr"/>
+      <c r="N22" s="26" t="inlineStr"/>
       <c r="O22" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P22" s="25" t="inlineStr">
@@ -1911,9 +1915,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q22" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+      <c r="Q22" s="27" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1923,54 +1927,44 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1026.06</v>
+        <v>1035.01</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-1000.16</v>
+        <v>-1035.01</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.975</v>
+        <v>-1</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>22233</v>
+        <v>30285</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>17.66</v>
+        <v>24.05</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N23" s="33" t="n">
-        <v>0.629</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="inlineStr"/>
+      <c r="L23" s="13" t="inlineStr"/>
+      <c r="M23" s="12" t="inlineStr"/>
+      <c r="N23" s="14" t="inlineStr"/>
       <c r="O23" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P23" s="13" t="inlineStr">
@@ -1978,9 +1972,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+      <c r="Q23" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1990,44 +1984,54 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D24" s="19" t="n">
-        <v>0</v>
+        <v>1223.25</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>909.1900000000001</v>
+        <v>2191.45</v>
       </c>
       <c r="F24" s="20" t="n">
-        <v>-909.1900000000001</v>
+        <v>-968.2</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>-1</v>
+        <v>-0.442</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>30285</v>
+        <v>2931</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>24.05</v>
+        <v>2.33</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K24" s="24" t="inlineStr"/>
-      <c r="L24" s="25" t="inlineStr"/>
-      <c r="M24" s="24" t="inlineStr"/>
-      <c r="N24" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>218.67</v>
+      </c>
+      <c r="L24" s="25" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M24" s="19" t="n">
+        <v>197.18</v>
+      </c>
+      <c r="N24" s="33" t="n">
+        <v>0.109</v>
+      </c>
       <c r="O24" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P24" s="25" t="inlineStr">
@@ -2035,9 +2039,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q24" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q24" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -2047,54 +2051,44 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>936.36</v>
+        <v>372.59</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>1817.02</v>
+        <v>1278.48</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-880.66</v>
+        <v>-905.89</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.485</v>
+        <v>-0.7090000000000001</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>837</v>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>0.66</v>
+        <v>9864</v>
+      </c>
+      <c r="I25" s="28" t="n">
+        <v>7.83</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>315.46</v>
-      </c>
-      <c r="L25" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N25" s="33" t="n">
-        <v>0.333</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="inlineStr"/>
+      <c r="L25" s="13" t="inlineStr"/>
+      <c r="M25" s="12" t="inlineStr"/>
+      <c r="N25" s="14" t="inlineStr"/>
       <c r="O25" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P25" s="13" t="inlineStr">
@@ -2102,9 +2096,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+      <c r="Q25" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2114,54 +2108,50 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D26" s="19" t="n">
-        <v>1050.82</v>
+        <v>2019.56</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>1925.06</v>
+        <v>2913.63</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>-874.24</v>
+        <v>-894.0700000000001</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>-0.454</v>
+        <v>-0.307</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>2931</v>
+        <v>2081</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K26" s="19" t="n">
-        <v>218.67</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="inlineStr"/>
       <c r="L26" s="25" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
       <c r="M26" s="19" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N26" s="31" t="n">
-        <v>0.109</v>
-      </c>
+        <v>549.9</v>
+      </c>
+      <c r="N26" s="26" t="inlineStr"/>
       <c r="O26" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P26" s="25" t="inlineStr">
@@ -2169,9 +2159,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q26" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+      <c r="Q26" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2181,44 +2171,54 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>315.09</v>
+        <v>1161.19</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>1123.08</v>
+        <v>1970.89</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-807.99</v>
+        <v>-809.7</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.7190000000000001</v>
+        <v>-0.411</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>9864</v>
+        <v>3992</v>
       </c>
       <c r="I27" s="28" t="n">
-        <v>7.83</v>
+        <v>3.17</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K27" s="12" t="inlineStr"/>
-      <c r="L27" s="13" t="inlineStr"/>
-      <c r="M27" s="12" t="inlineStr"/>
-      <c r="N27" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="N27" s="30" t="n">
+        <v>0.396</v>
+      </c>
       <c r="O27" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr">
@@ -2226,9 +2226,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q27" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -2238,54 +2238,44 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10052540</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
         </is>
       </c>
       <c r="D28" s="19" t="n">
-        <v>1041.2</v>
+        <v>687.12</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>1731.32</v>
+        <v>1389.1</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>-690.12</v>
+        <v>-701.98</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>-0.399</v>
+        <v>-0.505</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>3992</v>
+        <v>2601</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>3.17</v>
+        <v>2.07</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K28" s="19" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="L28" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>107</v>
-      </c>
-      <c r="N28" s="31" t="n">
-        <v>0.396</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr"/>
+      <c r="L28" s="25" t="inlineStr"/>
+      <c r="M28" s="24" t="inlineStr"/>
+      <c r="N28" s="26" t="inlineStr"/>
       <c r="O28" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P28" s="25" t="inlineStr">
@@ -2293,9 +2283,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q28" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+      <c r="Q28" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2305,31 +2295,31 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>100008085</t>
+          <t>10099241</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>ELIQUIS 5MG 60TBS PFIZER</t>
+          <t>NAN COMFOR 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>5.98</v>
+        <v>927.8200000000001</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>603.35</v>
+        <v>1608.14</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-597.37</v>
+        <v>-680.3200000000001</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-0.99</v>
+        <v>-0.423</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>2887</v>
+        <v>13024</v>
       </c>
       <c r="I29" s="28" t="n">
-        <v>2.29</v>
+        <v>10.34</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2362,31 +2352,31 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>10041082</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>0</v>
+        <v>857.6900000000001</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>554.87</v>
+        <v>1530.92</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>-554.87</v>
+        <v>-673.23</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>-1</v>
+        <v>-0.44</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>5609</v>
+        <v>11106</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>4.46</v>
+        <v>8.82</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -2419,54 +2409,44 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>100022270</t>
+          <t>10041082</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>225.46</v>
+        <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>774.01</v>
+        <v>631.65</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-548.55</v>
+        <v>-631.65</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-0.7090000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>1962</v>
+        <v>5609</v>
       </c>
       <c r="I31" s="28" t="n">
-        <v>1.56</v>
+        <v>4.46</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>185.61</v>
-      </c>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="n">
-        <v>158.66</v>
-      </c>
-      <c r="N31" s="33" t="n">
-        <v>0.17</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="inlineStr"/>
+      <c r="L31" s="13" t="inlineStr"/>
+      <c r="M31" s="12" t="inlineStr"/>
+      <c r="N31" s="14" t="inlineStr"/>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P31" s="13" t="inlineStr">
@@ -2474,9 +2454,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
+      <c r="Q31" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2486,46 +2466,40 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10041858</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
         </is>
       </c>
       <c r="D32" s="19" t="n">
-        <v>2019.56</v>
+        <v>169.9</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>2559.46</v>
+        <v>740.78</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>-539.9</v>
+        <v>-570.88</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>-0.211</v>
+        <v>-0.7709999999999999</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>2081</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>1.65</v>
+        <v>646</v>
+      </c>
+      <c r="I32" s="23" t="n">
+        <v>0.51</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K32" s="24" t="inlineStr"/>
-      <c r="L32" s="25" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M32" s="19" t="n">
-        <v>549.9</v>
-      </c>
+      <c r="L32" s="25" t="inlineStr"/>
+      <c r="M32" s="24" t="inlineStr"/>
       <c r="N32" s="26" t="inlineStr"/>
       <c r="O32" s="25" t="inlineStr">
         <is>
@@ -2539,7 +2513,7 @@
       </c>
       <c r="Q32" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2549,44 +2523,54 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10052540</t>
+          <t>10038798</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
+          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>687.12</v>
+        <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1220.25</v>
+        <v>567.48</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-533.13</v>
+        <v>-567.48</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.4370000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>2601</v>
-      </c>
-      <c r="I33" s="28" t="n">
-        <v>2.07</v>
+        <v>1623</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>1.29</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K33" s="12" t="inlineStr"/>
-      <c r="L33" s="13" t="inlineStr"/>
-      <c r="M33" s="12" t="inlineStr"/>
-      <c r="N33" s="14" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>180.79</v>
+      </c>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="N33" s="30" t="n">
+        <v>0.028</v>
+      </c>
       <c r="O33" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P33" s="13" t="inlineStr">
@@ -2596,7 +2580,7 @@
       </c>
       <c r="Q33" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2606,31 +2590,31 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>10038798</t>
+          <t>10040748</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
+          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>498.5</v>
+        <v>549.58</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>-498.5</v>
+        <v>-549.58</v>
       </c>
       <c r="G34" s="21" t="n">
         <v>-1</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>1623</v>
+        <v>402</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>1.29</v>
+        <v>0.32</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -2638,22 +2622,22 @@
         </is>
       </c>
       <c r="K34" s="19" t="n">
-        <v>180.79</v>
+        <v>1298.54</v>
       </c>
       <c r="L34" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M34" s="19" t="n">
-        <v>175.9</v>
+        <v>1298.54</v>
       </c>
       <c r="N34" s="31" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P34" s="25" t="inlineStr">
@@ -2673,31 +2657,31 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10001098</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>857.6900000000001</v>
+        <v>1129.42</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1344.83</v>
+        <v>1660.61</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-487.14</v>
+        <v>-531.1900000000001</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-0.362</v>
+        <v>-0.32</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>11106</v>
+        <v>8492</v>
       </c>
       <c r="I35" s="28" t="n">
-        <v>8.82</v>
+        <v>6.75</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2730,35 +2714,35 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>10099241</t>
+          <t>999705</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>NAN COMFOR 1 800G NESTLE</t>
+          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>927.8200000000001</v>
+        <v>0</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>1412.66</v>
+        <v>510.68</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>-484.84</v>
+        <v>-510.68</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>-0.343</v>
+        <v>-1</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>13024</v>
-      </c>
-      <c r="I36" s="29" t="n">
-        <v>10.34</v>
+        <v>37</v>
+      </c>
+      <c r="I36" s="23" t="n">
+        <v>0.03</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K36" s="24" t="inlineStr"/>
@@ -2777,7 +2761,7 @@
       </c>
       <c r="Q36" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2787,54 +2771,44 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10040748</t>
+          <t>10044679</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
+          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0</v>
+        <v>142.52</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>482.78</v>
+        <v>642.6799999999999</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-482.78</v>
+        <v>-500.16</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-1</v>
+        <v>-0.778</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>402</v>
+        <v>324</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K37" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="L37" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N37" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K37" s="12" t="inlineStr"/>
+      <c r="L37" s="13" t="inlineStr"/>
+      <c r="M37" s="12" t="inlineStr"/>
+      <c r="N37" s="14" t="inlineStr"/>
       <c r="O37" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P37" s="13" t="inlineStr">
@@ -2854,35 +2828,35 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>10041858</t>
+          <t>10033759</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER M 66UN</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>169.9</v>
+        <v>169.8</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>650.73</v>
+        <v>666.0700000000001</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>-480.83</v>
+        <v>-496.27</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>-0.7390000000000001</v>
+        <v>-0.745</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>646</v>
-      </c>
-      <c r="I38" s="23" t="n">
-        <v>0.51</v>
+        <v>10622</v>
+      </c>
+      <c r="I38" s="29" t="n">
+        <v>8.44</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K38" s="24" t="inlineStr"/>
@@ -2901,7 +2875,7 @@
       </c>
       <c r="Q38" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2911,31 +2885,31 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10001098</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>978.5599999999999</v>
+        <v>1866.48</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1458.75</v>
+        <v>2348.34</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-480.19</v>
+        <v>-481.86</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.329</v>
+        <v>-0.205</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8492</v>
+        <v>15647</v>
       </c>
       <c r="I39" s="28" t="n">
-        <v>6.75</v>
+        <v>12.43</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2968,50 +2942,50 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>100001425</t>
+          <t>10025441</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
+          <t>CREATINE 300G MAXTITANIUM</t>
         </is>
       </c>
       <c r="D40" s="19" t="n">
-        <v>179.3</v>
+        <v>291.41</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>631.3200000000001</v>
+        <v>762.67</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>-452.02</v>
+        <v>-471.26</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>-0.716</v>
+        <v>-0.618</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>13421</v>
+        <v>3506</v>
       </c>
       <c r="I40" s="29" t="n">
-        <v>10.66</v>
+        <v>2.78</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K40" s="19" t="n">
-        <v>29.9</v>
+        <v>59.9</v>
       </c>
       <c r="L40" s="25" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M40" s="19" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="N40" s="31" t="n">
-        <v>0.035</v>
+        <v>39.96</v>
+      </c>
+      <c r="N40" s="33" t="n">
+        <v>0.499</v>
       </c>
       <c r="O40" s="25" t="inlineStr">
         <is>
@@ -3023,9 +2997,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q40" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q40" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 39.96)</t>
         </is>
       </c>
     </row>
@@ -3035,44 +3009,54 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>999705</t>
+          <t>100022385</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
+          <t>ENTRESTO 50MG 28CP REV NOVARTIS</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0</v>
+        <v>343.58</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>448.61</v>
+        <v>814.52</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-448.61</v>
+        <v>-470.94</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-1</v>
+        <v>-0.578</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>0.03</v>
+        <v>6572</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>5.22</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K41" s="12" t="inlineStr"/>
-      <c r="L41" s="13" t="inlineStr"/>
-      <c r="M41" s="12" t="inlineStr"/>
-      <c r="N41" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>202.11</v>
+      </c>
+      <c r="L41" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>171.85</v>
+      </c>
+      <c r="N41" s="30" t="n">
+        <v>0.176</v>
+      </c>
       <c r="O41" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P41" s="13" t="inlineStr">
@@ -3080,9 +3064,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q41" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 171.85)</t>
         </is>
       </c>
     </row>
@@ -3092,31 +3076,31 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>10025441</t>
+          <t>100022270</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>CREATINE 300G MAXTITANIUM</t>
+          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
         </is>
       </c>
       <c r="D42" s="19" t="n">
-        <v>231.51</v>
+        <v>416.44</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>669.96</v>
+        <v>881.11</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>-438.45</v>
+        <v>-464.67</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>-0.654</v>
+        <v>-0.527</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>3506</v>
+        <v>1962</v>
       </c>
       <c r="I42" s="29" t="n">
-        <v>2.78</v>
+        <v>1.56</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -3124,18 +3108,18 @@
         </is>
       </c>
       <c r="K42" s="19" t="n">
-        <v>59.9</v>
+        <v>185.61</v>
       </c>
       <c r="L42" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M42" s="19" t="n">
-        <v>39.96</v>
-      </c>
-      <c r="N42" s="31" t="n">
-        <v>0.499</v>
+        <v>158.66</v>
+      </c>
+      <c r="N42" s="33" t="n">
+        <v>0.17</v>
       </c>
       <c r="O42" s="25" t="inlineStr">
         <is>
@@ -3149,7 +3133,7 @@
       </c>
       <c r="Q42" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 39.96)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
         </is>
       </c>
     </row>
@@ -3159,54 +3143,54 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10051297</t>
+          <t>10050639</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>LEAVE IN ELSEVE 100ML COLAGENO LIFTER</t>
+          <t>EXTENSIOR 0,25MG+0,5MG 1,5ML NOVO EUROFARMA</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>110.16</v>
+        <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>533.36</v>
+        <v>449.81</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-423.2</v>
+        <v>-449.81</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-0.7929999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>6815</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>5.41</v>
+        <v>784</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>0.62</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K43" s="7" t="n">
-        <v>59.99</v>
+        <v>955.85</v>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="N43" s="33" t="n">
-        <v>0.7190000000000001</v>
+        <v>955.85</v>
+      </c>
+      <c r="N43" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="O43" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P43" s="13" t="inlineStr">
@@ -3214,9 +3198,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 34.90)</t>
+      <c r="Q43" s="15" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3226,35 +3210,35 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>10044679</t>
+          <t>10049066</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
+          <t>KIT DOVE SH 350+COND 175ML HIDRATACAO+HIALURON VIT</t>
         </is>
       </c>
       <c r="D44" s="19" t="n">
-        <v>142.52</v>
+        <v>168.82</v>
       </c>
       <c r="E44" s="19" t="n">
-        <v>564.5599999999999</v>
+        <v>613.21</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>-422.04</v>
+        <v>-444.39</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>-0.748</v>
+        <v>-0.725</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>324</v>
-      </c>
-      <c r="I44" s="23" t="n">
-        <v>0.26</v>
+        <v>18637</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>14.8</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K44" s="24" t="inlineStr"/>
@@ -3273,7 +3257,7 @@
       </c>
       <c r="Q44" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3283,50 +3267,50 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10050453</t>
+          <t>100018652</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>HORMUS 250MG/ML SOL INJ 2AMP 4ML EUROFARMA (C5)</t>
+          <t>OLEO BIO OIL 200ML PURCELLIN</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>417.11</v>
+        <v>432.66</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-417.11</v>
+        <v>-432.66</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>834</v>
-      </c>
-      <c r="I45" s="11" t="n">
-        <v>0.66</v>
+        <v>2638</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>2.1</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K45" s="7" t="n">
-        <v>957.25</v>
+        <v>134.99</v>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
-        <v>438.02</v>
-      </c>
-      <c r="N45" s="33" t="n">
-        <v>1.185</v>
+        <v>67.19</v>
+      </c>
+      <c r="N45" s="30" t="n">
+        <v>1.009</v>
       </c>
       <c r="O45" s="13" t="inlineStr">
         <is>
@@ -3340,7 +3324,7 @@
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Drogaraia R$ 438.02)</t>
+          <t>Reprecificar no Digital (Amazon R$ 67.19)</t>
         </is>
       </c>
     </row>
@@ -3350,54 +3334,50 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>10100048</t>
+          <t>10044745</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>RITALINA LA 10MG 30CP NOVARTIS (A3)</t>
+          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
         </is>
       </c>
       <c r="D46" s="19" t="n">
-        <v>242.08</v>
+        <v>618.83</v>
       </c>
       <c r="E46" s="19" t="n">
-        <v>659.12</v>
+        <v>1051.15</v>
       </c>
       <c r="F46" s="20" t="n">
-        <v>-417.04</v>
+        <v>-432.32</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>-0.633</v>
+        <v>-0.411</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>3843</v>
+        <v>5858</v>
       </c>
       <c r="I46" s="29" t="n">
-        <v>3.05</v>
+        <v>4.65</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K46" s="19" t="n">
-        <v>137.55</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="inlineStr"/>
       <c r="L46" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M46" s="19" t="n">
-        <v>120.9</v>
-      </c>
-      <c r="N46" s="31" t="n">
-        <v>0.138</v>
-      </c>
+        <v>83.92</v>
+      </c>
+      <c r="N46" s="26" t="inlineStr"/>
       <c r="O46" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P46" s="25" t="inlineStr">
@@ -3405,9 +3385,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q46" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 120.90)</t>
+      <c r="Q46" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3417,40 +3397,46 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10033759</t>
+          <t>10035972</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER M 66UN</t>
+          <t>CONDRES LONGBIO 90CAP EMS</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>169.8</v>
+        <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>585.1</v>
+        <v>422.03</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-415.3</v>
+        <v>-422.03</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-0.71</v>
+        <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>10622</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>8.44</v>
+        <v>1136</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>0.9</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr"/>
-      <c r="L47" s="13" t="inlineStr"/>
-      <c r="M47" s="12" t="inlineStr"/>
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>352.33</v>
+      </c>
       <c r="N47" s="14" t="inlineStr"/>
       <c r="O47" s="13" t="inlineStr">
         <is>
@@ -3464,7 +3450,7 @@
       </c>
       <c r="Q47" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3474,54 +3460,44 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>10050653</t>
+          <t>100008756</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>POVIZTRA 1,7MG 3ML EUROFARMA</t>
+          <t>LEITE NEOCATE LCP 400G DANONE</t>
         </is>
       </c>
       <c r="D48" s="19" t="n">
-        <v>829</v>
+        <v>281.99</v>
       </c>
       <c r="E48" s="19" t="n">
-        <v>1231.45</v>
+        <v>694.99</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>-402.45</v>
+        <v>-413</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>-0.327</v>
+        <v>-0.594</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>2647</v>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>2.1</v>
+        <v>1484</v>
+      </c>
+      <c r="I48" s="23" t="n">
+        <v>1.18</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K48" s="19" t="n">
-        <v>1347.91</v>
-      </c>
-      <c r="L48" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M48" s="19" t="n">
-        <v>1347.89</v>
-      </c>
-      <c r="N48" s="30" t="n">
-        <v>0</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="inlineStr"/>
+      <c r="L48" s="25" t="inlineStr"/>
+      <c r="M48" s="24" t="inlineStr"/>
+      <c r="N48" s="26" t="inlineStr"/>
       <c r="O48" s="25" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P48" s="25" t="inlineStr">
@@ -3531,7 +3507,7 @@
       </c>
       <c r="Q48" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3541,44 +3517,54 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10049066</t>
+          <t>10032625</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 175ML HIDRATACAO+HIALURON VIT</t>
+          <t>EXTRATO DE CANNABIS SATIVA 79,14MG 30ML MANTECORP (B1)</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>141.22</v>
+        <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>538.67</v>
+        <v>411.42</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-397.45</v>
+        <v>-411.42</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-0.738</v>
+        <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>18637</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>14.8</v>
+        <v>112</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>0.09</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr"/>
-      <c r="L49" s="13" t="inlineStr"/>
-      <c r="M49" s="12" t="inlineStr"/>
-      <c r="N49" s="14" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>961.2</v>
+      </c>
+      <c r="L49" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="n">
+        <v>925.9</v>
+      </c>
+      <c r="N49" s="30" t="n">
+        <v>0.038</v>
+      </c>
       <c r="O49" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P49" s="13" t="inlineStr">
@@ -3588,7 +3574,7 @@
       </c>
       <c r="Q49" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3598,31 +3584,31 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>10050639</t>
+          <t>10028272</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>EXTENSIOR 0,25MG+0,5MG 1,5ML NOVO EUROFARMA</t>
+          <t>MTOR 1G 90CP EUROFARMA</t>
         </is>
       </c>
       <c r="D50" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>395.13</v>
+        <v>407.87</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>-395.13</v>
+        <v>-407.87</v>
       </c>
       <c r="G50" s="21" t="n">
         <v>-1</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>784</v>
+        <v>1017</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>0.62</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -3630,22 +3616,22 @@
         </is>
       </c>
       <c r="K50" s="19" t="n">
-        <v>955.85</v>
+        <v>366.7</v>
       </c>
       <c r="L50" s="25" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M50" s="19" t="n">
-        <v>955.85</v>
-      </c>
-      <c r="N50" s="30" t="n">
-        <v>0</v>
+        <v>359.99</v>
+      </c>
+      <c r="N50" s="33" t="n">
+        <v>0.019</v>
       </c>
       <c r="O50" s="25" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P50" s="25" t="inlineStr">
@@ -3665,50 +3651,54 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10044745</t>
+          <t>10007354</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
+          <t>ITRACONAZOL 100MG 15CAP GEN GEOLAB</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>532.29</v>
+        <v>445.43</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>923.37</v>
+        <v>849.9400000000001</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-391.08</v>
+        <v>-404.51</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.424</v>
+        <v>-0.476</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>5858</v>
+        <v>5153</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>4.65</v>
+        <v>4.09</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K51" s="12" t="inlineStr"/>
+      <c r="K51" s="7" t="n">
+        <v>49.9</v>
+      </c>
       <c r="L51" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
-        <v>83.92</v>
-      </c>
-      <c r="N51" s="14" t="inlineStr"/>
+        <v>75.98999999999999</v>
+      </c>
+      <c r="N51" s="32" t="n">
+        <v>-0.343</v>
+      </c>
       <c r="O51" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P51" s="13" t="inlineStr">
@@ -3728,54 +3718,50 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>10000913</t>
+          <t>10089756</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>TADALAFILA 20MG 8CP REV GEN PRATI</t>
+          <t>RITALINA 10MG 60CP NOVARTIS (A3)</t>
         </is>
       </c>
       <c r="D52" s="19" t="n">
-        <v>300.86</v>
+        <v>81.95</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>691.66</v>
+        <v>475.93</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>-390.8</v>
+        <v>-393.98</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.828</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>12867</v>
+        <v>7860</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>10.22</v>
+        <v>6.24</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K52" s="19" t="n">
-        <v>59.31</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K52" s="24" t="inlineStr"/>
       <c r="L52" s="25" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
       <c r="M52" s="19" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N52" s="31" t="n">
-        <v>1.98</v>
-      </c>
+        <v>92.95</v>
+      </c>
+      <c r="N52" s="26" t="inlineStr"/>
       <c r="O52" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P52" s="25" t="inlineStr">
@@ -3783,9 +3769,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q52" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 19.90)</t>
+      <c r="Q52" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3795,54 +3781,54 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>100018652</t>
+          <t>10045450</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>OLEO BIO OIL 200ML PURCELLIN</t>
+          <t>TOALHAS UMED BABYSEC ULTRA FRESH LV4PG3</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
+        <v>233.99</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>617.34</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>-383.35</v>
+      </c>
+      <c r="G53" s="9" t="n">
+        <v>-0.621</v>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>1964</v>
+      </c>
+      <c r="I53" s="28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="L53" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="N53" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="7" t="n">
-        <v>380.07</v>
-      </c>
-      <c r="F53" s="8" t="n">
-        <v>-380.07</v>
-      </c>
-      <c r="G53" s="9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H53" s="10" t="n">
-        <v>2638</v>
-      </c>
-      <c r="I53" s="28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>134.99</v>
-      </c>
-      <c r="L53" s="13" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
-        <v>67.19</v>
-      </c>
-      <c r="N53" s="33" t="n">
-        <v>1.009</v>
-      </c>
       <c r="O53" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P53" s="13" t="inlineStr">
@@ -3850,9 +3836,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 67.19)</t>
+      <c r="Q53" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3862,50 +3848,50 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>100022385</t>
+          <t>100001425</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>ENTRESTO 50MG 28CP REV NOVARTIS</t>
+          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D54" s="19" t="n">
-        <v>343.58</v>
+        <v>335.39</v>
       </c>
       <c r="E54" s="19" t="n">
-        <v>715.51</v>
+        <v>718.6799999999999</v>
       </c>
       <c r="F54" s="20" t="n">
-        <v>-371.93</v>
+        <v>-383.29</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>-0.52</v>
+        <v>-0.5329999999999999</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>6572</v>
+        <v>13421</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>5.22</v>
+        <v>10.66</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K54" s="19" t="n">
-        <v>202.11</v>
+        <v>29.9</v>
       </c>
       <c r="L54" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M54" s="19" t="n">
-        <v>171.85</v>
-      </c>
-      <c r="N54" s="31" t="n">
-        <v>0.176</v>
+        <v>28.9</v>
+      </c>
+      <c r="N54" s="33" t="n">
+        <v>0.035</v>
       </c>
       <c r="O54" s="25" t="inlineStr">
         <is>
@@ -3917,9 +3903,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q54" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 171.85)</t>
+      <c r="Q54" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -294,16 +294,16 @@
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 16:53:43 (16:53) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 17:53:48 (17:53) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7775.31</v>
+        <v>8723.91</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-7775.31</v>
+        <v>-8723.91</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>-1</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>5183.54</v>
+        <v>5815.94</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>-5183.54</v>
+        <v>-5815.94</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>-1</v>
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>419.3</v>
+        <v>504.2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>2532.73</v>
+        <v>2841.73</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-2113.43</v>
+        <v>-2337.53</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.8340000000000001</v>
+        <v>-0.823</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>26223</v>
@@ -989,16 +989,16 @@
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>295.96</v>
+        <v>369.95</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>2238.81</v>
+        <v>2511.95</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>-1942.85</v>
+        <v>-2142</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>-0.868</v>
+        <v>-0.853</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>39477</v>
@@ -1049,13 +1049,13 @@
         <v>509.9</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2252.44</v>
+        <v>2527.24</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1742.54</v>
+        <v>-2017.34</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.774</v>
+        <v>-0.7979999999999999</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>3146</v>
@@ -1106,13 +1106,13 @@
         <v>249.17</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>1914.57</v>
+        <v>2148.15</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-1665.4</v>
+        <v>-1898.98</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>-0.87</v>
+        <v>-0.884</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>4427</v>
@@ -1157,54 +1157,50 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1995.92</v>
+        <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3491.28</v>
+        <v>1646.06</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-1495.36</v>
+        <v>-1646.06</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.428</v>
+        <v>-1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>2446</v>
-      </c>
-      <c r="I11" s="28" t="n">
-        <v>1.94</v>
+        <v>204</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>0.16</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>99.90000000000001</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr"/>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N11" s="30" t="n">
-        <v>1.132</v>
-      </c>
+        <v>1212.9</v>
+      </c>
+      <c r="N11" s="14" t="inlineStr"/>
       <c r="O11" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P11" s="13" t="inlineStr">
@@ -1212,9 +1208,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+      <c r="Q11" s="15" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1224,50 +1220,54 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>10025098</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>0</v>
+        <v>2395.52</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>1467.07</v>
+        <v>3917.22</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>-1467.07</v>
+        <v>-1521.7</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-1</v>
+        <v>-0.388</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>204</v>
-      </c>
-      <c r="I12" s="23" t="n">
-        <v>0.16</v>
+        <v>2446</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>1.94</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K12" s="24" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>99.90000000000001</v>
+      </c>
       <c r="L12" s="25" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M12" s="19" t="n">
-        <v>1212.9</v>
-      </c>
-      <c r="N12" s="26" t="inlineStr"/>
+        <v>46.85</v>
+      </c>
+      <c r="N12" s="30" t="n">
+        <v>1.132</v>
+      </c>
       <c r="O12" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P12" s="25" t="inlineStr">
@@ -1275,9 +1275,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q12" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q12" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -1287,44 +1287,54 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2291.87</v>
+        <v>592.53</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3710.39</v>
+        <v>2011.03</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-1418.52</v>
+        <v>-1418.5</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.382</v>
+        <v>-0.705</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>8275</v>
+        <v>12853</v>
       </c>
       <c r="I13" s="28" t="n">
-        <v>6.57</v>
+        <v>10.21</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr"/>
-      <c r="L13" s="13" t="inlineStr"/>
-      <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="N13" s="31" t="n">
+        <v>0.113</v>
+      </c>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr">
@@ -1332,9 +1342,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q13" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -1344,54 +1354,44 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>10024521</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0</v>
+        <v>838.66</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>1352.65</v>
+        <v>2252.16</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>-1352.65</v>
+        <v>-1413.5</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>-1</v>
+        <v>-0.628</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>575</v>
+        <v>1270</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>0.46</v>
+        <v>1.01</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K14" s="19" t="n">
-        <v>799.9</v>
-      </c>
-      <c r="L14" s="25" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>814.9</v>
-      </c>
-      <c r="N14" s="31" t="n">
-        <v>-0.018</v>
-      </c>
+      <c r="K14" s="24" t="inlineStr"/>
+      <c r="L14" s="25" t="inlineStr"/>
+      <c r="M14" s="24" t="inlineStr"/>
+      <c r="N14" s="26" t="inlineStr"/>
       <c r="O14" s="25" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P14" s="25" t="inlineStr">
@@ -1411,54 +1411,54 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10025745</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1010.62</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2309.05</v>
+        <v>1398.46</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-1298.43</v>
+        <v>-1398.46</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8909</v>
-      </c>
-      <c r="I15" s="28" t="n">
-        <v>7.08</v>
+        <v>122</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>0.1</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K15" s="7" t="n">
-        <v>108.49</v>
+        <v>1105.6</v>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N15" s="30" t="n">
-        <v>0.111</v>
+        <v>1170.01</v>
+      </c>
+      <c r="N15" s="32" t="n">
+        <v>-0.055</v>
       </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P15" s="13" t="inlineStr">
@@ -1466,9 +1466,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+      <c r="Q15" s="15" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1478,54 +1478,44 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>5659</v>
+        <v>2839.91</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>6951.22</v>
+        <v>4163.07</v>
       </c>
       <c r="F16" s="20" t="n">
-        <v>-1292.22</v>
+        <v>-1323.16</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>-0.186</v>
+        <v>-0.318</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>9409</v>
+        <v>8275</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>7.47</v>
+        <v>6.57</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K16" s="19" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="L16" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N16" s="31" t="n">
-        <v>0</v>
-      </c>
+      <c r="K16" s="24" t="inlineStr"/>
+      <c r="L16" s="25" t="inlineStr"/>
+      <c r="M16" s="24" t="inlineStr"/>
+      <c r="N16" s="26" t="inlineStr"/>
       <c r="O16" s="25" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P16" s="25" t="inlineStr">
@@ -1545,54 +1535,44 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10025745</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1246.39</v>
+        <v>1360.78</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-1246.39</v>
+        <v>-1266.35</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-1</v>
+        <v>-0.9309999999999999</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>122</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>0.1</v>
+        <v>11806</v>
+      </c>
+      <c r="I17" s="28" t="n">
+        <v>9.380000000000001</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>1105.6</v>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>1170.01</v>
-      </c>
-      <c r="N17" s="32" t="n">
-        <v>-0.055</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="13" t="inlineStr"/>
+      <c r="M17" s="12" t="inlineStr"/>
+      <c r="N17" s="14" t="inlineStr"/>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P17" s="13" t="inlineStr">
@@ -1602,7 +1582,7 @@
       </c>
       <c r="Q17" s="15" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1612,31 +1592,31 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>0</v>
+        <v>2019.56</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>1212.81</v>
+        <v>3269.09</v>
       </c>
       <c r="F18" s="20" t="n">
-        <v>-1212.81</v>
+        <v>-1249.53</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>-1</v>
+        <v>-0.382</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>11806</v>
+        <v>2081</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>9.380000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1644,8 +1624,14 @@
         </is>
       </c>
       <c r="K18" s="24" t="inlineStr"/>
-      <c r="L18" s="25" t="inlineStr"/>
-      <c r="M18" s="24" t="inlineStr"/>
+      <c r="L18" s="25" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M18" s="19" t="n">
+        <v>549.9</v>
+      </c>
       <c r="N18" s="26" t="inlineStr"/>
       <c r="O18" s="25" t="inlineStr">
         <is>
@@ -1669,31 +1655,31 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>592.53</v>
+        <v>1223.25</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1792.36</v>
+        <v>2458.81</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-1199.83</v>
+        <v>-1235.56</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-0.669</v>
+        <v>-0.503</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>12853</v>
+        <v>2931</v>
       </c>
       <c r="I19" s="28" t="n">
-        <v>10.21</v>
+        <v>2.33</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1701,18 +1687,18 @@
         </is>
       </c>
       <c r="K19" s="7" t="n">
-        <v>67.98999999999999</v>
+        <v>218.67</v>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M19" s="7" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N19" s="30" t="n">
-        <v>0.113</v>
+        <v>197.18</v>
+      </c>
+      <c r="N19" s="31" t="n">
+        <v>0.109</v>
       </c>
       <c r="O19" s="13" t="inlineStr">
         <is>
@@ -1726,7 +1712,7 @@
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -1736,50 +1722,50 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>936.36</v>
+        <v>90.02</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>2068.45</v>
+        <v>1310.55</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>-1132.09</v>
+        <v>-1220.53</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>-0.547</v>
+        <v>-0.9309999999999999</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>837</v>
-      </c>
-      <c r="I20" s="23" t="n">
-        <v>0.66</v>
+        <v>22233</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>17.66</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K20" s="19" t="n">
-        <v>315.46</v>
+        <v>25.9</v>
       </c>
       <c r="L20" s="25" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M20" s="19" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N20" s="33" t="n">
-        <v>0.333</v>
+        <v>15.9</v>
+      </c>
+      <c r="N20" s="30" t="n">
+        <v>0.629</v>
       </c>
       <c r="O20" s="25" t="inlineStr">
         <is>
@@ -1793,7 +1779,7 @@
       </c>
       <c r="Q20" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -1803,54 +1789,44 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>90.02</v>
+        <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1168.04</v>
+        <v>1161.28</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-1078.02</v>
+        <v>-1161.28</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-0.9229999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>22233</v>
+        <v>30285</v>
       </c>
       <c r="I21" s="28" t="n">
-        <v>17.66</v>
+        <v>24.05</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="L21" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N21" s="30" t="n">
-        <v>0.629</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr"/>
+      <c r="L21" s="13" t="inlineStr"/>
+      <c r="M21" s="12" t="inlineStr"/>
+      <c r="N21" s="14" t="inlineStr"/>
       <c r="O21" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P21" s="13" t="inlineStr">
@@ -1858,9 +1834,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+      <c r="Q21" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1870,54 +1846,64 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D22" s="19" t="n">
-        <v>944.5599999999999</v>
+        <v>1598.13</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>2007.27</v>
+        <v>2590.76</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>-1062.71</v>
+        <v>-992.63</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>-0.529</v>
+        <v>-0.383</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>1270</v>
-      </c>
-      <c r="I22" s="23" t="n">
-        <v>1.01</v>
+        <v>8909</v>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>7.08</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K22" s="24" t="inlineStr"/>
-      <c r="L22" s="25" t="inlineStr"/>
-      <c r="M22" s="24" t="inlineStr"/>
-      <c r="N22" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>108.49</v>
+      </c>
+      <c r="L22" s="25" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M22" s="19" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="N22" s="30" t="n">
+        <v>0.111</v>
+      </c>
       <c r="O22" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P22" s="25" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
-        </is>
-      </c>
-      <c r="Q22" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Neutro</t>
+        </is>
+      </c>
+      <c r="Q22" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -1927,31 +1913,31 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0</v>
+        <v>459.11</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1035.01</v>
+        <v>1434.46</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-1035.01</v>
+        <v>-975.35</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-1</v>
+        <v>-0.68</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>30285</v>
+        <v>9864</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>24.05</v>
+        <v>7.83</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1969,7 +1955,7 @@
       </c>
       <c r="P23" s="13" t="inlineStr">
         <is>
-          <t>Detrator Moderado</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="Q23" s="15" t="inlineStr">
@@ -1984,31 +1970,31 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D24" s="19" t="n">
-        <v>1223.25</v>
+        <v>1271.42</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>2191.45</v>
+        <v>2211.35</v>
       </c>
       <c r="F24" s="20" t="n">
-        <v>-968.2</v>
+        <v>-939.9299999999999</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>-0.442</v>
+        <v>-0.425</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>2931</v>
+        <v>3992</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>2.33</v>
+        <v>3.17</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -2016,18 +2002,18 @@
         </is>
       </c>
       <c r="K24" s="19" t="n">
-        <v>218.67</v>
+        <v>149.4</v>
       </c>
       <c r="L24" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M24" s="19" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N24" s="33" t="n">
-        <v>0.109</v>
+        <v>107</v>
+      </c>
+      <c r="N24" s="30" t="n">
+        <v>0.396</v>
       </c>
       <c r="O24" s="25" t="inlineStr">
         <is>
@@ -2041,7 +2027,7 @@
       </c>
       <c r="Q24" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -2051,44 +2037,54 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>372.59</v>
+        <v>1438.54</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>1278.48</v>
+        <v>2320.8</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-905.89</v>
+        <v>-882.26</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.7090000000000001</v>
+        <v>-0.38</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>9864</v>
-      </c>
-      <c r="I25" s="28" t="n">
-        <v>7.83</v>
+        <v>837</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>0.66</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K25" s="12" t="inlineStr"/>
-      <c r="L25" s="13" t="inlineStr"/>
-      <c r="M25" s="12" t="inlineStr"/>
-      <c r="N25" s="14" t="inlineStr"/>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>315.46</v>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="N25" s="31" t="n">
+        <v>0.333</v>
+      </c>
       <c r="O25" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P25" s="13" t="inlineStr">
@@ -2096,9 +2092,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q25" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -2108,31 +2104,31 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10099241</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>NAN COMFOR 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D26" s="19" t="n">
-        <v>2019.56</v>
+        <v>922.87</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>2913.63</v>
+        <v>1804.34</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>-894.0700000000001</v>
+        <v>-881.47</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>-0.307</v>
+        <v>-0.489</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>2081</v>
+        <v>13024</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>1.65</v>
+        <v>10.34</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -2140,14 +2136,8 @@
         </is>
       </c>
       <c r="K26" s="24" t="inlineStr"/>
-      <c r="L26" s="25" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M26" s="19" t="n">
-        <v>549.9</v>
-      </c>
+      <c r="L26" s="25" t="inlineStr"/>
+      <c r="M26" s="24" t="inlineStr"/>
       <c r="N26" s="26" t="inlineStr"/>
       <c r="O26" s="25" t="inlineStr">
         <is>
@@ -2171,54 +2161,44 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10052540</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1161.19</v>
+        <v>687.12</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>1970.89</v>
+        <v>1558.58</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-809.7</v>
+        <v>-871.46</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.411</v>
+        <v>-0.5589999999999999</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>3992</v>
+        <v>2601</v>
       </c>
       <c r="I27" s="28" t="n">
-        <v>3.17</v>
+        <v>2.07</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="L27" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="N27" s="30" t="n">
-        <v>0.396</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K27" s="12" t="inlineStr"/>
+      <c r="L27" s="13" t="inlineStr"/>
+      <c r="M27" s="12" t="inlineStr"/>
+      <c r="N27" s="14" t="inlineStr"/>
       <c r="O27" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr">
@@ -2226,9 +2206,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+      <c r="Q27" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2238,44 +2218,54 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>10052540</t>
+          <t>10024521</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
+          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D28" s="19" t="n">
-        <v>687.12</v>
+        <v>799.9</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>1389.1</v>
+        <v>1517.67</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>-701.98</v>
+        <v>-717.77</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>-0.505</v>
+        <v>-0.473</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>2601</v>
-      </c>
-      <c r="I28" s="29" t="n">
-        <v>2.07</v>
+        <v>575</v>
+      </c>
+      <c r="I28" s="23" t="n">
+        <v>0.46</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K28" s="24" t="inlineStr"/>
-      <c r="L28" s="25" t="inlineStr"/>
-      <c r="M28" s="24" t="inlineStr"/>
-      <c r="N28" s="26" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K28" s="19" t="n">
+        <v>799.9</v>
+      </c>
+      <c r="L28" s="25" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>814.9</v>
+      </c>
+      <c r="N28" s="33" t="n">
+        <v>-0.018</v>
+      </c>
       <c r="O28" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P28" s="25" t="inlineStr">
@@ -2285,7 +2275,7 @@
       </c>
       <c r="Q28" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2295,31 +2285,31 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10099241</t>
+          <t>10041082</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>NAN COMFOR 1 800G NESTLE</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>927.8200000000001</v>
+        <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>1608.14</v>
+        <v>708.71</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-680.3200000000001</v>
+        <v>-708.71</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-0.423</v>
+        <v>-1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>13024</v>
+        <v>5609</v>
       </c>
       <c r="I29" s="28" t="n">
-        <v>10.34</v>
+        <v>4.46</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2352,44 +2342,54 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10038798</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>857.6900000000001</v>
+        <v>0</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>1530.92</v>
+        <v>636.71</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>-673.23</v>
+        <v>-636.71</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>-0.44</v>
+        <v>-1</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>11106</v>
-      </c>
-      <c r="I30" s="29" t="n">
-        <v>8.82</v>
+        <v>1623</v>
+      </c>
+      <c r="I30" s="23" t="n">
+        <v>1.29</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K30" s="24" t="inlineStr"/>
-      <c r="L30" s="25" t="inlineStr"/>
-      <c r="M30" s="24" t="inlineStr"/>
-      <c r="N30" s="26" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>180.79</v>
+      </c>
+      <c r="L30" s="25" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M30" s="19" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="N30" s="30" t="n">
+        <v>0.028</v>
+      </c>
       <c r="O30" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P30" s="25" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="Q30" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2409,44 +2409,54 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10041082</t>
+          <t>10025441</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
+          <t>CREATINE 300G MAXTITANIUM</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0</v>
+        <v>231.51</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>631.65</v>
+        <v>855.71</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-631.65</v>
+        <v>-624.2</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-1</v>
+        <v>-0.7290000000000001</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>5609</v>
+        <v>3506</v>
       </c>
       <c r="I31" s="28" t="n">
-        <v>4.46</v>
+        <v>2.78</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K31" s="12" t="inlineStr"/>
-      <c r="L31" s="13" t="inlineStr"/>
-      <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="N31" s="31" t="n">
+        <v>0.499</v>
+      </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P31" s="13" t="inlineStr">
@@ -2454,9 +2464,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q31" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 39.96)</t>
         </is>
       </c>
     </row>
@@ -2466,35 +2476,35 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>10041858</t>
+          <t>10001098</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS PREMIUM CARE XXXG 80UN</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
         </is>
       </c>
       <c r="D32" s="19" t="n">
-        <v>169.9</v>
+        <v>1241.12</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>740.78</v>
+        <v>1863.21</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>-570.88</v>
+        <v>-622.09</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>-0.7709999999999999</v>
+        <v>-0.334</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>646</v>
-      </c>
-      <c r="I32" s="23" t="n">
-        <v>0.51</v>
+        <v>8492</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>6.75</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K32" s="24" t="inlineStr"/>
@@ -2513,7 +2523,7 @@
       </c>
       <c r="Q32" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2523,31 +2533,31 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10038798</t>
+          <t>10040748</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
+          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>567.48</v>
+        <v>616.63</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-567.48</v>
+        <v>-616.63</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>1623</v>
+        <v>402</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.29</v>
+        <v>0.32</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2555,22 +2565,22 @@
         </is>
       </c>
       <c r="K33" s="7" t="n">
-        <v>180.79</v>
+        <v>1298.54</v>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M33" s="7" t="n">
-        <v>175.9</v>
-      </c>
-      <c r="N33" s="30" t="n">
-        <v>0.028</v>
+        <v>1298.54</v>
+      </c>
+      <c r="N33" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="O33" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P33" s="13" t="inlineStr">
@@ -2590,54 +2600,44 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>10040748</t>
+          <t>10033759</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER M 66UN</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>0</v>
+        <v>169.8</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>549.58</v>
+        <v>747.33</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>-549.58</v>
+        <v>-577.53</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>-1</v>
+        <v>-0.773</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>402</v>
-      </c>
-      <c r="I34" s="23" t="n">
-        <v>0.32</v>
+        <v>10622</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <v>8.44</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K34" s="19" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="L34" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M34" s="19" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N34" s="31" t="n">
-        <v>0</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="inlineStr"/>
+      <c r="L34" s="25" t="inlineStr"/>
+      <c r="M34" s="24" t="inlineStr"/>
+      <c r="N34" s="26" t="inlineStr"/>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P34" s="25" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="Q34" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2657,35 +2657,35 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>10001098</t>
+          <t>999705</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
+          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>1129.42</v>
+        <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1660.61</v>
+        <v>572.99</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-531.1900000000001</v>
+        <v>-572.99</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-0.32</v>
+        <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8492</v>
-      </c>
-      <c r="I35" s="28" t="n">
-        <v>6.75</v>
+        <v>37</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>0.03</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="Q35" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2714,44 +2714,54 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>999705</t>
+          <t>100022270</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
+          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0</v>
+        <v>416.44</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>510.68</v>
+        <v>988.61</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>-510.68</v>
+        <v>-572.17</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>-1</v>
+        <v>-0.579</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>37</v>
-      </c>
-      <c r="I36" s="23" t="n">
-        <v>0.03</v>
+        <v>1962</v>
+      </c>
+      <c r="I36" s="29" t="n">
+        <v>1.56</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K36" s="24" t="inlineStr"/>
-      <c r="L36" s="25" t="inlineStr"/>
-      <c r="M36" s="24" t="inlineStr"/>
-      <c r="N36" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K36" s="19" t="n">
+        <v>185.61</v>
+      </c>
+      <c r="L36" s="25" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M36" s="19" t="n">
+        <v>158.66</v>
+      </c>
+      <c r="N36" s="30" t="n">
+        <v>0.17</v>
+      </c>
       <c r="O36" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P36" s="25" t="inlineStr">
@@ -2759,9 +2769,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q36" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q36" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
         </is>
       </c>
     </row>
@@ -2771,44 +2781,54 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10044679</t>
+          <t>100022385</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
+          <t>ENTRESTO 50MG 28CP REV NOVARTIS</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>142.52</v>
+        <v>343.58</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>642.6799999999999</v>
+        <v>913.89</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-500.16</v>
+        <v>-570.3099999999999</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.778</v>
+        <v>-0.624</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>324</v>
-      </c>
-      <c r="I37" s="11" t="n">
-        <v>0.26</v>
+        <v>6572</v>
+      </c>
+      <c r="I37" s="28" t="n">
+        <v>5.22</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K37" s="12" t="inlineStr"/>
-      <c r="L37" s="13" t="inlineStr"/>
-      <c r="M37" s="12" t="inlineStr"/>
-      <c r="N37" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>202.11</v>
+      </c>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>171.85</v>
+      </c>
+      <c r="N37" s="31" t="n">
+        <v>0.176</v>
+      </c>
       <c r="O37" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P37" s="13" t="inlineStr">
@@ -2816,9 +2836,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q37" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 171.85)</t>
         </is>
       </c>
     </row>
@@ -2828,31 +2848,31 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>10033759</t>
+          <t>10049066</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER M 66UN</t>
+          <t>KIT DOVE SH 350+COND 175ML HIDRATACAO+HIALURON VIT</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>169.8</v>
+        <v>168.82</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>666.0700000000001</v>
+        <v>688.03</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>-496.27</v>
+        <v>-519.21</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>-0.745</v>
+        <v>-0.755</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>10622</v>
+        <v>18637</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>8.44</v>
+        <v>14.8</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -2885,31 +2905,31 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1866.48</v>
+        <v>1205.39</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>2348.34</v>
+        <v>1717.7</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-481.86</v>
+        <v>-512.3099999999999</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.205</v>
+        <v>-0.298</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>15647</v>
+        <v>11106</v>
       </c>
       <c r="I39" s="28" t="n">
-        <v>12.43</v>
+        <v>8.82</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2942,54 +2962,54 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>10025441</t>
+          <t>10050639</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>CREATINE 300G MAXTITANIUM</t>
+          <t>EXTENSIOR 0,25MG+0,5MG 1,5ML NOVO EUROFARMA</t>
         </is>
       </c>
       <c r="D40" s="19" t="n">
-        <v>291.41</v>
+        <v>0</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>762.67</v>
+        <v>504.69</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>-471.26</v>
+        <v>-504.69</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>-0.618</v>
+        <v>-1</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>3506</v>
-      </c>
-      <c r="I40" s="29" t="n">
-        <v>2.78</v>
+        <v>784</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>0.62</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K40" s="19" t="n">
-        <v>59.9</v>
+        <v>955.85</v>
       </c>
       <c r="L40" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M40" s="19" t="n">
-        <v>39.96</v>
+        <v>955.85</v>
       </c>
       <c r="N40" s="33" t="n">
-        <v>0.499</v>
+        <v>0</v>
       </c>
       <c r="O40" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P40" s="25" t="inlineStr">
@@ -2997,9 +3017,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q40" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 39.96)</t>
+      <c r="Q40" s="27" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3009,54 +3029,44 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>100022385</t>
+          <t>100011549</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>ENTRESTO 50MG 28CP REV NOVARTIS</t>
+          <t>NAN SUPREME 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>343.58</v>
+        <v>1011.52</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>814.52</v>
+        <v>1510.83</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-470.94</v>
+        <v>-499.31</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-0.578</v>
+        <v>-0.33</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>6572</v>
+        <v>7665</v>
       </c>
       <c r="I41" s="28" t="n">
-        <v>5.22</v>
+        <v>6.09</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>202.11</v>
-      </c>
-      <c r="L41" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="n">
-        <v>171.85</v>
-      </c>
-      <c r="N41" s="30" t="n">
-        <v>0.176</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K41" s="12" t="inlineStr"/>
+      <c r="L41" s="13" t="inlineStr"/>
+      <c r="M41" s="12" t="inlineStr"/>
+      <c r="N41" s="14" t="inlineStr"/>
       <c r="O41" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P41" s="13" t="inlineStr">
@@ -3064,9 +3074,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 171.85)</t>
+      <c r="Q41" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3076,54 +3086,44 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>100022270</t>
+          <t>100008756</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
+          <t>LEITE NEOCATE LCP 400G DANONE</t>
         </is>
       </c>
       <c r="D42" s="19" t="n">
-        <v>416.44</v>
+        <v>281.99</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>881.11</v>
+        <v>779.78</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>-464.67</v>
+        <v>-497.79</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>-0.527</v>
+        <v>-0.638</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>1962</v>
-      </c>
-      <c r="I42" s="29" t="n">
-        <v>1.56</v>
+        <v>1484</v>
+      </c>
+      <c r="I42" s="23" t="n">
+        <v>1.18</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K42" s="19" t="n">
-        <v>185.61</v>
-      </c>
-      <c r="L42" s="25" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M42" s="19" t="n">
-        <v>158.66</v>
-      </c>
-      <c r="N42" s="33" t="n">
-        <v>0.17</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="inlineStr"/>
+      <c r="L42" s="25" t="inlineStr"/>
+      <c r="M42" s="24" t="inlineStr"/>
+      <c r="N42" s="26" t="inlineStr"/>
       <c r="O42" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P42" s="25" t="inlineStr">
@@ -3131,9 +3131,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q42" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
+      <c r="Q42" s="27" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3143,54 +3143,54 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10050639</t>
+          <t>100018652</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>EXTENSIOR 0,25MG+0,5MG 1,5ML NOVO EUROFARMA</t>
+          <t>OLEO BIO OIL 200ML PURCELLIN</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>449.81</v>
+        <v>485.44</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-449.81</v>
+        <v>-485.44</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>784</v>
-      </c>
-      <c r="I43" s="11" t="n">
-        <v>0.62</v>
+        <v>2638</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>2.1</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K43" s="7" t="n">
-        <v>955.85</v>
+        <v>134.99</v>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M43" s="7" t="n">
-        <v>955.85</v>
-      </c>
-      <c r="N43" s="32" t="n">
-        <v>0</v>
+        <v>67.19</v>
+      </c>
+      <c r="N43" s="31" t="n">
+        <v>1.009</v>
       </c>
       <c r="O43" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P43" s="13" t="inlineStr">
@@ -3198,9 +3198,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q43" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 67.19)</t>
         </is>
       </c>
     </row>
@@ -3210,31 +3210,31 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>10049066</t>
+          <t>10046010</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 175ML HIDRATACAO+HIALURON VIT</t>
+          <t>FR PAMPERS SUPERSEC MEGA M 40UN</t>
         </is>
       </c>
       <c r="D44" s="19" t="n">
-        <v>168.82</v>
+        <v>494.76</v>
       </c>
       <c r="E44" s="19" t="n">
-        <v>613.21</v>
+        <v>979.28</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>-444.39</v>
+        <v>-484.52</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>-0.725</v>
+        <v>-0.495</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>18637</v>
+        <v>6394</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>14.8</v>
+        <v>5.08</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -3267,54 +3267,50 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>100018652</t>
+          <t>10035972</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>OLEO BIO OIL 200ML PURCELLIN</t>
+          <t>CONDRES LONGBIO 90CAP EMS</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>432.66</v>
+        <v>473.52</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-432.66</v>
+        <v>-473.52</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>2638</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>2.1</v>
+        <v>1136</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>0.9</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>134.99</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K45" s="12" t="inlineStr"/>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
-        <v>67.19</v>
-      </c>
-      <c r="N45" s="30" t="n">
-        <v>1.009</v>
-      </c>
+        <v>352.33</v>
+      </c>
+      <c r="N45" s="14" t="inlineStr"/>
       <c r="O45" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P45" s="13" t="inlineStr">
@@ -3322,9 +3318,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 67.19)</t>
+      <c r="Q45" s="15" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3334,50 +3330,54 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>10044745</t>
+          <t>100001425</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
+          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D46" s="19" t="n">
-        <v>618.83</v>
+        <v>335.39</v>
       </c>
       <c r="E46" s="19" t="n">
-        <v>1051.15</v>
+        <v>806.36</v>
       </c>
       <c r="F46" s="20" t="n">
-        <v>-432.32</v>
+        <v>-470.97</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>-0.411</v>
+        <v>-0.584</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>5858</v>
+        <v>13421</v>
       </c>
       <c r="I46" s="29" t="n">
-        <v>4.65</v>
+        <v>10.66</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K46" s="24" t="inlineStr"/>
+      <c r="K46" s="19" t="n">
+        <v>29.9</v>
+      </c>
       <c r="L46" s="25" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M46" s="19" t="n">
-        <v>83.92</v>
-      </c>
-      <c r="N46" s="26" t="inlineStr"/>
+        <v>28.9</v>
+      </c>
+      <c r="N46" s="30" t="n">
+        <v>0.035</v>
+      </c>
       <c r="O46" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P46" s="25" t="inlineStr">
@@ -3397,50 +3397,54 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10035972</t>
+          <t>10032625</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>CONDRES LONGBIO 90CAP EMS</t>
+          <t>EXTRATO DE CANNABIS SATIVA 79,14MG 30ML MANTECORP (B1)</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>422.03</v>
+        <v>461.62</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-422.03</v>
+        <v>-461.62</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>1136</v>
+        <v>112</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>0.9</v>
+        <v>0.09</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr"/>
+      <c r="K47" s="7" t="n">
+        <v>961.2</v>
+      </c>
       <c r="L47" s="13" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
-        <v>352.33</v>
-      </c>
-      <c r="N47" s="14" t="inlineStr"/>
+        <v>925.9</v>
+      </c>
+      <c r="N47" s="31" t="n">
+        <v>0.038</v>
+      </c>
       <c r="O47" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P47" s="13" t="inlineStr">
@@ -3460,44 +3464,54 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>100008756</t>
+          <t>10028272</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>LEITE NEOCATE LCP 400G DANONE</t>
+          <t>MTOR 1G 90CP EUROFARMA</t>
         </is>
       </c>
       <c r="D48" s="19" t="n">
-        <v>281.99</v>
+        <v>0</v>
       </c>
       <c r="E48" s="19" t="n">
-        <v>694.99</v>
+        <v>457.64</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>-413</v>
+        <v>-457.64</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>-0.594</v>
+        <v>-1</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>1484</v>
+        <v>1017</v>
       </c>
       <c r="I48" s="23" t="n">
-        <v>1.18</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K48" s="24" t="inlineStr"/>
-      <c r="L48" s="25" t="inlineStr"/>
-      <c r="M48" s="24" t="inlineStr"/>
-      <c r="N48" s="26" t="inlineStr"/>
+      <c r="K48" s="19" t="n">
+        <v>366.7</v>
+      </c>
+      <c r="L48" s="25" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M48" s="19" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="N48" s="30" t="n">
+        <v>0.019</v>
+      </c>
       <c r="O48" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P48" s="25" t="inlineStr">
@@ -3517,54 +3531,50 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10032625</t>
+          <t>10089756</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>EXTRATO DE CANNABIS SATIVA 79,14MG 30ML MANTECORP (B1)</t>
+          <t>RITALINA 10MG 60CP NOVARTIS (A3)</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0</v>
+        <v>81.95</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>411.42</v>
+        <v>533.99</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-411.42</v>
+        <v>-452.04</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-1</v>
+        <v>-0.847</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>112</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>0.09</v>
+        <v>7860</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>6.24</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>961.2</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr"/>
       <c r="L49" s="13" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>925.9</v>
-      </c>
-      <c r="N49" s="30" t="n">
-        <v>0.038</v>
-      </c>
+        <v>92.95</v>
+      </c>
+      <c r="N49" s="14" t="inlineStr"/>
       <c r="O49" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P49" s="13" t="inlineStr">
@@ -3574,7 +3584,7 @@
       </c>
       <c r="Q49" s="15" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3584,54 +3594,44 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>10028272</t>
+          <t>10044679</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>MTOR 1G 90CP EUROFARMA</t>
+          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
         </is>
       </c>
       <c r="D50" s="19" t="n">
-        <v>0</v>
+        <v>285.04</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>407.87</v>
+        <v>721.09</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>-407.87</v>
+        <v>-436.05</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>-1</v>
+        <v>-0.605</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>1017</v>
+        <v>324</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K50" s="19" t="n">
-        <v>366.7</v>
-      </c>
-      <c r="L50" s="25" t="inlineStr">
-        <is>
-          <t>PANVEL</t>
-        </is>
-      </c>
-      <c r="M50" s="19" t="n">
-        <v>359.99</v>
-      </c>
-      <c r="N50" s="33" t="n">
-        <v>0.019</v>
-      </c>
+      <c r="K50" s="24" t="inlineStr"/>
+      <c r="L50" s="25" t="inlineStr"/>
+      <c r="M50" s="24" t="inlineStr"/>
+      <c r="N50" s="26" t="inlineStr"/>
       <c r="O50" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P50" s="25" t="inlineStr">
@@ -3651,54 +3651,44 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10007354</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>ITRACONAZOL 100MG 15CAP GEN GEOLAB</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>445.43</v>
+        <v>2204.95</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>849.9400000000001</v>
+        <v>2634.84</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-404.51</v>
+        <v>-429.89</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.476</v>
+        <v>-0.163</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>5153</v>
+        <v>15647</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>4.09</v>
+        <v>12.43</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K51" s="7" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="L51" s="13" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="n">
-        <v>75.98999999999999</v>
-      </c>
-      <c r="N51" s="32" t="n">
-        <v>-0.343</v>
-      </c>
+      <c r="K51" s="12" t="inlineStr"/>
+      <c r="L51" s="13" t="inlineStr"/>
+      <c r="M51" s="12" t="inlineStr"/>
+      <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="13" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P51" s="13" t="inlineStr">
@@ -3718,31 +3708,31 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>10089756</t>
+          <t>10037279</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>RITALINA 10MG 60CP NOVARTIS (A3)</t>
+          <t>FR CAPRICHO BABY MEGA XXG 54UN</t>
         </is>
       </c>
       <c r="D52" s="19" t="n">
-        <v>81.95</v>
+        <v>111.48</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>475.93</v>
+        <v>536.29</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>-393.98</v>
+        <v>-424.81</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>-0.828</v>
+        <v>-0.792</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>7860</v>
+        <v>5320</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>6.24</v>
+        <v>4.23</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -3750,14 +3740,8 @@
         </is>
       </c>
       <c r="K52" s="24" t="inlineStr"/>
-      <c r="L52" s="25" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M52" s="19" t="n">
-        <v>92.95</v>
-      </c>
+      <c r="L52" s="25" t="inlineStr"/>
+      <c r="M52" s="24" t="inlineStr"/>
       <c r="N52" s="26" t="inlineStr"/>
       <c r="O52" s="25" t="inlineStr">
         <is>
@@ -3781,31 +3765,31 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>10045450</t>
+          <t>100001759</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>TOALHAS UMED BABYSEC ULTRA FRESH LV4PG3</t>
+          <t>GESTINOL 0,075+0,03MG 84CP LIBBS</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>233.99</v>
+        <v>112.82</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>617.34</v>
+        <v>537.11</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-383.35</v>
+        <v>-424.29</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>-0.621</v>
+        <v>-0.79</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>1964</v>
+        <v>3208</v>
       </c>
       <c r="I53" s="28" t="n">
-        <v>1.56</v>
+        <v>2.55</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3813,18 +3797,18 @@
         </is>
       </c>
       <c r="K53" s="7" t="n">
-        <v>29.9</v>
+        <v>127.85</v>
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M53" s="7" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="N53" s="32" t="n">
-        <v>0</v>
+        <v>127.77</v>
+      </c>
+      <c r="N53" s="31" t="n">
+        <v>0.001</v>
       </c>
       <c r="O53" s="13" t="inlineStr">
         <is>
@@ -3848,54 +3832,44 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>100001425</t>
+          <t>10052031</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
+          <t>FIGURINHAS COPA DO MUNDO 2026 7UN</t>
         </is>
       </c>
       <c r="D54" s="19" t="n">
-        <v>335.39</v>
+        <v>7</v>
       </c>
       <c r="E54" s="19" t="n">
-        <v>718.6799999999999</v>
+        <v>427.37</v>
       </c>
       <c r="F54" s="20" t="n">
-        <v>-383.29</v>
+        <v>-420.37</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>-0.5329999999999999</v>
+        <v>-0.9840000000000001</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>13421</v>
+        <v>24208</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>10.66</v>
+        <v>19.23</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K54" s="19" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="L54" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M54" s="19" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="N54" s="33" t="n">
-        <v>0.035</v>
-      </c>
+      <c r="K54" s="24" t="inlineStr"/>
+      <c r="L54" s="25" t="inlineStr"/>
+      <c r="M54" s="24" t="inlineStr"/>
+      <c r="N54" s="26" t="inlineStr"/>
       <c r="O54" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P54" s="25" t="inlineStr">

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -297,13 +297,13 @@
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 17:53:48 (17:53) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 18:54:20 (18:54) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>8723.91</v>
+        <v>9927.690000000001</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-8723.91</v>
+        <v>-9927.690000000001</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>-1</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>5815.94</v>
+        <v>6618.46</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>-5815.94</v>
+        <v>-6618.46</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>-1</v>
@@ -935,13 +935,13 @@
         <v>504.2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>2841.73</v>
+        <v>3233.85</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-2337.53</v>
+        <v>-2729.65</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.823</v>
+        <v>-0.8440000000000001</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>26223</v>
@@ -992,13 +992,13 @@
         <v>369.95</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>2511.95</v>
+        <v>2858.57</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>-2142</v>
+        <v>-2488.62</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>-0.853</v>
+        <v>-0.871</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>39477</v>
@@ -1049,13 +1049,13 @@
         <v>509.9</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2527.24</v>
+        <v>2875.97</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-2017.34</v>
+        <v>-2366.07</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.7979999999999999</v>
+        <v>-0.823</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>3146</v>
@@ -1106,13 +1106,13 @@
         <v>249.17</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>2148.15</v>
+        <v>2444.57</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-1898.98</v>
+        <v>-2195.4</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>-0.884</v>
+        <v>-0.898</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>4427</v>
@@ -1169,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1646.06</v>
+        <v>1873.19</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-1646.06</v>
+        <v>-1873.19</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>-1</v>
@@ -1229,16 +1229,16 @@
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>2395.52</v>
+        <v>2595.32</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>3917.22</v>
+        <v>4457.75</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>-1521.7</v>
+        <v>-1862.43</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.388</v>
+        <v>-0.418</v>
       </c>
       <c r="H12" s="22" t="n">
         <v>2446</v>
@@ -1287,54 +1287,50 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>592.53</v>
+        <v>2019.56</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2011.03</v>
+        <v>3720.19</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-1418.5</v>
+        <v>-1700.63</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.705</v>
+        <v>-0.457</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>12853</v>
+        <v>2081</v>
       </c>
       <c r="I13" s="28" t="n">
-        <v>10.21</v>
+        <v>1.65</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>67.98999999999999</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr"/>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N13" s="31" t="n">
-        <v>0.113</v>
-      </c>
+        <v>549.9</v>
+      </c>
+      <c r="N13" s="14" t="inlineStr"/>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr">
@@ -1342,9 +1338,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+      <c r="Q13" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1354,44 +1350,54 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10025745</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>838.66</v>
+        <v>0</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>2252.16</v>
+        <v>1591.42</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>-1413.5</v>
+        <v>-1591.42</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>-0.628</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>1270</v>
+        <v>122</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>1.01</v>
+        <v>0.1</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K14" s="24" t="inlineStr"/>
-      <c r="L14" s="25" t="inlineStr"/>
-      <c r="M14" s="24" t="inlineStr"/>
-      <c r="N14" s="26" t="inlineStr"/>
+      <c r="K14" s="19" t="n">
+        <v>1105.6</v>
+      </c>
+      <c r="L14" s="25" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>1170.01</v>
+      </c>
+      <c r="N14" s="31" t="n">
+        <v>-0.055</v>
+      </c>
       <c r="O14" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P14" s="25" t="inlineStr">
@@ -1411,54 +1417,54 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10025745</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0</v>
+        <v>1223.25</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1398.46</v>
+        <v>2798.09</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-1398.46</v>
+        <v>-1574.84</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-1</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>122</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>0.1</v>
+        <v>2931</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>2.33</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K15" s="7" t="n">
-        <v>1105.6</v>
+        <v>218.67</v>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
-        <v>1170.01</v>
+        <v>197.18</v>
       </c>
       <c r="N15" s="32" t="n">
-        <v>-0.055</v>
+        <v>0.109</v>
       </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P15" s="13" t="inlineStr">
@@ -1466,9 +1472,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q15" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -1478,35 +1484,35 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>2839.91</v>
+        <v>1050.46</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>4163.07</v>
+        <v>2562.93</v>
       </c>
       <c r="F16" s="20" t="n">
-        <v>-1323.16</v>
+        <v>-1512.47</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>-0.318</v>
+        <v>-0.59</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>8275</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <v>6.57</v>
+        <v>1270</v>
+      </c>
+      <c r="I16" s="23" t="n">
+        <v>1.01</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K16" s="24" t="inlineStr"/>
@@ -1525,7 +1531,7 @@
       </c>
       <c r="Q16" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1535,44 +1541,54 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>94.43000000000001</v>
+        <v>90.02</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1360.78</v>
+        <v>1491.39</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-1266.35</v>
+        <v>-1401.37</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-0.9309999999999999</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>11806</v>
+        <v>22233</v>
       </c>
       <c r="I17" s="28" t="n">
-        <v>9.380000000000001</v>
+        <v>17.66</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="13" t="inlineStr"/>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N17" s="32" t="n">
+        <v>0.629</v>
+      </c>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P17" s="13" t="inlineStr">
@@ -1580,9 +1596,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q17" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -1592,31 +1608,31 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>2019.56</v>
+        <v>192.3</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>3269.09</v>
+        <v>1548.54</v>
       </c>
       <c r="F18" s="20" t="n">
-        <v>-1249.53</v>
+        <v>-1356.24</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>-0.382</v>
+        <v>-0.8759999999999999</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>2081</v>
+        <v>11806</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>1.65</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1624,14 +1640,8 @@
         </is>
       </c>
       <c r="K18" s="24" t="inlineStr"/>
-      <c r="L18" s="25" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M18" s="19" t="n">
-        <v>549.9</v>
-      </c>
+      <c r="L18" s="25" t="inlineStr"/>
+      <c r="M18" s="24" t="inlineStr"/>
       <c r="N18" s="26" t="inlineStr"/>
       <c r="O18" s="25" t="inlineStr">
         <is>
@@ -1655,54 +1665,44 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1223.25</v>
+        <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>2458.81</v>
+        <v>1321.52</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-1235.56</v>
+        <v>-1321.52</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-0.503</v>
+        <v>-1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>2931</v>
+        <v>30285</v>
       </c>
       <c r="I19" s="28" t="n">
-        <v>2.33</v>
+        <v>24.05</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>218.67</v>
-      </c>
-      <c r="L19" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>197.18</v>
-      </c>
-      <c r="N19" s="31" t="n">
-        <v>0.109</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr"/>
+      <c r="L19" s="13" t="inlineStr"/>
+      <c r="M19" s="12" t="inlineStr"/>
+      <c r="N19" s="14" t="inlineStr"/>
       <c r="O19" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P19" s="13" t="inlineStr">
@@ -1710,9 +1710,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+      <c r="Q19" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1722,31 +1722,31 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>90.02</v>
+        <v>1033.31</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>1310.55</v>
+        <v>2288.52</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>-1220.53</v>
+        <v>-1255.21</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>-0.9309999999999999</v>
+        <v>-0.5479999999999999</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>22233</v>
+        <v>12853</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>17.66</v>
+        <v>10.21</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1754,18 +1754,18 @@
         </is>
       </c>
       <c r="K20" s="19" t="n">
-        <v>25.9</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L20" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M20" s="19" t="n">
-        <v>15.9</v>
+        <v>61.06</v>
       </c>
       <c r="N20" s="30" t="n">
-        <v>0.629</v>
+        <v>0.113</v>
       </c>
       <c r="O20" s="25" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Q20" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -1789,31 +1789,31 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0</v>
+        <v>3483.24</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1161.28</v>
+        <v>4737.52</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-1161.28</v>
+        <v>-1254.28</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-1</v>
+        <v>-0.265</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>30285</v>
+        <v>8275</v>
       </c>
       <c r="I21" s="28" t="n">
-        <v>24.05</v>
+        <v>6.57</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1846,31 +1846,31 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D22" s="19" t="n">
-        <v>1598.13</v>
+        <v>1271.42</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>2590.76</v>
+        <v>2516.48</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>-992.63</v>
+        <v>-1245.06</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>-0.383</v>
+        <v>-0.495</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>8909</v>
+        <v>3992</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>7.08</v>
+        <v>3.17</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="K22" s="19" t="n">
-        <v>108.49</v>
+        <v>149.4</v>
       </c>
       <c r="L22" s="25" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="M22" s="19" t="n">
-        <v>97.69</v>
+        <v>107</v>
       </c>
       <c r="N22" s="30" t="n">
-        <v>0.111</v>
+        <v>0.396</v>
       </c>
       <c r="O22" s="25" t="inlineStr">
         <is>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="P22" s="25" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q22" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -1913,49 +1913,59 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>459.11</v>
+        <v>7638</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1434.46</v>
+        <v>8875.48</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-975.35</v>
+        <v>-1237.48</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.68</v>
+        <v>-0.139</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>9864</v>
+        <v>9409</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>7.83</v>
+        <v>7.47</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr"/>
-      <c r="L23" s="13" t="inlineStr"/>
-      <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="14" t="inlineStr"/>
+      <c r="K23" s="7" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>988.22</v>
+      </c>
+      <c r="N23" s="33" t="n">
+        <v>0</v>
+      </c>
       <c r="O23" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P23" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q23" s="15" t="inlineStr">
@@ -1970,31 +1980,31 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D24" s="19" t="n">
-        <v>1271.42</v>
+        <v>1775.71</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>2211.35</v>
+        <v>2948.25</v>
       </c>
       <c r="F24" s="20" t="n">
-        <v>-939.9299999999999</v>
+        <v>-1172.54</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>-0.425</v>
+        <v>-0.398</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>3992</v>
+        <v>8909</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>3.17</v>
+        <v>7.08</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -2002,7 +2012,7 @@
         </is>
       </c>
       <c r="K24" s="19" t="n">
-        <v>149.4</v>
+        <v>108.49</v>
       </c>
       <c r="L24" s="25" t="inlineStr">
         <is>
@@ -2010,10 +2020,10 @@
         </is>
       </c>
       <c r="M24" s="19" t="n">
-        <v>107</v>
+        <v>97.69</v>
       </c>
       <c r="N24" s="30" t="n">
-        <v>0.396</v>
+        <v>0.111</v>
       </c>
       <c r="O24" s="25" t="inlineStr">
         <is>
@@ -2022,12 +2032,12 @@
       </c>
       <c r="P24" s="25" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q24" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -2037,64 +2047,54 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>1438.54</v>
+        <v>575.72</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>2320.8</v>
+        <v>1632.4</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-882.26</v>
+        <v>-1056.68</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.38</v>
+        <v>-0.647</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>837</v>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>0.66</v>
+        <v>9864</v>
+      </c>
+      <c r="I25" s="28" t="n">
+        <v>7.83</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>315.46</v>
-      </c>
-      <c r="L25" s="13" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N25" s="31" t="n">
-        <v>0.333</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="inlineStr"/>
+      <c r="L25" s="13" t="inlineStr"/>
+      <c r="M25" s="12" t="inlineStr"/>
+      <c r="N25" s="14" t="inlineStr"/>
       <c r="O25" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P25" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q25" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2113,16 +2113,16 @@
         </is>
       </c>
       <c r="D26" s="19" t="n">
-        <v>922.87</v>
+        <v>1010.77</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>1804.34</v>
+        <v>2053.31</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>-881.47</v>
+        <v>-1042.54</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>-0.489</v>
+        <v>-0.508</v>
       </c>
       <c r="H26" s="22" t="n">
         <v>13024</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P26" s="25" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Detrator Moderado</t>
         </is>
       </c>
       <c r="Q26" s="27" t="inlineStr">
@@ -2161,44 +2161,54 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10052540</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>687.12</v>
+        <v>1672.1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>1558.58</v>
+        <v>2641.04</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-871.46</v>
+        <v>-968.9400000000001</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.5589999999999999</v>
+        <v>-0.367</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>2601</v>
-      </c>
-      <c r="I27" s="28" t="n">
-        <v>2.07</v>
+        <v>837</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>0.66</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K27" s="12" t="inlineStr"/>
-      <c r="L27" s="13" t="inlineStr"/>
-      <c r="M27" s="12" t="inlineStr"/>
-      <c r="N27" s="14" t="inlineStr"/>
+          <t>⚠️ Duplo Detrator</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>315.46</v>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="N27" s="32" t="n">
+        <v>0.333</v>
+      </c>
       <c r="O27" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr">
@@ -2206,9 +2216,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q27" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -2230,13 +2240,13 @@
         <v>799.9</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>1517.67</v>
+        <v>1727.09</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>-717.77</v>
+        <v>-927.1900000000001</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>-0.473</v>
+        <v>-0.537</v>
       </c>
       <c r="H28" s="22" t="n">
         <v>575</v>
@@ -2260,7 +2270,7 @@
       <c r="M28" s="19" t="n">
         <v>814.9</v>
       </c>
-      <c r="N28" s="33" t="n">
+      <c r="N28" s="31" t="n">
         <v>-0.018</v>
       </c>
       <c r="O28" s="25" t="inlineStr">
@@ -2297,10 +2307,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>708.71</v>
+        <v>806.51</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-708.71</v>
+        <v>-806.51</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>-1</v>
@@ -2342,54 +2352,44 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>10038798</t>
+          <t>10001098</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>0</v>
+        <v>1318.92</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>636.71</v>
+        <v>2120.3</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>-636.71</v>
+        <v>-801.38</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>-1</v>
+        <v>-0.3779999999999999</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>1623</v>
-      </c>
-      <c r="I30" s="23" t="n">
-        <v>1.29</v>
+        <v>8492</v>
+      </c>
+      <c r="I30" s="29" t="n">
+        <v>6.75</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>180.79</v>
-      </c>
-      <c r="L30" s="25" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M30" s="19" t="n">
-        <v>175.9</v>
-      </c>
-      <c r="N30" s="30" t="n">
-        <v>0.028</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="inlineStr"/>
+      <c r="L30" s="25" t="inlineStr"/>
+      <c r="M30" s="24" t="inlineStr"/>
+      <c r="N30" s="26" t="inlineStr"/>
       <c r="O30" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P30" s="25" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="Q30" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2409,54 +2409,44 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10025441</t>
+          <t>10052540</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>CREATINE 300G MAXTITANIUM</t>
+          <t>FR PAMPERS PANTS AJUSTE TOTAL MAX G 90UN</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>231.51</v>
+        <v>1016.05</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>855.71</v>
+        <v>1773.64</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-624.2</v>
+        <v>-757.59</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-0.7290000000000001</v>
+        <v>-0.427</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>3506</v>
+        <v>2601</v>
       </c>
       <c r="I31" s="28" t="n">
-        <v>2.78</v>
+        <v>2.07</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="n">
-        <v>39.96</v>
-      </c>
-      <c r="N31" s="31" t="n">
-        <v>0.499</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="inlineStr"/>
+      <c r="L31" s="13" t="inlineStr"/>
+      <c r="M31" s="12" t="inlineStr"/>
+      <c r="N31" s="14" t="inlineStr"/>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P31" s="13" t="inlineStr">
@@ -2464,9 +2454,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 39.96)</t>
+      <c r="Q31" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2476,44 +2466,54 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>10001098</t>
+          <t>10038798</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
+          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
         </is>
       </c>
       <c r="D32" s="19" t="n">
-        <v>1241.12</v>
+        <v>0</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>1863.21</v>
+        <v>724.5700000000001</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>-622.09</v>
+        <v>-724.5700000000001</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>-0.334</v>
+        <v>-1</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>8492</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>6.75</v>
+        <v>1623</v>
+      </c>
+      <c r="I32" s="23" t="n">
+        <v>1.29</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K32" s="24" t="inlineStr"/>
-      <c r="L32" s="25" t="inlineStr"/>
-      <c r="M32" s="24" t="inlineStr"/>
-      <c r="N32" s="26" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>180.79</v>
+      </c>
+      <c r="L32" s="25" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M32" s="19" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="N32" s="30" t="n">
+        <v>0.028</v>
+      </c>
       <c r="O32" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P32" s="25" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="Q32" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2533,54 +2533,54 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>10040748</t>
+          <t>100022270</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
+          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0</v>
+        <v>416.44</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>616.63</v>
+        <v>1125.02</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-616.63</v>
+        <v>-708.58</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-1</v>
+        <v>-0.63</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>402</v>
-      </c>
-      <c r="I33" s="11" t="n">
-        <v>0.32</v>
+        <v>1962</v>
+      </c>
+      <c r="I33" s="28" t="n">
+        <v>1.56</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K33" s="7" t="n">
-        <v>1298.54</v>
+        <v>185.61</v>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M33" s="7" t="n">
-        <v>1298.54</v>
+        <v>158.66</v>
       </c>
       <c r="N33" s="32" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="O33" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P33" s="13" t="inlineStr">
@@ -2588,9 +2588,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q33" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
         </is>
       </c>
     </row>
@@ -2600,44 +2600,54 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>10033759</t>
+          <t>10040748</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER M 66UN</t>
+          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>169.8</v>
+        <v>0</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>747.33</v>
+        <v>701.72</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>-577.53</v>
+        <v>-701.72</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>-0.773</v>
+        <v>-1</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>10622</v>
-      </c>
-      <c r="I34" s="29" t="n">
-        <v>8.44</v>
+        <v>402</v>
+      </c>
+      <c r="I34" s="23" t="n">
+        <v>0.32</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K34" s="24" t="inlineStr"/>
-      <c r="L34" s="25" t="inlineStr"/>
-      <c r="M34" s="24" t="inlineStr"/>
-      <c r="N34" s="26" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="L34" s="25" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M34" s="19" t="n">
+        <v>1298.54</v>
+      </c>
+      <c r="N34" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P34" s="25" t="inlineStr">
@@ -2647,7 +2657,7 @@
       </c>
       <c r="Q34" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2657,44 +2667,54 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>999705</t>
+          <t>100022385</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
+          <t>ENTRESTO 50MG 28CP REV NOVARTIS</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0</v>
+        <v>343.58</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>572.99</v>
+        <v>1040</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-572.99</v>
+        <v>-696.42</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-1</v>
+        <v>-0.67</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>0.03</v>
+        <v>6572</v>
+      </c>
+      <c r="I35" s="28" t="n">
+        <v>5.22</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K35" s="12" t="inlineStr"/>
-      <c r="L35" s="13" t="inlineStr"/>
-      <c r="M35" s="12" t="inlineStr"/>
-      <c r="N35" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>202.11</v>
+      </c>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>171.85</v>
+      </c>
+      <c r="N35" s="32" t="n">
+        <v>0.176</v>
+      </c>
       <c r="O35" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P35" s="13" t="inlineStr">
@@ -2702,9 +2722,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q35" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 171.85)</t>
         </is>
       </c>
     </row>
@@ -2714,31 +2734,31 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>100022270</t>
+          <t>10025441</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
+          <t>CREATINE 300G MAXTITANIUM</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>416.44</v>
+        <v>291.41</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>988.61</v>
+        <v>973.79</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>-572.17</v>
+        <v>-682.38</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>-0.579</v>
+        <v>-0.701</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>1962</v>
+        <v>3506</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>1.56</v>
+        <v>2.78</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -2746,18 +2766,18 @@
         </is>
       </c>
       <c r="K36" s="19" t="n">
-        <v>185.61</v>
+        <v>59.9</v>
       </c>
       <c r="L36" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M36" s="19" t="n">
-        <v>158.66</v>
+        <v>39.96</v>
       </c>
       <c r="N36" s="30" t="n">
-        <v>0.17</v>
+        <v>0.499</v>
       </c>
       <c r="O36" s="25" t="inlineStr">
         <is>
@@ -2771,7 +2791,7 @@
       </c>
       <c r="Q36" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
+          <t>Reprecificar no Digital (Amazon R$ 39.96)</t>
         </is>
       </c>
     </row>
@@ -2781,54 +2801,44 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>100022385</t>
+          <t>10033759</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>ENTRESTO 50MG 28CP REV NOVARTIS</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER M 66UN</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>343.58</v>
+        <v>169.8</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>913.89</v>
+        <v>850.45</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-570.3099999999999</v>
+        <v>-680.65</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.624</v>
+        <v>-0.8</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>6572</v>
+        <v>10622</v>
       </c>
       <c r="I37" s="28" t="n">
-        <v>5.22</v>
+        <v>8.44</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>202.11</v>
-      </c>
-      <c r="L37" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="n">
-        <v>171.85</v>
-      </c>
-      <c r="N37" s="31" t="n">
-        <v>0.176</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K37" s="12" t="inlineStr"/>
+      <c r="L37" s="13" t="inlineStr"/>
+      <c r="M37" s="12" t="inlineStr"/>
+      <c r="N37" s="14" t="inlineStr"/>
       <c r="O37" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P37" s="13" t="inlineStr">
@@ -2836,9 +2846,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 171.85)</t>
+      <c r="Q37" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2848,31 +2858,31 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>10049066</t>
+          <t>10052533</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 175ML HIDRATACAO+HIALURON VIT</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>168.82</v>
+        <v>2320.85</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>688.03</v>
+        <v>2998.41</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>-519.21</v>
+        <v>-677.5599999999999</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>-0.755</v>
+        <v>-0.226</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>18637</v>
+        <v>15647</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>14.8</v>
+        <v>12.43</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -2905,35 +2915,35 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>999705</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>ZOLADEX 3,6MG DEPOT INJ ASTRAZENECA</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1205.39</v>
+        <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1717.7</v>
+        <v>652.05</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-512.3099999999999</v>
+        <v>-652.05</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>-0.298</v>
+        <v>-1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>11106</v>
-      </c>
-      <c r="I39" s="28" t="n">
-        <v>8.82</v>
+        <v>37</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>0.03</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr"/>
@@ -2952,7 +2962,7 @@
       </c>
       <c r="Q39" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2962,54 +2972,44 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>10050639</t>
+          <t>100008756</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>EXTENSIOR 0,25MG+0,5MG 1,5ML NOVO EUROFARMA</t>
+          <t>LEITE NEOCATE LCP 400G DANONE</t>
         </is>
       </c>
       <c r="D40" s="19" t="n">
-        <v>0</v>
+        <v>281.99</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>504.69</v>
+        <v>887.37</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>-504.69</v>
+        <v>-605.38</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>-1</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>784</v>
+        <v>1484</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>0.62</v>
+        <v>1.18</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K40" s="19" t="n">
-        <v>955.85</v>
-      </c>
-      <c r="L40" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M40" s="19" t="n">
-        <v>955.85</v>
-      </c>
-      <c r="N40" s="33" t="n">
-        <v>0</v>
-      </c>
+      <c r="K40" s="24" t="inlineStr"/>
+      <c r="L40" s="25" t="inlineStr"/>
+      <c r="M40" s="24" t="inlineStr"/>
+      <c r="N40" s="26" t="inlineStr"/>
       <c r="O40" s="25" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P40" s="25" t="inlineStr">
@@ -3029,40 +3029,46 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>100011549</t>
+          <t>10093877</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>NAN SUPREME 2 800G NESTLE</t>
+          <t>MIRENA 52MG 1END+INS BAYER</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1011.52</v>
+        <v>1291.9</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1510.83</v>
+        <v>1871.1</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-499.31</v>
+        <v>-579.2</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-0.33</v>
+        <v>-0.31</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>7665</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>6.09</v>
+        <v>501</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>0.4</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr"/>
-      <c r="L41" s="13" t="inlineStr"/>
-      <c r="M41" s="12" t="inlineStr"/>
+      <c r="L41" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>1225.89</v>
+      </c>
       <c r="N41" s="14" t="inlineStr"/>
       <c r="O41" s="13" t="inlineStr">
         <is>
@@ -3076,7 +3082,7 @@
       </c>
       <c r="Q41" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3086,44 +3092,54 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>100008756</t>
+          <t>10050639</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>LEITE NEOCATE LCP 400G DANONE</t>
+          <t>EXTENSIOR 0,25MG+0,5MG 1,5ML NOVO EUROFARMA</t>
         </is>
       </c>
       <c r="D42" s="19" t="n">
-        <v>281.99</v>
+        <v>0</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>779.78</v>
+        <v>574.33</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>-497.79</v>
+        <v>-574.33</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>-0.638</v>
+        <v>-1</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>1484</v>
+        <v>784</v>
       </c>
       <c r="I42" s="23" t="n">
-        <v>1.18</v>
+        <v>0.62</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K42" s="24" t="inlineStr"/>
-      <c r="L42" s="25" t="inlineStr"/>
-      <c r="M42" s="24" t="inlineStr"/>
-      <c r="N42" s="26" t="inlineStr"/>
+      <c r="K42" s="19" t="n">
+        <v>955.85</v>
+      </c>
+      <c r="L42" s="25" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M42" s="19" t="n">
+        <v>955.85</v>
+      </c>
+      <c r="N42" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="O42" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P42" s="25" t="inlineStr">
@@ -3143,54 +3159,44 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>100018652</t>
+          <t>10046010</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>OLEO BIO OIL 200ML PURCELLIN</t>
+          <t>FR PAMPERS SUPERSEC MEGA M 40UN</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0</v>
+        <v>540.66</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>485.44</v>
+        <v>1114.41</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-485.44</v>
+        <v>-573.75</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-1</v>
+        <v>-0.515</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>2638</v>
+        <v>6394</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>2.1</v>
+        <v>5.08</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>134.99</v>
-      </c>
-      <c r="L43" s="13" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="n">
-        <v>67.19</v>
-      </c>
-      <c r="N43" s="31" t="n">
-        <v>1.009</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K43" s="12" t="inlineStr"/>
+      <c r="L43" s="13" t="inlineStr"/>
+      <c r="M43" s="12" t="inlineStr"/>
+      <c r="N43" s="14" t="inlineStr"/>
       <c r="O43" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P43" s="13" t="inlineStr">
@@ -3198,9 +3204,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 67.19)</t>
+      <c r="Q43" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3210,31 +3216,31 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>10046010</t>
+          <t>10044745</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS SUPERSEC MEGA M 40UN</t>
+          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
         </is>
       </c>
       <c r="D44" s="19" t="n">
-        <v>494.76</v>
+        <v>783.11</v>
       </c>
       <c r="E44" s="19" t="n">
-        <v>979.28</v>
+        <v>1342.13</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>-484.52</v>
+        <v>-559.02</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>-0.495</v>
+        <v>-0.417</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>6394</v>
+        <v>5858</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>5.08</v>
+        <v>4.65</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -3242,8 +3248,14 @@
         </is>
       </c>
       <c r="K44" s="24" t="inlineStr"/>
-      <c r="L44" s="25" t="inlineStr"/>
-      <c r="M44" s="24" t="inlineStr"/>
+      <c r="L44" s="25" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>83.92</v>
+      </c>
       <c r="N44" s="26" t="inlineStr"/>
       <c r="O44" s="25" t="inlineStr">
         <is>
@@ -3267,50 +3279,54 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>10035972</t>
+          <t>100018652</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>CONDRES LONGBIO 90CAP EMS</t>
+          <t>OLEO BIO OIL 200ML PURCELLIN</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>473.52</v>
+        <v>552.4299999999999</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-473.52</v>
+        <v>-552.4299999999999</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>1136</v>
-      </c>
-      <c r="I45" s="11" t="n">
-        <v>0.9</v>
+        <v>2638</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>2.1</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>134.99</v>
+      </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
-        <v>352.33</v>
-      </c>
-      <c r="N45" s="14" t="inlineStr"/>
+        <v>67.19</v>
+      </c>
+      <c r="N45" s="32" t="n">
+        <v>1.009</v>
+      </c>
       <c r="O45" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P45" s="13" t="inlineStr">
@@ -3318,9 +3334,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q45" s="15" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 67.19)</t>
         </is>
       </c>
     </row>
@@ -3330,54 +3346,50 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>100001425</t>
+          <t>10035972</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
+          <t>CONDRES LONGBIO 90CAP EMS</t>
         </is>
       </c>
       <c r="D46" s="19" t="n">
-        <v>335.39</v>
+        <v>0</v>
       </c>
       <c r="E46" s="19" t="n">
-        <v>806.36</v>
+        <v>538.85</v>
       </c>
       <c r="F46" s="20" t="n">
-        <v>-470.97</v>
+        <v>-538.85</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>-0.584</v>
+        <v>-1</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>13421</v>
-      </c>
-      <c r="I46" s="29" t="n">
-        <v>10.66</v>
+        <v>1136</v>
+      </c>
+      <c r="I46" s="23" t="n">
+        <v>0.9</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K46" s="19" t="n">
-        <v>29.9</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="inlineStr"/>
       <c r="L46" s="25" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M46" s="19" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="N46" s="30" t="n">
-        <v>0.035</v>
-      </c>
+        <v>352.33</v>
+      </c>
+      <c r="N46" s="26" t="inlineStr"/>
       <c r="O46" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P46" s="25" t="inlineStr">
@@ -3387,7 +3399,7 @@
       </c>
       <c r="Q46" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3397,54 +3409,44 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10032625</t>
+          <t>10044679</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>EXTRATO DE CANNABIS SATIVA 79,14MG 30ML MANTECORP (B1)</t>
+          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0</v>
+        <v>285.04</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>461.62</v>
+        <v>820.59</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-461.62</v>
+        <v>-535.55</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-1</v>
+        <v>-0.653</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>112</v>
+        <v>324</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K47" s="7" t="n">
-        <v>961.2</v>
-      </c>
-      <c r="L47" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="n">
-        <v>925.9</v>
-      </c>
-      <c r="N47" s="31" t="n">
-        <v>0.038</v>
-      </c>
+      <c r="K47" s="12" t="inlineStr"/>
+      <c r="L47" s="13" t="inlineStr"/>
+      <c r="M47" s="12" t="inlineStr"/>
+      <c r="N47" s="14" t="inlineStr"/>
       <c r="O47" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P47" s="13" t="inlineStr">
@@ -3464,54 +3466,50 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>10028272</t>
+          <t>10089756</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>MTOR 1G 90CP EUROFARMA</t>
+          <t>RITALINA 10MG 60CP NOVARTIS (A3)</t>
         </is>
       </c>
       <c r="D48" s="19" t="n">
-        <v>0</v>
+        <v>81.95</v>
       </c>
       <c r="E48" s="19" t="n">
-        <v>457.64</v>
+        <v>607.67</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>-457.64</v>
+        <v>-525.72</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>-1</v>
+        <v>-0.865</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>1017</v>
-      </c>
-      <c r="I48" s="23" t="n">
-        <v>0.8100000000000001</v>
+        <v>7860</v>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>6.24</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K48" s="19" t="n">
-        <v>366.7</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="inlineStr"/>
       <c r="L48" s="25" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M48" s="19" t="n">
-        <v>359.99</v>
-      </c>
-      <c r="N48" s="30" t="n">
-        <v>0.019</v>
-      </c>
+        <v>92.95</v>
+      </c>
+      <c r="N48" s="26" t="inlineStr"/>
       <c r="O48" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P48" s="25" t="inlineStr">
@@ -3521,7 +3519,7 @@
       </c>
       <c r="Q48" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3531,50 +3529,54 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10089756</t>
+          <t>10032625</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>RITALINA 10MG 60CP NOVARTIS (A3)</t>
+          <t>EXTRATO DE CANNABIS SATIVA 79,14MG 30ML MANTECORP (B1)</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>81.95</v>
+        <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>533.99</v>
+        <v>525.3200000000001</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-452.04</v>
+        <v>-525.3200000000001</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-0.847</v>
+        <v>-1</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7860</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>6.24</v>
+        <v>112</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>0.09</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>961.2</v>
+      </c>
       <c r="L49" s="13" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>92.95</v>
-      </c>
-      <c r="N49" s="14" t="inlineStr"/>
+        <v>925.9</v>
+      </c>
+      <c r="N49" s="32" t="n">
+        <v>0.038</v>
+      </c>
       <c r="O49" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P49" s="13" t="inlineStr">
@@ -3584,7 +3586,7 @@
       </c>
       <c r="Q49" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3594,44 +3596,54 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>10044679</t>
+          <t>10028272</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
+          <t>MTOR 1G 90CP EUROFARMA</t>
         </is>
       </c>
       <c r="D50" s="19" t="n">
-        <v>285.04</v>
+        <v>0</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>721.09</v>
+        <v>520.78</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>-436.05</v>
+        <v>-520.78</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>-0.605</v>
+        <v>-1</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>324</v>
+        <v>1017</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>0.26</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K50" s="24" t="inlineStr"/>
-      <c r="L50" s="25" t="inlineStr"/>
-      <c r="M50" s="24" t="inlineStr"/>
-      <c r="N50" s="26" t="inlineStr"/>
+      <c r="K50" s="19" t="n">
+        <v>366.7</v>
+      </c>
+      <c r="L50" s="25" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M50" s="19" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="N50" s="30" t="n">
+        <v>0.019</v>
+      </c>
       <c r="O50" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P50" s="25" t="inlineStr">
@@ -3651,31 +3663,31 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10052535</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>2204.95</v>
+        <v>1437.19</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>2634.84</v>
+        <v>1954.72</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-429.89</v>
+        <v>-517.53</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.163</v>
+        <v>-0.265</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>15647</v>
+        <v>11106</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>12.43</v>
+        <v>8.82</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -3708,44 +3720,54 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>10037279</t>
+          <t>10100048</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>FR CAPRICHO BABY MEGA XXG 54UN</t>
+          <t>RITALINA LA 10MG 30CP NOVARTIS (A3)</t>
         </is>
       </c>
       <c r="D52" s="19" t="n">
-        <v>111.48</v>
+        <v>454.25</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>536.29</v>
+        <v>958.04</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>-424.81</v>
+        <v>-503.79</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>-0.792</v>
+        <v>-0.526</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>5320</v>
+        <v>3843</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>4.23</v>
+        <v>3.05</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K52" s="24" t="inlineStr"/>
-      <c r="L52" s="25" t="inlineStr"/>
-      <c r="M52" s="24" t="inlineStr"/>
-      <c r="N52" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K52" s="19" t="n">
+        <v>137.55</v>
+      </c>
+      <c r="L52" s="25" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M52" s="19" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="N52" s="30" t="n">
+        <v>0.138</v>
+      </c>
       <c r="O52" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P52" s="25" t="inlineStr">
@@ -3753,9 +3775,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q52" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q52" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 120.90)</t>
         </is>
       </c>
     </row>
@@ -3765,54 +3787,54 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>100001759</t>
+          <t>10046754</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>GESTINOL 0,075+0,03MG 84CP LIBBS</t>
+          <t>GINOBIOTTA 30CAP MARJAN</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>112.82</v>
+        <v>175.9</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>537.11</v>
+        <v>675.09</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-424.29</v>
+        <v>-499.19</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>-0.79</v>
+        <v>-0.7390000000000001</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>3208</v>
+        <v>2137</v>
       </c>
       <c r="I53" s="28" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K53" s="7" t="n">
-        <v>127.85</v>
+        <v>193.6</v>
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M53" s="7" t="n">
-        <v>127.77</v>
-      </c>
-      <c r="N53" s="31" t="n">
-        <v>0.001</v>
+        <v>165.59</v>
+      </c>
+      <c r="N53" s="32" t="n">
+        <v>0.169</v>
       </c>
       <c r="O53" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P53" s="13" t="inlineStr">
@@ -3820,9 +3842,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q53" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 165.59)</t>
         </is>
       </c>
     </row>
@@ -3832,31 +3854,31 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>10052031</t>
+          <t>10037279</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>FIGURINHAS COPA DO MUNDO 2026 7UN</t>
+          <t>FR CAPRICHO BABY MEGA XXG 54UN</t>
         </is>
       </c>
       <c r="D54" s="19" t="n">
-        <v>7</v>
+        <v>111.48</v>
       </c>
       <c r="E54" s="19" t="n">
-        <v>427.37</v>
+        <v>610.29</v>
       </c>
       <c r="F54" s="20" t="n">
-        <v>-420.37</v>
+        <v>-498.81</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>-0.9840000000000001</v>
+        <v>-0.8170000000000001</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>24208</v>
+        <v>5320</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>19.23</v>
+        <v>4.23</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -294,16 +294,16 @@
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 18:54:20 (18:54) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 19:53:25 (19:53) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>9927.690000000001</v>
+        <v>11248.11</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-9927.690000000001</v>
+        <v>-11248.11</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>-1</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>6618.46</v>
+        <v>7498.74</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>-6618.46</v>
+        <v>-7498.74</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>-1</v>
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>504.2</v>
+        <v>758.9</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3233.85</v>
+        <v>3663.96</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-2729.65</v>
+        <v>-2905.06</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.8440000000000001</v>
+        <v>-0.7929999999999999</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>26223</v>
@@ -980,31 +980,31 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10041263</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>369.95</v>
+        <v>509.9</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>2858.57</v>
+        <v>3258.48</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>-2488.62</v>
+        <v>-2748.58</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>-0.871</v>
+        <v>-0.8440000000000001</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>39477</v>
+        <v>3146</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>31.36</v>
+        <v>2.5</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10041263</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX G 88U</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>509.9</v>
+        <v>581.92</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2875.97</v>
+        <v>3238.77</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-2366.07</v>
+        <v>-2656.85</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.823</v>
+        <v>-0.82</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>3146</v>
+        <v>39477</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>2.5</v>
+        <v>31.36</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1106,13 +1106,13 @@
         <v>249.17</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>2444.57</v>
+        <v>2769.71</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-2195.4</v>
+        <v>-2520.54</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>-0.898</v>
+        <v>-0.91</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>4427</v>
@@ -1157,45 +1157,45 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10025098</t>
+          <t>10034724</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
+          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0</v>
+        <v>2019.56</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1873.19</v>
+        <v>4214.98</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-1873.19</v>
+        <v>-2195.42</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-1</v>
+        <v>-0.521</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>204</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>0.16</v>
+        <v>2081</v>
+      </c>
+      <c r="I11" s="28" t="n">
+        <v>1.65</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr"/>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
-        <v>1212.9</v>
+        <v>549.9</v>
       </c>
       <c r="N11" s="14" t="inlineStr"/>
       <c r="O11" s="13" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Q11" s="15" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1220,54 +1220,50 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>10037731</t>
+          <t>10025098</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
+          <t>AJOVY 225MG 1,5ML SER PREENC TEVA</t>
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>2595.32</v>
+        <v>0</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>4457.75</v>
+        <v>2122.33</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>-1862.43</v>
+        <v>-2122.33</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.418</v>
+        <v>-1</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>2446</v>
-      </c>
-      <c r="I12" s="29" t="n">
-        <v>1.94</v>
+        <v>204</v>
+      </c>
+      <c r="I12" s="23" t="n">
+        <v>0.16</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>99.90000000000001</v>
-      </c>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K12" s="24" t="inlineStr"/>
       <c r="L12" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PANVEL</t>
         </is>
       </c>
       <c r="M12" s="19" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="N12" s="30" t="n">
-        <v>1.132</v>
-      </c>
+        <v>1212.9</v>
+      </c>
+      <c r="N12" s="26" t="inlineStr"/>
       <c r="O12" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P12" s="25" t="inlineStr">
@@ -1275,9 +1271,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q12" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
+      <c r="Q12" s="27" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1287,50 +1283,54 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10034724</t>
+          <t>10050648</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>CONTRAVE 8+90MG 120CP REV LIB PROL MERCK (C1)</t>
+          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2019.56</v>
+        <v>7947</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3720.19</v>
+        <v>10055.94</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-1700.63</v>
+        <v>-2108.94</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.457</v>
+        <v>-0.21</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>2081</v>
+        <v>9409</v>
       </c>
       <c r="I13" s="28" t="n">
-        <v>1.65</v>
+        <v>7.47</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr"/>
+      <c r="K13" s="7" t="n">
+        <v>988.22</v>
+      </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
-        <v>549.9</v>
-      </c>
-      <c r="N13" s="14" t="inlineStr"/>
+        <v>988.22</v>
+      </c>
+      <c r="N13" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr">
@@ -1350,54 +1350,54 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>10025745</t>
+          <t>10049094</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
+          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0</v>
+        <v>1223.25</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>1591.42</v>
+        <v>3170.25</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>-1591.42</v>
+        <v>-1947</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>-1</v>
+        <v>-0.614</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>122</v>
-      </c>
-      <c r="I14" s="23" t="n">
-        <v>0.1</v>
+        <v>2931</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>2.33</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K14" s="19" t="n">
-        <v>1105.6</v>
+        <v>218.67</v>
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>DROGARAIA</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M14" s="19" t="n">
-        <v>1170.01</v>
+        <v>197.18</v>
       </c>
       <c r="N14" s="31" t="n">
-        <v>-0.055</v>
+        <v>0.109</v>
       </c>
       <c r="O14" s="25" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P14" s="25" t="inlineStr">
@@ -1405,9 +1405,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q14" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q14" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
         </is>
       </c>
     </row>
@@ -1417,31 +1417,31 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>10049094</t>
+          <t>10037731</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>NUSTENDI 180MG/10MG 30CP DAIICHI</t>
+          <t>CREATINA HARDCORE 300G INTEGRALMEDICA</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1223.25</v>
+        <v>3194.72</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2798.09</v>
+        <v>5050.64</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-1574.84</v>
+        <v>-1855.92</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.367</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>2931</v>
+        <v>2446</v>
       </c>
       <c r="I15" s="28" t="n">
-        <v>2.33</v>
+        <v>1.94</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1449,18 +1449,18 @@
         </is>
       </c>
       <c r="K15" s="7" t="n">
-        <v>218.67</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
-        <v>197.18</v>
+        <v>46.85</v>
       </c>
       <c r="N15" s="32" t="n">
-        <v>0.109</v>
+        <v>1.132</v>
       </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 197.18)</t>
+          <t>Reprecificar no Digital (Amazon R$ 46.85)</t>
         </is>
       </c>
     </row>
@@ -1484,44 +1484,54 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>10041261</t>
+          <t>10025745</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
+          <t>DENSIS 5MG SOL INJ 100ML C/BOLSA MOMENTA</t>
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>1050.46</v>
+        <v>0</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>2562.93</v>
+        <v>1803.09</v>
       </c>
       <c r="F16" s="20" t="n">
-        <v>-1512.47</v>
+        <v>-1803.09</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>-0.59</v>
+        <v>-1</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>1270</v>
+        <v>122</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>1.01</v>
+        <v>0.1</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K16" s="24" t="inlineStr"/>
-      <c r="L16" s="25" t="inlineStr"/>
-      <c r="M16" s="24" t="inlineStr"/>
-      <c r="N16" s="26" t="inlineStr"/>
+      <c r="K16" s="19" t="n">
+        <v>1105.6</v>
+      </c>
+      <c r="L16" s="25" t="inlineStr">
+        <is>
+          <t>DROGARAIA</t>
+        </is>
+      </c>
+      <c r="M16" s="19" t="n">
+        <v>1170.01</v>
+      </c>
+      <c r="N16" s="33" t="n">
+        <v>-0.055</v>
+      </c>
       <c r="O16" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P16" s="25" t="inlineStr">
@@ -1541,54 +1551,44 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>100020215</t>
+          <t>10006600</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
+          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>90.02</v>
+        <v>192.3</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1491.39</v>
+        <v>1754.51</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-1401.37</v>
+        <v>-1562.21</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.89</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>22233</v>
+        <v>11806</v>
       </c>
       <c r="I17" s="28" t="n">
-        <v>17.66</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N17" s="32" t="n">
-        <v>0.629</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="13" t="inlineStr"/>
+      <c r="M17" s="12" t="inlineStr"/>
+      <c r="N17" s="14" t="inlineStr"/>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P17" s="13" t="inlineStr">
@@ -1596,9 +1596,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
+      <c r="Q17" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1608,44 +1608,54 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>10006600</t>
+          <t>100020215</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>LEITE NINHO 800G 1+PREBIO 20% DESC 2ªUN</t>
+          <t>DES DOVE AERO 150ML REGULAR ORIGINAL</t>
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>192.3</v>
+        <v>138.94</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>1548.54</v>
+        <v>1689.74</v>
       </c>
       <c r="F18" s="20" t="n">
-        <v>-1356.24</v>
+        <v>-1550.8</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>-0.8759999999999999</v>
+        <v>-0.9179999999999999</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>11806</v>
+        <v>22233</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>9.380000000000001</v>
+        <v>17.66</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K18" s="24" t="inlineStr"/>
-      <c r="L18" s="25" t="inlineStr"/>
-      <c r="M18" s="24" t="inlineStr"/>
-      <c r="N18" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L18" s="25" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M18" s="19" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N18" s="31" t="n">
+        <v>0.629</v>
+      </c>
       <c r="O18" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P18" s="25" t="inlineStr">
@@ -1653,9 +1663,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q18" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q18" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 15.90)</t>
         </is>
       </c>
     </row>
@@ -1665,35 +1675,35 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>10028706</t>
+          <t>10041261</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>FR SAO JOAO BABY BAG XG 58UN</t>
+          <t>FR HUGGIES ROUPINHA ACOLCHOADA MAX XXG 7</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0</v>
+        <v>1368.16</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1321.52</v>
+        <v>2903.81</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-1321.52</v>
+        <v>-1535.65</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-1</v>
+        <v>-0.529</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>30285</v>
-      </c>
-      <c r="I19" s="28" t="n">
-        <v>24.05</v>
+        <v>1270</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>1.01</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr"/>
@@ -1712,7 +1722,7 @@
       </c>
       <c r="Q19" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -1722,54 +1732,44 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>10097312</t>
+          <t>10028706</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>NESTOGENO 2 800G NESTLE</t>
+          <t>FR SAO JOAO BABY BAG XG 58UN</t>
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>1033.31</v>
+        <v>0</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>2288.52</v>
+        <v>1497.29</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>-1255.21</v>
+        <v>-1497.29</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>-0.5479999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>12853</v>
+        <v>30285</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>10.21</v>
+        <v>24.05</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="L20" s="25" t="inlineStr">
-        <is>
-          <t>DROGARAIA</t>
-        </is>
-      </c>
-      <c r="M20" s="19" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="N20" s="30" t="n">
-        <v>0.113</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K20" s="24" t="inlineStr"/>
+      <c r="L20" s="25" t="inlineStr"/>
+      <c r="M20" s="24" t="inlineStr"/>
+      <c r="N20" s="26" t="inlineStr"/>
       <c r="O20" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P20" s="25" t="inlineStr">
@@ -1777,9 +1777,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q20" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
+      <c r="Q20" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -1789,44 +1789,54 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10052534</t>
+          <t>10026927</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
+          <t>NANLAC SUPREME 800G NESTLE</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3483.24</v>
+        <v>1953.29</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>4737.52</v>
+        <v>3340.37</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-1254.28</v>
+        <v>-1387.08</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>-0.265</v>
+        <v>-0.415</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>8275</v>
+        <v>8909</v>
       </c>
       <c r="I21" s="28" t="n">
-        <v>6.57</v>
+        <v>7.08</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="inlineStr"/>
-      <c r="L21" s="13" t="inlineStr"/>
-      <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="14" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>108.49</v>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="N21" s="32" t="n">
+        <v>0.111</v>
+      </c>
       <c r="O21" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P21" s="13" t="inlineStr">
@@ -1834,9 +1844,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q21" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
         </is>
       </c>
     </row>
@@ -1846,31 +1856,31 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>999697</t>
+          <t>10097312</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
+          <t>NESTOGENO 2 800G NESTLE</t>
         </is>
       </c>
       <c r="D22" s="19" t="n">
-        <v>1271.42</v>
+        <v>1229.88</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>2516.48</v>
+        <v>2592.9</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>-1245.06</v>
+        <v>-1363.02</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>-0.495</v>
+        <v>-0.526</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>3992</v>
+        <v>12853</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>3.17</v>
+        <v>10.21</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1878,18 +1888,18 @@
         </is>
       </c>
       <c r="K22" s="19" t="n">
-        <v>149.4</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="L22" s="25" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>DROGARAIA</t>
         </is>
       </c>
       <c r="M22" s="19" t="n">
-        <v>107</v>
-      </c>
-      <c r="N22" s="30" t="n">
-        <v>0.396</v>
+        <v>61.06</v>
+      </c>
+      <c r="N22" s="31" t="n">
+        <v>0.113</v>
       </c>
       <c r="O22" s="25" t="inlineStr">
         <is>
@@ -1903,7 +1913,7 @@
       </c>
       <c r="Q22" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
+          <t>Reprecificar no Digital (Drogaraia R$ 61.06)</t>
         </is>
       </c>
     </row>
@@ -1913,39 +1923,39 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10050648</t>
+          <t>999697</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>POVIZTRA 1MG 3ML EUROFARMA</t>
+          <t>EVRA 0,6+6MG 3ADES GEDEON RICHTER</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>7638</v>
+        <v>1511.4</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>8875.48</v>
+        <v>2851.18</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-1237.48</v>
+        <v>-1339.78</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.139</v>
+        <v>-0.47</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>9409</v>
+        <v>3992</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>7.47</v>
+        <v>3.17</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K23" s="7" t="n">
-        <v>988.22</v>
+        <v>149.4</v>
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
@@ -1953,14 +1963,14 @@
         </is>
       </c>
       <c r="M23" s="7" t="n">
-        <v>988.22</v>
-      </c>
-      <c r="N23" s="33" t="n">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="N23" s="32" t="n">
+        <v>0.396</v>
       </c>
       <c r="O23" s="13" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P23" s="13" t="inlineStr">
@@ -1968,9 +1978,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q23" s="15" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Precopopular R$ 107.00)</t>
         </is>
       </c>
     </row>
@@ -1980,54 +1990,44 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>10026927</t>
+          <t>10099241</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>NANLAC SUPREME 800G NESTLE</t>
+          <t>NAN COMFOR 1 800G NESTLE</t>
         </is>
       </c>
       <c r="D24" s="19" t="n">
-        <v>1775.71</v>
+        <v>1098.67</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>2948.25</v>
+        <v>2326.41</v>
       </c>
       <c r="F24" s="20" t="n">
-        <v>-1172.54</v>
+        <v>-1227.74</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>-0.398</v>
+        <v>-0.528</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>8909</v>
+        <v>13024</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>7.08</v>
+        <v>10.34</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K24" s="19" t="n">
-        <v>108.49</v>
-      </c>
-      <c r="L24" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M24" s="19" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="N24" s="30" t="n">
-        <v>0.111</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K24" s="24" t="inlineStr"/>
+      <c r="L24" s="25" t="inlineStr"/>
+      <c r="M24" s="24" t="inlineStr"/>
+      <c r="N24" s="26" t="inlineStr"/>
       <c r="O24" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P24" s="25" t="inlineStr">
@@ -2035,9 +2035,9 @@
           <t>Detrator Moderado</t>
         </is>
       </c>
-      <c r="Q24" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Precopopular R$ 97.69)</t>
+      <c r="Q24" s="27" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -2047,31 +2047,31 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10040659</t>
+          <t>10052534</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
+          <t>FR PAMPERS CONFORTSEC BAG MAX XG 86UN</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>575.72</v>
+        <v>4161.29</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>1632.4</v>
+        <v>5367.62</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-1056.68</v>
+        <v>-1206.33</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-0.647</v>
+        <v>-0.225</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>9864</v>
+        <v>8275</v>
       </c>
       <c r="I25" s="28" t="n">
-        <v>7.83</v>
+        <v>6.57</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -2104,31 +2104,31 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>10099241</t>
+          <t>10040659</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>NAN COMFOR 1 800G NESTLE</t>
+          <t>KIT DOVE SH 350+COND 150ML BOND INTENSE REPAIR</t>
         </is>
       </c>
       <c r="D26" s="19" t="n">
-        <v>1010.77</v>
+        <v>665.42</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>2053.31</v>
+        <v>1849.51</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>-1042.54</v>
+        <v>-1184.09</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>-0.508</v>
+        <v>-0.64</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>13024</v>
+        <v>9864</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>10.34</v>
+        <v>7.83</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -2161,64 +2161,64 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>10050440</t>
+          <t>10024521</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>AMMY 4MG 72CP REV MANTECORP</t>
+          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1672.1</v>
+        <v>799.9</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>2641.04</v>
+        <v>1956.8</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-968.9400000000001</v>
+        <v>-1156.9</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.367</v>
+        <v>-0.591</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>837</v>
+        <v>575</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>⚠️ Duplo Detrator</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K27" s="7" t="n">
-        <v>315.46</v>
+        <v>799.9</v>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M27" s="7" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="N27" s="32" t="n">
-        <v>0.333</v>
+        <v>814.9</v>
+      </c>
+      <c r="N27" s="30" t="n">
+        <v>-0.018</v>
       </c>
       <c r="O27" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Líder de Preço</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q27" s="15" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2228,64 +2228,64 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>10024521</t>
+          <t>10050440</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>XIFAXAN 550MG 28CP REV BIOLAB</t>
+          <t>AMMY 4MG 72CP REV MANTECORP</t>
         </is>
       </c>
       <c r="D28" s="19" t="n">
-        <v>799.9</v>
+        <v>1903.19</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>1727.09</v>
+        <v>2992.31</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>-927.1900000000001</v>
+        <v>-1089.12</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>-0.537</v>
+        <v>-0.364</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>575</v>
+        <v>837</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>0.46</v>
+        <v>0.66</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>⚠️ Duplo Detrator</t>
         </is>
       </c>
       <c r="K28" s="19" t="n">
-        <v>799.9</v>
+        <v>315.46</v>
       </c>
       <c r="L28" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M28" s="19" t="n">
-        <v>814.9</v>
+        <v>236.6</v>
       </c>
       <c r="N28" s="31" t="n">
-        <v>-0.018</v>
+        <v>0.333</v>
       </c>
       <c r="O28" s="25" t="inlineStr">
         <is>
-          <t>Líder de Preço</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P28" s="25" t="inlineStr">
         <is>
-          <t>Neutro</t>
-        </is>
-      </c>
-      <c r="Q28" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Detrator Moderado</t>
+        </is>
+      </c>
+      <c r="Q28" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar e Remanejar (Precopopular R$ 236.60)</t>
         </is>
       </c>
     </row>
@@ -2295,31 +2295,31 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>10041082</t>
+          <t>10001098</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
+          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0</v>
+        <v>1471.43</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>806.51</v>
+        <v>2402.31</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-806.51</v>
+        <v>-930.88</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-1</v>
+        <v>-0.387</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>5609</v>
+        <v>8492</v>
       </c>
       <c r="I29" s="28" t="n">
-        <v>4.46</v>
+        <v>6.75</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2352,31 +2352,31 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>10001098</t>
+          <t>10041082</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>TOALHAS UMED HUGGIES 192UN HIDRATACAO</t>
+          <t>FR HUGGIES MAXIMA PROT HIPER XXXG 46UN</t>
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>1318.92</v>
+        <v>0</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>2120.3</v>
+        <v>913.78</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>-801.38</v>
+        <v>-913.78</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>-0.3779999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>8492</v>
+        <v>5609</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>6.75</v>
+        <v>4.46</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -2418,16 +2418,16 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1016.05</v>
+        <v>1121.57</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>1773.64</v>
+        <v>2009.54</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-757.59</v>
+        <v>-887.97</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>-0.427</v>
+        <v>-0.442</v>
       </c>
       <c r="H31" s="10" t="n">
         <v>2601</v>
@@ -2466,50 +2466,50 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>10038798</t>
+          <t>100022270</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
+          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
         </is>
       </c>
       <c r="D32" s="19" t="n">
-        <v>0</v>
+        <v>416.44</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>724.5700000000001</v>
+        <v>1274.66</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>-724.5700000000001</v>
+        <v>-858.22</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>-1</v>
+        <v>-0.6729999999999999</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>1623</v>
-      </c>
-      <c r="I32" s="23" t="n">
-        <v>1.29</v>
+        <v>1962</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>1.56</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>🏷️ Preço Desalinhado</t>
         </is>
       </c>
       <c r="K32" s="19" t="n">
-        <v>180.79</v>
+        <v>185.61</v>
       </c>
       <c r="L32" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M32" s="19" t="n">
-        <v>175.9</v>
-      </c>
-      <c r="N32" s="30" t="n">
-        <v>0.028</v>
+        <v>158.66</v>
+      </c>
+      <c r="N32" s="31" t="n">
+        <v>0.17</v>
       </c>
       <c r="O32" s="25" t="inlineStr">
         <is>
@@ -2521,9 +2521,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q32" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q32" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
         </is>
       </c>
     </row>
@@ -2533,31 +2533,31 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>100022270</t>
+          <t>100022385</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>ELIFORE 50MG 28CP REV LIB CONT PFIZER (C1)</t>
+          <t>ENTRESTO 50MG 28CP REV NOVARTIS</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>416.44</v>
+        <v>343.58</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1125.02</v>
+        <v>1178.32</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-708.58</v>
+        <v>-834.74</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-0.63</v>
+        <v>-0.708</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>1962</v>
+        <v>6572</v>
       </c>
       <c r="I33" s="28" t="n">
-        <v>1.56</v>
+        <v>5.22</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="K33" s="7" t="n">
-        <v>185.61</v>
+        <v>202.11</v>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="M33" s="7" t="n">
-        <v>158.66</v>
+        <v>171.85</v>
       </c>
       <c r="N33" s="32" t="n">
-        <v>0.17</v>
+        <v>0.176</v>
       </c>
       <c r="O33" s="13" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 158.66)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 171.85)</t>
         </is>
       </c>
     </row>
@@ -2600,54 +2600,50 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>10040748</t>
+          <t>10093877</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
+          <t>MIRENA 52MG 1END+INS BAYER</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>0</v>
+        <v>1291.9</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>701.72</v>
+        <v>2119.97</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>-701.72</v>
+        <v>-828.0700000000001</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>-1</v>
+        <v>-0.391</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>402</v>
+        <v>501</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
           <t>🚨 Ruptura Logística</t>
         </is>
       </c>
-      <c r="K34" s="19" t="n">
-        <v>1298.54</v>
-      </c>
+      <c r="K34" s="24" t="inlineStr"/>
       <c r="L34" s="25" t="inlineStr">
         <is>
-          <t>PREÇO POPULAR</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M34" s="19" t="n">
-        <v>1298.54</v>
-      </c>
-      <c r="N34" s="31" t="n">
-        <v>0</v>
-      </c>
+        <v>1225.89</v>
+      </c>
+      <c r="N34" s="26" t="inlineStr"/>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P34" s="25" t="inlineStr">
@@ -2667,50 +2663,50 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>100022385</t>
+          <t>10038798</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>ENTRESTO 50MG 28CP REV NOVARTIS</t>
+          <t>GENOVA CABELOS E UNHAS 60CP EUROFARMA</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>343.58</v>
+        <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1040</v>
+        <v>820.9400000000001</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-696.42</v>
+        <v>-820.9400000000001</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-0.67</v>
+        <v>-1</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>6572</v>
-      </c>
-      <c r="I35" s="28" t="n">
-        <v>5.22</v>
+        <v>1623</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>1.29</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K35" s="7" t="n">
-        <v>202.11</v>
+        <v>180.79</v>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M35" s="7" t="n">
-        <v>171.85</v>
+        <v>175.9</v>
       </c>
       <c r="N35" s="32" t="n">
-        <v>0.176</v>
+        <v>0.028</v>
       </c>
       <c r="O35" s="13" t="inlineStr">
         <is>
@@ -2722,9 +2718,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 171.85)</t>
+      <c r="Q35" s="15" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2734,54 +2730,54 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>10025441</t>
+          <t>10040748</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>CREATINE 300G MAXTITANIUM</t>
+          <t>WEGOVY 0,5MG 1,5ML NOVO NORDISK</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>291.41</v>
+        <v>0</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>973.79</v>
+        <v>795.05</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>-682.38</v>
+        <v>-795.05</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>-0.701</v>
+        <v>-1</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>3506</v>
-      </c>
-      <c r="I36" s="29" t="n">
-        <v>2.78</v>
+        <v>402</v>
+      </c>
+      <c r="I36" s="23" t="n">
+        <v>0.32</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K36" s="19" t="n">
-        <v>59.9</v>
+        <v>1298.54</v>
       </c>
       <c r="L36" s="25" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M36" s="19" t="n">
-        <v>39.96</v>
-      </c>
-      <c r="N36" s="30" t="n">
-        <v>0.499</v>
+        <v>1298.54</v>
+      </c>
+      <c r="N36" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="O36" s="25" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P36" s="25" t="inlineStr">
@@ -2789,9 +2785,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q36" s="18" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 39.96)</t>
+      <c r="Q36" s="27" t="inlineStr">
+        <is>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -2813,13 +2809,13 @@
         <v>169.8</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>850.45</v>
+        <v>963.5700000000001</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-680.65</v>
+        <v>-793.77</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-0.8</v>
+        <v>-0.8240000000000001</v>
       </c>
       <c r="H37" s="10" t="n">
         <v>10622</v>
@@ -2858,44 +2854,54 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>10052533</t>
+          <t>10025441</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX XXG 82UN</t>
+          <t>CREATINE 300G MAXTITANIUM</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>2320.85</v>
+        <v>351.31</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>2998.41</v>
+        <v>1103.31</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>-677.5599999999999</v>
+        <v>-752</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>-0.226</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>15647</v>
+        <v>3506</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>12.43</v>
+        <v>2.78</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K38" s="24" t="inlineStr"/>
-      <c r="L38" s="25" t="inlineStr"/>
-      <c r="M38" s="24" t="inlineStr"/>
-      <c r="N38" s="26" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L38" s="25" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="M38" s="19" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="N38" s="31" t="n">
+        <v>0.499</v>
+      </c>
       <c r="O38" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P38" s="25" t="inlineStr">
@@ -2903,9 +2909,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q38" s="27" t="inlineStr">
-        <is>
-          <t>Ação Promocional / Destaque Home</t>
+      <c r="Q38" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 39.96)</t>
         </is>
       </c>
     </row>
@@ -2927,10 +2933,10 @@
         <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>652.05</v>
+        <v>738.78</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-652.05</v>
+        <v>-738.78</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>-1</v>
@@ -2984,13 +2990,13 @@
         <v>281.99</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>887.37</v>
+        <v>1005.4</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>-605.38</v>
+        <v>-723.41</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.72</v>
       </c>
       <c r="H40" s="22" t="n">
         <v>1484</v>
@@ -3029,46 +3035,40 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>10093877</t>
+          <t>10046010</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>MIRENA 52MG 1END+INS BAYER</t>
+          <t>FR PAMPERS SUPERSEC MEGA M 40UN</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1291.9</v>
+        <v>586.5599999999999</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1871.1</v>
+        <v>1262.63</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-579.2</v>
+        <v>-676.0700000000001</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>-0.31</v>
+        <v>-0.535</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>501</v>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>0.4</v>
+        <v>6394</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>5.08</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
+          <t>📉 Demanda Normal</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr"/>
-      <c r="L41" s="13" t="inlineStr">
-        <is>
-          <t>NISSEI</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="n">
-        <v>1225.89</v>
-      </c>
+      <c r="L41" s="13" t="inlineStr"/>
+      <c r="M41" s="12" t="inlineStr"/>
       <c r="N41" s="14" t="inlineStr"/>
       <c r="O41" s="13" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Q41" s="15" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3092,54 +3092,50 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>10050639</t>
+          <t>10044745</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>EXTENSIOR 0,25MG+0,5MG 1,5ML NOVO EUROFARMA</t>
+          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
         </is>
       </c>
       <c r="D42" s="19" t="n">
-        <v>0</v>
+        <v>863.73</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>574.33</v>
+        <v>1520.64</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>-574.33</v>
+        <v>-656.91</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>-1</v>
+        <v>-0.4320000000000001</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>784</v>
-      </c>
-      <c r="I42" s="23" t="n">
-        <v>0.62</v>
+        <v>5858</v>
+      </c>
+      <c r="I42" s="29" t="n">
+        <v>4.65</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K42" s="19" t="n">
-        <v>955.85</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="inlineStr"/>
       <c r="L42" s="25" t="inlineStr">
         <is>
           <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M42" s="19" t="n">
-        <v>955.85</v>
-      </c>
-      <c r="N42" s="31" t="n">
-        <v>0</v>
-      </c>
+        <v>83.92</v>
+      </c>
+      <c r="N42" s="26" t="inlineStr"/>
       <c r="O42" s="25" t="inlineStr">
         <is>
-          <t>Preço Alinhado</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P42" s="25" t="inlineStr">
@@ -3149,7 +3145,7 @@
       </c>
       <c r="Q42" s="27" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3159,44 +3155,54 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>10046010</t>
+          <t>10050639</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS SUPERSEC MEGA M 40UN</t>
+          <t>EXTENSIOR 0,25MG+0,5MG 1,5ML NOVO EUROFARMA</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>540.66</v>
+        <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>1114.41</v>
+        <v>650.72</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-573.75</v>
+        <v>-650.72</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-0.515</v>
+        <v>-1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>6394</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>5.08</v>
+        <v>784</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>0.62</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K43" s="12" t="inlineStr"/>
-      <c r="L43" s="13" t="inlineStr"/>
-      <c r="M43" s="12" t="inlineStr"/>
-      <c r="N43" s="14" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>955.85</v>
+      </c>
+      <c r="L43" s="13" t="inlineStr">
+        <is>
+          <t>PREÇO POPULAR</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>955.85</v>
+      </c>
+      <c r="N43" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="O43" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>Preço Alinhado</t>
         </is>
       </c>
       <c r="P43" s="13" t="inlineStr">
@@ -3206,7 +3212,7 @@
       </c>
       <c r="Q43" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3216,46 +3222,40 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>10044745</t>
+          <t>10044679</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>NEXTELA 15MG+3MG 24+4CP REV LIBBS</t>
+          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
         </is>
       </c>
       <c r="D44" s="19" t="n">
-        <v>783.11</v>
+        <v>285.04</v>
       </c>
       <c r="E44" s="19" t="n">
-        <v>1342.13</v>
+        <v>929.73</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>-559.02</v>
+        <v>-644.6900000000001</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>-0.417</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>5858</v>
-      </c>
-      <c r="I44" s="29" t="n">
-        <v>4.65</v>
+        <v>324</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>0.26</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
+          <t>🚨 Ruptura Logística</t>
         </is>
       </c>
       <c r="K44" s="24" t="inlineStr"/>
-      <c r="L44" s="25" t="inlineStr">
-        <is>
-          <t>PREÇO POPULAR</t>
-        </is>
-      </c>
-      <c r="M44" s="19" t="n">
-        <v>83.92</v>
-      </c>
+      <c r="L44" s="25" t="inlineStr"/>
+      <c r="M44" s="24" t="inlineStr"/>
       <c r="N44" s="26" t="inlineStr"/>
       <c r="O44" s="25" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="Q44" s="27" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3279,31 +3279,31 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>100018652</t>
+          <t>10100048</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>OLEO BIO OIL 200ML PURCELLIN</t>
+          <t>RITALINA LA 10MG 30CP NOVARTIS (A3)</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0</v>
+        <v>454.25</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>552.4299999999999</v>
+        <v>1085.46</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-552.4299999999999</v>
+        <v>-631.21</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>-1</v>
+        <v>-0.5820000000000001</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>2638</v>
+        <v>3843</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -3311,18 +3311,18 @@
         </is>
       </c>
       <c r="K45" s="7" t="n">
-        <v>134.99</v>
+        <v>137.55</v>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
-        <v>67.19</v>
+        <v>120.9</v>
       </c>
       <c r="N45" s="32" t="n">
-        <v>1.009</v>
+        <v>0.138</v>
       </c>
       <c r="O45" s="13" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Amazon R$ 67.19)</t>
+          <t>Reprecificar no Digital (Farmaciasnissei R$ 120.90)</t>
         </is>
       </c>
     </row>
@@ -3346,50 +3346,54 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>10035972</t>
+          <t>100018652</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>CONDRES LONGBIO 90CAP EMS</t>
+          <t>OLEO BIO OIL 200ML PURCELLIN</t>
         </is>
       </c>
       <c r="D46" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="19" t="n">
-        <v>538.85</v>
+        <v>625.9</v>
       </c>
       <c r="F46" s="20" t="n">
-        <v>-538.85</v>
+        <v>-625.9</v>
       </c>
       <c r="G46" s="21" t="n">
         <v>-1</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>1136</v>
-      </c>
-      <c r="I46" s="23" t="n">
-        <v>0.9</v>
+        <v>2638</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>2.1</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K46" s="24" t="inlineStr"/>
+          <t>🏷️ Preço Desalinhado</t>
+        </is>
+      </c>
+      <c r="K46" s="19" t="n">
+        <v>134.99</v>
+      </c>
       <c r="L46" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M46" s="19" t="n">
-        <v>352.33</v>
-      </c>
-      <c r="N46" s="26" t="inlineStr"/>
+        <v>67.19</v>
+      </c>
+      <c r="N46" s="31" t="n">
+        <v>1.009</v>
+      </c>
       <c r="O46" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P46" s="25" t="inlineStr">
@@ -3397,9 +3401,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q46" s="27" t="inlineStr">
-        <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+      <c r="Q46" s="18" t="inlineStr">
+        <is>
+          <t>Reprecificar no Digital (Amazon R$ 67.19)</t>
         </is>
       </c>
     </row>
@@ -3409,31 +3413,31 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>10044679</t>
+          <t>10035972</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>LISDEV 70MG 30CAP REV MOMENTA (A3)</t>
+          <t>CONDRES LONGBIO 90CAP EMS</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>285.04</v>
+        <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>820.59</v>
+        <v>610.52</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-535.55</v>
+        <v>-610.52</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>-0.653</v>
+        <v>-1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>324</v>
+        <v>1136</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>0.26</v>
+        <v>0.9</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -3441,8 +3445,14 @@
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr"/>
-      <c r="L47" s="13" t="inlineStr"/>
-      <c r="M47" s="12" t="inlineStr"/>
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>NISSEI</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>352.33</v>
+      </c>
       <c r="N47" s="14" t="inlineStr"/>
       <c r="O47" s="13" t="inlineStr">
         <is>
@@ -3466,50 +3476,54 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>10089756</t>
+          <t>100001425</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>RITALINA 10MG 60CP NOVARTIS (A3)</t>
+          <t>ESCITALOPRAM 10MG 30CP REV GEN EMS (C1)</t>
         </is>
       </c>
       <c r="D48" s="19" t="n">
-        <v>81.95</v>
+        <v>429.49</v>
       </c>
       <c r="E48" s="19" t="n">
-        <v>607.67</v>
+        <v>1039.68</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>-525.72</v>
+        <v>-610.1900000000001</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>-0.865</v>
+        <v>-0.5870000000000001</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>7860</v>
+        <v>13421</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>6.24</v>
+        <v>10.66</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
           <t>📉 Demanda Normal</t>
         </is>
       </c>
-      <c r="K48" s="24" t="inlineStr"/>
+      <c r="K48" s="19" t="n">
+        <v>29.9</v>
+      </c>
       <c r="L48" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>PREÇO POPULAR</t>
         </is>
       </c>
       <c r="M48" s="19" t="n">
-        <v>92.95</v>
-      </c>
-      <c r="N48" s="26" t="inlineStr"/>
+        <v>28.9</v>
+      </c>
+      <c r="N48" s="31" t="n">
+        <v>0.035</v>
+      </c>
       <c r="O48" s="25" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P48" s="25" t="inlineStr">
@@ -3529,54 +3543,50 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>10032625</t>
+          <t>10089756</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>EXTRATO DE CANNABIS SATIVA 79,14MG 30ML MANTECORP (B1)</t>
+          <t>RITALINA 10MG 60CP NOVARTIS (A3)</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0</v>
+        <v>81.95</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>525.3200000000001</v>
+        <v>688.5</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-525.3200000000001</v>
+        <v>-606.55</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>-1</v>
+        <v>-0.8809999999999999</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>112</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>0.09</v>
+        <v>7860</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>6.24</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>🚨 Ruptura Logística</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>961.2</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr"/>
       <c r="L49" s="13" t="inlineStr">
         <is>
           <t>NISSEI</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
-        <v>925.9</v>
-      </c>
-      <c r="N49" s="32" t="n">
-        <v>0.038</v>
-      </c>
+        <v>92.95</v>
+      </c>
+      <c r="N49" s="14" t="inlineStr"/>
       <c r="O49" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P49" s="13" t="inlineStr">
@@ -3586,7 +3596,7 @@
       </c>
       <c r="Q49" s="15" t="inlineStr">
         <is>
-          <t>Abastecimento Emergencial Lojas/CD</t>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3596,31 +3606,31 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>10028272</t>
+          <t>10032625</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>MTOR 1G 90CP EUROFARMA</t>
+          <t>EXTRATO DE CANNABIS SATIVA 79,14MG 30ML MANTECORP (B1)</t>
         </is>
       </c>
       <c r="D50" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>520.78</v>
+        <v>595.1900000000001</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>-520.78</v>
+        <v>-595.1900000000001</v>
       </c>
       <c r="G50" s="21" t="n">
         <v>-1</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>1017</v>
+        <v>112</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -3628,18 +3638,18 @@
         </is>
       </c>
       <c r="K50" s="19" t="n">
-        <v>366.7</v>
+        <v>961.2</v>
       </c>
       <c r="L50" s="25" t="inlineStr">
         <is>
-          <t>PANVEL</t>
+          <t>NISSEI</t>
         </is>
       </c>
       <c r="M50" s="19" t="n">
-        <v>359.99</v>
-      </c>
-      <c r="N50" s="30" t="n">
-        <v>0.019</v>
+        <v>925.9</v>
+      </c>
+      <c r="N50" s="31" t="n">
+        <v>0.038</v>
       </c>
       <c r="O50" s="25" t="inlineStr">
         <is>
@@ -3663,44 +3673,54 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>10052535</t>
+          <t>10028272</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>FR PAMPERS CONFORTSEC BAG MAX G 92UN</t>
+          <t>MTOR 1G 90CP EUROFARMA</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1437.19</v>
+        <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>1954.72</v>
+        <v>590.05</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-517.53</v>
+        <v>-590.05</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-0.265</v>
+        <v>-1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>11106</v>
-      </c>
-      <c r="I51" s="28" t="n">
-        <v>8.82</v>
+        <v>1017</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>📉 Demanda Normal</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr"/>
-      <c r="L51" s="13" t="inlineStr"/>
-      <c r="M51" s="12" t="inlineStr"/>
-      <c r="N51" s="14" t="inlineStr"/>
+          <t>🚨 Ruptura Logística</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>366.7</v>
+      </c>
+      <c r="L51" s="13" t="inlineStr">
+        <is>
+          <t>PANVEL</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="N51" s="32" t="n">
+        <v>0.019</v>
+      </c>
       <c r="O51" s="13" t="inlineStr">
         <is>
-          <t>Não Monitorado</t>
+          <t>São João Mais Cara</t>
         </is>
       </c>
       <c r="P51" s="13" t="inlineStr">
@@ -3710,7 +3730,7 @@
       </c>
       <c r="Q51" s="15" t="inlineStr">
         <is>
-          <t>Ação Promocional / Destaque Home</t>
+          <t>Abastecimento Emergencial Lojas/CD</t>
         </is>
       </c>
     </row>
@@ -3720,31 +3740,31 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>10100048</t>
+          <t>10046754</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>RITALINA LA 10MG 30CP NOVARTIS (A3)</t>
+          <t>GINOBIOTTA 30CAP MARJAN</t>
         </is>
       </c>
       <c r="D52" s="19" t="n">
-        <v>454.25</v>
+        <v>175.9</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>958.04</v>
+        <v>764.88</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>-503.79</v>
+        <v>-588.98</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>-0.526</v>
+        <v>-0.77</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>3843</v>
+        <v>2137</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -3752,18 +3772,18 @@
         </is>
       </c>
       <c r="K52" s="19" t="n">
-        <v>137.55</v>
+        <v>193.6</v>
       </c>
       <c r="L52" s="25" t="inlineStr">
         <is>
-          <t>NISSEI</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="M52" s="19" t="n">
-        <v>120.9</v>
-      </c>
-      <c r="N52" s="30" t="n">
-        <v>0.138</v>
+        <v>165.59</v>
+      </c>
+      <c r="N52" s="31" t="n">
+        <v>0.169</v>
       </c>
       <c r="O52" s="25" t="inlineStr">
         <is>
@@ -3777,7 +3797,7 @@
       </c>
       <c r="Q52" s="18" t="inlineStr">
         <is>
-          <t>Reprecificar no Digital (Farmaciasnissei R$ 120.90)</t>
+          <t>Reprecificar no Digital (Amazon R$ 165.59)</t>
         </is>
       </c>
     </row>
@@ -3787,54 +3807,44 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>10046754</t>
+          <t>10037279</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>GINOBIOTTA 30CAP MARJAN</t>
+          <t>FR CAPRICHO BABY MEGA XXG 54UN</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>175.9</v>
+        <v>111.48</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>675.09</v>
+        <v>691.46</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-499.19</v>
+        <v>-579.98</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>-0.7390000000000001</v>
+        <v>-0.8390000000000001</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>2137</v>
+        <v>5320</v>
       </c>
       <c r="I53" s="28" t="n">
-        <v>1.7</v>
+        <v>4.23</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>🏷️ Preço Desalinhado</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>193.6</v>
-      </c>
-      <c r="L53" s="13" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
-        <v>165.59</v>
-      </c>
-      <c r="N53" s="32" t="n">
-        <v>0.169</v>
-      </c>
+          <t>📉 Demanda Normal</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr"/>
+      <c r="L53" s="13" t="inlineStr"/>
+      <c r="M53" s="12" t="inlineStr"/>
+      <c r="N53" s="14" t="inlineStr"/>
       <c r="O53" s="13" t="inlineStr">
         <is>
-          <t>São João Mais Cara</t>
+          <t>Não Monitorado</t>
         </is>
       </c>
       <c r="P53" s="13" t="inlineStr">
@@ -3842,9 +3852,9 @@
           <t>Neutro</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>Reprecificar no Digital (Amazon R$ 165.59)</t>
+      <c r="Q53" s="15" t="inlineStr">
+        <is>
+          <t>Ação Promocional / Destaque Home</t>
         </is>
       </c>
     </row>
@@ -3854,31 +3864,31 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>10037279</t>
+          <t>100008085</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>FR CAPRICHO BABY MEGA XXG 54UN</t>
+          <t>ELIQUIS 5MG 60TBS PFIZER</t>
         </is>
       </c>
       <c r="D54" s="19" t="n">
-        <v>111.48</v>
+        <v>421.98</v>
       </c>
       <c r="E54" s="19" t="n">
-        <v>610.29</v>
+        <v>993.61</v>
       </c>
       <c r="F54" s="20" t="n">
-        <v>-498.81</v>
+        <v>-571.63</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>-0.8170000000000001</v>
+        <v>-0.575</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>5320</v>
+        <v>2887</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>4.23</v>
+        <v>2.29</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>

--- a/data/Top_50_Detratores_Canais_Digitais.xlsx
+++ b/data/Top_50_Detratores_Canais_Digitais.xlsx
@@ -294,16 +294,16 @@
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -711,7 +711,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 19:53:25 (19:53) • Tríade Estoque x Preço x Demanda</t>
+          <t>Canais Digitais (App, Site, Marketplace) • Horário de Corte: 09/09/2026 20:53:49 (20:53) • Tríade Estoque x Preço x Demanda</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>11248.11</v>
+        <v>12367.83</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-11248.11</v>
+        <v>-12367.83</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>-1</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>7498.74</v>
+        <v>8245.219999999999</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>-7498.74</v>
+        <v>-8245.219999999999</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>-1</v>
@@ -923,31 +923,31 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>10033758</t>
+          <t>10028708</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>FR HUGGIES MAXIMA PROT HIPER XG 56UN</t>
+          <t>FR SAO JOAO BABY BAG XXG 56UN</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>758.9</v>
+        <v>581.92</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3663.96</v>
+        <v>3561.18</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-2905.06</v>
+        <v>-2979.26</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.7929999999999999</v>
+        <v>-0.8370000000000001</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>26223</v>
+        <v>39477</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>20.83</v>
+        <v>31.36</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -989,16 +989,16 @@
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>509.9</v>
+        <v>615.8</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>3258.48</v>
+        <v>3582.85</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>-2748.58</v>
+        <v>-2967.05</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>-0.8440000000000001</v>
+        <v>-0.828</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>3146</v>
@@ -1037,31 +1037,31 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10028708</t>
+          <t>10033758</t